--- a/data/sentiment/NAAIM Exposure Index.xlsx
+++ b/data/sentiment/NAAIM Exposure Index.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\sentiment\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/AlternativeData/data/sentiment/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07180AB7-4637-487E-BA5B-FFC6DA8225E3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C6E52A0-FBBE-7E45-ABDF-5E67A99EC317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="22605" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="16160" yWindow="780" windowWidth="19840" windowHeight="20700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NAAIM" sheetId="1" r:id="rId1"/>
@@ -70,29 +70,29 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="178" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="180" formatCode="0.00_ "/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="18"/>
       <color theme="3"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri Light"/>
       <family val="2"/>
       <scheme val="major"/>
     </font>
@@ -100,7 +100,7 @@
       <b/>
       <sz val="15"/>
       <color theme="3"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -108,7 +108,7 @@
       <b/>
       <sz val="13"/>
       <color theme="3"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -116,35 +116,35 @@
       <b/>
       <sz val="11"/>
       <color theme="3"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C5700"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -152,7 +152,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -160,14 +160,14 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -175,14 +175,14 @@
       <b/>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -190,7 +190,7 @@
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -198,20 +198,20 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -220,7 +220,7 @@
       <b/>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -228,7 +228,7 @@
       <b/>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -236,9 +236,17 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -539,7 +547,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="43">
+  <cellStyleXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
@@ -585,10 +593,11 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -598,65 +607,67 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="178" fontId="20" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="20" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="178" fontId="21" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="21" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="178" fontId="21" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="180" fontId="20" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="21" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="20" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="180" fontId="21" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="21" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="180" fontId="21" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="21" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="43"/>
   </cellXfs>
-  <cellStyles count="43">
-    <cellStyle name="20% - 강조색1" xfId="19" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20% - 강조색2" xfId="23" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20% - 강조색3" xfId="27" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20% - 강조색4" xfId="31" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20% - 강조색5" xfId="35" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20% - 강조색6" xfId="39" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="40% - 강조색1" xfId="20" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40% - 강조색2" xfId="24" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40% - 강조색3" xfId="28" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40% - 강조색4" xfId="32" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40% - 강조색5" xfId="36" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40% - 강조색6" xfId="40" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="60% - 강조색1" xfId="21" builtinId="32" customBuiltin="1"/>
-    <cellStyle name="60% - 강조색2" xfId="25" builtinId="36" customBuiltin="1"/>
-    <cellStyle name="60% - 강조색3" xfId="29" builtinId="40" customBuiltin="1"/>
-    <cellStyle name="60% - 강조색4" xfId="33" builtinId="44" customBuiltin="1"/>
-    <cellStyle name="60% - 강조색5" xfId="37" builtinId="48" customBuiltin="1"/>
-    <cellStyle name="60% - 강조색6" xfId="41" builtinId="52" customBuiltin="1"/>
-    <cellStyle name="강조색1" xfId="18" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="강조색2" xfId="22" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="강조색3" xfId="26" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="강조색4" xfId="30" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="강조색5" xfId="34" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="강조색6" xfId="38" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="경고문" xfId="14" builtinId="11" customBuiltin="1"/>
-    <cellStyle name="계산" xfId="11" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="나쁨" xfId="7" builtinId="27" customBuiltin="1"/>
-    <cellStyle name="메모" xfId="15" builtinId="10" customBuiltin="1"/>
-    <cellStyle name="보통" xfId="8" builtinId="28" customBuiltin="1"/>
-    <cellStyle name="설명 텍스트" xfId="16" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="셀 확인" xfId="13" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="쉼표" xfId="42" builtinId="3"/>
-    <cellStyle name="연결된 셀" xfId="12" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="요약" xfId="17" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="입력" xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="제목" xfId="1" builtinId="15" customBuiltin="1"/>
-    <cellStyle name="제목 1" xfId="2" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="제목 2" xfId="3" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="제목 3" xfId="4" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="제목 4" xfId="5" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="좋음" xfId="6" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="출력" xfId="10" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+  <cellStyles count="44">
+    <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - Accent4" xfId="31" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - Accent5" xfId="35" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - Accent6" xfId="39" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - Accent1" xfId="20" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - Accent2" xfId="24" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - Accent3" xfId="28" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - Accent4" xfId="32" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - Accent5" xfId="36" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - Accent6" xfId="40" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - Accent1" xfId="21" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - Accent2" xfId="25" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - Accent3" xfId="29" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - Accent4" xfId="33" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - Accent5" xfId="37" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - Accent6" xfId="41" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="Accent1" xfId="18" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="Accent2" xfId="22" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="Accent3" xfId="26" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Comma" xfId="42" builtinId="3"/>
+    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Hyperlink" xfId="43" builtinId="8"/>
+    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -672,9 +683,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -712,7 +723,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -818,7 +829,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -960,7 +971,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -968,22 +979,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I1019"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:I1020"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.5" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.5" style="1" customWidth="1"/>
-    <col min="3" max="3" width="8.125" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.1640625" style="6" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.375" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.33203125" style="6" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8" style="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.375" style="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.33203125" style="6" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11.5" style="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.625" style="6" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.875" style="3"/>
+    <col min="9" max="9" width="16.6640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.83203125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>11</v>
       </c>
@@ -1012,7 +1023,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>38903</v>
       </c>
@@ -1041,7 +1052,7 @@
         <v>55.55</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>38910</v>
       </c>
@@ -1070,7 +1081,7 @@
         <v>47.84</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>38903</v>
       </c>
@@ -1099,7 +1110,7 @@
         <v>55.549999722194443</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>38910</v>
       </c>
@@ -1128,7 +1139,7 @@
         <v>47.838896308338889</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>38917</v>
       </c>
@@ -1157,7 +1168,7 @@
         <v>38.170438823780898</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>38924</v>
       </c>
@@ -1186,7 +1197,7 @@
         <v>33.778460222455372</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>38931</v>
       </c>
@@ -1215,7 +1226,7 @@
         <v>43.692625871599382</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>38938</v>
       </c>
@@ -1244,7 +1255,7 @@
         <v>47.483927790753583</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>38945</v>
       </c>
@@ -1273,7 +1284,7 @@
         <v>56.524684873071166</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>38952</v>
       </c>
@@ -1302,7 +1313,7 @@
         <v>45.170475778833321</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>38959</v>
       </c>
@@ -1331,7 +1342,7 @@
         <v>45.170475778833321</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>38966</v>
       </c>
@@ -1360,7 +1371,7 @@
         <v>50.374290674884271</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>38973</v>
       </c>
@@ -1389,7 +1400,7 @@
         <v>56.228640389040173</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>38980</v>
       </c>
@@ -1418,7 +1429,7 @@
         <v>31.264996401726965</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>38987</v>
       </c>
@@ -1447,7 +1458,7 @@
         <v>55.807410979021469</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>38994</v>
       </c>
@@ -1476,7 +1487,7 @@
         <v>59.404629449227272</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <v>39001</v>
       </c>
@@ -1505,7 +1516,7 @@
         <v>59.825434763385545</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>39008</v>
       </c>
@@ -1534,7 +1545,7 @@
         <v>33.215082952435786</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <v>39015</v>
       </c>
@@ -1563,7 +1574,7 @@
         <v>53.121506002748077</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <v>39022</v>
       </c>
@@ -1592,7 +1603,7 @@
         <v>53.864396997357062</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <v>39029</v>
       </c>
@@ -1621,7 +1632,7 @@
         <v>46.653652879834993</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <v>39036</v>
       </c>
@@ -1650,7 +1661,7 @@
         <v>61.297793607386772</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <v>39043</v>
       </c>
@@ -1679,7 +1690,7 @@
         <v>20.824828195876073</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <v>39050</v>
       </c>
@@ -1708,7 +1719,7 @@
         <v>38.414042173363363</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <v>39057</v>
       </c>
@@ -1737,7 +1748,7 @@
         <v>58.029540018794734</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
         <v>39064</v>
       </c>
@@ -1766,7 +1777,7 @@
         <v>19.415261547359616</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
         <v>39071</v>
       </c>
@@ -1795,7 +1806,7 @@
         <v>22.354395725773102</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
         <v>39078</v>
       </c>
@@ -1824,7 +1835,7 @@
         <v>35.213204259954928</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
         <v>39085</v>
       </c>
@@ -1853,7 +1864,7 @@
         <v>32.236442245024186</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
         <v>39092</v>
       </c>
@@ -1882,7 +1893,7 @@
         <v>65.212862654704111</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
         <v>39099</v>
       </c>
@@ -1911,7 +1922,7 @@
         <v>27.899999503569333</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A33" s="1">
         <v>39106</v>
       </c>
@@ -1940,7 +1951,7 @@
         <v>42.723911860082509</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34" s="1">
         <v>39113</v>
       </c>
@@ -1969,7 +1980,7 @@
         <v>49.378006237595294</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A35" s="1">
         <v>39120</v>
       </c>
@@ -1998,7 +2009,7 @@
         <v>45.927163507298019</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A36" s="1">
         <v>39127</v>
       </c>
@@ -2027,7 +2038,7 @@
         <v>55.649805268718424</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A37" s="1">
         <v>39134</v>
       </c>
@@ -2056,7 +2067,7 @@
         <v>52.764818137257436</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A38" s="1">
         <v>39141</v>
       </c>
@@ -2085,7 +2096,7 @@
         <v>53.726231363347424</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A39" s="1">
         <v>39148</v>
       </c>
@@ -2114,7 +2125,7 @@
         <v>48.602880573068916</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A40" s="1">
         <v>39155</v>
       </c>
@@ -2143,7 +2154,7 @@
         <v>68.635171039352031</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A41" s="1">
         <v>39162</v>
       </c>
@@ -2172,7 +2183,7 @@
         <v>54.906588487696794</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A42" s="1">
         <v>39169</v>
       </c>
@@ -2201,7 +2212,7 @@
         <v>61.630606010506028</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A43" s="1">
         <v>39176</v>
       </c>
@@ -2230,7 +2241,7 @@
         <v>64.537968733792852</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A44" s="1">
         <v>39183</v>
       </c>
@@ -2259,7 +2270,7 @@
         <v>57.825060311252592</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A45" s="1">
         <v>39190</v>
       </c>
@@ -2288,7 +2299,7 @@
         <v>69.279479346364909</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A46" s="1">
         <v>39197</v>
       </c>
@@ -2317,7 +2328,7 @@
         <v>59.001416591157486</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A47" s="1">
         <v>39204</v>
       </c>
@@ -2346,7 +2357,7 @@
         <v>59.063995424924954</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A48" s="1">
         <v>39211</v>
       </c>
@@ -2375,7 +2386,7 @@
         <v>55.064860745205635</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A49" s="1">
         <v>39218</v>
       </c>
@@ -2404,7 +2415,7 @@
         <v>51.819247148139851</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A50" s="1">
         <v>39225</v>
       </c>
@@ -2433,7 +2444,7 @@
         <v>53.983793864455286</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A51" s="1">
         <v>39232</v>
       </c>
@@ -2462,7 +2473,7 @@
         <v>48.786852991286374</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A52" s="1">
         <v>39239</v>
       </c>
@@ -2491,7 +2502,7 @@
         <v>62.811083593759328</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A53" s="1">
         <v>39246</v>
       </c>
@@ -2520,7 +2531,7 @@
         <v>65.542340513594723</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A54" s="1">
         <v>39253</v>
       </c>
@@ -2549,7 +2560,7 @@
         <v>67.954431672633518</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A55" s="1">
         <v>39260</v>
       </c>
@@ -2578,7 +2589,7 @@
         <v>55.826175891531534</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A56" s="1">
         <v>39268</v>
       </c>
@@ -2607,7 +2618,7 @@
         <v>60.176790324426577</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A57" s="1">
         <v>39274</v>
       </c>
@@ -2636,7 +2647,7 @@
         <v>51.354938031690303</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A58" s="1">
         <v>39281</v>
       </c>
@@ -2665,7 +2676,7 @@
         <v>45.888802797874582</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A59" s="1">
         <v>39288</v>
       </c>
@@ -2694,7 +2705,7 @@
         <v>63.76609180512709</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A60" s="1">
         <v>39295</v>
       </c>
@@ -2723,7 +2734,7 @@
         <v>59.657354953098618</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A61" s="1">
         <v>39302</v>
       </c>
@@ -2752,7 +2763,7 @@
         <v>65.099669293697346</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A62" s="1">
         <v>39309</v>
       </c>
@@ -2781,7 +2792,7 @@
         <v>57.034529015325447</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A63" s="1">
         <v>39316</v>
       </c>
@@ -2810,7 +2821,7 @@
         <v>52.701658833000693</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A64" s="1">
         <v>39323</v>
       </c>
@@ -2839,7 +2850,7 @@
         <v>72.566359583555496</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A65" s="1">
         <v>39330</v>
       </c>
@@ -2868,7 +2879,7 @@
         <v>45.022968675258781</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A66" s="1">
         <v>39337</v>
       </c>
@@ -2897,7 +2908,7 @@
         <v>69.603104472428257</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A67" s="1">
         <v>39344</v>
       </c>
@@ -2926,7 +2937,7 @@
         <v>42.408304442812678</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A68" s="1">
         <v>39351</v>
       </c>
@@ -2955,7 +2966,7 @@
         <v>38.186796212286225</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A69" s="1">
         <v>39358</v>
       </c>
@@ -2984,7 +2995,7 @@
         <v>61.369548273391054</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A70" s="1">
         <v>39365</v>
       </c>
@@ -3013,7 +3024,7 @@
         <v>56.227919122877815</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A71" s="1">
         <v>39372</v>
       </c>
@@ -3042,7 +3053,7 @@
         <v>49.208363214031834</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A72" s="1">
         <v>39379</v>
       </c>
@@ -3071,7 +3082,7 @@
         <v>65.850867379966061</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A73" s="1">
         <v>39386</v>
       </c>
@@ -3100,7 +3111,7 @@
         <v>75.074716234904798</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A74" s="1">
         <v>39393</v>
       </c>
@@ -3129,7 +3140,7 @@
         <v>52.534527153195896</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A75" s="1">
         <v>39400</v>
       </c>
@@ -3158,7 +3169,7 @@
         <v>40.679745770792763</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A76" s="1">
         <v>39407</v>
       </c>
@@ -3187,7 +3198,7 @@
         <v>60.493442596881707</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A77" s="1">
         <v>39414</v>
       </c>
@@ -3216,7 +3227,7 @@
         <v>68.934714752142</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A78" s="1">
         <v>39421</v>
       </c>
@@ -3245,7 +3256,7 @@
         <v>60.536316005812211</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A79" s="1">
         <v>39428</v>
       </c>
@@ -3274,7 +3285,7 @@
         <v>69.021440028975547</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A80" s="1">
         <v>39435</v>
       </c>
@@ -3303,7 +3314,7 @@
         <v>71.467344717337483</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A81" s="1">
         <v>39442</v>
       </c>
@@ -3332,7 +3343,7 @@
         <v>50.496362770611753</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A82" s="1">
         <v>39449</v>
       </c>
@@ -3361,7 +3372,7 @@
         <v>55.229668567997003</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A83" s="1">
         <v>39456</v>
       </c>
@@ -3390,7 +3401,7 @@
         <v>75.139220764041383</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A84" s="1">
         <v>39463</v>
       </c>
@@ -3419,7 +3430,7 @@
         <v>58.387484404345059</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A85" s="1">
         <v>39470</v>
       </c>
@@ -3448,7 +3459,7 @@
         <v>74.040278246155765</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A86" s="1">
         <v>39477</v>
       </c>
@@ -3477,7 +3488,7 @@
         <v>62.164148383994373</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A87" s="1">
         <v>39484</v>
       </c>
@@ -3506,7 +3517,7 @@
         <v>70.447213919214661</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A88" s="1">
         <v>39491</v>
       </c>
@@ -3535,7 +3546,7 @@
         <v>74.676338659280532</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A89" s="1">
         <v>39498</v>
       </c>
@@ -3564,7 +3575,7 @@
         <v>57.328488167363666</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A90" s="1">
         <v>39505</v>
       </c>
@@ -3593,7 +3604,7 @@
         <v>82.926777823027351</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A91" s="1">
         <v>39512</v>
       </c>
@@ -3622,7 +3633,7 @@
         <v>56.330836013124284</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A92" s="1">
         <v>39519</v>
       </c>
@@ -3651,7 +3662,7 @@
         <v>63.152843166400672</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A93" s="1">
         <v>39526</v>
       </c>
@@ -3680,7 +3691,7 @@
         <v>44.173359780366653</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A94" s="1">
         <v>39533</v>
       </c>
@@ -3709,7 +3720,7 @@
         <v>69.09468937538611</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A95" s="1">
         <v>39540</v>
       </c>
@@ -3738,7 +3749,7 @@
         <v>72.946618726802328</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A96" s="1">
         <v>39547</v>
       </c>
@@ -3767,7 +3778,7 @@
         <v>69.469947459315094</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A97" s="1">
         <v>39554</v>
       </c>
@@ -3796,7 +3807,7 @@
         <v>56.323052699867915</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A98" s="1">
         <v>39561</v>
       </c>
@@ -3825,7 +3836,7 @@
         <v>41.974862158849767</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A99" s="1">
         <v>39569</v>
       </c>
@@ -3854,7 +3865,7 @@
         <v>44.962229438992097</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A100" s="1">
         <v>39575</v>
       </c>
@@ -3883,7 +3894,7 @@
         <v>37.798178950335576</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A101" s="1">
         <v>39582</v>
       </c>
@@ -3912,7 +3923,7 @@
         <v>68.460251596471679</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A102" s="1">
         <v>39589</v>
       </c>
@@ -3941,7 +3952,7 @@
         <v>65.70356446097523</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A103" s="1">
         <v>39596</v>
       </c>
@@ -3970,7 +3981,7 @@
         <v>66.213667550072984</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A104" s="1">
         <v>39603</v>
       </c>
@@ -3999,7 +4010,7 @@
         <v>65.788974489430842</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A105" s="1">
         <v>39610</v>
       </c>
@@ -4028,7 +4039,7 @@
         <v>78.830161121302538</v>
       </c>
     </row>
-    <row r="106" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A106" s="1">
         <v>39617</v>
       </c>
@@ -4057,7 +4068,7 @@
         <v>65.083754207393383</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A107" s="1">
         <v>39624</v>
       </c>
@@ -4086,7 +4097,7 @@
         <v>55.264758647687017</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A108" s="1">
         <v>39631</v>
       </c>
@@ -4115,7 +4126,7 @@
         <v>52.723327174933317</v>
       </c>
     </row>
-    <row r="109" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A109" s="1">
         <v>39638</v>
       </c>
@@ -4144,7 +4155,7 @@
         <v>75.848904583590468</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A110" s="1">
         <v>39645</v>
       </c>
@@ -4173,7 +4184,7 @@
         <v>51.278326455349131</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A111" s="1">
         <v>39652</v>
       </c>
@@ -4202,7 +4213,7 @@
         <v>57.909108469652679</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A112" s="1">
         <v>39659</v>
       </c>
@@ -4231,7 +4242,7 @@
         <v>61.750517406739192</v>
       </c>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A113" s="1">
         <v>39666</v>
       </c>
@@ -4260,7 +4271,7 @@
         <v>52.661575232504951</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A114" s="1">
         <v>39673</v>
       </c>
@@ -4289,7 +4300,7 @@
         <v>53.118250871076597</v>
       </c>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A115" s="1">
         <v>39681</v>
       </c>
@@ -4318,7 +4329,7 @@
         <v>50.104043997600584</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A116" s="1">
         <v>39687</v>
       </c>
@@ -4347,7 +4358,7 @@
         <v>50.177676148596895</v>
       </c>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A117" s="1">
         <v>39694</v>
       </c>
@@ -4376,7 +4387,7 @@
         <v>65.073504542370074</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A118" s="1">
         <v>39701</v>
       </c>
@@ -4405,7 +4416,7 @@
         <v>44.254182598587626</v>
       </c>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A119" s="1">
         <v>39708</v>
       </c>
@@ -4434,7 +4445,7 @@
         <v>47.422942867393644</v>
       </c>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A120" s="1">
         <v>39715</v>
       </c>
@@ -4463,7 +4474,7 @@
         <v>46.359571574198242</v>
       </c>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A121" s="1">
         <v>39722</v>
       </c>
@@ -4492,7 +4503,7 @@
         <v>33.405873873919091</v>
       </c>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A122" s="1">
         <v>39729</v>
       </c>
@@ -4521,7 +4532,7 @@
         <v>51.281080608690978</v>
       </c>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A123" s="1">
         <v>39736</v>
       </c>
@@ -4550,7 +4561,7 @@
         <v>40.551750201988128</v>
       </c>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A124" s="1">
         <v>39743</v>
       </c>
@@ -4579,7 +4590,7 @@
         <v>44.129844927173707</v>
       </c>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A125" s="1">
         <v>39750</v>
       </c>
@@ -4608,7 +4619,7 @@
         <v>53.882588406027168</v>
       </c>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A126" s="1">
         <v>39757</v>
       </c>
@@ -4637,7 +4648,7 @@
         <v>49.886350075701394</v>
       </c>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A127" s="1">
         <v>39764</v>
       </c>
@@ -4666,7 +4677,7 @@
         <v>44.405800463275128</v>
       </c>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A128" s="1">
         <v>39771</v>
       </c>
@@ -4695,7 +4706,7 @@
         <v>43.976952126529874</v>
       </c>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A129" s="1">
         <v>39778</v>
       </c>
@@ -4724,7 +4735,7 @@
         <v>57.854397526301433</v>
       </c>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A130" s="1">
         <v>39785</v>
       </c>
@@ -4753,7 +4764,7 @@
         <v>45.357327933111691</v>
       </c>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A131" s="1">
         <v>39792</v>
       </c>
@@ -4782,7 +4793,7 @@
         <v>49.214072926201013</v>
       </c>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A132" s="1">
         <v>39799</v>
       </c>
@@ -4811,7 +4822,7 @@
         <v>53.491406900967732</v>
       </c>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A133" s="1">
         <v>39806</v>
       </c>
@@ -4840,7 +4851,7 @@
         <v>55.286482576750558</v>
       </c>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A134" s="1">
         <v>39813</v>
       </c>
@@ -4869,7 +4880,7 @@
         <v>55.143723549589758</v>
       </c>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A135" s="1">
         <v>39820</v>
       </c>
@@ -4898,7 +4909,7 @@
         <v>51.012811516083978</v>
       </c>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A136" s="1">
         <v>39827</v>
       </c>
@@ -4927,7 +4938,7 @@
         <v>64.584992254313974</v>
       </c>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A137" s="1">
         <v>39834</v>
       </c>
@@ -4956,7 +4967,7 @@
         <v>51.036330889936345</v>
       </c>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A138" s="1">
         <v>39841</v>
       </c>
@@ -4985,7 +4996,7 @@
         <v>49.006860617093729</v>
       </c>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A139" s="1">
         <v>39848</v>
       </c>
@@ -5014,7 +5025,7 @@
         <v>33.08758938678627</v>
       </c>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A140" s="1">
         <v>39855</v>
       </c>
@@ -5043,7 +5054,7 @@
         <v>42.688334209137516</v>
       </c>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A141" s="1">
         <v>39862</v>
       </c>
@@ -5072,7 +5083,7 @@
         <v>49.836210913235156</v>
       </c>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A142" s="1">
         <v>39869</v>
       </c>
@@ -5101,7 +5112,7 @@
         <v>46.376897362766087</v>
       </c>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A143" s="1">
         <v>39876</v>
       </c>
@@ -5130,7 +5141,7 @@
         <v>48.797982331083887</v>
       </c>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A144" s="1">
         <v>39883</v>
       </c>
@@ -5159,7 +5170,7 @@
         <v>50.995285896575474</v>
       </c>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A145" s="1">
         <v>39890</v>
       </c>
@@ -5188,7 +5199,7 @@
         <v>50.632752300623871</v>
       </c>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A146" s="1">
         <v>39897</v>
       </c>
@@ -5217,7 +5228,7 @@
         <v>49.159815906896966</v>
       </c>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A147" s="1">
         <v>39904</v>
       </c>
@@ -5246,7 +5257,7 @@
         <v>67.93322071407249</v>
       </c>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A148" s="1">
         <v>39911</v>
       </c>
@@ -5275,7 +5286,7 @@
         <v>59.144140747470985</v>
       </c>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A149" s="1">
         <v>39918</v>
       </c>
@@ -5304,7 +5315,7 @@
         <v>48.417328037810883</v>
       </c>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A150" s="1">
         <v>39925</v>
       </c>
@@ -5333,7 +5344,7 @@
         <v>65.507189828231219</v>
       </c>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A151" s="1">
         <v>39932</v>
       </c>
@@ -5362,7 +5373,7 @@
         <v>67.77459535800439</v>
       </c>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A152" s="1">
         <v>39939</v>
       </c>
@@ -5391,7 +5402,7 @@
         <v>67.144419826628891</v>
       </c>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A153" s="1">
         <v>39946</v>
       </c>
@@ -5420,7 +5431,7 @@
         <v>50.709106035336958</v>
       </c>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A154" s="1">
         <v>39953</v>
       </c>
@@ -5449,7 +5460,7 @@
         <v>45.673803993182069</v>
       </c>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A155" s="1">
         <v>39960</v>
       </c>
@@ -5478,7 +5489,7 @@
         <v>56.578290137928242</v>
       </c>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A156" s="1">
         <v>39967</v>
       </c>
@@ -5507,7 +5518,7 @@
         <v>65.158129608233793</v>
       </c>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A157" s="1">
         <v>39974</v>
       </c>
@@ -5536,7 +5547,7 @@
         <v>44.471505975736868</v>
       </c>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A158" s="1">
         <v>39981</v>
       </c>
@@ -5565,7 +5576,7 @@
         <v>52.627079222161107</v>
       </c>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A159" s="1">
         <v>39988</v>
       </c>
@@ -5594,7 +5605,7 @@
         <v>66.261051954921754</v>
       </c>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A160" s="1">
         <v>39995</v>
       </c>
@@ -5623,7 +5634,7 @@
         <v>54.893058424976317</v>
       </c>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A161" s="1">
         <v>40002</v>
       </c>
@@ -5652,7 +5663,7 @@
         <v>64.161205849108597</v>
       </c>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A162" s="1">
         <v>40009</v>
       </c>
@@ -5681,7 +5692,7 @@
         <v>52.811235830415114</v>
       </c>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A163" s="1">
         <v>40016</v>
       </c>
@@ -5710,7 +5721,7 @@
         <v>57.645867319279404</v>
       </c>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A164" s="1">
         <v>40023</v>
       </c>
@@ -5739,7 +5750,7 @@
         <v>61.365403956693434</v>
       </c>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A165" s="1">
         <v>40030</v>
       </c>
@@ -5768,7 +5779,7 @@
         <v>44.582988427682338</v>
       </c>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A166" s="1">
         <v>40037</v>
       </c>
@@ -5797,7 +5808,7 @@
         <v>54.166951121047973</v>
       </c>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A167" s="1">
         <v>40044</v>
       </c>
@@ -5826,7 +5837,7 @@
         <v>76.385981144531414</v>
       </c>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A168" s="1">
         <v>40051</v>
       </c>
@@ -5855,7 +5866,7 @@
         <v>71.141667275747665</v>
       </c>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A169" s="1">
         <v>40058</v>
       </c>
@@ -5884,7 +5895,7 @@
         <v>81.41339889263179</v>
       </c>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A170" s="1">
         <v>40065</v>
       </c>
@@ -5913,7 +5924,7 @@
         <v>63.355150657102897</v>
       </c>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A171" s="1">
         <v>40072</v>
       </c>
@@ -5942,7 +5953,7 @@
         <v>63.586872250336747</v>
       </c>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A172" s="1">
         <v>40079</v>
       </c>
@@ -5971,7 +5982,7 @@
         <v>53.318827599106207</v>
       </c>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A173" s="1">
         <v>40086</v>
       </c>
@@ -6000,7 +6011,7 @@
         <v>49.477873007591704</v>
       </c>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A174" s="1">
         <v>40093</v>
       </c>
@@ -6029,7 +6040,7 @@
         <v>71.403538470599969</v>
       </c>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A175" s="1">
         <v>40100</v>
       </c>
@@ -6058,7 +6069,7 @@
         <v>61.732827908030352</v>
       </c>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A176" s="1">
         <v>40107</v>
       </c>
@@ -6087,7 +6098,7 @@
         <v>52.229993511604249</v>
       </c>
     </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A177" s="1">
         <v>40114</v>
       </c>
@@ -6116,7 +6127,7 @@
         <v>64.598575021541549</v>
       </c>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A178" s="1">
         <v>40121</v>
       </c>
@@ -6145,7 +6156,7 @@
         <v>61.131436014016572</v>
       </c>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A179" s="1">
         <v>40128</v>
       </c>
@@ -6174,7 +6185,7 @@
         <v>53.907207534999003</v>
       </c>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A180" s="1">
         <v>40135</v>
       </c>
@@ -6203,7 +6214,7 @@
         <v>44.756939056977522</v>
       </c>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A181" s="1">
         <v>40142</v>
       </c>
@@ -6232,7 +6243,7 @@
         <v>56.685418081441156</v>
       </c>
     </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A182" s="1">
         <v>40149</v>
       </c>
@@ -6261,7 +6272,7 @@
         <v>49.326994067650219</v>
       </c>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A183" s="1">
         <v>40156</v>
       </c>
@@ -6290,7 +6301,7 @@
         <v>56.94789248873581</v>
       </c>
     </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A184" s="1">
         <v>40163</v>
       </c>
@@ -6319,7 +6330,7 @@
         <v>53.684534257154517</v>
       </c>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A185" s="1">
         <v>40170</v>
       </c>
@@ -6348,7 +6359,7 @@
         <v>65.364947708147739</v>
       </c>
     </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A186" s="1">
         <v>40177</v>
       </c>
@@ -6377,7 +6388,7 @@
         <v>53.704634029690361</v>
       </c>
     </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A187" s="1">
         <v>40184</v>
       </c>
@@ -6406,7 +6417,7 @@
         <v>54.771375546492628</v>
       </c>
     </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A188" s="1">
         <v>40191</v>
       </c>
@@ -6435,7 +6446,7 @@
         <v>57.833752535015343</v>
       </c>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A189" s="1">
         <v>40198</v>
       </c>
@@ -6464,7 +6475,7 @@
         <v>79.252584956089748</v>
       </c>
     </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A190" s="1">
         <v>40205</v>
       </c>
@@ -6493,7 +6504,7 @@
         <v>66.112908932661171</v>
       </c>
     </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A191" s="1">
         <v>40212</v>
       </c>
@@ -6522,7 +6533,7 @@
         <v>68.480905740352668</v>
       </c>
     </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A192" s="1">
         <v>40219</v>
       </c>
@@ -6551,7 +6562,7 @@
         <v>68.820680112015253</v>
       </c>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A193" s="1">
         <v>40226</v>
       </c>
@@ -6580,7 +6591,7 @@
         <v>59.032374376182737</v>
       </c>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A194" s="1">
         <v>40233</v>
       </c>
@@ -6609,7 +6620,7 @@
         <v>60.995325657513426</v>
       </c>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A195" s="1">
         <v>40240</v>
       </c>
@@ -6638,7 +6649,7 @@
         <v>61.01651833892263</v>
       </c>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A196" s="1">
         <v>40247</v>
       </c>
@@ -6667,7 +6678,7 @@
         <v>68.948409164893818</v>
       </c>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A197" s="1">
         <v>40254</v>
       </c>
@@ -6696,7 +6707,7 @@
         <v>55.495282272042076</v>
       </c>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A198" s="1">
         <v>40261</v>
       </c>
@@ -6725,7 +6736,7 @@
         <v>57.756350696573961</v>
       </c>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A199" s="1">
         <v>40268</v>
       </c>
@@ -6754,7 +6765,7 @@
         <v>46.374631010759359</v>
       </c>
     </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A200" s="1">
         <v>40275</v>
       </c>
@@ -6783,7 +6794,7 @@
         <v>50.035497779699199</v>
       </c>
     </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A201" s="1">
         <v>40282</v>
       </c>
@@ -6812,7 +6823,7 @@
         <v>45.14920394961522</v>
       </c>
     </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A202" s="1">
         <v>40289</v>
       </c>
@@ -6841,7 +6852,7 @@
         <v>42.330808834030208</v>
       </c>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A203" s="1">
         <v>40296</v>
       </c>
@@ -6870,7 +6881,7 @@
         <v>46.031147244235598</v>
       </c>
     </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A204" s="1">
         <v>40303</v>
       </c>
@@ -6899,7 +6910,7 @@
         <v>73.783147168729855</v>
       </c>
     </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A205" s="1">
         <v>40310</v>
       </c>
@@ -6928,7 +6939,7 @@
         <v>67.420059029224618</v>
       </c>
     </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A206" s="1">
         <v>40317</v>
       </c>
@@ -6957,7 +6968,7 @@
         <v>65.236302377809508</v>
       </c>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A207" s="1">
         <v>40324</v>
       </c>
@@ -6986,7 +6997,7 @@
         <v>45.438603264918548</v>
       </c>
     </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A208" s="1">
         <v>40331</v>
       </c>
@@ -7015,7 +7026,7 @@
         <v>55.842613656597415</v>
       </c>
     </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A209" s="1">
         <v>40338</v>
       </c>
@@ -7044,7 +7055,7 @@
         <v>50.566226976684703</v>
       </c>
     </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A210" s="1">
         <v>40345</v>
       </c>
@@ -7073,7 +7084,7 @@
         <v>60.167993983512531</v>
       </c>
     </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A211" s="1">
         <v>40352</v>
       </c>
@@ -7102,7 +7113,7 @@
         <v>59.384867216709665</v>
       </c>
     </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A212" s="1">
         <v>40359</v>
       </c>
@@ -7131,7 +7142,7 @@
         <v>51.877165703250242</v>
       </c>
     </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A213" s="1">
         <v>40366</v>
       </c>
@@ -7160,7 +7171,7 @@
         <v>60.791159694094574</v>
       </c>
     </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A214" s="1">
         <v>40373</v>
       </c>
@@ -7189,7 +7200,7 @@
         <v>52.381556868806406</v>
       </c>
     </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A215" s="1">
         <v>40380</v>
       </c>
@@ -7218,7 +7229,7 @@
         <v>55.497901708236633</v>
       </c>
     </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A216" s="1">
         <v>40387</v>
       </c>
@@ -7247,7 +7258,7 @@
         <v>63.648541403343927</v>
       </c>
     </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A217" s="1">
         <v>40394</v>
       </c>
@@ -7276,7 +7287,7 @@
         <v>58.51627398414611</v>
       </c>
     </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A218" s="1">
         <v>40401</v>
       </c>
@@ -7305,7 +7316,7 @@
         <v>70.168158657672691</v>
       </c>
     </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A219" s="1">
         <v>40408</v>
       </c>
@@ -7334,7 +7345,7 @@
         <v>53.947041077312385</v>
       </c>
     </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A220" s="1">
         <v>40415</v>
       </c>
@@ -7363,7 +7374,7 @@
         <v>55.908131213647891</v>
       </c>
     </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A221" s="1">
         <v>40422</v>
       </c>
@@ -7392,7 +7403,7 @@
         <v>62.564187638553811</v>
       </c>
     </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A222" s="1">
         <v>40429</v>
       </c>
@@ -7421,7 +7432,7 @@
         <v>72.423309874299363</v>
       </c>
     </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A223" s="1">
         <v>40436</v>
       </c>
@@ -7450,7 +7461,7 @@
         <v>73.388746907379783</v>
       </c>
     </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A224" s="1">
         <v>40443</v>
       </c>
@@ -7479,7 +7490,7 @@
         <v>74.427829003026858</v>
       </c>
     </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A225" s="1">
         <v>40450</v>
       </c>
@@ -7508,7 +7519,7 @@
         <v>65.974731715358232</v>
       </c>
     </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A226" s="1">
         <v>40457</v>
       </c>
@@ -7537,7 +7548,7 @@
         <v>59.692906241492011</v>
       </c>
     </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A227" s="1">
         <v>40464</v>
       </c>
@@ -7566,7 +7577,7 @@
         <v>55.007204521826623</v>
       </c>
     </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A228" s="1">
         <v>40471</v>
       </c>
@@ -7595,7 +7606,7 @@
         <v>54.037281159418455</v>
       </c>
     </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A229" s="1">
         <v>40478</v>
       </c>
@@ -7624,7 +7635,7 @@
         <v>74.053447495288836</v>
       </c>
     </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A230" s="1">
         <v>40485</v>
       </c>
@@ -7653,7 +7664,7 @@
         <v>57.599139747516887</v>
       </c>
     </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A231" s="1">
         <v>40493</v>
       </c>
@@ -7682,7 +7693,7 @@
         <v>73.628931758084974</v>
       </c>
     </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A232" s="1">
         <v>40499</v>
       </c>
@@ -7711,7 +7722,7 @@
         <v>64.712269652083734</v>
       </c>
     </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A233" s="1">
         <v>40506</v>
       </c>
@@ -7740,7 +7751,7 @@
         <v>68.728127833919316</v>
       </c>
     </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A234" s="1">
         <v>40513</v>
       </c>
@@ -7769,7 +7780,7 @@
         <v>71.396578703865657</v>
       </c>
     </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A235" s="1">
         <v>40520</v>
       </c>
@@ -7798,7 +7809,7 @@
         <v>56.848732557127434</v>
       </c>
     </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A236" s="1">
         <v>40527</v>
       </c>
@@ -7827,7 +7838,7 @@
         <v>48.876462768440668</v>
       </c>
     </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A237" s="1">
         <v>40534</v>
       </c>
@@ -7856,7 +7867,7 @@
         <v>30.939366105335772</v>
       </c>
     </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A238" s="1">
         <v>40541</v>
       </c>
@@ -7885,7 +7896,7 @@
         <v>25.867679114547297</v>
       </c>
     </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A239" s="1">
         <v>40548</v>
       </c>
@@ -7914,7 +7925,7 @@
         <v>35.99596195192472</v>
       </c>
     </row>
-    <row r="240" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A240" s="1">
         <v>40555</v>
       </c>
@@ -7943,7 +7954,7 @@
         <v>34.5248029413723</v>
       </c>
     </row>
-    <row r="241" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A241" s="1">
         <v>40562</v>
       </c>
@@ -7972,7 +7983,7 @@
         <v>48.204614903131251</v>
       </c>
     </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A242" s="1">
         <v>40569</v>
       </c>
@@ -8001,7 +8012,7 @@
         <v>44.563550516112116</v>
       </c>
     </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A243" s="1">
         <v>40576</v>
       </c>
@@ -8030,7 +8041,7 @@
         <v>37.30092994819298</v>
       </c>
     </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A244" s="1">
         <v>40583</v>
       </c>
@@ -8059,7 +8070,7 @@
         <v>36.241942484664484</v>
       </c>
     </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A245" s="1">
         <v>40590</v>
       </c>
@@ -8088,7 +8099,7 @@
         <v>39.530799594711759</v>
       </c>
     </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A246" s="1">
         <v>40597</v>
       </c>
@@ -8117,7 +8128,7 @@
         <v>53.939404659302646</v>
       </c>
     </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A247" s="1">
         <v>40604</v>
       </c>
@@ -8146,7 +8157,7 @@
         <v>43.942750002449529</v>
       </c>
     </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A248" s="1">
         <v>40611</v>
       </c>
@@ -8175,7 +8186,7 @@
         <v>34.894786457057684</v>
       </c>
     </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A249" s="1">
         <v>40618</v>
       </c>
@@ -8204,7 +8215,7 @@
         <v>64.316923641190016</v>
       </c>
     </row>
-    <row r="250" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A250" s="1">
         <v>40625</v>
       </c>
@@ -8233,7 +8244,7 @@
         <v>54.669969412425644</v>
       </c>
     </row>
-    <row r="251" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A251" s="1">
         <v>40632</v>
       </c>
@@ -8262,7 +8273,7 @@
         <v>33.436812839822487</v>
       </c>
     </row>
-    <row r="252" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A252" s="1">
         <v>40639</v>
       </c>
@@ -8291,7 +8302,7 @@
         <v>39.172313642501635</v>
       </c>
     </row>
-    <row r="253" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A253" s="1">
         <v>40646</v>
       </c>
@@ -8320,7 +8331,7 @@
         <v>38.729050102374607</v>
       </c>
     </row>
-    <row r="254" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A254" s="1">
         <v>40653</v>
       </c>
@@ -8349,7 +8360,7 @@
         <v>41.715563146345993</v>
       </c>
     </row>
-    <row r="255" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A255" s="1">
         <v>40660</v>
       </c>
@@ -8378,7 +8389,7 @@
         <v>43.741742077791095</v>
       </c>
     </row>
-    <row r="256" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A256" s="1">
         <v>40667</v>
       </c>
@@ -8407,7 +8418,7 @@
         <v>47.873989122981456</v>
       </c>
     </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A257" s="1">
         <v>40674</v>
       </c>
@@ -8436,7 +8447,7 @@
         <v>51.779665709540218</v>
       </c>
     </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A258" s="1">
         <v>40681</v>
       </c>
@@ -8465,7 +8476,7 @@
         <v>57.023035358289334</v>
       </c>
     </row>
-    <row r="259" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A259" s="1">
         <v>40688</v>
       </c>
@@ -8494,7 +8505,7 @@
         <v>56.87088409797628</v>
       </c>
     </row>
-    <row r="260" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A260" s="1">
         <v>40695</v>
       </c>
@@ -8523,7 +8534,7 @@
         <v>47.063569688632143</v>
       </c>
     </row>
-    <row r="261" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A261" s="1">
         <v>40702</v>
       </c>
@@ -8552,7 +8563,7 @@
         <v>58.561562455438484</v>
       </c>
     </row>
-    <row r="262" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A262" s="1">
         <v>40709</v>
       </c>
@@ -8581,7 +8592,7 @@
         <v>54.876464024706216</v>
       </c>
     </row>
-    <row r="263" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A263" s="1">
         <v>40716</v>
       </c>
@@ -8610,7 +8621,7 @@
         <v>48.129506282529015</v>
       </c>
     </row>
-    <row r="264" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A264" s="1">
         <v>40723</v>
       </c>
@@ -8639,7 +8650,7 @@
         <v>53.998865301934728</v>
       </c>
     </row>
-    <row r="265" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A265" s="1">
         <v>40730</v>
       </c>
@@ -8668,7 +8679,7 @@
         <v>57.89850820929329</v>
       </c>
     </row>
-    <row r="266" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A266" s="1">
         <v>40737</v>
       </c>
@@ -8697,7 +8708,7 @@
         <v>53.479549570113456</v>
       </c>
     </row>
-    <row r="267" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A267" s="1">
         <v>40744</v>
       </c>
@@ -8726,7 +8737,7 @@
         <v>49.79143878947302</v>
       </c>
     </row>
-    <row r="268" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A268" s="1">
         <v>40751</v>
       </c>
@@ -8755,7 +8766,7 @@
         <v>42.651475813694034</v>
       </c>
     </row>
-    <row r="269" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A269" s="1">
         <v>40758</v>
       </c>
@@ -8784,7 +8795,7 @@
         <v>50.439188817558389</v>
       </c>
     </row>
-    <row r="270" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A270" s="1">
         <v>40765</v>
       </c>
@@ -8813,7 +8824,7 @@
         <v>42.049324508367285</v>
       </c>
     </row>
-    <row r="271" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A271" s="1">
         <v>40772</v>
       </c>
@@ -8842,7 +8853,7 @@
         <v>47.516027185636773</v>
       </c>
     </row>
-    <row r="272" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A272" s="1">
         <v>40779</v>
       </c>
@@ -8871,7 +8882,7 @@
         <v>40.399772058656886</v>
       </c>
     </row>
-    <row r="273" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A273" s="1">
         <v>40786</v>
       </c>
@@ -8900,7 +8911,7 @@
         <v>44.783201620610939</v>
       </c>
     </row>
-    <row r="274" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A274" s="1">
         <v>40793</v>
       </c>
@@ -8929,7 +8940,7 @@
         <v>46.854774319627346</v>
       </c>
     </row>
-    <row r="275" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A275" s="1">
         <v>40800</v>
       </c>
@@ -8958,7 +8969,7 @@
         <v>50.572231681862235</v>
       </c>
     </row>
-    <row r="276" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A276" s="1">
         <v>40807</v>
       </c>
@@ -8987,7 +8998,7 @@
         <v>51.000097894093308</v>
       </c>
     </row>
-    <row r="277" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A277" s="1">
         <v>40814</v>
       </c>
@@ -9016,7 +9027,7 @@
         <v>38.969787977354969</v>
       </c>
     </row>
-    <row r="278" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A278" s="1">
         <v>40821</v>
       </c>
@@ -9045,7 +9056,7 @@
         <v>54.517864058372737</v>
       </c>
     </row>
-    <row r="279" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A279" s="1">
         <v>40828</v>
       </c>
@@ -9074,7 +9085,7 @@
         <v>58.875398087826127</v>
       </c>
     </row>
-    <row r="280" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A280" s="1">
         <v>40835</v>
       </c>
@@ -9103,7 +9114,7 @@
         <v>40.918862469344425</v>
       </c>
     </row>
-    <row r="281" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A281" s="1">
         <v>40842</v>
       </c>
@@ -9132,7 +9143,7 @@
         <v>45.233867381064172</v>
       </c>
     </row>
-    <row r="282" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A282" s="1">
         <v>40849</v>
       </c>
@@ -9161,7 +9172,7 @@
         <v>55.320831293464849</v>
       </c>
     </row>
-    <row r="283" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A283" s="1">
         <v>40856</v>
       </c>
@@ -9190,7 +9201,7 @@
         <v>55.690513263814637</v>
       </c>
     </row>
-    <row r="284" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A284" s="1">
         <v>40863</v>
       </c>
@@ -9219,7 +9230,7 @@
         <v>51.999145292121014</v>
       </c>
     </row>
-    <row r="285" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A285" s="1">
         <v>40870</v>
       </c>
@@ -9248,7 +9259,7 @@
         <v>45.873095396241652</v>
       </c>
     </row>
-    <row r="286" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A286" s="1">
         <v>40877</v>
       </c>
@@ -9277,7 +9288,7 @@
         <v>42.216169288999922</v>
       </c>
     </row>
-    <row r="287" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A287" s="1">
         <v>40884</v>
       </c>
@@ -9306,7 +9317,7 @@
         <v>43.664531422515303</v>
       </c>
     </row>
-    <row r="288" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A288" s="1">
         <v>40891</v>
       </c>
@@ -9335,7 +9346,7 @@
         <v>48.198670933439651</v>
       </c>
     </row>
-    <row r="289" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A289" s="1">
         <v>40898</v>
       </c>
@@ -9364,7 +9375,7 @@
         <v>39.516792034075834</v>
       </c>
     </row>
-    <row r="290" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A290" s="1">
         <v>40905</v>
       </c>
@@ -9393,7 +9404,7 @@
         <v>28.563193765273795</v>
       </c>
     </row>
-    <row r="291" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A291" s="1">
         <v>40912</v>
       </c>
@@ -9422,7 +9433,7 @@
         <v>41.403003244764143</v>
       </c>
     </row>
-    <row r="292" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A292" s="1">
         <v>40919</v>
       </c>
@@ -9451,7 +9462,7 @@
         <v>47.072652594140706</v>
       </c>
     </row>
-    <row r="293" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A293" s="1">
         <v>40926</v>
       </c>
@@ -9480,7 +9491,7 @@
         <v>49.053078858054825</v>
       </c>
     </row>
-    <row r="294" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A294" s="1">
         <v>40933</v>
       </c>
@@ -9509,7 +9520,7 @@
         <v>53.510954226421923</v>
       </c>
     </row>
-    <row r="295" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A295" s="1">
         <v>40940</v>
       </c>
@@ -9538,7 +9549,7 @@
         <v>39.384750530886507</v>
       </c>
     </row>
-    <row r="296" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A296" s="1">
         <v>40947</v>
       </c>
@@ -9567,7 +9578,7 @@
         <v>36.817697808266423</v>
       </c>
     </row>
-    <row r="297" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A297" s="1">
         <v>40954</v>
       </c>
@@ -9596,7 +9607,7 @@
         <v>36.233572758862671</v>
       </c>
     </row>
-    <row r="298" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A298" s="1">
         <v>40961</v>
       </c>
@@ -9625,7 +9636,7 @@
         <v>37.171889580703322</v>
       </c>
     </row>
-    <row r="299" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A299" s="1">
         <v>40968</v>
       </c>
@@ -9654,7 +9665,7 @@
         <v>36.759941210655207</v>
       </c>
     </row>
-    <row r="300" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A300" s="1">
         <v>40975</v>
       </c>
@@ -9683,7 +9694,7 @@
         <v>56.661237586866619</v>
       </c>
     </row>
-    <row r="301" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A301" s="1">
         <v>40982</v>
       </c>
@@ -9712,7 +9723,7 @@
         <v>47.798457305394521</v>
       </c>
     </row>
-    <row r="302" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A302" s="1">
         <v>40989</v>
       </c>
@@ -9741,7 +9752,7 @@
         <v>47.064324329465158</v>
       </c>
     </row>
-    <row r="303" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A303" s="1">
         <v>40996</v>
       </c>
@@ -9770,7 +9781,7 @@
         <v>40.595204301061202</v>
       </c>
     </row>
-    <row r="304" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A304" s="1">
         <v>41003</v>
       </c>
@@ -9799,7 +9810,7 @@
         <v>38.549937035348876</v>
       </c>
     </row>
-    <row r="305" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A305" s="1">
         <v>41010</v>
       </c>
@@ -9828,7 +9839,7 @@
         <v>53.214477468494394</v>
       </c>
     </row>
-    <row r="306" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A306" s="1">
         <v>41017</v>
       </c>
@@ -9857,7 +9868,7 @@
         <v>56.900572530695925</v>
       </c>
     </row>
-    <row r="307" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A307" s="1">
         <v>41024</v>
       </c>
@@ -9886,7 +9897,7 @@
         <v>56.771006536281874</v>
       </c>
     </row>
-    <row r="308" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A308" s="1">
         <v>41031</v>
       </c>
@@ -9915,7 +9926,7 @@
         <v>50.543476884317684</v>
       </c>
     </row>
-    <row r="309" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A309" s="1">
         <v>41038</v>
       </c>
@@ -9944,7 +9955,7 @@
         <v>54.137497957615317</v>
       </c>
     </row>
-    <row r="310" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A310" s="1">
         <v>41045</v>
       </c>
@@ -9973,7 +9984,7 @@
         <v>41.363917899541384</v>
       </c>
     </row>
-    <row r="311" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A311" s="1">
         <v>41052</v>
       </c>
@@ -10002,7 +10013,7 @@
         <v>45.49777201728218</v>
       </c>
     </row>
-    <row r="312" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A312" s="1">
         <v>41059</v>
       </c>
@@ -10031,7 +10042,7 @@
         <v>46.729614872834489</v>
       </c>
     </row>
-    <row r="313" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A313" s="1">
         <v>41066</v>
       </c>
@@ -10060,7 +10071,7 @@
         <v>34.956741028578463</v>
       </c>
     </row>
-    <row r="314" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A314" s="1">
         <v>41073</v>
       </c>
@@ -10089,7 +10100,7 @@
         <v>29.532500348198187</v>
       </c>
     </row>
-    <row r="315" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A315" s="1">
         <v>41080</v>
       </c>
@@ -10118,7 +10129,7 @@
         <v>45.65945115969452</v>
       </c>
     </row>
-    <row r="316" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A316" s="1">
         <v>41087</v>
       </c>
@@ -10147,7 +10158,7 @@
         <v>48.136271215938542</v>
       </c>
     </row>
-    <row r="317" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A317" s="1">
         <v>41095</v>
       </c>
@@ -10176,7 +10187,7 @@
         <v>49.207476611003706</v>
       </c>
     </row>
-    <row r="318" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A318" s="1">
         <v>41101</v>
       </c>
@@ -10205,7 +10216,7 @@
         <v>53.618962087056566</v>
       </c>
     </row>
-    <row r="319" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A319" s="1">
         <v>41108</v>
       </c>
@@ -10234,7 +10245,7 @@
         <v>52.76407806027715</v>
       </c>
     </row>
-    <row r="320" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A320" s="1">
         <v>41115</v>
       </c>
@@ -10263,7 +10274,7 @@
         <v>50.011052339523104</v>
       </c>
     </row>
-    <row r="321" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A321" s="1">
         <v>41122</v>
       </c>
@@ -10292,7 +10303,7 @@
         <v>53.937797639233743</v>
       </c>
     </row>
-    <row r="322" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A322" s="1">
         <v>41129</v>
       </c>
@@ -10321,7 +10332,7 @@
         <v>39.420666681528402</v>
       </c>
     </row>
-    <row r="323" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A323" s="1">
         <v>41136</v>
       </c>
@@ -10350,7 +10361,7 @@
         <v>42.597308792434582</v>
       </c>
     </row>
-    <row r="324" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A324" s="1">
         <v>41143</v>
       </c>
@@ -10379,7 +10390,7 @@
         <v>59.566739758018073</v>
       </c>
     </row>
-    <row r="325" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A325" s="1">
         <v>41150</v>
       </c>
@@ -10408,7 +10419,7 @@
         <v>40.667483971490398</v>
       </c>
     </row>
-    <row r="326" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A326" s="1">
         <v>41157</v>
       </c>
@@ -10437,7 +10448,7 @@
         <v>50.154861297471179</v>
       </c>
     </row>
-    <row r="327" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A327" s="1">
         <v>41164</v>
       </c>
@@ -10466,7 +10477,7 @@
         <v>50.124976846592538</v>
       </c>
     </row>
-    <row r="328" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A328" s="1">
         <v>41171</v>
       </c>
@@ -10495,7 +10506,7 @@
         <v>52.943578895895669</v>
       </c>
     </row>
-    <row r="329" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A329" s="1">
         <v>41178</v>
       </c>
@@ -10524,7 +10535,7 @@
         <v>56.021511245433409</v>
       </c>
     </row>
-    <row r="330" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A330" s="1">
         <v>41185</v>
       </c>
@@ -10553,7 +10564,7 @@
         <v>57.266397751374981</v>
       </c>
     </row>
-    <row r="331" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A331" s="1">
         <v>41192</v>
       </c>
@@ -10582,7 +10593,7 @@
         <v>66.483484497561491</v>
       </c>
     </row>
-    <row r="332" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A332" s="1">
         <v>41199</v>
       </c>
@@ -10611,7 +10622,7 @@
         <v>71.777760309165402</v>
       </c>
     </row>
-    <row r="333" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A333" s="1">
         <v>41206</v>
       </c>
@@ -10640,7 +10651,7 @@
         <v>59.778361750310793</v>
       </c>
     </row>
-    <row r="334" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A334" s="1">
         <v>41213</v>
       </c>
@@ -10669,7 +10680,7 @@
         <v>59.216704581992914</v>
       </c>
     </row>
-    <row r="335" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A335" s="1">
         <v>41220</v>
       </c>
@@ -10698,7 +10709,7 @@
         <v>57.538374466714032</v>
       </c>
     </row>
-    <row r="336" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A336" s="1">
         <v>41227</v>
       </c>
@@ -10727,7 +10738,7 @@
         <v>64.794060427377659</v>
       </c>
     </row>
-    <row r="337" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A337" s="1">
         <v>41234</v>
       </c>
@@ -10756,7 +10767,7 @@
         <v>42.978585224257763</v>
       </c>
     </row>
-    <row r="338" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A338" s="1">
         <v>41241</v>
       </c>
@@ -10785,7 +10796,7 @@
         <v>58.262610437726366</v>
       </c>
     </row>
-    <row r="339" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A339" s="1">
         <v>41248</v>
       </c>
@@ -10814,7 +10825,7 @@
         <v>53.947354080111261</v>
       </c>
     </row>
-    <row r="340" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A340" s="1">
         <v>41255</v>
       </c>
@@ -10843,7 +10854,7 @@
         <v>40.867278029986856</v>
       </c>
     </row>
-    <row r="341" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A341" s="1">
         <v>41262</v>
       </c>
@@ -10872,7 +10883,7 @@
         <v>49.812955030683419</v>
       </c>
     </row>
-    <row r="342" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A342" s="1">
         <v>41269</v>
       </c>
@@ -10901,7 +10912,7 @@
         <v>44.510630134900872</v>
       </c>
     </row>
-    <row r="343" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A343" s="1">
         <v>41276</v>
       </c>
@@ -10930,7 +10941,7 @@
         <v>53.24693033779436</v>
       </c>
     </row>
-    <row r="344" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A344" s="1">
         <v>41283</v>
       </c>
@@ -10959,7 +10970,7 @@
         <v>43.585114686349307</v>
       </c>
     </row>
-    <row r="345" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A345" s="1">
         <v>41290</v>
       </c>
@@ -10988,7 +10999,7 @@
         <v>60.84780147014353</v>
       </c>
     </row>
-    <row r="346" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A346" s="1">
         <v>41297</v>
       </c>
@@ -11017,7 +11028,7 @@
         <v>53.953140270861297</v>
       </c>
     </row>
-    <row r="347" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A347" s="1">
         <v>41304</v>
       </c>
@@ -11046,7 +11057,7 @@
         <v>32.239533185206014</v>
       </c>
     </row>
-    <row r="348" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A348" s="1">
         <v>41311</v>
       </c>
@@ -11075,7 +11086,7 @@
         <v>40.084712867791588</v>
       </c>
     </row>
-    <row r="349" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A349" s="1">
         <v>41318</v>
       </c>
@@ -11104,7 +11115,7 @@
         <v>38.38710256166938</v>
       </c>
     </row>
-    <row r="350" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A350" s="1">
         <v>41325</v>
       </c>
@@ -11133,7 +11144,7 @@
         <v>38.080293444545788</v>
       </c>
     </row>
-    <row r="351" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A351" s="1">
         <v>41332</v>
       </c>
@@ -11162,7 +11173,7 @@
         <v>48.402767285139547</v>
       </c>
     </row>
-    <row r="352" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A352" s="1">
         <v>41339</v>
       </c>
@@ -11191,7 +11202,7 @@
         <v>40.094000618700669</v>
       </c>
     </row>
-    <row r="353" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A353" s="1">
         <v>41346</v>
       </c>
@@ -11220,7 +11231,7 @@
         <v>42.821783159517786</v>
       </c>
     </row>
-    <row r="354" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A354" s="1">
         <v>41353</v>
       </c>
@@ -11249,7 +11260,7 @@
         <v>32.607118719705234</v>
       </c>
     </row>
-    <row r="355" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A355" s="1">
         <v>41360</v>
       </c>
@@ -11278,7 +11289,7 @@
         <v>40.659143503192773</v>
       </c>
     </row>
-    <row r="356" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A356" s="1">
         <v>41367</v>
       </c>
@@ -11307,7 +11318,7 @@
         <v>61.567550890600387</v>
       </c>
     </row>
-    <row r="357" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A357" s="1">
         <v>41374</v>
       </c>
@@ -11336,7 +11347,7 @@
         <v>52.116557963159231</v>
       </c>
     </row>
-    <row r="358" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A358" s="1">
         <v>41381</v>
       </c>
@@ -11365,7 +11376,7 @@
         <v>53.354057268656028</v>
       </c>
     </row>
-    <row r="359" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A359" s="1">
         <v>41388</v>
       </c>
@@ -11394,7 +11405,7 @@
         <v>58.802213497238505</v>
       </c>
     </row>
-    <row r="360" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A360" s="1">
         <v>41395</v>
       </c>
@@ -11423,7 +11434,7 @@
         <v>37.937705662389739</v>
       </c>
     </row>
-    <row r="361" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A361" s="1">
         <v>41402</v>
       </c>
@@ -11452,7 +11463,7 @@
         <v>54.929642662956802</v>
       </c>
     </row>
-    <row r="362" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A362" s="1">
         <v>41409</v>
       </c>
@@ -11481,7 +11492,7 @@
         <v>35.515606966366008</v>
       </c>
     </row>
-    <row r="363" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A363" s="1">
         <v>41416</v>
       </c>
@@ -11510,7 +11521,7 @@
         <v>47.22321621646487</v>
       </c>
     </row>
-    <row r="364" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A364" s="1">
         <v>41423</v>
       </c>
@@ -11539,7 +11550,7 @@
         <v>58.20055953610327</v>
       </c>
     </row>
-    <row r="365" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A365" s="1">
         <v>41430</v>
       </c>
@@ -11568,7 +11579,7 @@
         <v>58.972667790307163</v>
       </c>
     </row>
-    <row r="366" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A366" s="1">
         <v>41437</v>
       </c>
@@ -11597,7 +11608,7 @@
         <v>54.209657868522129</v>
       </c>
     </row>
-    <row r="367" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A367" s="1">
         <v>41444</v>
       </c>
@@ -11626,7 +11637,7 @@
         <v>49.424558707629132</v>
       </c>
     </row>
-    <row r="368" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A368" s="1">
         <v>41451</v>
       </c>
@@ -11655,7 +11666,7 @@
         <v>49.303982121743722</v>
       </c>
     </row>
-    <row r="369" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A369" s="1">
         <v>41458</v>
       </c>
@@ -11684,7 +11695,7 @@
         <v>35.218787549159295</v>
       </c>
     </row>
-    <row r="370" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A370" s="1">
         <v>41465</v>
       </c>
@@ -11713,7 +11724,7 @@
         <v>55.882367115793201</v>
       </c>
     </row>
-    <row r="371" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A371" s="1">
         <v>41472</v>
       </c>
@@ -11742,7 +11753,7 @@
         <v>53.110925423170286</v>
       </c>
     </row>
-    <row r="372" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A372" s="1">
         <v>41479</v>
       </c>
@@ -11771,7 +11782,7 @@
         <v>33.44447705914984</v>
       </c>
     </row>
-    <row r="373" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A373" s="1">
         <v>41486</v>
       </c>
@@ -11800,7 +11811,7 @@
         <v>54.484641664282961</v>
       </c>
     </row>
-    <row r="374" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A374" s="1">
         <v>41493</v>
       </c>
@@ -11829,7 +11840,7 @@
         <v>30.238330855873073</v>
       </c>
     </row>
-    <row r="375" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A375" s="1">
         <v>41500</v>
       </c>
@@ -11858,7 +11869,7 @@
         <v>42.699029269899285</v>
       </c>
     </row>
-    <row r="376" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A376" s="1">
         <v>41507</v>
       </c>
@@ -11887,7 +11898,7 @@
         <v>56.528524201883307</v>
       </c>
     </row>
-    <row r="377" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A377" s="1">
         <v>41514</v>
       </c>
@@ -11916,7 +11927,7 @@
         <v>45.736639980287038</v>
       </c>
     </row>
-    <row r="378" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A378" s="1">
         <v>41521</v>
       </c>
@@ -11945,7 +11956,7 @@
         <v>44.32004194458554</v>
       </c>
     </row>
-    <row r="379" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A379" s="1">
         <v>41528</v>
       </c>
@@ -11974,7 +11985,7 @@
         <v>31.097341411399512</v>
       </c>
     </row>
-    <row r="380" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A380" s="1">
         <v>41535</v>
       </c>
@@ -12003,7 +12014,7 @@
         <v>32.054779929422871</v>
       </c>
     </row>
-    <row r="381" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A381" s="1">
         <v>41542</v>
       </c>
@@ -12032,7 +12043,7 @@
         <v>48.279990820009985</v>
       </c>
     </row>
-    <row r="382" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A382" s="1">
         <v>41549</v>
       </c>
@@ -12061,7 +12072,7 @@
         <v>55.268275006754301</v>
       </c>
     </row>
-    <row r="383" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A383" s="1">
         <v>41556</v>
       </c>
@@ -12090,7 +12101,7 @@
         <v>64.648358122534788</v>
       </c>
     </row>
-    <row r="384" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A384" s="1">
         <v>41563</v>
       </c>
@@ -12119,7 +12130,7 @@
         <v>30.40107245824677</v>
       </c>
     </row>
-    <row r="385" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A385" s="1">
         <v>41570</v>
       </c>
@@ -12148,7 +12159,7 @@
         <v>46.050815851660722</v>
       </c>
     </row>
-    <row r="386" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A386" s="1">
         <v>41577</v>
       </c>
@@ -12177,7 +12188,7 @@
         <v>29.663869105622428</v>
       </c>
     </row>
-    <row r="387" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A387" s="1">
         <v>41584</v>
       </c>
@@ -12206,7 +12217,7 @@
         <v>29.763192589775961</v>
       </c>
     </row>
-    <row r="388" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A388" s="1">
         <v>41591</v>
       </c>
@@ -12235,7 +12246,7 @@
         <v>53.718056830358535</v>
       </c>
     </row>
-    <row r="389" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A389" s="1">
         <v>41598</v>
       </c>
@@ -12264,7 +12275,7 @@
         <v>47.320660371123139</v>
       </c>
     </row>
-    <row r="390" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A390" s="1">
         <v>41605</v>
       </c>
@@ -12293,7 +12304,7 @@
         <v>26.84883647436958</v>
       </c>
     </row>
-    <row r="391" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A391" s="1">
         <v>41612</v>
       </c>
@@ -12322,7 +12333,7 @@
         <v>30.228012575603316</v>
       </c>
     </row>
-    <row r="392" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A392" s="1">
         <v>41619</v>
       </c>
@@ -12351,7 +12362,7 @@
         <v>35.628299402813028</v>
       </c>
     </row>
-    <row r="393" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A393" s="1">
         <v>41626</v>
       </c>
@@ -12380,7 +12391,7 @@
         <v>29.564716897124189</v>
       </c>
     </row>
-    <row r="394" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A394" s="1">
         <v>41634</v>
       </c>
@@ -12409,7 +12420,7 @@
         <v>25.48504766173663</v>
       </c>
     </row>
-    <row r="395" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A395" s="1">
         <v>41641</v>
       </c>
@@ -12438,7 +12449,7 @@
         <v>29.440463564644233</v>
       </c>
     </row>
-    <row r="396" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A396" s="1">
         <v>41647</v>
       </c>
@@ -12467,7 +12478,7 @@
         <v>36.868005424758209</v>
       </c>
     </row>
-    <row r="397" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A397" s="1">
         <v>41654</v>
       </c>
@@ -12496,7 +12507,7 @@
         <v>33.543405654015224</v>
       </c>
     </row>
-    <row r="398" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A398" s="1">
         <v>41661</v>
       </c>
@@ -12525,7 +12536,7 @@
         <v>33.281205492789098</v>
       </c>
     </row>
-    <row r="399" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A399" s="1">
         <v>41668</v>
       </c>
@@ -12554,7 +12565,7 @@
         <v>48.6755678567065</v>
       </c>
     </row>
-    <row r="400" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A400" s="1">
         <v>41675</v>
       </c>
@@ -12583,7 +12594,7 @@
         <v>48.899855436252473</v>
       </c>
     </row>
-    <row r="401" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A401" s="1">
         <v>41682</v>
       </c>
@@ -12612,7 +12623,7 @@
         <v>50.456539714887306</v>
       </c>
     </row>
-    <row r="402" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A402" s="1">
         <v>41689</v>
       </c>
@@ -12641,7 +12652,7 @@
         <v>53.893528968558918</v>
       </c>
     </row>
-    <row r="403" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A403" s="1">
         <v>41696</v>
       </c>
@@ -12670,7 +12681,7 @@
         <v>32.173253175865931</v>
       </c>
     </row>
-    <row r="404" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A404" s="1">
         <v>41703</v>
       </c>
@@ -12699,7 +12710,7 @@
         <v>28.177917475995674</v>
       </c>
     </row>
-    <row r="405" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A405" s="1">
         <v>41710</v>
       </c>
@@ -12728,7 +12739,7 @@
         <v>38.591960706244812</v>
       </c>
     </row>
-    <row r="406" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A406" s="1">
         <v>41716</v>
       </c>
@@ -12757,7 +12768,7 @@
         <v>62.434033436115925</v>
       </c>
     </row>
-    <row r="407" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A407" s="1">
         <v>41717</v>
       </c>
@@ -12786,7 +12797,7 @@
         <v>38.474239554033893</v>
       </c>
     </row>
-    <row r="408" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A408" s="1">
         <v>41724</v>
       </c>
@@ -12815,7 +12826,7 @@
         <v>30.022064656219442</v>
       </c>
     </row>
-    <row r="409" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A409" s="1">
         <v>41731</v>
       </c>
@@ -12844,7 +12855,7 @@
         <v>44.188138476313277</v>
       </c>
     </row>
-    <row r="410" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A410" s="1">
         <v>41738</v>
       </c>
@@ -12873,7 +12884,7 @@
         <v>31.323363729632899</v>
       </c>
     </row>
-    <row r="411" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A411" s="1">
         <v>41745</v>
       </c>
@@ -12902,7 +12913,7 @@
         <v>35.606324792337006</v>
       </c>
     </row>
-    <row r="412" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A412" s="1">
         <v>41752</v>
       </c>
@@ -12931,7 +12942,7 @@
         <v>35.382781553838939</v>
       </c>
     </row>
-    <row r="413" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A413" s="1">
         <v>41759</v>
       </c>
@@ -12960,7 +12971,7 @@
         <v>45.803062444786249</v>
       </c>
     </row>
-    <row r="414" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A414" s="1">
         <v>41766</v>
       </c>
@@ -12989,7 +13000,7 @@
         <v>37.395218193640751</v>
       </c>
     </row>
-    <row r="415" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A415" s="1">
         <v>41773</v>
       </c>
@@ -13018,7 +13029,7 @@
         <v>30.364171137854051</v>
       </c>
     </row>
-    <row r="416" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A416" s="1">
         <v>41780</v>
       </c>
@@ -13047,7 +13058,7 @@
         <v>46.926276851752007</v>
       </c>
     </row>
-    <row r="417" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A417" s="1">
         <v>41787</v>
       </c>
@@ -13076,7 +13087,7 @@
         <v>56.381294114615542</v>
       </c>
     </row>
-    <row r="418" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A418" s="1">
         <v>41794</v>
       </c>
@@ -13105,7 +13116,7 @@
         <v>42.349237020811792</v>
       </c>
     </row>
-    <row r="419" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A419" s="1">
         <v>41801</v>
       </c>
@@ -13134,7 +13145,7 @@
         <v>38.373204647880215</v>
       </c>
     </row>
-    <row r="420" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A420" s="1">
         <v>41808</v>
       </c>
@@ -13163,7 +13174,7 @@
         <v>44.314119769408713</v>
       </c>
     </row>
-    <row r="421" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A421" s="1">
         <v>41815</v>
       </c>
@@ -13192,7 +13203,7 @@
         <v>60.45119572753616</v>
       </c>
     </row>
-    <row r="422" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A422" s="1">
         <v>41822</v>
       </c>
@@ -13221,7 +13232,7 @@
         <v>47.49836466704955</v>
       </c>
     </row>
-    <row r="423" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A423" s="1">
         <v>41829</v>
       </c>
@@ -13250,7 +13261,7 @@
         <v>35.064608489041966</v>
       </c>
     </row>
-    <row r="424" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A424" s="1">
         <v>41836</v>
       </c>
@@ -13279,7 +13290,7 @@
         <v>44.721213423875326</v>
       </c>
     </row>
-    <row r="425" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A425" s="1">
         <v>41843</v>
       </c>
@@ -13308,7 +13319,7 @@
         <v>39.312318980389804</v>
       </c>
     </row>
-    <row r="426" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A426" s="1">
         <v>41850</v>
       </c>
@@ -13337,7 +13348,7 @@
         <v>34.47072790576</v>
       </c>
     </row>
-    <row r="427" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A427" s="1">
         <v>41857</v>
       </c>
@@ -13366,7 +13377,7 @@
         <v>51.803015068152312</v>
       </c>
     </row>
-    <row r="428" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A428" s="1">
         <v>41864</v>
       </c>
@@ -13395,7 +13406,7 @@
         <v>45.922649241726944</v>
       </c>
     </row>
-    <row r="429" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A429" s="1">
         <v>41871</v>
       </c>
@@ -13424,7 +13435,7 @@
         <v>62.557833587887913</v>
       </c>
     </row>
-    <row r="430" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A430" s="1">
         <v>41878</v>
       </c>
@@ -13453,7 +13464,7 @@
         <v>47.65914443041865</v>
       </c>
     </row>
-    <row r="431" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A431" s="1">
         <v>41885</v>
       </c>
@@ -13482,7 +13493,7 @@
         <v>59.213557190072954</v>
       </c>
     </row>
-    <row r="432" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A432" s="1">
         <v>41892</v>
       </c>
@@ -13511,7 +13522,7 @@
         <v>57.333019762644675</v>
       </c>
     </row>
-    <row r="433" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A433" s="1">
         <v>41899</v>
       </c>
@@ -13540,7 +13551,7 @@
         <v>49.133395431991111</v>
       </c>
     </row>
-    <row r="434" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A434" s="1">
         <v>41906</v>
       </c>
@@ -13569,7 +13580,7 @@
         <v>55.537677707137746</v>
       </c>
     </row>
-    <row r="435" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A435" s="1">
         <v>41913</v>
       </c>
@@ -13598,7 +13609,7 @@
         <v>66.806525599248758</v>
       </c>
     </row>
-    <row r="436" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A436" s="1">
         <v>41920</v>
       </c>
@@ -13627,7 +13638,7 @@
         <v>66.570355280429666</v>
       </c>
     </row>
-    <row r="437" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A437" s="1">
         <v>41927</v>
       </c>
@@ -13656,7 +13667,7 @@
         <v>67.686973863523022</v>
       </c>
     </row>
-    <row r="438" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A438" s="1">
         <v>41934</v>
       </c>
@@ -13685,7 +13696,7 @@
         <v>62.311923006128566</v>
       </c>
     </row>
-    <row r="439" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A439" s="1">
         <v>41941</v>
       </c>
@@ -13714,7 +13725,7 @@
         <v>65.532799765784759</v>
       </c>
     </row>
-    <row r="440" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A440" s="1">
         <v>41948</v>
       </c>
@@ -13743,7 +13754,7 @@
         <v>62.905619401035253</v>
       </c>
     </row>
-    <row r="441" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A441" s="1">
         <v>41955</v>
       </c>
@@ -13772,7 +13783,7 @@
         <v>59.753766943925129</v>
       </c>
     </row>
-    <row r="442" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A442" s="1">
         <v>41962</v>
       </c>
@@ -13801,7 +13812,7 @@
         <v>54.685208883890532</v>
       </c>
     </row>
-    <row r="443" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A443" s="1">
         <v>41968</v>
       </c>
@@ -13830,7 +13841,7 @@
         <v>64.443637389582548</v>
       </c>
     </row>
-    <row r="444" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A444" s="1">
         <v>41976</v>
       </c>
@@ -13859,7 +13870,7 @@
         <v>53.372403786390393</v>
       </c>
     </row>
-    <row r="445" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A445" s="1">
         <v>41983</v>
       </c>
@@ -13888,7 +13899,7 @@
         <v>52.550400098141971</v>
       </c>
     </row>
-    <row r="446" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A446" s="1">
         <v>41990</v>
       </c>
@@ -13917,7 +13928,7 @@
         <v>61.82397380318033</v>
       </c>
     </row>
-    <row r="447" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A447" s="1">
         <v>41997</v>
       </c>
@@ -13946,7 +13957,7 @@
         <v>32.707053916439136</v>
       </c>
     </row>
-    <row r="448" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A448" s="1">
         <v>42004</v>
       </c>
@@ -13975,7 +13986,7 @@
         <v>43.310807829305034</v>
       </c>
     </row>
-    <row r="449" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A449" s="1">
         <v>42011</v>
       </c>
@@ -14004,7 +14015,7 @@
         <v>73.520753699141281</v>
       </c>
     </row>
-    <row r="450" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A450" s="1">
         <v>42018</v>
       </c>
@@ -14033,7 +14044,7 @@
         <v>53.380532408043727</v>
       </c>
     </row>
-    <row r="451" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A451" s="1">
         <v>42025</v>
       </c>
@@ -14062,7 +14073,7 @@
         <v>52.550400098141971</v>
       </c>
     </row>
-    <row r="452" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A452" s="1">
         <v>42032</v>
       </c>
@@ -14091,7 +14102,7 @@
         <v>39.19736690032088</v>
       </c>
     </row>
-    <row r="453" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A453" s="1">
         <v>42039</v>
       </c>
@@ -14120,7 +14131,7 @@
         <v>44.064003122982612</v>
       </c>
     </row>
-    <row r="454" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A454" s="1">
         <v>42046</v>
       </c>
@@ -14149,7 +14160,7 @@
         <v>37.007673607771878</v>
       </c>
     </row>
-    <row r="455" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A455" s="1">
         <v>42053</v>
       </c>
@@ -14178,7 +14189,7 @@
         <v>42.561466476456637</v>
       </c>
     </row>
-    <row r="456" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A456" s="1">
         <v>42060</v>
       </c>
@@ -14207,7 +14218,7 @@
         <v>45.402755221031484</v>
       </c>
     </row>
-    <row r="457" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A457" s="1">
         <v>42067</v>
       </c>
@@ -14236,7 +14247,7 @@
         <v>48.211272729748821</v>
       </c>
     </row>
-    <row r="458" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A458" s="1">
         <v>42074</v>
       </c>
@@ -14265,7 +14276,7 @@
         <v>67.383421717313624</v>
       </c>
     </row>
-    <row r="459" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A459" s="1">
         <v>42088</v>
       </c>
@@ -14294,7 +14305,7 @@
         <v>30.956834906605707</v>
       </c>
     </row>
-    <row r="460" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A460" s="1">
         <v>42095</v>
       </c>
@@ -14323,7 +14334,7 @@
         <v>54.500081021599833</v>
       </c>
     </row>
-    <row r="461" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A461" s="1">
         <v>42102</v>
       </c>
@@ -14352,7 +14363,7 @@
         <v>28.291363992271719</v>
       </c>
     </row>
-    <row r="462" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A462" s="1">
         <v>42109</v>
       </c>
@@ -14381,7 +14392,7 @@
         <v>40.543750857694739</v>
       </c>
     </row>
-    <row r="463" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A463" s="1">
         <v>42116</v>
       </c>
@@ -14410,7 +14421,7 @@
         <v>59.571201699918042</v>
       </c>
     </row>
-    <row r="464" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A464" s="1">
         <v>42123</v>
       </c>
@@ -14439,7 +14450,7 @@
         <v>34.27313982014654</v>
       </c>
     </row>
-    <row r="465" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A465" s="1">
         <v>42130</v>
       </c>
@@ -14468,7 +14479,7 @@
         <v>56.955691995283715</v>
       </c>
     </row>
-    <row r="466" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A466" s="1">
         <v>42137</v>
       </c>
@@ -14497,7 +14508,7 @@
         <v>54.764046582566408</v>
       </c>
     </row>
-    <row r="467" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A467" s="1">
         <v>42144</v>
       </c>
@@ -14526,7 +14537,7 @@
         <v>55.757136500127764</v>
       </c>
     </row>
-    <row r="468" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A468" s="1">
         <v>42151</v>
       </c>
@@ -14555,7 +14566,7 @@
         <v>59.139689894729841</v>
       </c>
     </row>
-    <row r="469" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A469" s="1">
         <v>42158</v>
       </c>
@@ -14584,7 +14595,7 @@
         <v>58.565690013670491</v>
       </c>
     </row>
-    <row r="470" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A470" s="1">
         <v>42165</v>
       </c>
@@ -14613,7 +14624,7 @@
         <v>58.285726582262178</v>
       </c>
     </row>
-    <row r="471" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A471" s="1">
         <v>42172</v>
       </c>
@@ -14642,7 +14653,7 @@
         <v>51.057335391353512</v>
       </c>
     </row>
-    <row r="472" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A472" s="1">
         <v>42179</v>
       </c>
@@ -14671,7 +14682,7 @@
         <v>58.045476963818579</v>
       </c>
     </row>
-    <row r="473" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A473" s="1">
         <v>42186</v>
       </c>
@@ -14700,7 +14711,7 @@
         <v>60.134571875867529</v>
       </c>
     </row>
-    <row r="474" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A474" s="1">
         <v>42193</v>
       </c>
@@ -14729,7 +14740,7 @@
         <v>64.152197101026005</v>
       </c>
     </row>
-    <row r="475" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A475" s="1">
         <v>42200</v>
       </c>
@@ -14758,7 +14769,7 @@
         <v>62.876249643492336</v>
       </c>
     </row>
-    <row r="476" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A476" s="1">
         <v>42207</v>
       </c>
@@ -14787,7 +14798,7 @@
         <v>69.115289526281927</v>
       </c>
     </row>
-    <row r="477" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A477" s="1">
         <v>42214</v>
       </c>
@@ -14816,7 +14827,7 @@
         <v>65.005582381367375</v>
       </c>
     </row>
-    <row r="478" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A478" s="1">
         <v>42221</v>
       </c>
@@ -14845,7 +14856,7 @@
         <v>63.076909141434115</v>
       </c>
     </row>
-    <row r="479" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A479" s="1">
         <v>42228</v>
       </c>
@@ -14874,7 +14885,7 @@
         <v>62.189535700762221</v>
       </c>
     </row>
-    <row r="480" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A480" s="1">
         <v>42235</v>
       </c>
@@ -14903,7 +14914,7 @@
         <v>56.905421187389813</v>
       </c>
     </row>
-    <row r="481" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A481" s="1">
         <v>42242</v>
       </c>
@@ -14932,7 +14943,7 @@
         <v>54.437212556646394</v>
       </c>
     </row>
-    <row r="482" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A482" s="1">
         <v>42249</v>
       </c>
@@ -14961,7 +14972,7 @@
         <v>45.740626444393065</v>
       </c>
     </row>
-    <row r="483" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A483" s="1">
         <v>42256</v>
       </c>
@@ -14990,7 +15001,7 @@
         <v>39.805313843808364</v>
       </c>
     </row>
-    <row r="484" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A484" s="1">
         <v>42263</v>
       </c>
@@ -15019,7 +15030,7 @@
         <v>43.806543446148218</v>
       </c>
     </row>
-    <row r="485" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A485" s="1">
         <v>42270</v>
       </c>
@@ -15048,7 +15059,7 @@
         <v>51.716685867776327</v>
       </c>
     </row>
-    <row r="486" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A486" s="1">
         <v>42277</v>
       </c>
@@ -15077,7 +15088,7 @@
         <v>58.081158609585614</v>
       </c>
     </row>
-    <row r="487" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A487" s="1">
         <v>42284</v>
       </c>
@@ -15106,7 +15117,7 @@
         <v>56.825158228391729</v>
       </c>
     </row>
-    <row r="488" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A488" s="1">
         <v>42291</v>
       </c>
@@ -15135,7 +15146,7 @@
         <v>67.174925319764782</v>
       </c>
     </row>
-    <row r="489" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A489" s="1">
         <v>42298</v>
       </c>
@@ -15164,7 +15175,7 @@
         <v>45.345586579315764</v>
       </c>
     </row>
-    <row r="490" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A490" s="1">
         <v>42305</v>
       </c>
@@ -15193,7 +15204,7 @@
         <v>57.374167645036572</v>
       </c>
     </row>
-    <row r="491" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A491" s="1">
         <v>42312</v>
       </c>
@@ -15222,7 +15233,7 @@
         <v>51.179056631292994</v>
       </c>
     </row>
-    <row r="492" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A492" s="1">
         <v>42319</v>
       </c>
@@ -15251,7 +15262,7 @@
         <v>53.107945174576969</v>
       </c>
     </row>
-    <row r="493" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A493" s="1">
         <v>42326</v>
       </c>
@@ -15280,7 +15291,7 @@
         <v>58.422447069085209</v>
       </c>
     </row>
-    <row r="494" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A494" s="1">
         <v>42333</v>
       </c>
@@ -15309,7 +15320,7 @@
         <v>34.740224585926597</v>
       </c>
     </row>
-    <row r="495" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A495" s="1">
         <v>42340</v>
       </c>
@@ -15338,7 +15349,7 @@
         <v>53.475606892716783</v>
       </c>
     </row>
-    <row r="496" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A496" s="1">
         <v>42347</v>
       </c>
@@ -15367,7 +15378,7 @@
         <v>49.782638326185712</v>
       </c>
     </row>
-    <row r="497" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A497" s="1">
         <v>42354</v>
       </c>
@@ -15396,7 +15407,7 @@
         <v>64.682794789944978</v>
       </c>
     </row>
-    <row r="498" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A498" s="1">
         <v>42361</v>
       </c>
@@ -15425,7 +15436,7 @@
         <v>58.632036840912747</v>
       </c>
     </row>
-    <row r="499" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A499" s="1">
         <v>42368</v>
       </c>
@@ -15454,7 +15465,7 @@
         <v>60.952600023373698</v>
       </c>
     </row>
-    <row r="500" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A500" s="1">
         <v>42375</v>
       </c>
@@ -15483,7 +15494,7 @@
         <v>66.58828791661989</v>
       </c>
     </row>
-    <row r="501" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A501" s="1">
         <v>42382</v>
       </c>
@@ -15512,7 +15523,7 @@
         <v>64.934642249421515</v>
       </c>
     </row>
-    <row r="502" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A502" s="1">
         <v>42396</v>
       </c>
@@ -15541,7 +15552,7 @@
         <v>41.40576650661113</v>
       </c>
     </row>
-    <row r="503" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A503" s="1">
         <v>42403</v>
       </c>
@@ -15570,7 +15581,7 @@
         <v>31.776137400465753</v>
       </c>
     </row>
-    <row r="504" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A504" s="1">
         <v>42410</v>
       </c>
@@ -15599,7 +15610,7 @@
         <v>53.128851841152972</v>
       </c>
     </row>
-    <row r="505" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A505" s="1">
         <v>42417</v>
       </c>
@@ -15628,7 +15639,7 @@
         <v>38.552772794324362</v>
       </c>
     </row>
-    <row r="506" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A506" s="1">
         <v>42424</v>
       </c>
@@ -15657,7 +15668,7 @@
         <v>57.386093846065783</v>
       </c>
     </row>
-    <row r="507" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A507" s="1">
         <v>42431</v>
       </c>
@@ -15686,7 +15697,7 @@
         <v>56.216108002049303</v>
       </c>
     </row>
-    <row r="508" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A508" s="1">
         <v>42438</v>
       </c>
@@ -15715,7 +15726,7 @@
         <v>49.345050684492676</v>
       </c>
     </row>
-    <row r="509" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A509" s="1">
         <v>42445</v>
       </c>
@@ -15744,7 +15755,7 @@
         <v>47.469934929618582</v>
       </c>
     </row>
-    <row r="510" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A510" s="1">
         <v>42452</v>
       </c>
@@ -15773,7 +15784,7 @@
         <v>55.942502690409157</v>
       </c>
     </row>
-    <row r="511" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A511" s="1">
         <v>42459</v>
       </c>
@@ -15802,7 +15813,7 @@
         <v>51.171281684204004</v>
       </c>
     </row>
-    <row r="512" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A512" s="1">
         <v>42466</v>
       </c>
@@ -15831,7 +15842,7 @@
         <v>44.987298684587493</v>
       </c>
     </row>
-    <row r="513" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A513" s="1">
         <v>42473</v>
       </c>
@@ -15860,7 +15871,7 @@
         <v>52.267754767722032</v>
       </c>
     </row>
-    <row r="514" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A514" s="1">
         <v>42480</v>
       </c>
@@ -15889,7 +15900,7 @@
         <v>59.274689783916969</v>
       </c>
     </row>
-    <row r="515" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A515" s="1">
         <v>42487</v>
       </c>
@@ -15918,7 +15929,7 @@
         <v>56.059043268503345</v>
       </c>
     </row>
-    <row r="516" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A516" s="1">
         <v>42494</v>
       </c>
@@ -15947,7 +15958,7 @@
         <v>63.557616832598796</v>
       </c>
     </row>
-    <row r="517" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A517" s="1">
         <v>42501</v>
       </c>
@@ -15976,7 +15987,7 @@
         <v>60.325228184861054</v>
       </c>
     </row>
-    <row r="518" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A518" s="1">
         <v>42508</v>
       </c>
@@ -16005,7 +16016,7 @@
         <v>66.025148795269672</v>
       </c>
     </row>
-    <row r="519" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A519" s="1">
         <v>42515</v>
       </c>
@@ -16034,7 +16045,7 @@
         <v>65.838860527469308</v>
       </c>
     </row>
-    <row r="520" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A520" s="1">
         <v>42522</v>
       </c>
@@ -16063,7 +16074,7 @@
         <v>58.204477883361697</v>
       </c>
     </row>
-    <row r="521" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A521" s="1">
         <v>42529</v>
       </c>
@@ -16092,7 +16103,7 @@
         <v>67.614110056909553</v>
       </c>
     </row>
-    <row r="522" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A522" s="1">
         <v>42536</v>
       </c>
@@ -16121,7 +16132,7 @@
         <v>74.11356391861203</v>
       </c>
     </row>
-    <row r="523" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A523" s="1">
         <v>42543</v>
       </c>
@@ -16150,7 +16161,7 @@
         <v>73.151472857827756</v>
       </c>
     </row>
-    <row r="524" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A524" s="1">
         <v>42550</v>
       </c>
@@ -16179,7 +16190,7 @@
         <v>61.145192933839347</v>
       </c>
     </row>
-    <row r="525" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A525" s="1">
         <v>42557</v>
       </c>
@@ -16208,7 +16219,7 @@
         <v>59.461294600399974</v>
       </c>
     </row>
-    <row r="526" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A526" s="1">
         <v>42564</v>
       </c>
@@ -16237,7 +16248,7 @@
         <v>55.474316952158986</v>
       </c>
     </row>
-    <row r="527" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A527" s="1">
         <v>42571</v>
       </c>
@@ -16266,7 +16277,7 @@
         <v>47.642829505911699</v>
       </c>
     </row>
-    <row r="528" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A528" s="1">
         <v>42578</v>
       </c>
@@ -16295,7 +16306,7 @@
         <v>38.757015074458316</v>
       </c>
     </row>
-    <row r="529" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A529" s="1">
         <v>42585</v>
       </c>
@@ -16324,7 +16335,7 @@
         <v>40.898792194128127</v>
       </c>
     </row>
-    <row r="530" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A530" s="1">
         <v>42592</v>
       </c>
@@ -16353,7 +16364,7 @@
         <v>44.684911157119551</v>
       </c>
     </row>
-    <row r="531" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A531" s="1">
         <v>42599</v>
       </c>
@@ -16382,7 +16393,7 @@
         <v>38.351540526685874</v>
       </c>
     </row>
-    <row r="532" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A532" s="1">
         <v>42606</v>
       </c>
@@ -16411,7 +16422,7 @@
         <v>52.845347659285657</v>
       </c>
     </row>
-    <row r="533" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A533" s="1">
         <v>42613</v>
       </c>
@@ -16440,7 +16451,7 @@
         <v>50.592178955136646</v>
       </c>
     </row>
-    <row r="534" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A534" s="1">
         <v>42620</v>
       </c>
@@ -16469,7 +16480,7 @@
         <v>45.8727017663767</v>
       </c>
     </row>
-    <row r="535" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A535" s="1">
         <v>42627</v>
       </c>
@@ -16498,7 +16509,7 @@
         <v>74.814030546861105</v>
       </c>
     </row>
-    <row r="536" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A536" s="1">
         <v>42634</v>
       </c>
@@ -16527,7 +16538,7 @@
         <v>53.632347230101267</v>
       </c>
     </row>
-    <row r="537" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A537" s="1">
         <v>42641</v>
       </c>
@@ -16556,7 +16567,7 @@
         <v>48.896571681685643</v>
       </c>
     </row>
-    <row r="538" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A538" s="1">
         <v>42648</v>
       </c>
@@ -16585,7 +16596,7 @@
         <v>61.205113840328835</v>
       </c>
     </row>
-    <row r="539" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A539" s="1">
         <v>42655</v>
       </c>
@@ -16614,7 +16625,7 @@
         <v>57.785327901705259</v>
       </c>
     </row>
-    <row r="540" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A540" s="1">
         <v>42662</v>
       </c>
@@ -16643,7 +16654,7 @@
         <v>79.940100561197539</v>
       </c>
     </row>
-    <row r="541" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A541" s="1">
         <v>42669</v>
       </c>
@@ -16672,7 +16683,7 @@
         <v>73.199803298495794</v>
       </c>
     </row>
-    <row r="542" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A542" s="1">
         <v>42676</v>
       </c>
@@ -16701,7 +16712,7 @@
         <v>81.972971493996454</v>
       </c>
     </row>
-    <row r="543" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A543" s="1">
         <v>42683</v>
       </c>
@@ -16730,7 +16741,7 @@
         <v>70.252181451028676</v>
       </c>
     </row>
-    <row r="544" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A544" s="1">
         <v>42689</v>
       </c>
@@ -16759,7 +16770,7 @@
         <v>45.034554333138182</v>
       </c>
     </row>
-    <row r="545" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A545" s="1">
         <v>42697</v>
       </c>
@@ -16788,7 +16799,7 @@
         <v>31.902622834964525</v>
       </c>
     </row>
-    <row r="546" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A546" s="1">
         <v>42704</v>
       </c>
@@ -16817,7 +16828,7 @@
         <v>33.812107442362681</v>
       </c>
     </row>
-    <row r="547" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A547" s="1">
         <v>42711</v>
       </c>
@@ -16846,7 +16857,7 @@
         <v>44.571790079241985</v>
       </c>
     </row>
-    <row r="548" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A548" s="1">
         <v>42718</v>
       </c>
@@ -16875,7 +16886,7 @@
         <v>51.225600837105361</v>
       </c>
     </row>
-    <row r="549" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A549" s="1">
         <v>42725</v>
       </c>
@@ -16904,7 +16915,7 @@
         <v>31.324298121335335</v>
       </c>
     </row>
-    <row r="550" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A550" s="1">
         <v>42732</v>
       </c>
@@ -16933,7 +16944,7 @@
         <v>40.560500686953205</v>
       </c>
     </row>
-    <row r="551" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A551" s="1">
         <v>42739</v>
       </c>
@@ -16962,7 +16973,7 @@
         <v>41.368869961849803</v>
       </c>
     </row>
-    <row r="552" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A552" s="1">
         <v>42746</v>
       </c>
@@ -16991,7 +17002,7 @@
         <v>36.188090354038536</v>
       </c>
     </row>
-    <row r="553" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A553" s="1">
         <v>42753</v>
       </c>
@@ -17020,7 +17031,7 @@
         <v>37.743249902447104</v>
       </c>
     </row>
-    <row r="554" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A554" s="1">
         <v>42760</v>
       </c>
@@ -17049,7 +17060,7 @@
         <v>38.125600177425255</v>
       </c>
     </row>
-    <row r="555" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A555" s="1">
         <v>42767</v>
       </c>
@@ -17078,7 +17089,7 @@
         <v>35.21374453775752</v>
       </c>
     </row>
-    <row r="556" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A556" s="1">
         <v>42774</v>
       </c>
@@ -17107,7 +17118,7 @@
         <v>37.200813418944776</v>
       </c>
     </row>
-    <row r="557" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A557" s="1">
         <v>42781</v>
       </c>
@@ -17136,7 +17147,7 @@
         <v>46.401461865606194</v>
       </c>
     </row>
-    <row r="558" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A558" s="1">
         <v>42788</v>
       </c>
@@ -17165,7 +17176,7 @@
         <v>47.306097125086168</v>
       </c>
     </row>
-    <row r="559" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A559" s="1">
         <v>42795</v>
       </c>
@@ -17194,7 +17205,7 @@
         <v>40.981014136054526</v>
       </c>
     </row>
-    <row r="560" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A560" s="1">
         <v>42802</v>
       </c>
@@ -17223,7 +17234,7 @@
         <v>33.994932520079296</v>
       </c>
     </row>
-    <row r="561" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A561" s="1">
         <v>42809</v>
       </c>
@@ -17252,7 +17263,7 @@
         <v>44.968363852363964</v>
       </c>
     </row>
-    <row r="562" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A562" s="1">
         <v>42816</v>
       </c>
@@ -17281,7 +17292,7 @@
         <v>49.659201917259722</v>
       </c>
     </row>
-    <row r="563" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A563" s="1">
         <v>42823</v>
       </c>
@@ -17310,7 +17321,7 @@
         <v>64.362780454268531</v>
       </c>
     </row>
-    <row r="564" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A564" s="1">
         <v>42830</v>
       </c>
@@ -17339,7 +17350,7 @@
         <v>64.776799001384475</v>
       </c>
     </row>
-    <row r="565" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A565" s="1">
         <v>42837</v>
       </c>
@@ -17368,7 +17379,7 @@
         <v>65.166932244503599</v>
       </c>
     </row>
-    <row r="566" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A566" s="1">
         <v>42844</v>
       </c>
@@ -17397,7 +17408,7 @@
         <v>59.958870200350503</v>
       </c>
     </row>
-    <row r="567" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A567" s="1">
         <v>42851</v>
       </c>
@@ -17426,7 +17437,7 @@
         <v>59.381621852968017</v>
       </c>
     </row>
-    <row r="568" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A568" s="1">
         <v>42858</v>
       </c>
@@ -17455,7 +17466,7 @@
         <v>43.61543763393874</v>
       </c>
     </row>
-    <row r="569" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A569" s="1">
         <v>42865</v>
       </c>
@@ -17484,7 +17495,7 @@
         <v>45.396879132363082</v>
       </c>
     </row>
-    <row r="570" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A570" s="1">
         <v>42872</v>
       </c>
@@ -17513,7 +17524,7 @@
         <v>57.001842496633159</v>
       </c>
     </row>
-    <row r="571" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A571" s="1">
         <v>42879</v>
       </c>
@@ -17542,7 +17553,7 @@
         <v>43.069217656771137</v>
       </c>
     </row>
-    <row r="572" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A572" s="1">
         <v>42886</v>
       </c>
@@ -17571,7 +17582,7 @@
         <v>48.392374712148168</v>
       </c>
     </row>
-    <row r="573" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A573" s="1">
         <v>42893</v>
       </c>
@@ -17600,7 +17611,7 @@
         <v>40.948483493075209</v>
       </c>
     </row>
-    <row r="574" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A574" s="1">
         <v>42900</v>
       </c>
@@ -17629,7 +17640,7 @@
         <v>37.402091766235387</v>
       </c>
     </row>
-    <row r="575" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A575" s="1">
         <v>42907</v>
       </c>
@@ -17658,7 +17669,7 @@
         <v>46.287563991280784</v>
       </c>
     </row>
-    <row r="576" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A576" s="1">
         <v>42914</v>
       </c>
@@ -17687,7 +17698,7 @@
         <v>51.63023920146022</v>
       </c>
     </row>
-    <row r="577" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A577" s="1">
         <v>42921</v>
       </c>
@@ -17716,7 +17727,7 @@
         <v>38.938715947404972</v>
       </c>
     </row>
-    <row r="578" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A578" s="1">
         <v>42928</v>
       </c>
@@ -17745,7 +17756,7 @@
         <v>32.992166958557021</v>
       </c>
     </row>
-    <row r="579" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A579" s="1">
         <v>42935</v>
       </c>
@@ -17774,7 +17785,7 @@
         <v>41.819650581896475</v>
       </c>
     </row>
-    <row r="580" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A580" s="1">
         <v>42942</v>
       </c>
@@ -17803,7 +17814,7 @@
         <v>50.264603848036046</v>
       </c>
     </row>
-    <row r="581" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A581" s="1">
         <v>42949</v>
       </c>
@@ -17832,7 +17843,7 @@
         <v>42.982310991380189</v>
       </c>
     </row>
-    <row r="582" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A582" s="1">
         <v>42956</v>
       </c>
@@ -17861,7 +17872,7 @@
         <v>42.602862162618685</v>
       </c>
     </row>
-    <row r="583" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A583" s="1">
         <v>42963</v>
       </c>
@@ -17890,7 +17901,7 @@
         <v>35.515471002867969</v>
       </c>
     </row>
-    <row r="584" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A584" s="1">
         <v>42970</v>
       </c>
@@ -17919,7 +17930,7 @@
         <v>41.20422836194178</v>
       </c>
     </row>
-    <row r="585" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A585" s="1">
         <v>42977</v>
       </c>
@@ -17948,7 +17959,7 @@
         <v>46.305875728509086</v>
       </c>
     </row>
-    <row r="586" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A586" s="1">
         <v>42984</v>
       </c>
@@ -17977,7 +17988,7 @@
         <v>52.28157999497369</v>
       </c>
     </row>
-    <row r="587" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A587" s="1">
         <v>42991</v>
       </c>
@@ -18006,7 +18017,7 @@
         <v>45.246656707228858</v>
       </c>
     </row>
-    <row r="588" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A588" s="1">
         <v>42998</v>
       </c>
@@ -18035,7 +18046,7 @@
         <v>42.836271786367632</v>
       </c>
     </row>
-    <row r="589" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A589" s="1">
         <v>43005</v>
       </c>
@@ -18064,7 +18075,7 @@
         <v>25.850229689501795</v>
       </c>
     </row>
-    <row r="590" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A590" s="1">
         <v>43012</v>
       </c>
@@ -18093,7 +18104,7 @@
         <v>29.219171788399478</v>
       </c>
     </row>
-    <row r="591" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A591" s="1">
         <v>43019</v>
       </c>
@@ -18122,7 +18133,7 @@
         <v>47.697764295090394</v>
       </c>
     </row>
-    <row r="592" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A592" s="1">
         <v>43026</v>
       </c>
@@ -18151,7 +18162,7 @@
         <v>38.422382980352594</v>
       </c>
     </row>
-    <row r="593" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A593" s="1">
         <v>43033</v>
       </c>
@@ -18180,7 +18191,7 @@
         <v>64.258296622360419</v>
       </c>
     </row>
-    <row r="594" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A594" s="1">
         <v>43040</v>
       </c>
@@ -18209,7 +18220,7 @@
         <v>57.905260906954553</v>
       </c>
     </row>
-    <row r="595" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A595" s="1">
         <v>43047</v>
       </c>
@@ -18238,7 +18249,7 @@
         <v>34.736286502733705</v>
       </c>
     </row>
-    <row r="596" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A596" s="1">
         <v>43054</v>
       </c>
@@ -18267,7 +18278,7 @@
         <v>68.592291112048443</v>
       </c>
     </row>
-    <row r="597" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A597" s="1">
         <v>43061</v>
       </c>
@@ -18296,7 +18307,7 @@
         <v>27.3096898737011</v>
       </c>
     </row>
-    <row r="598" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A598" s="1">
         <v>43068</v>
       </c>
@@ -18325,7 +18336,7 @@
         <v>47.380261477684584</v>
       </c>
     </row>
-    <row r="599" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A599" s="1">
         <v>43075</v>
       </c>
@@ -18354,7 +18365,7 @@
         <v>48.440037392978304</v>
       </c>
     </row>
-    <row r="600" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A600" s="1">
         <v>43082</v>
       </c>
@@ -18383,7 +18394,7 @@
         <v>44.562343622567724</v>
       </c>
     </row>
-    <row r="601" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A601" s="1">
         <v>43089</v>
       </c>
@@ -18412,7 +18423,7 @@
         <v>36.623281382599032</v>
       </c>
     </row>
-    <row r="602" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A602" s="1">
         <v>43096</v>
       </c>
@@ -18441,7 +18452,7 @@
         <v>34.643577434597006</v>
       </c>
     </row>
-    <row r="603" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A603" s="1">
         <v>43103</v>
       </c>
@@ -18470,7 +18481,7 @@
         <v>25.360655270394762</v>
       </c>
     </row>
-    <row r="604" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A604" s="1">
         <v>43110</v>
       </c>
@@ -18499,7 +18510,7 @@
         <v>25.396638870684793</v>
       </c>
     </row>
-    <row r="605" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A605" s="1">
         <v>43117</v>
       </c>
@@ -18528,7 +18539,7 @@
         <v>27.71</v>
       </c>
     </row>
-    <row r="606" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A606" s="1">
         <v>43124</v>
       </c>
@@ -18557,7 +18568,7 @@
         <v>29.33</v>
       </c>
     </row>
-    <row r="607" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A607" s="1">
         <v>43131</v>
       </c>
@@ -18586,7 +18597,7 @@
         <v>53.07</v>
       </c>
     </row>
-    <row r="608" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A608" s="1">
         <v>43138</v>
       </c>
@@ -18615,7 +18626,7 @@
         <v>44.02</v>
       </c>
     </row>
-    <row r="609" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A609" s="1">
         <v>43145</v>
       </c>
@@ -18644,7 +18655,7 @@
         <v>55.52</v>
       </c>
     </row>
-    <row r="610" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A610" s="1">
         <v>43152</v>
       </c>
@@ -18673,7 +18684,7 @@
         <v>50.17</v>
       </c>
     </row>
-    <row r="611" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A611" s="1">
         <v>43159</v>
       </c>
@@ -18702,7 +18713,7 @@
         <v>34.54</v>
       </c>
     </row>
-    <row r="612" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A612" s="1">
         <v>43166</v>
       </c>
@@ -18731,7 +18742,7 @@
         <v>53.35</v>
       </c>
     </row>
-    <row r="613" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A613" s="1">
         <v>43173</v>
       </c>
@@ -18760,7 +18771,7 @@
         <v>34.69</v>
       </c>
     </row>
-    <row r="614" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A614" s="1">
         <v>43180</v>
       </c>
@@ -18789,7 +18800,7 @@
         <v>50.12</v>
       </c>
     </row>
-    <row r="615" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A615" s="1">
         <v>43187</v>
       </c>
@@ -18818,7 +18829,7 @@
         <v>66.569999999999993</v>
       </c>
     </row>
-    <row r="616" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A616" s="1">
         <v>43194</v>
       </c>
@@ -18847,7 +18858,7 @@
         <v>58.83</v>
       </c>
     </row>
-    <row r="617" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A617" s="1">
         <v>43201</v>
       </c>
@@ -18876,7 +18887,7 @@
         <v>48.61</v>
       </c>
     </row>
-    <row r="618" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A618" s="1">
         <v>43208</v>
       </c>
@@ -18905,7 +18916,7 @@
         <v>38.979999999999997</v>
       </c>
     </row>
-    <row r="619" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A619" s="1">
         <v>43215</v>
       </c>
@@ -18934,7 +18945,7 @@
         <v>63.14</v>
       </c>
     </row>
-    <row r="620" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A620" s="1">
         <v>43222</v>
       </c>
@@ -18963,7 +18974,7 @@
         <v>68.150000000000006</v>
       </c>
     </row>
-    <row r="621" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A621" s="1">
         <v>43229</v>
       </c>
@@ -18992,7 +19003,7 @@
         <v>39.549999999999997</v>
       </c>
     </row>
-    <row r="622" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A622" s="1">
         <v>43236</v>
       </c>
@@ -19021,7 +19032,7 @@
         <v>54.33</v>
       </c>
     </row>
-    <row r="623" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A623" s="1">
         <v>43243</v>
       </c>
@@ -19050,7 +19061,7 @@
         <v>53.99</v>
       </c>
     </row>
-    <row r="624" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A624" s="1">
         <v>43250</v>
       </c>
@@ -19079,7 +19090,7 @@
         <v>39.76</v>
       </c>
     </row>
-    <row r="625" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A625" s="1">
         <v>43257</v>
       </c>
@@ -19108,7 +19119,7 @@
         <v>34.51</v>
       </c>
     </row>
-    <row r="626" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A626" s="1">
         <v>43264</v>
       </c>
@@ -19137,7 +19148,7 @@
         <v>41.63</v>
       </c>
     </row>
-    <row r="627" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A627" s="1">
         <v>43271</v>
       </c>
@@ -19166,7 +19177,7 @@
         <v>34.5</v>
       </c>
     </row>
-    <row r="628" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A628" s="1">
         <v>43278</v>
       </c>
@@ -19195,7 +19206,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="629" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A629" s="1">
         <v>43285</v>
       </c>
@@ -19224,7 +19235,7 @@
         <v>46.74</v>
       </c>
     </row>
-    <row r="630" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A630" s="1">
         <v>43292</v>
       </c>
@@ -19253,7 +19264,7 @@
         <v>38.47</v>
       </c>
     </row>
-    <row r="631" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A631" s="1">
         <v>43299</v>
       </c>
@@ -19282,7 +19293,7 @@
         <v>38.82</v>
       </c>
     </row>
-    <row r="632" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A632" s="1">
         <v>43306</v>
       </c>
@@ -19311,7 +19322,7 @@
         <v>39.159999999999997</v>
       </c>
     </row>
-    <row r="633" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A633" s="1">
         <v>43313</v>
       </c>
@@ -19340,7 +19351,7 @@
         <v>40.450000000000003</v>
       </c>
     </row>
-    <row r="634" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A634" s="1">
         <v>43320</v>
       </c>
@@ -19369,7 +19380,7 @@
         <v>32.78</v>
       </c>
     </row>
-    <row r="635" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A635" s="1">
         <v>43327</v>
       </c>
@@ -19398,7 +19409,7 @@
         <v>38.94</v>
       </c>
     </row>
-    <row r="636" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A636" s="1">
         <v>43334</v>
       </c>
@@ -19427,7 +19438,7 @@
         <v>31.73</v>
       </c>
     </row>
-    <row r="637" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A637" s="1">
         <v>43341</v>
       </c>
@@ -19456,7 +19467,7 @@
         <v>38.53</v>
       </c>
     </row>
-    <row r="638" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A638" s="1">
         <v>43348</v>
       </c>
@@ -19485,7 +19496,7 @@
         <v>43.57</v>
       </c>
     </row>
-    <row r="639" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A639" s="1">
         <v>43355</v>
       </c>
@@ -19514,7 +19525,7 @@
         <v>37.619999999999997</v>
       </c>
     </row>
-    <row r="640" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A640" s="1">
         <v>43362</v>
       </c>
@@ -19543,7 +19554,7 @@
         <v>38.020000000000003</v>
       </c>
     </row>
-    <row r="641" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A641" s="1">
         <v>43369</v>
       </c>
@@ -19572,7 +19583,7 @@
         <v>44.58</v>
       </c>
     </row>
-    <row r="642" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A642" s="1">
         <v>43376</v>
       </c>
@@ -19601,7 +19612,7 @@
         <v>43.37</v>
       </c>
     </row>
-    <row r="643" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A643" s="1">
         <v>43383</v>
       </c>
@@ -19630,7 +19641,7 @@
         <v>64.94</v>
       </c>
     </row>
-    <row r="644" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A644" s="1">
         <v>43391</v>
       </c>
@@ -19659,7 +19670,7 @@
         <v>45.19</v>
       </c>
     </row>
-    <row r="645" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A645" s="1">
         <v>43397</v>
       </c>
@@ -19688,7 +19699,7 @@
         <v>72.86</v>
       </c>
     </row>
-    <row r="646" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A646" s="1">
         <v>43404</v>
       </c>
@@ -19717,7 +19728,7 @@
         <v>38.96</v>
       </c>
     </row>
-    <row r="647" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A647" s="1">
         <v>43411</v>
       </c>
@@ -19746,7 +19757,7 @@
         <v>33.590000000000003</v>
       </c>
     </row>
-    <row r="648" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A648" s="1">
         <v>43418</v>
       </c>
@@ -19775,7 +19786,7 @@
         <v>48.37</v>
       </c>
     </row>
-    <row r="649" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A649" s="1">
         <v>43425</v>
       </c>
@@ -19804,7 +19815,7 @@
         <v>73.89</v>
       </c>
     </row>
-    <row r="650" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A650" s="1">
         <v>43432</v>
       </c>
@@ -19833,7 +19844,7 @@
         <v>39.99</v>
       </c>
     </row>
-    <row r="651" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A651" s="1">
         <v>43439</v>
       </c>
@@ -19862,7 +19873,7 @@
         <v>61.26</v>
       </c>
     </row>
-    <row r="652" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A652" s="1">
         <v>43446</v>
       </c>
@@ -19891,7 +19902,7 @@
         <v>50.14</v>
       </c>
     </row>
-    <row r="653" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A653" s="1">
         <v>43453</v>
       </c>
@@ -19920,7 +19931,7 @@
         <v>63.86</v>
       </c>
     </row>
-    <row r="654" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A654" s="1">
         <v>43460</v>
       </c>
@@ -19949,7 +19960,7 @@
         <v>50.7</v>
       </c>
     </row>
-    <row r="655" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A655" s="1">
         <v>43467</v>
       </c>
@@ -19978,7 +19989,7 @@
         <v>53.3</v>
       </c>
     </row>
-    <row r="656" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A656" s="1">
         <v>43474</v>
       </c>
@@ -20007,7 +20018,7 @@
         <v>60.63</v>
       </c>
     </row>
-    <row r="657" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A657" s="1">
         <v>43481</v>
       </c>
@@ -20036,7 +20047,7 @@
         <v>51.01</v>
       </c>
     </row>
-    <row r="658" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A658" s="1">
         <v>43488</v>
       </c>
@@ -20065,7 +20076,7 @@
         <v>45.67</v>
       </c>
     </row>
-    <row r="659" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A659" s="1">
         <v>43495</v>
       </c>
@@ -20094,7 +20105,7 @@
         <v>46.03</v>
       </c>
     </row>
-    <row r="660" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A660" s="1">
         <v>43502</v>
       </c>
@@ -20123,7 +20134,7 @@
         <v>42.17</v>
       </c>
     </row>
-    <row r="661" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A661" s="1">
         <v>43509</v>
       </c>
@@ -20152,7 +20163,7 @@
         <v>40.51</v>
       </c>
     </row>
-    <row r="662" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A662" s="1">
         <v>43516</v>
       </c>
@@ -20181,7 +20192,7 @@
         <v>46.58</v>
       </c>
     </row>
-    <row r="663" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A663" s="1">
         <v>43523</v>
       </c>
@@ -20210,7 +20221,7 @@
         <v>48.78</v>
       </c>
     </row>
-    <row r="664" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A664" s="1">
         <v>43530</v>
       </c>
@@ -20239,7 +20250,7 @@
         <v>51.87</v>
       </c>
     </row>
-    <row r="665" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A665" s="1">
         <v>43537</v>
       </c>
@@ -20268,7 +20279,7 @@
         <v>50.84</v>
       </c>
     </row>
-    <row r="666" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A666" s="1">
         <v>43544</v>
       </c>
@@ -20297,7 +20308,7 @@
         <v>57.44</v>
       </c>
     </row>
-    <row r="667" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A667" s="1">
         <v>43551</v>
       </c>
@@ -20326,7 +20337,7 @@
         <v>58.85</v>
       </c>
     </row>
-    <row r="668" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A668" s="1">
         <v>43558</v>
       </c>
@@ -20355,7 +20366,7 @@
         <v>37.44</v>
       </c>
     </row>
-    <row r="669" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A669" s="1">
         <v>43565</v>
       </c>
@@ -20384,7 +20395,7 @@
         <v>44.35</v>
       </c>
     </row>
-    <row r="670" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A670" s="1">
         <v>43572</v>
       </c>
@@ -20413,7 +20424,7 @@
         <v>29.9</v>
       </c>
     </row>
-    <row r="671" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A671" s="1">
         <v>43579</v>
       </c>
@@ -20442,7 +20453,7 @@
         <v>38.32</v>
       </c>
     </row>
-    <row r="672" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A672" s="1">
         <v>43586</v>
       </c>
@@ -20471,7 +20482,7 @@
         <v>43.11</v>
       </c>
     </row>
-    <row r="673" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A673" s="1">
         <v>43593</v>
       </c>
@@ -20500,7 +20511,7 @@
         <v>63.69</v>
       </c>
     </row>
-    <row r="674" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A674" s="1">
         <v>43600</v>
       </c>
@@ -20529,7 +20540,7 @@
         <v>54.45</v>
       </c>
     </row>
-    <row r="675" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A675" s="1">
         <v>43607</v>
       </c>
@@ -20558,7 +20569,7 @@
         <v>38.76</v>
       </c>
     </row>
-    <row r="676" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A676" s="1">
         <v>43614</v>
       </c>
@@ -20587,7 +20598,7 @@
         <v>76.66</v>
       </c>
     </row>
-    <row r="677" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A677" s="1">
         <v>43621</v>
       </c>
@@ -20616,7 +20627,7 @@
         <v>57.55</v>
       </c>
     </row>
-    <row r="678" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A678" s="1">
         <v>43628</v>
       </c>
@@ -20645,7 +20656,7 @@
         <v>36.67</v>
       </c>
     </row>
-    <row r="679" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A679" s="1">
         <v>43635</v>
       </c>
@@ -20674,7 +20685,7 @@
         <v>25.39</v>
       </c>
     </row>
-    <row r="680" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A680" s="1">
         <v>43642</v>
       </c>
@@ -20703,7 +20714,7 @@
         <v>56.56</v>
       </c>
     </row>
-    <row r="681" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A681" s="1">
         <v>43649</v>
       </c>
@@ -20732,7 +20743,7 @@
         <v>37.46</v>
       </c>
     </row>
-    <row r="682" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A682" s="1">
         <v>43656</v>
       </c>
@@ -20761,7 +20772,7 @@
         <v>35.630000000000003</v>
       </c>
     </row>
-    <row r="683" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A683" s="1">
         <v>43663</v>
       </c>
@@ -20790,7 +20801,7 @@
         <v>53.98</v>
       </c>
     </row>
-    <row r="684" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A684" s="1">
         <v>43670</v>
       </c>
@@ -20819,7 +20830,7 @@
         <v>37.93</v>
       </c>
     </row>
-    <row r="685" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A685" s="1">
         <v>43677</v>
       </c>
@@ -20848,7 +20859,7 @@
         <v>41.31</v>
       </c>
     </row>
-    <row r="686" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A686" s="1">
         <v>43684</v>
       </c>
@@ -20877,7 +20888,7 @@
         <v>61.58</v>
       </c>
     </row>
-    <row r="687" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A687" s="1">
         <v>43691</v>
       </c>
@@ -20906,7 +20917,7 @@
         <v>49.29</v>
       </c>
     </row>
-    <row r="688" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A688" s="1">
         <v>43698</v>
       </c>
@@ -20935,7 +20946,7 @@
         <v>60.34</v>
       </c>
     </row>
-    <row r="689" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A689" s="1">
         <v>43705</v>
       </c>
@@ -20964,7 +20975,7 @@
         <v>66.010000000000005</v>
       </c>
     </row>
-    <row r="690" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A690" s="1">
         <v>43712</v>
       </c>
@@ -20993,7 +21004,7 @@
         <v>53.29</v>
       </c>
     </row>
-    <row r="691" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A691" s="1">
         <v>43719</v>
       </c>
@@ -21022,7 +21033,7 @@
         <v>58.2</v>
       </c>
     </row>
-    <row r="692" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A692" s="1">
         <v>43726</v>
       </c>
@@ -21051,7 +21062,7 @@
         <v>62.04</v>
       </c>
     </row>
-    <row r="693" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A693" s="1">
         <v>43733</v>
       </c>
@@ -21080,7 +21091,7 @@
         <v>53.22</v>
       </c>
     </row>
-    <row r="694" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A694" s="1">
         <v>43740</v>
       </c>
@@ -21109,7 +21120,7 @@
         <v>78.3</v>
       </c>
     </row>
-    <row r="695" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A695" s="1">
         <v>43747</v>
       </c>
@@ -21138,7 +21149,7 @@
         <v>57.1</v>
       </c>
     </row>
-    <row r="696" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A696" s="1">
         <v>43754</v>
       </c>
@@ -21167,7 +21178,7 @@
         <v>67.400000000000006</v>
       </c>
     </row>
-    <row r="697" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A697" s="1">
         <v>43761</v>
       </c>
@@ -21196,7 +21207,7 @@
         <v>38.35</v>
       </c>
     </row>
-    <row r="698" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A698" s="1">
         <v>43768</v>
       </c>
@@ -21225,7 +21236,7 @@
         <v>39.58</v>
       </c>
     </row>
-    <row r="699" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A699" s="1">
         <v>43775</v>
       </c>
@@ -21254,7 +21265,7 @@
         <v>35.5</v>
       </c>
     </row>
-    <row r="700" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A700" s="1">
         <v>43782</v>
       </c>
@@ -21283,7 +21294,7 @@
         <v>49.68</v>
       </c>
     </row>
-    <row r="701" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A701" s="1">
         <v>43789</v>
       </c>
@@ -21312,7 +21323,7 @@
         <v>52.05</v>
       </c>
     </row>
-    <row r="702" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A702" s="1">
         <v>43796</v>
       </c>
@@ -21341,7 +21352,7 @@
         <v>41.28</v>
       </c>
     </row>
-    <row r="703" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A703" s="1">
         <v>43803</v>
       </c>
@@ -21370,7 +21381,7 @@
         <v>56.13</v>
       </c>
     </row>
-    <row r="704" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A704" s="1">
         <v>43810</v>
       </c>
@@ -21399,7 +21410,7 @@
         <v>50.69</v>
       </c>
     </row>
-    <row r="705" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A705" s="1">
         <v>43817</v>
       </c>
@@ -21428,7 +21439,7 @@
         <v>35.82</v>
       </c>
     </row>
-    <row r="706" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A706" s="1">
         <v>43824</v>
       </c>
@@ -21457,7 +21468,7 @@
         <v>29.16</v>
       </c>
     </row>
-    <row r="707" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A707" s="1">
         <v>43831</v>
       </c>
@@ -21486,7 +21497,7 @@
         <v>32.42</v>
       </c>
     </row>
-    <row r="708" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A708" s="1">
         <v>43838</v>
       </c>
@@ -21515,7 +21526,7 @@
         <v>40.659999999999997</v>
       </c>
     </row>
-    <row r="709" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A709" s="1">
         <v>43845</v>
       </c>
@@ -21544,7 +21555,7 @@
         <v>37.35</v>
       </c>
     </row>
-    <row r="710" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A710" s="1">
         <v>43852</v>
       </c>
@@ -21573,7 +21584,7 @@
         <v>21.13</v>
       </c>
     </row>
-    <row r="711" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A711" s="1">
         <v>43859</v>
       </c>
@@ -21602,7 +21613,7 @@
         <v>57.93</v>
       </c>
     </row>
-    <row r="712" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A712" s="1">
         <v>43866</v>
       </c>
@@ -21631,7 +21642,7 @@
         <v>57.84</v>
       </c>
     </row>
-    <row r="713" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A713" s="1">
         <v>43873</v>
       </c>
@@ -21660,7 +21671,7 @@
         <v>37.590000000000003</v>
       </c>
     </row>
-    <row r="714" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A714" s="1">
         <v>43880</v>
       </c>
@@ -21689,7 +21700,7 @@
         <v>35.15</v>
       </c>
     </row>
-    <row r="715" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A715" s="1">
         <v>43887</v>
       </c>
@@ -21718,7 +21729,7 @@
         <v>69.72</v>
       </c>
     </row>
-    <row r="716" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A716" s="1">
         <v>43894</v>
       </c>
@@ -21747,7 +21758,7 @@
         <v>72.709999999999994</v>
       </c>
     </row>
-    <row r="717" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A717" s="1">
         <v>43901</v>
       </c>
@@ -21776,7 +21787,7 @@
         <v>58.88</v>
       </c>
     </row>
-    <row r="718" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A718" s="1">
         <v>43908</v>
       </c>
@@ -21805,7 +21816,7 @@
         <v>42.67</v>
       </c>
     </row>
-    <row r="719" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A719" s="1">
         <v>43915</v>
       </c>
@@ -21834,7 +21845,7 @@
         <v>34.049999999999997</v>
       </c>
     </row>
-    <row r="720" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A720" s="1">
         <v>43922</v>
       </c>
@@ -21863,7 +21874,7 @@
         <v>40.64</v>
       </c>
     </row>
-    <row r="721" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A721" s="1">
         <v>43929</v>
       </c>
@@ -21892,7 +21903,7 @@
         <v>44.54</v>
       </c>
     </row>
-    <row r="722" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A722" s="1">
         <v>43936</v>
       </c>
@@ -21921,7 +21932,7 @@
         <v>56.57</v>
       </c>
     </row>
-    <row r="723" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A723" s="1">
         <v>43943</v>
       </c>
@@ -21950,7 +21961,7 @@
         <v>57.95</v>
       </c>
     </row>
-    <row r="724" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A724" s="1">
         <v>43950</v>
       </c>
@@ -21979,7 +21990,7 @@
         <v>41.89</v>
       </c>
     </row>
-    <row r="725" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A725" s="1">
         <v>43957</v>
       </c>
@@ -22008,7 +22019,7 @@
         <v>41.07</v>
       </c>
     </row>
-    <row r="726" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A726" s="1">
         <v>43964</v>
       </c>
@@ -22037,7 +22048,7 @@
         <v>49.3</v>
       </c>
     </row>
-    <row r="727" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A727" s="1">
         <v>43971</v>
       </c>
@@ -22066,7 +22077,7 @@
         <v>51.08</v>
       </c>
     </row>
-    <row r="728" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A728" s="1">
         <v>43978</v>
       </c>
@@ -22095,7 +22106,7 @@
         <v>43.17</v>
       </c>
     </row>
-    <row r="729" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A729" s="1">
         <v>43985</v>
       </c>
@@ -22124,7 +22135,7 @@
         <v>36.69</v>
       </c>
     </row>
-    <row r="730" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A730" s="1">
         <v>43992</v>
       </c>
@@ -22153,7 +22164,7 @@
         <v>54.73</v>
       </c>
     </row>
-    <row r="731" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A731" s="1">
         <v>43999</v>
       </c>
@@ -22182,7 +22193,7 @@
         <v>37.33</v>
       </c>
     </row>
-    <row r="732" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A732" s="1">
         <v>44006</v>
       </c>
@@ -22211,7 +22222,7 @@
         <v>43.91</v>
       </c>
     </row>
-    <row r="733" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A733" s="1">
         <v>44013</v>
       </c>
@@ -22240,7 +22251,7 @@
         <v>52.64</v>
       </c>
     </row>
-    <row r="734" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A734" s="1">
         <v>44020</v>
       </c>
@@ -22269,7 +22280,7 @@
         <v>50.49</v>
       </c>
     </row>
-    <row r="735" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A735" s="1">
         <v>44027</v>
       </c>
@@ -22298,7 +22309,7 @@
         <v>49.38</v>
       </c>
     </row>
-    <row r="736" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A736" s="1">
         <v>44034</v>
       </c>
@@ -22327,7 +22338,7 @@
         <v>33.909999999999997</v>
       </c>
     </row>
-    <row r="737" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A737" s="1">
         <v>44041</v>
       </c>
@@ -22356,7 +22367,7 @@
         <v>36.130000000000003</v>
       </c>
     </row>
-    <row r="738" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A738" s="1">
         <v>44048</v>
       </c>
@@ -22385,7 +22396,7 @@
         <v>49.4</v>
       </c>
     </row>
-    <row r="739" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A739" s="1">
         <v>44055</v>
       </c>
@@ -22414,7 +22425,7 @@
         <v>29.1</v>
       </c>
     </row>
-    <row r="740" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A740" s="1">
         <v>44062</v>
       </c>
@@ -22443,7 +22454,7 @@
         <v>42.31</v>
       </c>
     </row>
-    <row r="741" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A741" s="1">
         <v>44069</v>
       </c>
@@ -22472,7 +22483,7 @@
         <v>38.44</v>
       </c>
     </row>
-    <row r="742" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A742" s="1">
         <v>44076</v>
       </c>
@@ -22501,7 +22512,7 @@
         <v>35.47</v>
       </c>
     </row>
-    <row r="743" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A743" s="1">
         <v>44083</v>
       </c>
@@ -22530,7 +22541,7 @@
         <v>60.47</v>
       </c>
     </row>
-    <row r="744" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A744" s="1">
         <v>44090</v>
       </c>
@@ -22559,7 +22570,7 @@
         <v>71.73</v>
       </c>
     </row>
-    <row r="745" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A745" s="1">
         <v>44097</v>
       </c>
@@ -22588,7 +22599,7 @@
         <v>82.7</v>
       </c>
     </row>
-    <row r="746" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A746" s="1">
         <v>44104</v>
       </c>
@@ -22617,7 +22628,7 @@
         <v>62.62</v>
       </c>
     </row>
-    <row r="747" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A747" s="1">
         <v>44111</v>
       </c>
@@ -22646,7 +22657,7 @@
         <v>63.41</v>
       </c>
     </row>
-    <row r="748" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A748" s="1">
         <v>44118</v>
       </c>
@@ -22675,7 +22686,7 @@
         <v>41.56</v>
       </c>
     </row>
-    <row r="749" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A749" s="1">
         <v>44125</v>
       </c>
@@ -22704,7 +22715,7 @@
         <v>42.48</v>
       </c>
     </row>
-    <row r="750" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A750" s="1">
         <v>44132</v>
       </c>
@@ -22733,7 +22744,7 @@
         <v>49.64</v>
       </c>
     </row>
-    <row r="751" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A751" s="1">
         <v>44139</v>
       </c>
@@ -22762,7 +22773,7 @@
         <v>49.7</v>
       </c>
     </row>
-    <row r="752" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="752" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A752" s="1">
         <v>44146</v>
       </c>
@@ -22791,7 +22802,7 @@
         <v>50.26</v>
       </c>
     </row>
-    <row r="753" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A753" s="1">
         <v>44153</v>
       </c>
@@ -22820,7 +22831,7 @@
         <v>44.54</v>
       </c>
     </row>
-    <row r="754" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A754" s="1">
         <v>44160</v>
       </c>
@@ -22849,7 +22860,7 @@
         <v>44.54</v>
       </c>
     </row>
-    <row r="755" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A755" s="1">
         <v>44167</v>
       </c>
@@ -22878,7 +22889,7 @@
         <v>38.9</v>
       </c>
     </row>
-    <row r="756" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="756" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A756" s="1">
         <v>44174</v>
       </c>
@@ -22907,7 +22918,7 @@
         <v>40.98</v>
       </c>
     </row>
-    <row r="757" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="757" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A757" s="1">
         <v>44181</v>
       </c>
@@ -22936,7 +22947,7 @@
         <v>42.33</v>
       </c>
     </row>
-    <row r="758" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="758" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A758" s="1">
         <v>44188</v>
       </c>
@@ -22965,7 +22976,7 @@
         <v>44.19</v>
       </c>
     </row>
-    <row r="759" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="759" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A759" s="1">
         <v>44195</v>
       </c>
@@ -22994,7 +23005,7 @@
         <v>47.07</v>
       </c>
     </row>
-    <row r="760" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="760" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A760" s="1">
         <v>44202</v>
       </c>
@@ -23023,7 +23034,7 @@
         <v>39.11</v>
       </c>
     </row>
-    <row r="761" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="761" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A761" s="1">
         <v>44209</v>
       </c>
@@ -23052,7 +23063,7 @@
         <v>39.85</v>
       </c>
     </row>
-    <row r="762" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="762" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A762" s="1">
         <v>44216</v>
       </c>
@@ -23081,7 +23092,7 @@
         <v>36.46</v>
       </c>
     </row>
-    <row r="763" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="763" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A763" s="1">
         <v>44223</v>
       </c>
@@ -23110,7 +23121,7 @@
         <v>53.82</v>
       </c>
     </row>
-    <row r="764" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="764" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A764" s="1">
         <v>44230</v>
       </c>
@@ -23139,7 +23150,7 @@
         <v>50.88</v>
       </c>
     </row>
-    <row r="765" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="765" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A765" s="1">
         <v>44237</v>
       </c>
@@ -23168,7 +23179,7 @@
         <v>29.44</v>
       </c>
     </row>
-    <row r="766" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="766" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A766" s="1">
         <v>44244</v>
       </c>
@@ -23197,7 +23208,7 @@
         <v>44.76</v>
       </c>
     </row>
-    <row r="767" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="767" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A767" s="1">
         <v>44251</v>
       </c>
@@ -23226,7 +23237,7 @@
         <v>48.64</v>
       </c>
     </row>
-    <row r="768" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="768" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A768" s="1">
         <v>44258</v>
       </c>
@@ -23255,7 +23266,7 @@
         <v>62.65</v>
       </c>
     </row>
-    <row r="769" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="769" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A769" s="1">
         <v>44265</v>
       </c>
@@ -23284,7 +23295,7 @@
         <v>54.1</v>
       </c>
     </row>
-    <row r="770" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="770" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A770" s="1">
         <v>44272</v>
       </c>
@@ -23313,7 +23324,7 @@
         <v>33.979999999999997</v>
       </c>
     </row>
-    <row r="771" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="771" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A771" s="1">
         <v>44279</v>
       </c>
@@ -23342,7 +23353,7 @@
         <v>42.24</v>
       </c>
     </row>
-    <row r="772" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="772" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A772" s="1">
         <v>44286</v>
       </c>
@@ -23371,7 +23382,7 @@
         <v>47.49</v>
       </c>
     </row>
-    <row r="773" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="773" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A773" s="1">
         <v>44293</v>
       </c>
@@ -23400,7 +23411,7 @@
         <v>35.159999999999997</v>
       </c>
     </row>
-    <row r="774" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="774" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A774" s="1">
         <v>44300</v>
       </c>
@@ -23429,7 +23440,7 @@
         <v>39.590000000000003</v>
       </c>
     </row>
-    <row r="775" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="775" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A775" s="1">
         <v>44307</v>
       </c>
@@ -23458,7 +23469,7 @@
         <v>39.06</v>
       </c>
     </row>
-    <row r="776" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="776" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A776" s="1">
         <v>44314</v>
       </c>
@@ -23487,7 +23498,7 @@
         <v>43.65</v>
       </c>
     </row>
-    <row r="777" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="777" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A777" s="1">
         <v>44321</v>
       </c>
@@ -23516,7 +23527,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="778" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="778" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A778" s="1">
         <v>44328</v>
       </c>
@@ -23545,7 +23556,7 @@
         <v>44.2</v>
       </c>
     </row>
-    <row r="779" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="779" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A779" s="1">
         <v>44335</v>
       </c>
@@ -23574,7 +23585,7 @@
         <v>35.25</v>
       </c>
     </row>
-    <row r="780" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="780" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A780" s="1">
         <v>44342</v>
       </c>
@@ -23603,7 +23614,7 @@
         <v>35.119999999999997</v>
       </c>
     </row>
-    <row r="781" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="781" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A781" s="1">
         <v>44349</v>
       </c>
@@ -23632,7 +23643,7 @@
         <v>35.83</v>
       </c>
     </row>
-    <row r="782" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="782" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A782" s="1">
         <v>44356</v>
       </c>
@@ -23661,7 +23672,7 @@
         <v>38.92</v>
       </c>
     </row>
-    <row r="783" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="783" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A783" s="1">
         <v>44363</v>
       </c>
@@ -23690,7 +23701,7 @@
         <v>34.159999999999997</v>
       </c>
     </row>
-    <row r="784" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="784" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A784" s="1">
         <v>44370</v>
       </c>
@@ -23719,7 +23730,7 @@
         <v>42.79</v>
       </c>
     </row>
-    <row r="785" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="785" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A785" s="1">
         <v>44377</v>
       </c>
@@ -23748,7 +23759,7 @@
         <v>38.18</v>
       </c>
     </row>
-    <row r="786" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="786" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A786" s="1">
         <v>44384</v>
       </c>
@@ -23777,7 +23788,7 @@
         <v>42.66</v>
       </c>
     </row>
-    <row r="787" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="787" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A787" s="1">
         <v>44391</v>
       </c>
@@ -23806,7 +23817,7 @@
         <v>37.85</v>
       </c>
     </row>
-    <row r="788" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="788" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A788" s="1">
         <v>44398</v>
       </c>
@@ -23835,7 +23846,7 @@
         <v>48.75</v>
       </c>
     </row>
-    <row r="789" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="789" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A789" s="1">
         <v>44405</v>
       </c>
@@ -23864,7 +23875,7 @@
         <v>43.07</v>
       </c>
     </row>
-    <row r="790" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="790" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A790" s="1">
         <v>44412</v>
       </c>
@@ -23893,7 +23904,7 @@
         <v>41.16</v>
       </c>
     </row>
-    <row r="791" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="791" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A791" s="1">
         <v>44419</v>
       </c>
@@ -23922,7 +23933,7 @@
         <v>38.54</v>
       </c>
     </row>
-    <row r="792" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="792" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A792" s="1">
         <v>44426</v>
       </c>
@@ -23951,7 +23962,7 @@
         <v>58.22</v>
       </c>
     </row>
-    <row r="793" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="793" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A793" s="1">
         <v>44433</v>
       </c>
@@ -23980,7 +23991,7 @@
         <v>37.950000000000003</v>
       </c>
     </row>
-    <row r="794" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="794" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A794" s="1">
         <v>44440</v>
       </c>
@@ -24009,7 +24020,7 @@
         <v>39.24</v>
       </c>
     </row>
-    <row r="795" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="795" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A795" s="1">
         <v>44447</v>
       </c>
@@ -24038,7 +24049,7 @@
         <v>43.85</v>
       </c>
     </row>
-    <row r="796" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="796" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A796" s="1">
         <v>44454</v>
       </c>
@@ -24067,7 +24078,7 @@
         <v>47.86</v>
       </c>
     </row>
-    <row r="797" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="797" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A797" s="1">
         <v>44461</v>
       </c>
@@ -24096,7 +24107,7 @@
         <v>47.37</v>
       </c>
     </row>
-    <row r="798" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="798" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A798" s="1">
         <v>44468</v>
       </c>
@@ -24125,7 +24136,7 @@
         <v>72.13</v>
       </c>
     </row>
-    <row r="799" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="799" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A799" s="1">
         <v>44475</v>
       </c>
@@ -24154,7 +24165,7 @@
         <v>51.09</v>
       </c>
     </row>
-    <row r="800" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="800" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A800" s="1">
         <v>44482</v>
       </c>
@@ -24183,7 +24194,7 @@
         <v>52.37</v>
       </c>
     </row>
-    <row r="801" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="801" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A801" s="1">
         <v>44489</v>
       </c>
@@ -24212,7 +24223,7 @@
         <v>33.46</v>
       </c>
     </row>
-    <row r="802" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="802" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A802" s="1">
         <v>44496</v>
       </c>
@@ -24241,7 +24252,7 @@
         <v>33.03</v>
       </c>
     </row>
-    <row r="803" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="803" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A803" s="1">
         <v>44503</v>
       </c>
@@ -24270,7 +24281,7 @@
         <v>37.31</v>
       </c>
     </row>
-    <row r="804" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="804" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A804" s="1">
         <v>44510</v>
       </c>
@@ -24299,7 +24310,7 @@
         <v>43.41</v>
       </c>
     </row>
-    <row r="805" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="805" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A805" s="1">
         <v>44517</v>
       </c>
@@ -24328,7 +24339,7 @@
         <v>47.38</v>
       </c>
     </row>
-    <row r="806" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="806" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A806" s="1">
         <v>44524</v>
       </c>
@@ -24357,7 +24368,7 @@
         <v>46.63</v>
       </c>
     </row>
-    <row r="807" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="807" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A807" s="1">
         <v>44531</v>
       </c>
@@ -24386,7 +24397,7 @@
         <v>59.91</v>
       </c>
     </row>
-    <row r="808" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="808" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A808" s="1">
         <v>44538</v>
       </c>
@@ -24415,7 +24426,7 @@
         <v>78.33</v>
       </c>
     </row>
-    <row r="809" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="809" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A809" s="1">
         <v>44545</v>
       </c>
@@ -24444,7 +24455,7 @@
         <v>61.89</v>
       </c>
     </row>
-    <row r="810" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="810" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A810" s="1">
         <v>44552</v>
       </c>
@@ -24473,7 +24484,7 @@
         <v>51.45</v>
       </c>
     </row>
-    <row r="811" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="811" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A811" s="1">
         <v>44559</v>
       </c>
@@ -24502,7 +24513,7 @@
         <v>38.94</v>
       </c>
     </row>
-    <row r="812" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="812" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A812" s="1">
         <v>44566</v>
       </c>
@@ -24531,7 +24542,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="813" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="813" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A813" s="1">
         <v>44573</v>
       </c>
@@ -24560,7 +24571,7 @@
         <v>66.02</v>
       </c>
     </row>
-    <row r="814" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="814" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A814" s="1">
         <v>44580</v>
       </c>
@@ -24589,7 +24600,7 @@
         <v>76.22</v>
       </c>
     </row>
-    <row r="815" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="815" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A815" s="1">
         <v>44587</v>
       </c>
@@ -24618,7 +24629,7 @@
         <v>66.22</v>
       </c>
     </row>
-    <row r="816" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="816" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A816" s="1">
         <v>44594</v>
       </c>
@@ -24647,7 +24658,7 @@
         <v>49.17</v>
       </c>
     </row>
-    <row r="817" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="817" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A817" s="1">
         <v>44601</v>
       </c>
@@ -24676,7 +24687,7 @@
         <v>40.53</v>
       </c>
     </row>
-    <row r="818" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="818" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A818" s="1">
         <v>44608</v>
       </c>
@@ -24705,7 +24716,7 @@
         <v>72.38</v>
       </c>
     </row>
-    <row r="819" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="819" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A819" s="1">
         <v>44615</v>
       </c>
@@ -24734,7 +24745,7 @@
         <v>71.64</v>
       </c>
     </row>
-    <row r="820" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="820" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A820" s="1">
         <v>44622</v>
       </c>
@@ -24763,7 +24774,7 @@
         <v>72.260000000000005</v>
       </c>
     </row>
-    <row r="821" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="821" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A821" s="1">
         <v>44629</v>
       </c>
@@ -24792,7 +24803,7 @@
         <v>70.959999999999994</v>
       </c>
     </row>
-    <row r="822" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="822" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A822" s="1">
         <v>44636</v>
       </c>
@@ -24821,7 +24832,7 @@
         <v>60.48</v>
       </c>
     </row>
-    <row r="823" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="823" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A823" s="1">
         <v>44643</v>
       </c>
@@ -24850,7 +24861,7 @@
         <v>65.23</v>
       </c>
     </row>
-    <row r="824" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="824" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A824" s="1">
         <v>44650</v>
       </c>
@@ -24879,7 +24890,7 @@
         <v>21.67</v>
       </c>
     </row>
-    <row r="825" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="825" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A825" s="1">
         <v>44657</v>
       </c>
@@ -24908,7 +24919,7 @@
         <v>40.35</v>
       </c>
     </row>
-    <row r="826" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="826" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A826" s="1">
         <v>44664</v>
       </c>
@@ -24937,7 +24948,7 @@
         <v>31.86</v>
       </c>
     </row>
-    <row r="827" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="827" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A827" s="1">
         <v>44671</v>
       </c>
@@ -24966,7 +24977,7 @@
         <v>28.88</v>
       </c>
     </row>
-    <row r="828" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="828" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A828" s="1">
         <v>44678</v>
       </c>
@@ -24995,7 +25006,7 @@
         <v>69.22</v>
       </c>
     </row>
-    <row r="829" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="829" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A829" s="1">
         <v>44685</v>
       </c>
@@ -25024,7 +25035,7 @@
         <v>45.33</v>
       </c>
     </row>
-    <row r="830" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="830" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A830" s="1">
         <v>44692</v>
       </c>
@@ -25053,7 +25064,7 @@
         <v>58.81</v>
       </c>
     </row>
-    <row r="831" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="831" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A831" s="1">
         <v>44699</v>
       </c>
@@ -25082,7 +25093,7 @@
         <v>44.74</v>
       </c>
     </row>
-    <row r="832" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="832" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A832" s="1">
         <v>44706</v>
       </c>
@@ -25111,7 +25122,7 @@
         <v>35.08</v>
       </c>
     </row>
-    <row r="833" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="833" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A833" s="1">
         <v>44713</v>
       </c>
@@ -25140,7 +25151,7 @@
         <v>74.08</v>
       </c>
     </row>
-    <row r="834" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="834" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A834" s="1">
         <v>44720</v>
       </c>
@@ -25169,7 +25180,7 @@
         <v>43.01</v>
       </c>
     </row>
-    <row r="835" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="835" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A835" s="1">
         <v>44727</v>
       </c>
@@ -25198,7 +25209,7 @@
         <v>50.59</v>
       </c>
     </row>
-    <row r="836" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="836" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A836" s="1">
         <v>44734</v>
       </c>
@@ -25227,7 +25238,7 @@
         <v>59.84</v>
       </c>
     </row>
-    <row r="837" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="837" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A837" s="1">
         <v>44741</v>
       </c>
@@ -25256,7 +25267,7 @@
         <v>51.78</v>
       </c>
     </row>
-    <row r="838" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="838" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A838" s="1">
         <v>44748</v>
       </c>
@@ -25285,7 +25296,7 @@
         <v>62.05</v>
       </c>
     </row>
-    <row r="839" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="839" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A839" s="1">
         <v>44755</v>
       </c>
@@ -25314,7 +25325,7 @@
         <v>58.93</v>
       </c>
     </row>
-    <row r="840" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="840" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A840" s="1">
         <v>44762</v>
       </c>
@@ -25343,7 +25354,7 @@
         <v>51.59</v>
       </c>
     </row>
-    <row r="841" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="841" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A841" s="1">
         <v>44769</v>
       </c>
@@ -25372,7 +25383,7 @@
         <v>50.16</v>
       </c>
     </row>
-    <row r="842" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="842" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A842" s="1">
         <v>44776</v>
       </c>
@@ -25401,7 +25412,7 @@
         <v>53.21</v>
       </c>
     </row>
-    <row r="843" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="843" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A843" s="1">
         <v>44783</v>
       </c>
@@ -25430,7 +25441,7 @@
         <v>54.24</v>
       </c>
     </row>
-    <row r="844" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="844" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A844" s="1">
         <v>44790</v>
       </c>
@@ -25459,7 +25470,7 @@
         <v>54.27</v>
       </c>
     </row>
-    <row r="845" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="845" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A845" s="1">
         <v>44797</v>
       </c>
@@ -25488,7 +25499,7 @@
         <v>59.7</v>
       </c>
     </row>
-    <row r="846" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="846" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A846" s="1">
         <v>44804</v>
       </c>
@@ -25517,7 +25528,7 @@
         <v>60.43</v>
       </c>
     </row>
-    <row r="847" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="847" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A847" s="1">
         <v>44811</v>
       </c>
@@ -25546,7 +25557,7 @@
         <v>60.04</v>
       </c>
     </row>
-    <row r="848" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="848" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A848" s="1">
         <v>44818</v>
       </c>
@@ -25575,7 +25586,7 @@
         <v>70.459999999999994</v>
       </c>
     </row>
-    <row r="849" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="849" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A849" s="1">
         <v>44825</v>
       </c>
@@ -25604,7 +25615,7 @@
         <v>60.97</v>
       </c>
     </row>
-    <row r="850" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="850" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A850" s="1">
         <v>44832</v>
       </c>
@@ -25633,7 +25644,7 @@
         <v>66.88</v>
       </c>
     </row>
-    <row r="851" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="851" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A851" s="1">
         <v>44839</v>
       </c>
@@ -25662,7 +25673,7 @@
         <v>58.96</v>
       </c>
     </row>
-    <row r="852" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="852" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A852" s="1">
         <v>44846</v>
       </c>
@@ -25691,7 +25702,7 @@
         <v>59.65</v>
       </c>
     </row>
-    <row r="853" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="853" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A853" s="1">
         <v>44853</v>
       </c>
@@ -25720,7 +25731,7 @@
         <v>55.43</v>
       </c>
     </row>
-    <row r="854" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="854" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A854" s="1">
         <v>44860</v>
       </c>
@@ -25749,7 +25760,7 @@
         <v>54.08</v>
       </c>
     </row>
-    <row r="855" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="855" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A855" s="1">
         <v>44867</v>
       </c>
@@ -25778,7 +25789,7 @@
         <v>59.48</v>
       </c>
     </row>
-    <row r="856" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="856" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A856" s="1">
         <v>44874</v>
       </c>
@@ -25807,7 +25818,7 @@
         <v>54.63</v>
       </c>
     </row>
-    <row r="857" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="857" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A857" s="1">
         <v>44881</v>
       </c>
@@ -25836,7 +25847,7 @@
         <v>60.66</v>
       </c>
     </row>
-    <row r="858" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="858" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A858" s="1">
         <v>44888</v>
       </c>
@@ -25865,7 +25876,7 @@
         <v>56.55</v>
       </c>
     </row>
-    <row r="859" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="859" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A859" s="1">
         <v>44895</v>
       </c>
@@ -25894,7 +25905,7 @@
         <v>50.1</v>
       </c>
     </row>
-    <row r="860" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="860" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A860" s="1">
         <v>44902</v>
       </c>
@@ -25923,7 +25934,7 @@
         <v>50.27</v>
       </c>
     </row>
-    <row r="861" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="861" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A861" s="1">
         <v>44909</v>
       </c>
@@ -25952,7 +25963,7 @@
         <v>48.94</v>
       </c>
     </row>
-    <row r="862" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="862" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A862" s="1">
         <v>44916</v>
       </c>
@@ -25981,7 +25992,7 @@
         <v>53.8</v>
       </c>
     </row>
-    <row r="863" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="863" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A863" s="1">
         <v>44923</v>
       </c>
@@ -26010,7 +26021,7 @@
         <v>46.68</v>
       </c>
     </row>
-    <row r="864" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="864" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A864" s="1">
         <v>44930</v>
       </c>
@@ -26039,7 +26050,7 @@
         <v>53.9</v>
       </c>
     </row>
-    <row r="865" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="865" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A865" s="1">
         <v>44937</v>
       </c>
@@ -26068,7 +26079,7 @@
         <v>39.74</v>
       </c>
     </row>
-    <row r="866" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="866" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A866" s="1">
         <v>44944</v>
       </c>
@@ -26097,7 +26108,7 @@
         <v>58.85</v>
       </c>
     </row>
-    <row r="867" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="867" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A867" s="1">
         <v>44951</v>
       </c>
@@ -26126,7 +26137,7 @@
         <v>45.01</v>
       </c>
     </row>
-    <row r="868" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="868" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A868" s="1">
         <v>44958</v>
       </c>
@@ -26155,7 +26166,7 @@
         <v>44.29</v>
       </c>
     </row>
-    <row r="869" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="869" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A869" s="1">
         <v>44965</v>
       </c>
@@ -26184,7 +26195,7 @@
         <v>44.25</v>
       </c>
     </row>
-    <row r="870" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="870" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A870" s="1">
         <v>44972</v>
       </c>
@@ -26213,7 +26224,7 @@
         <v>47.28</v>
       </c>
     </row>
-    <row r="871" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="871" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A871" s="1">
         <v>44979</v>
       </c>
@@ -26242,7 +26253,7 @@
         <v>71.14</v>
       </c>
     </row>
-    <row r="872" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="872" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A872" s="1">
         <v>44986</v>
       </c>
@@ -26271,7 +26282,7 @@
         <v>69.319999999999993</v>
       </c>
     </row>
-    <row r="873" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="873" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A873" s="1">
         <v>44993</v>
       </c>
@@ -26300,7 +26311,7 @@
         <v>63.44</v>
       </c>
     </row>
-    <row r="874" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="874" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A874" s="1">
         <v>45000</v>
       </c>
@@ -26329,7 +26340,7 @@
         <v>66.69</v>
       </c>
     </row>
-    <row r="875" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="875" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A875" s="1">
         <v>45007</v>
       </c>
@@ -26358,7 +26369,7 @@
         <v>57.12</v>
       </c>
     </row>
-    <row r="876" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="876" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A876" s="1">
         <v>45014</v>
       </c>
@@ -26387,7 +26398,7 @@
         <v>49.69</v>
       </c>
     </row>
-    <row r="877" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="877" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A877" s="1">
         <v>45021</v>
       </c>
@@ -26416,7 +26427,7 @@
         <v>45.38</v>
       </c>
     </row>
-    <row r="878" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="878" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A878" s="1">
         <v>45028</v>
       </c>
@@ -26445,7 +26456,7 @@
         <v>64.83</v>
       </c>
     </row>
-    <row r="879" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="879" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A879" s="1">
         <v>45035</v>
       </c>
@@ -26474,7 +26485,7 @@
         <v>39.61</v>
       </c>
     </row>
-    <row r="880" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="880" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A880" s="1">
         <v>45042</v>
       </c>
@@ -26503,7 +26514,7 @@
         <v>56.93</v>
       </c>
     </row>
-    <row r="881" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="881" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A881" s="1">
         <v>45049</v>
       </c>
@@ -26532,7 +26543,7 @@
         <v>43.05</v>
       </c>
     </row>
-    <row r="882" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="882" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A882" s="1">
         <v>45056</v>
       </c>
@@ -26561,7 +26572,7 @@
         <v>50.84</v>
       </c>
     </row>
-    <row r="883" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="883" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A883" s="1">
         <v>45063</v>
       </c>
@@ -26590,7 +26601,7 @@
         <v>48.49</v>
       </c>
     </row>
-    <row r="884" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="884" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A884" s="1">
         <v>45070</v>
       </c>
@@ -26619,7 +26630,7 @@
         <v>52.21</v>
       </c>
     </row>
-    <row r="885" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="885" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A885" s="1">
         <v>45077</v>
       </c>
@@ -26648,7 +26659,7 @@
         <v>59.12</v>
       </c>
     </row>
-    <row r="886" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="886" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A886" s="1">
         <v>45084</v>
       </c>
@@ -26677,7 +26688,7 @@
         <v>40.46</v>
       </c>
     </row>
-    <row r="887" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="887" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A887" s="1">
         <v>45091</v>
       </c>
@@ -26706,7 +26717,7 @@
         <v>56.21</v>
       </c>
     </row>
-    <row r="888" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="888" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A888" s="1">
         <v>45098</v>
       </c>
@@ -26735,7 +26746,7 @@
         <v>45.51</v>
       </c>
     </row>
-    <row r="889" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="889" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A889" s="1">
         <v>45105</v>
       </c>
@@ -26764,7 +26775,7 @@
         <v>54.14</v>
       </c>
     </row>
-    <row r="890" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="890" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A890" s="1">
         <v>45112</v>
       </c>
@@ -26793,7 +26804,7 @@
         <v>50.49</v>
       </c>
     </row>
-    <row r="891" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="891" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A891" s="1">
         <v>45119</v>
       </c>
@@ -26822,7 +26833,7 @@
         <v>44.26</v>
       </c>
     </row>
-    <row r="892" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="892" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A892" s="1">
         <v>45126</v>
       </c>
@@ -26851,7 +26862,7 @@
         <v>44.69</v>
       </c>
     </row>
-    <row r="893" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="893" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A893" s="1">
         <v>45133</v>
       </c>
@@ -26880,7 +26891,7 @@
         <v>36.340000000000003</v>
       </c>
     </row>
-    <row r="894" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="894" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A894" s="1">
         <v>45140</v>
       </c>
@@ -26909,7 +26920,7 @@
         <v>72.739999999999995</v>
       </c>
     </row>
-    <row r="895" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="895" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A895" s="1">
         <v>45147</v>
       </c>
@@ -26938,7 +26949,7 @@
         <v>63.43</v>
       </c>
     </row>
-    <row r="896" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="896" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A896" s="1">
         <v>45154</v>
       </c>
@@ -26967,7 +26978,7 @@
         <v>67.22</v>
       </c>
     </row>
-    <row r="897" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="897" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A897" s="1">
         <v>45161</v>
       </c>
@@ -26996,7 +27007,7 @@
         <v>79.38</v>
       </c>
     </row>
-    <row r="898" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="898" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A898" s="1">
         <v>45168</v>
       </c>
@@ -27025,7 +27036,7 @@
         <v>63.6</v>
       </c>
     </row>
-    <row r="899" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="899" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A899" s="1">
         <v>45175</v>
       </c>
@@ -27054,7 +27065,7 @@
         <v>70.89</v>
       </c>
     </row>
-    <row r="900" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="900" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A900" s="1">
         <v>45182</v>
       </c>
@@ -27083,7 +27094,7 @@
         <v>64.010000000000005</v>
       </c>
     </row>
-    <row r="901" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="901" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A901" s="1">
         <v>45189</v>
       </c>
@@ -27112,7 +27123,7 @@
         <v>53.81</v>
       </c>
     </row>
-    <row r="902" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="902" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A902" s="1">
         <v>45196</v>
       </c>
@@ -27141,7 +27152,7 @@
         <v>60.53</v>
       </c>
     </row>
-    <row r="903" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="903" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A903" s="1">
         <v>45203</v>
       </c>
@@ -27170,7 +27181,7 @@
         <v>74.3</v>
       </c>
     </row>
-    <row r="904" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="904" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A904" s="1">
         <v>45210</v>
       </c>
@@ -27199,7 +27210,7 @@
         <v>70.16</v>
       </c>
     </row>
-    <row r="905" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="905" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A905" s="1">
         <v>45217</v>
       </c>
@@ -27228,7 +27239,7 @@
         <v>60.7</v>
       </c>
     </row>
-    <row r="906" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="906" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A906" s="1">
         <v>45224</v>
       </c>
@@ -27257,7 +27268,7 @@
         <v>73.540000000000006</v>
       </c>
     </row>
-    <row r="907" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="907" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A907" s="1">
         <v>45231</v>
       </c>
@@ -27286,7 +27297,7 @@
         <v>71.180000000000007</v>
       </c>
     </row>
-    <row r="908" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="908" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A908" s="1">
         <v>45238</v>
       </c>
@@ -27315,7 +27326,7 @@
         <v>52.63</v>
       </c>
     </row>
-    <row r="909" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="909" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A909" s="1">
         <v>45245</v>
       </c>
@@ -27344,7 +27355,7 @@
         <v>70.599999999999994</v>
       </c>
     </row>
-    <row r="910" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="910" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A910" s="1">
         <v>45252</v>
       </c>
@@ -27373,7 +27384,7 @@
         <v>68.56</v>
       </c>
     </row>
-    <row r="911" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="911" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A911" s="1">
         <v>45259</v>
       </c>
@@ -27402,7 +27413,7 @@
         <v>64.95</v>
       </c>
     </row>
-    <row r="912" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="912" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A912" s="1">
         <v>45266</v>
       </c>
@@ -27431,7 +27442,7 @@
         <v>71.14</v>
       </c>
     </row>
-    <row r="913" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="913" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A913" s="1">
         <v>45273</v>
       </c>
@@ -27460,7 +27471,7 @@
         <v>69.78</v>
       </c>
     </row>
-    <row r="914" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="914" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A914" s="1">
         <v>45280</v>
       </c>
@@ -27489,7 +27500,7 @@
         <v>49.87</v>
       </c>
     </row>
-    <row r="915" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="915" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A915" s="1">
         <v>45287</v>
       </c>
@@ -27518,7 +27529,7 @@
         <v>48.43</v>
       </c>
     </row>
-    <row r="916" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="916" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A916" s="1">
         <v>45294</v>
       </c>
@@ -27547,7 +27558,7 @@
         <v>68.19</v>
       </c>
     </row>
-    <row r="917" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="917" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A917" s="1">
         <v>45301</v>
       </c>
@@ -27576,7 +27587,7 @@
         <v>43.94</v>
       </c>
     </row>
-    <row r="918" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="918" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A918" s="1">
         <v>45308</v>
       </c>
@@ -27605,7 +27616,7 @@
         <v>71.66</v>
       </c>
     </row>
-    <row r="919" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="919" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A919" s="1">
         <v>45315</v>
       </c>
@@ -27634,7 +27645,7 @@
         <v>70.540000000000006</v>
       </c>
     </row>
-    <row r="920" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="920" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A920" s="1">
         <v>45322</v>
       </c>
@@ -27663,7 +27674,7 @@
         <v>67.72</v>
       </c>
     </row>
-    <row r="921" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="921" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A921" s="1">
         <v>45329</v>
       </c>
@@ -27692,7 +27703,7 @@
         <v>40.520000000000003</v>
       </c>
     </row>
-    <row r="922" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="922" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A922" s="1">
         <v>45336</v>
       </c>
@@ -27721,7 +27732,7 @@
         <v>42.93</v>
       </c>
     </row>
-    <row r="923" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="923" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A923" s="1">
         <v>45343</v>
       </c>
@@ -27750,7 +27761,7 @@
         <v>87.34</v>
       </c>
     </row>
-    <row r="924" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="924" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A924" s="1">
         <v>45350</v>
       </c>
@@ -27779,7 +27790,7 @@
         <v>63.8</v>
       </c>
     </row>
-    <row r="925" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="925" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A925" s="1">
         <v>45357</v>
       </c>
@@ -27808,7 +27819,7 @@
         <v>43.54</v>
       </c>
     </row>
-    <row r="926" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="926" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A926" s="1">
         <v>45364</v>
       </c>
@@ -27837,7 +27848,7 @@
         <v>45.2</v>
       </c>
     </row>
-    <row r="927" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="927" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A927" s="1">
         <v>45371</v>
       </c>
@@ -27866,7 +27877,7 @@
         <v>71.209999999999994</v>
       </c>
     </row>
-    <row r="928" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="928" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A928" s="1">
         <v>45378</v>
       </c>
@@ -27895,7 +27906,7 @@
         <v>31.21</v>
       </c>
     </row>
-    <row r="929" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="929" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A929" s="1">
         <v>45385</v>
       </c>
@@ -27924,7 +27935,7 @@
         <v>68.209999999999994</v>
       </c>
     </row>
-    <row r="930" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="930" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A930" s="1">
         <v>45392</v>
       </c>
@@ -27953,7 +27964,7 @@
         <v>65.73</v>
       </c>
     </row>
-    <row r="931" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="931" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A931" s="1">
         <v>45399</v>
       </c>
@@ -27982,7 +27993,7 @@
         <v>71.42</v>
       </c>
     </row>
-    <row r="932" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="932" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A932" s="1">
         <v>45406</v>
       </c>
@@ -28011,7 +28022,7 @@
         <v>70.790000000000006</v>
       </c>
     </row>
-    <row r="933" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="933" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A933" s="1">
         <v>45413</v>
       </c>
@@ -28040,7 +28051,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="934" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="934" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A934" s="1">
         <v>45420</v>
       </c>
@@ -28069,7 +28080,7 @@
         <v>59.39</v>
       </c>
     </row>
-    <row r="935" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="935" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A935" s="1">
         <v>45427</v>
       </c>
@@ -28098,7 +28109,7 @@
         <v>71.739999999999995</v>
       </c>
     </row>
-    <row r="936" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="936" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A936" s="1">
         <v>45434</v>
       </c>
@@ -28127,7 +28138,7 @@
         <v>72.540000000000006</v>
       </c>
     </row>
-    <row r="937" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="937" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A937" s="1">
         <v>45441</v>
       </c>
@@ -28156,7 +28167,7 @@
         <v>78.959999999999994</v>
       </c>
     </row>
-    <row r="938" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="938" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A938" s="1">
         <v>45448</v>
       </c>
@@ -28185,7 +28196,7 @@
         <v>90.94</v>
       </c>
     </row>
-    <row r="939" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="939" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A939" s="1">
         <v>45455</v>
       </c>
@@ -28214,7 +28225,7 @@
         <v>56.33</v>
       </c>
     </row>
-    <row r="940" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="940" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A940" s="1">
         <v>45462</v>
       </c>
@@ -28243,7 +28254,7 @@
         <v>74.87</v>
       </c>
     </row>
-    <row r="941" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="941" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A941" s="1">
         <v>45469</v>
       </c>
@@ -28272,7 +28283,7 @@
         <v>58.35</v>
       </c>
     </row>
-    <row r="942" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="942" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A942" s="1">
         <v>45476</v>
       </c>
@@ -28301,7 +28312,7 @@
         <v>55.2</v>
       </c>
     </row>
-    <row r="943" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="943" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A943" s="1">
         <v>45483</v>
       </c>
@@ -28330,7 +28341,7 @@
         <v>71.989999999999995</v>
       </c>
     </row>
-    <row r="944" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="944" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A944" s="1">
         <v>45490</v>
       </c>
@@ -28359,7 +28370,7 @@
         <v>71.55</v>
       </c>
     </row>
-    <row r="945" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="945" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A945" s="1">
         <v>45497</v>
       </c>
@@ -28388,7 +28399,7 @@
         <v>54.03</v>
       </c>
     </row>
-    <row r="946" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="946" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A946" s="1">
         <v>45504</v>
       </c>
@@ -28417,7 +28428,7 @@
         <v>62.38</v>
       </c>
     </row>
-    <row r="947" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="947" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A947" s="1">
         <v>45511</v>
       </c>
@@ -28446,7 +28457,7 @@
         <v>60.29</v>
       </c>
     </row>
-    <row r="948" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="948" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A948" s="1">
         <v>45518</v>
       </c>
@@ -28475,7 +28486,7 @@
         <v>89.06</v>
       </c>
     </row>
-    <row r="949" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="949" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A949" s="1">
         <v>45525</v>
       </c>
@@ -28504,7 +28515,7 @@
         <v>67.78</v>
       </c>
     </row>
-    <row r="950" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="950" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A950" s="1">
         <v>45532</v>
       </c>
@@ -28533,7 +28544,7 @@
         <v>76.260000000000005</v>
       </c>
     </row>
-    <row r="951" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="951" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A951" s="1">
         <v>45539</v>
       </c>
@@ -28562,7 +28573,7 @@
         <v>70.38</v>
       </c>
     </row>
-    <row r="952" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="952" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A952" s="1">
         <v>45546</v>
       </c>
@@ -28591,7 +28602,7 @@
         <v>70.66</v>
       </c>
     </row>
-    <row r="953" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="953" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A953" s="1">
         <v>45553</v>
       </c>
@@ -28620,7 +28631,7 @@
         <v>69.36</v>
       </c>
     </row>
-    <row r="954" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="954" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A954" s="1">
         <v>45560</v>
       </c>
@@ -28649,7 +28660,7 @@
         <v>75.61</v>
       </c>
     </row>
-    <row r="955" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="955" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A955" s="1">
         <v>45567</v>
       </c>
@@ -28678,7 +28689,7 @@
         <v>56.15</v>
       </c>
     </row>
-    <row r="956" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="956" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A956" s="1">
         <v>45574</v>
       </c>
@@ -28707,7 +28718,7 @@
         <v>54.22</v>
       </c>
     </row>
-    <row r="957" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="957" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A957" s="1">
         <v>45581</v>
       </c>
@@ -28736,7 +28747,7 @@
         <v>70.319999999999993</v>
       </c>
     </row>
-    <row r="958" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="958" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A958" s="1">
         <v>45588</v>
       </c>
@@ -28765,7 +28776,7 @@
         <v>75.64</v>
       </c>
     </row>
-    <row r="959" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="959" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A959" s="1">
         <v>45595</v>
       </c>
@@ -28794,7 +28805,7 @@
         <v>60.95</v>
       </c>
     </row>
-    <row r="960" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="960" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A960" s="1">
         <v>45602</v>
       </c>
@@ -28823,7 +28834,7 @@
         <v>56.27</v>
       </c>
     </row>
-    <row r="961" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="961" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A961" s="1">
         <v>45609</v>
       </c>
@@ -28852,7 +28863,7 @@
         <v>66.66</v>
       </c>
     </row>
-    <row r="962" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="962" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A962" s="1">
         <v>45616</v>
       </c>
@@ -28881,7 +28892,7 @@
         <v>55.21</v>
       </c>
     </row>
-    <row r="963" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="963" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A963" s="1">
         <v>45623</v>
       </c>
@@ -28910,7 +28921,7 @@
         <v>44.97</v>
       </c>
     </row>
-    <row r="964" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="964" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A964" s="1">
         <v>45630</v>
       </c>
@@ -28939,7 +28950,7 @@
         <v>65.58</v>
       </c>
     </row>
-    <row r="965" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="965" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A965" s="1">
         <v>45637</v>
       </c>
@@ -28968,7 +28979,7 @@
         <v>50.55</v>
       </c>
     </row>
-    <row r="966" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="966" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A966" s="1">
         <v>45644</v>
       </c>
@@ -28997,7 +29008,7 @@
         <v>55.02</v>
       </c>
     </row>
-    <row r="967" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="967" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A967" s="1">
         <v>45651</v>
       </c>
@@ -29026,7 +29037,7 @@
         <v>72.16</v>
       </c>
     </row>
-    <row r="968" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="968" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A968" s="1">
         <v>45658</v>
       </c>
@@ -29055,7 +29066,7 @@
         <v>90.01</v>
       </c>
     </row>
-    <row r="969" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="969" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A969" s="1">
         <v>45665</v>
       </c>
@@ -29084,7 +29095,7 @@
         <v>55.05</v>
       </c>
     </row>
-    <row r="970" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="970" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A970" s="1">
         <v>45672</v>
       </c>
@@ -29113,7 +29124,7 @@
         <v>58.09</v>
       </c>
     </row>
-    <row r="971" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="971" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A971" s="1">
         <v>45679</v>
       </c>
@@ -29142,7 +29153,7 @@
         <v>45.88</v>
       </c>
     </row>
-    <row r="972" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="972" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A972" s="1">
         <v>45686</v>
       </c>
@@ -29171,7 +29182,7 @@
         <v>65.86</v>
       </c>
     </row>
-    <row r="973" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="973" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A973" s="1">
         <v>45693</v>
       </c>
@@ -29200,7 +29211,7 @@
         <v>54.2</v>
       </c>
     </row>
-    <row r="974" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="974" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A974" s="1">
         <v>45700</v>
       </c>
@@ -29229,7 +29240,7 @@
         <v>52.44</v>
       </c>
     </row>
-    <row r="975" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="975" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A975" s="1">
         <v>45707</v>
       </c>
@@ -29258,7 +29269,7 @@
         <v>49.61</v>
       </c>
     </row>
-    <row r="976" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="976" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A976" s="1">
         <v>45714</v>
       </c>
@@ -29287,7 +29298,7 @@
         <v>51.43</v>
       </c>
     </row>
-    <row r="977" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="977" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A977" s="1">
         <v>45721</v>
       </c>
@@ -29316,7 +29327,7 @@
         <v>69.739999999999995</v>
       </c>
     </row>
-    <row r="978" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="978" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A978" s="1">
         <v>45728</v>
       </c>
@@ -29345,7 +29356,7 @@
         <v>70.47</v>
       </c>
     </row>
-    <row r="979" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="979" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A979" s="1">
         <v>45735</v>
       </c>
@@ -29374,7 +29385,7 @@
         <v>53.55</v>
       </c>
     </row>
-    <row r="980" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="980" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A980" s="1">
         <v>45742</v>
       </c>
@@ -29403,7 +29414,7 @@
         <v>54.17</v>
       </c>
     </row>
-    <row r="981" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="981" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A981" s="1">
         <v>45749</v>
       </c>
@@ -29432,7 +29443,7 @@
         <v>83.68</v>
       </c>
     </row>
-    <row r="982" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="982" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A982" s="1">
         <v>45756</v>
       </c>
@@ -29461,7 +29472,7 @@
         <v>60.04</v>
       </c>
     </row>
-    <row r="983" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="983" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A983" s="1">
         <v>45763</v>
       </c>
@@ -29490,7 +29501,7 @@
         <v>65.53</v>
       </c>
     </row>
-    <row r="984" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="984" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A984" s="1">
         <v>45770</v>
       </c>
@@ -29519,7 +29530,7 @@
         <v>50.87</v>
       </c>
     </row>
-    <row r="985" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="985" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A985" s="1">
         <v>45777</v>
       </c>
@@ -29548,7 +29559,7 @@
         <v>77.239999999999995</v>
       </c>
     </row>
-    <row r="986" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="986" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A986" s="1">
         <v>45784</v>
       </c>
@@ -29577,7 +29588,7 @@
         <v>51.46</v>
       </c>
     </row>
-    <row r="987" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="987" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A987" s="1">
         <v>45791</v>
       </c>
@@ -29606,7 +29617,7 @@
         <v>65.03</v>
       </c>
     </row>
-    <row r="988" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="988" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A988" s="1">
         <v>45798</v>
       </c>
@@ -29635,7 +29646,7 @@
         <v>60.35</v>
       </c>
     </row>
-    <row r="989" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="989" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A989" s="1">
         <v>45805</v>
       </c>
@@ -29664,7 +29675,7 @@
         <v>53.2</v>
       </c>
     </row>
-    <row r="990" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="990" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A990" s="1">
         <v>45812</v>
       </c>
@@ -29693,7 +29704,7 @@
         <v>67.680000000000007</v>
       </c>
     </row>
-    <row r="991" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="991" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A991" s="1">
         <v>45819</v>
       </c>
@@ -29722,7 +29733,7 @@
         <v>73.680000000000007</v>
       </c>
     </row>
-    <row r="992" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="992" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A992" s="1">
         <v>45826</v>
       </c>
@@ -29751,7 +29762,7 @@
         <v>52.15</v>
       </c>
     </row>
-    <row r="993" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="993" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A993" s="1">
         <v>45833</v>
       </c>
@@ -29780,7 +29791,7 @@
         <v>72.73</v>
       </c>
     </row>
-    <row r="994" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="994" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A994" s="1">
         <v>45840</v>
       </c>
@@ -29809,7 +29820,7 @@
         <v>54.77</v>
       </c>
     </row>
-    <row r="995" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="995" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A995" s="1">
         <v>45847</v>
       </c>
@@ -29838,7 +29849,7 @@
         <v>69.709999999999994</v>
       </c>
     </row>
-    <row r="996" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="996" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A996" s="1">
         <v>45854</v>
       </c>
@@ -29867,7 +29878,7 @@
         <v>57.22</v>
       </c>
     </row>
-    <row r="997" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="997" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A997" s="1">
         <v>45861</v>
       </c>
@@ -29896,7 +29907,7 @@
         <v>64.98</v>
       </c>
     </row>
-    <row r="998" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="998" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A998" s="1">
         <v>45868</v>
       </c>
@@ -29925,7 +29936,7 @@
         <v>64.89</v>
       </c>
     </row>
-    <row r="999" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="999" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A999" s="1">
         <v>45875</v>
       </c>
@@ -29954,7 +29965,7 @@
         <v>35.96</v>
       </c>
     </row>
-    <row r="1000" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1000" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1000" s="1">
         <v>45882</v>
       </c>
@@ -29983,7 +29994,7 @@
         <v>69.55</v>
       </c>
     </row>
-    <row r="1001" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1001" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1001" s="1">
         <v>45889</v>
       </c>
@@ -30012,7 +30023,7 @@
         <v>44.79</v>
       </c>
     </row>
-    <row r="1002" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1002" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1002" s="1">
         <v>45896</v>
       </c>
@@ -30041,7 +30052,7 @@
         <v>44.7</v>
       </c>
     </row>
-    <row r="1003" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1003" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1003" s="1">
         <v>45903</v>
       </c>
@@ -30070,7 +30081,7 @@
         <v>63.56</v>
       </c>
     </row>
-    <row r="1004" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1004" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1004" s="1">
         <v>45910</v>
       </c>
@@ -30099,7 +30110,7 @@
         <v>71.06</v>
       </c>
     </row>
-    <row r="1005" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1005" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1005" s="1">
         <v>45917</v>
       </c>
@@ -30128,7 +30139,7 @@
         <v>71.959999999999994</v>
       </c>
     </row>
-    <row r="1006" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1006" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1006" s="1">
         <v>45924</v>
       </c>
@@ -30157,7 +30168,7 @@
         <v>66.77</v>
       </c>
     </row>
-    <row r="1007" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1007" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1007" s="1">
         <v>45931</v>
       </c>
@@ -30186,7 +30197,7 @@
         <v>71.13</v>
       </c>
     </row>
-    <row r="1008" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1008" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1008" s="1">
         <v>45938</v>
       </c>
@@ -30215,7 +30226,7 @@
         <v>69.27</v>
       </c>
     </row>
-    <row r="1009" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1009" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1009" s="1">
         <v>45945</v>
       </c>
@@ -30244,7 +30255,7 @@
         <v>50.98</v>
       </c>
     </row>
-    <row r="1010" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1010" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1010" s="1">
         <v>45952</v>
       </c>
@@ -30273,7 +30284,7 @@
         <v>52.1</v>
       </c>
     </row>
-    <row r="1011" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1011" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1011" s="1">
         <v>45959</v>
       </c>
@@ -30302,7 +30313,7 @@
         <v>55.36</v>
       </c>
     </row>
-    <row r="1012" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1012" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1012" s="1">
         <v>45966</v>
       </c>
@@ -30331,7 +30342,7 @@
         <v>40.86</v>
       </c>
     </row>
-    <row r="1013" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1013" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1013" s="1">
         <v>45973</v>
       </c>
@@ -30360,7 +30371,7 @@
         <v>39.42</v>
       </c>
     </row>
-    <row r="1014" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1014" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1014" s="1">
         <v>45980</v>
       </c>
@@ -30389,7 +30400,7 @@
         <v>51.59</v>
       </c>
     </row>
-    <row r="1015" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1015" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1015" s="1">
         <v>45987</v>
       </c>
@@ -30418,7 +30429,7 @@
         <v>50.29</v>
       </c>
     </row>
-    <row r="1016" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1016" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1016" s="1">
         <v>45994</v>
       </c>
@@ -30447,7 +30458,7 @@
         <v>47.59</v>
       </c>
     </row>
-    <row r="1017" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1017" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1017" s="1">
         <v>46001</v>
       </c>
@@ -30476,7 +30487,7 @@
         <v>45.89</v>
       </c>
     </row>
-    <row r="1018" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1018" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1018" s="1">
         <v>46008</v>
       </c>
@@ -30505,7 +30516,7 @@
         <v>46.38</v>
       </c>
     </row>
-    <row r="1019" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1019" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1019" s="1">
         <v>46015</v>
       </c>
@@ -30532,6 +30543,35 @@
       </c>
       <c r="I1019" s="6">
         <v>49.27</v>
+      </c>
+    </row>
+    <row r="1020" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1020" s="1">
+        <v>46022</v>
+      </c>
+      <c r="B1020" s="1">
+        <v>46023</v>
+      </c>
+      <c r="C1020" s="6">
+        <v>92.93</v>
+      </c>
+      <c r="D1020" s="9">
+        <v>0</v>
+      </c>
+      <c r="E1020" s="6">
+        <v>81.25</v>
+      </c>
+      <c r="F1020" s="6">
+        <v>100</v>
+      </c>
+      <c r="G1020" s="6">
+        <v>100</v>
+      </c>
+      <c r="H1020" s="6">
+        <v>200</v>
+      </c>
+      <c r="I1020" s="6">
+        <v>48.97</v>
       </c>
     </row>
   </sheetData>
@@ -30544,17 +30584,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44703C2A-D4C6-BD4F-B5E9-874C8C9CFE9E}">
   <dimension ref="B2:C3"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="11" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B3" t="s">
         <v>9</v>
       </c>
@@ -30564,6 +30604,9 @@
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{A82A1AB3-CBB7-F444-B7E1-7D406688AF01}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/sentiment/NAAIM Exposure Index.xlsx
+++ b/data/sentiment/NAAIM Exposure Index.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\sentiment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD36149F-7302-439E-9532-07FA8CA89DD9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74309A08-C248-4F5A-985C-2DAC75F38716}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16155" yWindow="780" windowWidth="19845" windowHeight="20700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="16155" yWindow="780" windowWidth="19845" windowHeight="20700" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NAAIM" sheetId="1" r:id="rId1"/>
-    <sheet name="info" sheetId="2" r:id="rId2"/>
+    <sheet name="fig" sheetId="3" r:id="rId2"/>
+    <sheet name="info" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
 </workbook>
@@ -82,7 +83,7 @@
     <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="178" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="179" formatCode="0.00_ "/>
-    <numFmt numFmtId="183" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="180" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
   <fonts count="22" x14ac:knownFonts="1">
     <font>
@@ -630,10 +631,10 @@
     <xf numFmtId="177" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="183" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="183" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -694,6 +695,7044 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ko-KR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>NAAIM Index</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>NAAIM!$B$2:$B$1030</c:f>
+              <c:numCache>
+                <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
+                <c:ptCount val="1029"/>
+                <c:pt idx="0">
+                  <c:v>38904</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>38911</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>38904</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>38911</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>38918</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>38925</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>38932</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>38939</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>38946</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>38953</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>38960</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>38967</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>38974</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>38981</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>38988</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>38995</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>39002</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>39009</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>39016</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>39023</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>39030</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>39037</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>39044</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>39051</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>39058</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>39065</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>39072</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>39079</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>39086</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>39093</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>39100</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>39107</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>39114</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>39121</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>39128</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>39135</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>39142</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>39149</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>39156</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>39163</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>39170</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>39177</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>39184</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>39191</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>39198</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>39205</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>39212</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>39219</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>39226</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>39233</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>39240</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>39247</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>39254</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>39261</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>39269</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>39275</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>39282</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>39289</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>39296</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>39303</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>39310</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>39317</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>39324</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>39331</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>39338</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>39345</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>39352</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>39359</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>39366</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>39373</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>39380</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>39387</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>39394</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>39401</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>39408</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>39415</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>39422</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>39429</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>39436</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>39443</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>39450</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>39457</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>39464</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>39471</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>39478</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>39485</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>39492</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>39499</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>39506</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>39513</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>39520</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>39527</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>39534</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>39541</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>39548</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>39555</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>39562</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>39570</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>39576</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>39583</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>39590</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>39597</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>39604</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>39611</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>39618</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>39625</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>39632</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>39639</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>39646</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>39653</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>39660</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>39667</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>39674</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>39682</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>39688</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>39695</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>39702</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>39709</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>39716</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>39723</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>39730</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>39737</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>39744</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>39751</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>39758</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>39765</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>39772</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>39779</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>39786</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>39793</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>39800</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>39807</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>39814</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>39821</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>39828</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>39835</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>39842</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>39849</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>39856</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>39863</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>39870</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>39877</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>39884</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>39891</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>39898</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>39905</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>39912</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>39919</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>39926</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>39933</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>39940</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>39947</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>39954</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>39961</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>39968</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>39975</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>39982</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>39989</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>39996</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>40003</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>40010</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>40017</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>40024</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>40031</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>40038</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>40045</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>40052</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>40059</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>40066</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>40073</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>40080</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>40087</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>40094</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>40101</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>40108</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>40115</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>40122</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>40129</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>40136</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>40143</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>40150</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>40157</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>40164</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>40171</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>40178</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>40185</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>40192</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>40199</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>40206</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>40213</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>40220</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>40227</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>40234</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>40241</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>40248</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>40255</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>40262</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>40269</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>40276</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>40283</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>40290</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>40297</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>40304</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>40311</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>40318</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>40325</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>40332</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>40339</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>40346</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>40353</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>40360</c:v>
+                </c:pt>
+                <c:pt idx="211">
+                  <c:v>40367</c:v>
+                </c:pt>
+                <c:pt idx="212">
+                  <c:v>40374</c:v>
+                </c:pt>
+                <c:pt idx="213">
+                  <c:v>40381</c:v>
+                </c:pt>
+                <c:pt idx="214">
+                  <c:v>40388</c:v>
+                </c:pt>
+                <c:pt idx="215">
+                  <c:v>40395</c:v>
+                </c:pt>
+                <c:pt idx="216">
+                  <c:v>40402</c:v>
+                </c:pt>
+                <c:pt idx="217">
+                  <c:v>40409</c:v>
+                </c:pt>
+                <c:pt idx="218">
+                  <c:v>40416</c:v>
+                </c:pt>
+                <c:pt idx="219">
+                  <c:v>40423</c:v>
+                </c:pt>
+                <c:pt idx="220">
+                  <c:v>40430</c:v>
+                </c:pt>
+                <c:pt idx="221">
+                  <c:v>40437</c:v>
+                </c:pt>
+                <c:pt idx="222">
+                  <c:v>40444</c:v>
+                </c:pt>
+                <c:pt idx="223">
+                  <c:v>40451</c:v>
+                </c:pt>
+                <c:pt idx="224">
+                  <c:v>40458</c:v>
+                </c:pt>
+                <c:pt idx="225">
+                  <c:v>40465</c:v>
+                </c:pt>
+                <c:pt idx="226">
+                  <c:v>40472</c:v>
+                </c:pt>
+                <c:pt idx="227">
+                  <c:v>40479</c:v>
+                </c:pt>
+                <c:pt idx="228">
+                  <c:v>40486</c:v>
+                </c:pt>
+                <c:pt idx="229">
+                  <c:v>40494</c:v>
+                </c:pt>
+                <c:pt idx="230">
+                  <c:v>40500</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>40507</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>40514</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>40521</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>40528</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>40535</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>40542</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>40549</c:v>
+                </c:pt>
+                <c:pt idx="238">
+                  <c:v>40556</c:v>
+                </c:pt>
+                <c:pt idx="239">
+                  <c:v>40563</c:v>
+                </c:pt>
+                <c:pt idx="240">
+                  <c:v>40570</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>40577</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>40584</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>40591</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>40598</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>40605</c:v>
+                </c:pt>
+                <c:pt idx="246">
+                  <c:v>40612</c:v>
+                </c:pt>
+                <c:pt idx="247">
+                  <c:v>40619</c:v>
+                </c:pt>
+                <c:pt idx="248">
+                  <c:v>40626</c:v>
+                </c:pt>
+                <c:pt idx="249">
+                  <c:v>40633</c:v>
+                </c:pt>
+                <c:pt idx="250">
+                  <c:v>40640</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>40647</c:v>
+                </c:pt>
+                <c:pt idx="252">
+                  <c:v>40654</c:v>
+                </c:pt>
+                <c:pt idx="253">
+                  <c:v>40661</c:v>
+                </c:pt>
+                <c:pt idx="254">
+                  <c:v>40668</c:v>
+                </c:pt>
+                <c:pt idx="255">
+                  <c:v>40675</c:v>
+                </c:pt>
+                <c:pt idx="256">
+                  <c:v>40682</c:v>
+                </c:pt>
+                <c:pt idx="257">
+                  <c:v>40689</c:v>
+                </c:pt>
+                <c:pt idx="258">
+                  <c:v>40696</c:v>
+                </c:pt>
+                <c:pt idx="259">
+                  <c:v>40703</c:v>
+                </c:pt>
+                <c:pt idx="260">
+                  <c:v>40710</c:v>
+                </c:pt>
+                <c:pt idx="261">
+                  <c:v>40717</c:v>
+                </c:pt>
+                <c:pt idx="262">
+                  <c:v>40724</c:v>
+                </c:pt>
+                <c:pt idx="263">
+                  <c:v>40731</c:v>
+                </c:pt>
+                <c:pt idx="264">
+                  <c:v>40738</c:v>
+                </c:pt>
+                <c:pt idx="265">
+                  <c:v>40745</c:v>
+                </c:pt>
+                <c:pt idx="266">
+                  <c:v>40752</c:v>
+                </c:pt>
+                <c:pt idx="267">
+                  <c:v>40759</c:v>
+                </c:pt>
+                <c:pt idx="268">
+                  <c:v>40766</c:v>
+                </c:pt>
+                <c:pt idx="269">
+                  <c:v>40773</c:v>
+                </c:pt>
+                <c:pt idx="270">
+                  <c:v>40780</c:v>
+                </c:pt>
+                <c:pt idx="271">
+                  <c:v>40787</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>40794</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>40801</c:v>
+                </c:pt>
+                <c:pt idx="274">
+                  <c:v>40808</c:v>
+                </c:pt>
+                <c:pt idx="275">
+                  <c:v>40815</c:v>
+                </c:pt>
+                <c:pt idx="276">
+                  <c:v>40822</c:v>
+                </c:pt>
+                <c:pt idx="277">
+                  <c:v>40829</c:v>
+                </c:pt>
+                <c:pt idx="278">
+                  <c:v>40836</c:v>
+                </c:pt>
+                <c:pt idx="279">
+                  <c:v>40843</c:v>
+                </c:pt>
+                <c:pt idx="280">
+                  <c:v>40850</c:v>
+                </c:pt>
+                <c:pt idx="281">
+                  <c:v>40857</c:v>
+                </c:pt>
+                <c:pt idx="282">
+                  <c:v>40864</c:v>
+                </c:pt>
+                <c:pt idx="283">
+                  <c:v>40871</c:v>
+                </c:pt>
+                <c:pt idx="284">
+                  <c:v>40878</c:v>
+                </c:pt>
+                <c:pt idx="285">
+                  <c:v>40885</c:v>
+                </c:pt>
+                <c:pt idx="286">
+                  <c:v>40892</c:v>
+                </c:pt>
+                <c:pt idx="287">
+                  <c:v>40899</c:v>
+                </c:pt>
+                <c:pt idx="288">
+                  <c:v>40906</c:v>
+                </c:pt>
+                <c:pt idx="289">
+                  <c:v>40913</c:v>
+                </c:pt>
+                <c:pt idx="290">
+                  <c:v>40920</c:v>
+                </c:pt>
+                <c:pt idx="291">
+                  <c:v>40927</c:v>
+                </c:pt>
+                <c:pt idx="292">
+                  <c:v>40934</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>40941</c:v>
+                </c:pt>
+                <c:pt idx="294">
+                  <c:v>40948</c:v>
+                </c:pt>
+                <c:pt idx="295">
+                  <c:v>40955</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>40962</c:v>
+                </c:pt>
+                <c:pt idx="297">
+                  <c:v>40969</c:v>
+                </c:pt>
+                <c:pt idx="298">
+                  <c:v>40976</c:v>
+                </c:pt>
+                <c:pt idx="299">
+                  <c:v>40983</c:v>
+                </c:pt>
+                <c:pt idx="300">
+                  <c:v>40990</c:v>
+                </c:pt>
+                <c:pt idx="301">
+                  <c:v>40997</c:v>
+                </c:pt>
+                <c:pt idx="302">
+                  <c:v>41004</c:v>
+                </c:pt>
+                <c:pt idx="303">
+                  <c:v>41011</c:v>
+                </c:pt>
+                <c:pt idx="304">
+                  <c:v>41018</c:v>
+                </c:pt>
+                <c:pt idx="305">
+                  <c:v>41025</c:v>
+                </c:pt>
+                <c:pt idx="306">
+                  <c:v>41032</c:v>
+                </c:pt>
+                <c:pt idx="307">
+                  <c:v>41039</c:v>
+                </c:pt>
+                <c:pt idx="308">
+                  <c:v>41046</c:v>
+                </c:pt>
+                <c:pt idx="309">
+                  <c:v>41053</c:v>
+                </c:pt>
+                <c:pt idx="310">
+                  <c:v>41060</c:v>
+                </c:pt>
+                <c:pt idx="311">
+                  <c:v>41067</c:v>
+                </c:pt>
+                <c:pt idx="312">
+                  <c:v>41074</c:v>
+                </c:pt>
+                <c:pt idx="313">
+                  <c:v>41081</c:v>
+                </c:pt>
+                <c:pt idx="314">
+                  <c:v>41088</c:v>
+                </c:pt>
+                <c:pt idx="315">
+                  <c:v>41096</c:v>
+                </c:pt>
+                <c:pt idx="316">
+                  <c:v>41102</c:v>
+                </c:pt>
+                <c:pt idx="317">
+                  <c:v>41109</c:v>
+                </c:pt>
+                <c:pt idx="318">
+                  <c:v>41116</c:v>
+                </c:pt>
+                <c:pt idx="319">
+                  <c:v>41123</c:v>
+                </c:pt>
+                <c:pt idx="320">
+                  <c:v>41130</c:v>
+                </c:pt>
+                <c:pt idx="321">
+                  <c:v>41137</c:v>
+                </c:pt>
+                <c:pt idx="322">
+                  <c:v>41144</c:v>
+                </c:pt>
+                <c:pt idx="323">
+                  <c:v>41151</c:v>
+                </c:pt>
+                <c:pt idx="324">
+                  <c:v>41158</c:v>
+                </c:pt>
+                <c:pt idx="325">
+                  <c:v>41165</c:v>
+                </c:pt>
+                <c:pt idx="326">
+                  <c:v>41172</c:v>
+                </c:pt>
+                <c:pt idx="327">
+                  <c:v>41179</c:v>
+                </c:pt>
+                <c:pt idx="328">
+                  <c:v>41186</c:v>
+                </c:pt>
+                <c:pt idx="329">
+                  <c:v>41193</c:v>
+                </c:pt>
+                <c:pt idx="330">
+                  <c:v>41200</c:v>
+                </c:pt>
+                <c:pt idx="331">
+                  <c:v>41207</c:v>
+                </c:pt>
+                <c:pt idx="332">
+                  <c:v>41214</c:v>
+                </c:pt>
+                <c:pt idx="333">
+                  <c:v>41221</c:v>
+                </c:pt>
+                <c:pt idx="334">
+                  <c:v>41228</c:v>
+                </c:pt>
+                <c:pt idx="335">
+                  <c:v>41235</c:v>
+                </c:pt>
+                <c:pt idx="336">
+                  <c:v>41242</c:v>
+                </c:pt>
+                <c:pt idx="337">
+                  <c:v>41249</c:v>
+                </c:pt>
+                <c:pt idx="338">
+                  <c:v>41256</c:v>
+                </c:pt>
+                <c:pt idx="339">
+                  <c:v>41263</c:v>
+                </c:pt>
+                <c:pt idx="340">
+                  <c:v>41270</c:v>
+                </c:pt>
+                <c:pt idx="341">
+                  <c:v>41277</c:v>
+                </c:pt>
+                <c:pt idx="342">
+                  <c:v>41284</c:v>
+                </c:pt>
+                <c:pt idx="343">
+                  <c:v>41291</c:v>
+                </c:pt>
+                <c:pt idx="344">
+                  <c:v>41298</c:v>
+                </c:pt>
+                <c:pt idx="345">
+                  <c:v>41305</c:v>
+                </c:pt>
+                <c:pt idx="346">
+                  <c:v>41312</c:v>
+                </c:pt>
+                <c:pt idx="347">
+                  <c:v>41319</c:v>
+                </c:pt>
+                <c:pt idx="348">
+                  <c:v>41326</c:v>
+                </c:pt>
+                <c:pt idx="349">
+                  <c:v>41333</c:v>
+                </c:pt>
+                <c:pt idx="350">
+                  <c:v>41340</c:v>
+                </c:pt>
+                <c:pt idx="351">
+                  <c:v>41347</c:v>
+                </c:pt>
+                <c:pt idx="352">
+                  <c:v>41354</c:v>
+                </c:pt>
+                <c:pt idx="353">
+                  <c:v>41361</c:v>
+                </c:pt>
+                <c:pt idx="354">
+                  <c:v>41368</c:v>
+                </c:pt>
+                <c:pt idx="355">
+                  <c:v>41375</c:v>
+                </c:pt>
+                <c:pt idx="356">
+                  <c:v>41382</c:v>
+                </c:pt>
+                <c:pt idx="357">
+                  <c:v>41389</c:v>
+                </c:pt>
+                <c:pt idx="358">
+                  <c:v>41396</c:v>
+                </c:pt>
+                <c:pt idx="359">
+                  <c:v>41403</c:v>
+                </c:pt>
+                <c:pt idx="360">
+                  <c:v>41410</c:v>
+                </c:pt>
+                <c:pt idx="361">
+                  <c:v>41417</c:v>
+                </c:pt>
+                <c:pt idx="362">
+                  <c:v>41424</c:v>
+                </c:pt>
+                <c:pt idx="363">
+                  <c:v>41431</c:v>
+                </c:pt>
+                <c:pt idx="364">
+                  <c:v>41438</c:v>
+                </c:pt>
+                <c:pt idx="365">
+                  <c:v>41445</c:v>
+                </c:pt>
+                <c:pt idx="366">
+                  <c:v>41452</c:v>
+                </c:pt>
+                <c:pt idx="367">
+                  <c:v>41459</c:v>
+                </c:pt>
+                <c:pt idx="368">
+                  <c:v>41466</c:v>
+                </c:pt>
+                <c:pt idx="369">
+                  <c:v>41473</c:v>
+                </c:pt>
+                <c:pt idx="370">
+                  <c:v>41480</c:v>
+                </c:pt>
+                <c:pt idx="371">
+                  <c:v>41487</c:v>
+                </c:pt>
+                <c:pt idx="372">
+                  <c:v>41494</c:v>
+                </c:pt>
+                <c:pt idx="373">
+                  <c:v>41501</c:v>
+                </c:pt>
+                <c:pt idx="374">
+                  <c:v>41508</c:v>
+                </c:pt>
+                <c:pt idx="375">
+                  <c:v>41515</c:v>
+                </c:pt>
+                <c:pt idx="376">
+                  <c:v>41522</c:v>
+                </c:pt>
+                <c:pt idx="377">
+                  <c:v>41529</c:v>
+                </c:pt>
+                <c:pt idx="378">
+                  <c:v>41536</c:v>
+                </c:pt>
+                <c:pt idx="379">
+                  <c:v>41543</c:v>
+                </c:pt>
+                <c:pt idx="380">
+                  <c:v>41550</c:v>
+                </c:pt>
+                <c:pt idx="381">
+                  <c:v>41557</c:v>
+                </c:pt>
+                <c:pt idx="382">
+                  <c:v>41564</c:v>
+                </c:pt>
+                <c:pt idx="383">
+                  <c:v>41571</c:v>
+                </c:pt>
+                <c:pt idx="384">
+                  <c:v>41578</c:v>
+                </c:pt>
+                <c:pt idx="385">
+                  <c:v>41585</c:v>
+                </c:pt>
+                <c:pt idx="386">
+                  <c:v>41592</c:v>
+                </c:pt>
+                <c:pt idx="387">
+                  <c:v>41599</c:v>
+                </c:pt>
+                <c:pt idx="388">
+                  <c:v>41606</c:v>
+                </c:pt>
+                <c:pt idx="389">
+                  <c:v>41613</c:v>
+                </c:pt>
+                <c:pt idx="390">
+                  <c:v>41620</c:v>
+                </c:pt>
+                <c:pt idx="391">
+                  <c:v>41627</c:v>
+                </c:pt>
+                <c:pt idx="392">
+                  <c:v>41635</c:v>
+                </c:pt>
+                <c:pt idx="393">
+                  <c:v>41642</c:v>
+                </c:pt>
+                <c:pt idx="394">
+                  <c:v>41648</c:v>
+                </c:pt>
+                <c:pt idx="395">
+                  <c:v>41655</c:v>
+                </c:pt>
+                <c:pt idx="396">
+                  <c:v>41662</c:v>
+                </c:pt>
+                <c:pt idx="397">
+                  <c:v>41669</c:v>
+                </c:pt>
+                <c:pt idx="398">
+                  <c:v>41676</c:v>
+                </c:pt>
+                <c:pt idx="399">
+                  <c:v>41683</c:v>
+                </c:pt>
+                <c:pt idx="400">
+                  <c:v>41690</c:v>
+                </c:pt>
+                <c:pt idx="401">
+                  <c:v>41697</c:v>
+                </c:pt>
+                <c:pt idx="402">
+                  <c:v>41704</c:v>
+                </c:pt>
+                <c:pt idx="403">
+                  <c:v>41711</c:v>
+                </c:pt>
+                <c:pt idx="404">
+                  <c:v>41717</c:v>
+                </c:pt>
+                <c:pt idx="405">
+                  <c:v>41718</c:v>
+                </c:pt>
+                <c:pt idx="406">
+                  <c:v>41725</c:v>
+                </c:pt>
+                <c:pt idx="407">
+                  <c:v>41732</c:v>
+                </c:pt>
+                <c:pt idx="408">
+                  <c:v>41739</c:v>
+                </c:pt>
+                <c:pt idx="409">
+                  <c:v>41746</c:v>
+                </c:pt>
+                <c:pt idx="410">
+                  <c:v>41753</c:v>
+                </c:pt>
+                <c:pt idx="411">
+                  <c:v>41760</c:v>
+                </c:pt>
+                <c:pt idx="412">
+                  <c:v>41767</c:v>
+                </c:pt>
+                <c:pt idx="413">
+                  <c:v>41774</c:v>
+                </c:pt>
+                <c:pt idx="414">
+                  <c:v>41781</c:v>
+                </c:pt>
+                <c:pt idx="415">
+                  <c:v>41788</c:v>
+                </c:pt>
+                <c:pt idx="416">
+                  <c:v>41795</c:v>
+                </c:pt>
+                <c:pt idx="417">
+                  <c:v>41802</c:v>
+                </c:pt>
+                <c:pt idx="418">
+                  <c:v>41809</c:v>
+                </c:pt>
+                <c:pt idx="419">
+                  <c:v>41816</c:v>
+                </c:pt>
+                <c:pt idx="420">
+                  <c:v>41823</c:v>
+                </c:pt>
+                <c:pt idx="421">
+                  <c:v>41830</c:v>
+                </c:pt>
+                <c:pt idx="422">
+                  <c:v>41837</c:v>
+                </c:pt>
+                <c:pt idx="423">
+                  <c:v>41844</c:v>
+                </c:pt>
+                <c:pt idx="424">
+                  <c:v>41851</c:v>
+                </c:pt>
+                <c:pt idx="425">
+                  <c:v>41858</c:v>
+                </c:pt>
+                <c:pt idx="426">
+                  <c:v>41865</c:v>
+                </c:pt>
+                <c:pt idx="427">
+                  <c:v>41872</c:v>
+                </c:pt>
+                <c:pt idx="428">
+                  <c:v>41879</c:v>
+                </c:pt>
+                <c:pt idx="429">
+                  <c:v>41886</c:v>
+                </c:pt>
+                <c:pt idx="430">
+                  <c:v>41893</c:v>
+                </c:pt>
+                <c:pt idx="431">
+                  <c:v>41900</c:v>
+                </c:pt>
+                <c:pt idx="432">
+                  <c:v>41907</c:v>
+                </c:pt>
+                <c:pt idx="433">
+                  <c:v>41914</c:v>
+                </c:pt>
+                <c:pt idx="434">
+                  <c:v>41921</c:v>
+                </c:pt>
+                <c:pt idx="435">
+                  <c:v>41928</c:v>
+                </c:pt>
+                <c:pt idx="436">
+                  <c:v>41935</c:v>
+                </c:pt>
+                <c:pt idx="437">
+                  <c:v>41942</c:v>
+                </c:pt>
+                <c:pt idx="438">
+                  <c:v>41949</c:v>
+                </c:pt>
+                <c:pt idx="439">
+                  <c:v>41956</c:v>
+                </c:pt>
+                <c:pt idx="440">
+                  <c:v>41963</c:v>
+                </c:pt>
+                <c:pt idx="441">
+                  <c:v>41969</c:v>
+                </c:pt>
+                <c:pt idx="442">
+                  <c:v>41977</c:v>
+                </c:pt>
+                <c:pt idx="443">
+                  <c:v>41984</c:v>
+                </c:pt>
+                <c:pt idx="444">
+                  <c:v>41991</c:v>
+                </c:pt>
+                <c:pt idx="445">
+                  <c:v>41998</c:v>
+                </c:pt>
+                <c:pt idx="446">
+                  <c:v>42005</c:v>
+                </c:pt>
+                <c:pt idx="447">
+                  <c:v>42012</c:v>
+                </c:pt>
+                <c:pt idx="448">
+                  <c:v>42019</c:v>
+                </c:pt>
+                <c:pt idx="449">
+                  <c:v>42026</c:v>
+                </c:pt>
+                <c:pt idx="450">
+                  <c:v>42033</c:v>
+                </c:pt>
+                <c:pt idx="451">
+                  <c:v>42040</c:v>
+                </c:pt>
+                <c:pt idx="452">
+                  <c:v>42047</c:v>
+                </c:pt>
+                <c:pt idx="453">
+                  <c:v>42054</c:v>
+                </c:pt>
+                <c:pt idx="454">
+                  <c:v>42061</c:v>
+                </c:pt>
+                <c:pt idx="455">
+                  <c:v>42068</c:v>
+                </c:pt>
+                <c:pt idx="456">
+                  <c:v>42075</c:v>
+                </c:pt>
+                <c:pt idx="457">
+                  <c:v>42089</c:v>
+                </c:pt>
+                <c:pt idx="458">
+                  <c:v>42096</c:v>
+                </c:pt>
+                <c:pt idx="459">
+                  <c:v>42103</c:v>
+                </c:pt>
+                <c:pt idx="460">
+                  <c:v>42110</c:v>
+                </c:pt>
+                <c:pt idx="461">
+                  <c:v>42117</c:v>
+                </c:pt>
+                <c:pt idx="462">
+                  <c:v>42124</c:v>
+                </c:pt>
+                <c:pt idx="463">
+                  <c:v>42131</c:v>
+                </c:pt>
+                <c:pt idx="464">
+                  <c:v>42138</c:v>
+                </c:pt>
+                <c:pt idx="465">
+                  <c:v>42145</c:v>
+                </c:pt>
+                <c:pt idx="466">
+                  <c:v>42152</c:v>
+                </c:pt>
+                <c:pt idx="467">
+                  <c:v>42159</c:v>
+                </c:pt>
+                <c:pt idx="468">
+                  <c:v>42166</c:v>
+                </c:pt>
+                <c:pt idx="469">
+                  <c:v>42173</c:v>
+                </c:pt>
+                <c:pt idx="470">
+                  <c:v>42180</c:v>
+                </c:pt>
+                <c:pt idx="471">
+                  <c:v>42187</c:v>
+                </c:pt>
+                <c:pt idx="472">
+                  <c:v>42194</c:v>
+                </c:pt>
+                <c:pt idx="473">
+                  <c:v>42201</c:v>
+                </c:pt>
+                <c:pt idx="474">
+                  <c:v>42208</c:v>
+                </c:pt>
+                <c:pt idx="475">
+                  <c:v>42215</c:v>
+                </c:pt>
+                <c:pt idx="476">
+                  <c:v>42222</c:v>
+                </c:pt>
+                <c:pt idx="477">
+                  <c:v>42229</c:v>
+                </c:pt>
+                <c:pt idx="478">
+                  <c:v>42236</c:v>
+                </c:pt>
+                <c:pt idx="479">
+                  <c:v>42243</c:v>
+                </c:pt>
+                <c:pt idx="480">
+                  <c:v>42250</c:v>
+                </c:pt>
+                <c:pt idx="481">
+                  <c:v>42257</c:v>
+                </c:pt>
+                <c:pt idx="482">
+                  <c:v>42264</c:v>
+                </c:pt>
+                <c:pt idx="483">
+                  <c:v>42271</c:v>
+                </c:pt>
+                <c:pt idx="484">
+                  <c:v>42278</c:v>
+                </c:pt>
+                <c:pt idx="485">
+                  <c:v>42285</c:v>
+                </c:pt>
+                <c:pt idx="486">
+                  <c:v>42292</c:v>
+                </c:pt>
+                <c:pt idx="487">
+                  <c:v>42299</c:v>
+                </c:pt>
+                <c:pt idx="488">
+                  <c:v>42306</c:v>
+                </c:pt>
+                <c:pt idx="489">
+                  <c:v>42313</c:v>
+                </c:pt>
+                <c:pt idx="490">
+                  <c:v>42320</c:v>
+                </c:pt>
+                <c:pt idx="491">
+                  <c:v>42327</c:v>
+                </c:pt>
+                <c:pt idx="492">
+                  <c:v>42334</c:v>
+                </c:pt>
+                <c:pt idx="493">
+                  <c:v>42341</c:v>
+                </c:pt>
+                <c:pt idx="494">
+                  <c:v>42348</c:v>
+                </c:pt>
+                <c:pt idx="495">
+                  <c:v>42355</c:v>
+                </c:pt>
+                <c:pt idx="496">
+                  <c:v>42362</c:v>
+                </c:pt>
+                <c:pt idx="497">
+                  <c:v>42369</c:v>
+                </c:pt>
+                <c:pt idx="498">
+                  <c:v>42376</c:v>
+                </c:pt>
+                <c:pt idx="499">
+                  <c:v>42383</c:v>
+                </c:pt>
+                <c:pt idx="500">
+                  <c:v>42397</c:v>
+                </c:pt>
+                <c:pt idx="501">
+                  <c:v>42404</c:v>
+                </c:pt>
+                <c:pt idx="502">
+                  <c:v>42411</c:v>
+                </c:pt>
+                <c:pt idx="503">
+                  <c:v>42418</c:v>
+                </c:pt>
+                <c:pt idx="504">
+                  <c:v>42425</c:v>
+                </c:pt>
+                <c:pt idx="505">
+                  <c:v>42432</c:v>
+                </c:pt>
+                <c:pt idx="506">
+                  <c:v>42439</c:v>
+                </c:pt>
+                <c:pt idx="507">
+                  <c:v>42446</c:v>
+                </c:pt>
+                <c:pt idx="508">
+                  <c:v>42453</c:v>
+                </c:pt>
+                <c:pt idx="509">
+                  <c:v>42460</c:v>
+                </c:pt>
+                <c:pt idx="510">
+                  <c:v>42467</c:v>
+                </c:pt>
+                <c:pt idx="511">
+                  <c:v>42474</c:v>
+                </c:pt>
+                <c:pt idx="512">
+                  <c:v>42481</c:v>
+                </c:pt>
+                <c:pt idx="513">
+                  <c:v>42488</c:v>
+                </c:pt>
+                <c:pt idx="514">
+                  <c:v>42495</c:v>
+                </c:pt>
+                <c:pt idx="515">
+                  <c:v>42502</c:v>
+                </c:pt>
+                <c:pt idx="516">
+                  <c:v>42509</c:v>
+                </c:pt>
+                <c:pt idx="517">
+                  <c:v>42516</c:v>
+                </c:pt>
+                <c:pt idx="518">
+                  <c:v>42523</c:v>
+                </c:pt>
+                <c:pt idx="519">
+                  <c:v>42530</c:v>
+                </c:pt>
+                <c:pt idx="520">
+                  <c:v>42537</c:v>
+                </c:pt>
+                <c:pt idx="521">
+                  <c:v>42544</c:v>
+                </c:pt>
+                <c:pt idx="522">
+                  <c:v>42551</c:v>
+                </c:pt>
+                <c:pt idx="523">
+                  <c:v>42558</c:v>
+                </c:pt>
+                <c:pt idx="524">
+                  <c:v>42565</c:v>
+                </c:pt>
+                <c:pt idx="525">
+                  <c:v>42572</c:v>
+                </c:pt>
+                <c:pt idx="526">
+                  <c:v>42579</c:v>
+                </c:pt>
+                <c:pt idx="527">
+                  <c:v>42586</c:v>
+                </c:pt>
+                <c:pt idx="528">
+                  <c:v>42593</c:v>
+                </c:pt>
+                <c:pt idx="529">
+                  <c:v>42600</c:v>
+                </c:pt>
+                <c:pt idx="530">
+                  <c:v>42607</c:v>
+                </c:pt>
+                <c:pt idx="531">
+                  <c:v>42614</c:v>
+                </c:pt>
+                <c:pt idx="532">
+                  <c:v>42621</c:v>
+                </c:pt>
+                <c:pt idx="533">
+                  <c:v>42628</c:v>
+                </c:pt>
+                <c:pt idx="534">
+                  <c:v>42635</c:v>
+                </c:pt>
+                <c:pt idx="535">
+                  <c:v>42642</c:v>
+                </c:pt>
+                <c:pt idx="536">
+                  <c:v>42649</c:v>
+                </c:pt>
+                <c:pt idx="537">
+                  <c:v>42656</c:v>
+                </c:pt>
+                <c:pt idx="538">
+                  <c:v>42663</c:v>
+                </c:pt>
+                <c:pt idx="539">
+                  <c:v>42670</c:v>
+                </c:pt>
+                <c:pt idx="540">
+                  <c:v>42677</c:v>
+                </c:pt>
+                <c:pt idx="541">
+                  <c:v>42684</c:v>
+                </c:pt>
+                <c:pt idx="542">
+                  <c:v>42690</c:v>
+                </c:pt>
+                <c:pt idx="543">
+                  <c:v>42698</c:v>
+                </c:pt>
+                <c:pt idx="544">
+                  <c:v>42705</c:v>
+                </c:pt>
+                <c:pt idx="545">
+                  <c:v>42712</c:v>
+                </c:pt>
+                <c:pt idx="546">
+                  <c:v>42719</c:v>
+                </c:pt>
+                <c:pt idx="547">
+                  <c:v>42726</c:v>
+                </c:pt>
+                <c:pt idx="548">
+                  <c:v>42733</c:v>
+                </c:pt>
+                <c:pt idx="549">
+                  <c:v>42740</c:v>
+                </c:pt>
+                <c:pt idx="550">
+                  <c:v>42747</c:v>
+                </c:pt>
+                <c:pt idx="551">
+                  <c:v>42754</c:v>
+                </c:pt>
+                <c:pt idx="552">
+                  <c:v>42761</c:v>
+                </c:pt>
+                <c:pt idx="553">
+                  <c:v>42768</c:v>
+                </c:pt>
+                <c:pt idx="554">
+                  <c:v>42775</c:v>
+                </c:pt>
+                <c:pt idx="555">
+                  <c:v>42782</c:v>
+                </c:pt>
+                <c:pt idx="556">
+                  <c:v>42789</c:v>
+                </c:pt>
+                <c:pt idx="557">
+                  <c:v>42796</c:v>
+                </c:pt>
+                <c:pt idx="558">
+                  <c:v>42803</c:v>
+                </c:pt>
+                <c:pt idx="559">
+                  <c:v>42810</c:v>
+                </c:pt>
+                <c:pt idx="560">
+                  <c:v>42817</c:v>
+                </c:pt>
+                <c:pt idx="561">
+                  <c:v>42824</c:v>
+                </c:pt>
+                <c:pt idx="562">
+                  <c:v>42831</c:v>
+                </c:pt>
+                <c:pt idx="563">
+                  <c:v>42838</c:v>
+                </c:pt>
+                <c:pt idx="564">
+                  <c:v>42845</c:v>
+                </c:pt>
+                <c:pt idx="565">
+                  <c:v>42852</c:v>
+                </c:pt>
+                <c:pt idx="566">
+                  <c:v>42859</c:v>
+                </c:pt>
+                <c:pt idx="567">
+                  <c:v>42866</c:v>
+                </c:pt>
+                <c:pt idx="568">
+                  <c:v>42873</c:v>
+                </c:pt>
+                <c:pt idx="569">
+                  <c:v>42880</c:v>
+                </c:pt>
+                <c:pt idx="570">
+                  <c:v>42887</c:v>
+                </c:pt>
+                <c:pt idx="571">
+                  <c:v>42894</c:v>
+                </c:pt>
+                <c:pt idx="572">
+                  <c:v>42901</c:v>
+                </c:pt>
+                <c:pt idx="573">
+                  <c:v>42908</c:v>
+                </c:pt>
+                <c:pt idx="574">
+                  <c:v>42915</c:v>
+                </c:pt>
+                <c:pt idx="575">
+                  <c:v>42922</c:v>
+                </c:pt>
+                <c:pt idx="576">
+                  <c:v>42929</c:v>
+                </c:pt>
+                <c:pt idx="577">
+                  <c:v>42936</c:v>
+                </c:pt>
+                <c:pt idx="578">
+                  <c:v>42943</c:v>
+                </c:pt>
+                <c:pt idx="579">
+                  <c:v>42950</c:v>
+                </c:pt>
+                <c:pt idx="580">
+                  <c:v>42957</c:v>
+                </c:pt>
+                <c:pt idx="581">
+                  <c:v>42964</c:v>
+                </c:pt>
+                <c:pt idx="582">
+                  <c:v>42971</c:v>
+                </c:pt>
+                <c:pt idx="583">
+                  <c:v>42978</c:v>
+                </c:pt>
+                <c:pt idx="584">
+                  <c:v>42985</c:v>
+                </c:pt>
+                <c:pt idx="585">
+                  <c:v>42992</c:v>
+                </c:pt>
+                <c:pt idx="586">
+                  <c:v>42999</c:v>
+                </c:pt>
+                <c:pt idx="587">
+                  <c:v>43006</c:v>
+                </c:pt>
+                <c:pt idx="588">
+                  <c:v>43013</c:v>
+                </c:pt>
+                <c:pt idx="589">
+                  <c:v>43020</c:v>
+                </c:pt>
+                <c:pt idx="590">
+                  <c:v>43027</c:v>
+                </c:pt>
+                <c:pt idx="591">
+                  <c:v>43034</c:v>
+                </c:pt>
+                <c:pt idx="592">
+                  <c:v>43041</c:v>
+                </c:pt>
+                <c:pt idx="593">
+                  <c:v>43048</c:v>
+                </c:pt>
+                <c:pt idx="594">
+                  <c:v>43055</c:v>
+                </c:pt>
+                <c:pt idx="595">
+                  <c:v>43062</c:v>
+                </c:pt>
+                <c:pt idx="596">
+                  <c:v>43069</c:v>
+                </c:pt>
+                <c:pt idx="597">
+                  <c:v>43076</c:v>
+                </c:pt>
+                <c:pt idx="598">
+                  <c:v>43083</c:v>
+                </c:pt>
+                <c:pt idx="599">
+                  <c:v>43090</c:v>
+                </c:pt>
+                <c:pt idx="600">
+                  <c:v>43097</c:v>
+                </c:pt>
+                <c:pt idx="601">
+                  <c:v>43104</c:v>
+                </c:pt>
+                <c:pt idx="602">
+                  <c:v>43111</c:v>
+                </c:pt>
+                <c:pt idx="603">
+                  <c:v>43118</c:v>
+                </c:pt>
+                <c:pt idx="604">
+                  <c:v>43125</c:v>
+                </c:pt>
+                <c:pt idx="605">
+                  <c:v>43132</c:v>
+                </c:pt>
+                <c:pt idx="606">
+                  <c:v>43139</c:v>
+                </c:pt>
+                <c:pt idx="607">
+                  <c:v>43146</c:v>
+                </c:pt>
+                <c:pt idx="608">
+                  <c:v>43153</c:v>
+                </c:pt>
+                <c:pt idx="609">
+                  <c:v>43160</c:v>
+                </c:pt>
+                <c:pt idx="610">
+                  <c:v>43167</c:v>
+                </c:pt>
+                <c:pt idx="611">
+                  <c:v>43174</c:v>
+                </c:pt>
+                <c:pt idx="612">
+                  <c:v>43181</c:v>
+                </c:pt>
+                <c:pt idx="613">
+                  <c:v>43188</c:v>
+                </c:pt>
+                <c:pt idx="614">
+                  <c:v>43195</c:v>
+                </c:pt>
+                <c:pt idx="615">
+                  <c:v>43202</c:v>
+                </c:pt>
+                <c:pt idx="616">
+                  <c:v>43209</c:v>
+                </c:pt>
+                <c:pt idx="617">
+                  <c:v>43216</c:v>
+                </c:pt>
+                <c:pt idx="618">
+                  <c:v>43223</c:v>
+                </c:pt>
+                <c:pt idx="619">
+                  <c:v>43230</c:v>
+                </c:pt>
+                <c:pt idx="620">
+                  <c:v>43237</c:v>
+                </c:pt>
+                <c:pt idx="621">
+                  <c:v>43244</c:v>
+                </c:pt>
+                <c:pt idx="622">
+                  <c:v>43251</c:v>
+                </c:pt>
+                <c:pt idx="623">
+                  <c:v>43258</c:v>
+                </c:pt>
+                <c:pt idx="624">
+                  <c:v>43265</c:v>
+                </c:pt>
+                <c:pt idx="625">
+                  <c:v>43272</c:v>
+                </c:pt>
+                <c:pt idx="626">
+                  <c:v>43279</c:v>
+                </c:pt>
+                <c:pt idx="627">
+                  <c:v>43286</c:v>
+                </c:pt>
+                <c:pt idx="628">
+                  <c:v>43293</c:v>
+                </c:pt>
+                <c:pt idx="629">
+                  <c:v>43300</c:v>
+                </c:pt>
+                <c:pt idx="630">
+                  <c:v>43307</c:v>
+                </c:pt>
+                <c:pt idx="631">
+                  <c:v>43314</c:v>
+                </c:pt>
+                <c:pt idx="632">
+                  <c:v>43321</c:v>
+                </c:pt>
+                <c:pt idx="633">
+                  <c:v>43328</c:v>
+                </c:pt>
+                <c:pt idx="634">
+                  <c:v>43335</c:v>
+                </c:pt>
+                <c:pt idx="635">
+                  <c:v>43342</c:v>
+                </c:pt>
+                <c:pt idx="636">
+                  <c:v>43349</c:v>
+                </c:pt>
+                <c:pt idx="637">
+                  <c:v>43356</c:v>
+                </c:pt>
+                <c:pt idx="638">
+                  <c:v>43363</c:v>
+                </c:pt>
+                <c:pt idx="639">
+                  <c:v>43370</c:v>
+                </c:pt>
+                <c:pt idx="640">
+                  <c:v>43377</c:v>
+                </c:pt>
+                <c:pt idx="641">
+                  <c:v>43384</c:v>
+                </c:pt>
+                <c:pt idx="642">
+                  <c:v>43392</c:v>
+                </c:pt>
+                <c:pt idx="643">
+                  <c:v>43398</c:v>
+                </c:pt>
+                <c:pt idx="644">
+                  <c:v>43405</c:v>
+                </c:pt>
+                <c:pt idx="645">
+                  <c:v>43412</c:v>
+                </c:pt>
+                <c:pt idx="646">
+                  <c:v>43419</c:v>
+                </c:pt>
+                <c:pt idx="647">
+                  <c:v>43426</c:v>
+                </c:pt>
+                <c:pt idx="648">
+                  <c:v>43433</c:v>
+                </c:pt>
+                <c:pt idx="649">
+                  <c:v>43440</c:v>
+                </c:pt>
+                <c:pt idx="650">
+                  <c:v>43447</c:v>
+                </c:pt>
+                <c:pt idx="651">
+                  <c:v>43454</c:v>
+                </c:pt>
+                <c:pt idx="652">
+                  <c:v>43461</c:v>
+                </c:pt>
+                <c:pt idx="653">
+                  <c:v>43468</c:v>
+                </c:pt>
+                <c:pt idx="654">
+                  <c:v>43475</c:v>
+                </c:pt>
+                <c:pt idx="655">
+                  <c:v>43482</c:v>
+                </c:pt>
+                <c:pt idx="656">
+                  <c:v>43489</c:v>
+                </c:pt>
+                <c:pt idx="657">
+                  <c:v>43496</c:v>
+                </c:pt>
+                <c:pt idx="658">
+                  <c:v>43503</c:v>
+                </c:pt>
+                <c:pt idx="659">
+                  <c:v>43510</c:v>
+                </c:pt>
+                <c:pt idx="660">
+                  <c:v>43517</c:v>
+                </c:pt>
+                <c:pt idx="661">
+                  <c:v>43524</c:v>
+                </c:pt>
+                <c:pt idx="662">
+                  <c:v>43531</c:v>
+                </c:pt>
+                <c:pt idx="663">
+                  <c:v>43538</c:v>
+                </c:pt>
+                <c:pt idx="664">
+                  <c:v>43545</c:v>
+                </c:pt>
+                <c:pt idx="665">
+                  <c:v>43552</c:v>
+                </c:pt>
+                <c:pt idx="666">
+                  <c:v>43559</c:v>
+                </c:pt>
+                <c:pt idx="667">
+                  <c:v>43566</c:v>
+                </c:pt>
+                <c:pt idx="668">
+                  <c:v>43573</c:v>
+                </c:pt>
+                <c:pt idx="669">
+                  <c:v>43580</c:v>
+                </c:pt>
+                <c:pt idx="670">
+                  <c:v>43587</c:v>
+                </c:pt>
+                <c:pt idx="671">
+                  <c:v>43594</c:v>
+                </c:pt>
+                <c:pt idx="672">
+                  <c:v>43601</c:v>
+                </c:pt>
+                <c:pt idx="673">
+                  <c:v>43608</c:v>
+                </c:pt>
+                <c:pt idx="674">
+                  <c:v>43615</c:v>
+                </c:pt>
+                <c:pt idx="675">
+                  <c:v>43622</c:v>
+                </c:pt>
+                <c:pt idx="676">
+                  <c:v>43629</c:v>
+                </c:pt>
+                <c:pt idx="677">
+                  <c:v>43636</c:v>
+                </c:pt>
+                <c:pt idx="678">
+                  <c:v>43643</c:v>
+                </c:pt>
+                <c:pt idx="679">
+                  <c:v>43650</c:v>
+                </c:pt>
+                <c:pt idx="680">
+                  <c:v>43657</c:v>
+                </c:pt>
+                <c:pt idx="681">
+                  <c:v>43664</c:v>
+                </c:pt>
+                <c:pt idx="682">
+                  <c:v>43671</c:v>
+                </c:pt>
+                <c:pt idx="683">
+                  <c:v>43678</c:v>
+                </c:pt>
+                <c:pt idx="684">
+                  <c:v>43685</c:v>
+                </c:pt>
+                <c:pt idx="685">
+                  <c:v>43692</c:v>
+                </c:pt>
+                <c:pt idx="686">
+                  <c:v>43699</c:v>
+                </c:pt>
+                <c:pt idx="687">
+                  <c:v>43706</c:v>
+                </c:pt>
+                <c:pt idx="688">
+                  <c:v>43713</c:v>
+                </c:pt>
+                <c:pt idx="689">
+                  <c:v>43720</c:v>
+                </c:pt>
+                <c:pt idx="690">
+                  <c:v>43727</c:v>
+                </c:pt>
+                <c:pt idx="691">
+                  <c:v>43734</c:v>
+                </c:pt>
+                <c:pt idx="692">
+                  <c:v>43741</c:v>
+                </c:pt>
+                <c:pt idx="693">
+                  <c:v>43748</c:v>
+                </c:pt>
+                <c:pt idx="694">
+                  <c:v>43755</c:v>
+                </c:pt>
+                <c:pt idx="695">
+                  <c:v>43762</c:v>
+                </c:pt>
+                <c:pt idx="696">
+                  <c:v>43769</c:v>
+                </c:pt>
+                <c:pt idx="697">
+                  <c:v>43776</c:v>
+                </c:pt>
+                <c:pt idx="698">
+                  <c:v>43783</c:v>
+                </c:pt>
+                <c:pt idx="699">
+                  <c:v>43790</c:v>
+                </c:pt>
+                <c:pt idx="700">
+                  <c:v>43797</c:v>
+                </c:pt>
+                <c:pt idx="701">
+                  <c:v>43804</c:v>
+                </c:pt>
+                <c:pt idx="702">
+                  <c:v>43811</c:v>
+                </c:pt>
+                <c:pt idx="703">
+                  <c:v>43818</c:v>
+                </c:pt>
+                <c:pt idx="704">
+                  <c:v>43825</c:v>
+                </c:pt>
+                <c:pt idx="705">
+                  <c:v>43832</c:v>
+                </c:pt>
+                <c:pt idx="706">
+                  <c:v>43839</c:v>
+                </c:pt>
+                <c:pt idx="707">
+                  <c:v>43846</c:v>
+                </c:pt>
+                <c:pt idx="708">
+                  <c:v>43853</c:v>
+                </c:pt>
+                <c:pt idx="709">
+                  <c:v>43860</c:v>
+                </c:pt>
+                <c:pt idx="710">
+                  <c:v>43867</c:v>
+                </c:pt>
+                <c:pt idx="711">
+                  <c:v>43874</c:v>
+                </c:pt>
+                <c:pt idx="712">
+                  <c:v>43881</c:v>
+                </c:pt>
+                <c:pt idx="713">
+                  <c:v>43888</c:v>
+                </c:pt>
+                <c:pt idx="714">
+                  <c:v>43895</c:v>
+                </c:pt>
+                <c:pt idx="715">
+                  <c:v>43902</c:v>
+                </c:pt>
+                <c:pt idx="716">
+                  <c:v>43909</c:v>
+                </c:pt>
+                <c:pt idx="717">
+                  <c:v>43916</c:v>
+                </c:pt>
+                <c:pt idx="718">
+                  <c:v>43923</c:v>
+                </c:pt>
+                <c:pt idx="719">
+                  <c:v>43930</c:v>
+                </c:pt>
+                <c:pt idx="720">
+                  <c:v>43937</c:v>
+                </c:pt>
+                <c:pt idx="721">
+                  <c:v>43944</c:v>
+                </c:pt>
+                <c:pt idx="722">
+                  <c:v>43951</c:v>
+                </c:pt>
+                <c:pt idx="723">
+                  <c:v>43958</c:v>
+                </c:pt>
+                <c:pt idx="724">
+                  <c:v>43965</c:v>
+                </c:pt>
+                <c:pt idx="725">
+                  <c:v>43972</c:v>
+                </c:pt>
+                <c:pt idx="726">
+                  <c:v>43979</c:v>
+                </c:pt>
+                <c:pt idx="727">
+                  <c:v>43986</c:v>
+                </c:pt>
+                <c:pt idx="728">
+                  <c:v>43993</c:v>
+                </c:pt>
+                <c:pt idx="729">
+                  <c:v>44000</c:v>
+                </c:pt>
+                <c:pt idx="730">
+                  <c:v>44007</c:v>
+                </c:pt>
+                <c:pt idx="731">
+                  <c:v>44014</c:v>
+                </c:pt>
+                <c:pt idx="732">
+                  <c:v>44021</c:v>
+                </c:pt>
+                <c:pt idx="733">
+                  <c:v>44028</c:v>
+                </c:pt>
+                <c:pt idx="734">
+                  <c:v>44035</c:v>
+                </c:pt>
+                <c:pt idx="735">
+                  <c:v>44042</c:v>
+                </c:pt>
+                <c:pt idx="736">
+                  <c:v>44049</c:v>
+                </c:pt>
+                <c:pt idx="737">
+                  <c:v>44056</c:v>
+                </c:pt>
+                <c:pt idx="738">
+                  <c:v>44063</c:v>
+                </c:pt>
+                <c:pt idx="739">
+                  <c:v>44070</c:v>
+                </c:pt>
+                <c:pt idx="740">
+                  <c:v>44077</c:v>
+                </c:pt>
+                <c:pt idx="741">
+                  <c:v>44084</c:v>
+                </c:pt>
+                <c:pt idx="742">
+                  <c:v>44091</c:v>
+                </c:pt>
+                <c:pt idx="743">
+                  <c:v>44098</c:v>
+                </c:pt>
+                <c:pt idx="744">
+                  <c:v>44105</c:v>
+                </c:pt>
+                <c:pt idx="745">
+                  <c:v>44112</c:v>
+                </c:pt>
+                <c:pt idx="746">
+                  <c:v>44119</c:v>
+                </c:pt>
+                <c:pt idx="747">
+                  <c:v>44126</c:v>
+                </c:pt>
+                <c:pt idx="748">
+                  <c:v>44133</c:v>
+                </c:pt>
+                <c:pt idx="749">
+                  <c:v>44140</c:v>
+                </c:pt>
+                <c:pt idx="750">
+                  <c:v>44147</c:v>
+                </c:pt>
+                <c:pt idx="751">
+                  <c:v>44154</c:v>
+                </c:pt>
+                <c:pt idx="752">
+                  <c:v>44161</c:v>
+                </c:pt>
+                <c:pt idx="753">
+                  <c:v>44168</c:v>
+                </c:pt>
+                <c:pt idx="754">
+                  <c:v>44175</c:v>
+                </c:pt>
+                <c:pt idx="755">
+                  <c:v>44182</c:v>
+                </c:pt>
+                <c:pt idx="756">
+                  <c:v>44189</c:v>
+                </c:pt>
+                <c:pt idx="757">
+                  <c:v>44196</c:v>
+                </c:pt>
+                <c:pt idx="758">
+                  <c:v>44203</c:v>
+                </c:pt>
+                <c:pt idx="759">
+                  <c:v>44210</c:v>
+                </c:pt>
+                <c:pt idx="760">
+                  <c:v>44217</c:v>
+                </c:pt>
+                <c:pt idx="761">
+                  <c:v>44224</c:v>
+                </c:pt>
+                <c:pt idx="762">
+                  <c:v>44231</c:v>
+                </c:pt>
+                <c:pt idx="763">
+                  <c:v>44238</c:v>
+                </c:pt>
+                <c:pt idx="764">
+                  <c:v>44245</c:v>
+                </c:pt>
+                <c:pt idx="765">
+                  <c:v>44252</c:v>
+                </c:pt>
+                <c:pt idx="766">
+                  <c:v>44259</c:v>
+                </c:pt>
+                <c:pt idx="767">
+                  <c:v>44266</c:v>
+                </c:pt>
+                <c:pt idx="768">
+                  <c:v>44273</c:v>
+                </c:pt>
+                <c:pt idx="769">
+                  <c:v>44280</c:v>
+                </c:pt>
+                <c:pt idx="770">
+                  <c:v>44287</c:v>
+                </c:pt>
+                <c:pt idx="771">
+                  <c:v>44294</c:v>
+                </c:pt>
+                <c:pt idx="772">
+                  <c:v>44301</c:v>
+                </c:pt>
+                <c:pt idx="773">
+                  <c:v>44308</c:v>
+                </c:pt>
+                <c:pt idx="774">
+                  <c:v>44315</c:v>
+                </c:pt>
+                <c:pt idx="775">
+                  <c:v>44322</c:v>
+                </c:pt>
+                <c:pt idx="776">
+                  <c:v>44329</c:v>
+                </c:pt>
+                <c:pt idx="777">
+                  <c:v>44336</c:v>
+                </c:pt>
+                <c:pt idx="778">
+                  <c:v>44343</c:v>
+                </c:pt>
+                <c:pt idx="779">
+                  <c:v>44350</c:v>
+                </c:pt>
+                <c:pt idx="780">
+                  <c:v>44357</c:v>
+                </c:pt>
+                <c:pt idx="781">
+                  <c:v>44364</c:v>
+                </c:pt>
+                <c:pt idx="782">
+                  <c:v>44371</c:v>
+                </c:pt>
+                <c:pt idx="783">
+                  <c:v>44378</c:v>
+                </c:pt>
+                <c:pt idx="784">
+                  <c:v>44385</c:v>
+                </c:pt>
+                <c:pt idx="785">
+                  <c:v>44392</c:v>
+                </c:pt>
+                <c:pt idx="786">
+                  <c:v>44399</c:v>
+                </c:pt>
+                <c:pt idx="787">
+                  <c:v>44406</c:v>
+                </c:pt>
+                <c:pt idx="788">
+                  <c:v>44413</c:v>
+                </c:pt>
+                <c:pt idx="789">
+                  <c:v>44420</c:v>
+                </c:pt>
+                <c:pt idx="790">
+                  <c:v>44427</c:v>
+                </c:pt>
+                <c:pt idx="791">
+                  <c:v>44434</c:v>
+                </c:pt>
+                <c:pt idx="792">
+                  <c:v>44441</c:v>
+                </c:pt>
+                <c:pt idx="793">
+                  <c:v>44448</c:v>
+                </c:pt>
+                <c:pt idx="794">
+                  <c:v>44455</c:v>
+                </c:pt>
+                <c:pt idx="795">
+                  <c:v>44462</c:v>
+                </c:pt>
+                <c:pt idx="796">
+                  <c:v>44469</c:v>
+                </c:pt>
+                <c:pt idx="797">
+                  <c:v>44476</c:v>
+                </c:pt>
+                <c:pt idx="798">
+                  <c:v>44483</c:v>
+                </c:pt>
+                <c:pt idx="799">
+                  <c:v>44490</c:v>
+                </c:pt>
+                <c:pt idx="800">
+                  <c:v>44497</c:v>
+                </c:pt>
+                <c:pt idx="801">
+                  <c:v>44504</c:v>
+                </c:pt>
+                <c:pt idx="802">
+                  <c:v>44511</c:v>
+                </c:pt>
+                <c:pt idx="803">
+                  <c:v>44518</c:v>
+                </c:pt>
+                <c:pt idx="804">
+                  <c:v>44525</c:v>
+                </c:pt>
+                <c:pt idx="805">
+                  <c:v>44532</c:v>
+                </c:pt>
+                <c:pt idx="806">
+                  <c:v>44539</c:v>
+                </c:pt>
+                <c:pt idx="807">
+                  <c:v>44546</c:v>
+                </c:pt>
+                <c:pt idx="808">
+                  <c:v>44553</c:v>
+                </c:pt>
+                <c:pt idx="809">
+                  <c:v>44560</c:v>
+                </c:pt>
+                <c:pt idx="810">
+                  <c:v>44567</c:v>
+                </c:pt>
+                <c:pt idx="811">
+                  <c:v>44574</c:v>
+                </c:pt>
+                <c:pt idx="812">
+                  <c:v>44581</c:v>
+                </c:pt>
+                <c:pt idx="813">
+                  <c:v>44588</c:v>
+                </c:pt>
+                <c:pt idx="814">
+                  <c:v>44595</c:v>
+                </c:pt>
+                <c:pt idx="815">
+                  <c:v>44602</c:v>
+                </c:pt>
+                <c:pt idx="816">
+                  <c:v>44609</c:v>
+                </c:pt>
+                <c:pt idx="817">
+                  <c:v>44616</c:v>
+                </c:pt>
+                <c:pt idx="818">
+                  <c:v>44623</c:v>
+                </c:pt>
+                <c:pt idx="819">
+                  <c:v>44630</c:v>
+                </c:pt>
+                <c:pt idx="820">
+                  <c:v>44637</c:v>
+                </c:pt>
+                <c:pt idx="821">
+                  <c:v>44644</c:v>
+                </c:pt>
+                <c:pt idx="822">
+                  <c:v>44651</c:v>
+                </c:pt>
+                <c:pt idx="823">
+                  <c:v>44658</c:v>
+                </c:pt>
+                <c:pt idx="824">
+                  <c:v>44665</c:v>
+                </c:pt>
+                <c:pt idx="825">
+                  <c:v>44672</c:v>
+                </c:pt>
+                <c:pt idx="826">
+                  <c:v>44679</c:v>
+                </c:pt>
+                <c:pt idx="827">
+                  <c:v>44686</c:v>
+                </c:pt>
+                <c:pt idx="828">
+                  <c:v>44693</c:v>
+                </c:pt>
+                <c:pt idx="829">
+                  <c:v>44700</c:v>
+                </c:pt>
+                <c:pt idx="830">
+                  <c:v>44707</c:v>
+                </c:pt>
+                <c:pt idx="831">
+                  <c:v>44714</c:v>
+                </c:pt>
+                <c:pt idx="832">
+                  <c:v>44721</c:v>
+                </c:pt>
+                <c:pt idx="833">
+                  <c:v>44728</c:v>
+                </c:pt>
+                <c:pt idx="834">
+                  <c:v>44735</c:v>
+                </c:pt>
+                <c:pt idx="835">
+                  <c:v>44742</c:v>
+                </c:pt>
+                <c:pt idx="836">
+                  <c:v>44749</c:v>
+                </c:pt>
+                <c:pt idx="837">
+                  <c:v>44756</c:v>
+                </c:pt>
+                <c:pt idx="838">
+                  <c:v>44763</c:v>
+                </c:pt>
+                <c:pt idx="839">
+                  <c:v>44770</c:v>
+                </c:pt>
+                <c:pt idx="840">
+                  <c:v>44777</c:v>
+                </c:pt>
+                <c:pt idx="841">
+                  <c:v>44784</c:v>
+                </c:pt>
+                <c:pt idx="842">
+                  <c:v>44791</c:v>
+                </c:pt>
+                <c:pt idx="843">
+                  <c:v>44798</c:v>
+                </c:pt>
+                <c:pt idx="844">
+                  <c:v>44805</c:v>
+                </c:pt>
+                <c:pt idx="845">
+                  <c:v>44812</c:v>
+                </c:pt>
+                <c:pt idx="846">
+                  <c:v>44819</c:v>
+                </c:pt>
+                <c:pt idx="847">
+                  <c:v>44826</c:v>
+                </c:pt>
+                <c:pt idx="848">
+                  <c:v>44833</c:v>
+                </c:pt>
+                <c:pt idx="849">
+                  <c:v>44840</c:v>
+                </c:pt>
+                <c:pt idx="850">
+                  <c:v>44847</c:v>
+                </c:pt>
+                <c:pt idx="851">
+                  <c:v>44854</c:v>
+                </c:pt>
+                <c:pt idx="852">
+                  <c:v>44861</c:v>
+                </c:pt>
+                <c:pt idx="853">
+                  <c:v>44868</c:v>
+                </c:pt>
+                <c:pt idx="854">
+                  <c:v>44875</c:v>
+                </c:pt>
+                <c:pt idx="855">
+                  <c:v>44882</c:v>
+                </c:pt>
+                <c:pt idx="856">
+                  <c:v>44889</c:v>
+                </c:pt>
+                <c:pt idx="857">
+                  <c:v>44896</c:v>
+                </c:pt>
+                <c:pt idx="858">
+                  <c:v>44903</c:v>
+                </c:pt>
+                <c:pt idx="859">
+                  <c:v>44910</c:v>
+                </c:pt>
+                <c:pt idx="860">
+                  <c:v>44917</c:v>
+                </c:pt>
+                <c:pt idx="861">
+                  <c:v>44924</c:v>
+                </c:pt>
+                <c:pt idx="862">
+                  <c:v>44931</c:v>
+                </c:pt>
+                <c:pt idx="863">
+                  <c:v>44938</c:v>
+                </c:pt>
+                <c:pt idx="864">
+                  <c:v>44945</c:v>
+                </c:pt>
+                <c:pt idx="865">
+                  <c:v>44952</c:v>
+                </c:pt>
+                <c:pt idx="866">
+                  <c:v>44959</c:v>
+                </c:pt>
+                <c:pt idx="867">
+                  <c:v>44966</c:v>
+                </c:pt>
+                <c:pt idx="868">
+                  <c:v>44973</c:v>
+                </c:pt>
+                <c:pt idx="869">
+                  <c:v>44980</c:v>
+                </c:pt>
+                <c:pt idx="870">
+                  <c:v>44987</c:v>
+                </c:pt>
+                <c:pt idx="871">
+                  <c:v>44994</c:v>
+                </c:pt>
+                <c:pt idx="872">
+                  <c:v>45001</c:v>
+                </c:pt>
+                <c:pt idx="873">
+                  <c:v>45008</c:v>
+                </c:pt>
+                <c:pt idx="874">
+                  <c:v>45015</c:v>
+                </c:pt>
+                <c:pt idx="875">
+                  <c:v>45022</c:v>
+                </c:pt>
+                <c:pt idx="876">
+                  <c:v>45029</c:v>
+                </c:pt>
+                <c:pt idx="877">
+                  <c:v>45036</c:v>
+                </c:pt>
+                <c:pt idx="878">
+                  <c:v>45043</c:v>
+                </c:pt>
+                <c:pt idx="879">
+                  <c:v>45050</c:v>
+                </c:pt>
+                <c:pt idx="880">
+                  <c:v>45057</c:v>
+                </c:pt>
+                <c:pt idx="881">
+                  <c:v>45064</c:v>
+                </c:pt>
+                <c:pt idx="882">
+                  <c:v>45071</c:v>
+                </c:pt>
+                <c:pt idx="883">
+                  <c:v>45078</c:v>
+                </c:pt>
+                <c:pt idx="884">
+                  <c:v>45085</c:v>
+                </c:pt>
+                <c:pt idx="885">
+                  <c:v>45092</c:v>
+                </c:pt>
+                <c:pt idx="886">
+                  <c:v>45099</c:v>
+                </c:pt>
+                <c:pt idx="887">
+                  <c:v>45106</c:v>
+                </c:pt>
+                <c:pt idx="888">
+                  <c:v>45113</c:v>
+                </c:pt>
+                <c:pt idx="889">
+                  <c:v>45120</c:v>
+                </c:pt>
+                <c:pt idx="890">
+                  <c:v>45127</c:v>
+                </c:pt>
+                <c:pt idx="891">
+                  <c:v>45134</c:v>
+                </c:pt>
+                <c:pt idx="892">
+                  <c:v>45141</c:v>
+                </c:pt>
+                <c:pt idx="893">
+                  <c:v>45148</c:v>
+                </c:pt>
+                <c:pt idx="894">
+                  <c:v>45155</c:v>
+                </c:pt>
+                <c:pt idx="895">
+                  <c:v>45162</c:v>
+                </c:pt>
+                <c:pt idx="896">
+                  <c:v>45169</c:v>
+                </c:pt>
+                <c:pt idx="897">
+                  <c:v>45176</c:v>
+                </c:pt>
+                <c:pt idx="898">
+                  <c:v>45183</c:v>
+                </c:pt>
+                <c:pt idx="899">
+                  <c:v>45190</c:v>
+                </c:pt>
+                <c:pt idx="900">
+                  <c:v>45197</c:v>
+                </c:pt>
+                <c:pt idx="901">
+                  <c:v>45204</c:v>
+                </c:pt>
+                <c:pt idx="902">
+                  <c:v>45211</c:v>
+                </c:pt>
+                <c:pt idx="903">
+                  <c:v>45218</c:v>
+                </c:pt>
+                <c:pt idx="904">
+                  <c:v>45225</c:v>
+                </c:pt>
+                <c:pt idx="905">
+                  <c:v>45232</c:v>
+                </c:pt>
+                <c:pt idx="906">
+                  <c:v>45239</c:v>
+                </c:pt>
+                <c:pt idx="907">
+                  <c:v>45246</c:v>
+                </c:pt>
+                <c:pt idx="908">
+                  <c:v>45253</c:v>
+                </c:pt>
+                <c:pt idx="909">
+                  <c:v>45260</c:v>
+                </c:pt>
+                <c:pt idx="910">
+                  <c:v>45267</c:v>
+                </c:pt>
+                <c:pt idx="911">
+                  <c:v>45274</c:v>
+                </c:pt>
+                <c:pt idx="912">
+                  <c:v>45281</c:v>
+                </c:pt>
+                <c:pt idx="913">
+                  <c:v>45288</c:v>
+                </c:pt>
+                <c:pt idx="914">
+                  <c:v>45295</c:v>
+                </c:pt>
+                <c:pt idx="915">
+                  <c:v>45302</c:v>
+                </c:pt>
+                <c:pt idx="916">
+                  <c:v>45309</c:v>
+                </c:pt>
+                <c:pt idx="917">
+                  <c:v>45316</c:v>
+                </c:pt>
+                <c:pt idx="918">
+                  <c:v>45323</c:v>
+                </c:pt>
+                <c:pt idx="919">
+                  <c:v>45330</c:v>
+                </c:pt>
+                <c:pt idx="920">
+                  <c:v>45337</c:v>
+                </c:pt>
+                <c:pt idx="921">
+                  <c:v>45344</c:v>
+                </c:pt>
+                <c:pt idx="922">
+                  <c:v>45351</c:v>
+                </c:pt>
+                <c:pt idx="923">
+                  <c:v>45358</c:v>
+                </c:pt>
+                <c:pt idx="924">
+                  <c:v>45365</c:v>
+                </c:pt>
+                <c:pt idx="925">
+                  <c:v>45372</c:v>
+                </c:pt>
+                <c:pt idx="926">
+                  <c:v>45379</c:v>
+                </c:pt>
+                <c:pt idx="927">
+                  <c:v>45386</c:v>
+                </c:pt>
+                <c:pt idx="928">
+                  <c:v>45393</c:v>
+                </c:pt>
+                <c:pt idx="929">
+                  <c:v>45400</c:v>
+                </c:pt>
+                <c:pt idx="930">
+                  <c:v>45407</c:v>
+                </c:pt>
+                <c:pt idx="931">
+                  <c:v>45414</c:v>
+                </c:pt>
+                <c:pt idx="932">
+                  <c:v>45421</c:v>
+                </c:pt>
+                <c:pt idx="933">
+                  <c:v>45428</c:v>
+                </c:pt>
+                <c:pt idx="934">
+                  <c:v>45435</c:v>
+                </c:pt>
+                <c:pt idx="935">
+                  <c:v>45442</c:v>
+                </c:pt>
+                <c:pt idx="936">
+                  <c:v>45449</c:v>
+                </c:pt>
+                <c:pt idx="937">
+                  <c:v>45456</c:v>
+                </c:pt>
+                <c:pt idx="938">
+                  <c:v>45463</c:v>
+                </c:pt>
+                <c:pt idx="939">
+                  <c:v>45470</c:v>
+                </c:pt>
+                <c:pt idx="940">
+                  <c:v>45477</c:v>
+                </c:pt>
+                <c:pt idx="941">
+                  <c:v>45484</c:v>
+                </c:pt>
+                <c:pt idx="942">
+                  <c:v>45491</c:v>
+                </c:pt>
+                <c:pt idx="943">
+                  <c:v>45498</c:v>
+                </c:pt>
+                <c:pt idx="944">
+                  <c:v>45505</c:v>
+                </c:pt>
+                <c:pt idx="945">
+                  <c:v>45512</c:v>
+                </c:pt>
+                <c:pt idx="946">
+                  <c:v>45519</c:v>
+                </c:pt>
+                <c:pt idx="947">
+                  <c:v>45526</c:v>
+                </c:pt>
+                <c:pt idx="948">
+                  <c:v>45533</c:v>
+                </c:pt>
+                <c:pt idx="949">
+                  <c:v>45540</c:v>
+                </c:pt>
+                <c:pt idx="950">
+                  <c:v>45547</c:v>
+                </c:pt>
+                <c:pt idx="951">
+                  <c:v>45554</c:v>
+                </c:pt>
+                <c:pt idx="952">
+                  <c:v>45561</c:v>
+                </c:pt>
+                <c:pt idx="953">
+                  <c:v>45568</c:v>
+                </c:pt>
+                <c:pt idx="954">
+                  <c:v>45575</c:v>
+                </c:pt>
+                <c:pt idx="955">
+                  <c:v>45582</c:v>
+                </c:pt>
+                <c:pt idx="956">
+                  <c:v>45589</c:v>
+                </c:pt>
+                <c:pt idx="957">
+                  <c:v>45596</c:v>
+                </c:pt>
+                <c:pt idx="958">
+                  <c:v>45603</c:v>
+                </c:pt>
+                <c:pt idx="959">
+                  <c:v>45610</c:v>
+                </c:pt>
+                <c:pt idx="960">
+                  <c:v>45617</c:v>
+                </c:pt>
+                <c:pt idx="961">
+                  <c:v>45624</c:v>
+                </c:pt>
+                <c:pt idx="962">
+                  <c:v>45631</c:v>
+                </c:pt>
+                <c:pt idx="963">
+                  <c:v>45638</c:v>
+                </c:pt>
+                <c:pt idx="964">
+                  <c:v>45645</c:v>
+                </c:pt>
+                <c:pt idx="965">
+                  <c:v>45652</c:v>
+                </c:pt>
+                <c:pt idx="966">
+                  <c:v>45659</c:v>
+                </c:pt>
+                <c:pt idx="967">
+                  <c:v>45666</c:v>
+                </c:pt>
+                <c:pt idx="968">
+                  <c:v>45673</c:v>
+                </c:pt>
+                <c:pt idx="969">
+                  <c:v>45680</c:v>
+                </c:pt>
+                <c:pt idx="970">
+                  <c:v>45687</c:v>
+                </c:pt>
+                <c:pt idx="971">
+                  <c:v>45694</c:v>
+                </c:pt>
+                <c:pt idx="972">
+                  <c:v>45701</c:v>
+                </c:pt>
+                <c:pt idx="973">
+                  <c:v>45708</c:v>
+                </c:pt>
+                <c:pt idx="974">
+                  <c:v>45715</c:v>
+                </c:pt>
+                <c:pt idx="975">
+                  <c:v>45722</c:v>
+                </c:pt>
+                <c:pt idx="976">
+                  <c:v>45729</c:v>
+                </c:pt>
+                <c:pt idx="977">
+                  <c:v>45736</c:v>
+                </c:pt>
+                <c:pt idx="978">
+                  <c:v>45743</c:v>
+                </c:pt>
+                <c:pt idx="979">
+                  <c:v>45750</c:v>
+                </c:pt>
+                <c:pt idx="980">
+                  <c:v>45757</c:v>
+                </c:pt>
+                <c:pt idx="981">
+                  <c:v>45764</c:v>
+                </c:pt>
+                <c:pt idx="982">
+                  <c:v>45771</c:v>
+                </c:pt>
+                <c:pt idx="983">
+                  <c:v>45778</c:v>
+                </c:pt>
+                <c:pt idx="984">
+                  <c:v>45785</c:v>
+                </c:pt>
+                <c:pt idx="985">
+                  <c:v>45792</c:v>
+                </c:pt>
+                <c:pt idx="986">
+                  <c:v>45799</c:v>
+                </c:pt>
+                <c:pt idx="987">
+                  <c:v>45806</c:v>
+                </c:pt>
+                <c:pt idx="988">
+                  <c:v>45813</c:v>
+                </c:pt>
+                <c:pt idx="989">
+                  <c:v>45820</c:v>
+                </c:pt>
+                <c:pt idx="990">
+                  <c:v>45827</c:v>
+                </c:pt>
+                <c:pt idx="991">
+                  <c:v>45834</c:v>
+                </c:pt>
+                <c:pt idx="992">
+                  <c:v>45841</c:v>
+                </c:pt>
+                <c:pt idx="993">
+                  <c:v>45848</c:v>
+                </c:pt>
+                <c:pt idx="994">
+                  <c:v>45855</c:v>
+                </c:pt>
+                <c:pt idx="995">
+                  <c:v>45862</c:v>
+                </c:pt>
+                <c:pt idx="996">
+                  <c:v>45869</c:v>
+                </c:pt>
+                <c:pt idx="997">
+                  <c:v>45876</c:v>
+                </c:pt>
+                <c:pt idx="998">
+                  <c:v>45883</c:v>
+                </c:pt>
+                <c:pt idx="999">
+                  <c:v>45890</c:v>
+                </c:pt>
+                <c:pt idx="1000">
+                  <c:v>45897</c:v>
+                </c:pt>
+                <c:pt idx="1001">
+                  <c:v>45904</c:v>
+                </c:pt>
+                <c:pt idx="1002">
+                  <c:v>45911</c:v>
+                </c:pt>
+                <c:pt idx="1003">
+                  <c:v>45918</c:v>
+                </c:pt>
+                <c:pt idx="1004">
+                  <c:v>45925</c:v>
+                </c:pt>
+                <c:pt idx="1005">
+                  <c:v>45932</c:v>
+                </c:pt>
+                <c:pt idx="1006">
+                  <c:v>45939</c:v>
+                </c:pt>
+                <c:pt idx="1007">
+                  <c:v>45946</c:v>
+                </c:pt>
+                <c:pt idx="1008">
+                  <c:v>45953</c:v>
+                </c:pt>
+                <c:pt idx="1009">
+                  <c:v>45960</c:v>
+                </c:pt>
+                <c:pt idx="1010">
+                  <c:v>45967</c:v>
+                </c:pt>
+                <c:pt idx="1011">
+                  <c:v>45974</c:v>
+                </c:pt>
+                <c:pt idx="1012">
+                  <c:v>45981</c:v>
+                </c:pt>
+                <c:pt idx="1013">
+                  <c:v>45988</c:v>
+                </c:pt>
+                <c:pt idx="1014">
+                  <c:v>45995</c:v>
+                </c:pt>
+                <c:pt idx="1015">
+                  <c:v>46002</c:v>
+                </c:pt>
+                <c:pt idx="1016">
+                  <c:v>46009</c:v>
+                </c:pt>
+                <c:pt idx="1017">
+                  <c:v>46016</c:v>
+                </c:pt>
+                <c:pt idx="1018">
+                  <c:v>46023</c:v>
+                </c:pt>
+                <c:pt idx="1019">
+                  <c:v>46030</c:v>
+                </c:pt>
+                <c:pt idx="1020">
+                  <c:v>46037</c:v>
+                </c:pt>
+                <c:pt idx="1021">
+                  <c:v>46044</c:v>
+                </c:pt>
+                <c:pt idx="1022">
+                  <c:v>46051</c:v>
+                </c:pt>
+                <c:pt idx="1023">
+                  <c:v>46058</c:v>
+                </c:pt>
+                <c:pt idx="1024">
+                  <c:v>46065</c:v>
+                </c:pt>
+                <c:pt idx="1025">
+                  <c:v>46072</c:v>
+                </c:pt>
+                <c:pt idx="1026">
+                  <c:v>46079</c:v>
+                </c:pt>
+                <c:pt idx="1027">
+                  <c:v>46086</c:v>
+                </c:pt>
+                <c:pt idx="1028">
+                  <c:v>46093</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>NAAIM!$E$2:$E$1030</c:f>
+              <c:numCache>
+                <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
+                <c:ptCount val="1029"/>
+                <c:pt idx="0">
+                  <c:v>19.440000000000001</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>31.2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>19.444444444444443</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>31.2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>18.760000000000002</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>17.375</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>44.233333333333334</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>45.018749999999997</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>38.6</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>42.095238095238095</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>42.095238095238095</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>49.38095238095238</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>45.8</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>78</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>49.904761904761905</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>69.7</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>60.090909090909093</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>84.409090909090907</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>80.16</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>80.958333333333329</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>73.956521739130437</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>68.095238095238102</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>92.428571428571431</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>86.668214285714285</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>74.730769230769226</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>93</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>92.909090909090907</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>85.173913043478265</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>100.04761904761905</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>58.884615384615387</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>84.89473684210526</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>72.590909090909093</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>80.75</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>82</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>79.090909090909093</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>73.681818181818187</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>89.333333333333329</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>52.4</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>38.05263157894737</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>47.695652173913047</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>44.541666666666664</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>45.653846153846153</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>59.32</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>54.142857142857146</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>75.42307692307692</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>82.666666666666671</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>73.833333333333329</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>87.375</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>82.5</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>80.545454545454547</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>57.633333333333333</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>53.04</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>61.472222222222221</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>74.225806451612897</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>56.0625</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>62.393939393939391</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>74.13333333333334</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>40.58064516129032</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>43.81818181818182</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>21.25</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>38.1875</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>-2.1111111111111112</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>39.625</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>46.551724137931032</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>63.5</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>77.36363636363636</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>75.49484848484849</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>66.433333333333337</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>86.464285714285708</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>69.142857142857139</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>65.692307692307693</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>84.444444444444443</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>68.34615384615384</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>51.041666666666664</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>51.071428571428569</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>69.433333333333337</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>73.571428571428569</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>56.269230769230766</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>74.785714285714292</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>83.551724137931032</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>41.448275862068968</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>12.919354838709678</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>39.911764705882355</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>25.62962962962963</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>30.892857142857142</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>15.333333333333334</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>33.666666666666664</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>13.962962962962964</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>38.34375</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>45.28</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>44</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>26.689655172413794</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>42.071428571428569</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>46.92</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>49.861111111111114</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>59.269230769230766</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>74.470588235294116</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>66.037037037037038</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>56.410256410256409</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>68.724137931034477</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>69.484848484848484</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>58.151515151515149</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>36.45945945945946</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>44.222222222222221</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>28.027777777777779</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>2.0285714285714285</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>10.216216216216216</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>13.8125</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>12.56</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>18.303030303030305</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>33.270270270270274</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>39.764705882352942</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>30.028571428571428</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>29.918918918918919</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>28.319444444444443</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>16.085714285714285</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>19.111111111111111</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>16.26829268292683</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>-2.9722222222222223</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>8.3684210526315788</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>9.617647058823529</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>15.060606060606061</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>11.705882352941176</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>9.6666666666666661</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>9.6470588235294112</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>3.6774193548387095</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>14.428571428571429</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>24.411764705882351</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>22.055555555555557</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>29.085714285714285</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>26.514285714285716</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>19.666666666666668</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>20.223529411764705</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>17.8</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>24.142857142857142</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>25.972972972972972</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>13.352941176470589</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>2.1470588235294117</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>4.2285714285714286</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>9.9705882352941178</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>47.75</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>18.85483870967742</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>35.303030303030305</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>41.611111111111114</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>22.666666666666668</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>35.757575757575758</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>33.185185185185183</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>56.815789473684212</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>50.414634146341463</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>40.341463414634148</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>51.46153846153846</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>64.8125</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>49.92307692307692</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>27.972222222222221</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>35.666666666666664</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>21.648648648648649</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>22.606060606060606</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>37.378378378378379</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>37.411764705882355</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>69</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>51.5625</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>31.216216216216218</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>55.212121212121211</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>54.70967741935484</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>63.060606060606062</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>68</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>80.638888888888886</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>86.409090909090907</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>67.857142857142861</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>74.382352941176464</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>77.833333333333329</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>74.675675675675677</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>64.944444444444443</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>69.205882352941174</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>65.5625</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>67.068965517241381</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>82.1875</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>68.743589743589737</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>75.567567567567565</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>61.083333333333336</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>74.558823529411768</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>70.648648648648646</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>72.974358974358978</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>63.833333333333336</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>61.905405405405403</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>33.179487179487182</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>21.763157894736842</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>36.514285714285712</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>44.545454545454547</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>54.885714285714286</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>51.189189189189186</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>77.303030303030297</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>76.451612903225808</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>83.264705882352942</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>85.911764705882348</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>77.222222222222229</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>81.638888888888886</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>83.90789473684211</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>67.892857142857139</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>42.386363636363633</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>40.384615384615387</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>40.666666666666664</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>27.05</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>34.761904761904759</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>30.416666666666668</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>54.243243243243242</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>36.054054054054056</c:v>
+                </c:pt>
+                <c:pt idx="211">
+                  <c:v>13.473684210526315</c:v>
+                </c:pt>
+                <c:pt idx="212">
+                  <c:v>49.85</c:v>
+                </c:pt>
+                <c:pt idx="213">
+                  <c:v>45.333333333333336</c:v>
+                </c:pt>
+                <c:pt idx="214">
+                  <c:v>50.212121212121211</c:v>
+                </c:pt>
+                <c:pt idx="215">
+                  <c:v>59.111111111111114</c:v>
+                </c:pt>
+                <c:pt idx="216">
+                  <c:v>54.675675675675677</c:v>
+                </c:pt>
+                <c:pt idx="217">
+                  <c:v>56.078947368421055</c:v>
+                </c:pt>
+                <c:pt idx="218">
+                  <c:v>43.944444444444443</c:v>
+                </c:pt>
+                <c:pt idx="219">
+                  <c:v>52.783783783783782</c:v>
+                </c:pt>
+                <c:pt idx="220">
+                  <c:v>48.264705882352942</c:v>
+                </c:pt>
+                <c:pt idx="221">
+                  <c:v>42.303030303030305</c:v>
+                </c:pt>
+                <c:pt idx="222">
+                  <c:v>55.294117647058826</c:v>
+                </c:pt>
+                <c:pt idx="223">
+                  <c:v>68.264705882352942</c:v>
+                </c:pt>
+                <c:pt idx="224">
+                  <c:v>76.416666666666671</c:v>
+                </c:pt>
+                <c:pt idx="225">
+                  <c:v>67.13513513513513</c:v>
+                </c:pt>
+                <c:pt idx="226">
+                  <c:v>72.171428571428578</c:v>
+                </c:pt>
+                <c:pt idx="227">
+                  <c:v>57.65625</c:v>
+                </c:pt>
+                <c:pt idx="228">
+                  <c:v>69.470588235294116</c:v>
+                </c:pt>
+                <c:pt idx="229">
+                  <c:v>71.457142857142856</c:v>
+                </c:pt>
+                <c:pt idx="230">
+                  <c:v>66.589743589743591</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>66.666666666666671</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>62.472222222222221</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>63.10526315789474</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>74.743589743589737</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>81.825000000000003</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>80.212121212121218</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>78.513513513513516</c:v>
+                </c:pt>
+                <c:pt idx="238">
+                  <c:v>76.88095238095238</c:v>
+                </c:pt>
+                <c:pt idx="239">
+                  <c:v>70.828571428571422</c:v>
+                </c:pt>
+                <c:pt idx="240">
+                  <c:v>76.17647058823529</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>82.125</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>86.277777777777771</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>83.731707317073173</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>68.125</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>70.916666666666671</c:v>
+                </c:pt>
+                <c:pt idx="246">
+                  <c:v>75.34210526315789</c:v>
+                </c:pt>
+                <c:pt idx="247">
+                  <c:v>41</c:v>
+                </c:pt>
+                <c:pt idx="248">
+                  <c:v>50.833333333333336</c:v>
+                </c:pt>
+                <c:pt idx="249">
+                  <c:v>70.918918918918919</c:v>
+                </c:pt>
+                <c:pt idx="250">
+                  <c:v>80.787878787878782</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>80.634146341463421</c:v>
+                </c:pt>
+                <c:pt idx="252">
+                  <c:v>82.952380952380949</c:v>
+                </c:pt>
+                <c:pt idx="253">
+                  <c:v>81.900000000000006</c:v>
+                </c:pt>
+                <c:pt idx="254">
+                  <c:v>76.129032258064512</c:v>
+                </c:pt>
+                <c:pt idx="255">
+                  <c:v>74.659090909090907</c:v>
+                </c:pt>
+                <c:pt idx="256">
+                  <c:v>68.410256410256409</c:v>
+                </c:pt>
+                <c:pt idx="257">
+                  <c:v>58.930232558139537</c:v>
+                </c:pt>
+                <c:pt idx="258">
+                  <c:v>52.857142857142854</c:v>
+                </c:pt>
+                <c:pt idx="259">
+                  <c:v>42.791666666666664</c:v>
+                </c:pt>
+                <c:pt idx="260">
+                  <c:v>25.952380952380953</c:v>
+                </c:pt>
+                <c:pt idx="261">
+                  <c:v>29.274999999999999</c:v>
+                </c:pt>
+                <c:pt idx="262">
+                  <c:v>31.975609756097562</c:v>
+                </c:pt>
+                <c:pt idx="263">
+                  <c:v>50.387096774193552</c:v>
+                </c:pt>
+                <c:pt idx="264">
+                  <c:v>53.93333333333333</c:v>
+                </c:pt>
+                <c:pt idx="265">
+                  <c:v>66.307692307692307</c:v>
+                </c:pt>
+                <c:pt idx="266">
+                  <c:v>62.695128205128206</c:v>
+                </c:pt>
+                <c:pt idx="267">
+                  <c:v>32.871794871794869</c:v>
+                </c:pt>
+                <c:pt idx="268">
+                  <c:v>21.404761904761905</c:v>
+                </c:pt>
+                <c:pt idx="269">
+                  <c:v>28.777777777777779</c:v>
+                </c:pt>
+                <c:pt idx="270">
+                  <c:v>20.170731707317074</c:v>
+                </c:pt>
+                <c:pt idx="271">
+                  <c:v>22.19047619047619</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>25.31111111111111</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>26.777777777777779</c:v>
+                </c:pt>
+                <c:pt idx="274">
+                  <c:v>27.903846153846153</c:v>
+                </c:pt>
+                <c:pt idx="275">
+                  <c:v>4.1749999999999998</c:v>
+                </c:pt>
+                <c:pt idx="276">
+                  <c:v>-3.5609756097560976</c:v>
+                </c:pt>
+                <c:pt idx="277">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="278">
+                  <c:v>21.318181818181817</c:v>
+                </c:pt>
+                <c:pt idx="279">
+                  <c:v>38.116279069767444</c:v>
+                </c:pt>
+                <c:pt idx="280">
+                  <c:v>45.424999999999997</c:v>
+                </c:pt>
+                <c:pt idx="281">
+                  <c:v>44.051282051282051</c:v>
+                </c:pt>
+                <c:pt idx="282">
+                  <c:v>54</c:v>
+                </c:pt>
+                <c:pt idx="283">
+                  <c:v>34.772368421052626</c:v>
+                </c:pt>
+                <c:pt idx="284">
+                  <c:v>30.021749999999997</c:v>
+                </c:pt>
+                <c:pt idx="285">
+                  <c:v>34.799999999999997</c:v>
+                </c:pt>
+                <c:pt idx="286">
+                  <c:v>35.694499999999998</c:v>
+                </c:pt>
+                <c:pt idx="287">
+                  <c:v>36.624047619047623</c:v>
+                </c:pt>
+                <c:pt idx="288">
+                  <c:v>43.560975609756099</c:v>
+                </c:pt>
+                <c:pt idx="289">
+                  <c:v>43.136363636363633</c:v>
+                </c:pt>
+                <c:pt idx="290">
+                  <c:v>49.341463414634148</c:v>
+                </c:pt>
+                <c:pt idx="291">
+                  <c:v>52.5</c:v>
+                </c:pt>
+                <c:pt idx="292">
+                  <c:v>56.333333333333336</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>67.522727272727266</c:v>
+                </c:pt>
+                <c:pt idx="294">
+                  <c:v>72.659090909090907</c:v>
+                </c:pt>
+                <c:pt idx="295">
+                  <c:v>73</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>76.275000000000006</c:v>
+                </c:pt>
+                <c:pt idx="297">
+                  <c:v>73.780487804878049</c:v>
+                </c:pt>
+                <c:pt idx="298">
+                  <c:v>57.368421052631582</c:v>
+                </c:pt>
+                <c:pt idx="299">
+                  <c:v>71.78947368421052</c:v>
+                </c:pt>
+                <c:pt idx="300">
+                  <c:v>68.641025641025635</c:v>
+                </c:pt>
+                <c:pt idx="301">
+                  <c:v>71.971428571428575</c:v>
+                </c:pt>
+                <c:pt idx="302">
+                  <c:v>69.815789473684205</c:v>
+                </c:pt>
+                <c:pt idx="303">
+                  <c:v>51.928571428571431</c:v>
+                </c:pt>
+                <c:pt idx="304">
+                  <c:v>46.138888888888886</c:v>
+                </c:pt>
+                <c:pt idx="305">
+                  <c:v>48.306774193548385</c:v>
+                </c:pt>
+                <c:pt idx="306">
+                  <c:v>63.68333333333333</c:v>
+                </c:pt>
+                <c:pt idx="307">
+                  <c:v>64.208684210526329</c:v>
+                </c:pt>
+                <c:pt idx="308">
+                  <c:v>58.713999999999999</c:v>
+                </c:pt>
+                <c:pt idx="309">
+                  <c:v>31.78</c:v>
+                </c:pt>
+                <c:pt idx="310">
+                  <c:v>28.651315789473685</c:v>
+                </c:pt>
+                <c:pt idx="311">
+                  <c:v>49.320882352941169</c:v>
+                </c:pt>
+                <c:pt idx="312">
+                  <c:v>43.629428571428576</c:v>
+                </c:pt>
+                <c:pt idx="313">
+                  <c:v>52.331891891891892</c:v>
+                </c:pt>
+                <c:pt idx="314">
+                  <c:v>44.844117647058823</c:v>
+                </c:pt>
+                <c:pt idx="315">
+                  <c:v>63.280645161290323</c:v>
+                </c:pt>
+                <c:pt idx="316">
+                  <c:v>61.846388888888896</c:v>
+                </c:pt>
+                <c:pt idx="317">
+                  <c:v>67.735142857142861</c:v>
+                </c:pt>
+                <c:pt idx="318">
+                  <c:v>74.38878787878788</c:v>
+                </c:pt>
+                <c:pt idx="319">
+                  <c:v>67.804864864864854</c:v>
+                </c:pt>
+                <c:pt idx="320">
+                  <c:v>70.75333333333333</c:v>
+                </c:pt>
+                <c:pt idx="321">
+                  <c:v>76.259444444444455</c:v>
+                </c:pt>
+                <c:pt idx="322">
+                  <c:v>69.205454545454543</c:v>
+                </c:pt>
+                <c:pt idx="323">
+                  <c:v>82.894000000000005</c:v>
+                </c:pt>
+                <c:pt idx="324">
+                  <c:v>77.425641025641028</c:v>
+                </c:pt>
+                <c:pt idx="325">
+                  <c:v>72.99351351351352</c:v>
+                </c:pt>
+                <c:pt idx="326">
+                  <c:v>81.186129032258066</c:v>
+                </c:pt>
+                <c:pt idx="327">
+                  <c:v>69.75</c:v>
+                </c:pt>
+                <c:pt idx="328">
+                  <c:v>76.029411764705884</c:v>
+                </c:pt>
+                <c:pt idx="329">
+                  <c:v>64.59375</c:v>
+                </c:pt>
+                <c:pt idx="330">
+                  <c:v>65.375</c:v>
+                </c:pt>
+                <c:pt idx="331">
+                  <c:v>64.385142857142853</c:v>
+                </c:pt>
+                <c:pt idx="332">
+                  <c:v>75.113142857142861</c:v>
+                </c:pt>
+                <c:pt idx="333">
+                  <c:v>57.953030303030303</c:v>
+                </c:pt>
+                <c:pt idx="334">
+                  <c:v>67.22</c:v>
+                </c:pt>
+                <c:pt idx="335">
+                  <c:v>64.2</c:v>
+                </c:pt>
+                <c:pt idx="336">
+                  <c:v>55.189189189189186</c:v>
+                </c:pt>
+                <c:pt idx="337">
+                  <c:v>75.71142857142857</c:v>
+                </c:pt>
+                <c:pt idx="338">
+                  <c:v>82.905555555555551</c:v>
+                </c:pt>
+                <c:pt idx="339">
+                  <c:v>80.186666666666667</c:v>
+                </c:pt>
+                <c:pt idx="340">
+                  <c:v>88.103448275862064</c:v>
+                </c:pt>
+                <c:pt idx="341">
+                  <c:v>75.98088235294118</c:v>
+                </c:pt>
+                <c:pt idx="342">
+                  <c:v>83.266666666666666</c:v>
+                </c:pt>
+                <c:pt idx="343">
+                  <c:v>84.672499999999999</c:v>
+                </c:pt>
+                <c:pt idx="344">
+                  <c:v>86.3839393939394</c:v>
+                </c:pt>
+                <c:pt idx="345">
+                  <c:v>104.25</c:v>
+                </c:pt>
+                <c:pt idx="346">
+                  <c:v>94.060606060606062</c:v>
+                </c:pt>
+                <c:pt idx="347">
+                  <c:v>89.85387096774194</c:v>
+                </c:pt>
+                <c:pt idx="348">
+                  <c:v>91.066578947368413</c:v>
+                </c:pt>
+                <c:pt idx="349">
+                  <c:v>82.765625</c:v>
+                </c:pt>
+                <c:pt idx="350">
+                  <c:v>90.146206896551718</c:v>
+                </c:pt>
+                <c:pt idx="351">
+                  <c:v>85.637931034482762</c:v>
+                </c:pt>
+                <c:pt idx="352">
+                  <c:v>79.768620689655165</c:v>
+                </c:pt>
+                <c:pt idx="353">
+                  <c:v>80.063636363636363</c:v>
+                </c:pt>
+                <c:pt idx="354">
+                  <c:v>72.707999999999998</c:v>
+                </c:pt>
+                <c:pt idx="355">
+                  <c:v>77.250882352941176</c:v>
+                </c:pt>
+                <c:pt idx="356">
+                  <c:v>69.63</c:v>
+                </c:pt>
+                <c:pt idx="357">
+                  <c:v>69.903225806451616</c:v>
+                </c:pt>
+                <c:pt idx="358">
+                  <c:v>80.612903225806448</c:v>
+                </c:pt>
+                <c:pt idx="359">
+                  <c:v>79.106129032258067</c:v>
+                </c:pt>
+                <c:pt idx="360">
+                  <c:v>84.23193548387097</c:v>
+                </c:pt>
+                <c:pt idx="361">
+                  <c:v>82.018235294117645</c:v>
+                </c:pt>
+                <c:pt idx="362">
+                  <c:v>77.19259259259259</c:v>
+                </c:pt>
+                <c:pt idx="363">
+                  <c:v>51.58387096774193</c:v>
+                </c:pt>
+                <c:pt idx="364">
+                  <c:v>61.897333333333336</c:v>
+                </c:pt>
+                <c:pt idx="365">
+                  <c:v>51.525357142857146</c:v>
+                </c:pt>
+                <c:pt idx="366">
+                  <c:v>34.214285714285715</c:v>
+                </c:pt>
+                <c:pt idx="367">
+                  <c:v>39.910344827586208</c:v>
+                </c:pt>
+                <c:pt idx="368">
+                  <c:v>47.077500000000001</c:v>
+                </c:pt>
+                <c:pt idx="369">
+                  <c:v>61.729166666666664</c:v>
+                </c:pt>
+                <c:pt idx="370">
+                  <c:v>87.496800000000007</c:v>
+                </c:pt>
+                <c:pt idx="371">
+                  <c:v>74.05263157894737</c:v>
+                </c:pt>
+                <c:pt idx="372">
+                  <c:v>75.703703703703709</c:v>
+                </c:pt>
+                <c:pt idx="373">
+                  <c:v>69.84615384615384</c:v>
+                </c:pt>
+                <c:pt idx="374">
+                  <c:v>34.764705882352942</c:v>
+                </c:pt>
+                <c:pt idx="375">
+                  <c:v>46.92307692307692</c:v>
+                </c:pt>
+                <c:pt idx="376">
+                  <c:v>42.25925925925926</c:v>
+                </c:pt>
+                <c:pt idx="377">
+                  <c:v>66.75</c:v>
+                </c:pt>
+                <c:pt idx="378">
+                  <c:v>62.481481481481481</c:v>
+                </c:pt>
+                <c:pt idx="379">
+                  <c:v>80.46555555555554</c:v>
+                </c:pt>
+                <c:pt idx="380">
+                  <c:v>73.13333333333334</c:v>
+                </c:pt>
+                <c:pt idx="381">
+                  <c:v>54.260869565217391</c:v>
+                </c:pt>
+                <c:pt idx="382">
+                  <c:v>82.045454545454547</c:v>
+                </c:pt>
+                <c:pt idx="383">
+                  <c:v>79.370370370370367</c:v>
+                </c:pt>
+                <c:pt idx="384">
+                  <c:v>94.592592592592595</c:v>
+                </c:pt>
+                <c:pt idx="385">
+                  <c:v>84.807692307692307</c:v>
+                </c:pt>
+                <c:pt idx="386">
+                  <c:v>80.666666666666671</c:v>
+                </c:pt>
+                <c:pt idx="387">
+                  <c:v>87.428571428571431</c:v>
+                </c:pt>
+                <c:pt idx="388">
+                  <c:v>101.44851851851851</c:v>
+                </c:pt>
+                <c:pt idx="389">
+                  <c:v>94.748750000000015</c:v>
+                </c:pt>
+                <c:pt idx="390">
+                  <c:v>100.69347826086955</c:v>
+                </c:pt>
+                <c:pt idx="391">
+                  <c:v>94.34615384615384</c:v>
+                </c:pt>
+                <c:pt idx="392">
+                  <c:v>98.944444444444443</c:v>
+                </c:pt>
+                <c:pt idx="393">
+                  <c:v>95.032258064516128</c:v>
+                </c:pt>
+                <c:pt idx="394">
+                  <c:v>92.274000000000001</c:v>
+                </c:pt>
+                <c:pt idx="395">
+                  <c:v>96.834230769230771</c:v>
+                </c:pt>
+                <c:pt idx="396">
+                  <c:v>95.13384615384615</c:v>
+                </c:pt>
+                <c:pt idx="397">
+                  <c:v>70.941111111111113</c:v>
+                </c:pt>
+                <c:pt idx="398">
+                  <c:v>50.971923076923076</c:v>
+                </c:pt>
+                <c:pt idx="399">
+                  <c:v>73.260000000000005</c:v>
+                </c:pt>
+                <c:pt idx="400">
+                  <c:v>75.94793103448275</c:v>
+                </c:pt>
+                <c:pt idx="401">
+                  <c:v>91.620285714285714</c:v>
+                </c:pt>
+                <c:pt idx="402">
+                  <c:v>89.061153846153857</c:v>
+                </c:pt>
+                <c:pt idx="403">
+                  <c:v>85.204687500000006</c:v>
+                </c:pt>
+                <c:pt idx="404">
+                  <c:v>67.770571428571429</c:v>
+                </c:pt>
+                <c:pt idx="405">
+                  <c:v>89.839354838709681</c:v>
+                </c:pt>
+                <c:pt idx="406">
+                  <c:v>91.122666666666674</c:v>
+                </c:pt>
+                <c:pt idx="407">
+                  <c:v>91.432424242424247</c:v>
+                </c:pt>
+                <c:pt idx="408">
+                  <c:v>85.208620689655177</c:v>
+                </c:pt>
+                <c:pt idx="409">
+                  <c:v>75.919999999999987</c:v>
+                </c:pt>
+                <c:pt idx="410">
+                  <c:v>76.575757575757578</c:v>
+                </c:pt>
+                <c:pt idx="411">
+                  <c:v>82.626111111111115</c:v>
+                </c:pt>
+                <c:pt idx="412">
+                  <c:v>76.8125</c:v>
+                </c:pt>
+                <c:pt idx="413">
+                  <c:v>78.180000000000007</c:v>
+                </c:pt>
+                <c:pt idx="414">
+                  <c:v>67.229459459459449</c:v>
+                </c:pt>
+                <c:pt idx="415">
+                  <c:v>72.520526315789468</c:v>
+                </c:pt>
+                <c:pt idx="416">
+                  <c:v>90.864571428571438</c:v>
+                </c:pt>
+                <c:pt idx="417">
+                  <c:v>87.300588235294128</c:v>
+                </c:pt>
+                <c:pt idx="418">
+                  <c:v>88.59375</c:v>
+                </c:pt>
+                <c:pt idx="419">
+                  <c:v>88.154666666666671</c:v>
+                </c:pt>
+                <c:pt idx="420">
+                  <c:v>85.47682926829269</c:v>
+                </c:pt>
+                <c:pt idx="421">
+                  <c:v>82.468285714285727</c:v>
+                </c:pt>
+                <c:pt idx="422">
+                  <c:v>81.914117647058816</c:v>
+                </c:pt>
+                <c:pt idx="423">
+                  <c:v>82.746176470588239</c:v>
+                </c:pt>
+                <c:pt idx="424">
+                  <c:v>81.62</c:v>
+                </c:pt>
+                <c:pt idx="425">
+                  <c:v>50.867948717948714</c:v>
+                </c:pt>
+                <c:pt idx="426">
+                  <c:v>50.61238095238096</c:v>
+                </c:pt>
+                <c:pt idx="427">
+                  <c:v>56.771111111111111</c:v>
+                </c:pt>
+                <c:pt idx="428">
+                  <c:v>78.842777777777783</c:v>
+                </c:pt>
+                <c:pt idx="429">
+                  <c:v>82.491428571428571</c:v>
+                </c:pt>
+                <c:pt idx="430">
+                  <c:v>63.629117647058834</c:v>
+                </c:pt>
+                <c:pt idx="431">
+                  <c:v>67.077837837837848</c:v>
+                </c:pt>
+                <c:pt idx="432">
+                  <c:v>59.755641025641033</c:v>
+                </c:pt>
+                <c:pt idx="433">
+                  <c:v>41.032258064516128</c:v>
+                </c:pt>
+                <c:pt idx="434">
+                  <c:v>33.139117647058825</c:v>
+                </c:pt>
+                <c:pt idx="435">
+                  <c:v>9.9741935483870989</c:v>
+                </c:pt>
+                <c:pt idx="436">
+                  <c:v>41.378378378378379</c:v>
+                </c:pt>
+                <c:pt idx="437">
+                  <c:v>74.78378378378379</c:v>
+                </c:pt>
+                <c:pt idx="438">
+                  <c:v>77.681351351351353</c:v>
+                </c:pt>
+                <c:pt idx="439">
+                  <c:v>85.432105263157894</c:v>
+                </c:pt>
+                <c:pt idx="440">
+                  <c:v>72.063823529411764</c:v>
+                </c:pt>
+                <c:pt idx="441">
+                  <c:v>86.779999999999987</c:v>
+                </c:pt>
+                <c:pt idx="442">
+                  <c:v>86.063749999999999</c:v>
+                </c:pt>
+                <c:pt idx="443">
+                  <c:v>89.011891891891892</c:v>
+                </c:pt>
+                <c:pt idx="444">
+                  <c:v>65.116571428571433</c:v>
+                </c:pt>
+                <c:pt idx="445">
+                  <c:v>90.592500000000001</c:v>
+                </c:pt>
+                <c:pt idx="446">
+                  <c:v>95.863235294117644</c:v>
+                </c:pt>
+                <c:pt idx="447">
+                  <c:v>71.114285714285714</c:v>
+                </c:pt>
+                <c:pt idx="448">
+                  <c:v>87.125789473684208</c:v>
+                </c:pt>
+                <c:pt idx="449">
+                  <c:v>89.011891891891892</c:v>
+                </c:pt>
+                <c:pt idx="450">
+                  <c:v>92.622285714285709</c:v>
+                </c:pt>
+                <c:pt idx="451">
+                  <c:v>88.242333333333335</c:v>
+                </c:pt>
+                <c:pt idx="452">
+                  <c:v>84.054374999999993</c:v>
+                </c:pt>
+                <c:pt idx="453">
+                  <c:v>87.811388888888885</c:v>
+                </c:pt>
+                <c:pt idx="454">
+                  <c:v>99.226470588235287</c:v>
+                </c:pt>
+                <c:pt idx="455">
+                  <c:v>92.151333333333326</c:v>
+                </c:pt>
+                <c:pt idx="456">
+                  <c:v>65.679000000000002</c:v>
+                </c:pt>
+                <c:pt idx="457">
+                  <c:v>84.321481481481499</c:v>
+                </c:pt>
+                <c:pt idx="458">
+                  <c:v>75.863846153846154</c:v>
+                </c:pt>
+                <c:pt idx="459">
+                  <c:v>86.725555555555559</c:v>
+                </c:pt>
+                <c:pt idx="460">
+                  <c:v>86.667741935483861</c:v>
+                </c:pt>
+                <c:pt idx="461">
+                  <c:v>75.884705882352932</c:v>
+                </c:pt>
+                <c:pt idx="462">
+                  <c:v>90.596666666666664</c:v>
+                </c:pt>
+                <c:pt idx="463">
+                  <c:v>80.304347826086953</c:v>
+                </c:pt>
+                <c:pt idx="464">
+                  <c:v>60.378620689655172</c:v>
+                </c:pt>
+                <c:pt idx="465">
+                  <c:v>67.605142857142852</c:v>
+                </c:pt>
+                <c:pt idx="466">
+                  <c:v>65.50393939393939</c:v>
+                </c:pt>
+                <c:pt idx="467">
+                  <c:v>71.069687500000001</c:v>
+                </c:pt>
+                <c:pt idx="468">
+                  <c:v>68.703666666666649</c:v>
+                </c:pt>
+                <c:pt idx="469">
+                  <c:v>58.636896551724128</c:v>
+                </c:pt>
+                <c:pt idx="470">
+                  <c:v>58.963793103448268</c:v>
+                </c:pt>
+                <c:pt idx="471">
+                  <c:v>54.842857142857142</c:v>
+                </c:pt>
+                <c:pt idx="472">
+                  <c:v>54.990666666666662</c:v>
+                </c:pt>
+                <c:pt idx="473">
+                  <c:v>52.239999999999995</c:v>
+                </c:pt>
+                <c:pt idx="474">
+                  <c:v>52.341923076923074</c:v>
+                </c:pt>
+                <c:pt idx="475">
+                  <c:v>50.75</c:v>
+                </c:pt>
+                <c:pt idx="476">
+                  <c:v>63.167857142857144</c:v>
+                </c:pt>
+                <c:pt idx="477">
+                  <c:v>48.079032258064508</c:v>
+                </c:pt>
+                <c:pt idx="478">
+                  <c:v>41.480303030303027</c:v>
+                </c:pt>
+                <c:pt idx="479">
+                  <c:v>28.313750000000002</c:v>
+                </c:pt>
+                <c:pt idx="480">
+                  <c:v>23.848214285714285</c:v>
+                </c:pt>
+                <c:pt idx="481">
+                  <c:v>26.035714285714285</c:v>
+                </c:pt>
+                <c:pt idx="482">
+                  <c:v>31.573548387096775</c:v>
+                </c:pt>
+                <c:pt idx="483">
+                  <c:v>21.335517241379311</c:v>
+                </c:pt>
+                <c:pt idx="484">
+                  <c:v>16.391290322580645</c:v>
+                </c:pt>
+                <c:pt idx="485">
+                  <c:v>38.298148148148144</c:v>
+                </c:pt>
+                <c:pt idx="486">
+                  <c:v>44.269230769230766</c:v>
+                </c:pt>
+                <c:pt idx="487">
+                  <c:v>35.666666666666664</c:v>
+                </c:pt>
+                <c:pt idx="488">
+                  <c:v>56.71206896551724</c:v>
+                </c:pt>
+                <c:pt idx="489">
+                  <c:v>69.164516129032251</c:v>
+                </c:pt>
+                <c:pt idx="490">
+                  <c:v>68.58275862068966</c:v>
+                </c:pt>
+                <c:pt idx="491">
+                  <c:v>58.465483870967738</c:v>
+                </c:pt>
+                <c:pt idx="492">
+                  <c:v>70.445172413793102</c:v>
+                </c:pt>
+                <c:pt idx="493">
+                  <c:v>68.115384615384613</c:v>
+                </c:pt>
+                <c:pt idx="494">
+                  <c:v>67.916206896551728</c:v>
+                </c:pt>
+                <c:pt idx="495">
+                  <c:v>61.323703703703714</c:v>
+                </c:pt>
+                <c:pt idx="496">
+                  <c:v>56.657241379310342</c:v>
+                </c:pt>
+                <c:pt idx="497">
+                  <c:v>47.669375000000002</c:v>
+                </c:pt>
+                <c:pt idx="498">
+                  <c:v>50.256999999999998</c:v>
+                </c:pt>
+                <c:pt idx="499">
+                  <c:v>34.496296296296293</c:v>
+                </c:pt>
+                <c:pt idx="500">
+                  <c:v>42.25</c:v>
+                </c:pt>
+                <c:pt idx="501">
+                  <c:v>22.407407407407408</c:v>
+                </c:pt>
+                <c:pt idx="502">
+                  <c:v>32.871428571428574</c:v>
+                </c:pt>
+                <c:pt idx="503">
+                  <c:v>41.051724137931032</c:v>
+                </c:pt>
+                <c:pt idx="504">
+                  <c:v>31.654838709677424</c:v>
+                </c:pt>
+                <c:pt idx="505">
+                  <c:v>54.436363636363637</c:v>
+                </c:pt>
+                <c:pt idx="506">
+                  <c:v>51.012903225806454</c:v>
+                </c:pt>
+                <c:pt idx="507">
+                  <c:v>62.716666666666669</c:v>
+                </c:pt>
+                <c:pt idx="508">
+                  <c:v>59.585294117647059</c:v>
+                </c:pt>
+                <c:pt idx="509">
+                  <c:v>67.941176470588232</c:v>
+                </c:pt>
+                <c:pt idx="510">
+                  <c:v>73.207894736842107</c:v>
+                </c:pt>
+                <c:pt idx="511">
+                  <c:v>63.972972972972975</c:v>
+                </c:pt>
+                <c:pt idx="512">
+                  <c:v>82.497142857142862</c:v>
+                </c:pt>
+                <c:pt idx="513">
+                  <c:v>74.188235294117646</c:v>
+                </c:pt>
+                <c:pt idx="514">
+                  <c:v>67.658823529411762</c:v>
+                </c:pt>
+                <c:pt idx="515">
+                  <c:v>49.546666666666667</c:v>
+                </c:pt>
+                <c:pt idx="516">
+                  <c:v>60.168750000000003</c:v>
+                </c:pt>
+                <c:pt idx="517">
+                  <c:v>64.666666666666671</c:v>
+                </c:pt>
+                <c:pt idx="518">
+                  <c:v>68.941176470588232</c:v>
+                </c:pt>
+                <c:pt idx="519">
+                  <c:v>74.8</c:v>
+                </c:pt>
+                <c:pt idx="520">
+                  <c:v>75.958620689655177</c:v>
+                </c:pt>
+                <c:pt idx="521">
+                  <c:v>69.348387096774204</c:v>
+                </c:pt>
+                <c:pt idx="522">
+                  <c:v>74.515151515151516</c:v>
+                </c:pt>
+                <c:pt idx="523">
+                  <c:v>65.433333333333337</c:v>
+                </c:pt>
+                <c:pt idx="524">
+                  <c:v>96.5234375</c:v>
+                </c:pt>
+                <c:pt idx="525">
+                  <c:v>92.639655172413796</c:v>
+                </c:pt>
+                <c:pt idx="526">
+                  <c:v>101.01774193548388</c:v>
+                </c:pt>
+                <c:pt idx="527">
+                  <c:v>93.053030303030297</c:v>
+                </c:pt>
+                <c:pt idx="528">
+                  <c:v>92.862903225806448</c:v>
+                </c:pt>
+                <c:pt idx="529">
+                  <c:v>98.791935483870972</c:v>
+                </c:pt>
+                <c:pt idx="530">
+                  <c:v>97.800000000000011</c:v>
+                </c:pt>
+                <c:pt idx="531">
+                  <c:v>88.1</c:v>
+                </c:pt>
+                <c:pt idx="532">
+                  <c:v>90.854285714285723</c:v>
+                </c:pt>
+                <c:pt idx="533">
+                  <c:v>68.55</c:v>
+                </c:pt>
+                <c:pt idx="534">
+                  <c:v>79.31481481481481</c:v>
+                </c:pt>
+                <c:pt idx="535">
+                  <c:v>84.516666666666666</c:v>
+                </c:pt>
+                <c:pt idx="536">
+                  <c:v>78.485294117647058</c:v>
+                </c:pt>
+                <c:pt idx="537">
+                  <c:v>86.532258064516128</c:v>
+                </c:pt>
+                <c:pt idx="538">
+                  <c:v>63.703125</c:v>
+                </c:pt>
+                <c:pt idx="539">
+                  <c:v>66.469696969696969</c:v>
+                </c:pt>
+                <c:pt idx="540">
+                  <c:v>58.083333333333336</c:v>
+                </c:pt>
+                <c:pt idx="541">
+                  <c:v>72.962962962962962</c:v>
+                </c:pt>
+                <c:pt idx="542">
+                  <c:v>83.421875</c:v>
+                </c:pt>
+                <c:pt idx="543">
+                  <c:v>86.5625</c:v>
+                </c:pt>
+                <c:pt idx="544">
+                  <c:v>98.017857142857139</c:v>
+                </c:pt>
+                <c:pt idx="545">
+                  <c:v>101.60344827586206</c:v>
+                </c:pt>
+                <c:pt idx="546">
+                  <c:v>96.232142857142861</c:v>
+                </c:pt>
+                <c:pt idx="547">
+                  <c:v>101.32758620689656</c:v>
+                </c:pt>
+                <c:pt idx="548">
+                  <c:v>100.59615384615384</c:v>
+                </c:pt>
+                <c:pt idx="549">
+                  <c:v>99.425925925925924</c:v>
+                </c:pt>
+                <c:pt idx="550">
+                  <c:v>89.293103448275858</c:v>
+                </c:pt>
+                <c:pt idx="551">
+                  <c:v>94.08620689655173</c:v>
+                </c:pt>
+                <c:pt idx="552">
+                  <c:v>99.283333333333331</c:v>
+                </c:pt>
+                <c:pt idx="553">
+                  <c:v>94.016129032258064</c:v>
+                </c:pt>
+                <c:pt idx="554">
+                  <c:v>96.264705882352942</c:v>
+                </c:pt>
+                <c:pt idx="555">
+                  <c:v>95.892857142857139</c:v>
+                </c:pt>
+                <c:pt idx="556">
+                  <c:v>100.82758620689656</c:v>
+                </c:pt>
+                <c:pt idx="557">
+                  <c:v>102.06896551724138</c:v>
+                </c:pt>
+                <c:pt idx="558">
+                  <c:v>87.088709677419359</c:v>
+                </c:pt>
+                <c:pt idx="559">
+                  <c:v>80.7734375</c:v>
+                </c:pt>
+                <c:pt idx="560">
+                  <c:v>68.682692307692307</c:v>
+                </c:pt>
+                <c:pt idx="561">
+                  <c:v>68.282258064516128</c:v>
+                </c:pt>
+                <c:pt idx="562">
+                  <c:v>71.024193548387103</c:v>
+                </c:pt>
+                <c:pt idx="563">
+                  <c:v>82.947916666666671</c:v>
+                </c:pt>
+                <c:pt idx="564">
+                  <c:v>74.204545454545453</c:v>
+                </c:pt>
+                <c:pt idx="565">
+                  <c:v>88.091666666666669</c:v>
+                </c:pt>
+                <c:pt idx="566">
+                  <c:v>82.31</c:v>
+                </c:pt>
+                <c:pt idx="567">
+                  <c:v>95.198275862068968</c:v>
+                </c:pt>
+                <c:pt idx="568">
+                  <c:v>94.620370370370367</c:v>
+                </c:pt>
+                <c:pt idx="569">
+                  <c:v>97.491071428571431</c:v>
+                </c:pt>
+                <c:pt idx="570">
+                  <c:v>95.862903225806448</c:v>
+                </c:pt>
+                <c:pt idx="571">
+                  <c:v>92.098214285714292</c:v>
+                </c:pt>
+                <c:pt idx="572">
+                  <c:v>93.370689655172413</c:v>
+                </c:pt>
+                <c:pt idx="573">
+                  <c:v>92.694444444444443</c:v>
+                </c:pt>
+                <c:pt idx="574">
+                  <c:v>97.47</c:v>
+                </c:pt>
+                <c:pt idx="575">
+                  <c:v>93.356060606060609</c:v>
+                </c:pt>
+                <c:pt idx="576">
+                  <c:v>90.990384615384613</c:v>
+                </c:pt>
+                <c:pt idx="577">
+                  <c:v>85.818965517241381</c:v>
+                </c:pt>
+                <c:pt idx="578">
+                  <c:v>96.39</c:v>
+                </c:pt>
+                <c:pt idx="579">
+                  <c:v>90.947916666666671</c:v>
+                </c:pt>
+                <c:pt idx="580">
+                  <c:v>83.818965517241381</c:v>
+                </c:pt>
+                <c:pt idx="581">
+                  <c:v>85.191666666666663</c:v>
+                </c:pt>
+                <c:pt idx="582">
+                  <c:v>87.934210526315795</c:v>
+                </c:pt>
+                <c:pt idx="583">
+                  <c:v>84.083333333333329</c:v>
+                </c:pt>
+                <c:pt idx="584">
+                  <c:v>88.65625</c:v>
+                </c:pt>
+                <c:pt idx="585">
+                  <c:v>97.125</c:v>
+                </c:pt>
+                <c:pt idx="586">
+                  <c:v>102.04166666666667</c:v>
+                </c:pt>
+                <c:pt idx="587">
+                  <c:v>106.625</c:v>
+                </c:pt>
+                <c:pt idx="588">
+                  <c:v>109.2</c:v>
+                </c:pt>
+                <c:pt idx="589">
+                  <c:v>95.837500000000006</c:v>
+                </c:pt>
+                <c:pt idx="590">
+                  <c:v>95.375</c:v>
+                </c:pt>
+                <c:pt idx="591">
+                  <c:v>91.36904761904762</c:v>
+                </c:pt>
+                <c:pt idx="592">
+                  <c:v>83.079545454545453</c:v>
+                </c:pt>
+                <c:pt idx="593">
+                  <c:v>87.23</c:v>
+                </c:pt>
+                <c:pt idx="594">
+                  <c:v>78.510000000000005</c:v>
+                </c:pt>
+                <c:pt idx="595">
+                  <c:v>88.36904761904762</c:v>
+                </c:pt>
+                <c:pt idx="596">
+                  <c:v>97.336956521739125</c:v>
+                </c:pt>
+                <c:pt idx="597">
+                  <c:v>89.836538461538467</c:v>
+                </c:pt>
+                <c:pt idx="598">
+                  <c:v>120.55555555555556</c:v>
+                </c:pt>
+                <c:pt idx="599">
+                  <c:v>101.8452380952381</c:v>
+                </c:pt>
+                <c:pt idx="600">
+                  <c:v>96.293478260869563</c:v>
+                </c:pt>
+                <c:pt idx="601">
+                  <c:v>90.397727272727266</c:v>
+                </c:pt>
+                <c:pt idx="602">
+                  <c:v>88.881578947368425</c:v>
+                </c:pt>
+                <c:pt idx="603">
+                  <c:v>86.34</c:v>
+                </c:pt>
+                <c:pt idx="604">
+                  <c:v>95.38</c:v>
+                </c:pt>
+                <c:pt idx="605">
+                  <c:v>84.93</c:v>
+                </c:pt>
+                <c:pt idx="606">
+                  <c:v>75.900000000000006</c:v>
+                </c:pt>
+                <c:pt idx="607">
+                  <c:v>65.430000000000007</c:v>
+                </c:pt>
+                <c:pt idx="608">
+                  <c:v>62.69</c:v>
+                </c:pt>
+                <c:pt idx="609">
+                  <c:v>81</c:v>
+                </c:pt>
+                <c:pt idx="610">
+                  <c:v>72.05</c:v>
+                </c:pt>
+                <c:pt idx="611">
+                  <c:v>85.35</c:v>
+                </c:pt>
+                <c:pt idx="612">
+                  <c:v>77.28</c:v>
+                </c:pt>
+                <c:pt idx="613">
+                  <c:v>49.36</c:v>
+                </c:pt>
+                <c:pt idx="614">
+                  <c:v>55.57</c:v>
+                </c:pt>
+                <c:pt idx="615">
+                  <c:v>65.12</c:v>
+                </c:pt>
+                <c:pt idx="616">
+                  <c:v>77.64</c:v>
+                </c:pt>
+                <c:pt idx="617">
+                  <c:v>64.2</c:v>
+                </c:pt>
+                <c:pt idx="618">
+                  <c:v>52.56</c:v>
+                </c:pt>
+                <c:pt idx="619">
+                  <c:v>69.819999999999993</c:v>
+                </c:pt>
+                <c:pt idx="620">
+                  <c:v>85.43</c:v>
+                </c:pt>
+                <c:pt idx="621">
+                  <c:v>83.95</c:v>
+                </c:pt>
+                <c:pt idx="622">
+                  <c:v>82.24</c:v>
+                </c:pt>
+                <c:pt idx="623">
+                  <c:v>91.67</c:v>
+                </c:pt>
+                <c:pt idx="624">
+                  <c:v>103.93</c:v>
+                </c:pt>
+                <c:pt idx="625">
+                  <c:v>89.2</c:v>
+                </c:pt>
+                <c:pt idx="626">
+                  <c:v>85.06</c:v>
+                </c:pt>
+                <c:pt idx="627">
+                  <c:v>76.38</c:v>
+                </c:pt>
+                <c:pt idx="628">
+                  <c:v>88.56</c:v>
+                </c:pt>
+                <c:pt idx="629">
+                  <c:v>82.01</c:v>
+                </c:pt>
+                <c:pt idx="630">
+                  <c:v>84.96</c:v>
+                </c:pt>
+                <c:pt idx="631">
+                  <c:v>76.36</c:v>
+                </c:pt>
+                <c:pt idx="632">
+                  <c:v>87.68</c:v>
+                </c:pt>
+                <c:pt idx="633">
+                  <c:v>78.27</c:v>
+                </c:pt>
+                <c:pt idx="634">
+                  <c:v>86.46</c:v>
+                </c:pt>
+                <c:pt idx="635">
+                  <c:v>98.3</c:v>
+                </c:pt>
+                <c:pt idx="636">
+                  <c:v>85.01</c:v>
+                </c:pt>
+                <c:pt idx="637">
+                  <c:v>90.19</c:v>
+                </c:pt>
+                <c:pt idx="638">
+                  <c:v>83.92</c:v>
+                </c:pt>
+                <c:pt idx="639">
+                  <c:v>90.73</c:v>
+                </c:pt>
+                <c:pt idx="640">
+                  <c:v>84.49</c:v>
+                </c:pt>
+                <c:pt idx="641">
+                  <c:v>52.86</c:v>
+                </c:pt>
+                <c:pt idx="642">
+                  <c:v>67.760000000000005</c:v>
+                </c:pt>
+                <c:pt idx="643">
+                  <c:v>51.49</c:v>
+                </c:pt>
+                <c:pt idx="644">
+                  <c:v>61.47</c:v>
+                </c:pt>
+                <c:pt idx="645">
+                  <c:v>64.959999999999994</c:v>
+                </c:pt>
+                <c:pt idx="646">
+                  <c:v>35.130000000000003</c:v>
+                </c:pt>
+                <c:pt idx="647">
+                  <c:v>30.55</c:v>
+                </c:pt>
+                <c:pt idx="648">
+                  <c:v>53.21</c:v>
+                </c:pt>
+                <c:pt idx="649">
+                  <c:v>61.96</c:v>
+                </c:pt>
+                <c:pt idx="650">
+                  <c:v>55.51</c:v>
+                </c:pt>
+                <c:pt idx="651">
+                  <c:v>31.96</c:v>
+                </c:pt>
+                <c:pt idx="652">
+                  <c:v>47.59</c:v>
+                </c:pt>
+                <c:pt idx="653">
+                  <c:v>59.43</c:v>
+                </c:pt>
+                <c:pt idx="654">
+                  <c:v>66.8</c:v>
+                </c:pt>
+                <c:pt idx="655">
+                  <c:v>75.510000000000005</c:v>
+                </c:pt>
+                <c:pt idx="656">
+                  <c:v>72.84</c:v>
+                </c:pt>
+                <c:pt idx="657">
+                  <c:v>76.33</c:v>
+                </c:pt>
+                <c:pt idx="658">
+                  <c:v>83.39</c:v>
+                </c:pt>
+                <c:pt idx="659">
+                  <c:v>82.01</c:v>
+                </c:pt>
+                <c:pt idx="660">
+                  <c:v>77.86</c:v>
+                </c:pt>
+                <c:pt idx="661">
+                  <c:v>79.33</c:v>
+                </c:pt>
+                <c:pt idx="662">
+                  <c:v>73.900000000000006</c:v>
+                </c:pt>
+                <c:pt idx="663">
+                  <c:v>77.400000000000006</c:v>
+                </c:pt>
+                <c:pt idx="664">
+                  <c:v>78.25</c:v>
+                </c:pt>
+                <c:pt idx="665">
+                  <c:v>61.69</c:v>
+                </c:pt>
+                <c:pt idx="666">
+                  <c:v>91.92</c:v>
+                </c:pt>
+                <c:pt idx="667">
+                  <c:v>88.9</c:v>
+                </c:pt>
+                <c:pt idx="668">
+                  <c:v>93.37</c:v>
+                </c:pt>
+                <c:pt idx="669">
+                  <c:v>92.43</c:v>
+                </c:pt>
+                <c:pt idx="670">
+                  <c:v>89.8</c:v>
+                </c:pt>
+                <c:pt idx="671">
+                  <c:v>82.02</c:v>
+                </c:pt>
+                <c:pt idx="672">
+                  <c:v>72.819999999999993</c:v>
+                </c:pt>
+                <c:pt idx="673">
+                  <c:v>70.069999999999993</c:v>
+                </c:pt>
+                <c:pt idx="674">
+                  <c:v>59.69</c:v>
+                </c:pt>
+                <c:pt idx="675">
+                  <c:v>54.99</c:v>
+                </c:pt>
+                <c:pt idx="676">
+                  <c:v>74.260000000000005</c:v>
+                </c:pt>
+                <c:pt idx="677">
+                  <c:v>74.91</c:v>
+                </c:pt>
+                <c:pt idx="678">
+                  <c:v>72.28</c:v>
+                </c:pt>
+                <c:pt idx="679">
+                  <c:v>79.36</c:v>
+                </c:pt>
+                <c:pt idx="680">
+                  <c:v>87.34</c:v>
+                </c:pt>
+                <c:pt idx="681">
+                  <c:v>81.849999999999994</c:v>
+                </c:pt>
+                <c:pt idx="682">
+                  <c:v>95.75</c:v>
+                </c:pt>
+                <c:pt idx="683">
+                  <c:v>91.41</c:v>
+                </c:pt>
+                <c:pt idx="684">
+                  <c:v>56.59</c:v>
+                </c:pt>
+                <c:pt idx="685">
+                  <c:v>58.08</c:v>
+                </c:pt>
+                <c:pt idx="686">
+                  <c:v>70.180000000000007</c:v>
+                </c:pt>
+                <c:pt idx="687">
+                  <c:v>59.99</c:v>
+                </c:pt>
+                <c:pt idx="688">
+                  <c:v>56.15</c:v>
+                </c:pt>
+                <c:pt idx="689">
+                  <c:v>75.760000000000005</c:v>
+                </c:pt>
+                <c:pt idx="690">
+                  <c:v>77.09</c:v>
+                </c:pt>
+                <c:pt idx="691">
+                  <c:v>64.849999999999994</c:v>
+                </c:pt>
+                <c:pt idx="692">
+                  <c:v>57.39</c:v>
+                </c:pt>
+                <c:pt idx="693">
+                  <c:v>57.32</c:v>
+                </c:pt>
+                <c:pt idx="694">
+                  <c:v>57.08</c:v>
+                </c:pt>
+                <c:pt idx="695">
+                  <c:v>65.67</c:v>
+                </c:pt>
+                <c:pt idx="696">
+                  <c:v>88.94</c:v>
+                </c:pt>
+                <c:pt idx="697">
+                  <c:v>92.26</c:v>
+                </c:pt>
+                <c:pt idx="698">
+                  <c:v>72.25</c:v>
+                </c:pt>
+                <c:pt idx="699">
+                  <c:v>78.23</c:v>
+                </c:pt>
+                <c:pt idx="700">
+                  <c:v>76.66</c:v>
+                </c:pt>
+                <c:pt idx="701">
+                  <c:v>77.8</c:v>
+                </c:pt>
+                <c:pt idx="702">
+                  <c:v>78.709999999999994</c:v>
+                </c:pt>
+                <c:pt idx="703">
+                  <c:v>98.9</c:v>
+                </c:pt>
+                <c:pt idx="704">
+                  <c:v>97.44</c:v>
+                </c:pt>
+                <c:pt idx="705">
+                  <c:v>86.99</c:v>
+                </c:pt>
+                <c:pt idx="706">
+                  <c:v>94.16</c:v>
+                </c:pt>
+                <c:pt idx="707">
+                  <c:v>89.47</c:v>
+                </c:pt>
+                <c:pt idx="708">
+                  <c:v>93.75</c:v>
+                </c:pt>
+                <c:pt idx="709">
+                  <c:v>77.069999999999993</c:v>
+                </c:pt>
+                <c:pt idx="710">
+                  <c:v>62.49</c:v>
+                </c:pt>
+                <c:pt idx="711">
+                  <c:v>86.08</c:v>
+                </c:pt>
+                <c:pt idx="712">
+                  <c:v>87.91</c:v>
+                </c:pt>
+                <c:pt idx="713">
+                  <c:v>65.03</c:v>
+                </c:pt>
+                <c:pt idx="714">
+                  <c:v>29.03</c:v>
+                </c:pt>
+                <c:pt idx="715">
+                  <c:v>16.59</c:v>
+                </c:pt>
+                <c:pt idx="716">
+                  <c:v>10.65</c:v>
+                </c:pt>
+                <c:pt idx="717">
+                  <c:v>25.87</c:v>
+                </c:pt>
+                <c:pt idx="718">
+                  <c:v>23.67</c:v>
+                </c:pt>
+                <c:pt idx="719">
+                  <c:v>26.74</c:v>
+                </c:pt>
+                <c:pt idx="720">
+                  <c:v>28.71</c:v>
+                </c:pt>
+                <c:pt idx="721">
+                  <c:v>45.34</c:v>
+                </c:pt>
+                <c:pt idx="722">
+                  <c:v>78.55</c:v>
+                </c:pt>
+                <c:pt idx="723">
+                  <c:v>67.95</c:v>
+                </c:pt>
+                <c:pt idx="724">
+                  <c:v>57.71</c:v>
+                </c:pt>
+                <c:pt idx="725">
+                  <c:v>63.22</c:v>
+                </c:pt>
+                <c:pt idx="726">
+                  <c:v>81.650000000000006</c:v>
+                </c:pt>
+                <c:pt idx="727">
+                  <c:v>91.6</c:v>
+                </c:pt>
+                <c:pt idx="728">
+                  <c:v>77.48</c:v>
+                </c:pt>
+                <c:pt idx="729">
+                  <c:v>88.25</c:v>
+                </c:pt>
+                <c:pt idx="730">
+                  <c:v>76.569999999999993</c:v>
+                </c:pt>
+                <c:pt idx="731">
+                  <c:v>71.47</c:v>
+                </c:pt>
+                <c:pt idx="732">
+                  <c:v>85.09</c:v>
+                </c:pt>
+                <c:pt idx="733">
+                  <c:v>90.53</c:v>
+                </c:pt>
+                <c:pt idx="734">
+                  <c:v>97.88</c:v>
+                </c:pt>
+                <c:pt idx="735">
+                  <c:v>97.44</c:v>
+                </c:pt>
+                <c:pt idx="736">
+                  <c:v>94.55</c:v>
+                </c:pt>
+                <c:pt idx="737">
+                  <c:v>101.2</c:v>
+                </c:pt>
+                <c:pt idx="738">
+                  <c:v>100.13</c:v>
+                </c:pt>
+                <c:pt idx="739">
+                  <c:v>106.56</c:v>
+                </c:pt>
+                <c:pt idx="740">
+                  <c:v>94.71</c:v>
+                </c:pt>
+                <c:pt idx="741">
+                  <c:v>53.09</c:v>
+                </c:pt>
+                <c:pt idx="742">
+                  <c:v>59.3</c:v>
+                </c:pt>
+                <c:pt idx="743">
+                  <c:v>55.3</c:v>
+                </c:pt>
+                <c:pt idx="744">
+                  <c:v>58.25</c:v>
+                </c:pt>
+                <c:pt idx="745">
+                  <c:v>73.05</c:v>
+                </c:pt>
+                <c:pt idx="746">
+                  <c:v>102.93</c:v>
+                </c:pt>
+                <c:pt idx="747">
+                  <c:v>87.07</c:v>
+                </c:pt>
+                <c:pt idx="748">
+                  <c:v>77.87</c:v>
+                </c:pt>
+                <c:pt idx="749">
+                  <c:v>69.2</c:v>
+                </c:pt>
+                <c:pt idx="750">
+                  <c:v>96.3</c:v>
+                </c:pt>
+                <c:pt idx="751">
+                  <c:v>106.41</c:v>
+                </c:pt>
+                <c:pt idx="752">
+                  <c:v>106.74</c:v>
+                </c:pt>
+                <c:pt idx="753">
+                  <c:v>103.17</c:v>
+                </c:pt>
+                <c:pt idx="754">
+                  <c:v>106.11</c:v>
+                </c:pt>
+                <c:pt idx="755">
+                  <c:v>101.47</c:v>
+                </c:pt>
+                <c:pt idx="756">
+                  <c:v>89.11</c:v>
+                </c:pt>
+                <c:pt idx="757">
+                  <c:v>82.97</c:v>
+                </c:pt>
+                <c:pt idx="758">
+                  <c:v>94.51</c:v>
+                </c:pt>
+                <c:pt idx="759">
+                  <c:v>106.76</c:v>
+                </c:pt>
+                <c:pt idx="760">
+                  <c:v>112.93</c:v>
+                </c:pt>
+                <c:pt idx="761">
+                  <c:v>83.51</c:v>
+                </c:pt>
+                <c:pt idx="762">
+                  <c:v>79.150000000000006</c:v>
+                </c:pt>
+                <c:pt idx="763">
+                  <c:v>110.28</c:v>
+                </c:pt>
+                <c:pt idx="764">
+                  <c:v>108.32</c:v>
+                </c:pt>
+                <c:pt idx="765">
+                  <c:v>84.99</c:v>
+                </c:pt>
+                <c:pt idx="766">
+                  <c:v>65.37</c:v>
+                </c:pt>
+                <c:pt idx="767">
+                  <c:v>48.62</c:v>
+                </c:pt>
+                <c:pt idx="768">
+                  <c:v>78.55</c:v>
+                </c:pt>
+                <c:pt idx="769">
+                  <c:v>57.52</c:v>
+                </c:pt>
+                <c:pt idx="770">
+                  <c:v>52.02</c:v>
+                </c:pt>
+                <c:pt idx="771">
+                  <c:v>89.85</c:v>
+                </c:pt>
+                <c:pt idx="772">
+                  <c:v>96.57</c:v>
+                </c:pt>
+                <c:pt idx="773">
+                  <c:v>95.6</c:v>
+                </c:pt>
+                <c:pt idx="774">
+                  <c:v>103.72</c:v>
+                </c:pt>
+                <c:pt idx="775">
+                  <c:v>87.79</c:v>
+                </c:pt>
+                <c:pt idx="776">
+                  <c:v>46.86</c:v>
+                </c:pt>
+                <c:pt idx="777">
+                  <c:v>44.21</c:v>
+                </c:pt>
+                <c:pt idx="778">
+                  <c:v>68.3</c:v>
+                </c:pt>
+                <c:pt idx="779">
+                  <c:v>82.27</c:v>
+                </c:pt>
+                <c:pt idx="780">
+                  <c:v>79.650000000000006</c:v>
+                </c:pt>
+                <c:pt idx="781">
+                  <c:v>98.52</c:v>
+                </c:pt>
+                <c:pt idx="782">
+                  <c:v>70.86</c:v>
+                </c:pt>
+                <c:pt idx="783">
+                  <c:v>91.72</c:v>
+                </c:pt>
+                <c:pt idx="784">
+                  <c:v>82.54</c:v>
+                </c:pt>
+                <c:pt idx="785">
+                  <c:v>93.27</c:v>
+                </c:pt>
+                <c:pt idx="786">
+                  <c:v>71.040000000000006</c:v>
+                </c:pt>
+                <c:pt idx="787">
+                  <c:v>78.39</c:v>
+                </c:pt>
+                <c:pt idx="788">
+                  <c:v>97.72</c:v>
+                </c:pt>
+                <c:pt idx="789">
+                  <c:v>97.55</c:v>
+                </c:pt>
+                <c:pt idx="790">
+                  <c:v>70.569999999999993</c:v>
+                </c:pt>
+                <c:pt idx="791">
+                  <c:v>92.83</c:v>
+                </c:pt>
+                <c:pt idx="792">
+                  <c:v>93.95</c:v>
+                </c:pt>
+                <c:pt idx="793">
+                  <c:v>84.68</c:v>
+                </c:pt>
+                <c:pt idx="794">
+                  <c:v>87.02</c:v>
+                </c:pt>
+                <c:pt idx="795">
+                  <c:v>77.7</c:v>
+                </c:pt>
+                <c:pt idx="796">
+                  <c:v>55.02</c:v>
+                </c:pt>
+                <c:pt idx="797">
+                  <c:v>68.599999999999994</c:v>
+                </c:pt>
+                <c:pt idx="798">
+                  <c:v>64.459999999999994</c:v>
+                </c:pt>
+                <c:pt idx="799">
+                  <c:v>98.02</c:v>
+                </c:pt>
+                <c:pt idx="800">
+                  <c:v>103.35</c:v>
+                </c:pt>
+                <c:pt idx="801">
+                  <c:v>107.99</c:v>
+                </c:pt>
+                <c:pt idx="802">
+                  <c:v>103.69</c:v>
+                </c:pt>
+                <c:pt idx="803">
+                  <c:v>102.54</c:v>
+                </c:pt>
+                <c:pt idx="804">
+                  <c:v>103.14</c:v>
+                </c:pt>
+                <c:pt idx="805">
+                  <c:v>87.87</c:v>
+                </c:pt>
+                <c:pt idx="806">
+                  <c:v>69.459999999999994</c:v>
+                </c:pt>
+                <c:pt idx="807">
+                  <c:v>52.22</c:v>
+                </c:pt>
+                <c:pt idx="808">
+                  <c:v>67.02</c:v>
+                </c:pt>
+                <c:pt idx="809">
+                  <c:v>85.71</c:v>
+                </c:pt>
+                <c:pt idx="810">
+                  <c:v>89.54</c:v>
+                </c:pt>
+                <c:pt idx="811">
+                  <c:v>74.78</c:v>
+                </c:pt>
+                <c:pt idx="812">
+                  <c:v>56.73</c:v>
+                </c:pt>
+                <c:pt idx="813">
+                  <c:v>53.39</c:v>
+                </c:pt>
+                <c:pt idx="814">
+                  <c:v>62.54</c:v>
+                </c:pt>
+                <c:pt idx="815">
+                  <c:v>66.8</c:v>
+                </c:pt>
+                <c:pt idx="816">
+                  <c:v>53.49</c:v>
+                </c:pt>
+                <c:pt idx="817">
+                  <c:v>44.41</c:v>
+                </c:pt>
+                <c:pt idx="818">
+                  <c:v>30.3</c:v>
+                </c:pt>
+                <c:pt idx="819">
+                  <c:v>42.58</c:v>
+                </c:pt>
+                <c:pt idx="820">
+                  <c:v>46.68</c:v>
+                </c:pt>
+                <c:pt idx="821">
+                  <c:v>52.69</c:v>
+                </c:pt>
+                <c:pt idx="822">
+                  <c:v>79.72</c:v>
+                </c:pt>
+                <c:pt idx="823">
+                  <c:v>83.41</c:v>
+                </c:pt>
+                <c:pt idx="824">
+                  <c:v>63.29</c:v>
+                </c:pt>
+                <c:pt idx="825">
+                  <c:v>74.05</c:v>
+                </c:pt>
+                <c:pt idx="826">
+                  <c:v>46.25</c:v>
+                </c:pt>
+                <c:pt idx="827">
+                  <c:v>31.76</c:v>
+                </c:pt>
+                <c:pt idx="828">
+                  <c:v>24.31</c:v>
+                </c:pt>
+                <c:pt idx="829">
+                  <c:v>19.510000000000002</c:v>
+                </c:pt>
+                <c:pt idx="830">
+                  <c:v>33.19</c:v>
+                </c:pt>
+                <c:pt idx="831">
+                  <c:v>34.33</c:v>
+                </c:pt>
+                <c:pt idx="832">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="833">
+                  <c:v>32.18</c:v>
+                </c:pt>
+                <c:pt idx="834">
+                  <c:v>19.86</c:v>
+                </c:pt>
+                <c:pt idx="835">
+                  <c:v>30.66</c:v>
+                </c:pt>
+                <c:pt idx="836">
+                  <c:v>27.85</c:v>
+                </c:pt>
+                <c:pt idx="837">
+                  <c:v>26.74</c:v>
+                </c:pt>
+                <c:pt idx="838">
+                  <c:v>44.48</c:v>
+                </c:pt>
+                <c:pt idx="839">
+                  <c:v>47.21</c:v>
+                </c:pt>
+                <c:pt idx="840">
+                  <c:v>55.28</c:v>
+                </c:pt>
+                <c:pt idx="841">
+                  <c:v>71.59</c:v>
+                </c:pt>
+                <c:pt idx="842">
+                  <c:v>64.44</c:v>
+                </c:pt>
+                <c:pt idx="843">
+                  <c:v>54.86</c:v>
+                </c:pt>
+                <c:pt idx="844">
+                  <c:v>32.36</c:v>
+                </c:pt>
+                <c:pt idx="845">
+                  <c:v>27.33</c:v>
+                </c:pt>
+                <c:pt idx="846">
+                  <c:v>33.86</c:v>
+                </c:pt>
+                <c:pt idx="847">
+                  <c:v>29.59</c:v>
+                </c:pt>
+                <c:pt idx="848">
+                  <c:v>12.61</c:v>
+                </c:pt>
+                <c:pt idx="849">
+                  <c:v>38.11</c:v>
+                </c:pt>
+                <c:pt idx="850">
+                  <c:v>19.84</c:v>
+                </c:pt>
+                <c:pt idx="851">
+                  <c:v>43.28</c:v>
+                </c:pt>
+                <c:pt idx="852">
+                  <c:v>53.91</c:v>
+                </c:pt>
+                <c:pt idx="853">
+                  <c:v>55.22</c:v>
+                </c:pt>
+                <c:pt idx="854">
+                  <c:v>53.33</c:v>
+                </c:pt>
+                <c:pt idx="855">
+                  <c:v>64.959999999999994</c:v>
+                </c:pt>
+                <c:pt idx="856">
+                  <c:v>60.29</c:v>
+                </c:pt>
+                <c:pt idx="857">
+                  <c:v>64.36</c:v>
+                </c:pt>
+                <c:pt idx="858">
+                  <c:v>55.69</c:v>
+                </c:pt>
+                <c:pt idx="859">
+                  <c:v>71.599999999999994</c:v>
+                </c:pt>
+                <c:pt idx="860">
+                  <c:v>39.35</c:v>
+                </c:pt>
+                <c:pt idx="861">
+                  <c:v>43.48</c:v>
+                </c:pt>
+                <c:pt idx="862">
+                  <c:v>38.79</c:v>
+                </c:pt>
+                <c:pt idx="863">
+                  <c:v>45.31</c:v>
+                </c:pt>
+                <c:pt idx="864">
+                  <c:v>65.069999999999993</c:v>
+                </c:pt>
+                <c:pt idx="865">
+                  <c:v>75.23</c:v>
+                </c:pt>
+                <c:pt idx="866">
+                  <c:v>78.37</c:v>
+                </c:pt>
+                <c:pt idx="867">
+                  <c:v>85.4</c:v>
+                </c:pt>
+                <c:pt idx="868">
+                  <c:v>81.430000000000007</c:v>
+                </c:pt>
+                <c:pt idx="869">
+                  <c:v>57.09</c:v>
+                </c:pt>
+                <c:pt idx="870">
+                  <c:v>47.41</c:v>
+                </c:pt>
+                <c:pt idx="871">
+                  <c:v>60.11</c:v>
+                </c:pt>
+                <c:pt idx="872">
+                  <c:v>41.92</c:v>
+                </c:pt>
+                <c:pt idx="873">
+                  <c:v>53.21</c:v>
+                </c:pt>
+                <c:pt idx="874">
+                  <c:v>65.150000000000006</c:v>
+                </c:pt>
+                <c:pt idx="875">
+                  <c:v>72.89</c:v>
+                </c:pt>
+                <c:pt idx="876">
+                  <c:v>58.71</c:v>
+                </c:pt>
+                <c:pt idx="877">
+                  <c:v>78.260000000000005</c:v>
+                </c:pt>
+                <c:pt idx="878">
+                  <c:v>50.81</c:v>
+                </c:pt>
+                <c:pt idx="879">
+                  <c:v>67.010000000000005</c:v>
+                </c:pt>
+                <c:pt idx="880">
+                  <c:v>65.22</c:v>
+                </c:pt>
+                <c:pt idx="881">
+                  <c:v>59</c:v>
+                </c:pt>
+                <c:pt idx="882">
+                  <c:v>65.510000000000005</c:v>
+                </c:pt>
+                <c:pt idx="883">
+                  <c:v>53.92</c:v>
+                </c:pt>
+                <c:pt idx="884">
+                  <c:v>90.07</c:v>
+                </c:pt>
+                <c:pt idx="885">
+                  <c:v>81.66</c:v>
+                </c:pt>
+                <c:pt idx="886">
+                  <c:v>83.6</c:v>
+                </c:pt>
+                <c:pt idx="887">
+                  <c:v>75.930000000000007</c:v>
+                </c:pt>
+                <c:pt idx="888">
+                  <c:v>83.11</c:v>
+                </c:pt>
+                <c:pt idx="889">
+                  <c:v>93.34</c:v>
+                </c:pt>
+                <c:pt idx="890">
+                  <c:v>99.05</c:v>
+                </c:pt>
+                <c:pt idx="891">
+                  <c:v>101.82</c:v>
+                </c:pt>
+                <c:pt idx="892">
+                  <c:v>78.459999999999994</c:v>
+                </c:pt>
+                <c:pt idx="893">
+                  <c:v>65.489999999999995</c:v>
+                </c:pt>
+                <c:pt idx="894">
+                  <c:v>59.87</c:v>
+                </c:pt>
+                <c:pt idx="895">
+                  <c:v>34.36</c:v>
+                </c:pt>
+                <c:pt idx="896">
+                  <c:v>61.19</c:v>
+                </c:pt>
+                <c:pt idx="897">
+                  <c:v>49.73</c:v>
+                </c:pt>
+                <c:pt idx="898">
+                  <c:v>57.98</c:v>
+                </c:pt>
+                <c:pt idx="899">
+                  <c:v>54.33</c:v>
+                </c:pt>
+                <c:pt idx="900">
+                  <c:v>43.01</c:v>
+                </c:pt>
+                <c:pt idx="901">
+                  <c:v>36.21</c:v>
+                </c:pt>
+                <c:pt idx="902">
+                  <c:v>45.8</c:v>
+                </c:pt>
+                <c:pt idx="903">
+                  <c:v>66.67</c:v>
+                </c:pt>
+                <c:pt idx="904">
+                  <c:v>24.82</c:v>
+                </c:pt>
+                <c:pt idx="905">
+                  <c:v>29.17</c:v>
+                </c:pt>
+                <c:pt idx="906">
+                  <c:v>61.76</c:v>
+                </c:pt>
+                <c:pt idx="907">
+                  <c:v>72.06</c:v>
+                </c:pt>
+                <c:pt idx="908">
+                  <c:v>77.95</c:v>
+                </c:pt>
+                <c:pt idx="909">
+                  <c:v>81.38</c:v>
+                </c:pt>
+                <c:pt idx="910">
+                  <c:v>76.09</c:v>
+                </c:pt>
+                <c:pt idx="911">
+                  <c:v>77.97</c:v>
+                </c:pt>
+                <c:pt idx="912">
+                  <c:v>97.32</c:v>
+                </c:pt>
+                <c:pt idx="913">
+                  <c:v>102.71</c:v>
+                </c:pt>
+                <c:pt idx="914">
+                  <c:v>70.95</c:v>
+                </c:pt>
+                <c:pt idx="915">
+                  <c:v>80.180000000000007</c:v>
+                </c:pt>
+                <c:pt idx="916">
+                  <c:v>53.54</c:v>
+                </c:pt>
+                <c:pt idx="917">
+                  <c:v>84.13</c:v>
+                </c:pt>
+                <c:pt idx="918">
+                  <c:v>87.36</c:v>
+                </c:pt>
+                <c:pt idx="919">
+                  <c:v>93.77</c:v>
+                </c:pt>
+                <c:pt idx="920">
+                  <c:v>95.58</c:v>
+                </c:pt>
+                <c:pt idx="921">
+                  <c:v>74.7</c:v>
+                </c:pt>
+                <c:pt idx="922">
+                  <c:v>88.99</c:v>
+                </c:pt>
+                <c:pt idx="923">
+                  <c:v>93.99</c:v>
+                </c:pt>
+                <c:pt idx="924">
+                  <c:v>104.75</c:v>
+                </c:pt>
+                <c:pt idx="925">
+                  <c:v>93.22</c:v>
+                </c:pt>
+                <c:pt idx="926">
+                  <c:v>103.88</c:v>
+                </c:pt>
+                <c:pt idx="927">
+                  <c:v>84.24</c:v>
+                </c:pt>
+                <c:pt idx="928">
+                  <c:v>81.92</c:v>
+                </c:pt>
+                <c:pt idx="929">
+                  <c:v>62.98</c:v>
+                </c:pt>
+                <c:pt idx="930">
+                  <c:v>59.48</c:v>
+                </c:pt>
+                <c:pt idx="931">
+                  <c:v>61.97</c:v>
+                </c:pt>
+                <c:pt idx="932">
+                  <c:v>91.55</c:v>
+                </c:pt>
+                <c:pt idx="933">
+                  <c:v>89.25</c:v>
+                </c:pt>
+                <c:pt idx="934">
+                  <c:v>94.45</c:v>
+                </c:pt>
+                <c:pt idx="935">
+                  <c:v>92.21</c:v>
+                </c:pt>
+                <c:pt idx="936">
+                  <c:v>68.650000000000006</c:v>
+                </c:pt>
+                <c:pt idx="937">
+                  <c:v>86.3</c:v>
+                </c:pt>
+                <c:pt idx="938">
+                  <c:v>85.26</c:v>
+                </c:pt>
+                <c:pt idx="939">
+                  <c:v>85.44</c:v>
+                </c:pt>
+                <c:pt idx="940">
+                  <c:v>103.66</c:v>
+                </c:pt>
+                <c:pt idx="941">
+                  <c:v>93.84</c:v>
+                </c:pt>
+                <c:pt idx="942">
+                  <c:v>87.94</c:v>
+                </c:pt>
+                <c:pt idx="943">
+                  <c:v>76.7</c:v>
+                </c:pt>
+                <c:pt idx="944">
+                  <c:v>83.93</c:v>
+                </c:pt>
+                <c:pt idx="945">
+                  <c:v>75.33</c:v>
+                </c:pt>
+                <c:pt idx="946">
+                  <c:v>56.57</c:v>
+                </c:pt>
+                <c:pt idx="947">
+                  <c:v>74.680000000000007</c:v>
+                </c:pt>
+                <c:pt idx="948">
+                  <c:v>81.34</c:v>
+                </c:pt>
+                <c:pt idx="949">
+                  <c:v>70.650000000000006</c:v>
+                </c:pt>
+                <c:pt idx="950">
+                  <c:v>71.930000000000007</c:v>
+                </c:pt>
+                <c:pt idx="951">
+                  <c:v>87.46</c:v>
+                </c:pt>
+                <c:pt idx="952">
+                  <c:v>86.64</c:v>
+                </c:pt>
+                <c:pt idx="953">
+                  <c:v>86.93</c:v>
+                </c:pt>
+                <c:pt idx="954">
+                  <c:v>90.26</c:v>
+                </c:pt>
+                <c:pt idx="955">
+                  <c:v>81.680000000000007</c:v>
+                </c:pt>
+                <c:pt idx="956">
+                  <c:v>79.13</c:v>
+                </c:pt>
+                <c:pt idx="957">
+                  <c:v>82.53</c:v>
+                </c:pt>
+                <c:pt idx="958">
+                  <c:v>88.31</c:v>
+                </c:pt>
+                <c:pt idx="959">
+                  <c:v>91.6</c:v>
+                </c:pt>
+                <c:pt idx="960">
+                  <c:v>91.33</c:v>
+                </c:pt>
+                <c:pt idx="961">
+                  <c:v>98.93</c:v>
+                </c:pt>
+                <c:pt idx="962">
+                  <c:v>85.49</c:v>
+                </c:pt>
+                <c:pt idx="963">
+                  <c:v>99.24</c:v>
+                </c:pt>
+                <c:pt idx="964">
+                  <c:v>82.5</c:v>
+                </c:pt>
+                <c:pt idx="965">
+                  <c:v>80.39</c:v>
+                </c:pt>
+                <c:pt idx="966">
+                  <c:v>64.099999999999994</c:v>
+                </c:pt>
+                <c:pt idx="967">
+                  <c:v>65.38</c:v>
+                </c:pt>
+                <c:pt idx="968">
+                  <c:v>70.209999999999994</c:v>
+                </c:pt>
+                <c:pt idx="969">
+                  <c:v>86.08</c:v>
+                </c:pt>
+                <c:pt idx="970">
+                  <c:v>68.28</c:v>
+                </c:pt>
+                <c:pt idx="971">
+                  <c:v>84.91</c:v>
+                </c:pt>
+                <c:pt idx="972">
+                  <c:v>75.62</c:v>
+                </c:pt>
+                <c:pt idx="973">
+                  <c:v>91.48</c:v>
+                </c:pt>
+                <c:pt idx="974">
+                  <c:v>87.87</c:v>
+                </c:pt>
+                <c:pt idx="975">
+                  <c:v>74.959999999999994</c:v>
+                </c:pt>
+                <c:pt idx="976">
+                  <c:v>68.8</c:v>
+                </c:pt>
+                <c:pt idx="977">
+                  <c:v>64.64</c:v>
+                </c:pt>
+                <c:pt idx="978">
+                  <c:v>57.55</c:v>
+                </c:pt>
+                <c:pt idx="979">
+                  <c:v>49.37</c:v>
+                </c:pt>
+                <c:pt idx="980">
+                  <c:v>56.96</c:v>
+                </c:pt>
+                <c:pt idx="981">
+                  <c:v>35.159999999999997</c:v>
+                </c:pt>
+                <c:pt idx="982">
+                  <c:v>40.67</c:v>
+                </c:pt>
+                <c:pt idx="983">
+                  <c:v>59.92</c:v>
+                </c:pt>
+                <c:pt idx="984">
+                  <c:v>81.06</c:v>
+                </c:pt>
+                <c:pt idx="985">
+                  <c:v>70.56</c:v>
+                </c:pt>
+                <c:pt idx="986">
+                  <c:v>80.87</c:v>
+                </c:pt>
+                <c:pt idx="987">
+                  <c:v>88.41</c:v>
+                </c:pt>
+                <c:pt idx="988">
+                  <c:v>81.62</c:v>
+                </c:pt>
+                <c:pt idx="989">
+                  <c:v>82.66</c:v>
+                </c:pt>
+                <c:pt idx="990">
+                  <c:v>94.09</c:v>
+                </c:pt>
+                <c:pt idx="991">
+                  <c:v>81.41</c:v>
+                </c:pt>
+                <c:pt idx="992">
+                  <c:v>99.3</c:v>
+                </c:pt>
+                <c:pt idx="993">
+                  <c:v>86.28</c:v>
+                </c:pt>
+                <c:pt idx="994">
+                  <c:v>83.69</c:v>
+                </c:pt>
+                <c:pt idx="995">
+                  <c:v>81.069999999999993</c:v>
+                </c:pt>
+                <c:pt idx="996">
+                  <c:v>76.849999999999994</c:v>
+                </c:pt>
+                <c:pt idx="997">
+                  <c:v>96.26</c:v>
+                </c:pt>
+                <c:pt idx="998">
+                  <c:v>85.66</c:v>
+                </c:pt>
+                <c:pt idx="999">
+                  <c:v>98.15</c:v>
+                </c:pt>
+                <c:pt idx="1000">
+                  <c:v>92.94</c:v>
+                </c:pt>
+                <c:pt idx="1001">
+                  <c:v>81.58</c:v>
+                </c:pt>
+                <c:pt idx="1002">
+                  <c:v>86.11</c:v>
+                </c:pt>
+                <c:pt idx="1003">
+                  <c:v>84.76</c:v>
+                </c:pt>
+                <c:pt idx="1004">
+                  <c:v>86.24</c:v>
+                </c:pt>
+                <c:pt idx="1005">
+                  <c:v>80.66</c:v>
+                </c:pt>
+                <c:pt idx="1006">
+                  <c:v>84.57</c:v>
+                </c:pt>
+                <c:pt idx="1007">
+                  <c:v>84.87</c:v>
+                </c:pt>
+                <c:pt idx="1008">
+                  <c:v>90.35</c:v>
+                </c:pt>
+                <c:pt idx="1009">
+                  <c:v>100.83</c:v>
+                </c:pt>
+                <c:pt idx="1010">
+                  <c:v>90.06</c:v>
+                </c:pt>
+                <c:pt idx="1011">
+                  <c:v>87.87</c:v>
+                </c:pt>
+                <c:pt idx="1012">
+                  <c:v>86.56</c:v>
+                </c:pt>
+                <c:pt idx="1013">
+                  <c:v>89.92</c:v>
+                </c:pt>
+                <c:pt idx="1014">
+                  <c:v>98.57</c:v>
+                </c:pt>
+                <c:pt idx="1015">
+                  <c:v>97.13</c:v>
+                </c:pt>
+                <c:pt idx="1016">
+                  <c:v>100.7</c:v>
+                </c:pt>
+                <c:pt idx="1017">
+                  <c:v>95.08</c:v>
+                </c:pt>
+                <c:pt idx="1018">
+                  <c:v>92.93</c:v>
+                </c:pt>
+                <c:pt idx="1019">
+                  <c:v>97.72</c:v>
+                </c:pt>
+                <c:pt idx="1020">
+                  <c:v>96.01</c:v>
+                </c:pt>
+                <c:pt idx="1021">
+                  <c:v>88.46</c:v>
+                </c:pt>
+                <c:pt idx="1022">
+                  <c:v>92.58</c:v>
+                </c:pt>
+                <c:pt idx="1023">
+                  <c:v>84.93</c:v>
+                </c:pt>
+                <c:pt idx="1024">
+                  <c:v>80.61</c:v>
+                </c:pt>
+                <c:pt idx="1025">
+                  <c:v>82.87</c:v>
+                </c:pt>
+                <c:pt idx="1026">
+                  <c:v>74.930000000000007</c:v>
+                </c:pt>
+                <c:pt idx="1027">
+                  <c:v>79.290000000000006</c:v>
+                </c:pt>
+                <c:pt idx="1028">
+                  <c:v>66.989999999999995</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-E1F1-44C0-9C39-3A0F885D4C68}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1641748639"/>
+        <c:axId val="1641975983"/>
+      </c:lineChart>
+      <c:dateAx>
+        <c:axId val="1641748639"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="46387"/>
+          <c:min val="43101"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="yyyy;@" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="low"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ko-KR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1641975983"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblOffset val="100"/>
+        <c:baseTimeUnit val="days"/>
+        <c:majorUnit val="1"/>
+        <c:majorTimeUnit val="years"/>
+      </c:dateAx>
+      <c:valAx>
+        <c:axId val="1641975983"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="120"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="#,##0_);[Red]\(#,##0\)" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ko-KR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1641748639"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ko-KR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:noFill/>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ko-KR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>685799</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>9524</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="차트 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{55FC02D4-5A33-4C65-8BBE-753CECD07046}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -993,7 +8032,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K1028"/>
+  <dimension ref="A1:K1030"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.75" style="15" bestFit="1" customWidth="1"/>
@@ -38287,6 +45326,93 @@
         <v>64.84</v>
       </c>
     </row>
+    <row r="1029" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A1029" s="15">
+        <v>46085</v>
+      </c>
+      <c r="B1029" s="15">
+        <v>46086</v>
+      </c>
+      <c r="C1029" s="17">
+        <v>0.41666666666666802</v>
+      </c>
+      <c r="D1029" s="15" t="str">
+        <f t="shared" si="16"/>
+        <v>UTC-4</v>
+      </c>
+      <c r="E1029" s="7">
+        <v>79.290000000000006</v>
+      </c>
+      <c r="F1029" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1029" s="7">
+        <v>45</v>
+      </c>
+      <c r="H1029" s="9">
+        <v>98</v>
+      </c>
+      <c r="I1029" s="9">
+        <v>100</v>
+      </c>
+      <c r="J1029" s="9">
+        <v>200</v>
+      </c>
+      <c r="K1029" s="7">
+        <v>49.98</v>
+      </c>
+    </row>
+    <row r="1030" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A1030" s="15">
+        <v>46092</v>
+      </c>
+      <c r="B1030" s="15">
+        <v>46093</v>
+      </c>
+      <c r="C1030" s="17">
+        <v>0.41666666666666802</v>
+      </c>
+      <c r="D1030" s="15" t="str">
+        <f t="shared" ref="D1030" si="17">IF(
+ AND(
+  B1031 &gt;= IF(
+         YEAR(B1031)&gt;=2007,
+         DATE(YEAR(B1031),3,14)-WEEKDAY(DATE(YEAR(B1031),3,14),1)+1 + TIME(2,0,0),
+         DATE(YEAR(B1031),4,7)-WEEKDAY(DATE(YEAR(B1031),4,7),1)+1 + TIME(2,0,0)
+       ),
+  B1031 &lt;  IF(
+         YEAR(B1031)&gt;=2007,
+         DATE(YEAR(B1031),11,7)-WEEKDAY(DATE(YEAR(B1031),11,7),1)+1 + TIME(2,0,0),
+         DATE(YEAR(B1031),10,31)-WEEKDAY(DATE(YEAR(B1031),10,31),1) + TIME(2,0,0)
+       )
+ ),
+ "UTC-4",
+ "UTC-5"
+)</f>
+        <v>UTC-5</v>
+      </c>
+      <c r="E1030" s="7">
+        <v>66.989999999999995</v>
+      </c>
+      <c r="F1030" s="8">
+        <v>-200</v>
+      </c>
+      <c r="G1030" s="7">
+        <v>50</v>
+      </c>
+      <c r="H1030" s="9">
+        <v>88</v>
+      </c>
+      <c r="I1030" s="9">
+        <v>100</v>
+      </c>
+      <c r="J1030" s="9">
+        <v>200</v>
+      </c>
+      <c r="K1030" s="7">
+        <v>62.78</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -38295,6 +45421,17 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{115169E1-C49D-409D-8D5D-92B2FD26EE0D}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44703C2A-D4C6-BD4F-B5E9-874C8C9CFE9E}">
   <dimension ref="B2:C3"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>

--- a/data/sentiment/NAAIM Exposure Index.xlsx
+++ b/data/sentiment/NAAIM Exposure Index.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\sentiment\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\sentiment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B70FB63F-A4C6-4F01-92C2-DFC1D75258E7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6346AA13-45CF-4995-9D67-C6DFC433D96A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16155" yWindow="780" windowWidth="19845" windowHeight="20700" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NAAIM" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,19 @@
     <sheet name="info" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -79,31 +92,31 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="178" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="179" formatCode="0.00_ "/>
-    <numFmt numFmtId="180" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="0.00_ "/>
+    <numFmt numFmtId="167" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="18"/>
       <color theme="3"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri Light"/>
       <family val="2"/>
       <scheme val="major"/>
     </font>
@@ -111,7 +124,7 @@
       <b/>
       <sz val="15"/>
       <color theme="3"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -119,7 +132,7 @@
       <b/>
       <sz val="13"/>
       <color theme="3"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -127,35 +140,35 @@
       <b/>
       <sz val="11"/>
       <color theme="3"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C5700"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -163,7 +176,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -171,14 +184,14 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -186,14 +199,14 @@
       <b/>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -201,7 +214,7 @@
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -209,20 +222,20 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -231,7 +244,7 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -589,7 +602,7 @@
     <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -597,92 +610,92 @@
   <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="43"/>
-    <xf numFmtId="177" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="20" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" xfId="42" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="179" fontId="20" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="20" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="178" fontId="20" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="20" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="176" fontId="21" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="21" fillId="0" borderId="0" xfId="42" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="179" fontId="21" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="21" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="178" fontId="21" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="21" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="176" fontId="21" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="21" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="21" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="21" fillId="0" borderId="0" xfId="42" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="21" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="21" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="180" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="180" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="44">
-    <cellStyle name="20% - 강조색1" xfId="19" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20% - 강조색2" xfId="23" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20% - 강조색3" xfId="27" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20% - 강조색4" xfId="31" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20% - 강조색5" xfId="35" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20% - 강조색6" xfId="39" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="40% - 강조색1" xfId="20" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40% - 강조색2" xfId="24" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40% - 강조색3" xfId="28" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40% - 강조색4" xfId="32" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40% - 강조색5" xfId="36" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40% - 강조색6" xfId="40" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="60% - 강조색1" xfId="21" builtinId="32" customBuiltin="1"/>
-    <cellStyle name="60% - 강조색2" xfId="25" builtinId="36" customBuiltin="1"/>
-    <cellStyle name="60% - 강조색3" xfId="29" builtinId="40" customBuiltin="1"/>
-    <cellStyle name="60% - 강조색4" xfId="33" builtinId="44" customBuiltin="1"/>
-    <cellStyle name="60% - 강조색5" xfId="37" builtinId="48" customBuiltin="1"/>
-    <cellStyle name="60% - 강조색6" xfId="41" builtinId="52" customBuiltin="1"/>
-    <cellStyle name="강조색1" xfId="18" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="강조색2" xfId="22" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="강조색3" xfId="26" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="강조색4" xfId="30" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="강조색5" xfId="34" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="강조색6" xfId="38" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="경고문" xfId="14" builtinId="11" customBuiltin="1"/>
-    <cellStyle name="계산" xfId="11" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="나쁨" xfId="7" builtinId="27" customBuiltin="1"/>
-    <cellStyle name="메모" xfId="15" builtinId="10" customBuiltin="1"/>
-    <cellStyle name="보통" xfId="8" builtinId="28" customBuiltin="1"/>
-    <cellStyle name="설명 텍스트" xfId="16" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="셀 확인" xfId="13" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="쉼표" xfId="42" builtinId="3"/>
-    <cellStyle name="연결된 셀" xfId="12" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="요약" xfId="17" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="입력" xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="제목" xfId="1" builtinId="15" customBuiltin="1"/>
-    <cellStyle name="제목 1" xfId="2" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="제목 2" xfId="3" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="제목 3" xfId="4" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="제목 4" xfId="5" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="좋음" xfId="6" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="출력" xfId="10" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="하이퍼링크" xfId="43" builtinId="8"/>
+    <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - Accent4" xfId="31" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - Accent5" xfId="35" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - Accent6" xfId="39" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - Accent1" xfId="20" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - Accent2" xfId="24" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - Accent3" xfId="28" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - Accent4" xfId="32" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - Accent5" xfId="36" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - Accent6" xfId="40" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - Accent1" xfId="21" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - Accent2" xfId="25" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - Accent3" xfId="29" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - Accent4" xfId="33" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - Accent5" xfId="37" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - Accent6" xfId="41" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="Accent1" xfId="18" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="Accent2" xfId="22" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="Accent3" xfId="26" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Comma" xfId="42" builtinId="3"/>
+    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Hyperlink" xfId="43" builtinId="8"/>
+    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -700,7 +713,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -737,10 +750,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>NAAIM!$B$2:$B$1030</c:f>
+              <c:f>NAAIM!$B$2:$B$11030</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
-                <c:ptCount val="1029"/>
+                <c:ptCount val="11029"/>
                 <c:pt idx="0">
                   <c:v>38904</c:v>
                 </c:pt>
@@ -3827,16 +3840,22 @@
                 </c:pt>
                 <c:pt idx="1028">
                   <c:v>46093</c:v>
+                </c:pt>
+                <c:pt idx="1029">
+                  <c:v>46100</c:v>
+                </c:pt>
+                <c:pt idx="1030">
+                  <c:v>46107</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>NAAIM!$E$2:$E$1030</c:f>
+              <c:f>NAAIM!$E$2:$E$11030</c:f>
               <c:numCache>
                 <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
-                <c:ptCount val="1029"/>
+                <c:ptCount val="11029"/>
                 <c:pt idx="0">
                   <c:v>19.440000000000001</c:v>
                 </c:pt>
@@ -6923,6 +6942,12 @@
                 </c:pt>
                 <c:pt idx="1028">
                   <c:v>66.989999999999995</c:v>
+                </c:pt>
+                <c:pt idx="1029">
+                  <c:v>60.24</c:v>
+                </c:pt>
+                <c:pt idx="1030">
+                  <c:v>68.52</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7099,6 +7124,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -7106,7 +7132,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -7139,7 +7164,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -7184,10 +7209,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>NAAIM!$B$2:$B$1031</c:f>
+              <c:f>NAAIM!$B$2:$B$11031</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
-                <c:ptCount val="1030"/>
+                <c:ptCount val="11030"/>
                 <c:pt idx="0">
                   <c:v>38904</c:v>
                 </c:pt>
@@ -10277,16 +10302,19 @@
                 </c:pt>
                 <c:pt idx="1029">
                   <c:v>46100</c:v>
+                </c:pt>
+                <c:pt idx="1030">
+                  <c:v>46107</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>NAAIM!$K$2:$K$1031</c:f>
+              <c:f>NAAIM!$K$2:$K$11031</c:f>
               <c:numCache>
                 <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
-                <c:ptCount val="1030"/>
+                <c:ptCount val="11030"/>
                 <c:pt idx="0">
                   <c:v>55.55</c:v>
                 </c:pt>
@@ -13376,6 +13404,9 @@
                 </c:pt>
                 <c:pt idx="1029">
                   <c:v>68.13</c:v>
+                </c:pt>
+                <c:pt idx="1030">
+                  <c:v>47.03</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13551,6 +13582,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -13558,7 +13590,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -14785,9 +14816,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -14825,7 +14856,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -14931,7 +14962,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -15073,7 +15104,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -15081,24 +15112,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K1031"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:K1032"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.75" style="15" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.7265625" style="15" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" style="15" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5" style="17" customWidth="1"/>
-    <col min="4" max="4" width="12.5" style="15" customWidth="1"/>
-    <col min="5" max="5" width="11.125" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.26953125" style="17" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.453125" style="15" customWidth="1"/>
+    <col min="5" max="5" width="11.08984375" style="7" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14" style="8" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.375" style="7" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.25" style="9" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.375" style="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.36328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.26953125" style="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.36328125" style="9" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="15" style="9" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="21.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="8.875" style="10"/>
+    <col min="11" max="11" width="21.7265625" style="7" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.90625" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" s="6" customFormat="1">
       <c r="A1" s="2" t="s">
         <v>10</v>
       </c>
@@ -15133,7 +15164,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11">
       <c r="A2" s="15">
         <v>38903</v>
       </c>
@@ -15184,7 +15215,7 @@
         <v>55.55</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11">
       <c r="A3" s="15">
         <v>38910</v>
       </c>
@@ -15235,7 +15266,7 @@
         <v>47.84</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11">
       <c r="A4" s="15">
         <v>38903</v>
       </c>
@@ -15271,7 +15302,7 @@
         <v>55.549999722194443</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11">
       <c r="A5" s="15">
         <v>38910</v>
       </c>
@@ -15307,7 +15338,7 @@
         <v>47.838896308338889</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11">
       <c r="A6" s="15">
         <v>38917</v>
       </c>
@@ -15343,7 +15374,7 @@
         <v>38.170438823780898</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11">
       <c r="A7" s="15">
         <v>38924</v>
       </c>
@@ -15379,7 +15410,7 @@
         <v>33.778460222455372</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11">
       <c r="A8" s="15">
         <v>38931</v>
       </c>
@@ -15415,7 +15446,7 @@
         <v>43.692625871599382</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11">
       <c r="A9" s="15">
         <v>38938</v>
       </c>
@@ -15451,7 +15482,7 @@
         <v>47.483927790753583</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11">
       <c r="A10" s="15">
         <v>38945</v>
       </c>
@@ -15487,7 +15518,7 @@
         <v>56.524684873071166</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11">
       <c r="A11" s="15">
         <v>38952</v>
       </c>
@@ -15523,7 +15554,7 @@
         <v>45.170475778833321</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11">
       <c r="A12" s="15">
         <v>38959</v>
       </c>
@@ -15559,7 +15590,7 @@
         <v>45.170475778833321</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11">
       <c r="A13" s="15">
         <v>38966</v>
       </c>
@@ -15595,7 +15626,7 @@
         <v>50.374290674884271</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11">
       <c r="A14" s="15">
         <v>38973</v>
       </c>
@@ -15631,7 +15662,7 @@
         <v>56.228640389040173</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11">
       <c r="A15" s="15">
         <v>38980</v>
       </c>
@@ -15667,7 +15698,7 @@
         <v>31.264996401726965</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11">
       <c r="A16" s="15">
         <v>38987</v>
       </c>
@@ -15703,7 +15734,7 @@
         <v>55.807410979021469</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:11">
       <c r="A17" s="15">
         <v>38994</v>
       </c>
@@ -15739,7 +15770,7 @@
         <v>59.404629449227272</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:11">
       <c r="A18" s="15">
         <v>39001</v>
       </c>
@@ -15775,7 +15806,7 @@
         <v>59.825434763385545</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:11">
       <c r="A19" s="15">
         <v>39008</v>
       </c>
@@ -15811,7 +15842,7 @@
         <v>33.215082952435786</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:11">
       <c r="A20" s="15">
         <v>39015</v>
       </c>
@@ -15847,7 +15878,7 @@
         <v>53.121506002748077</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:11">
       <c r="A21" s="15">
         <v>39022</v>
       </c>
@@ -15883,7 +15914,7 @@
         <v>53.864396997357062</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:11">
       <c r="A22" s="15">
         <v>39029</v>
       </c>
@@ -15919,7 +15950,7 @@
         <v>46.653652879834993</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:11">
       <c r="A23" s="15">
         <v>39036</v>
       </c>
@@ -15955,7 +15986,7 @@
         <v>61.297793607386772</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:11">
       <c r="A24" s="15">
         <v>39043</v>
       </c>
@@ -15991,7 +16022,7 @@
         <v>20.824828195876073</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:11">
       <c r="A25" s="15">
         <v>39050</v>
       </c>
@@ -16027,7 +16058,7 @@
         <v>38.414042173363363</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:11">
       <c r="A26" s="15">
         <v>39057</v>
       </c>
@@ -16063,7 +16094,7 @@
         <v>58.029540018794734</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:11">
       <c r="A27" s="15">
         <v>39064</v>
       </c>
@@ -16099,7 +16130,7 @@
         <v>19.415261547359616</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:11">
       <c r="A28" s="15">
         <v>39071</v>
       </c>
@@ -16135,7 +16166,7 @@
         <v>22.354395725773102</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:11">
       <c r="A29" s="15">
         <v>39078</v>
       </c>
@@ -16171,7 +16202,7 @@
         <v>35.213204259954928</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:11">
       <c r="A30" s="15">
         <v>39085</v>
       </c>
@@ -16207,7 +16238,7 @@
         <v>32.236442245024186</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:11">
       <c r="A31" s="15">
         <v>39092</v>
       </c>
@@ -16243,7 +16274,7 @@
         <v>65.212862654704111</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:11">
       <c r="A32" s="15">
         <v>39099</v>
       </c>
@@ -16279,7 +16310,7 @@
         <v>27.899999503569333</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:11">
       <c r="A33" s="15">
         <v>39106</v>
       </c>
@@ -16315,7 +16346,7 @@
         <v>42.723911860082509</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:11">
       <c r="A34" s="15">
         <v>39113</v>
       </c>
@@ -16351,7 +16382,7 @@
         <v>49.378006237595294</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:11">
       <c r="A35" s="15">
         <v>39120</v>
       </c>
@@ -16387,7 +16418,7 @@
         <v>45.927163507298019</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:11">
       <c r="A36" s="15">
         <v>39127</v>
       </c>
@@ -16423,7 +16454,7 @@
         <v>55.649805268718424</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:11">
       <c r="A37" s="15">
         <v>39134</v>
       </c>
@@ -16459,7 +16490,7 @@
         <v>52.764818137257436</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:11">
       <c r="A38" s="15">
         <v>39141</v>
       </c>
@@ -16495,7 +16526,7 @@
         <v>53.726231363347424</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:11">
       <c r="A39" s="15">
         <v>39148</v>
       </c>
@@ -16531,7 +16562,7 @@
         <v>48.602880573068916</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:11">
       <c r="A40" s="15">
         <v>39155</v>
       </c>
@@ -16567,7 +16598,7 @@
         <v>68.635171039352031</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:11">
       <c r="A41" s="15">
         <v>39162</v>
       </c>
@@ -16603,7 +16634,7 @@
         <v>54.906588487696794</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:11">
       <c r="A42" s="15">
         <v>39169</v>
       </c>
@@ -16639,7 +16670,7 @@
         <v>61.630606010506028</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:11">
       <c r="A43" s="15">
         <v>39176</v>
       </c>
@@ -16675,7 +16706,7 @@
         <v>64.537968733792852</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:11">
       <c r="A44" s="15">
         <v>39183</v>
       </c>
@@ -16711,7 +16742,7 @@
         <v>57.825060311252592</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:11">
       <c r="A45" s="15">
         <v>39190</v>
       </c>
@@ -16747,7 +16778,7 @@
         <v>69.279479346364909</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:11">
       <c r="A46" s="15">
         <v>39197</v>
       </c>
@@ -16783,7 +16814,7 @@
         <v>59.001416591157486</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:11">
       <c r="A47" s="15">
         <v>39204</v>
       </c>
@@ -16819,7 +16850,7 @@
         <v>59.063995424924954</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:11">
       <c r="A48" s="15">
         <v>39211</v>
       </c>
@@ -16855,7 +16886,7 @@
         <v>55.064860745205635</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:11">
       <c r="A49" s="15">
         <v>39218</v>
       </c>
@@ -16891,7 +16922,7 @@
         <v>51.819247148139851</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:11">
       <c r="A50" s="15">
         <v>39225</v>
       </c>
@@ -16927,7 +16958,7 @@
         <v>53.983793864455286</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:11">
       <c r="A51" s="15">
         <v>39232</v>
       </c>
@@ -16963,7 +16994,7 @@
         <v>48.786852991286374</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:11">
       <c r="A52" s="15">
         <v>39239</v>
       </c>
@@ -16999,7 +17030,7 @@
         <v>62.811083593759328</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:11">
       <c r="A53" s="15">
         <v>39246</v>
       </c>
@@ -17035,7 +17066,7 @@
         <v>65.542340513594723</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:11">
       <c r="A54" s="15">
         <v>39253</v>
       </c>
@@ -17071,7 +17102,7 @@
         <v>67.954431672633518</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:11">
       <c r="A55" s="15">
         <v>39260</v>
       </c>
@@ -17107,7 +17138,7 @@
         <v>55.826175891531534</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:11">
       <c r="A56" s="15">
         <v>39268</v>
       </c>
@@ -17143,7 +17174,7 @@
         <v>60.176790324426577</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:11">
       <c r="A57" s="15">
         <v>39274</v>
       </c>
@@ -17179,7 +17210,7 @@
         <v>51.354938031690303</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:11">
       <c r="A58" s="15">
         <v>39281</v>
       </c>
@@ -17215,7 +17246,7 @@
         <v>45.888802797874582</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:11">
       <c r="A59" s="15">
         <v>39288</v>
       </c>
@@ -17251,7 +17282,7 @@
         <v>63.76609180512709</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:11">
       <c r="A60" s="15">
         <v>39295</v>
       </c>
@@ -17287,7 +17318,7 @@
         <v>59.657354953098618</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:11">
       <c r="A61" s="15">
         <v>39302</v>
       </c>
@@ -17323,7 +17354,7 @@
         <v>65.099669293697346</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:11">
       <c r="A62" s="15">
         <v>39309</v>
       </c>
@@ -17359,7 +17390,7 @@
         <v>57.034529015325447</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:11">
       <c r="A63" s="15">
         <v>39316</v>
       </c>
@@ -17395,7 +17426,7 @@
         <v>52.701658833000693</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:11">
       <c r="A64" s="15">
         <v>39323</v>
       </c>
@@ -17431,7 +17462,7 @@
         <v>72.566359583555496</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:11">
       <c r="A65" s="15">
         <v>39330</v>
       </c>
@@ -17467,7 +17498,7 @@
         <v>45.022968675258781</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:11">
       <c r="A66" s="15">
         <v>39337</v>
       </c>
@@ -17503,7 +17534,7 @@
         <v>69.603104472428257</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:11">
       <c r="A67" s="15">
         <v>39344</v>
       </c>
@@ -17554,7 +17585,7 @@
         <v>42.408304442812678</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:11">
       <c r="A68" s="15">
         <v>39351</v>
       </c>
@@ -17590,7 +17621,7 @@
         <v>38.186796212286225</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:11">
       <c r="A69" s="15">
         <v>39358</v>
       </c>
@@ -17626,7 +17657,7 @@
         <v>61.369548273391054</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:11">
       <c r="A70" s="15">
         <v>39365</v>
       </c>
@@ -17662,7 +17693,7 @@
         <v>56.227919122877815</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:11">
       <c r="A71" s="15">
         <v>39372</v>
       </c>
@@ -17698,7 +17729,7 @@
         <v>49.208363214031834</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:11">
       <c r="A72" s="15">
         <v>39379</v>
       </c>
@@ -17734,7 +17765,7 @@
         <v>65.850867379966061</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:11">
       <c r="A73" s="15">
         <v>39386</v>
       </c>
@@ -17770,7 +17801,7 @@
         <v>75.074716234904798</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:11">
       <c r="A74" s="15">
         <v>39393</v>
       </c>
@@ -17806,7 +17837,7 @@
         <v>52.534527153195896</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:11">
       <c r="A75" s="15">
         <v>39400</v>
       </c>
@@ -17842,7 +17873,7 @@
         <v>40.679745770792763</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:11">
       <c r="A76" s="15">
         <v>39407</v>
       </c>
@@ -17878,7 +17909,7 @@
         <v>60.493442596881707</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:11">
       <c r="A77" s="15">
         <v>39414</v>
       </c>
@@ -17914,7 +17945,7 @@
         <v>68.934714752142</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:11">
       <c r="A78" s="15">
         <v>39421</v>
       </c>
@@ -17950,7 +17981,7 @@
         <v>60.536316005812211</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:11">
       <c r="A79" s="15">
         <v>39428</v>
       </c>
@@ -17986,7 +18017,7 @@
         <v>69.021440028975547</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:11">
       <c r="A80" s="15">
         <v>39435</v>
       </c>
@@ -18022,7 +18053,7 @@
         <v>71.467344717337483</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:11">
       <c r="A81" s="15">
         <v>39442</v>
       </c>
@@ -18058,7 +18089,7 @@
         <v>50.496362770611753</v>
       </c>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:11">
       <c r="A82" s="15">
         <v>39449</v>
       </c>
@@ -18094,7 +18125,7 @@
         <v>55.229668567997003</v>
       </c>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:11">
       <c r="A83" s="15">
         <v>39456</v>
       </c>
@@ -18130,7 +18161,7 @@
         <v>75.139220764041383</v>
       </c>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:11">
       <c r="A84" s="15">
         <v>39463</v>
       </c>
@@ -18166,7 +18197,7 @@
         <v>58.387484404345059</v>
       </c>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:11">
       <c r="A85" s="15">
         <v>39470</v>
       </c>
@@ -18202,7 +18233,7 @@
         <v>74.040278246155765</v>
       </c>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:11">
       <c r="A86" s="15">
         <v>39477</v>
       </c>
@@ -18238,7 +18269,7 @@
         <v>62.164148383994373</v>
       </c>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:11">
       <c r="A87" s="15">
         <v>39484</v>
       </c>
@@ -18274,7 +18305,7 @@
         <v>70.447213919214661</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:11">
       <c r="A88" s="15">
         <v>39491</v>
       </c>
@@ -18310,7 +18341,7 @@
         <v>74.676338659280532</v>
       </c>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:11">
       <c r="A89" s="15">
         <v>39498</v>
       </c>
@@ -18346,7 +18377,7 @@
         <v>57.328488167363666</v>
       </c>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:11">
       <c r="A90" s="15">
         <v>39505</v>
       </c>
@@ -18382,7 +18413,7 @@
         <v>82.926777823027351</v>
       </c>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:11">
       <c r="A91" s="15">
         <v>39512</v>
       </c>
@@ -18418,7 +18449,7 @@
         <v>56.330836013124284</v>
       </c>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:11">
       <c r="A92" s="15">
         <v>39519</v>
       </c>
@@ -18454,7 +18485,7 @@
         <v>63.152843166400672</v>
       </c>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:11">
       <c r="A93" s="15">
         <v>39526</v>
       </c>
@@ -18490,7 +18521,7 @@
         <v>44.173359780366653</v>
       </c>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:11">
       <c r="A94" s="15">
         <v>39533</v>
       </c>
@@ -18526,7 +18557,7 @@
         <v>69.09468937538611</v>
       </c>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:11">
       <c r="A95" s="15">
         <v>39540</v>
       </c>
@@ -18562,7 +18593,7 @@
         <v>72.946618726802328</v>
       </c>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:11">
       <c r="A96" s="15">
         <v>39547</v>
       </c>
@@ -18598,7 +18629,7 @@
         <v>69.469947459315094</v>
       </c>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:11">
       <c r="A97" s="15">
         <v>39554</v>
       </c>
@@ -18634,7 +18665,7 @@
         <v>56.323052699867915</v>
       </c>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:11">
       <c r="A98" s="15">
         <v>39561</v>
       </c>
@@ -18670,7 +18701,7 @@
         <v>41.974862158849767</v>
       </c>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:11">
       <c r="A99" s="15">
         <v>39569</v>
       </c>
@@ -18706,7 +18737,7 @@
         <v>44.962229438992097</v>
       </c>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:11">
       <c r="A100" s="15">
         <v>39575</v>
       </c>
@@ -18742,7 +18773,7 @@
         <v>37.798178950335576</v>
       </c>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:11">
       <c r="A101" s="15">
         <v>39582</v>
       </c>
@@ -18778,7 +18809,7 @@
         <v>68.460251596471679</v>
       </c>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:11">
       <c r="A102" s="15">
         <v>39589</v>
       </c>
@@ -18814,7 +18845,7 @@
         <v>65.70356446097523</v>
       </c>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:11">
       <c r="A103" s="15">
         <v>39596</v>
       </c>
@@ -18850,7 +18881,7 @@
         <v>66.213667550072984</v>
       </c>
     </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:11">
       <c r="A104" s="15">
         <v>39603</v>
       </c>
@@ -18886,7 +18917,7 @@
         <v>65.788974489430842</v>
       </c>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:11">
       <c r="A105" s="15">
         <v>39610</v>
       </c>
@@ -18922,7 +18953,7 @@
         <v>78.830161121302538</v>
       </c>
     </row>
-    <row r="106" spans="1:11" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:11" s="11" customFormat="1">
       <c r="A106" s="15">
         <v>39617</v>
       </c>
@@ -18958,7 +18989,7 @@
         <v>65.083754207393383</v>
       </c>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:11">
       <c r="A107" s="15">
         <v>39624</v>
       </c>
@@ -18994,7 +19025,7 @@
         <v>55.264758647687017</v>
       </c>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:11">
       <c r="A108" s="15">
         <v>39631</v>
       </c>
@@ -19030,7 +19061,7 @@
         <v>52.723327174933317</v>
       </c>
     </row>
-    <row r="109" spans="1:11" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:11" s="11" customFormat="1">
       <c r="A109" s="15">
         <v>39638</v>
       </c>
@@ -19066,7 +19097,7 @@
         <v>75.848904583590468</v>
       </c>
     </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:11">
       <c r="A110" s="15">
         <v>39645</v>
       </c>
@@ -19102,7 +19133,7 @@
         <v>51.278326455349131</v>
       </c>
     </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:11">
       <c r="A111" s="15">
         <v>39652</v>
       </c>
@@ -19138,7 +19169,7 @@
         <v>57.909108469652679</v>
       </c>
     </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:11">
       <c r="A112" s="15">
         <v>39659</v>
       </c>
@@ -19174,7 +19205,7 @@
         <v>61.750517406739192</v>
       </c>
     </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:11">
       <c r="A113" s="15">
         <v>39666</v>
       </c>
@@ -19210,7 +19241,7 @@
         <v>52.661575232504951</v>
       </c>
     </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:11">
       <c r="A114" s="15">
         <v>39673</v>
       </c>
@@ -19246,7 +19277,7 @@
         <v>53.118250871076597</v>
       </c>
     </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:11">
       <c r="A115" s="15">
         <v>39681</v>
       </c>
@@ -19282,7 +19313,7 @@
         <v>50.104043997600584</v>
       </c>
     </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:11">
       <c r="A116" s="15">
         <v>39687</v>
       </c>
@@ -19318,7 +19349,7 @@
         <v>50.177676148596895</v>
       </c>
     </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:11">
       <c r="A117" s="15">
         <v>39694</v>
       </c>
@@ -19354,7 +19385,7 @@
         <v>65.073504542370074</v>
       </c>
     </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:11">
       <c r="A118" s="15">
         <v>39701</v>
       </c>
@@ -19390,7 +19421,7 @@
         <v>44.254182598587626</v>
       </c>
     </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:11">
       <c r="A119" s="15">
         <v>39708</v>
       </c>
@@ -19426,7 +19457,7 @@
         <v>47.422942867393644</v>
       </c>
     </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:11">
       <c r="A120" s="15">
         <v>39715</v>
       </c>
@@ -19462,7 +19493,7 @@
         <v>46.359571574198242</v>
       </c>
     </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:11">
       <c r="A121" s="15">
         <v>39722</v>
       </c>
@@ -19498,7 +19529,7 @@
         <v>33.405873873919091</v>
       </c>
     </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:11">
       <c r="A122" s="15">
         <v>39729</v>
       </c>
@@ -19534,7 +19565,7 @@
         <v>51.281080608690978</v>
       </c>
     </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:11">
       <c r="A123" s="15">
         <v>39736</v>
       </c>
@@ -19570,7 +19601,7 @@
         <v>40.551750201988128</v>
       </c>
     </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:11">
       <c r="A124" s="15">
         <v>39743</v>
       </c>
@@ -19606,7 +19637,7 @@
         <v>44.129844927173707</v>
       </c>
     </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:11">
       <c r="A125" s="15">
         <v>39750</v>
       </c>
@@ -19642,7 +19673,7 @@
         <v>53.882588406027168</v>
       </c>
     </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:11">
       <c r="A126" s="15">
         <v>39757</v>
       </c>
@@ -19678,7 +19709,7 @@
         <v>49.886350075701394</v>
       </c>
     </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:11">
       <c r="A127" s="15">
         <v>39764</v>
       </c>
@@ -19714,7 +19745,7 @@
         <v>44.405800463275128</v>
       </c>
     </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:11">
       <c r="A128" s="15">
         <v>39771</v>
       </c>
@@ -19750,7 +19781,7 @@
         <v>43.976952126529874</v>
       </c>
     </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:11">
       <c r="A129" s="15">
         <v>39778</v>
       </c>
@@ -19786,7 +19817,7 @@
         <v>57.854397526301433</v>
       </c>
     </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:11">
       <c r="A130" s="15">
         <v>39785</v>
       </c>
@@ -19822,7 +19853,7 @@
         <v>45.357327933111691</v>
       </c>
     </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:11">
       <c r="A131" s="15">
         <v>39792</v>
       </c>
@@ -19873,7 +19904,7 @@
         <v>49.214072926201013</v>
       </c>
     </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:11">
       <c r="A132" s="15">
         <v>39799</v>
       </c>
@@ -19909,7 +19940,7 @@
         <v>53.491406900967732</v>
       </c>
     </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:11">
       <c r="A133" s="15">
         <v>39806</v>
       </c>
@@ -19945,7 +19976,7 @@
         <v>55.286482576750558</v>
       </c>
     </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:11">
       <c r="A134" s="15">
         <v>39813</v>
       </c>
@@ -19981,7 +20012,7 @@
         <v>55.143723549589758</v>
       </c>
     </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:11">
       <c r="A135" s="15">
         <v>39820</v>
       </c>
@@ -20017,7 +20048,7 @@
         <v>51.012811516083978</v>
       </c>
     </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:11">
       <c r="A136" s="15">
         <v>39827</v>
       </c>
@@ -20053,7 +20084,7 @@
         <v>64.584992254313974</v>
       </c>
     </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:11">
       <c r="A137" s="15">
         <v>39834</v>
       </c>
@@ -20089,7 +20120,7 @@
         <v>51.036330889936345</v>
       </c>
     </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:11">
       <c r="A138" s="15">
         <v>39841</v>
       </c>
@@ -20125,7 +20156,7 @@
         <v>49.006860617093729</v>
       </c>
     </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:11">
       <c r="A139" s="15">
         <v>39848</v>
       </c>
@@ -20161,7 +20192,7 @@
         <v>33.08758938678627</v>
       </c>
     </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:11">
       <c r="A140" s="15">
         <v>39855</v>
       </c>
@@ -20197,7 +20228,7 @@
         <v>42.688334209137516</v>
       </c>
     </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:11">
       <c r="A141" s="15">
         <v>39862</v>
       </c>
@@ -20233,7 +20264,7 @@
         <v>49.836210913235156</v>
       </c>
     </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:11">
       <c r="A142" s="15">
         <v>39869</v>
       </c>
@@ -20269,7 +20300,7 @@
         <v>46.376897362766087</v>
       </c>
     </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:11">
       <c r="A143" s="15">
         <v>39876</v>
       </c>
@@ -20305,7 +20336,7 @@
         <v>48.797982331083887</v>
       </c>
     </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:11">
       <c r="A144" s="15">
         <v>39883</v>
       </c>
@@ -20341,7 +20372,7 @@
         <v>50.995285896575474</v>
       </c>
     </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:11">
       <c r="A145" s="15">
         <v>39890</v>
       </c>
@@ -20377,7 +20408,7 @@
         <v>50.632752300623871</v>
       </c>
     </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:11">
       <c r="A146" s="15">
         <v>39897</v>
       </c>
@@ -20413,7 +20444,7 @@
         <v>49.159815906896966</v>
       </c>
     </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:11">
       <c r="A147" s="15">
         <v>39904</v>
       </c>
@@ -20449,7 +20480,7 @@
         <v>67.93322071407249</v>
       </c>
     </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:11">
       <c r="A148" s="15">
         <v>39911</v>
       </c>
@@ -20485,7 +20516,7 @@
         <v>59.144140747470985</v>
       </c>
     </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:11">
       <c r="A149" s="15">
         <v>39918</v>
       </c>
@@ -20521,7 +20552,7 @@
         <v>48.417328037810883</v>
       </c>
     </row>
-    <row r="150" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:11">
       <c r="A150" s="15">
         <v>39925</v>
       </c>
@@ -20557,7 +20588,7 @@
         <v>65.507189828231219</v>
       </c>
     </row>
-    <row r="151" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:11">
       <c r="A151" s="15">
         <v>39932</v>
       </c>
@@ -20593,7 +20624,7 @@
         <v>67.77459535800439</v>
       </c>
     </row>
-    <row r="152" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:11">
       <c r="A152" s="15">
         <v>39939</v>
       </c>
@@ -20629,7 +20660,7 @@
         <v>67.144419826628891</v>
       </c>
     </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:11">
       <c r="A153" s="15">
         <v>39946</v>
       </c>
@@ -20665,7 +20696,7 @@
         <v>50.709106035336958</v>
       </c>
     </row>
-    <row r="154" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:11">
       <c r="A154" s="15">
         <v>39953</v>
       </c>
@@ -20701,7 +20732,7 @@
         <v>45.673803993182069</v>
       </c>
     </row>
-    <row r="155" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:11">
       <c r="A155" s="15">
         <v>39960</v>
       </c>
@@ -20737,7 +20768,7 @@
         <v>56.578290137928242</v>
       </c>
     </row>
-    <row r="156" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:11">
       <c r="A156" s="15">
         <v>39967</v>
       </c>
@@ -20773,7 +20804,7 @@
         <v>65.158129608233793</v>
       </c>
     </row>
-    <row r="157" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:11">
       <c r="A157" s="15">
         <v>39974</v>
       </c>
@@ -20809,7 +20840,7 @@
         <v>44.471505975736868</v>
       </c>
     </row>
-    <row r="158" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:11">
       <c r="A158" s="15">
         <v>39981</v>
       </c>
@@ -20845,7 +20876,7 @@
         <v>52.627079222161107</v>
       </c>
     </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:11">
       <c r="A159" s="15">
         <v>39988</v>
       </c>
@@ -20881,7 +20912,7 @@
         <v>66.261051954921754</v>
       </c>
     </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:11">
       <c r="A160" s="15">
         <v>39995</v>
       </c>
@@ -20917,7 +20948,7 @@
         <v>54.893058424976317</v>
       </c>
     </row>
-    <row r="161" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:11">
       <c r="A161" s="15">
         <v>40002</v>
       </c>
@@ -20953,7 +20984,7 @@
         <v>64.161205849108597</v>
       </c>
     </row>
-    <row r="162" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:11">
       <c r="A162" s="15">
         <v>40009</v>
       </c>
@@ -20989,7 +21020,7 @@
         <v>52.811235830415114</v>
       </c>
     </row>
-    <row r="163" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:11">
       <c r="A163" s="15">
         <v>40016</v>
       </c>
@@ -21025,7 +21056,7 @@
         <v>57.645867319279404</v>
       </c>
     </row>
-    <row r="164" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:11">
       <c r="A164" s="15">
         <v>40023</v>
       </c>
@@ -21061,7 +21092,7 @@
         <v>61.365403956693434</v>
       </c>
     </row>
-    <row r="165" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:11">
       <c r="A165" s="15">
         <v>40030</v>
       </c>
@@ -21097,7 +21128,7 @@
         <v>44.582988427682338</v>
       </c>
     </row>
-    <row r="166" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:11">
       <c r="A166" s="15">
         <v>40037</v>
       </c>
@@ -21133,7 +21164,7 @@
         <v>54.166951121047973</v>
       </c>
     </row>
-    <row r="167" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:11">
       <c r="A167" s="15">
         <v>40044</v>
       </c>
@@ -21169,7 +21200,7 @@
         <v>76.385981144531414</v>
       </c>
     </row>
-    <row r="168" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:11">
       <c r="A168" s="15">
         <v>40051</v>
       </c>
@@ -21205,7 +21236,7 @@
         <v>71.141667275747665</v>
       </c>
     </row>
-    <row r="169" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:11">
       <c r="A169" s="15">
         <v>40058</v>
       </c>
@@ -21241,7 +21272,7 @@
         <v>81.41339889263179</v>
       </c>
     </row>
-    <row r="170" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:11">
       <c r="A170" s="15">
         <v>40065</v>
       </c>
@@ -21277,7 +21308,7 @@
         <v>63.355150657102897</v>
       </c>
     </row>
-    <row r="171" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:11">
       <c r="A171" s="15">
         <v>40072</v>
       </c>
@@ -21313,7 +21344,7 @@
         <v>63.586872250336747</v>
       </c>
     </row>
-    <row r="172" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:11">
       <c r="A172" s="15">
         <v>40079</v>
       </c>
@@ -21349,7 +21380,7 @@
         <v>53.318827599106207</v>
       </c>
     </row>
-    <row r="173" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:11">
       <c r="A173" s="15">
         <v>40086</v>
       </c>
@@ -21385,7 +21416,7 @@
         <v>49.477873007591704</v>
       </c>
     </row>
-    <row r="174" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:11">
       <c r="A174" s="15">
         <v>40093</v>
       </c>
@@ -21421,7 +21452,7 @@
         <v>71.403538470599969</v>
       </c>
     </row>
-    <row r="175" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:11">
       <c r="A175" s="15">
         <v>40100</v>
       </c>
@@ -21457,7 +21488,7 @@
         <v>61.732827908030352</v>
       </c>
     </row>
-    <row r="176" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:11">
       <c r="A176" s="15">
         <v>40107</v>
       </c>
@@ -21493,7 +21524,7 @@
         <v>52.229993511604249</v>
       </c>
     </row>
-    <row r="177" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:11">
       <c r="A177" s="15">
         <v>40114</v>
       </c>
@@ -21529,7 +21560,7 @@
         <v>64.598575021541549</v>
       </c>
     </row>
-    <row r="178" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:11">
       <c r="A178" s="15">
         <v>40121</v>
       </c>
@@ -21565,7 +21596,7 @@
         <v>61.131436014016572</v>
       </c>
     </row>
-    <row r="179" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:11">
       <c r="A179" s="15">
         <v>40128</v>
       </c>
@@ -21601,7 +21632,7 @@
         <v>53.907207534999003</v>
       </c>
     </row>
-    <row r="180" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:11">
       <c r="A180" s="15">
         <v>40135</v>
       </c>
@@ -21637,7 +21668,7 @@
         <v>44.756939056977522</v>
       </c>
     </row>
-    <row r="181" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:11">
       <c r="A181" s="15">
         <v>40142</v>
       </c>
@@ -21673,7 +21704,7 @@
         <v>56.685418081441156</v>
       </c>
     </row>
-    <row r="182" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:11">
       <c r="A182" s="15">
         <v>40149</v>
       </c>
@@ -21709,7 +21740,7 @@
         <v>49.326994067650219</v>
       </c>
     </row>
-    <row r="183" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:11">
       <c r="A183" s="15">
         <v>40156</v>
       </c>
@@ -21745,7 +21776,7 @@
         <v>56.94789248873581</v>
       </c>
     </row>
-    <row r="184" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:11">
       <c r="A184" s="15">
         <v>40163</v>
       </c>
@@ -21781,7 +21812,7 @@
         <v>53.684534257154517</v>
       </c>
     </row>
-    <row r="185" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:11">
       <c r="A185" s="15">
         <v>40170</v>
       </c>
@@ -21817,7 +21848,7 @@
         <v>65.364947708147739</v>
       </c>
     </row>
-    <row r="186" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:11">
       <c r="A186" s="15">
         <v>40177</v>
       </c>
@@ -21853,7 +21884,7 @@
         <v>53.704634029690361</v>
       </c>
     </row>
-    <row r="187" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:11">
       <c r="A187" s="15">
         <v>40184</v>
       </c>
@@ -21889,7 +21920,7 @@
         <v>54.771375546492628</v>
       </c>
     </row>
-    <row r="188" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:11">
       <c r="A188" s="15">
         <v>40191</v>
       </c>
@@ -21925,7 +21956,7 @@
         <v>57.833752535015343</v>
       </c>
     </row>
-    <row r="189" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:11">
       <c r="A189" s="15">
         <v>40198</v>
       </c>
@@ -21961,7 +21992,7 @@
         <v>79.252584956089748</v>
       </c>
     </row>
-    <row r="190" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:11">
       <c r="A190" s="15">
         <v>40205</v>
       </c>
@@ -21997,7 +22028,7 @@
         <v>66.112908932661171</v>
       </c>
     </row>
-    <row r="191" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:11">
       <c r="A191" s="15">
         <v>40212</v>
       </c>
@@ -22033,7 +22064,7 @@
         <v>68.480905740352668</v>
       </c>
     </row>
-    <row r="192" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:11">
       <c r="A192" s="15">
         <v>40219</v>
       </c>
@@ -22069,7 +22100,7 @@
         <v>68.820680112015253</v>
       </c>
     </row>
-    <row r="193" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:11">
       <c r="A193" s="15">
         <v>40226</v>
       </c>
@@ -22105,7 +22136,7 @@
         <v>59.032374376182737</v>
       </c>
     </row>
-    <row r="194" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:11">
       <c r="A194" s="15">
         <v>40233</v>
       </c>
@@ -22141,7 +22172,7 @@
         <v>60.995325657513426</v>
       </c>
     </row>
-    <row r="195" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:11">
       <c r="A195" s="15">
         <v>40240</v>
       </c>
@@ -22192,7 +22223,7 @@
         <v>61.01651833892263</v>
       </c>
     </row>
-    <row r="196" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:11">
       <c r="A196" s="15">
         <v>40247</v>
       </c>
@@ -22228,7 +22259,7 @@
         <v>68.948409164893818</v>
       </c>
     </row>
-    <row r="197" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:11">
       <c r="A197" s="15">
         <v>40254</v>
       </c>
@@ -22264,7 +22295,7 @@
         <v>55.495282272042076</v>
       </c>
     </row>
-    <row r="198" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:11">
       <c r="A198" s="15">
         <v>40261</v>
       </c>
@@ -22300,7 +22331,7 @@
         <v>57.756350696573961</v>
       </c>
     </row>
-    <row r="199" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:11">
       <c r="A199" s="15">
         <v>40268</v>
       </c>
@@ -22336,7 +22367,7 @@
         <v>46.374631010759359</v>
       </c>
     </row>
-    <row r="200" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:11">
       <c r="A200" s="15">
         <v>40275</v>
       </c>
@@ -22372,7 +22403,7 @@
         <v>50.035497779699199</v>
       </c>
     </row>
-    <row r="201" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:11">
       <c r="A201" s="15">
         <v>40282</v>
       </c>
@@ -22408,7 +22439,7 @@
         <v>45.14920394961522</v>
       </c>
     </row>
-    <row r="202" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:11">
       <c r="A202" s="15">
         <v>40289</v>
       </c>
@@ -22444,7 +22475,7 @@
         <v>42.330808834030208</v>
       </c>
     </row>
-    <row r="203" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:11">
       <c r="A203" s="15">
         <v>40296</v>
       </c>
@@ -22480,7 +22511,7 @@
         <v>46.031147244235598</v>
       </c>
     </row>
-    <row r="204" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:11">
       <c r="A204" s="15">
         <v>40303</v>
       </c>
@@ -22516,7 +22547,7 @@
         <v>73.783147168729855</v>
       </c>
     </row>
-    <row r="205" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:11">
       <c r="A205" s="15">
         <v>40310</v>
       </c>
@@ -22552,7 +22583,7 @@
         <v>67.420059029224618</v>
       </c>
     </row>
-    <row r="206" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:11">
       <c r="A206" s="15">
         <v>40317</v>
       </c>
@@ -22588,7 +22619,7 @@
         <v>65.236302377809508</v>
       </c>
     </row>
-    <row r="207" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:11">
       <c r="A207" s="15">
         <v>40324</v>
       </c>
@@ -22624,7 +22655,7 @@
         <v>45.438603264918548</v>
       </c>
     </row>
-    <row r="208" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:11">
       <c r="A208" s="15">
         <v>40331</v>
       </c>
@@ -22660,7 +22691,7 @@
         <v>55.842613656597415</v>
       </c>
     </row>
-    <row r="209" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:11">
       <c r="A209" s="15">
         <v>40338</v>
       </c>
@@ -22696,7 +22727,7 @@
         <v>50.566226976684703</v>
       </c>
     </row>
-    <row r="210" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:11">
       <c r="A210" s="15">
         <v>40345</v>
       </c>
@@ -22732,7 +22763,7 @@
         <v>60.167993983512531</v>
       </c>
     </row>
-    <row r="211" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:11">
       <c r="A211" s="15">
         <v>40352</v>
       </c>
@@ -22768,7 +22799,7 @@
         <v>59.384867216709665</v>
       </c>
     </row>
-    <row r="212" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:11">
       <c r="A212" s="15">
         <v>40359</v>
       </c>
@@ -22804,7 +22835,7 @@
         <v>51.877165703250242</v>
       </c>
     </row>
-    <row r="213" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:11">
       <c r="A213" s="15">
         <v>40366</v>
       </c>
@@ -22840,7 +22871,7 @@
         <v>60.791159694094574</v>
       </c>
     </row>
-    <row r="214" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:11">
       <c r="A214" s="15">
         <v>40373</v>
       </c>
@@ -22876,7 +22907,7 @@
         <v>52.381556868806406</v>
       </c>
     </row>
-    <row r="215" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:11">
       <c r="A215" s="15">
         <v>40380</v>
       </c>
@@ -22912,7 +22943,7 @@
         <v>55.497901708236633</v>
       </c>
     </row>
-    <row r="216" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:11">
       <c r="A216" s="15">
         <v>40387</v>
       </c>
@@ -22948,7 +22979,7 @@
         <v>63.648541403343927</v>
       </c>
     </row>
-    <row r="217" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:11">
       <c r="A217" s="15">
         <v>40394</v>
       </c>
@@ -22984,7 +23015,7 @@
         <v>58.51627398414611</v>
       </c>
     </row>
-    <row r="218" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:11">
       <c r="A218" s="15">
         <v>40401</v>
       </c>
@@ -23020,7 +23051,7 @@
         <v>70.168158657672691</v>
       </c>
     </row>
-    <row r="219" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:11">
       <c r="A219" s="15">
         <v>40408</v>
       </c>
@@ -23056,7 +23087,7 @@
         <v>53.947041077312385</v>
       </c>
     </row>
-    <row r="220" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:11">
       <c r="A220" s="15">
         <v>40415</v>
       </c>
@@ -23092,7 +23123,7 @@
         <v>55.908131213647891</v>
       </c>
     </row>
-    <row r="221" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:11">
       <c r="A221" s="15">
         <v>40422</v>
       </c>
@@ -23128,7 +23159,7 @@
         <v>62.564187638553811</v>
       </c>
     </row>
-    <row r="222" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:11">
       <c r="A222" s="15">
         <v>40429</v>
       </c>
@@ -23164,7 +23195,7 @@
         <v>72.423309874299363</v>
       </c>
     </row>
-    <row r="223" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:11">
       <c r="A223" s="15">
         <v>40436</v>
       </c>
@@ -23200,7 +23231,7 @@
         <v>73.388746907379783</v>
       </c>
     </row>
-    <row r="224" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:11">
       <c r="A224" s="15">
         <v>40443</v>
       </c>
@@ -23236,7 +23267,7 @@
         <v>74.427829003026858</v>
       </c>
     </row>
-    <row r="225" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:11">
       <c r="A225" s="15">
         <v>40450</v>
       </c>
@@ -23272,7 +23303,7 @@
         <v>65.974731715358232</v>
       </c>
     </row>
-    <row r="226" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:11">
       <c r="A226" s="15">
         <v>40457</v>
       </c>
@@ -23308,7 +23339,7 @@
         <v>59.692906241492011</v>
       </c>
     </row>
-    <row r="227" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:11">
       <c r="A227" s="15">
         <v>40464</v>
       </c>
@@ -23344,7 +23375,7 @@
         <v>55.007204521826623</v>
       </c>
     </row>
-    <row r="228" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:11">
       <c r="A228" s="15">
         <v>40471</v>
       </c>
@@ -23380,7 +23411,7 @@
         <v>54.037281159418455</v>
       </c>
     </row>
-    <row r="229" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:11">
       <c r="A229" s="15">
         <v>40478</v>
       </c>
@@ -23416,7 +23447,7 @@
         <v>74.053447495288836</v>
       </c>
     </row>
-    <row r="230" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:11">
       <c r="A230" s="15">
         <v>40485</v>
       </c>
@@ -23452,7 +23483,7 @@
         <v>57.599139747516887</v>
       </c>
     </row>
-    <row r="231" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:11">
       <c r="A231" s="15">
         <v>40493</v>
       </c>
@@ -23488,7 +23519,7 @@
         <v>73.628931758084974</v>
       </c>
     </row>
-    <row r="232" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:11">
       <c r="A232" s="15">
         <v>40499</v>
       </c>
@@ -23524,7 +23555,7 @@
         <v>64.712269652083734</v>
       </c>
     </row>
-    <row r="233" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:11">
       <c r="A233" s="15">
         <v>40506</v>
       </c>
@@ -23560,7 +23591,7 @@
         <v>68.728127833919316</v>
       </c>
     </row>
-    <row r="234" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:11">
       <c r="A234" s="15">
         <v>40513</v>
       </c>
@@ -23596,7 +23627,7 @@
         <v>71.396578703865657</v>
       </c>
     </row>
-    <row r="235" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:11">
       <c r="A235" s="15">
         <v>40520</v>
       </c>
@@ -23632,7 +23663,7 @@
         <v>56.848732557127434</v>
       </c>
     </row>
-    <row r="236" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:11">
       <c r="A236" s="15">
         <v>40527</v>
       </c>
@@ -23668,7 +23699,7 @@
         <v>48.876462768440668</v>
       </c>
     </row>
-    <row r="237" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:11">
       <c r="A237" s="15">
         <v>40534</v>
       </c>
@@ -23704,7 +23735,7 @@
         <v>30.939366105335772</v>
       </c>
     </row>
-    <row r="238" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:11">
       <c r="A238" s="15">
         <v>40541</v>
       </c>
@@ -23740,7 +23771,7 @@
         <v>25.867679114547297</v>
       </c>
     </row>
-    <row r="239" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:11">
       <c r="A239" s="15">
         <v>40548</v>
       </c>
@@ -23776,7 +23807,7 @@
         <v>35.99596195192472</v>
       </c>
     </row>
-    <row r="240" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:11">
       <c r="A240" s="15">
         <v>40555</v>
       </c>
@@ -23812,7 +23843,7 @@
         <v>34.5248029413723</v>
       </c>
     </row>
-    <row r="241" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:11">
       <c r="A241" s="15">
         <v>40562</v>
       </c>
@@ -23848,7 +23879,7 @@
         <v>48.204614903131251</v>
       </c>
     </row>
-    <row r="242" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:11">
       <c r="A242" s="15">
         <v>40569</v>
       </c>
@@ -23884,7 +23915,7 @@
         <v>44.563550516112116</v>
       </c>
     </row>
-    <row r="243" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:11">
       <c r="A243" s="15">
         <v>40576</v>
       </c>
@@ -23920,7 +23951,7 @@
         <v>37.30092994819298</v>
       </c>
     </row>
-    <row r="244" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:11">
       <c r="A244" s="15">
         <v>40583</v>
       </c>
@@ -23956,7 +23987,7 @@
         <v>36.241942484664484</v>
       </c>
     </row>
-    <row r="245" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:11">
       <c r="A245" s="15">
         <v>40590</v>
       </c>
@@ -23992,7 +24023,7 @@
         <v>39.530799594711759</v>
       </c>
     </row>
-    <row r="246" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:11">
       <c r="A246" s="15">
         <v>40597</v>
       </c>
@@ -24028,7 +24059,7 @@
         <v>53.939404659302646</v>
       </c>
     </row>
-    <row r="247" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:11">
       <c r="A247" s="15">
         <v>40604</v>
       </c>
@@ -24064,7 +24095,7 @@
         <v>43.942750002449529</v>
       </c>
     </row>
-    <row r="248" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:11">
       <c r="A248" s="15">
         <v>40611</v>
       </c>
@@ -24100,7 +24131,7 @@
         <v>34.894786457057684</v>
       </c>
     </row>
-    <row r="249" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:11">
       <c r="A249" s="15">
         <v>40618</v>
       </c>
@@ -24136,7 +24167,7 @@
         <v>64.316923641190016</v>
       </c>
     </row>
-    <row r="250" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:11">
       <c r="A250" s="15">
         <v>40625</v>
       </c>
@@ -24172,7 +24203,7 @@
         <v>54.669969412425644</v>
       </c>
     </row>
-    <row r="251" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:11">
       <c r="A251" s="15">
         <v>40632</v>
       </c>
@@ -24208,7 +24239,7 @@
         <v>33.436812839822487</v>
       </c>
     </row>
-    <row r="252" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:11">
       <c r="A252" s="15">
         <v>40639</v>
       </c>
@@ -24244,7 +24275,7 @@
         <v>39.172313642501635</v>
       </c>
     </row>
-    <row r="253" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:11">
       <c r="A253" s="15">
         <v>40646</v>
       </c>
@@ -24280,7 +24311,7 @@
         <v>38.729050102374607</v>
       </c>
     </row>
-    <row r="254" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:11">
       <c r="A254" s="15">
         <v>40653</v>
       </c>
@@ -24316,7 +24347,7 @@
         <v>41.715563146345993</v>
       </c>
     </row>
-    <row r="255" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:11">
       <c r="A255" s="15">
         <v>40660</v>
       </c>
@@ -24352,7 +24383,7 @@
         <v>43.741742077791095</v>
       </c>
     </row>
-    <row r="256" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:11">
       <c r="A256" s="15">
         <v>40667</v>
       </c>
@@ -24388,7 +24419,7 @@
         <v>47.873989122981456</v>
       </c>
     </row>
-    <row r="257" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:11">
       <c r="A257" s="15">
         <v>40674</v>
       </c>
@@ -24424,7 +24455,7 @@
         <v>51.779665709540218</v>
       </c>
     </row>
-    <row r="258" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:11">
       <c r="A258" s="15">
         <v>40681</v>
       </c>
@@ -24460,7 +24491,7 @@
         <v>57.023035358289334</v>
       </c>
     </row>
-    <row r="259" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:11">
       <c r="A259" s="15">
         <v>40688</v>
       </c>
@@ -24511,7 +24542,7 @@
         <v>56.87088409797628</v>
       </c>
     </row>
-    <row r="260" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:11">
       <c r="A260" s="15">
         <v>40695</v>
       </c>
@@ -24547,7 +24578,7 @@
         <v>47.063569688632143</v>
       </c>
     </row>
-    <row r="261" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:11">
       <c r="A261" s="15">
         <v>40702</v>
       </c>
@@ -24583,7 +24614,7 @@
         <v>58.561562455438484</v>
       </c>
     </row>
-    <row r="262" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:11">
       <c r="A262" s="15">
         <v>40709</v>
       </c>
@@ -24619,7 +24650,7 @@
         <v>54.876464024706216</v>
       </c>
     </row>
-    <row r="263" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:11">
       <c r="A263" s="15">
         <v>40716</v>
       </c>
@@ -24655,7 +24686,7 @@
         <v>48.129506282529015</v>
       </c>
     </row>
-    <row r="264" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:11">
       <c r="A264" s="15">
         <v>40723</v>
       </c>
@@ -24691,7 +24722,7 @@
         <v>53.998865301934728</v>
       </c>
     </row>
-    <row r="265" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:11">
       <c r="A265" s="15">
         <v>40730</v>
       </c>
@@ -24727,7 +24758,7 @@
         <v>57.89850820929329</v>
       </c>
     </row>
-    <row r="266" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:11">
       <c r="A266" s="15">
         <v>40737</v>
       </c>
@@ -24763,7 +24794,7 @@
         <v>53.479549570113456</v>
       </c>
     </row>
-    <row r="267" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:11">
       <c r="A267" s="15">
         <v>40744</v>
       </c>
@@ -24799,7 +24830,7 @@
         <v>49.79143878947302</v>
       </c>
     </row>
-    <row r="268" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:11">
       <c r="A268" s="15">
         <v>40751</v>
       </c>
@@ -24835,7 +24866,7 @@
         <v>42.651475813694034</v>
       </c>
     </row>
-    <row r="269" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:11">
       <c r="A269" s="15">
         <v>40758</v>
       </c>
@@ -24871,7 +24902,7 @@
         <v>50.439188817558389</v>
       </c>
     </row>
-    <row r="270" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:11">
       <c r="A270" s="15">
         <v>40765</v>
       </c>
@@ -24907,7 +24938,7 @@
         <v>42.049324508367285</v>
       </c>
     </row>
-    <row r="271" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:11">
       <c r="A271" s="15">
         <v>40772</v>
       </c>
@@ -24943,7 +24974,7 @@
         <v>47.516027185636773</v>
       </c>
     </row>
-    <row r="272" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:11">
       <c r="A272" s="15">
         <v>40779</v>
       </c>
@@ -24979,7 +25010,7 @@
         <v>40.399772058656886</v>
       </c>
     </row>
-    <row r="273" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:11">
       <c r="A273" s="15">
         <v>40786</v>
       </c>
@@ -25015,7 +25046,7 @@
         <v>44.783201620610939</v>
       </c>
     </row>
-    <row r="274" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:11">
       <c r="A274" s="15">
         <v>40793</v>
       </c>
@@ -25051,7 +25082,7 @@
         <v>46.854774319627346</v>
       </c>
     </row>
-    <row r="275" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:11">
       <c r="A275" s="15">
         <v>40800</v>
       </c>
@@ -25087,7 +25118,7 @@
         <v>50.572231681862235</v>
       </c>
     </row>
-    <row r="276" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:11">
       <c r="A276" s="15">
         <v>40807</v>
       </c>
@@ -25123,7 +25154,7 @@
         <v>51.000097894093308</v>
       </c>
     </row>
-    <row r="277" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:11">
       <c r="A277" s="15">
         <v>40814</v>
       </c>
@@ -25159,7 +25190,7 @@
         <v>38.969787977354969</v>
       </c>
     </row>
-    <row r="278" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:11">
       <c r="A278" s="15">
         <v>40821</v>
       </c>
@@ -25195,7 +25226,7 @@
         <v>54.517864058372737</v>
       </c>
     </row>
-    <row r="279" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:11">
       <c r="A279" s="15">
         <v>40828</v>
       </c>
@@ -25231,7 +25262,7 @@
         <v>58.875398087826127</v>
       </c>
     </row>
-    <row r="280" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:11">
       <c r="A280" s="15">
         <v>40835</v>
       </c>
@@ -25267,7 +25298,7 @@
         <v>40.918862469344425</v>
       </c>
     </row>
-    <row r="281" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:11">
       <c r="A281" s="15">
         <v>40842</v>
       </c>
@@ -25303,7 +25334,7 @@
         <v>45.233867381064172</v>
       </c>
     </row>
-    <row r="282" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:11">
       <c r="A282" s="15">
         <v>40849</v>
       </c>
@@ -25339,7 +25370,7 @@
         <v>55.320831293464849</v>
       </c>
     </row>
-    <row r="283" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:11">
       <c r="A283" s="15">
         <v>40856</v>
       </c>
@@ -25375,7 +25406,7 @@
         <v>55.690513263814637</v>
       </c>
     </row>
-    <row r="284" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:11">
       <c r="A284" s="15">
         <v>40863</v>
       </c>
@@ -25411,7 +25442,7 @@
         <v>51.999145292121014</v>
       </c>
     </row>
-    <row r="285" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:11">
       <c r="A285" s="15">
         <v>40870</v>
       </c>
@@ -25447,7 +25478,7 @@
         <v>45.873095396241652</v>
       </c>
     </row>
-    <row r="286" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:11">
       <c r="A286" s="15">
         <v>40877</v>
       </c>
@@ -25483,7 +25514,7 @@
         <v>42.216169288999922</v>
       </c>
     </row>
-    <row r="287" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:11">
       <c r="A287" s="15">
         <v>40884</v>
       </c>
@@ -25519,7 +25550,7 @@
         <v>43.664531422515303</v>
       </c>
     </row>
-    <row r="288" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:11">
       <c r="A288" s="15">
         <v>40891</v>
       </c>
@@ -25555,7 +25586,7 @@
         <v>48.198670933439651</v>
       </c>
     </row>
-    <row r="289" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:11">
       <c r="A289" s="15">
         <v>40898</v>
       </c>
@@ -25591,7 +25622,7 @@
         <v>39.516792034075834</v>
       </c>
     </row>
-    <row r="290" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:11">
       <c r="A290" s="15">
         <v>40905</v>
       </c>
@@ -25627,7 +25658,7 @@
         <v>28.563193765273795</v>
       </c>
     </row>
-    <row r="291" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:11">
       <c r="A291" s="15">
         <v>40912</v>
       </c>
@@ -25663,7 +25694,7 @@
         <v>41.403003244764143</v>
       </c>
     </row>
-    <row r="292" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:11">
       <c r="A292" s="15">
         <v>40919</v>
       </c>
@@ -25699,7 +25730,7 @@
         <v>47.072652594140706</v>
       </c>
     </row>
-    <row r="293" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:11">
       <c r="A293" s="15">
         <v>40926</v>
       </c>
@@ -25735,7 +25766,7 @@
         <v>49.053078858054825</v>
       </c>
     </row>
-    <row r="294" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:11">
       <c r="A294" s="15">
         <v>40933</v>
       </c>
@@ -25771,7 +25802,7 @@
         <v>53.510954226421923</v>
       </c>
     </row>
-    <row r="295" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:11">
       <c r="A295" s="15">
         <v>40940</v>
       </c>
@@ -25807,7 +25838,7 @@
         <v>39.384750530886507</v>
       </c>
     </row>
-    <row r="296" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:11">
       <c r="A296" s="15">
         <v>40947</v>
       </c>
@@ -25843,7 +25874,7 @@
         <v>36.817697808266423</v>
       </c>
     </row>
-    <row r="297" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:11">
       <c r="A297" s="15">
         <v>40954</v>
       </c>
@@ -25879,7 +25910,7 @@
         <v>36.233572758862671</v>
       </c>
     </row>
-    <row r="298" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:11">
       <c r="A298" s="15">
         <v>40961</v>
       </c>
@@ -25915,7 +25946,7 @@
         <v>37.171889580703322</v>
       </c>
     </row>
-    <row r="299" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:11">
       <c r="A299" s="15">
         <v>40968</v>
       </c>
@@ -25951,7 +25982,7 @@
         <v>36.759941210655207</v>
       </c>
     </row>
-    <row r="300" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:11">
       <c r="A300" s="15">
         <v>40975</v>
       </c>
@@ -25987,7 +26018,7 @@
         <v>56.661237586866619</v>
       </c>
     </row>
-    <row r="301" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:11">
       <c r="A301" s="15">
         <v>40982</v>
       </c>
@@ -26023,7 +26054,7 @@
         <v>47.798457305394521</v>
       </c>
     </row>
-    <row r="302" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:11">
       <c r="A302" s="15">
         <v>40989</v>
       </c>
@@ -26059,7 +26090,7 @@
         <v>47.064324329465158</v>
       </c>
     </row>
-    <row r="303" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:11">
       <c r="A303" s="15">
         <v>40996</v>
       </c>
@@ -26095,7 +26126,7 @@
         <v>40.595204301061202</v>
       </c>
     </row>
-    <row r="304" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:11">
       <c r="A304" s="15">
         <v>41003</v>
       </c>
@@ -26131,7 +26162,7 @@
         <v>38.549937035348876</v>
       </c>
     </row>
-    <row r="305" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:11">
       <c r="A305" s="15">
         <v>41010</v>
       </c>
@@ -26167,7 +26198,7 @@
         <v>53.214477468494394</v>
       </c>
     </row>
-    <row r="306" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:11">
       <c r="A306" s="15">
         <v>41017</v>
       </c>
@@ -26203,7 +26234,7 @@
         <v>56.900572530695925</v>
       </c>
     </row>
-    <row r="307" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:11">
       <c r="A307" s="15">
         <v>41024</v>
       </c>
@@ -26239,7 +26270,7 @@
         <v>56.771006536281874</v>
       </c>
     </row>
-    <row r="308" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:11">
       <c r="A308" s="15">
         <v>41031</v>
       </c>
@@ -26275,7 +26306,7 @@
         <v>50.543476884317684</v>
       </c>
     </row>
-    <row r="309" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:11">
       <c r="A309" s="15">
         <v>41038</v>
       </c>
@@ -26311,7 +26342,7 @@
         <v>54.137497957615317</v>
       </c>
     </row>
-    <row r="310" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:11">
       <c r="A310" s="15">
         <v>41045</v>
       </c>
@@ -26347,7 +26378,7 @@
         <v>41.363917899541384</v>
       </c>
     </row>
-    <row r="311" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:11">
       <c r="A311" s="15">
         <v>41052</v>
       </c>
@@ -26383,7 +26414,7 @@
         <v>45.49777201728218</v>
       </c>
     </row>
-    <row r="312" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:11">
       <c r="A312" s="15">
         <v>41059</v>
       </c>
@@ -26419,7 +26450,7 @@
         <v>46.729614872834489</v>
       </c>
     </row>
-    <row r="313" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:11">
       <c r="A313" s="15">
         <v>41066</v>
       </c>
@@ -26455,7 +26486,7 @@
         <v>34.956741028578463</v>
       </c>
     </row>
-    <row r="314" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:11">
       <c r="A314" s="15">
         <v>41073</v>
       </c>
@@ -26491,7 +26522,7 @@
         <v>29.532500348198187</v>
       </c>
     </row>
-    <row r="315" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:11">
       <c r="A315" s="15">
         <v>41080</v>
       </c>
@@ -26527,7 +26558,7 @@
         <v>45.65945115969452</v>
       </c>
     </row>
-    <row r="316" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:11">
       <c r="A316" s="15">
         <v>41087</v>
       </c>
@@ -26563,7 +26594,7 @@
         <v>48.136271215938542</v>
       </c>
     </row>
-    <row r="317" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:11">
       <c r="A317" s="15">
         <v>41095</v>
       </c>
@@ -26599,7 +26630,7 @@
         <v>49.207476611003706</v>
       </c>
     </row>
-    <row r="318" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:11">
       <c r="A318" s="15">
         <v>41101</v>
       </c>
@@ -26635,7 +26666,7 @@
         <v>53.618962087056566</v>
       </c>
     </row>
-    <row r="319" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:11">
       <c r="A319" s="15">
         <v>41108</v>
       </c>
@@ -26671,7 +26702,7 @@
         <v>52.76407806027715</v>
       </c>
     </row>
-    <row r="320" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:11">
       <c r="A320" s="15">
         <v>41115</v>
       </c>
@@ -26707,7 +26738,7 @@
         <v>50.011052339523104</v>
       </c>
     </row>
-    <row r="321" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:11">
       <c r="A321" s="15">
         <v>41122</v>
       </c>
@@ -26743,7 +26774,7 @@
         <v>53.937797639233743</v>
       </c>
     </row>
-    <row r="322" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:11">
       <c r="A322" s="15">
         <v>41129</v>
       </c>
@@ -26779,7 +26810,7 @@
         <v>39.420666681528402</v>
       </c>
     </row>
-    <row r="323" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:11">
       <c r="A323" s="15">
         <v>41136</v>
       </c>
@@ -26830,7 +26861,7 @@
         <v>42.597308792434582</v>
       </c>
     </row>
-    <row r="324" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:11">
       <c r="A324" s="15">
         <v>41143</v>
       </c>
@@ -26866,7 +26897,7 @@
         <v>59.566739758018073</v>
       </c>
     </row>
-    <row r="325" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:11">
       <c r="A325" s="15">
         <v>41150</v>
       </c>
@@ -26902,7 +26933,7 @@
         <v>40.667483971490398</v>
       </c>
     </row>
-    <row r="326" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:11">
       <c r="A326" s="15">
         <v>41157</v>
       </c>
@@ -26938,7 +26969,7 @@
         <v>50.154861297471179</v>
       </c>
     </row>
-    <row r="327" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:11">
       <c r="A327" s="15">
         <v>41164</v>
       </c>
@@ -26974,7 +27005,7 @@
         <v>50.124976846592538</v>
       </c>
     </row>
-    <row r="328" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:11">
       <c r="A328" s="15">
         <v>41171</v>
       </c>
@@ -27010,7 +27041,7 @@
         <v>52.943578895895669</v>
       </c>
     </row>
-    <row r="329" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:11">
       <c r="A329" s="15">
         <v>41178</v>
       </c>
@@ -27046,7 +27077,7 @@
         <v>56.021511245433409</v>
       </c>
     </row>
-    <row r="330" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:11">
       <c r="A330" s="15">
         <v>41185</v>
       </c>
@@ -27082,7 +27113,7 @@
         <v>57.266397751374981</v>
       </c>
     </row>
-    <row r="331" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:11">
       <c r="A331" s="15">
         <v>41192</v>
       </c>
@@ -27118,7 +27149,7 @@
         <v>66.483484497561491</v>
       </c>
     </row>
-    <row r="332" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:11">
       <c r="A332" s="15">
         <v>41199</v>
       </c>
@@ -27154,7 +27185,7 @@
         <v>71.777760309165402</v>
       </c>
     </row>
-    <row r="333" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:11">
       <c r="A333" s="15">
         <v>41206</v>
       </c>
@@ -27190,7 +27221,7 @@
         <v>59.778361750310793</v>
       </c>
     </row>
-    <row r="334" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:11">
       <c r="A334" s="15">
         <v>41213</v>
       </c>
@@ -27226,7 +27257,7 @@
         <v>59.216704581992914</v>
       </c>
     </row>
-    <row r="335" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:11">
       <c r="A335" s="15">
         <v>41220</v>
       </c>
@@ -27262,7 +27293,7 @@
         <v>57.538374466714032</v>
       </c>
     </row>
-    <row r="336" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:11">
       <c r="A336" s="15">
         <v>41227</v>
       </c>
@@ -27298,7 +27329,7 @@
         <v>64.794060427377659</v>
       </c>
     </row>
-    <row r="337" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:11">
       <c r="A337" s="15">
         <v>41234</v>
       </c>
@@ -27334,7 +27365,7 @@
         <v>42.978585224257763</v>
       </c>
     </row>
-    <row r="338" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:11">
       <c r="A338" s="15">
         <v>41241</v>
       </c>
@@ -27370,7 +27401,7 @@
         <v>58.262610437726366</v>
       </c>
     </row>
-    <row r="339" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:11">
       <c r="A339" s="15">
         <v>41248</v>
       </c>
@@ -27406,7 +27437,7 @@
         <v>53.947354080111261</v>
       </c>
     </row>
-    <row r="340" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:11">
       <c r="A340" s="15">
         <v>41255</v>
       </c>
@@ -27442,7 +27473,7 @@
         <v>40.867278029986856</v>
       </c>
     </row>
-    <row r="341" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:11">
       <c r="A341" s="15">
         <v>41262</v>
       </c>
@@ -27478,7 +27509,7 @@
         <v>49.812955030683419</v>
       </c>
     </row>
-    <row r="342" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:11">
       <c r="A342" s="15">
         <v>41269</v>
       </c>
@@ -27514,7 +27545,7 @@
         <v>44.510630134900872</v>
       </c>
     </row>
-    <row r="343" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:11">
       <c r="A343" s="15">
         <v>41276</v>
       </c>
@@ -27550,7 +27581,7 @@
         <v>53.24693033779436</v>
       </c>
     </row>
-    <row r="344" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:11">
       <c r="A344" s="15">
         <v>41283</v>
       </c>
@@ -27586,7 +27617,7 @@
         <v>43.585114686349307</v>
       </c>
     </row>
-    <row r="345" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:11">
       <c r="A345" s="15">
         <v>41290</v>
       </c>
@@ -27622,7 +27653,7 @@
         <v>60.84780147014353</v>
       </c>
     </row>
-    <row r="346" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:11">
       <c r="A346" s="15">
         <v>41297</v>
       </c>
@@ -27658,7 +27689,7 @@
         <v>53.953140270861297</v>
       </c>
     </row>
-    <row r="347" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:11">
       <c r="A347" s="15">
         <v>41304</v>
       </c>
@@ -27694,7 +27725,7 @@
         <v>32.239533185206014</v>
       </c>
     </row>
-    <row r="348" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:11">
       <c r="A348" s="15">
         <v>41311</v>
       </c>
@@ -27730,7 +27761,7 @@
         <v>40.084712867791588</v>
       </c>
     </row>
-    <row r="349" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:11">
       <c r="A349" s="15">
         <v>41318</v>
       </c>
@@ -27766,7 +27797,7 @@
         <v>38.38710256166938</v>
       </c>
     </row>
-    <row r="350" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:11">
       <c r="A350" s="15">
         <v>41325</v>
       </c>
@@ -27802,7 +27833,7 @@
         <v>38.080293444545788</v>
       </c>
     </row>
-    <row r="351" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:11">
       <c r="A351" s="15">
         <v>41332</v>
       </c>
@@ -27838,7 +27869,7 @@
         <v>48.402767285139547</v>
       </c>
     </row>
-    <row r="352" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:11">
       <c r="A352" s="15">
         <v>41339</v>
       </c>
@@ -27874,7 +27905,7 @@
         <v>40.094000618700669</v>
       </c>
     </row>
-    <row r="353" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:11">
       <c r="A353" s="15">
         <v>41346</v>
       </c>
@@ -27910,7 +27941,7 @@
         <v>42.821783159517786</v>
       </c>
     </row>
-    <row r="354" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:11">
       <c r="A354" s="15">
         <v>41353</v>
       </c>
@@ -27946,7 +27977,7 @@
         <v>32.607118719705234</v>
       </c>
     </row>
-    <row r="355" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:11">
       <c r="A355" s="15">
         <v>41360</v>
       </c>
@@ -27982,7 +28013,7 @@
         <v>40.659143503192773</v>
       </c>
     </row>
-    <row r="356" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:11">
       <c r="A356" s="15">
         <v>41367</v>
       </c>
@@ -28018,7 +28049,7 @@
         <v>61.567550890600387</v>
       </c>
     </row>
-    <row r="357" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:11">
       <c r="A357" s="15">
         <v>41374</v>
       </c>
@@ -28054,7 +28085,7 @@
         <v>52.116557963159231</v>
       </c>
     </row>
-    <row r="358" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:11">
       <c r="A358" s="15">
         <v>41381</v>
       </c>
@@ -28090,7 +28121,7 @@
         <v>53.354057268656028</v>
       </c>
     </row>
-    <row r="359" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:11">
       <c r="A359" s="15">
         <v>41388</v>
       </c>
@@ -28126,7 +28157,7 @@
         <v>58.802213497238505</v>
       </c>
     </row>
-    <row r="360" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:11">
       <c r="A360" s="15">
         <v>41395</v>
       </c>
@@ -28162,7 +28193,7 @@
         <v>37.937705662389739</v>
       </c>
     </row>
-    <row r="361" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:11">
       <c r="A361" s="15">
         <v>41402</v>
       </c>
@@ -28198,7 +28229,7 @@
         <v>54.929642662956802</v>
       </c>
     </row>
-    <row r="362" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:11">
       <c r="A362" s="15">
         <v>41409</v>
       </c>
@@ -28234,7 +28265,7 @@
         <v>35.515606966366008</v>
       </c>
     </row>
-    <row r="363" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:11">
       <c r="A363" s="15">
         <v>41416</v>
       </c>
@@ -28270,7 +28301,7 @@
         <v>47.22321621646487</v>
       </c>
     </row>
-    <row r="364" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:11">
       <c r="A364" s="15">
         <v>41423</v>
       </c>
@@ -28306,7 +28337,7 @@
         <v>58.20055953610327</v>
       </c>
     </row>
-    <row r="365" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:11">
       <c r="A365" s="15">
         <v>41430</v>
       </c>
@@ -28342,7 +28373,7 @@
         <v>58.972667790307163</v>
       </c>
     </row>
-    <row r="366" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:11">
       <c r="A366" s="15">
         <v>41437</v>
       </c>
@@ -28378,7 +28409,7 @@
         <v>54.209657868522129</v>
       </c>
     </row>
-    <row r="367" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:11">
       <c r="A367" s="15">
         <v>41444</v>
       </c>
@@ -28414,7 +28445,7 @@
         <v>49.424558707629132</v>
       </c>
     </row>
-    <row r="368" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:11">
       <c r="A368" s="15">
         <v>41451</v>
       </c>
@@ -28450,7 +28481,7 @@
         <v>49.303982121743722</v>
       </c>
     </row>
-    <row r="369" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:11">
       <c r="A369" s="15">
         <v>41458</v>
       </c>
@@ -28486,7 +28517,7 @@
         <v>35.218787549159295</v>
       </c>
     </row>
-    <row r="370" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:11">
       <c r="A370" s="15">
         <v>41465</v>
       </c>
@@ -28522,7 +28553,7 @@
         <v>55.882367115793201</v>
       </c>
     </row>
-    <row r="371" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:11">
       <c r="A371" s="15">
         <v>41472</v>
       </c>
@@ -28558,7 +28589,7 @@
         <v>53.110925423170286</v>
       </c>
     </row>
-    <row r="372" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:11">
       <c r="A372" s="15">
         <v>41479</v>
       </c>
@@ -28594,7 +28625,7 @@
         <v>33.44447705914984</v>
       </c>
     </row>
-    <row r="373" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:11">
       <c r="A373" s="15">
         <v>41486</v>
       </c>
@@ -28630,7 +28661,7 @@
         <v>54.484641664282961</v>
       </c>
     </row>
-    <row r="374" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:11">
       <c r="A374" s="15">
         <v>41493</v>
       </c>
@@ -28666,7 +28697,7 @@
         <v>30.238330855873073</v>
       </c>
     </row>
-    <row r="375" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:11">
       <c r="A375" s="15">
         <v>41500</v>
       </c>
@@ -28702,7 +28733,7 @@
         <v>42.699029269899285</v>
       </c>
     </row>
-    <row r="376" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:11">
       <c r="A376" s="15">
         <v>41507</v>
       </c>
@@ -28738,7 +28769,7 @@
         <v>56.528524201883307</v>
       </c>
     </row>
-    <row r="377" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:11">
       <c r="A377" s="15">
         <v>41514</v>
       </c>
@@ -28774,7 +28805,7 @@
         <v>45.736639980287038</v>
       </c>
     </row>
-    <row r="378" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:11">
       <c r="A378" s="15">
         <v>41521</v>
       </c>
@@ -28810,7 +28841,7 @@
         <v>44.32004194458554</v>
       </c>
     </row>
-    <row r="379" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:11">
       <c r="A379" s="15">
         <v>41528</v>
       </c>
@@ -28846,7 +28877,7 @@
         <v>31.097341411399512</v>
       </c>
     </row>
-    <row r="380" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:11">
       <c r="A380" s="15">
         <v>41535</v>
       </c>
@@ -28882,7 +28913,7 @@
         <v>32.054779929422871</v>
       </c>
     </row>
-    <row r="381" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:11">
       <c r="A381" s="15">
         <v>41542</v>
       </c>
@@ -28918,7 +28949,7 @@
         <v>48.279990820009985</v>
       </c>
     </row>
-    <row r="382" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:11">
       <c r="A382" s="15">
         <v>41549</v>
       </c>
@@ -28954,7 +28985,7 @@
         <v>55.268275006754301</v>
       </c>
     </row>
-    <row r="383" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:11">
       <c r="A383" s="15">
         <v>41556</v>
       </c>
@@ -28990,7 +29021,7 @@
         <v>64.648358122534788</v>
       </c>
     </row>
-    <row r="384" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:11">
       <c r="A384" s="15">
         <v>41563</v>
       </c>
@@ -29026,7 +29057,7 @@
         <v>30.40107245824677</v>
       </c>
     </row>
-    <row r="385" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:11">
       <c r="A385" s="15">
         <v>41570</v>
       </c>
@@ -29062,7 +29093,7 @@
         <v>46.050815851660722</v>
       </c>
     </row>
-    <row r="386" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:11">
       <c r="A386" s="15">
         <v>41577</v>
       </c>
@@ -29098,7 +29129,7 @@
         <v>29.663869105622428</v>
       </c>
     </row>
-    <row r="387" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:11">
       <c r="A387" s="15">
         <v>41584</v>
       </c>
@@ -29149,7 +29180,7 @@
         <v>29.763192589775961</v>
       </c>
     </row>
-    <row r="388" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:11">
       <c r="A388" s="15">
         <v>41591</v>
       </c>
@@ -29185,7 +29216,7 @@
         <v>53.718056830358535</v>
       </c>
     </row>
-    <row r="389" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:11">
       <c r="A389" s="15">
         <v>41598</v>
       </c>
@@ -29221,7 +29252,7 @@
         <v>47.320660371123139</v>
       </c>
     </row>
-    <row r="390" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:11">
       <c r="A390" s="15">
         <v>41605</v>
       </c>
@@ -29257,7 +29288,7 @@
         <v>26.84883647436958</v>
       </c>
     </row>
-    <row r="391" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:11">
       <c r="A391" s="15">
         <v>41612</v>
       </c>
@@ -29293,7 +29324,7 @@
         <v>30.228012575603316</v>
       </c>
     </row>
-    <row r="392" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:11">
       <c r="A392" s="15">
         <v>41619</v>
       </c>
@@ -29329,7 +29360,7 @@
         <v>35.628299402813028</v>
       </c>
     </row>
-    <row r="393" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:11">
       <c r="A393" s="15">
         <v>41626</v>
       </c>
@@ -29365,7 +29396,7 @@
         <v>29.564716897124189</v>
       </c>
     </row>
-    <row r="394" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:11">
       <c r="A394" s="15">
         <v>41634</v>
       </c>
@@ -29401,7 +29432,7 @@
         <v>25.48504766173663</v>
       </c>
     </row>
-    <row r="395" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:11">
       <c r="A395" s="15">
         <v>41641</v>
       </c>
@@ -29437,7 +29468,7 @@
         <v>29.440463564644233</v>
       </c>
     </row>
-    <row r="396" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:11">
       <c r="A396" s="15">
         <v>41647</v>
       </c>
@@ -29473,7 +29504,7 @@
         <v>36.868005424758209</v>
       </c>
     </row>
-    <row r="397" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:11">
       <c r="A397" s="15">
         <v>41654</v>
       </c>
@@ -29509,7 +29540,7 @@
         <v>33.543405654015224</v>
       </c>
     </row>
-    <row r="398" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:11">
       <c r="A398" s="15">
         <v>41661</v>
       </c>
@@ -29545,7 +29576,7 @@
         <v>33.281205492789098</v>
       </c>
     </row>
-    <row r="399" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:11">
       <c r="A399" s="15">
         <v>41668</v>
       </c>
@@ -29581,7 +29612,7 @@
         <v>48.6755678567065</v>
       </c>
     </row>
-    <row r="400" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:11">
       <c r="A400" s="15">
         <v>41675</v>
       </c>
@@ -29617,7 +29648,7 @@
         <v>48.899855436252473</v>
       </c>
     </row>
-    <row r="401" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:11">
       <c r="A401" s="15">
         <v>41682</v>
       </c>
@@ -29653,7 +29684,7 @@
         <v>50.456539714887306</v>
       </c>
     </row>
-    <row r="402" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:11">
       <c r="A402" s="15">
         <v>41689</v>
       </c>
@@ -29689,7 +29720,7 @@
         <v>53.893528968558918</v>
       </c>
     </row>
-    <row r="403" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:11">
       <c r="A403" s="15">
         <v>41696</v>
       </c>
@@ -29725,7 +29756,7 @@
         <v>32.173253175865931</v>
       </c>
     </row>
-    <row r="404" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:11">
       <c r="A404" s="15">
         <v>41703</v>
       </c>
@@ -29761,7 +29792,7 @@
         <v>28.177917475995674</v>
       </c>
     </row>
-    <row r="405" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:11">
       <c r="A405" s="15">
         <v>41710</v>
       </c>
@@ -29797,7 +29828,7 @@
         <v>38.591960706244812</v>
       </c>
     </row>
-    <row r="406" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:11">
       <c r="A406" s="15">
         <v>41716</v>
       </c>
@@ -29833,7 +29864,7 @@
         <v>62.434033436115925</v>
       </c>
     </row>
-    <row r="407" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:11">
       <c r="A407" s="15">
         <v>41717</v>
       </c>
@@ -29869,7 +29900,7 @@
         <v>38.474239554033893</v>
       </c>
     </row>
-    <row r="408" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:11">
       <c r="A408" s="15">
         <v>41724</v>
       </c>
@@ -29905,7 +29936,7 @@
         <v>30.022064656219442</v>
       </c>
     </row>
-    <row r="409" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:11">
       <c r="A409" s="15">
         <v>41731</v>
       </c>
@@ -29941,7 +29972,7 @@
         <v>44.188138476313277</v>
       </c>
     </row>
-    <row r="410" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:11">
       <c r="A410" s="15">
         <v>41738</v>
       </c>
@@ -29977,7 +30008,7 @@
         <v>31.323363729632899</v>
       </c>
     </row>
-    <row r="411" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:11">
       <c r="A411" s="15">
         <v>41745</v>
       </c>
@@ -30013,7 +30044,7 @@
         <v>35.606324792337006</v>
       </c>
     </row>
-    <row r="412" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:11">
       <c r="A412" s="15">
         <v>41752</v>
       </c>
@@ -30049,7 +30080,7 @@
         <v>35.382781553838939</v>
       </c>
     </row>
-    <row r="413" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:11">
       <c r="A413" s="15">
         <v>41759</v>
       </c>
@@ -30085,7 +30116,7 @@
         <v>45.803062444786249</v>
       </c>
     </row>
-    <row r="414" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:11">
       <c r="A414" s="15">
         <v>41766</v>
       </c>
@@ -30121,7 +30152,7 @@
         <v>37.395218193640751</v>
       </c>
     </row>
-    <row r="415" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:11">
       <c r="A415" s="15">
         <v>41773</v>
       </c>
@@ -30157,7 +30188,7 @@
         <v>30.364171137854051</v>
       </c>
     </row>
-    <row r="416" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:11">
       <c r="A416" s="15">
         <v>41780</v>
       </c>
@@ -30193,7 +30224,7 @@
         <v>46.926276851752007</v>
       </c>
     </row>
-    <row r="417" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:11">
       <c r="A417" s="15">
         <v>41787</v>
       </c>
@@ -30229,7 +30260,7 @@
         <v>56.381294114615542</v>
       </c>
     </row>
-    <row r="418" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:11">
       <c r="A418" s="15">
         <v>41794</v>
       </c>
@@ -30265,7 +30296,7 @@
         <v>42.349237020811792</v>
       </c>
     </row>
-    <row r="419" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:11">
       <c r="A419" s="15">
         <v>41801</v>
       </c>
@@ -30301,7 +30332,7 @@
         <v>38.373204647880215</v>
       </c>
     </row>
-    <row r="420" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:11">
       <c r="A420" s="15">
         <v>41808</v>
       </c>
@@ -30337,7 +30368,7 @@
         <v>44.314119769408713</v>
       </c>
     </row>
-    <row r="421" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:11">
       <c r="A421" s="15">
         <v>41815</v>
       </c>
@@ -30373,7 +30404,7 @@
         <v>60.45119572753616</v>
       </c>
     </row>
-    <row r="422" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:11">
       <c r="A422" s="15">
         <v>41822</v>
       </c>
@@ -30409,7 +30440,7 @@
         <v>47.49836466704955</v>
       </c>
     </row>
-    <row r="423" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:11">
       <c r="A423" s="15">
         <v>41829</v>
       </c>
@@ -30445,7 +30476,7 @@
         <v>35.064608489041966</v>
       </c>
     </row>
-    <row r="424" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:11">
       <c r="A424" s="15">
         <v>41836</v>
       </c>
@@ -30481,7 +30512,7 @@
         <v>44.721213423875326</v>
       </c>
     </row>
-    <row r="425" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:11">
       <c r="A425" s="15">
         <v>41843</v>
       </c>
@@ -30517,7 +30548,7 @@
         <v>39.312318980389804</v>
       </c>
     </row>
-    <row r="426" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:11">
       <c r="A426" s="15">
         <v>41850</v>
       </c>
@@ -30553,7 +30584,7 @@
         <v>34.47072790576</v>
       </c>
     </row>
-    <row r="427" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:11">
       <c r="A427" s="15">
         <v>41857</v>
       </c>
@@ -30589,7 +30620,7 @@
         <v>51.803015068152312</v>
       </c>
     </row>
-    <row r="428" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:11">
       <c r="A428" s="15">
         <v>41864</v>
       </c>
@@ -30625,7 +30656,7 @@
         <v>45.922649241726944</v>
       </c>
     </row>
-    <row r="429" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:11">
       <c r="A429" s="15">
         <v>41871</v>
       </c>
@@ -30661,7 +30692,7 @@
         <v>62.557833587887913</v>
       </c>
     </row>
-    <row r="430" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:11">
       <c r="A430" s="15">
         <v>41878</v>
       </c>
@@ -30697,7 +30728,7 @@
         <v>47.65914443041865</v>
       </c>
     </row>
-    <row r="431" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:11">
       <c r="A431" s="15">
         <v>41885</v>
       </c>
@@ -30733,7 +30764,7 @@
         <v>59.213557190072954</v>
       </c>
     </row>
-    <row r="432" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:11">
       <c r="A432" s="15">
         <v>41892</v>
       </c>
@@ -30769,7 +30800,7 @@
         <v>57.333019762644675</v>
       </c>
     </row>
-    <row r="433" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:11">
       <c r="A433" s="15">
         <v>41899</v>
       </c>
@@ -30805,7 +30836,7 @@
         <v>49.133395431991111</v>
       </c>
     </row>
-    <row r="434" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:11">
       <c r="A434" s="15">
         <v>41906</v>
       </c>
@@ -30841,7 +30872,7 @@
         <v>55.537677707137746</v>
       </c>
     </row>
-    <row r="435" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:11">
       <c r="A435" s="15">
         <v>41913</v>
       </c>
@@ -30877,7 +30908,7 @@
         <v>66.806525599248758</v>
       </c>
     </row>
-    <row r="436" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:11">
       <c r="A436" s="15">
         <v>41920</v>
       </c>
@@ -30913,7 +30944,7 @@
         <v>66.570355280429666</v>
       </c>
     </row>
-    <row r="437" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:11">
       <c r="A437" s="15">
         <v>41927</v>
       </c>
@@ -30949,7 +30980,7 @@
         <v>67.686973863523022</v>
       </c>
     </row>
-    <row r="438" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:11">
       <c r="A438" s="15">
         <v>41934</v>
       </c>
@@ -30985,7 +31016,7 @@
         <v>62.311923006128566</v>
       </c>
     </row>
-    <row r="439" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:11">
       <c r="A439" s="15">
         <v>41941</v>
       </c>
@@ -31021,7 +31052,7 @@
         <v>65.532799765784759</v>
       </c>
     </row>
-    <row r="440" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:11">
       <c r="A440" s="15">
         <v>41948</v>
       </c>
@@ -31057,7 +31088,7 @@
         <v>62.905619401035253</v>
       </c>
     </row>
-    <row r="441" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:11">
       <c r="A441" s="15">
         <v>41955</v>
       </c>
@@ -31093,7 +31124,7 @@
         <v>59.753766943925129</v>
       </c>
     </row>
-    <row r="442" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:11">
       <c r="A442" s="15">
         <v>41962</v>
       </c>
@@ -31129,7 +31160,7 @@
         <v>54.685208883890532</v>
       </c>
     </row>
-    <row r="443" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:11">
       <c r="A443" s="15">
         <v>41968</v>
       </c>
@@ -31165,7 +31196,7 @@
         <v>64.443637389582548</v>
       </c>
     </row>
-    <row r="444" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:11">
       <c r="A444" s="15">
         <v>41976</v>
       </c>
@@ -31201,7 +31232,7 @@
         <v>53.372403786390393</v>
       </c>
     </row>
-    <row r="445" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:11">
       <c r="A445" s="15">
         <v>41983</v>
       </c>
@@ -31237,7 +31268,7 @@
         <v>52.550400098141971</v>
       </c>
     </row>
-    <row r="446" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:11">
       <c r="A446" s="15">
         <v>41990</v>
       </c>
@@ -31273,7 +31304,7 @@
         <v>61.82397380318033</v>
       </c>
     </row>
-    <row r="447" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:11">
       <c r="A447" s="15">
         <v>41997</v>
       </c>
@@ -31309,7 +31340,7 @@
         <v>32.707053916439136</v>
       </c>
     </row>
-    <row r="448" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:11">
       <c r="A448" s="15">
         <v>42004</v>
       </c>
@@ -31345,7 +31376,7 @@
         <v>43.310807829305034</v>
       </c>
     </row>
-    <row r="449" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:11">
       <c r="A449" s="15">
         <v>42011</v>
       </c>
@@ -31381,7 +31412,7 @@
         <v>73.520753699141281</v>
       </c>
     </row>
-    <row r="450" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:11">
       <c r="A450" s="15">
         <v>42018</v>
       </c>
@@ -31417,7 +31448,7 @@
         <v>53.380532408043727</v>
       </c>
     </row>
-    <row r="451" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:11">
       <c r="A451" s="15">
         <v>42025</v>
       </c>
@@ -31468,7 +31499,7 @@
         <v>52.550400098141971</v>
       </c>
     </row>
-    <row r="452" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:11">
       <c r="A452" s="15">
         <v>42032</v>
       </c>
@@ -31504,7 +31535,7 @@
         <v>39.19736690032088</v>
       </c>
     </row>
-    <row r="453" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:11">
       <c r="A453" s="15">
         <v>42039</v>
       </c>
@@ -31540,7 +31571,7 @@
         <v>44.064003122982612</v>
       </c>
     </row>
-    <row r="454" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:11">
       <c r="A454" s="15">
         <v>42046</v>
       </c>
@@ -31576,7 +31607,7 @@
         <v>37.007673607771878</v>
       </c>
     </row>
-    <row r="455" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:11">
       <c r="A455" s="15">
         <v>42053</v>
       </c>
@@ -31612,7 +31643,7 @@
         <v>42.561466476456637</v>
       </c>
     </row>
-    <row r="456" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:11">
       <c r="A456" s="15">
         <v>42060</v>
       </c>
@@ -31648,7 +31679,7 @@
         <v>45.402755221031484</v>
       </c>
     </row>
-    <row r="457" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:11">
       <c r="A457" s="15">
         <v>42067</v>
       </c>
@@ -31684,7 +31715,7 @@
         <v>48.211272729748821</v>
       </c>
     </row>
-    <row r="458" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:11">
       <c r="A458" s="15">
         <v>42074</v>
       </c>
@@ -31720,7 +31751,7 @@
         <v>67.383421717313624</v>
       </c>
     </row>
-    <row r="459" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:11">
       <c r="A459" s="15">
         <v>42088</v>
       </c>
@@ -31756,7 +31787,7 @@
         <v>30.956834906605707</v>
       </c>
     </row>
-    <row r="460" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:11">
       <c r="A460" s="15">
         <v>42095</v>
       </c>
@@ -31792,7 +31823,7 @@
         <v>54.500081021599833</v>
       </c>
     </row>
-    <row r="461" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:11">
       <c r="A461" s="15">
         <v>42102</v>
       </c>
@@ -31828,7 +31859,7 @@
         <v>28.291363992271719</v>
       </c>
     </row>
-    <row r="462" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:11">
       <c r="A462" s="15">
         <v>42109</v>
       </c>
@@ -31864,7 +31895,7 @@
         <v>40.543750857694739</v>
       </c>
     </row>
-    <row r="463" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:11">
       <c r="A463" s="15">
         <v>42116</v>
       </c>
@@ -31900,7 +31931,7 @@
         <v>59.571201699918042</v>
       </c>
     </row>
-    <row r="464" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:11">
       <c r="A464" s="15">
         <v>42123</v>
       </c>
@@ -31936,7 +31967,7 @@
         <v>34.27313982014654</v>
       </c>
     </row>
-    <row r="465" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="465" spans="1:11">
       <c r="A465" s="15">
         <v>42130</v>
       </c>
@@ -31972,7 +32003,7 @@
         <v>56.955691995283715</v>
       </c>
     </row>
-    <row r="466" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:11">
       <c r="A466" s="15">
         <v>42137</v>
       </c>
@@ -32008,7 +32039,7 @@
         <v>54.764046582566408</v>
       </c>
     </row>
-    <row r="467" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:11">
       <c r="A467" s="15">
         <v>42144</v>
       </c>
@@ -32044,7 +32075,7 @@
         <v>55.757136500127764</v>
       </c>
     </row>
-    <row r="468" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:11">
       <c r="A468" s="15">
         <v>42151</v>
       </c>
@@ -32080,7 +32111,7 @@
         <v>59.139689894729841</v>
       </c>
     </row>
-    <row r="469" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:11">
       <c r="A469" s="15">
         <v>42158</v>
       </c>
@@ -32116,7 +32147,7 @@
         <v>58.565690013670491</v>
       </c>
     </row>
-    <row r="470" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:11">
       <c r="A470" s="15">
         <v>42165</v>
       </c>
@@ -32152,7 +32183,7 @@
         <v>58.285726582262178</v>
       </c>
     </row>
-    <row r="471" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:11">
       <c r="A471" s="15">
         <v>42172</v>
       </c>
@@ -32188,7 +32219,7 @@
         <v>51.057335391353512</v>
       </c>
     </row>
-    <row r="472" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="472" spans="1:11">
       <c r="A472" s="15">
         <v>42179</v>
       </c>
@@ -32224,7 +32255,7 @@
         <v>58.045476963818579</v>
       </c>
     </row>
-    <row r="473" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:11">
       <c r="A473" s="15">
         <v>42186</v>
       </c>
@@ -32260,7 +32291,7 @@
         <v>60.134571875867529</v>
       </c>
     </row>
-    <row r="474" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:11">
       <c r="A474" s="15">
         <v>42193</v>
       </c>
@@ -32296,7 +32327,7 @@
         <v>64.152197101026005</v>
       </c>
     </row>
-    <row r="475" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="475" spans="1:11">
       <c r="A475" s="15">
         <v>42200</v>
       </c>
@@ -32332,7 +32363,7 @@
         <v>62.876249643492336</v>
       </c>
     </row>
-    <row r="476" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="476" spans="1:11">
       <c r="A476" s="15">
         <v>42207</v>
       </c>
@@ -32368,7 +32399,7 @@
         <v>69.115289526281927</v>
       </c>
     </row>
-    <row r="477" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:11">
       <c r="A477" s="15">
         <v>42214</v>
       </c>
@@ -32404,7 +32435,7 @@
         <v>65.005582381367375</v>
       </c>
     </row>
-    <row r="478" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:11">
       <c r="A478" s="15">
         <v>42221</v>
       </c>
@@ -32440,7 +32471,7 @@
         <v>63.076909141434115</v>
       </c>
     </row>
-    <row r="479" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:11">
       <c r="A479" s="15">
         <v>42228</v>
       </c>
@@ -32476,7 +32507,7 @@
         <v>62.189535700762221</v>
       </c>
     </row>
-    <row r="480" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:11">
       <c r="A480" s="15">
         <v>42235</v>
       </c>
@@ -32512,7 +32543,7 @@
         <v>56.905421187389813</v>
       </c>
     </row>
-    <row r="481" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:11">
       <c r="A481" s="15">
         <v>42242</v>
       </c>
@@ -32548,7 +32579,7 @@
         <v>54.437212556646394</v>
       </c>
     </row>
-    <row r="482" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:11">
       <c r="A482" s="15">
         <v>42249</v>
       </c>
@@ -32584,7 +32615,7 @@
         <v>45.740626444393065</v>
       </c>
     </row>
-    <row r="483" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:11">
       <c r="A483" s="15">
         <v>42256</v>
       </c>
@@ -32620,7 +32651,7 @@
         <v>39.805313843808364</v>
       </c>
     </row>
-    <row r="484" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:11">
       <c r="A484" s="15">
         <v>42263</v>
       </c>
@@ -32656,7 +32687,7 @@
         <v>43.806543446148218</v>
       </c>
     </row>
-    <row r="485" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:11">
       <c r="A485" s="15">
         <v>42270</v>
       </c>
@@ -32692,7 +32723,7 @@
         <v>51.716685867776327</v>
       </c>
     </row>
-    <row r="486" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="486" spans="1:11">
       <c r="A486" s="15">
         <v>42277</v>
       </c>
@@ -32728,7 +32759,7 @@
         <v>58.081158609585614</v>
       </c>
     </row>
-    <row r="487" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="487" spans="1:11">
       <c r="A487" s="15">
         <v>42284</v>
       </c>
@@ -32764,7 +32795,7 @@
         <v>56.825158228391729</v>
       </c>
     </row>
-    <row r="488" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="488" spans="1:11">
       <c r="A488" s="15">
         <v>42291</v>
       </c>
@@ -32800,7 +32831,7 @@
         <v>67.174925319764782</v>
       </c>
     </row>
-    <row r="489" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:11">
       <c r="A489" s="15">
         <v>42298</v>
       </c>
@@ -32836,7 +32867,7 @@
         <v>45.345586579315764</v>
       </c>
     </row>
-    <row r="490" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="490" spans="1:11">
       <c r="A490" s="15">
         <v>42305</v>
       </c>
@@ -32872,7 +32903,7 @@
         <v>57.374167645036572</v>
       </c>
     </row>
-    <row r="491" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:11">
       <c r="A491" s="15">
         <v>42312</v>
       </c>
@@ -32908,7 +32939,7 @@
         <v>51.179056631292994</v>
       </c>
     </row>
-    <row r="492" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="492" spans="1:11">
       <c r="A492" s="15">
         <v>42319</v>
       </c>
@@ -32944,7 +32975,7 @@
         <v>53.107945174576969</v>
       </c>
     </row>
-    <row r="493" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="493" spans="1:11">
       <c r="A493" s="15">
         <v>42326</v>
       </c>
@@ -32980,7 +33011,7 @@
         <v>58.422447069085209</v>
       </c>
     </row>
-    <row r="494" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:11">
       <c r="A494" s="15">
         <v>42333</v>
       </c>
@@ -33016,7 +33047,7 @@
         <v>34.740224585926597</v>
       </c>
     </row>
-    <row r="495" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:11">
       <c r="A495" s="15">
         <v>42340</v>
       </c>
@@ -33052,7 +33083,7 @@
         <v>53.475606892716783</v>
       </c>
     </row>
-    <row r="496" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="496" spans="1:11">
       <c r="A496" s="15">
         <v>42347</v>
       </c>
@@ -33088,7 +33119,7 @@
         <v>49.782638326185712</v>
       </c>
     </row>
-    <row r="497" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="497" spans="1:11">
       <c r="A497" s="15">
         <v>42354</v>
       </c>
@@ -33124,7 +33155,7 @@
         <v>64.682794789944978</v>
       </c>
     </row>
-    <row r="498" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="498" spans="1:11">
       <c r="A498" s="15">
         <v>42361</v>
       </c>
@@ -33160,7 +33191,7 @@
         <v>58.632036840912747</v>
       </c>
     </row>
-    <row r="499" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="499" spans="1:11">
       <c r="A499" s="15">
         <v>42368</v>
       </c>
@@ -33196,7 +33227,7 @@
         <v>60.952600023373698</v>
       </c>
     </row>
-    <row r="500" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="500" spans="1:11">
       <c r="A500" s="15">
         <v>42375</v>
       </c>
@@ -33232,7 +33263,7 @@
         <v>66.58828791661989</v>
       </c>
     </row>
-    <row r="501" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="501" spans="1:11">
       <c r="A501" s="15">
         <v>42382</v>
       </c>
@@ -33268,7 +33299,7 @@
         <v>64.934642249421515</v>
       </c>
     </row>
-    <row r="502" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="502" spans="1:11">
       <c r="A502" s="15">
         <v>42396</v>
       </c>
@@ -33304,7 +33335,7 @@
         <v>41.40576650661113</v>
       </c>
     </row>
-    <row r="503" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="503" spans="1:11">
       <c r="A503" s="15">
         <v>42403</v>
       </c>
@@ -33340,7 +33371,7 @@
         <v>31.776137400465753</v>
       </c>
     </row>
-    <row r="504" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="504" spans="1:11">
       <c r="A504" s="15">
         <v>42410</v>
       </c>
@@ -33376,7 +33407,7 @@
         <v>53.128851841152972</v>
       </c>
     </row>
-    <row r="505" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="505" spans="1:11">
       <c r="A505" s="15">
         <v>42417</v>
       </c>
@@ -33412,7 +33443,7 @@
         <v>38.552772794324362</v>
       </c>
     </row>
-    <row r="506" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="506" spans="1:11">
       <c r="A506" s="15">
         <v>42424</v>
       </c>
@@ -33448,7 +33479,7 @@
         <v>57.386093846065783</v>
       </c>
     </row>
-    <row r="507" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="507" spans="1:11">
       <c r="A507" s="15">
         <v>42431</v>
       </c>
@@ -33484,7 +33515,7 @@
         <v>56.216108002049303</v>
       </c>
     </row>
-    <row r="508" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="508" spans="1:11">
       <c r="A508" s="15">
         <v>42438</v>
       </c>
@@ -33520,7 +33551,7 @@
         <v>49.345050684492676</v>
       </c>
     </row>
-    <row r="509" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="509" spans="1:11">
       <c r="A509" s="15">
         <v>42445</v>
       </c>
@@ -33556,7 +33587,7 @@
         <v>47.469934929618582</v>
       </c>
     </row>
-    <row r="510" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="510" spans="1:11">
       <c r="A510" s="15">
         <v>42452</v>
       </c>
@@ -33592,7 +33623,7 @@
         <v>55.942502690409157</v>
       </c>
     </row>
-    <row r="511" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="511" spans="1:11">
       <c r="A511" s="15">
         <v>42459</v>
       </c>
@@ -33628,7 +33659,7 @@
         <v>51.171281684204004</v>
       </c>
     </row>
-    <row r="512" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="512" spans="1:11">
       <c r="A512" s="15">
         <v>42466</v>
       </c>
@@ -33664,7 +33695,7 @@
         <v>44.987298684587493</v>
       </c>
     </row>
-    <row r="513" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="513" spans="1:11">
       <c r="A513" s="15">
         <v>42473</v>
       </c>
@@ -33700,7 +33731,7 @@
         <v>52.267754767722032</v>
       </c>
     </row>
-    <row r="514" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="514" spans="1:11">
       <c r="A514" s="15">
         <v>42480</v>
       </c>
@@ -33736,7 +33767,7 @@
         <v>59.274689783916969</v>
       </c>
     </row>
-    <row r="515" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="515" spans="1:11">
       <c r="A515" s="15">
         <v>42487</v>
       </c>
@@ -33787,7 +33818,7 @@
         <v>56.059043268503345</v>
       </c>
     </row>
-    <row r="516" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="516" spans="1:11">
       <c r="A516" s="15">
         <v>42494</v>
       </c>
@@ -33823,7 +33854,7 @@
         <v>63.557616832598796</v>
       </c>
     </row>
-    <row r="517" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="517" spans="1:11">
       <c r="A517" s="15">
         <v>42501</v>
       </c>
@@ -33859,7 +33890,7 @@
         <v>60.325228184861054</v>
       </c>
     </row>
-    <row r="518" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="518" spans="1:11">
       <c r="A518" s="15">
         <v>42508</v>
       </c>
@@ -33895,7 +33926,7 @@
         <v>66.025148795269672</v>
       </c>
     </row>
-    <row r="519" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="519" spans="1:11">
       <c r="A519" s="15">
         <v>42515</v>
       </c>
@@ -33931,7 +33962,7 @@
         <v>65.838860527469308</v>
       </c>
     </row>
-    <row r="520" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="520" spans="1:11">
       <c r="A520" s="15">
         <v>42522</v>
       </c>
@@ -33967,7 +33998,7 @@
         <v>58.204477883361697</v>
       </c>
     </row>
-    <row r="521" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="521" spans="1:11">
       <c r="A521" s="15">
         <v>42529</v>
       </c>
@@ -34003,7 +34034,7 @@
         <v>67.614110056909553</v>
       </c>
     </row>
-    <row r="522" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="522" spans="1:11">
       <c r="A522" s="15">
         <v>42536</v>
       </c>
@@ -34039,7 +34070,7 @@
         <v>74.11356391861203</v>
       </c>
     </row>
-    <row r="523" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="523" spans="1:11">
       <c r="A523" s="15">
         <v>42543</v>
       </c>
@@ -34075,7 +34106,7 @@
         <v>73.151472857827756</v>
       </c>
     </row>
-    <row r="524" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="524" spans="1:11">
       <c r="A524" s="15">
         <v>42550</v>
       </c>
@@ -34111,7 +34142,7 @@
         <v>61.145192933839347</v>
       </c>
     </row>
-    <row r="525" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="525" spans="1:11">
       <c r="A525" s="15">
         <v>42557</v>
       </c>
@@ -34147,7 +34178,7 @@
         <v>59.461294600399974</v>
       </c>
     </row>
-    <row r="526" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="526" spans="1:11">
       <c r="A526" s="15">
         <v>42564</v>
       </c>
@@ -34183,7 +34214,7 @@
         <v>55.474316952158986</v>
       </c>
     </row>
-    <row r="527" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="527" spans="1:11">
       <c r="A527" s="15">
         <v>42571</v>
       </c>
@@ -34219,7 +34250,7 @@
         <v>47.642829505911699</v>
       </c>
     </row>
-    <row r="528" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="528" spans="1:11">
       <c r="A528" s="15">
         <v>42578</v>
       </c>
@@ -34255,7 +34286,7 @@
         <v>38.757015074458316</v>
       </c>
     </row>
-    <row r="529" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="529" spans="1:11">
       <c r="A529" s="15">
         <v>42585</v>
       </c>
@@ -34291,7 +34322,7 @@
         <v>40.898792194128127</v>
       </c>
     </row>
-    <row r="530" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="530" spans="1:11">
       <c r="A530" s="15">
         <v>42592</v>
       </c>
@@ -34327,7 +34358,7 @@
         <v>44.684911157119551</v>
       </c>
     </row>
-    <row r="531" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="531" spans="1:11">
       <c r="A531" s="15">
         <v>42599</v>
       </c>
@@ -34363,7 +34394,7 @@
         <v>38.351540526685874</v>
       </c>
     </row>
-    <row r="532" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="532" spans="1:11">
       <c r="A532" s="15">
         <v>42606</v>
       </c>
@@ -34399,7 +34430,7 @@
         <v>52.845347659285657</v>
       </c>
     </row>
-    <row r="533" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="533" spans="1:11">
       <c r="A533" s="15">
         <v>42613</v>
       </c>
@@ -34435,7 +34466,7 @@
         <v>50.592178955136646</v>
       </c>
     </row>
-    <row r="534" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="534" spans="1:11">
       <c r="A534" s="15">
         <v>42620</v>
       </c>
@@ -34471,7 +34502,7 @@
         <v>45.8727017663767</v>
       </c>
     </row>
-    <row r="535" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="535" spans="1:11">
       <c r="A535" s="15">
         <v>42627</v>
       </c>
@@ -34507,7 +34538,7 @@
         <v>74.814030546861105</v>
       </c>
     </row>
-    <row r="536" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="536" spans="1:11">
       <c r="A536" s="15">
         <v>42634</v>
       </c>
@@ -34543,7 +34574,7 @@
         <v>53.632347230101267</v>
       </c>
     </row>
-    <row r="537" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="537" spans="1:11">
       <c r="A537" s="15">
         <v>42641</v>
       </c>
@@ -34579,7 +34610,7 @@
         <v>48.896571681685643</v>
       </c>
     </row>
-    <row r="538" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="538" spans="1:11">
       <c r="A538" s="15">
         <v>42648</v>
       </c>
@@ -34615,7 +34646,7 @@
         <v>61.205113840328835</v>
       </c>
     </row>
-    <row r="539" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="539" spans="1:11">
       <c r="A539" s="15">
         <v>42655</v>
       </c>
@@ -34651,7 +34682,7 @@
         <v>57.785327901705259</v>
       </c>
     </row>
-    <row r="540" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="540" spans="1:11">
       <c r="A540" s="15">
         <v>42662</v>
       </c>
@@ -34687,7 +34718,7 @@
         <v>79.940100561197539</v>
       </c>
     </row>
-    <row r="541" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="541" spans="1:11">
       <c r="A541" s="15">
         <v>42669</v>
       </c>
@@ -34723,7 +34754,7 @@
         <v>73.199803298495794</v>
       </c>
     </row>
-    <row r="542" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="542" spans="1:11">
       <c r="A542" s="15">
         <v>42676</v>
       </c>
@@ -34759,7 +34790,7 @@
         <v>81.972971493996454</v>
       </c>
     </row>
-    <row r="543" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="543" spans="1:11">
       <c r="A543" s="15">
         <v>42683</v>
       </c>
@@ -34795,7 +34826,7 @@
         <v>70.252181451028676</v>
       </c>
     </row>
-    <row r="544" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="544" spans="1:11">
       <c r="A544" s="15">
         <v>42689</v>
       </c>
@@ -34831,7 +34862,7 @@
         <v>45.034554333138182</v>
       </c>
     </row>
-    <row r="545" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="545" spans="1:11">
       <c r="A545" s="15">
         <v>42697</v>
       </c>
@@ -34867,7 +34898,7 @@
         <v>31.902622834964525</v>
       </c>
     </row>
-    <row r="546" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="546" spans="1:11">
       <c r="A546" s="15">
         <v>42704</v>
       </c>
@@ -34903,7 +34934,7 @@
         <v>33.812107442362681</v>
       </c>
     </row>
-    <row r="547" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="547" spans="1:11">
       <c r="A547" s="15">
         <v>42711</v>
       </c>
@@ -34939,7 +34970,7 @@
         <v>44.571790079241985</v>
       </c>
     </row>
-    <row r="548" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="548" spans="1:11">
       <c r="A548" s="15">
         <v>42718</v>
       </c>
@@ -34975,7 +35006,7 @@
         <v>51.225600837105361</v>
       </c>
     </row>
-    <row r="549" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="549" spans="1:11">
       <c r="A549" s="15">
         <v>42725</v>
       </c>
@@ -35011,7 +35042,7 @@
         <v>31.324298121335335</v>
       </c>
     </row>
-    <row r="550" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="550" spans="1:11">
       <c r="A550" s="15">
         <v>42732</v>
       </c>
@@ -35047,7 +35078,7 @@
         <v>40.560500686953205</v>
       </c>
     </row>
-    <row r="551" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="551" spans="1:11">
       <c r="A551" s="15">
         <v>42739</v>
       </c>
@@ -35083,7 +35114,7 @@
         <v>41.368869961849803</v>
       </c>
     </row>
-    <row r="552" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="552" spans="1:11">
       <c r="A552" s="15">
         <v>42746</v>
       </c>
@@ -35119,7 +35150,7 @@
         <v>36.188090354038536</v>
       </c>
     </row>
-    <row r="553" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="553" spans="1:11">
       <c r="A553" s="15">
         <v>42753</v>
       </c>
@@ -35155,7 +35186,7 @@
         <v>37.743249902447104</v>
       </c>
     </row>
-    <row r="554" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="554" spans="1:11">
       <c r="A554" s="15">
         <v>42760</v>
       </c>
@@ -35191,7 +35222,7 @@
         <v>38.125600177425255</v>
       </c>
     </row>
-    <row r="555" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="555" spans="1:11">
       <c r="A555" s="15">
         <v>42767</v>
       </c>
@@ -35227,7 +35258,7 @@
         <v>35.21374453775752</v>
       </c>
     </row>
-    <row r="556" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="556" spans="1:11">
       <c r="A556" s="15">
         <v>42774</v>
       </c>
@@ -35263,7 +35294,7 @@
         <v>37.200813418944776</v>
       </c>
     </row>
-    <row r="557" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="557" spans="1:11">
       <c r="A557" s="15">
         <v>42781</v>
       </c>
@@ -35299,7 +35330,7 @@
         <v>46.401461865606194</v>
       </c>
     </row>
-    <row r="558" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="558" spans="1:11">
       <c r="A558" s="15">
         <v>42788</v>
       </c>
@@ -35335,7 +35366,7 @@
         <v>47.306097125086168</v>
       </c>
     </row>
-    <row r="559" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="559" spans="1:11">
       <c r="A559" s="15">
         <v>42795</v>
       </c>
@@ -35371,7 +35402,7 @@
         <v>40.981014136054526</v>
       </c>
     </row>
-    <row r="560" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="560" spans="1:11">
       <c r="A560" s="15">
         <v>42802</v>
       </c>
@@ -35407,7 +35438,7 @@
         <v>33.994932520079296</v>
       </c>
     </row>
-    <row r="561" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="561" spans="1:11">
       <c r="A561" s="15">
         <v>42809</v>
       </c>
@@ -35443,7 +35474,7 @@
         <v>44.968363852363964</v>
       </c>
     </row>
-    <row r="562" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="562" spans="1:11">
       <c r="A562" s="15">
         <v>42816</v>
       </c>
@@ -35479,7 +35510,7 @@
         <v>49.659201917259722</v>
       </c>
     </row>
-    <row r="563" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="563" spans="1:11">
       <c r="A563" s="15">
         <v>42823</v>
       </c>
@@ -35515,7 +35546,7 @@
         <v>64.362780454268531</v>
       </c>
     </row>
-    <row r="564" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="564" spans="1:11">
       <c r="A564" s="15">
         <v>42830</v>
       </c>
@@ -35551,7 +35582,7 @@
         <v>64.776799001384475</v>
       </c>
     </row>
-    <row r="565" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="565" spans="1:11">
       <c r="A565" s="15">
         <v>42837</v>
       </c>
@@ -35587,7 +35618,7 @@
         <v>65.166932244503599</v>
       </c>
     </row>
-    <row r="566" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="566" spans="1:11">
       <c r="A566" s="15">
         <v>42844</v>
       </c>
@@ -35623,7 +35654,7 @@
         <v>59.958870200350503</v>
       </c>
     </row>
-    <row r="567" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="567" spans="1:11">
       <c r="A567" s="15">
         <v>42851</v>
       </c>
@@ -35659,7 +35690,7 @@
         <v>59.381621852968017</v>
       </c>
     </row>
-    <row r="568" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="568" spans="1:11">
       <c r="A568" s="15">
         <v>42858</v>
       </c>
@@ -35695,7 +35726,7 @@
         <v>43.61543763393874</v>
       </c>
     </row>
-    <row r="569" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="569" spans="1:11">
       <c r="A569" s="15">
         <v>42865</v>
       </c>
@@ -35731,7 +35762,7 @@
         <v>45.396879132363082</v>
       </c>
     </row>
-    <row r="570" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="570" spans="1:11">
       <c r="A570" s="15">
         <v>42872</v>
       </c>
@@ -35767,7 +35798,7 @@
         <v>57.001842496633159</v>
       </c>
     </row>
-    <row r="571" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="571" spans="1:11">
       <c r="A571" s="15">
         <v>42879</v>
       </c>
@@ -35803,7 +35834,7 @@
         <v>43.069217656771137</v>
       </c>
     </row>
-    <row r="572" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="572" spans="1:11">
       <c r="A572" s="15">
         <v>42886</v>
       </c>
@@ -35839,7 +35870,7 @@
         <v>48.392374712148168</v>
       </c>
     </row>
-    <row r="573" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="573" spans="1:11">
       <c r="A573" s="15">
         <v>42893</v>
       </c>
@@ -35875,7 +35906,7 @@
         <v>40.948483493075209</v>
       </c>
     </row>
-    <row r="574" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="574" spans="1:11">
       <c r="A574" s="15">
         <v>42900</v>
       </c>
@@ -35911,7 +35942,7 @@
         <v>37.402091766235387</v>
       </c>
     </row>
-    <row r="575" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="575" spans="1:11">
       <c r="A575" s="15">
         <v>42907</v>
       </c>
@@ -35947,7 +35978,7 @@
         <v>46.287563991280784</v>
       </c>
     </row>
-    <row r="576" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="576" spans="1:11">
       <c r="A576" s="15">
         <v>42914</v>
       </c>
@@ -35983,7 +36014,7 @@
         <v>51.63023920146022</v>
       </c>
     </row>
-    <row r="577" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="577" spans="1:11">
       <c r="A577" s="15">
         <v>42921</v>
       </c>
@@ -36019,7 +36050,7 @@
         <v>38.938715947404972</v>
       </c>
     </row>
-    <row r="578" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="578" spans="1:11">
       <c r="A578" s="15">
         <v>42928</v>
       </c>
@@ -36055,7 +36086,7 @@
         <v>32.992166958557021</v>
       </c>
     </row>
-    <row r="579" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="579" spans="1:11">
       <c r="A579" s="15">
         <v>42935</v>
       </c>
@@ -36106,7 +36137,7 @@
         <v>41.819650581896475</v>
       </c>
     </row>
-    <row r="580" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="580" spans="1:11">
       <c r="A580" s="15">
         <v>42942</v>
       </c>
@@ -36142,7 +36173,7 @@
         <v>50.264603848036046</v>
       </c>
     </row>
-    <row r="581" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="581" spans="1:11">
       <c r="A581" s="15">
         <v>42949</v>
       </c>
@@ -36178,7 +36209,7 @@
         <v>42.982310991380189</v>
       </c>
     </row>
-    <row r="582" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="582" spans="1:11">
       <c r="A582" s="15">
         <v>42956</v>
       </c>
@@ -36214,7 +36245,7 @@
         <v>42.602862162618685</v>
       </c>
     </row>
-    <row r="583" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="583" spans="1:11">
       <c r="A583" s="15">
         <v>42963</v>
       </c>
@@ -36250,7 +36281,7 @@
         <v>35.515471002867969</v>
       </c>
     </row>
-    <row r="584" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="584" spans="1:11">
       <c r="A584" s="15">
         <v>42970</v>
       </c>
@@ -36286,7 +36317,7 @@
         <v>41.20422836194178</v>
       </c>
     </row>
-    <row r="585" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="585" spans="1:11">
       <c r="A585" s="15">
         <v>42977</v>
       </c>
@@ -36322,7 +36353,7 @@
         <v>46.305875728509086</v>
       </c>
     </row>
-    <row r="586" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="586" spans="1:11">
       <c r="A586" s="15">
         <v>42984</v>
       </c>
@@ -36358,7 +36389,7 @@
         <v>52.28157999497369</v>
       </c>
     </row>
-    <row r="587" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="587" spans="1:11">
       <c r="A587" s="15">
         <v>42991</v>
       </c>
@@ -36394,7 +36425,7 @@
         <v>45.246656707228858</v>
       </c>
     </row>
-    <row r="588" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="588" spans="1:11">
       <c r="A588" s="15">
         <v>42998</v>
       </c>
@@ -36430,7 +36461,7 @@
         <v>42.836271786367632</v>
       </c>
     </row>
-    <row r="589" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="589" spans="1:11">
       <c r="A589" s="15">
         <v>43005</v>
       </c>
@@ -36466,7 +36497,7 @@
         <v>25.850229689501795</v>
       </c>
     </row>
-    <row r="590" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="590" spans="1:11">
       <c r="A590" s="15">
         <v>43012</v>
       </c>
@@ -36502,7 +36533,7 @@
         <v>29.219171788399478</v>
       </c>
     </row>
-    <row r="591" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="591" spans="1:11">
       <c r="A591" s="15">
         <v>43019</v>
       </c>
@@ -36538,7 +36569,7 @@
         <v>47.697764295090394</v>
       </c>
     </row>
-    <row r="592" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="592" spans="1:11">
       <c r="A592" s="15">
         <v>43026</v>
       </c>
@@ -36574,7 +36605,7 @@
         <v>38.422382980352594</v>
       </c>
     </row>
-    <row r="593" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="593" spans="1:11">
       <c r="A593" s="15">
         <v>43033</v>
       </c>
@@ -36610,7 +36641,7 @@
         <v>64.258296622360419</v>
       </c>
     </row>
-    <row r="594" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="594" spans="1:11">
       <c r="A594" s="15">
         <v>43040</v>
       </c>
@@ -36646,7 +36677,7 @@
         <v>57.905260906954553</v>
       </c>
     </row>
-    <row r="595" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="595" spans="1:11">
       <c r="A595" s="15">
         <v>43047</v>
       </c>
@@ -36682,7 +36713,7 @@
         <v>34.736286502733705</v>
       </c>
     </row>
-    <row r="596" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="596" spans="1:11">
       <c r="A596" s="15">
         <v>43054</v>
       </c>
@@ -36718,7 +36749,7 @@
         <v>68.592291112048443</v>
       </c>
     </row>
-    <row r="597" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="597" spans="1:11">
       <c r="A597" s="15">
         <v>43061</v>
       </c>
@@ -36754,7 +36785,7 @@
         <v>27.3096898737011</v>
       </c>
     </row>
-    <row r="598" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="598" spans="1:11">
       <c r="A598" s="15">
         <v>43068</v>
       </c>
@@ -36790,7 +36821,7 @@
         <v>47.380261477684584</v>
       </c>
     </row>
-    <row r="599" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="599" spans="1:11">
       <c r="A599" s="15">
         <v>43075</v>
       </c>
@@ -36826,7 +36857,7 @@
         <v>48.440037392978304</v>
       </c>
     </row>
-    <row r="600" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="600" spans="1:11">
       <c r="A600" s="15">
         <v>43082</v>
       </c>
@@ -36862,7 +36893,7 @@
         <v>44.562343622567724</v>
       </c>
     </row>
-    <row r="601" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="601" spans="1:11">
       <c r="A601" s="15">
         <v>43089</v>
       </c>
@@ -36898,7 +36929,7 @@
         <v>36.623281382599032</v>
       </c>
     </row>
-    <row r="602" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="602" spans="1:11">
       <c r="A602" s="15">
         <v>43096</v>
       </c>
@@ -36934,7 +36965,7 @@
         <v>34.643577434597006</v>
       </c>
     </row>
-    <row r="603" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="603" spans="1:11">
       <c r="A603" s="15">
         <v>43103</v>
       </c>
@@ -36970,7 +37001,7 @@
         <v>25.360655270394762</v>
       </c>
     </row>
-    <row r="604" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="604" spans="1:11">
       <c r="A604" s="15">
         <v>43110</v>
       </c>
@@ -37006,7 +37037,7 @@
         <v>25.396638870684793</v>
       </c>
     </row>
-    <row r="605" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="605" spans="1:11">
       <c r="A605" s="15">
         <v>43117</v>
       </c>
@@ -37042,7 +37073,7 @@
         <v>27.71</v>
       </c>
     </row>
-    <row r="606" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="606" spans="1:11">
       <c r="A606" s="15">
         <v>43124</v>
       </c>
@@ -37078,7 +37109,7 @@
         <v>29.33</v>
       </c>
     </row>
-    <row r="607" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="607" spans="1:11">
       <c r="A607" s="15">
         <v>43131</v>
       </c>
@@ -37114,7 +37145,7 @@
         <v>53.07</v>
       </c>
     </row>
-    <row r="608" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="608" spans="1:11">
       <c r="A608" s="15">
         <v>43138</v>
       </c>
@@ -37150,7 +37181,7 @@
         <v>44.02</v>
       </c>
     </row>
-    <row r="609" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="609" spans="1:11">
       <c r="A609" s="15">
         <v>43145</v>
       </c>
@@ -37186,7 +37217,7 @@
         <v>55.52</v>
       </c>
     </row>
-    <row r="610" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="610" spans="1:11">
       <c r="A610" s="15">
         <v>43152</v>
       </c>
@@ -37222,7 +37253,7 @@
         <v>50.17</v>
       </c>
     </row>
-    <row r="611" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="611" spans="1:11">
       <c r="A611" s="15">
         <v>43159</v>
       </c>
@@ -37258,7 +37289,7 @@
         <v>34.54</v>
       </c>
     </row>
-    <row r="612" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="612" spans="1:11">
       <c r="A612" s="15">
         <v>43166</v>
       </c>
@@ -37294,7 +37325,7 @@
         <v>53.35</v>
       </c>
     </row>
-    <row r="613" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="613" spans="1:11">
       <c r="A613" s="15">
         <v>43173</v>
       </c>
@@ -37330,7 +37361,7 @@
         <v>34.69</v>
       </c>
     </row>
-    <row r="614" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="614" spans="1:11">
       <c r="A614" s="15">
         <v>43180</v>
       </c>
@@ -37366,7 +37397,7 @@
         <v>50.12</v>
       </c>
     </row>
-    <row r="615" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="615" spans="1:11">
       <c r="A615" s="15">
         <v>43187</v>
       </c>
@@ -37402,7 +37433,7 @@
         <v>66.569999999999993</v>
       </c>
     </row>
-    <row r="616" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="616" spans="1:11">
       <c r="A616" s="15">
         <v>43194</v>
       </c>
@@ -37438,7 +37469,7 @@
         <v>58.83</v>
       </c>
     </row>
-    <row r="617" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="617" spans="1:11">
       <c r="A617" s="15">
         <v>43201</v>
       </c>
@@ -37474,7 +37505,7 @@
         <v>48.61</v>
       </c>
     </row>
-    <row r="618" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="618" spans="1:11">
       <c r="A618" s="15">
         <v>43208</v>
       </c>
@@ -37510,7 +37541,7 @@
         <v>38.979999999999997</v>
       </c>
     </row>
-    <row r="619" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="619" spans="1:11">
       <c r="A619" s="15">
         <v>43215</v>
       </c>
@@ -37546,7 +37577,7 @@
         <v>63.14</v>
       </c>
     </row>
-    <row r="620" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="620" spans="1:11">
       <c r="A620" s="15">
         <v>43222</v>
       </c>
@@ -37582,7 +37613,7 @@
         <v>68.150000000000006</v>
       </c>
     </row>
-    <row r="621" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="621" spans="1:11">
       <c r="A621" s="15">
         <v>43229</v>
       </c>
@@ -37618,7 +37649,7 @@
         <v>39.549999999999997</v>
       </c>
     </row>
-    <row r="622" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="622" spans="1:11">
       <c r="A622" s="15">
         <v>43236</v>
       </c>
@@ -37654,7 +37685,7 @@
         <v>54.33</v>
       </c>
     </row>
-    <row r="623" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="623" spans="1:11">
       <c r="A623" s="15">
         <v>43243</v>
       </c>
@@ -37690,7 +37721,7 @@
         <v>53.99</v>
       </c>
     </row>
-    <row r="624" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="624" spans="1:11">
       <c r="A624" s="15">
         <v>43250</v>
       </c>
@@ -37726,7 +37757,7 @@
         <v>39.76</v>
       </c>
     </row>
-    <row r="625" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="625" spans="1:11">
       <c r="A625" s="15">
         <v>43257</v>
       </c>
@@ -37762,7 +37793,7 @@
         <v>34.51</v>
       </c>
     </row>
-    <row r="626" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="626" spans="1:11">
       <c r="A626" s="15">
         <v>43264</v>
       </c>
@@ -37798,7 +37829,7 @@
         <v>41.63</v>
       </c>
     </row>
-    <row r="627" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="627" spans="1:11">
       <c r="A627" s="15">
         <v>43271</v>
       </c>
@@ -37834,7 +37865,7 @@
         <v>34.5</v>
       </c>
     </row>
-    <row r="628" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="628" spans="1:11">
       <c r="A628" s="15">
         <v>43278</v>
       </c>
@@ -37870,7 +37901,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="629" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="629" spans="1:11">
       <c r="A629" s="15">
         <v>43285</v>
       </c>
@@ -37906,7 +37937,7 @@
         <v>46.74</v>
       </c>
     </row>
-    <row r="630" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="630" spans="1:11">
       <c r="A630" s="15">
         <v>43292</v>
       </c>
@@ -37942,7 +37973,7 @@
         <v>38.47</v>
       </c>
     </row>
-    <row r="631" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="631" spans="1:11">
       <c r="A631" s="15">
         <v>43299</v>
       </c>
@@ -37978,7 +38009,7 @@
         <v>38.82</v>
       </c>
     </row>
-    <row r="632" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="632" spans="1:11">
       <c r="A632" s="15">
         <v>43306</v>
       </c>
@@ -38014,7 +38045,7 @@
         <v>39.159999999999997</v>
       </c>
     </row>
-    <row r="633" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="633" spans="1:11">
       <c r="A633" s="15">
         <v>43313</v>
       </c>
@@ -38050,7 +38081,7 @@
         <v>40.450000000000003</v>
       </c>
     </row>
-    <row r="634" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="634" spans="1:11">
       <c r="A634" s="15">
         <v>43320</v>
       </c>
@@ -38086,7 +38117,7 @@
         <v>32.78</v>
       </c>
     </row>
-    <row r="635" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="635" spans="1:11">
       <c r="A635" s="15">
         <v>43327</v>
       </c>
@@ -38122,7 +38153,7 @@
         <v>38.94</v>
       </c>
     </row>
-    <row r="636" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="636" spans="1:11">
       <c r="A636" s="15">
         <v>43334</v>
       </c>
@@ -38158,7 +38189,7 @@
         <v>31.73</v>
       </c>
     </row>
-    <row r="637" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="637" spans="1:11">
       <c r="A637" s="15">
         <v>43341</v>
       </c>
@@ -38194,7 +38225,7 @@
         <v>38.53</v>
       </c>
     </row>
-    <row r="638" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="638" spans="1:11">
       <c r="A638" s="15">
         <v>43348</v>
       </c>
@@ -38230,7 +38261,7 @@
         <v>43.57</v>
       </c>
     </row>
-    <row r="639" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="639" spans="1:11">
       <c r="A639" s="15">
         <v>43355</v>
       </c>
@@ -38266,7 +38297,7 @@
         <v>37.619999999999997</v>
       </c>
     </row>
-    <row r="640" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="640" spans="1:11">
       <c r="A640" s="15">
         <v>43362</v>
       </c>
@@ -38302,7 +38333,7 @@
         <v>38.020000000000003</v>
       </c>
     </row>
-    <row r="641" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="641" spans="1:11">
       <c r="A641" s="15">
         <v>43369</v>
       </c>
@@ -38338,7 +38369,7 @@
         <v>44.58</v>
       </c>
     </row>
-    <row r="642" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="642" spans="1:11">
       <c r="A642" s="15">
         <v>43376</v>
       </c>
@@ -38374,7 +38405,7 @@
         <v>43.37</v>
       </c>
     </row>
-    <row r="643" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="643" spans="1:11">
       <c r="A643" s="15">
         <v>43383</v>
       </c>
@@ -38425,7 +38456,7 @@
         <v>64.94</v>
       </c>
     </row>
-    <row r="644" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="644" spans="1:11">
       <c r="A644" s="15">
         <v>43391</v>
       </c>
@@ -38461,7 +38492,7 @@
         <v>45.19</v>
       </c>
     </row>
-    <row r="645" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="645" spans="1:11">
       <c r="A645" s="15">
         <v>43397</v>
       </c>
@@ -38497,7 +38528,7 @@
         <v>72.86</v>
       </c>
     </row>
-    <row r="646" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="646" spans="1:11">
       <c r="A646" s="15">
         <v>43404</v>
       </c>
@@ -38533,7 +38564,7 @@
         <v>38.96</v>
       </c>
     </row>
-    <row r="647" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="647" spans="1:11">
       <c r="A647" s="15">
         <v>43411</v>
       </c>
@@ -38569,7 +38600,7 @@
         <v>33.590000000000003</v>
       </c>
     </row>
-    <row r="648" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="648" spans="1:11">
       <c r="A648" s="15">
         <v>43418</v>
       </c>
@@ -38605,7 +38636,7 @@
         <v>48.37</v>
       </c>
     </row>
-    <row r="649" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="649" spans="1:11">
       <c r="A649" s="15">
         <v>43425</v>
       </c>
@@ -38641,7 +38672,7 @@
         <v>73.89</v>
       </c>
     </row>
-    <row r="650" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="650" spans="1:11">
       <c r="A650" s="15">
         <v>43432</v>
       </c>
@@ -38677,7 +38708,7 @@
         <v>39.99</v>
       </c>
     </row>
-    <row r="651" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="651" spans="1:11">
       <c r="A651" s="15">
         <v>43439</v>
       </c>
@@ -38713,7 +38744,7 @@
         <v>61.26</v>
       </c>
     </row>
-    <row r="652" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="652" spans="1:11">
       <c r="A652" s="15">
         <v>43446</v>
       </c>
@@ -38749,7 +38780,7 @@
         <v>50.14</v>
       </c>
     </row>
-    <row r="653" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="653" spans="1:11">
       <c r="A653" s="15">
         <v>43453</v>
       </c>
@@ -38785,7 +38816,7 @@
         <v>63.86</v>
       </c>
     </row>
-    <row r="654" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="654" spans="1:11">
       <c r="A654" s="15">
         <v>43460</v>
       </c>
@@ -38821,7 +38852,7 @@
         <v>50.7</v>
       </c>
     </row>
-    <row r="655" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="655" spans="1:11">
       <c r="A655" s="15">
         <v>43467</v>
       </c>
@@ -38857,7 +38888,7 @@
         <v>53.3</v>
       </c>
     </row>
-    <row r="656" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="656" spans="1:11">
       <c r="A656" s="15">
         <v>43474</v>
       </c>
@@ -38893,7 +38924,7 @@
         <v>60.63</v>
       </c>
     </row>
-    <row r="657" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="657" spans="1:11">
       <c r="A657" s="15">
         <v>43481</v>
       </c>
@@ -38929,7 +38960,7 @@
         <v>51.01</v>
       </c>
     </row>
-    <row r="658" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="658" spans="1:11">
       <c r="A658" s="15">
         <v>43488</v>
       </c>
@@ -38965,7 +38996,7 @@
         <v>45.67</v>
       </c>
     </row>
-    <row r="659" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="659" spans="1:11">
       <c r="A659" s="15">
         <v>43495</v>
       </c>
@@ -39001,7 +39032,7 @@
         <v>46.03</v>
       </c>
     </row>
-    <row r="660" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="660" spans="1:11">
       <c r="A660" s="15">
         <v>43502</v>
       </c>
@@ -39037,7 +39068,7 @@
         <v>42.17</v>
       </c>
     </row>
-    <row r="661" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="661" spans="1:11">
       <c r="A661" s="15">
         <v>43509</v>
       </c>
@@ -39073,7 +39104,7 @@
         <v>40.51</v>
       </c>
     </row>
-    <row r="662" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="662" spans="1:11">
       <c r="A662" s="15">
         <v>43516</v>
       </c>
@@ -39109,7 +39140,7 @@
         <v>46.58</v>
       </c>
     </row>
-    <row r="663" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="663" spans="1:11">
       <c r="A663" s="15">
         <v>43523</v>
       </c>
@@ -39145,7 +39176,7 @@
         <v>48.78</v>
       </c>
     </row>
-    <row r="664" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="664" spans="1:11">
       <c r="A664" s="15">
         <v>43530</v>
       </c>
@@ -39181,7 +39212,7 @@
         <v>51.87</v>
       </c>
     </row>
-    <row r="665" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="665" spans="1:11">
       <c r="A665" s="15">
         <v>43537</v>
       </c>
@@ -39217,7 +39248,7 @@
         <v>50.84</v>
       </c>
     </row>
-    <row r="666" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="666" spans="1:11">
       <c r="A666" s="15">
         <v>43544</v>
       </c>
@@ -39253,7 +39284,7 @@
         <v>57.44</v>
       </c>
     </row>
-    <row r="667" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="667" spans="1:11">
       <c r="A667" s="15">
         <v>43551</v>
       </c>
@@ -39289,7 +39320,7 @@
         <v>58.85</v>
       </c>
     </row>
-    <row r="668" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="668" spans="1:11">
       <c r="A668" s="15">
         <v>43558</v>
       </c>
@@ -39325,7 +39356,7 @@
         <v>37.44</v>
       </c>
     </row>
-    <row r="669" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="669" spans="1:11">
       <c r="A669" s="15">
         <v>43565</v>
       </c>
@@ -39361,7 +39392,7 @@
         <v>44.35</v>
       </c>
     </row>
-    <row r="670" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="670" spans="1:11">
       <c r="A670" s="15">
         <v>43572</v>
       </c>
@@ -39397,7 +39428,7 @@
         <v>29.9</v>
       </c>
     </row>
-    <row r="671" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="671" spans="1:11">
       <c r="A671" s="15">
         <v>43579</v>
       </c>
@@ -39433,7 +39464,7 @@
         <v>38.32</v>
       </c>
     </row>
-    <row r="672" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="672" spans="1:11">
       <c r="A672" s="15">
         <v>43586</v>
       </c>
@@ -39469,7 +39500,7 @@
         <v>43.11</v>
       </c>
     </row>
-    <row r="673" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="673" spans="1:11">
       <c r="A673" s="15">
         <v>43593</v>
       </c>
@@ -39505,7 +39536,7 @@
         <v>63.69</v>
       </c>
     </row>
-    <row r="674" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="674" spans="1:11">
       <c r="A674" s="15">
         <v>43600</v>
       </c>
@@ -39541,7 +39572,7 @@
         <v>54.45</v>
       </c>
     </row>
-    <row r="675" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="675" spans="1:11">
       <c r="A675" s="15">
         <v>43607</v>
       </c>
@@ -39577,7 +39608,7 @@
         <v>38.76</v>
       </c>
     </row>
-    <row r="676" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="676" spans="1:11">
       <c r="A676" s="15">
         <v>43614</v>
       </c>
@@ -39613,7 +39644,7 @@
         <v>76.66</v>
       </c>
     </row>
-    <row r="677" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="677" spans="1:11">
       <c r="A677" s="15">
         <v>43621</v>
       </c>
@@ -39649,7 +39680,7 @@
         <v>57.55</v>
       </c>
     </row>
-    <row r="678" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="678" spans="1:11">
       <c r="A678" s="15">
         <v>43628</v>
       </c>
@@ -39685,7 +39716,7 @@
         <v>36.67</v>
       </c>
     </row>
-    <row r="679" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="679" spans="1:11">
       <c r="A679" s="15">
         <v>43635</v>
       </c>
@@ -39721,7 +39752,7 @@
         <v>25.39</v>
       </c>
     </row>
-    <row r="680" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="680" spans="1:11">
       <c r="A680" s="15">
         <v>43642</v>
       </c>
@@ -39757,7 +39788,7 @@
         <v>56.56</v>
       </c>
     </row>
-    <row r="681" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="681" spans="1:11">
       <c r="A681" s="15">
         <v>43649</v>
       </c>
@@ -39793,7 +39824,7 @@
         <v>37.46</v>
       </c>
     </row>
-    <row r="682" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="682" spans="1:11">
       <c r="A682" s="15">
         <v>43656</v>
       </c>
@@ -39829,7 +39860,7 @@
         <v>35.630000000000003</v>
       </c>
     </row>
-    <row r="683" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="683" spans="1:11">
       <c r="A683" s="15">
         <v>43663</v>
       </c>
@@ -39865,7 +39896,7 @@
         <v>53.98</v>
       </c>
     </row>
-    <row r="684" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="684" spans="1:11">
       <c r="A684" s="15">
         <v>43670</v>
       </c>
@@ -39901,7 +39932,7 @@
         <v>37.93</v>
       </c>
     </row>
-    <row r="685" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="685" spans="1:11">
       <c r="A685" s="15">
         <v>43677</v>
       </c>
@@ -39937,7 +39968,7 @@
         <v>41.31</v>
       </c>
     </row>
-    <row r="686" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="686" spans="1:11">
       <c r="A686" s="15">
         <v>43684</v>
       </c>
@@ -39973,7 +40004,7 @@
         <v>61.58</v>
       </c>
     </row>
-    <row r="687" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="687" spans="1:11">
       <c r="A687" s="15">
         <v>43691</v>
       </c>
@@ -40009,7 +40040,7 @@
         <v>49.29</v>
       </c>
     </row>
-    <row r="688" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="688" spans="1:11">
       <c r="A688" s="15">
         <v>43698</v>
       </c>
@@ -40045,7 +40076,7 @@
         <v>60.34</v>
       </c>
     </row>
-    <row r="689" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="689" spans="1:11">
       <c r="A689" s="15">
         <v>43705</v>
       </c>
@@ -40081,7 +40112,7 @@
         <v>66.010000000000005</v>
       </c>
     </row>
-    <row r="690" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="690" spans="1:11">
       <c r="A690" s="15">
         <v>43712</v>
       </c>
@@ -40117,7 +40148,7 @@
         <v>53.29</v>
       </c>
     </row>
-    <row r="691" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="691" spans="1:11">
       <c r="A691" s="15">
         <v>43719</v>
       </c>
@@ -40153,7 +40184,7 @@
         <v>58.2</v>
       </c>
     </row>
-    <row r="692" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="692" spans="1:11">
       <c r="A692" s="15">
         <v>43726</v>
       </c>
@@ -40189,7 +40220,7 @@
         <v>62.04</v>
       </c>
     </row>
-    <row r="693" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="693" spans="1:11">
       <c r="A693" s="15">
         <v>43733</v>
       </c>
@@ -40225,7 +40256,7 @@
         <v>53.22</v>
       </c>
     </row>
-    <row r="694" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="694" spans="1:11">
       <c r="A694" s="15">
         <v>43740</v>
       </c>
@@ -40261,7 +40292,7 @@
         <v>78.3</v>
       </c>
     </row>
-    <row r="695" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="695" spans="1:11">
       <c r="A695" s="15">
         <v>43747</v>
       </c>
@@ -40297,7 +40328,7 @@
         <v>57.1</v>
       </c>
     </row>
-    <row r="696" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="696" spans="1:11">
       <c r="A696" s="15">
         <v>43754</v>
       </c>
@@ -40333,7 +40364,7 @@
         <v>67.400000000000006</v>
       </c>
     </row>
-    <row r="697" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="697" spans="1:11">
       <c r="A697" s="15">
         <v>43761</v>
       </c>
@@ -40369,7 +40400,7 @@
         <v>38.35</v>
       </c>
     </row>
-    <row r="698" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="698" spans="1:11">
       <c r="A698" s="15">
         <v>43768</v>
       </c>
@@ -40405,7 +40436,7 @@
         <v>39.58</v>
       </c>
     </row>
-    <row r="699" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="699" spans="1:11">
       <c r="A699" s="15">
         <v>43775</v>
       </c>
@@ -40441,7 +40472,7 @@
         <v>35.5</v>
       </c>
     </row>
-    <row r="700" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="700" spans="1:11">
       <c r="A700" s="15">
         <v>43782</v>
       </c>
@@ -40477,7 +40508,7 @@
         <v>49.68</v>
       </c>
     </row>
-    <row r="701" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="701" spans="1:11">
       <c r="A701" s="15">
         <v>43789</v>
       </c>
@@ -40513,7 +40544,7 @@
         <v>52.05</v>
       </c>
     </row>
-    <row r="702" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="702" spans="1:11">
       <c r="A702" s="15">
         <v>43796</v>
       </c>
@@ -40549,7 +40580,7 @@
         <v>41.28</v>
       </c>
     </row>
-    <row r="703" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="703" spans="1:11">
       <c r="A703" s="15">
         <v>43803</v>
       </c>
@@ -40585,7 +40616,7 @@
         <v>56.13</v>
       </c>
     </row>
-    <row r="704" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="704" spans="1:11">
       <c r="A704" s="15">
         <v>43810</v>
       </c>
@@ -40621,7 +40652,7 @@
         <v>50.69</v>
       </c>
     </row>
-    <row r="705" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="705" spans="1:11">
       <c r="A705" s="15">
         <v>43817</v>
       </c>
@@ -40657,7 +40688,7 @@
         <v>35.82</v>
       </c>
     </row>
-    <row r="706" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="706" spans="1:11">
       <c r="A706" s="15">
         <v>43824</v>
       </c>
@@ -40693,7 +40724,7 @@
         <v>29.16</v>
       </c>
     </row>
-    <row r="707" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="707" spans="1:11">
       <c r="A707" s="15">
         <v>43831</v>
       </c>
@@ -40744,7 +40775,7 @@
         <v>32.42</v>
       </c>
     </row>
-    <row r="708" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="708" spans="1:11">
       <c r="A708" s="15">
         <v>43838</v>
       </c>
@@ -40780,7 +40811,7 @@
         <v>40.659999999999997</v>
       </c>
     </row>
-    <row r="709" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="709" spans="1:11">
       <c r="A709" s="15">
         <v>43845</v>
       </c>
@@ -40816,7 +40847,7 @@
         <v>37.35</v>
       </c>
     </row>
-    <row r="710" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="710" spans="1:11">
       <c r="A710" s="15">
         <v>43852</v>
       </c>
@@ -40852,7 +40883,7 @@
         <v>21.13</v>
       </c>
     </row>
-    <row r="711" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="711" spans="1:11">
       <c r="A711" s="15">
         <v>43859</v>
       </c>
@@ -40888,7 +40919,7 @@
         <v>57.93</v>
       </c>
     </row>
-    <row r="712" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="712" spans="1:11">
       <c r="A712" s="15">
         <v>43866</v>
       </c>
@@ -40924,7 +40955,7 @@
         <v>57.84</v>
       </c>
     </row>
-    <row r="713" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="713" spans="1:11">
       <c r="A713" s="15">
         <v>43873</v>
       </c>
@@ -40960,7 +40991,7 @@
         <v>37.590000000000003</v>
       </c>
     </row>
-    <row r="714" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="714" spans="1:11">
       <c r="A714" s="15">
         <v>43880</v>
       </c>
@@ -40996,7 +41027,7 @@
         <v>35.15</v>
       </c>
     </row>
-    <row r="715" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="715" spans="1:11">
       <c r="A715" s="15">
         <v>43887</v>
       </c>
@@ -41032,7 +41063,7 @@
         <v>69.72</v>
       </c>
     </row>
-    <row r="716" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="716" spans="1:11">
       <c r="A716" s="15">
         <v>43894</v>
       </c>
@@ -41068,7 +41099,7 @@
         <v>72.709999999999994</v>
       </c>
     </row>
-    <row r="717" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="717" spans="1:11">
       <c r="A717" s="15">
         <v>43901</v>
       </c>
@@ -41104,7 +41135,7 @@
         <v>58.88</v>
       </c>
     </row>
-    <row r="718" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="718" spans="1:11">
       <c r="A718" s="15">
         <v>43908</v>
       </c>
@@ -41140,7 +41171,7 @@
         <v>42.67</v>
       </c>
     </row>
-    <row r="719" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="719" spans="1:11">
       <c r="A719" s="15">
         <v>43915</v>
       </c>
@@ -41176,7 +41207,7 @@
         <v>34.049999999999997</v>
       </c>
     </row>
-    <row r="720" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="720" spans="1:11">
       <c r="A720" s="15">
         <v>43922</v>
       </c>
@@ -41212,7 +41243,7 @@
         <v>40.64</v>
       </c>
     </row>
-    <row r="721" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="721" spans="1:11">
       <c r="A721" s="15">
         <v>43929</v>
       </c>
@@ -41248,7 +41279,7 @@
         <v>44.54</v>
       </c>
     </row>
-    <row r="722" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="722" spans="1:11">
       <c r="A722" s="15">
         <v>43936</v>
       </c>
@@ -41284,7 +41315,7 @@
         <v>56.57</v>
       </c>
     </row>
-    <row r="723" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="723" spans="1:11">
       <c r="A723" s="15">
         <v>43943</v>
       </c>
@@ -41320,7 +41351,7 @@
         <v>57.95</v>
       </c>
     </row>
-    <row r="724" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="724" spans="1:11">
       <c r="A724" s="15">
         <v>43950</v>
       </c>
@@ -41356,7 +41387,7 @@
         <v>41.89</v>
       </c>
     </row>
-    <row r="725" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="725" spans="1:11">
       <c r="A725" s="15">
         <v>43957</v>
       </c>
@@ -41392,7 +41423,7 @@
         <v>41.07</v>
       </c>
     </row>
-    <row r="726" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="726" spans="1:11">
       <c r="A726" s="15">
         <v>43964</v>
       </c>
@@ -41428,7 +41459,7 @@
         <v>49.3</v>
       </c>
     </row>
-    <row r="727" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="727" spans="1:11">
       <c r="A727" s="15">
         <v>43971</v>
       </c>
@@ -41464,7 +41495,7 @@
         <v>51.08</v>
       </c>
     </row>
-    <row r="728" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="728" spans="1:11">
       <c r="A728" s="15">
         <v>43978</v>
       </c>
@@ -41500,7 +41531,7 @@
         <v>43.17</v>
       </c>
     </row>
-    <row r="729" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="729" spans="1:11">
       <c r="A729" s="15">
         <v>43985</v>
       </c>
@@ -41536,7 +41567,7 @@
         <v>36.69</v>
       </c>
     </row>
-    <row r="730" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="730" spans="1:11">
       <c r="A730" s="15">
         <v>43992</v>
       </c>
@@ -41572,7 +41603,7 @@
         <v>54.73</v>
       </c>
     </row>
-    <row r="731" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="731" spans="1:11">
       <c r="A731" s="15">
         <v>43999</v>
       </c>
@@ -41608,7 +41639,7 @@
         <v>37.33</v>
       </c>
     </row>
-    <row r="732" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="732" spans="1:11">
       <c r="A732" s="15">
         <v>44006</v>
       </c>
@@ -41644,7 +41675,7 @@
         <v>43.91</v>
       </c>
     </row>
-    <row r="733" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="733" spans="1:11">
       <c r="A733" s="15">
         <v>44013</v>
       </c>
@@ -41680,7 +41711,7 @@
         <v>52.64</v>
       </c>
     </row>
-    <row r="734" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="734" spans="1:11">
       <c r="A734" s="15">
         <v>44020</v>
       </c>
@@ -41716,7 +41747,7 @@
         <v>50.49</v>
       </c>
     </row>
-    <row r="735" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="735" spans="1:11">
       <c r="A735" s="15">
         <v>44027</v>
       </c>
@@ -41752,7 +41783,7 @@
         <v>49.38</v>
       </c>
     </row>
-    <row r="736" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="736" spans="1:11">
       <c r="A736" s="15">
         <v>44034</v>
       </c>
@@ -41788,7 +41819,7 @@
         <v>33.909999999999997</v>
       </c>
     </row>
-    <row r="737" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="737" spans="1:11">
       <c r="A737" s="15">
         <v>44041</v>
       </c>
@@ -41824,7 +41855,7 @@
         <v>36.130000000000003</v>
       </c>
     </row>
-    <row r="738" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="738" spans="1:11">
       <c r="A738" s="15">
         <v>44048</v>
       </c>
@@ -41860,7 +41891,7 @@
         <v>49.4</v>
       </c>
     </row>
-    <row r="739" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="739" spans="1:11">
       <c r="A739" s="15">
         <v>44055</v>
       </c>
@@ -41896,7 +41927,7 @@
         <v>29.1</v>
       </c>
     </row>
-    <row r="740" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="740" spans="1:11">
       <c r="A740" s="15">
         <v>44062</v>
       </c>
@@ -41932,7 +41963,7 @@
         <v>42.31</v>
       </c>
     </row>
-    <row r="741" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="741" spans="1:11">
       <c r="A741" s="15">
         <v>44069</v>
       </c>
@@ -41968,7 +41999,7 @@
         <v>38.44</v>
       </c>
     </row>
-    <row r="742" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="742" spans="1:11">
       <c r="A742" s="15">
         <v>44076</v>
       </c>
@@ -42004,7 +42035,7 @@
         <v>35.47</v>
       </c>
     </row>
-    <row r="743" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="743" spans="1:11">
       <c r="A743" s="15">
         <v>44083</v>
       </c>
@@ -42040,7 +42071,7 @@
         <v>60.47</v>
       </c>
     </row>
-    <row r="744" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="744" spans="1:11">
       <c r="A744" s="15">
         <v>44090</v>
       </c>
@@ -42076,7 +42107,7 @@
         <v>71.73</v>
       </c>
     </row>
-    <row r="745" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="745" spans="1:11">
       <c r="A745" s="15">
         <v>44097</v>
       </c>
@@ -42112,7 +42143,7 @@
         <v>82.7</v>
       </c>
     </row>
-    <row r="746" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="746" spans="1:11">
       <c r="A746" s="15">
         <v>44104</v>
       </c>
@@ -42148,7 +42179,7 @@
         <v>62.62</v>
       </c>
     </row>
-    <row r="747" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="747" spans="1:11">
       <c r="A747" s="15">
         <v>44111</v>
       </c>
@@ -42184,7 +42215,7 @@
         <v>63.41</v>
       </c>
     </row>
-    <row r="748" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="748" spans="1:11">
       <c r="A748" s="15">
         <v>44118</v>
       </c>
@@ -42220,7 +42251,7 @@
         <v>41.56</v>
       </c>
     </row>
-    <row r="749" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="749" spans="1:11">
       <c r="A749" s="15">
         <v>44125</v>
       </c>
@@ -42256,7 +42287,7 @@
         <v>42.48</v>
       </c>
     </row>
-    <row r="750" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="750" spans="1:11">
       <c r="A750" s="15">
         <v>44132</v>
       </c>
@@ -42292,7 +42323,7 @@
         <v>49.64</v>
       </c>
     </row>
-    <row r="751" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="751" spans="1:11">
       <c r="A751" s="15">
         <v>44139</v>
       </c>
@@ -42328,7 +42359,7 @@
         <v>49.7</v>
       </c>
     </row>
-    <row r="752" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="752" spans="1:11">
       <c r="A752" s="15">
         <v>44146</v>
       </c>
@@ -42364,7 +42395,7 @@
         <v>50.26</v>
       </c>
     </row>
-    <row r="753" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="753" spans="1:11">
       <c r="A753" s="15">
         <v>44153</v>
       </c>
@@ -42400,7 +42431,7 @@
         <v>44.54</v>
       </c>
     </row>
-    <row r="754" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="754" spans="1:11">
       <c r="A754" s="15">
         <v>44160</v>
       </c>
@@ -42436,7 +42467,7 @@
         <v>44.54</v>
       </c>
     </row>
-    <row r="755" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="755" spans="1:11">
       <c r="A755" s="15">
         <v>44167</v>
       </c>
@@ -42472,7 +42503,7 @@
         <v>38.9</v>
       </c>
     </row>
-    <row r="756" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="756" spans="1:11">
       <c r="A756" s="15">
         <v>44174</v>
       </c>
@@ -42508,7 +42539,7 @@
         <v>40.98</v>
       </c>
     </row>
-    <row r="757" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="757" spans="1:11">
       <c r="A757" s="15">
         <v>44181</v>
       </c>
@@ -42544,7 +42575,7 @@
         <v>42.33</v>
       </c>
     </row>
-    <row r="758" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="758" spans="1:11">
       <c r="A758" s="15">
         <v>44188</v>
       </c>
@@ -42580,7 +42611,7 @@
         <v>44.19</v>
       </c>
     </row>
-    <row r="759" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="759" spans="1:11">
       <c r="A759" s="15">
         <v>44195</v>
       </c>
@@ -42616,7 +42647,7 @@
         <v>47.07</v>
       </c>
     </row>
-    <row r="760" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="760" spans="1:11">
       <c r="A760" s="15">
         <v>44202</v>
       </c>
@@ -42652,7 +42683,7 @@
         <v>39.11</v>
       </c>
     </row>
-    <row r="761" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="761" spans="1:11">
       <c r="A761" s="15">
         <v>44209</v>
       </c>
@@ -42688,7 +42719,7 @@
         <v>39.85</v>
       </c>
     </row>
-    <row r="762" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="762" spans="1:11">
       <c r="A762" s="15">
         <v>44216</v>
       </c>
@@ -42724,7 +42755,7 @@
         <v>36.46</v>
       </c>
     </row>
-    <row r="763" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="763" spans="1:11">
       <c r="A763" s="15">
         <v>44223</v>
       </c>
@@ -42760,7 +42791,7 @@
         <v>53.82</v>
       </c>
     </row>
-    <row r="764" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="764" spans="1:11">
       <c r="A764" s="15">
         <v>44230</v>
       </c>
@@ -42796,7 +42827,7 @@
         <v>50.88</v>
       </c>
     </row>
-    <row r="765" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="765" spans="1:11">
       <c r="A765" s="15">
         <v>44237</v>
       </c>
@@ -42832,7 +42863,7 @@
         <v>29.44</v>
       </c>
     </row>
-    <row r="766" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="766" spans="1:11">
       <c r="A766" s="15">
         <v>44244</v>
       </c>
@@ -42868,7 +42899,7 @@
         <v>44.76</v>
       </c>
     </row>
-    <row r="767" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="767" spans="1:11">
       <c r="A767" s="15">
         <v>44251</v>
       </c>
@@ -42904,7 +42935,7 @@
         <v>48.64</v>
       </c>
     </row>
-    <row r="768" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="768" spans="1:11">
       <c r="A768" s="15">
         <v>44258</v>
       </c>
@@ -42940,7 +42971,7 @@
         <v>62.65</v>
       </c>
     </row>
-    <row r="769" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="769" spans="1:11">
       <c r="A769" s="15">
         <v>44265</v>
       </c>
@@ -42976,7 +43007,7 @@
         <v>54.1</v>
       </c>
     </row>
-    <row r="770" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="770" spans="1:11">
       <c r="A770" s="15">
         <v>44272</v>
       </c>
@@ -43012,7 +43043,7 @@
         <v>33.979999999999997</v>
       </c>
     </row>
-    <row r="771" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="771" spans="1:11">
       <c r="A771" s="15">
         <v>44279</v>
       </c>
@@ -43063,7 +43094,7 @@
         <v>42.24</v>
       </c>
     </row>
-    <row r="772" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="772" spans="1:11">
       <c r="A772" s="15">
         <v>44286</v>
       </c>
@@ -43099,7 +43130,7 @@
         <v>47.49</v>
       </c>
     </row>
-    <row r="773" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="773" spans="1:11">
       <c r="A773" s="15">
         <v>44293</v>
       </c>
@@ -43135,7 +43166,7 @@
         <v>35.159999999999997</v>
       </c>
     </row>
-    <row r="774" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="774" spans="1:11">
       <c r="A774" s="15">
         <v>44300</v>
       </c>
@@ -43171,7 +43202,7 @@
         <v>39.590000000000003</v>
       </c>
     </row>
-    <row r="775" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="775" spans="1:11">
       <c r="A775" s="15">
         <v>44307</v>
       </c>
@@ -43207,7 +43238,7 @@
         <v>39.06</v>
       </c>
     </row>
-    <row r="776" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="776" spans="1:11">
       <c r="A776" s="15">
         <v>44314</v>
       </c>
@@ -43243,7 +43274,7 @@
         <v>43.65</v>
       </c>
     </row>
-    <row r="777" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="777" spans="1:11">
       <c r="A777" s="15">
         <v>44321</v>
       </c>
@@ -43279,7 +43310,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="778" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="778" spans="1:11">
       <c r="A778" s="15">
         <v>44328</v>
       </c>
@@ -43315,7 +43346,7 @@
         <v>44.2</v>
       </c>
     </row>
-    <row r="779" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="779" spans="1:11">
       <c r="A779" s="15">
         <v>44335</v>
       </c>
@@ -43351,7 +43382,7 @@
         <v>35.25</v>
       </c>
     </row>
-    <row r="780" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="780" spans="1:11">
       <c r="A780" s="15">
         <v>44342</v>
       </c>
@@ -43387,7 +43418,7 @@
         <v>35.119999999999997</v>
       </c>
     </row>
-    <row r="781" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="781" spans="1:11">
       <c r="A781" s="15">
         <v>44349</v>
       </c>
@@ -43423,7 +43454,7 @@
         <v>35.83</v>
       </c>
     </row>
-    <row r="782" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="782" spans="1:11">
       <c r="A782" s="15">
         <v>44356</v>
       </c>
@@ -43459,7 +43490,7 @@
         <v>38.92</v>
       </c>
     </row>
-    <row r="783" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="783" spans="1:11">
       <c r="A783" s="15">
         <v>44363</v>
       </c>
@@ -43495,7 +43526,7 @@
         <v>34.159999999999997</v>
       </c>
     </row>
-    <row r="784" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="784" spans="1:11">
       <c r="A784" s="15">
         <v>44370</v>
       </c>
@@ -43531,7 +43562,7 @@
         <v>42.79</v>
       </c>
     </row>
-    <row r="785" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="785" spans="1:11">
       <c r="A785" s="15">
         <v>44377</v>
       </c>
@@ -43567,7 +43598,7 @@
         <v>38.18</v>
       </c>
     </row>
-    <row r="786" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="786" spans="1:11">
       <c r="A786" s="15">
         <v>44384</v>
       </c>
@@ -43603,7 +43634,7 @@
         <v>42.66</v>
       </c>
     </row>
-    <row r="787" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="787" spans="1:11">
       <c r="A787" s="15">
         <v>44391</v>
       </c>
@@ -43639,7 +43670,7 @@
         <v>37.85</v>
       </c>
     </row>
-    <row r="788" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="788" spans="1:11">
       <c r="A788" s="15">
         <v>44398</v>
       </c>
@@ -43675,7 +43706,7 @@
         <v>48.75</v>
       </c>
     </row>
-    <row r="789" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="789" spans="1:11">
       <c r="A789" s="15">
         <v>44405</v>
       </c>
@@ -43711,7 +43742,7 @@
         <v>43.07</v>
       </c>
     </row>
-    <row r="790" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="790" spans="1:11">
       <c r="A790" s="15">
         <v>44412</v>
       </c>
@@ -43747,7 +43778,7 @@
         <v>41.16</v>
       </c>
     </row>
-    <row r="791" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="791" spans="1:11">
       <c r="A791" s="15">
         <v>44419</v>
       </c>
@@ -43783,7 +43814,7 @@
         <v>38.54</v>
       </c>
     </row>
-    <row r="792" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="792" spans="1:11">
       <c r="A792" s="15">
         <v>44426</v>
       </c>
@@ -43819,7 +43850,7 @@
         <v>58.22</v>
       </c>
     </row>
-    <row r="793" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="793" spans="1:11">
       <c r="A793" s="15">
         <v>44433</v>
       </c>
@@ -43855,7 +43886,7 @@
         <v>37.950000000000003</v>
       </c>
     </row>
-    <row r="794" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="794" spans="1:11">
       <c r="A794" s="15">
         <v>44440</v>
       </c>
@@ -43891,7 +43922,7 @@
         <v>39.24</v>
       </c>
     </row>
-    <row r="795" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="795" spans="1:11">
       <c r="A795" s="15">
         <v>44447</v>
       </c>
@@ -43927,7 +43958,7 @@
         <v>43.85</v>
       </c>
     </row>
-    <row r="796" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="796" spans="1:11">
       <c r="A796" s="15">
         <v>44454</v>
       </c>
@@ -43963,7 +43994,7 @@
         <v>47.86</v>
       </c>
     </row>
-    <row r="797" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="797" spans="1:11">
       <c r="A797" s="15">
         <v>44461</v>
       </c>
@@ -43999,7 +44030,7 @@
         <v>47.37</v>
       </c>
     </row>
-    <row r="798" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="798" spans="1:11">
       <c r="A798" s="15">
         <v>44468</v>
       </c>
@@ -44035,7 +44066,7 @@
         <v>72.13</v>
       </c>
     </row>
-    <row r="799" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="799" spans="1:11">
       <c r="A799" s="15">
         <v>44475</v>
       </c>
@@ -44071,7 +44102,7 @@
         <v>51.09</v>
       </c>
     </row>
-    <row r="800" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="800" spans="1:11">
       <c r="A800" s="15">
         <v>44482</v>
       </c>
@@ -44107,7 +44138,7 @@
         <v>52.37</v>
       </c>
     </row>
-    <row r="801" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="801" spans="1:11">
       <c r="A801" s="15">
         <v>44489</v>
       </c>
@@ -44143,7 +44174,7 @@
         <v>33.46</v>
       </c>
     </row>
-    <row r="802" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="802" spans="1:11">
       <c r="A802" s="15">
         <v>44496</v>
       </c>
@@ -44179,7 +44210,7 @@
         <v>33.03</v>
       </c>
     </row>
-    <row r="803" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="803" spans="1:11">
       <c r="A803" s="15">
         <v>44503</v>
       </c>
@@ -44215,7 +44246,7 @@
         <v>37.31</v>
       </c>
     </row>
-    <row r="804" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="804" spans="1:11">
       <c r="A804" s="15">
         <v>44510</v>
       </c>
@@ -44251,7 +44282,7 @@
         <v>43.41</v>
       </c>
     </row>
-    <row r="805" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="805" spans="1:11">
       <c r="A805" s="15">
         <v>44517</v>
       </c>
@@ -44287,7 +44318,7 @@
         <v>47.38</v>
       </c>
     </row>
-    <row r="806" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="806" spans="1:11">
       <c r="A806" s="15">
         <v>44524</v>
       </c>
@@ -44323,7 +44354,7 @@
         <v>46.63</v>
       </c>
     </row>
-    <row r="807" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="807" spans="1:11">
       <c r="A807" s="15">
         <v>44531</v>
       </c>
@@ -44359,7 +44390,7 @@
         <v>59.91</v>
       </c>
     </row>
-    <row r="808" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="808" spans="1:11">
       <c r="A808" s="15">
         <v>44538</v>
       </c>
@@ -44395,7 +44426,7 @@
         <v>78.33</v>
       </c>
     </row>
-    <row r="809" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="809" spans="1:11">
       <c r="A809" s="15">
         <v>44545</v>
       </c>
@@ -44431,7 +44462,7 @@
         <v>61.89</v>
       </c>
     </row>
-    <row r="810" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="810" spans="1:11">
       <c r="A810" s="15">
         <v>44552</v>
       </c>
@@ -44467,7 +44498,7 @@
         <v>51.45</v>
       </c>
     </row>
-    <row r="811" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="811" spans="1:11">
       <c r="A811" s="15">
         <v>44559</v>
       </c>
@@ -44503,7 +44534,7 @@
         <v>38.94</v>
       </c>
     </row>
-    <row r="812" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="812" spans="1:11">
       <c r="A812" s="15">
         <v>44566</v>
       </c>
@@ -44539,7 +44570,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="813" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="813" spans="1:11">
       <c r="A813" s="15">
         <v>44573</v>
       </c>
@@ -44575,7 +44606,7 @@
         <v>66.02</v>
       </c>
     </row>
-    <row r="814" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="814" spans="1:11">
       <c r="A814" s="15">
         <v>44580</v>
       </c>
@@ -44611,7 +44642,7 @@
         <v>76.22</v>
       </c>
     </row>
-    <row r="815" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="815" spans="1:11">
       <c r="A815" s="15">
         <v>44587</v>
       </c>
@@ -44647,7 +44678,7 @@
         <v>66.22</v>
       </c>
     </row>
-    <row r="816" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="816" spans="1:11">
       <c r="A816" s="15">
         <v>44594</v>
       </c>
@@ -44683,7 +44714,7 @@
         <v>49.17</v>
       </c>
     </row>
-    <row r="817" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="817" spans="1:11">
       <c r="A817" s="15">
         <v>44601</v>
       </c>
@@ -44719,7 +44750,7 @@
         <v>40.53</v>
       </c>
     </row>
-    <row r="818" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="818" spans="1:11">
       <c r="A818" s="15">
         <v>44608</v>
       </c>
@@ -44755,7 +44786,7 @@
         <v>72.38</v>
       </c>
     </row>
-    <row r="819" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="819" spans="1:11">
       <c r="A819" s="15">
         <v>44615</v>
       </c>
@@ -44791,7 +44822,7 @@
         <v>71.64</v>
       </c>
     </row>
-    <row r="820" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="820" spans="1:11">
       <c r="A820" s="15">
         <v>44622</v>
       </c>
@@ -44827,7 +44858,7 @@
         <v>72.260000000000005</v>
       </c>
     </row>
-    <row r="821" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="821" spans="1:11">
       <c r="A821" s="15">
         <v>44629</v>
       </c>
@@ -44863,7 +44894,7 @@
         <v>70.959999999999994</v>
       </c>
     </row>
-    <row r="822" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="822" spans="1:11">
       <c r="A822" s="15">
         <v>44636</v>
       </c>
@@ -44899,7 +44930,7 @@
         <v>60.48</v>
       </c>
     </row>
-    <row r="823" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="823" spans="1:11">
       <c r="A823" s="15">
         <v>44643</v>
       </c>
@@ -44935,7 +44966,7 @@
         <v>65.23</v>
       </c>
     </row>
-    <row r="824" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="824" spans="1:11">
       <c r="A824" s="15">
         <v>44650</v>
       </c>
@@ -44971,7 +45002,7 @@
         <v>21.67</v>
       </c>
     </row>
-    <row r="825" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="825" spans="1:11">
       <c r="A825" s="15">
         <v>44657</v>
       </c>
@@ -45007,7 +45038,7 @@
         <v>40.35</v>
       </c>
     </row>
-    <row r="826" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="826" spans="1:11">
       <c r="A826" s="15">
         <v>44664</v>
       </c>
@@ -45043,7 +45074,7 @@
         <v>31.86</v>
       </c>
     </row>
-    <row r="827" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="827" spans="1:11">
       <c r="A827" s="15">
         <v>44671</v>
       </c>
@@ -45079,7 +45110,7 @@
         <v>28.88</v>
       </c>
     </row>
-    <row r="828" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="828" spans="1:11">
       <c r="A828" s="15">
         <v>44678</v>
       </c>
@@ -45115,7 +45146,7 @@
         <v>69.22</v>
       </c>
     </row>
-    <row r="829" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="829" spans="1:11">
       <c r="A829" s="15">
         <v>44685</v>
       </c>
@@ -45151,7 +45182,7 @@
         <v>45.33</v>
       </c>
     </row>
-    <row r="830" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="830" spans="1:11">
       <c r="A830" s="15">
         <v>44692</v>
       </c>
@@ -45187,7 +45218,7 @@
         <v>58.81</v>
       </c>
     </row>
-    <row r="831" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="831" spans="1:11">
       <c r="A831" s="15">
         <v>44699</v>
       </c>
@@ -45223,7 +45254,7 @@
         <v>44.74</v>
       </c>
     </row>
-    <row r="832" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="832" spans="1:11">
       <c r="A832" s="15">
         <v>44706</v>
       </c>
@@ -45259,7 +45290,7 @@
         <v>35.08</v>
       </c>
     </row>
-    <row r="833" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="833" spans="1:11">
       <c r="A833" s="15">
         <v>44713</v>
       </c>
@@ -45295,7 +45326,7 @@
         <v>74.08</v>
       </c>
     </row>
-    <row r="834" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="834" spans="1:11">
       <c r="A834" s="15">
         <v>44720</v>
       </c>
@@ -45331,7 +45362,7 @@
         <v>43.01</v>
       </c>
     </row>
-    <row r="835" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="835" spans="1:11">
       <c r="A835" s="15">
         <v>44727</v>
       </c>
@@ -45382,7 +45413,7 @@
         <v>50.59</v>
       </c>
     </row>
-    <row r="836" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="836" spans="1:11">
       <c r="A836" s="15">
         <v>44734</v>
       </c>
@@ -45418,7 +45449,7 @@
         <v>59.84</v>
       </c>
     </row>
-    <row r="837" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="837" spans="1:11">
       <c r="A837" s="15">
         <v>44741</v>
       </c>
@@ -45454,7 +45485,7 @@
         <v>51.78</v>
       </c>
     </row>
-    <row r="838" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="838" spans="1:11">
       <c r="A838" s="15">
         <v>44748</v>
       </c>
@@ -45490,7 +45521,7 @@
         <v>62.05</v>
       </c>
     </row>
-    <row r="839" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="839" spans="1:11">
       <c r="A839" s="15">
         <v>44755</v>
       </c>
@@ -45526,7 +45557,7 @@
         <v>58.93</v>
       </c>
     </row>
-    <row r="840" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="840" spans="1:11">
       <c r="A840" s="15">
         <v>44762</v>
       </c>
@@ -45562,7 +45593,7 @@
         <v>51.59</v>
       </c>
     </row>
-    <row r="841" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="841" spans="1:11">
       <c r="A841" s="15">
         <v>44769</v>
       </c>
@@ -45598,7 +45629,7 @@
         <v>50.16</v>
       </c>
     </row>
-    <row r="842" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="842" spans="1:11">
       <c r="A842" s="15">
         <v>44776</v>
       </c>
@@ -45634,7 +45665,7 @@
         <v>53.21</v>
       </c>
     </row>
-    <row r="843" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="843" spans="1:11">
       <c r="A843" s="15">
         <v>44783</v>
       </c>
@@ -45670,7 +45701,7 @@
         <v>54.24</v>
       </c>
     </row>
-    <row r="844" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="844" spans="1:11">
       <c r="A844" s="15">
         <v>44790</v>
       </c>
@@ -45706,7 +45737,7 @@
         <v>54.27</v>
       </c>
     </row>
-    <row r="845" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="845" spans="1:11">
       <c r="A845" s="15">
         <v>44797</v>
       </c>
@@ -45742,7 +45773,7 @@
         <v>59.7</v>
       </c>
     </row>
-    <row r="846" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="846" spans="1:11">
       <c r="A846" s="15">
         <v>44804</v>
       </c>
@@ -45778,7 +45809,7 @@
         <v>60.43</v>
       </c>
     </row>
-    <row r="847" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="847" spans="1:11">
       <c r="A847" s="15">
         <v>44811</v>
       </c>
@@ -45814,7 +45845,7 @@
         <v>60.04</v>
       </c>
     </row>
-    <row r="848" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="848" spans="1:11">
       <c r="A848" s="15">
         <v>44818</v>
       </c>
@@ -45850,7 +45881,7 @@
         <v>70.459999999999994</v>
       </c>
     </row>
-    <row r="849" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="849" spans="1:11">
       <c r="A849" s="15">
         <v>44825</v>
       </c>
@@ -45886,7 +45917,7 @@
         <v>60.97</v>
       </c>
     </row>
-    <row r="850" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="850" spans="1:11">
       <c r="A850" s="15">
         <v>44832</v>
       </c>
@@ -45922,7 +45953,7 @@
         <v>66.88</v>
       </c>
     </row>
-    <row r="851" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="851" spans="1:11">
       <c r="A851" s="15">
         <v>44839</v>
       </c>
@@ -45958,7 +45989,7 @@
         <v>58.96</v>
       </c>
     </row>
-    <row r="852" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="852" spans="1:11">
       <c r="A852" s="15">
         <v>44846</v>
       </c>
@@ -45994,7 +46025,7 @@
         <v>59.65</v>
       </c>
     </row>
-    <row r="853" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="853" spans="1:11">
       <c r="A853" s="15">
         <v>44853</v>
       </c>
@@ -46030,7 +46061,7 @@
         <v>55.43</v>
       </c>
     </row>
-    <row r="854" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="854" spans="1:11">
       <c r="A854" s="15">
         <v>44860</v>
       </c>
@@ -46066,7 +46097,7 @@
         <v>54.08</v>
       </c>
     </row>
-    <row r="855" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="855" spans="1:11">
       <c r="A855" s="15">
         <v>44867</v>
       </c>
@@ -46102,7 +46133,7 @@
         <v>59.48</v>
       </c>
     </row>
-    <row r="856" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="856" spans="1:11">
       <c r="A856" s="15">
         <v>44874</v>
       </c>
@@ -46138,7 +46169,7 @@
         <v>54.63</v>
       </c>
     </row>
-    <row r="857" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="857" spans="1:11">
       <c r="A857" s="15">
         <v>44881</v>
       </c>
@@ -46174,7 +46205,7 @@
         <v>60.66</v>
       </c>
     </row>
-    <row r="858" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="858" spans="1:11">
       <c r="A858" s="15">
         <v>44888</v>
       </c>
@@ -46210,7 +46241,7 @@
         <v>56.55</v>
       </c>
     </row>
-    <row r="859" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="859" spans="1:11">
       <c r="A859" s="15">
         <v>44895</v>
       </c>
@@ -46246,7 +46277,7 @@
         <v>50.1</v>
       </c>
     </row>
-    <row r="860" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="860" spans="1:11">
       <c r="A860" s="15">
         <v>44902</v>
       </c>
@@ -46282,7 +46313,7 @@
         <v>50.27</v>
       </c>
     </row>
-    <row r="861" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="861" spans="1:11">
       <c r="A861" s="15">
         <v>44909</v>
       </c>
@@ -46318,7 +46349,7 @@
         <v>48.94</v>
       </c>
     </row>
-    <row r="862" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="862" spans="1:11">
       <c r="A862" s="15">
         <v>44916</v>
       </c>
@@ -46354,7 +46385,7 @@
         <v>53.8</v>
       </c>
     </row>
-    <row r="863" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="863" spans="1:11">
       <c r="A863" s="15">
         <v>44923</v>
       </c>
@@ -46390,7 +46421,7 @@
         <v>46.68</v>
       </c>
     </row>
-    <row r="864" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="864" spans="1:11">
       <c r="A864" s="15">
         <v>44930</v>
       </c>
@@ -46426,7 +46457,7 @@
         <v>53.9</v>
       </c>
     </row>
-    <row r="865" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="865" spans="1:11">
       <c r="A865" s="15">
         <v>44937</v>
       </c>
@@ -46462,7 +46493,7 @@
         <v>39.74</v>
       </c>
     </row>
-    <row r="866" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="866" spans="1:11">
       <c r="A866" s="15">
         <v>44944</v>
       </c>
@@ -46498,7 +46529,7 @@
         <v>58.85</v>
       </c>
     </row>
-    <row r="867" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="867" spans="1:11">
       <c r="A867" s="15">
         <v>44951</v>
       </c>
@@ -46534,7 +46565,7 @@
         <v>45.01</v>
       </c>
     </row>
-    <row r="868" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="868" spans="1:11">
       <c r="A868" s="15">
         <v>44958</v>
       </c>
@@ -46570,7 +46601,7 @@
         <v>44.29</v>
       </c>
     </row>
-    <row r="869" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="869" spans="1:11">
       <c r="A869" s="15">
         <v>44965</v>
       </c>
@@ -46606,7 +46637,7 @@
         <v>44.25</v>
       </c>
     </row>
-    <row r="870" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="870" spans="1:11">
       <c r="A870" s="15">
         <v>44972</v>
       </c>
@@ -46642,7 +46673,7 @@
         <v>47.28</v>
       </c>
     </row>
-    <row r="871" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="871" spans="1:11">
       <c r="A871" s="15">
         <v>44979</v>
       </c>
@@ -46678,7 +46709,7 @@
         <v>71.14</v>
       </c>
     </row>
-    <row r="872" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="872" spans="1:11">
       <c r="A872" s="15">
         <v>44986</v>
       </c>
@@ -46714,7 +46745,7 @@
         <v>69.319999999999993</v>
       </c>
     </row>
-    <row r="873" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="873" spans="1:11">
       <c r="A873" s="15">
         <v>44993</v>
       </c>
@@ -46750,7 +46781,7 @@
         <v>63.44</v>
       </c>
     </row>
-    <row r="874" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="874" spans="1:11">
       <c r="A874" s="15">
         <v>45000</v>
       </c>
@@ -46786,7 +46817,7 @@
         <v>66.69</v>
       </c>
     </row>
-    <row r="875" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="875" spans="1:11">
       <c r="A875" s="15">
         <v>45007</v>
       </c>
@@ -46822,7 +46853,7 @@
         <v>57.12</v>
       </c>
     </row>
-    <row r="876" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="876" spans="1:11">
       <c r="A876" s="15">
         <v>45014</v>
       </c>
@@ -46858,7 +46889,7 @@
         <v>49.69</v>
       </c>
     </row>
-    <row r="877" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="877" spans="1:11">
       <c r="A877" s="15">
         <v>45021</v>
       </c>
@@ -46894,7 +46925,7 @@
         <v>45.38</v>
       </c>
     </row>
-    <row r="878" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="878" spans="1:11">
       <c r="A878" s="15">
         <v>45028</v>
       </c>
@@ -46930,7 +46961,7 @@
         <v>64.83</v>
       </c>
     </row>
-    <row r="879" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="879" spans="1:11">
       <c r="A879" s="15">
         <v>45035</v>
       </c>
@@ -46966,7 +46997,7 @@
         <v>39.61</v>
       </c>
     </row>
-    <row r="880" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="880" spans="1:11">
       <c r="A880" s="15">
         <v>45042</v>
       </c>
@@ -47002,7 +47033,7 @@
         <v>56.93</v>
       </c>
     </row>
-    <row r="881" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="881" spans="1:11">
       <c r="A881" s="15">
         <v>45049</v>
       </c>
@@ -47038,7 +47069,7 @@
         <v>43.05</v>
       </c>
     </row>
-    <row r="882" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="882" spans="1:11">
       <c r="A882" s="15">
         <v>45056</v>
       </c>
@@ -47074,7 +47105,7 @@
         <v>50.84</v>
       </c>
     </row>
-    <row r="883" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="883" spans="1:11">
       <c r="A883" s="15">
         <v>45063</v>
       </c>
@@ -47110,7 +47141,7 @@
         <v>48.49</v>
       </c>
     </row>
-    <row r="884" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="884" spans="1:11">
       <c r="A884" s="15">
         <v>45070</v>
       </c>
@@ -47146,7 +47177,7 @@
         <v>52.21</v>
       </c>
     </row>
-    <row r="885" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="885" spans="1:11">
       <c r="A885" s="15">
         <v>45077</v>
       </c>
@@ -47182,7 +47213,7 @@
         <v>59.12</v>
       </c>
     </row>
-    <row r="886" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="886" spans="1:11">
       <c r="A886" s="15">
         <v>45084</v>
       </c>
@@ -47218,7 +47249,7 @@
         <v>40.46</v>
       </c>
     </row>
-    <row r="887" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="887" spans="1:11">
       <c r="A887" s="15">
         <v>45091</v>
       </c>
@@ -47254,7 +47285,7 @@
         <v>56.21</v>
       </c>
     </row>
-    <row r="888" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="888" spans="1:11">
       <c r="A888" s="15">
         <v>45098</v>
       </c>
@@ -47290,7 +47321,7 @@
         <v>45.51</v>
       </c>
     </row>
-    <row r="889" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="889" spans="1:11">
       <c r="A889" s="15">
         <v>45105</v>
       </c>
@@ -47326,7 +47357,7 @@
         <v>54.14</v>
       </c>
     </row>
-    <row r="890" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="890" spans="1:11">
       <c r="A890" s="15">
         <v>45112</v>
       </c>
@@ -47362,7 +47393,7 @@
         <v>50.49</v>
       </c>
     </row>
-    <row r="891" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="891" spans="1:11">
       <c r="A891" s="15">
         <v>45119</v>
       </c>
@@ -47398,7 +47429,7 @@
         <v>44.26</v>
       </c>
     </row>
-    <row r="892" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="892" spans="1:11">
       <c r="A892" s="15">
         <v>45126</v>
       </c>
@@ -47434,7 +47465,7 @@
         <v>44.69</v>
       </c>
     </row>
-    <row r="893" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="893" spans="1:11">
       <c r="A893" s="15">
         <v>45133</v>
       </c>
@@ -47470,7 +47501,7 @@
         <v>36.340000000000003</v>
       </c>
     </row>
-    <row r="894" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="894" spans="1:11">
       <c r="A894" s="15">
         <v>45140</v>
       </c>
@@ -47506,7 +47537,7 @@
         <v>72.739999999999995</v>
       </c>
     </row>
-    <row r="895" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="895" spans="1:11">
       <c r="A895" s="15">
         <v>45147</v>
       </c>
@@ -47542,7 +47573,7 @@
         <v>63.43</v>
       </c>
     </row>
-    <row r="896" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="896" spans="1:11">
       <c r="A896" s="15">
         <v>45154</v>
       </c>
@@ -47578,7 +47609,7 @@
         <v>67.22</v>
       </c>
     </row>
-    <row r="897" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="897" spans="1:11">
       <c r="A897" s="15">
         <v>45161</v>
       </c>
@@ -47614,7 +47645,7 @@
         <v>79.38</v>
       </c>
     </row>
-    <row r="898" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="898" spans="1:11">
       <c r="A898" s="15">
         <v>45168</v>
       </c>
@@ -47650,7 +47681,7 @@
         <v>63.6</v>
       </c>
     </row>
-    <row r="899" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="899" spans="1:11">
       <c r="A899" s="15">
         <v>45175</v>
       </c>
@@ -47701,7 +47732,7 @@
         <v>70.89</v>
       </c>
     </row>
-    <row r="900" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="900" spans="1:11">
       <c r="A900" s="15">
         <v>45182</v>
       </c>
@@ -47737,7 +47768,7 @@
         <v>64.010000000000005</v>
       </c>
     </row>
-    <row r="901" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="901" spans="1:11">
       <c r="A901" s="15">
         <v>45189</v>
       </c>
@@ -47773,7 +47804,7 @@
         <v>53.81</v>
       </c>
     </row>
-    <row r="902" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="902" spans="1:11">
       <c r="A902" s="15">
         <v>45196</v>
       </c>
@@ -47809,7 +47840,7 @@
         <v>60.53</v>
       </c>
     </row>
-    <row r="903" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="903" spans="1:11">
       <c r="A903" s="15">
         <v>45203</v>
       </c>
@@ -47845,7 +47876,7 @@
         <v>74.3</v>
       </c>
     </row>
-    <row r="904" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="904" spans="1:11">
       <c r="A904" s="15">
         <v>45210</v>
       </c>
@@ -47881,7 +47912,7 @@
         <v>70.16</v>
       </c>
     </row>
-    <row r="905" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="905" spans="1:11">
       <c r="A905" s="15">
         <v>45217</v>
       </c>
@@ -47917,7 +47948,7 @@
         <v>60.7</v>
       </c>
     </row>
-    <row r="906" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="906" spans="1:11">
       <c r="A906" s="15">
         <v>45224</v>
       </c>
@@ -47953,7 +47984,7 @@
         <v>73.540000000000006</v>
       </c>
     </row>
-    <row r="907" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="907" spans="1:11">
       <c r="A907" s="15">
         <v>45231</v>
       </c>
@@ -47989,7 +48020,7 @@
         <v>71.180000000000007</v>
       </c>
     </row>
-    <row r="908" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="908" spans="1:11">
       <c r="A908" s="15">
         <v>45238</v>
       </c>
@@ -48025,7 +48056,7 @@
         <v>52.63</v>
       </c>
     </row>
-    <row r="909" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="909" spans="1:11">
       <c r="A909" s="15">
         <v>45245</v>
       </c>
@@ -48061,7 +48092,7 @@
         <v>70.599999999999994</v>
       </c>
     </row>
-    <row r="910" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="910" spans="1:11">
       <c r="A910" s="15">
         <v>45252</v>
       </c>
@@ -48097,7 +48128,7 @@
         <v>68.56</v>
       </c>
     </row>
-    <row r="911" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="911" spans="1:11">
       <c r="A911" s="15">
         <v>45259</v>
       </c>
@@ -48133,7 +48164,7 @@
         <v>64.95</v>
       </c>
     </row>
-    <row r="912" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="912" spans="1:11">
       <c r="A912" s="15">
         <v>45266</v>
       </c>
@@ -48169,7 +48200,7 @@
         <v>71.14</v>
       </c>
     </row>
-    <row r="913" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="913" spans="1:11">
       <c r="A913" s="15">
         <v>45273</v>
       </c>
@@ -48205,7 +48236,7 @@
         <v>69.78</v>
       </c>
     </row>
-    <row r="914" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="914" spans="1:11">
       <c r="A914" s="15">
         <v>45280</v>
       </c>
@@ -48241,7 +48272,7 @@
         <v>49.87</v>
       </c>
     </row>
-    <row r="915" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="915" spans="1:11">
       <c r="A915" s="15">
         <v>45287</v>
       </c>
@@ -48277,7 +48308,7 @@
         <v>48.43</v>
       </c>
     </row>
-    <row r="916" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="916" spans="1:11">
       <c r="A916" s="15">
         <v>45294</v>
       </c>
@@ -48313,7 +48344,7 @@
         <v>68.19</v>
       </c>
     </row>
-    <row r="917" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="917" spans="1:11">
       <c r="A917" s="15">
         <v>45301</v>
       </c>
@@ -48349,7 +48380,7 @@
         <v>43.94</v>
       </c>
     </row>
-    <row r="918" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="918" spans="1:11">
       <c r="A918" s="15">
         <v>45308</v>
       </c>
@@ -48385,7 +48416,7 @@
         <v>71.66</v>
       </c>
     </row>
-    <row r="919" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="919" spans="1:11">
       <c r="A919" s="15">
         <v>45315</v>
       </c>
@@ -48421,7 +48452,7 @@
         <v>70.540000000000006</v>
       </c>
     </row>
-    <row r="920" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="920" spans="1:11">
       <c r="A920" s="15">
         <v>45322</v>
       </c>
@@ -48457,7 +48488,7 @@
         <v>67.72</v>
       </c>
     </row>
-    <row r="921" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="921" spans="1:11">
       <c r="A921" s="15">
         <v>45329</v>
       </c>
@@ -48493,7 +48524,7 @@
         <v>40.520000000000003</v>
       </c>
     </row>
-    <row r="922" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="922" spans="1:11">
       <c r="A922" s="15">
         <v>45336</v>
       </c>
@@ -48529,7 +48560,7 @@
         <v>42.93</v>
       </c>
     </row>
-    <row r="923" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="923" spans="1:11">
       <c r="A923" s="15">
         <v>45343</v>
       </c>
@@ -48565,7 +48596,7 @@
         <v>87.34</v>
       </c>
     </row>
-    <row r="924" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="924" spans="1:11">
       <c r="A924" s="15">
         <v>45350</v>
       </c>
@@ -48601,7 +48632,7 @@
         <v>63.8</v>
       </c>
     </row>
-    <row r="925" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="925" spans="1:11">
       <c r="A925" s="15">
         <v>45357</v>
       </c>
@@ -48637,7 +48668,7 @@
         <v>43.54</v>
       </c>
     </row>
-    <row r="926" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="926" spans="1:11">
       <c r="A926" s="15">
         <v>45364</v>
       </c>
@@ -48673,7 +48704,7 @@
         <v>45.2</v>
       </c>
     </row>
-    <row r="927" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="927" spans="1:11">
       <c r="A927" s="15">
         <v>45371</v>
       </c>
@@ -48709,7 +48740,7 @@
         <v>71.209999999999994</v>
       </c>
     </row>
-    <row r="928" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="928" spans="1:11">
       <c r="A928" s="15">
         <v>45378</v>
       </c>
@@ -48745,7 +48776,7 @@
         <v>31.21</v>
       </c>
     </row>
-    <row r="929" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="929" spans="1:11">
       <c r="A929" s="15">
         <v>45385</v>
       </c>
@@ -48781,7 +48812,7 @@
         <v>68.209999999999994</v>
       </c>
     </row>
-    <row r="930" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="930" spans="1:11">
       <c r="A930" s="15">
         <v>45392</v>
       </c>
@@ -48817,7 +48848,7 @@
         <v>65.73</v>
       </c>
     </row>
-    <row r="931" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="931" spans="1:11">
       <c r="A931" s="15">
         <v>45399</v>
       </c>
@@ -48853,7 +48884,7 @@
         <v>71.42</v>
       </c>
     </row>
-    <row r="932" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="932" spans="1:11">
       <c r="A932" s="15">
         <v>45406</v>
       </c>
@@ -48889,7 +48920,7 @@
         <v>70.790000000000006</v>
       </c>
     </row>
-    <row r="933" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="933" spans="1:11">
       <c r="A933" s="15">
         <v>45413</v>
       </c>
@@ -48925,7 +48956,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="934" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="934" spans="1:11">
       <c r="A934" s="15">
         <v>45420</v>
       </c>
@@ -48961,7 +48992,7 @@
         <v>59.39</v>
       </c>
     </row>
-    <row r="935" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="935" spans="1:11">
       <c r="A935" s="15">
         <v>45427</v>
       </c>
@@ -48997,7 +49028,7 @@
         <v>71.739999999999995</v>
       </c>
     </row>
-    <row r="936" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="936" spans="1:11">
       <c r="A936" s="15">
         <v>45434</v>
       </c>
@@ -49033,7 +49064,7 @@
         <v>72.540000000000006</v>
       </c>
     </row>
-    <row r="937" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="937" spans="1:11">
       <c r="A937" s="15">
         <v>45441</v>
       </c>
@@ -49069,7 +49100,7 @@
         <v>78.959999999999994</v>
       </c>
     </row>
-    <row r="938" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="938" spans="1:11">
       <c r="A938" s="15">
         <v>45448</v>
       </c>
@@ -49105,7 +49136,7 @@
         <v>90.94</v>
       </c>
     </row>
-    <row r="939" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="939" spans="1:11">
       <c r="A939" s="15">
         <v>45455</v>
       </c>
@@ -49141,7 +49172,7 @@
         <v>56.33</v>
       </c>
     </row>
-    <row r="940" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="940" spans="1:11">
       <c r="A940" s="15">
         <v>45462</v>
       </c>
@@ -49177,7 +49208,7 @@
         <v>74.87</v>
       </c>
     </row>
-    <row r="941" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="941" spans="1:11">
       <c r="A941" s="15">
         <v>45469</v>
       </c>
@@ -49213,7 +49244,7 @@
         <v>58.35</v>
       </c>
     </row>
-    <row r="942" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="942" spans="1:11">
       <c r="A942" s="15">
         <v>45476</v>
       </c>
@@ -49249,7 +49280,7 @@
         <v>55.2</v>
       </c>
     </row>
-    <row r="943" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="943" spans="1:11">
       <c r="A943" s="15">
         <v>45483</v>
       </c>
@@ -49285,7 +49316,7 @@
         <v>71.989999999999995</v>
       </c>
     </row>
-    <row r="944" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="944" spans="1:11">
       <c r="A944" s="15">
         <v>45490</v>
       </c>
@@ -49321,7 +49352,7 @@
         <v>71.55</v>
       </c>
     </row>
-    <row r="945" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="945" spans="1:11">
       <c r="A945" s="15">
         <v>45497</v>
       </c>
@@ -49357,7 +49388,7 @@
         <v>54.03</v>
       </c>
     </row>
-    <row r="946" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="946" spans="1:11">
       <c r="A946" s="15">
         <v>45504</v>
       </c>
@@ -49393,7 +49424,7 @@
         <v>62.38</v>
       </c>
     </row>
-    <row r="947" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="947" spans="1:11">
       <c r="A947" s="15">
         <v>45511</v>
       </c>
@@ -49429,7 +49460,7 @@
         <v>60.29</v>
       </c>
     </row>
-    <row r="948" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="948" spans="1:11">
       <c r="A948" s="15">
         <v>45518</v>
       </c>
@@ -49465,7 +49496,7 @@
         <v>89.06</v>
       </c>
     </row>
-    <row r="949" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="949" spans="1:11">
       <c r="A949" s="15">
         <v>45525</v>
       </c>
@@ -49501,7 +49532,7 @@
         <v>67.78</v>
       </c>
     </row>
-    <row r="950" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="950" spans="1:11">
       <c r="A950" s="15">
         <v>45532</v>
       </c>
@@ -49537,7 +49568,7 @@
         <v>76.260000000000005</v>
       </c>
     </row>
-    <row r="951" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="951" spans="1:11">
       <c r="A951" s="15">
         <v>45539</v>
       </c>
@@ -49573,7 +49604,7 @@
         <v>70.38</v>
       </c>
     </row>
-    <row r="952" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="952" spans="1:11">
       <c r="A952" s="15">
         <v>45546</v>
       </c>
@@ -49609,7 +49640,7 @@
         <v>70.66</v>
       </c>
     </row>
-    <row r="953" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="953" spans="1:11">
       <c r="A953" s="15">
         <v>45553</v>
       </c>
@@ -49645,7 +49676,7 @@
         <v>69.36</v>
       </c>
     </row>
-    <row r="954" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="954" spans="1:11">
       <c r="A954" s="15">
         <v>45560</v>
       </c>
@@ -49681,7 +49712,7 @@
         <v>75.61</v>
       </c>
     </row>
-    <row r="955" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="955" spans="1:11">
       <c r="A955" s="15">
         <v>45567</v>
       </c>
@@ -49717,7 +49748,7 @@
         <v>56.15</v>
       </c>
     </row>
-    <row r="956" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="956" spans="1:11">
       <c r="A956" s="15">
         <v>45574</v>
       </c>
@@ -49753,7 +49784,7 @@
         <v>54.22</v>
       </c>
     </row>
-    <row r="957" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="957" spans="1:11">
       <c r="A957" s="15">
         <v>45581</v>
       </c>
@@ -49789,7 +49820,7 @@
         <v>70.319999999999993</v>
       </c>
     </row>
-    <row r="958" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="958" spans="1:11">
       <c r="A958" s="15">
         <v>45588</v>
       </c>
@@ -49825,7 +49856,7 @@
         <v>75.64</v>
       </c>
     </row>
-    <row r="959" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="959" spans="1:11">
       <c r="A959" s="15">
         <v>45595</v>
       </c>
@@ -49861,7 +49892,7 @@
         <v>60.95</v>
       </c>
     </row>
-    <row r="960" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="960" spans="1:11">
       <c r="A960" s="15">
         <v>45602</v>
       </c>
@@ -49897,7 +49928,7 @@
         <v>56.27</v>
       </c>
     </row>
-    <row r="961" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="961" spans="1:11">
       <c r="A961" s="15">
         <v>45609</v>
       </c>
@@ -49933,7 +49964,7 @@
         <v>66.66</v>
       </c>
     </row>
-    <row r="962" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="962" spans="1:11">
       <c r="A962" s="15">
         <v>45616</v>
       </c>
@@ -49969,7 +50000,7 @@
         <v>55.21</v>
       </c>
     </row>
-    <row r="963" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="963" spans="1:11">
       <c r="A963" s="15">
         <v>45623</v>
       </c>
@@ -50020,7 +50051,7 @@
         <v>44.97</v>
       </c>
     </row>
-    <row r="964" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="964" spans="1:11">
       <c r="A964" s="15">
         <v>45630</v>
       </c>
@@ -50056,7 +50087,7 @@
         <v>65.58</v>
       </c>
     </row>
-    <row r="965" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="965" spans="1:11">
       <c r="A965" s="15">
         <v>45637</v>
       </c>
@@ -50092,7 +50123,7 @@
         <v>50.55</v>
       </c>
     </row>
-    <row r="966" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="966" spans="1:11">
       <c r="A966" s="15">
         <v>45644</v>
       </c>
@@ -50128,7 +50159,7 @@
         <v>55.02</v>
       </c>
     </row>
-    <row r="967" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="967" spans="1:11">
       <c r="A967" s="15">
         <v>45651</v>
       </c>
@@ -50164,7 +50195,7 @@
         <v>72.16</v>
       </c>
     </row>
-    <row r="968" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="968" spans="1:11">
       <c r="A968" s="15">
         <v>45658</v>
       </c>
@@ -50200,7 +50231,7 @@
         <v>90.01</v>
       </c>
     </row>
-    <row r="969" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="969" spans="1:11">
       <c r="A969" s="15">
         <v>45665</v>
       </c>
@@ -50236,7 +50267,7 @@
         <v>55.05</v>
       </c>
     </row>
-    <row r="970" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="970" spans="1:11">
       <c r="A970" s="15">
         <v>45672</v>
       </c>
@@ -50272,7 +50303,7 @@
         <v>58.09</v>
       </c>
     </row>
-    <row r="971" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="971" spans="1:11">
       <c r="A971" s="15">
         <v>45679</v>
       </c>
@@ -50308,7 +50339,7 @@
         <v>45.88</v>
       </c>
     </row>
-    <row r="972" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="972" spans="1:11">
       <c r="A972" s="15">
         <v>45686</v>
       </c>
@@ -50344,7 +50375,7 @@
         <v>65.86</v>
       </c>
     </row>
-    <row r="973" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="973" spans="1:11">
       <c r="A973" s="15">
         <v>45693</v>
       </c>
@@ -50380,7 +50411,7 @@
         <v>54.2</v>
       </c>
     </row>
-    <row r="974" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="974" spans="1:11">
       <c r="A974" s="15">
         <v>45700</v>
       </c>
@@ -50416,7 +50447,7 @@
         <v>52.44</v>
       </c>
     </row>
-    <row r="975" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="975" spans="1:11">
       <c r="A975" s="15">
         <v>45707</v>
       </c>
@@ -50452,7 +50483,7 @@
         <v>49.61</v>
       </c>
     </row>
-    <row r="976" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="976" spans="1:11">
       <c r="A976" s="15">
         <v>45714</v>
       </c>
@@ -50488,7 +50519,7 @@
         <v>51.43</v>
       </c>
     </row>
-    <row r="977" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="977" spans="1:11">
       <c r="A977" s="15">
         <v>45721</v>
       </c>
@@ -50524,7 +50555,7 @@
         <v>69.739999999999995</v>
       </c>
     </row>
-    <row r="978" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="978" spans="1:11">
       <c r="A978" s="15">
         <v>45728</v>
       </c>
@@ -50560,7 +50591,7 @@
         <v>70.47</v>
       </c>
     </row>
-    <row r="979" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="979" spans="1:11">
       <c r="A979" s="15">
         <v>45735</v>
       </c>
@@ -50596,7 +50627,7 @@
         <v>53.55</v>
       </c>
     </row>
-    <row r="980" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="980" spans="1:11">
       <c r="A980" s="15">
         <v>45742</v>
       </c>
@@ -50632,7 +50663,7 @@
         <v>54.17</v>
       </c>
     </row>
-    <row r="981" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="981" spans="1:11">
       <c r="A981" s="15">
         <v>45749</v>
       </c>
@@ -50668,7 +50699,7 @@
         <v>83.68</v>
       </c>
     </row>
-    <row r="982" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="982" spans="1:11">
       <c r="A982" s="15">
         <v>45756</v>
       </c>
@@ -50704,7 +50735,7 @@
         <v>60.04</v>
       </c>
     </row>
-    <row r="983" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="983" spans="1:11">
       <c r="A983" s="15">
         <v>45763</v>
       </c>
@@ -50740,7 +50771,7 @@
         <v>65.53</v>
       </c>
     </row>
-    <row r="984" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="984" spans="1:11">
       <c r="A984" s="15">
         <v>45770</v>
       </c>
@@ -50776,7 +50807,7 @@
         <v>50.87</v>
       </c>
     </row>
-    <row r="985" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="985" spans="1:11">
       <c r="A985" s="15">
         <v>45777</v>
       </c>
@@ -50812,7 +50843,7 @@
         <v>77.239999999999995</v>
       </c>
     </row>
-    <row r="986" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="986" spans="1:11">
       <c r="A986" s="15">
         <v>45784</v>
       </c>
@@ -50848,7 +50879,7 @@
         <v>51.46</v>
       </c>
     </row>
-    <row r="987" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="987" spans="1:11">
       <c r="A987" s="15">
         <v>45791</v>
       </c>
@@ -50884,7 +50915,7 @@
         <v>65.03</v>
       </c>
     </row>
-    <row r="988" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="988" spans="1:11">
       <c r="A988" s="15">
         <v>45798</v>
       </c>
@@ -50920,7 +50951,7 @@
         <v>60.35</v>
       </c>
     </row>
-    <row r="989" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="989" spans="1:11">
       <c r="A989" s="15">
         <v>45805</v>
       </c>
@@ -50956,7 +50987,7 @@
         <v>53.2</v>
       </c>
     </row>
-    <row r="990" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="990" spans="1:11">
       <c r="A990" s="15">
         <v>45812</v>
       </c>
@@ -50992,7 +51023,7 @@
         <v>67.680000000000007</v>
       </c>
     </row>
-    <row r="991" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="991" spans="1:11">
       <c r="A991" s="15">
         <v>45819</v>
       </c>
@@ -51028,7 +51059,7 @@
         <v>73.680000000000007</v>
       </c>
     </row>
-    <row r="992" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="992" spans="1:11">
       <c r="A992" s="15">
         <v>45826</v>
       </c>
@@ -51064,7 +51095,7 @@
         <v>52.15</v>
       </c>
     </row>
-    <row r="993" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="993" spans="1:11">
       <c r="A993" s="15">
         <v>45833</v>
       </c>
@@ -51100,7 +51131,7 @@
         <v>72.73</v>
       </c>
     </row>
-    <row r="994" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="994" spans="1:11">
       <c r="A994" s="15">
         <v>45840</v>
       </c>
@@ -51136,7 +51167,7 @@
         <v>54.77</v>
       </c>
     </row>
-    <row r="995" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="995" spans="1:11">
       <c r="A995" s="15">
         <v>45847</v>
       </c>
@@ -51172,7 +51203,7 @@
         <v>69.709999999999994</v>
       </c>
     </row>
-    <row r="996" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="996" spans="1:11">
       <c r="A996" s="15">
         <v>45854</v>
       </c>
@@ -51208,7 +51239,7 @@
         <v>57.22</v>
       </c>
     </row>
-    <row r="997" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="997" spans="1:11">
       <c r="A997" s="15">
         <v>45861</v>
       </c>
@@ -51244,7 +51275,7 @@
         <v>64.98</v>
       </c>
     </row>
-    <row r="998" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="998" spans="1:11">
       <c r="A998" s="15">
         <v>45868</v>
       </c>
@@ -51280,7 +51311,7 @@
         <v>64.89</v>
       </c>
     </row>
-    <row r="999" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="999" spans="1:11">
       <c r="A999" s="15">
         <v>45875</v>
       </c>
@@ -51316,7 +51347,7 @@
         <v>35.96</v>
       </c>
     </row>
-    <row r="1000" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1000" spans="1:11">
       <c r="A1000" s="15">
         <v>45882</v>
       </c>
@@ -51352,7 +51383,7 @@
         <v>69.55</v>
       </c>
     </row>
-    <row r="1001" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1001" spans="1:11">
       <c r="A1001" s="15">
         <v>45889</v>
       </c>
@@ -51388,7 +51419,7 @@
         <v>44.79</v>
       </c>
     </row>
-    <row r="1002" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1002" spans="1:11">
       <c r="A1002" s="15">
         <v>45896</v>
       </c>
@@ -51424,7 +51455,7 @@
         <v>44.7</v>
       </c>
     </row>
-    <row r="1003" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1003" spans="1:11">
       <c r="A1003" s="15">
         <v>45903</v>
       </c>
@@ -51460,7 +51491,7 @@
         <v>63.56</v>
       </c>
     </row>
-    <row r="1004" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1004" spans="1:11">
       <c r="A1004" s="15">
         <v>45910</v>
       </c>
@@ -51496,7 +51527,7 @@
         <v>71.06</v>
       </c>
     </row>
-    <row r="1005" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1005" spans="1:11">
       <c r="A1005" s="15">
         <v>45917</v>
       </c>
@@ -51532,7 +51563,7 @@
         <v>71.959999999999994</v>
       </c>
     </row>
-    <row r="1006" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1006" spans="1:11">
       <c r="A1006" s="15">
         <v>45924</v>
       </c>
@@ -51568,7 +51599,7 @@
         <v>66.77</v>
       </c>
     </row>
-    <row r="1007" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1007" spans="1:11">
       <c r="A1007" s="15">
         <v>45931</v>
       </c>
@@ -51604,7 +51635,7 @@
         <v>71.13</v>
       </c>
     </row>
-    <row r="1008" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1008" spans="1:11">
       <c r="A1008" s="15">
         <v>45938</v>
       </c>
@@ -51640,7 +51671,7 @@
         <v>69.27</v>
       </c>
     </row>
-    <row r="1009" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1009" spans="1:11">
       <c r="A1009" s="15">
         <v>45945</v>
       </c>
@@ -51676,7 +51707,7 @@
         <v>50.98</v>
       </c>
     </row>
-    <row r="1010" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1010" spans="1:11">
       <c r="A1010" s="15">
         <v>45952</v>
       </c>
@@ -51712,7 +51743,7 @@
         <v>52.1</v>
       </c>
     </row>
-    <row r="1011" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1011" spans="1:11">
       <c r="A1011" s="15">
         <v>45959</v>
       </c>
@@ -51748,7 +51779,7 @@
         <v>55.36</v>
       </c>
     </row>
-    <row r="1012" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1012" spans="1:11">
       <c r="A1012" s="15">
         <v>45966</v>
       </c>
@@ -51784,7 +51815,7 @@
         <v>40.86</v>
       </c>
     </row>
-    <row r="1013" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1013" spans="1:11">
       <c r="A1013" s="15">
         <v>45973</v>
       </c>
@@ -51820,7 +51851,7 @@
         <v>39.42</v>
       </c>
     </row>
-    <row r="1014" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1014" spans="1:11">
       <c r="A1014" s="15">
         <v>45980</v>
       </c>
@@ -51856,7 +51887,7 @@
         <v>51.59</v>
       </c>
     </row>
-    <row r="1015" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1015" spans="1:11">
       <c r="A1015" s="15">
         <v>45987</v>
       </c>
@@ -51892,7 +51923,7 @@
         <v>50.29</v>
       </c>
     </row>
-    <row r="1016" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1016" spans="1:11">
       <c r="A1016" s="15">
         <v>45994</v>
       </c>
@@ -51928,7 +51959,7 @@
         <v>47.59</v>
       </c>
     </row>
-    <row r="1017" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1017" spans="1:11">
       <c r="A1017" s="15">
         <v>46001</v>
       </c>
@@ -51964,7 +51995,7 @@
         <v>45.89</v>
       </c>
     </row>
-    <row r="1018" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1018" spans="1:11">
       <c r="A1018" s="15">
         <v>46008</v>
       </c>
@@ -52000,7 +52031,7 @@
         <v>46.38</v>
       </c>
     </row>
-    <row r="1019" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1019" spans="1:11">
       <c r="A1019" s="15">
         <v>46015</v>
       </c>
@@ -52036,7 +52067,7 @@
         <v>49.27</v>
       </c>
     </row>
-    <row r="1020" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1020" spans="1:11">
       <c r="A1020" s="15">
         <v>46022</v>
       </c>
@@ -52072,7 +52103,7 @@
         <v>48.97</v>
       </c>
     </row>
-    <row r="1021" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1021" spans="1:11">
       <c r="A1021" s="15">
         <v>46029</v>
       </c>
@@ -52108,7 +52139,7 @@
         <v>50.86</v>
       </c>
     </row>
-    <row r="1022" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1022" spans="1:11">
       <c r="A1022" s="15">
         <v>46036</v>
       </c>
@@ -52144,7 +52175,7 @@
         <v>50.37</v>
       </c>
     </row>
-    <row r="1023" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1023" spans="1:11">
       <c r="A1023" s="15">
         <v>46043</v>
       </c>
@@ -52180,7 +52211,7 @@
         <v>60.31</v>
       </c>
     </row>
-    <row r="1024" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1024" spans="1:11">
       <c r="A1024" s="15">
         <v>46050</v>
       </c>
@@ -52216,7 +52247,7 @@
         <v>46.41</v>
       </c>
     </row>
-    <row r="1025" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1025" spans="1:11">
       <c r="A1025" s="15">
         <v>46057</v>
       </c>
@@ -52252,7 +52283,7 @@
         <v>64.569999999999993</v>
       </c>
     </row>
-    <row r="1026" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1026" spans="1:11">
       <c r="A1026" s="15">
         <v>46064</v>
       </c>
@@ -52288,7 +52319,7 @@
         <v>63.52</v>
       </c>
     </row>
-    <row r="1027" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1027" spans="1:11">
       <c r="A1027" s="15">
         <v>46071</v>
       </c>
@@ -52339,7 +52370,7 @@
         <v>47.62</v>
       </c>
     </row>
-    <row r="1028" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1028" spans="1:11">
       <c r="A1028" s="15">
         <v>46078</v>
       </c>
@@ -52375,7 +52406,7 @@
         <v>64.84</v>
       </c>
     </row>
-    <row r="1029" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1029" spans="1:11">
       <c r="A1029" s="15">
         <v>46085</v>
       </c>
@@ -52411,7 +52442,7 @@
         <v>49.98</v>
       </c>
     </row>
-    <row r="1030" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1030" spans="1:11">
       <c r="A1030" s="15">
         <v>46092</v>
       </c>
@@ -52447,7 +52478,7 @@
         <v>62.78</v>
       </c>
     </row>
-    <row r="1031" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1031" spans="1:11">
       <c r="A1031" s="15">
         <v>46099</v>
       </c>
@@ -52481,6 +52512,57 @@
       </c>
       <c r="K1031" s="7">
         <v>68.13</v>
+      </c>
+    </row>
+    <row r="1032" spans="1:11">
+      <c r="A1032" s="15">
+        <v>46106</v>
+      </c>
+      <c r="B1032" s="15">
+        <v>46107</v>
+      </c>
+      <c r="C1032" s="17">
+        <v>0.41666666666666802</v>
+      </c>
+      <c r="D1032" s="15" t="str">
+        <f t="shared" ref="D1032" si="17">IF(
+ AND(
+  B1032 &gt;= IF(
+         YEAR(B1032)&gt;=2007,
+         DATE(YEAR(B1032),3,14)-WEEKDAY(DATE(YEAR(B1032),3,14),1)+1 + TIME(2,0,0),
+         DATE(YEAR(B1032),4,7)-WEEKDAY(DATE(YEAR(B1032),4,7),1)+1 + TIME(2,0,0)
+       ),
+  B1032 &lt;  IF(
+         YEAR(B1032)&gt;=2007,
+         DATE(YEAR(B1032),11,7)-WEEKDAY(DATE(YEAR(B1032),11,7),1)+1 + TIME(2,0,0),
+         DATE(YEAR(B1032),10,31)-WEEKDAY(DATE(YEAR(B1032),10,31),1) + TIME(2,0,0)
+       )
+ ),
+ "UTC-4",
+ "UTC-5"
+)</f>
+        <v>UTC-4</v>
+      </c>
+      <c r="E1032" s="7">
+        <v>68.52</v>
+      </c>
+      <c r="F1032" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1032" s="7">
+        <v>31.75</v>
+      </c>
+      <c r="H1032" s="9">
+        <v>82</v>
+      </c>
+      <c r="I1032" s="9">
+        <v>100</v>
+      </c>
+      <c r="J1032" s="9">
+        <v>200</v>
+      </c>
+      <c r="K1032" s="7">
+        <v>47.03</v>
       </c>
     </row>
   </sheetData>
@@ -52493,7 +52575,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{115169E1-C49D-409D-8D5D-92B2FD26EE0D}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData/>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -52504,9 +52586,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44703C2A-D4C6-BD4F-B5E9-874C8C9CFE9E}">
   <dimension ref="B2:C3"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.5"/>
   <sheetData>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:3">
       <c r="B2" t="s">
         <v>7</v>
       </c>
@@ -52514,7 +52596,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:3">
       <c r="B3" t="s">
         <v>8</v>
       </c>

--- a/data/sentiment/NAAIM Exposure Index.xlsx
+++ b/data/sentiment/NAAIM Exposure Index.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\sentiment\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\sentiment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C7585D5-65BD-47F4-8FBA-634CED33CC5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC547176-F2EE-405B-AB46-70E98873E482}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NAAIM" sheetId="1" r:id="rId1"/>
@@ -90,31 +90,31 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="178" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="179" formatCode="0.00_ "/>
-    <numFmt numFmtId="180" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="0.00_ "/>
+    <numFmt numFmtId="167" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="18"/>
       <color theme="3"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri Light"/>
       <family val="2"/>
       <scheme val="major"/>
     </font>
@@ -122,7 +122,7 @@
       <b/>
       <sz val="15"/>
       <color theme="3"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -130,7 +130,7 @@
       <b/>
       <sz val="13"/>
       <color theme="3"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -138,35 +138,35 @@
       <b/>
       <sz val="11"/>
       <color theme="3"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C5700"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -174,7 +174,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -182,14 +182,14 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -197,14 +197,14 @@
       <b/>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -212,7 +212,7 @@
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -220,20 +220,20 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -242,7 +242,7 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -600,7 +600,7 @@
     <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -608,92 +608,92 @@
   <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="43"/>
-    <xf numFmtId="177" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="20" fillId="0" borderId="0" xfId="42" applyFont="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" xfId="42" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="179" fontId="20" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="20" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="178" fontId="20" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="20" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="176" fontId="21" fillId="0" borderId="0" xfId="42" applyFont="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="21" fillId="0" borderId="0" xfId="42" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="179" fontId="21" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="21" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="178" fontId="21" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="21" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="176" fontId="21" fillId="0" borderId="0" xfId="42" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="21" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="21" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="21" fillId="0" borderId="0" xfId="42" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="21" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="21" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="180" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="180" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="44">
-    <cellStyle name="20% - 강조색1" xfId="19" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20% - 강조색2" xfId="23" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20% - 강조색3" xfId="27" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20% - 강조색4" xfId="31" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20% - 강조색5" xfId="35" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20% - 강조색6" xfId="39" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="40% - 강조색1" xfId="20" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40% - 강조색2" xfId="24" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40% - 강조색3" xfId="28" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40% - 강조색4" xfId="32" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40% - 강조색5" xfId="36" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40% - 강조색6" xfId="40" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="60% - 강조색1" xfId="21" builtinId="32" customBuiltin="1"/>
-    <cellStyle name="60% - 강조색2" xfId="25" builtinId="36" customBuiltin="1"/>
-    <cellStyle name="60% - 강조색3" xfId="29" builtinId="40" customBuiltin="1"/>
-    <cellStyle name="60% - 강조색4" xfId="33" builtinId="44" customBuiltin="1"/>
-    <cellStyle name="60% - 강조색5" xfId="37" builtinId="48" customBuiltin="1"/>
-    <cellStyle name="60% - 강조색6" xfId="41" builtinId="52" customBuiltin="1"/>
-    <cellStyle name="강조색1" xfId="18" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="강조색2" xfId="22" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="강조색3" xfId="26" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="강조색4" xfId="30" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="강조색5" xfId="34" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="강조색6" xfId="38" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="경고문" xfId="14" builtinId="11" customBuiltin="1"/>
-    <cellStyle name="계산" xfId="11" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="나쁨" xfId="7" builtinId="27" customBuiltin="1"/>
-    <cellStyle name="메모" xfId="15" builtinId="10" customBuiltin="1"/>
-    <cellStyle name="보통" xfId="8" builtinId="28" customBuiltin="1"/>
-    <cellStyle name="설명 텍스트" xfId="16" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="셀 확인" xfId="13" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="쉼표" xfId="42" builtinId="3"/>
-    <cellStyle name="연결된 셀" xfId="12" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="요약" xfId="17" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="입력" xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="제목" xfId="1" builtinId="15" customBuiltin="1"/>
-    <cellStyle name="제목 1" xfId="2" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="제목 2" xfId="3" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="제목 3" xfId="4" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="제목 4" xfId="5" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="좋음" xfId="6" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="출력" xfId="10" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="하이퍼링크" xfId="43" builtinId="8"/>
+    <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - Accent4" xfId="31" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - Accent5" xfId="35" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - Accent6" xfId="39" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - Accent1" xfId="20" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - Accent2" xfId="24" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - Accent3" xfId="28" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - Accent4" xfId="32" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - Accent5" xfId="36" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - Accent6" xfId="40" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - Accent1" xfId="21" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - Accent2" xfId="25" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - Accent3" xfId="29" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - Accent4" xfId="33" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - Accent5" xfId="37" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - Accent6" xfId="41" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="Accent1" xfId="18" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="Accent2" xfId="22" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="Accent3" xfId="26" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Comma" xfId="42" builtinId="3"/>
+    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Hyperlink" xfId="43" builtinId="8"/>
+    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -711,7 +711,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -3851,6 +3851,9 @@
                 <c:pt idx="1032">
                   <c:v>46121</c:v>
                 </c:pt>
+                <c:pt idx="1033">
+                  <c:v>46128</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -6958,6 +6961,9 @@
                 </c:pt>
                 <c:pt idx="1032">
                   <c:v>69.38</c:v>
+                </c:pt>
+                <c:pt idx="1033">
+                  <c:v>79.489999999999995</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7174,7 +7180,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -10322,6 +10328,9 @@
                 <c:pt idx="1032">
                   <c:v>46121</c:v>
                 </c:pt>
+                <c:pt idx="1033">
+                  <c:v>46128</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -13429,6 +13438,9 @@
                 </c:pt>
                 <c:pt idx="1032">
                   <c:v>51.31</c:v>
+                </c:pt>
+                <c:pt idx="1033">
+                  <c:v>68.87</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14839,9 +14851,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -14879,7 +14891,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -14985,7 +14997,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -15127,7 +15139,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -15135,24 +15147,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K1034"/>
-  <sheetFormatPr defaultColWidth="8.8984375" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:K1035"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.69921875" style="15" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14" style="15" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.19921875" style="17" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.5" style="15" customWidth="1"/>
-    <col min="5" max="5" width="11.09765625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.7265625" style="15" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.36328125" style="15" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.26953125" style="17" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.453125" style="15" customWidth="1"/>
+    <col min="5" max="5" width="11.08984375" style="7" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14" style="8" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.3984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.19921875" style="9" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.3984375" style="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.36328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.1796875" style="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.36328125" style="9" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="15" style="9" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="21.69921875" style="7" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="8.8984375" style="10"/>
+    <col min="11" max="11" width="21.7265625" style="7" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.90625" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" s="6" customFormat="1">
       <c r="A1" s="2" t="s">
         <v>10</v>
       </c>
@@ -15187,7 +15199,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11">
       <c r="A2" s="15">
         <v>38903</v>
       </c>
@@ -15238,7 +15250,7 @@
         <v>55.55</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11">
       <c r="A3" s="15">
         <v>38910</v>
       </c>
@@ -15289,7 +15301,7 @@
         <v>47.84</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11">
       <c r="A4" s="15">
         <v>38903</v>
       </c>
@@ -15325,7 +15337,7 @@
         <v>55.549999722194443</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11">
       <c r="A5" s="15">
         <v>38910</v>
       </c>
@@ -15361,7 +15373,7 @@
         <v>47.838896308338889</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11">
       <c r="A6" s="15">
         <v>38917</v>
       </c>
@@ -15397,7 +15409,7 @@
         <v>38.170438823780898</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11">
       <c r="A7" s="15">
         <v>38924</v>
       </c>
@@ -15433,7 +15445,7 @@
         <v>33.778460222455372</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11">
       <c r="A8" s="15">
         <v>38931</v>
       </c>
@@ -15469,7 +15481,7 @@
         <v>43.692625871599382</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11">
       <c r="A9" s="15">
         <v>38938</v>
       </c>
@@ -15505,7 +15517,7 @@
         <v>47.483927790753583</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11">
       <c r="A10" s="15">
         <v>38945</v>
       </c>
@@ -15541,7 +15553,7 @@
         <v>56.524684873071166</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11">
       <c r="A11" s="15">
         <v>38952</v>
       </c>
@@ -15577,7 +15589,7 @@
         <v>45.170475778833321</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11">
       <c r="A12" s="15">
         <v>38959</v>
       </c>
@@ -15613,7 +15625,7 @@
         <v>45.170475778833321</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11">
       <c r="A13" s="15">
         <v>38966</v>
       </c>
@@ -15649,7 +15661,7 @@
         <v>50.374290674884271</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11">
       <c r="A14" s="15">
         <v>38973</v>
       </c>
@@ -15685,7 +15697,7 @@
         <v>56.228640389040173</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11">
       <c r="A15" s="15">
         <v>38980</v>
       </c>
@@ -15721,7 +15733,7 @@
         <v>31.264996401726965</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11">
       <c r="A16" s="15">
         <v>38987</v>
       </c>
@@ -15757,7 +15769,7 @@
         <v>55.807410979021469</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:11">
       <c r="A17" s="15">
         <v>38994</v>
       </c>
@@ -15793,7 +15805,7 @@
         <v>59.404629449227272</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:11">
       <c r="A18" s="15">
         <v>39001</v>
       </c>
@@ -15829,7 +15841,7 @@
         <v>59.825434763385545</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:11">
       <c r="A19" s="15">
         <v>39008</v>
       </c>
@@ -15865,7 +15877,7 @@
         <v>33.215082952435786</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:11">
       <c r="A20" s="15">
         <v>39015</v>
       </c>
@@ -15901,7 +15913,7 @@
         <v>53.121506002748077</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:11">
       <c r="A21" s="15">
         <v>39022</v>
       </c>
@@ -15937,7 +15949,7 @@
         <v>53.864396997357062</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:11">
       <c r="A22" s="15">
         <v>39029</v>
       </c>
@@ -15973,7 +15985,7 @@
         <v>46.653652879834993</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:11">
       <c r="A23" s="15">
         <v>39036</v>
       </c>
@@ -16009,7 +16021,7 @@
         <v>61.297793607386772</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:11">
       <c r="A24" s="15">
         <v>39043</v>
       </c>
@@ -16045,7 +16057,7 @@
         <v>20.824828195876073</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:11">
       <c r="A25" s="15">
         <v>39050</v>
       </c>
@@ -16081,7 +16093,7 @@
         <v>38.414042173363363</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:11">
       <c r="A26" s="15">
         <v>39057</v>
       </c>
@@ -16117,7 +16129,7 @@
         <v>58.029540018794734</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:11">
       <c r="A27" s="15">
         <v>39064</v>
       </c>
@@ -16153,7 +16165,7 @@
         <v>19.415261547359616</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:11">
       <c r="A28" s="15">
         <v>39071</v>
       </c>
@@ -16189,7 +16201,7 @@
         <v>22.354395725773102</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:11">
       <c r="A29" s="15">
         <v>39078</v>
       </c>
@@ -16225,7 +16237,7 @@
         <v>35.213204259954928</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:11">
       <c r="A30" s="15">
         <v>39085</v>
       </c>
@@ -16261,7 +16273,7 @@
         <v>32.236442245024186</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:11">
       <c r="A31" s="15">
         <v>39092</v>
       </c>
@@ -16297,7 +16309,7 @@
         <v>65.212862654704111</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:11">
       <c r="A32" s="15">
         <v>39099</v>
       </c>
@@ -16333,7 +16345,7 @@
         <v>27.899999503569333</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:11">
       <c r="A33" s="15">
         <v>39106</v>
       </c>
@@ -16369,7 +16381,7 @@
         <v>42.723911860082509</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:11">
       <c r="A34" s="15">
         <v>39113</v>
       </c>
@@ -16405,7 +16417,7 @@
         <v>49.378006237595294</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:11">
       <c r="A35" s="15">
         <v>39120</v>
       </c>
@@ -16441,7 +16453,7 @@
         <v>45.927163507298019</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:11">
       <c r="A36" s="15">
         <v>39127</v>
       </c>
@@ -16477,7 +16489,7 @@
         <v>55.649805268718424</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:11">
       <c r="A37" s="15">
         <v>39134</v>
       </c>
@@ -16513,7 +16525,7 @@
         <v>52.764818137257436</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:11">
       <c r="A38" s="15">
         <v>39141</v>
       </c>
@@ -16549,7 +16561,7 @@
         <v>53.726231363347424</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:11">
       <c r="A39" s="15">
         <v>39148</v>
       </c>
@@ -16585,7 +16597,7 @@
         <v>48.602880573068916</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:11">
       <c r="A40" s="15">
         <v>39155</v>
       </c>
@@ -16621,7 +16633,7 @@
         <v>68.635171039352031</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:11">
       <c r="A41" s="15">
         <v>39162</v>
       </c>
@@ -16657,7 +16669,7 @@
         <v>54.906588487696794</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:11">
       <c r="A42" s="15">
         <v>39169</v>
       </c>
@@ -16693,7 +16705,7 @@
         <v>61.630606010506028</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:11">
       <c r="A43" s="15">
         <v>39176</v>
       </c>
@@ -16729,7 +16741,7 @@
         <v>64.537968733792852</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:11">
       <c r="A44" s="15">
         <v>39183</v>
       </c>
@@ -16765,7 +16777,7 @@
         <v>57.825060311252592</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:11">
       <c r="A45" s="15">
         <v>39190</v>
       </c>
@@ -16801,7 +16813,7 @@
         <v>69.279479346364909</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:11">
       <c r="A46" s="15">
         <v>39197</v>
       </c>
@@ -16837,7 +16849,7 @@
         <v>59.001416591157486</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:11">
       <c r="A47" s="15">
         <v>39204</v>
       </c>
@@ -16873,7 +16885,7 @@
         <v>59.063995424924954</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:11">
       <c r="A48" s="15">
         <v>39211</v>
       </c>
@@ -16909,7 +16921,7 @@
         <v>55.064860745205635</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:11">
       <c r="A49" s="15">
         <v>39218</v>
       </c>
@@ -16945,7 +16957,7 @@
         <v>51.819247148139851</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:11">
       <c r="A50" s="15">
         <v>39225</v>
       </c>
@@ -16981,7 +16993,7 @@
         <v>53.983793864455286</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:11">
       <c r="A51" s="15">
         <v>39232</v>
       </c>
@@ -17017,7 +17029,7 @@
         <v>48.786852991286374</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:11">
       <c r="A52" s="15">
         <v>39239</v>
       </c>
@@ -17053,7 +17065,7 @@
         <v>62.811083593759328</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:11">
       <c r="A53" s="15">
         <v>39246</v>
       </c>
@@ -17089,7 +17101,7 @@
         <v>65.542340513594723</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:11">
       <c r="A54" s="15">
         <v>39253</v>
       </c>
@@ -17125,7 +17137,7 @@
         <v>67.954431672633518</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:11">
       <c r="A55" s="15">
         <v>39260</v>
       </c>
@@ -17161,7 +17173,7 @@
         <v>55.826175891531534</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:11">
       <c r="A56" s="15">
         <v>39268</v>
       </c>
@@ -17197,7 +17209,7 @@
         <v>60.176790324426577</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:11">
       <c r="A57" s="15">
         <v>39274</v>
       </c>
@@ -17233,7 +17245,7 @@
         <v>51.354938031690303</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:11">
       <c r="A58" s="15">
         <v>39281</v>
       </c>
@@ -17269,7 +17281,7 @@
         <v>45.888802797874582</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:11">
       <c r="A59" s="15">
         <v>39288</v>
       </c>
@@ -17305,7 +17317,7 @@
         <v>63.76609180512709</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:11">
       <c r="A60" s="15">
         <v>39295</v>
       </c>
@@ -17341,7 +17353,7 @@
         <v>59.657354953098618</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:11">
       <c r="A61" s="15">
         <v>39302</v>
       </c>
@@ -17377,7 +17389,7 @@
         <v>65.099669293697346</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:11">
       <c r="A62" s="15">
         <v>39309</v>
       </c>
@@ -17413,7 +17425,7 @@
         <v>57.034529015325447</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:11">
       <c r="A63" s="15">
         <v>39316</v>
       </c>
@@ -17449,7 +17461,7 @@
         <v>52.701658833000693</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:11">
       <c r="A64" s="15">
         <v>39323</v>
       </c>
@@ -17485,7 +17497,7 @@
         <v>72.566359583555496</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:11">
       <c r="A65" s="15">
         <v>39330</v>
       </c>
@@ -17521,7 +17533,7 @@
         <v>45.022968675258781</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:11">
       <c r="A66" s="15">
         <v>39337</v>
       </c>
@@ -17557,7 +17569,7 @@
         <v>69.603104472428257</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:11">
       <c r="A67" s="15">
         <v>39344</v>
       </c>
@@ -17608,7 +17620,7 @@
         <v>42.408304442812678</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:11">
       <c r="A68" s="15">
         <v>39351</v>
       </c>
@@ -17644,7 +17656,7 @@
         <v>38.186796212286225</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:11">
       <c r="A69" s="15">
         <v>39358</v>
       </c>
@@ -17680,7 +17692,7 @@
         <v>61.369548273391054</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:11">
       <c r="A70" s="15">
         <v>39365</v>
       </c>
@@ -17716,7 +17728,7 @@
         <v>56.227919122877815</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:11">
       <c r="A71" s="15">
         <v>39372</v>
       </c>
@@ -17752,7 +17764,7 @@
         <v>49.208363214031834</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:11">
       <c r="A72" s="15">
         <v>39379</v>
       </c>
@@ -17788,7 +17800,7 @@
         <v>65.850867379966061</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:11">
       <c r="A73" s="15">
         <v>39386</v>
       </c>
@@ -17824,7 +17836,7 @@
         <v>75.074716234904798</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:11">
       <c r="A74" s="15">
         <v>39393</v>
       </c>
@@ -17860,7 +17872,7 @@
         <v>52.534527153195896</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:11">
       <c r="A75" s="15">
         <v>39400</v>
       </c>
@@ -17896,7 +17908,7 @@
         <v>40.679745770792763</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:11">
       <c r="A76" s="15">
         <v>39407</v>
       </c>
@@ -17932,7 +17944,7 @@
         <v>60.493442596881707</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:11">
       <c r="A77" s="15">
         <v>39414</v>
       </c>
@@ -17968,7 +17980,7 @@
         <v>68.934714752142</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:11">
       <c r="A78" s="15">
         <v>39421</v>
       </c>
@@ -18004,7 +18016,7 @@
         <v>60.536316005812211</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:11">
       <c r="A79" s="15">
         <v>39428</v>
       </c>
@@ -18040,7 +18052,7 @@
         <v>69.021440028975547</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:11">
       <c r="A80" s="15">
         <v>39435</v>
       </c>
@@ -18076,7 +18088,7 @@
         <v>71.467344717337483</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:11">
       <c r="A81" s="15">
         <v>39442</v>
       </c>
@@ -18112,7 +18124,7 @@
         <v>50.496362770611753</v>
       </c>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:11">
       <c r="A82" s="15">
         <v>39449</v>
       </c>
@@ -18148,7 +18160,7 @@
         <v>55.229668567997003</v>
       </c>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:11">
       <c r="A83" s="15">
         <v>39456</v>
       </c>
@@ -18184,7 +18196,7 @@
         <v>75.139220764041383</v>
       </c>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:11">
       <c r="A84" s="15">
         <v>39463</v>
       </c>
@@ -18220,7 +18232,7 @@
         <v>58.387484404345059</v>
       </c>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:11">
       <c r="A85" s="15">
         <v>39470</v>
       </c>
@@ -18256,7 +18268,7 @@
         <v>74.040278246155765</v>
       </c>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:11">
       <c r="A86" s="15">
         <v>39477</v>
       </c>
@@ -18292,7 +18304,7 @@
         <v>62.164148383994373</v>
       </c>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:11">
       <c r="A87" s="15">
         <v>39484</v>
       </c>
@@ -18328,7 +18340,7 @@
         <v>70.447213919214661</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:11">
       <c r="A88" s="15">
         <v>39491</v>
       </c>
@@ -18364,7 +18376,7 @@
         <v>74.676338659280532</v>
       </c>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:11">
       <c r="A89" s="15">
         <v>39498</v>
       </c>
@@ -18400,7 +18412,7 @@
         <v>57.328488167363666</v>
       </c>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:11">
       <c r="A90" s="15">
         <v>39505</v>
       </c>
@@ -18436,7 +18448,7 @@
         <v>82.926777823027351</v>
       </c>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:11">
       <c r="A91" s="15">
         <v>39512</v>
       </c>
@@ -18472,7 +18484,7 @@
         <v>56.330836013124284</v>
       </c>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:11">
       <c r="A92" s="15">
         <v>39519</v>
       </c>
@@ -18508,7 +18520,7 @@
         <v>63.152843166400672</v>
       </c>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:11">
       <c r="A93" s="15">
         <v>39526</v>
       </c>
@@ -18544,7 +18556,7 @@
         <v>44.173359780366653</v>
       </c>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:11">
       <c r="A94" s="15">
         <v>39533</v>
       </c>
@@ -18580,7 +18592,7 @@
         <v>69.09468937538611</v>
       </c>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:11">
       <c r="A95" s="15">
         <v>39540</v>
       </c>
@@ -18616,7 +18628,7 @@
         <v>72.946618726802328</v>
       </c>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:11">
       <c r="A96" s="15">
         <v>39547</v>
       </c>
@@ -18652,7 +18664,7 @@
         <v>69.469947459315094</v>
       </c>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:11">
       <c r="A97" s="15">
         <v>39554</v>
       </c>
@@ -18688,7 +18700,7 @@
         <v>56.323052699867915</v>
       </c>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:11">
       <c r="A98" s="15">
         <v>39561</v>
       </c>
@@ -18724,7 +18736,7 @@
         <v>41.974862158849767</v>
       </c>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:11">
       <c r="A99" s="15">
         <v>39569</v>
       </c>
@@ -18760,7 +18772,7 @@
         <v>44.962229438992097</v>
       </c>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:11">
       <c r="A100" s="15">
         <v>39575</v>
       </c>
@@ -18796,7 +18808,7 @@
         <v>37.798178950335576</v>
       </c>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:11">
       <c r="A101" s="15">
         <v>39582</v>
       </c>
@@ -18832,7 +18844,7 @@
         <v>68.460251596471679</v>
       </c>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:11">
       <c r="A102" s="15">
         <v>39589</v>
       </c>
@@ -18868,7 +18880,7 @@
         <v>65.70356446097523</v>
       </c>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:11">
       <c r="A103" s="15">
         <v>39596</v>
       </c>
@@ -18904,7 +18916,7 @@
         <v>66.213667550072984</v>
       </c>
     </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:11">
       <c r="A104" s="15">
         <v>39603</v>
       </c>
@@ -18940,7 +18952,7 @@
         <v>65.788974489430842</v>
       </c>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:11">
       <c r="A105" s="15">
         <v>39610</v>
       </c>
@@ -18976,7 +18988,7 @@
         <v>78.830161121302538</v>
       </c>
     </row>
-    <row r="106" spans="1:11" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:11" s="11" customFormat="1">
       <c r="A106" s="15">
         <v>39617</v>
       </c>
@@ -19012,7 +19024,7 @@
         <v>65.083754207393383</v>
       </c>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:11">
       <c r="A107" s="15">
         <v>39624</v>
       </c>
@@ -19048,7 +19060,7 @@
         <v>55.264758647687017</v>
       </c>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:11">
       <c r="A108" s="15">
         <v>39631</v>
       </c>
@@ -19084,7 +19096,7 @@
         <v>52.723327174933317</v>
       </c>
     </row>
-    <row r="109" spans="1:11" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:11" s="11" customFormat="1">
       <c r="A109" s="15">
         <v>39638</v>
       </c>
@@ -19120,7 +19132,7 @@
         <v>75.848904583590468</v>
       </c>
     </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:11">
       <c r="A110" s="15">
         <v>39645</v>
       </c>
@@ -19156,7 +19168,7 @@
         <v>51.278326455349131</v>
       </c>
     </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:11">
       <c r="A111" s="15">
         <v>39652</v>
       </c>
@@ -19192,7 +19204,7 @@
         <v>57.909108469652679</v>
       </c>
     </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:11">
       <c r="A112" s="15">
         <v>39659</v>
       </c>
@@ -19228,7 +19240,7 @@
         <v>61.750517406739192</v>
       </c>
     </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:11">
       <c r="A113" s="15">
         <v>39666</v>
       </c>
@@ -19264,7 +19276,7 @@
         <v>52.661575232504951</v>
       </c>
     </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:11">
       <c r="A114" s="15">
         <v>39673</v>
       </c>
@@ -19300,7 +19312,7 @@
         <v>53.118250871076597</v>
       </c>
     </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:11">
       <c r="A115" s="15">
         <v>39681</v>
       </c>
@@ -19336,7 +19348,7 @@
         <v>50.104043997600584</v>
       </c>
     </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:11">
       <c r="A116" s="15">
         <v>39687</v>
       </c>
@@ -19372,7 +19384,7 @@
         <v>50.177676148596895</v>
       </c>
     </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:11">
       <c r="A117" s="15">
         <v>39694</v>
       </c>
@@ -19408,7 +19420,7 @@
         <v>65.073504542370074</v>
       </c>
     </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:11">
       <c r="A118" s="15">
         <v>39701</v>
       </c>
@@ -19444,7 +19456,7 @@
         <v>44.254182598587626</v>
       </c>
     </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:11">
       <c r="A119" s="15">
         <v>39708</v>
       </c>
@@ -19480,7 +19492,7 @@
         <v>47.422942867393644</v>
       </c>
     </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:11">
       <c r="A120" s="15">
         <v>39715</v>
       </c>
@@ -19516,7 +19528,7 @@
         <v>46.359571574198242</v>
       </c>
     </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:11">
       <c r="A121" s="15">
         <v>39722</v>
       </c>
@@ -19552,7 +19564,7 @@
         <v>33.405873873919091</v>
       </c>
     </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:11">
       <c r="A122" s="15">
         <v>39729</v>
       </c>
@@ -19588,7 +19600,7 @@
         <v>51.281080608690978</v>
       </c>
     </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:11">
       <c r="A123" s="15">
         <v>39736</v>
       </c>
@@ -19624,7 +19636,7 @@
         <v>40.551750201988128</v>
       </c>
     </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:11">
       <c r="A124" s="15">
         <v>39743</v>
       </c>
@@ -19660,7 +19672,7 @@
         <v>44.129844927173707</v>
       </c>
     </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:11">
       <c r="A125" s="15">
         <v>39750</v>
       </c>
@@ -19696,7 +19708,7 @@
         <v>53.882588406027168</v>
       </c>
     </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:11">
       <c r="A126" s="15">
         <v>39757</v>
       </c>
@@ -19732,7 +19744,7 @@
         <v>49.886350075701394</v>
       </c>
     </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:11">
       <c r="A127" s="15">
         <v>39764</v>
       </c>
@@ -19768,7 +19780,7 @@
         <v>44.405800463275128</v>
       </c>
     </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:11">
       <c r="A128" s="15">
         <v>39771</v>
       </c>
@@ -19804,7 +19816,7 @@
         <v>43.976952126529874</v>
       </c>
     </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:11">
       <c r="A129" s="15">
         <v>39778</v>
       </c>
@@ -19840,7 +19852,7 @@
         <v>57.854397526301433</v>
       </c>
     </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:11">
       <c r="A130" s="15">
         <v>39785</v>
       </c>
@@ -19876,7 +19888,7 @@
         <v>45.357327933111691</v>
       </c>
     </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:11">
       <c r="A131" s="15">
         <v>39792</v>
       </c>
@@ -19927,7 +19939,7 @@
         <v>49.214072926201013</v>
       </c>
     </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:11">
       <c r="A132" s="15">
         <v>39799</v>
       </c>
@@ -19963,7 +19975,7 @@
         <v>53.491406900967732</v>
       </c>
     </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:11">
       <c r="A133" s="15">
         <v>39806</v>
       </c>
@@ -19999,7 +20011,7 @@
         <v>55.286482576750558</v>
       </c>
     </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:11">
       <c r="A134" s="15">
         <v>39813</v>
       </c>
@@ -20035,7 +20047,7 @@
         <v>55.143723549589758</v>
       </c>
     </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:11">
       <c r="A135" s="15">
         <v>39820</v>
       </c>
@@ -20071,7 +20083,7 @@
         <v>51.012811516083978</v>
       </c>
     </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:11">
       <c r="A136" s="15">
         <v>39827</v>
       </c>
@@ -20107,7 +20119,7 @@
         <v>64.584992254313974</v>
       </c>
     </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:11">
       <c r="A137" s="15">
         <v>39834</v>
       </c>
@@ -20143,7 +20155,7 @@
         <v>51.036330889936345</v>
       </c>
     </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:11">
       <c r="A138" s="15">
         <v>39841</v>
       </c>
@@ -20179,7 +20191,7 @@
         <v>49.006860617093729</v>
       </c>
     </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:11">
       <c r="A139" s="15">
         <v>39848</v>
       </c>
@@ -20215,7 +20227,7 @@
         <v>33.08758938678627</v>
       </c>
     </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:11">
       <c r="A140" s="15">
         <v>39855</v>
       </c>
@@ -20251,7 +20263,7 @@
         <v>42.688334209137516</v>
       </c>
     </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:11">
       <c r="A141" s="15">
         <v>39862</v>
       </c>
@@ -20287,7 +20299,7 @@
         <v>49.836210913235156</v>
       </c>
     </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:11">
       <c r="A142" s="15">
         <v>39869</v>
       </c>
@@ -20323,7 +20335,7 @@
         <v>46.376897362766087</v>
       </c>
     </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:11">
       <c r="A143" s="15">
         <v>39876</v>
       </c>
@@ -20359,7 +20371,7 @@
         <v>48.797982331083887</v>
       </c>
     </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:11">
       <c r="A144" s="15">
         <v>39883</v>
       </c>
@@ -20395,7 +20407,7 @@
         <v>50.995285896575474</v>
       </c>
     </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:11">
       <c r="A145" s="15">
         <v>39890</v>
       </c>
@@ -20431,7 +20443,7 @@
         <v>50.632752300623871</v>
       </c>
     </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:11">
       <c r="A146" s="15">
         <v>39897</v>
       </c>
@@ -20467,7 +20479,7 @@
         <v>49.159815906896966</v>
       </c>
     </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:11">
       <c r="A147" s="15">
         <v>39904</v>
       </c>
@@ -20503,7 +20515,7 @@
         <v>67.93322071407249</v>
       </c>
     </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:11">
       <c r="A148" s="15">
         <v>39911</v>
       </c>
@@ -20539,7 +20551,7 @@
         <v>59.144140747470985</v>
       </c>
     </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:11">
       <c r="A149" s="15">
         <v>39918</v>
       </c>
@@ -20575,7 +20587,7 @@
         <v>48.417328037810883</v>
       </c>
     </row>
-    <row r="150" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:11">
       <c r="A150" s="15">
         <v>39925</v>
       </c>
@@ -20611,7 +20623,7 @@
         <v>65.507189828231219</v>
       </c>
     </row>
-    <row r="151" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:11">
       <c r="A151" s="15">
         <v>39932</v>
       </c>
@@ -20647,7 +20659,7 @@
         <v>67.77459535800439</v>
       </c>
     </row>
-    <row r="152" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:11">
       <c r="A152" s="15">
         <v>39939</v>
       </c>
@@ -20683,7 +20695,7 @@
         <v>67.144419826628891</v>
       </c>
     </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:11">
       <c r="A153" s="15">
         <v>39946</v>
       </c>
@@ -20719,7 +20731,7 @@
         <v>50.709106035336958</v>
       </c>
     </row>
-    <row r="154" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:11">
       <c r="A154" s="15">
         <v>39953</v>
       </c>
@@ -20755,7 +20767,7 @@
         <v>45.673803993182069</v>
       </c>
     </row>
-    <row r="155" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:11">
       <c r="A155" s="15">
         <v>39960</v>
       </c>
@@ -20791,7 +20803,7 @@
         <v>56.578290137928242</v>
       </c>
     </row>
-    <row r="156" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:11">
       <c r="A156" s="15">
         <v>39967</v>
       </c>
@@ -20827,7 +20839,7 @@
         <v>65.158129608233793</v>
       </c>
     </row>
-    <row r="157" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:11">
       <c r="A157" s="15">
         <v>39974</v>
       </c>
@@ -20863,7 +20875,7 @@
         <v>44.471505975736868</v>
       </c>
     </row>
-    <row r="158" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:11">
       <c r="A158" s="15">
         <v>39981</v>
       </c>
@@ -20899,7 +20911,7 @@
         <v>52.627079222161107</v>
       </c>
     </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:11">
       <c r="A159" s="15">
         <v>39988</v>
       </c>
@@ -20935,7 +20947,7 @@
         <v>66.261051954921754</v>
       </c>
     </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:11">
       <c r="A160" s="15">
         <v>39995</v>
       </c>
@@ -20971,7 +20983,7 @@
         <v>54.893058424976317</v>
       </c>
     </row>
-    <row r="161" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:11">
       <c r="A161" s="15">
         <v>40002</v>
       </c>
@@ -21007,7 +21019,7 @@
         <v>64.161205849108597</v>
       </c>
     </row>
-    <row r="162" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:11">
       <c r="A162" s="15">
         <v>40009</v>
       </c>
@@ -21043,7 +21055,7 @@
         <v>52.811235830415114</v>
       </c>
     </row>
-    <row r="163" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:11">
       <c r="A163" s="15">
         <v>40016</v>
       </c>
@@ -21079,7 +21091,7 @@
         <v>57.645867319279404</v>
       </c>
     </row>
-    <row r="164" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:11">
       <c r="A164" s="15">
         <v>40023</v>
       </c>
@@ -21115,7 +21127,7 @@
         <v>61.365403956693434</v>
       </c>
     </row>
-    <row r="165" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:11">
       <c r="A165" s="15">
         <v>40030</v>
       </c>
@@ -21151,7 +21163,7 @@
         <v>44.582988427682338</v>
       </c>
     </row>
-    <row r="166" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:11">
       <c r="A166" s="15">
         <v>40037</v>
       </c>
@@ -21187,7 +21199,7 @@
         <v>54.166951121047973</v>
       </c>
     </row>
-    <row r="167" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:11">
       <c r="A167" s="15">
         <v>40044</v>
       </c>
@@ -21223,7 +21235,7 @@
         <v>76.385981144531414</v>
       </c>
     </row>
-    <row r="168" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:11">
       <c r="A168" s="15">
         <v>40051</v>
       </c>
@@ -21259,7 +21271,7 @@
         <v>71.141667275747665</v>
       </c>
     </row>
-    <row r="169" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:11">
       <c r="A169" s="15">
         <v>40058</v>
       </c>
@@ -21295,7 +21307,7 @@
         <v>81.41339889263179</v>
       </c>
     </row>
-    <row r="170" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:11">
       <c r="A170" s="15">
         <v>40065</v>
       </c>
@@ -21331,7 +21343,7 @@
         <v>63.355150657102897</v>
       </c>
     </row>
-    <row r="171" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:11">
       <c r="A171" s="15">
         <v>40072</v>
       </c>
@@ -21367,7 +21379,7 @@
         <v>63.586872250336747</v>
       </c>
     </row>
-    <row r="172" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:11">
       <c r="A172" s="15">
         <v>40079</v>
       </c>
@@ -21403,7 +21415,7 @@
         <v>53.318827599106207</v>
       </c>
     </row>
-    <row r="173" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:11">
       <c r="A173" s="15">
         <v>40086</v>
       </c>
@@ -21439,7 +21451,7 @@
         <v>49.477873007591704</v>
       </c>
     </row>
-    <row r="174" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:11">
       <c r="A174" s="15">
         <v>40093</v>
       </c>
@@ -21475,7 +21487,7 @@
         <v>71.403538470599969</v>
       </c>
     </row>
-    <row r="175" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:11">
       <c r="A175" s="15">
         <v>40100</v>
       </c>
@@ -21511,7 +21523,7 @@
         <v>61.732827908030352</v>
       </c>
     </row>
-    <row r="176" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:11">
       <c r="A176" s="15">
         <v>40107</v>
       </c>
@@ -21547,7 +21559,7 @@
         <v>52.229993511604249</v>
       </c>
     </row>
-    <row r="177" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:11">
       <c r="A177" s="15">
         <v>40114</v>
       </c>
@@ -21583,7 +21595,7 @@
         <v>64.598575021541549</v>
       </c>
     </row>
-    <row r="178" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:11">
       <c r="A178" s="15">
         <v>40121</v>
       </c>
@@ -21619,7 +21631,7 @@
         <v>61.131436014016572</v>
       </c>
     </row>
-    <row r="179" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:11">
       <c r="A179" s="15">
         <v>40128</v>
       </c>
@@ -21655,7 +21667,7 @@
         <v>53.907207534999003</v>
       </c>
     </row>
-    <row r="180" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:11">
       <c r="A180" s="15">
         <v>40135</v>
       </c>
@@ -21691,7 +21703,7 @@
         <v>44.756939056977522</v>
       </c>
     </row>
-    <row r="181" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:11">
       <c r="A181" s="15">
         <v>40142</v>
       </c>
@@ -21727,7 +21739,7 @@
         <v>56.685418081441156</v>
       </c>
     </row>
-    <row r="182" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:11">
       <c r="A182" s="15">
         <v>40149</v>
       </c>
@@ -21763,7 +21775,7 @@
         <v>49.326994067650219</v>
       </c>
     </row>
-    <row r="183" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:11">
       <c r="A183" s="15">
         <v>40156</v>
       </c>
@@ -21799,7 +21811,7 @@
         <v>56.94789248873581</v>
       </c>
     </row>
-    <row r="184" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:11">
       <c r="A184" s="15">
         <v>40163</v>
       </c>
@@ -21835,7 +21847,7 @@
         <v>53.684534257154517</v>
       </c>
     </row>
-    <row r="185" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:11">
       <c r="A185" s="15">
         <v>40170</v>
       </c>
@@ -21871,7 +21883,7 @@
         <v>65.364947708147739</v>
       </c>
     </row>
-    <row r="186" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:11">
       <c r="A186" s="15">
         <v>40177</v>
       </c>
@@ -21907,7 +21919,7 @@
         <v>53.704634029690361</v>
       </c>
     </row>
-    <row r="187" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:11">
       <c r="A187" s="15">
         <v>40184</v>
       </c>
@@ -21943,7 +21955,7 @@
         <v>54.771375546492628</v>
       </c>
     </row>
-    <row r="188" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:11">
       <c r="A188" s="15">
         <v>40191</v>
       </c>
@@ -21979,7 +21991,7 @@
         <v>57.833752535015343</v>
       </c>
     </row>
-    <row r="189" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:11">
       <c r="A189" s="15">
         <v>40198</v>
       </c>
@@ -22015,7 +22027,7 @@
         <v>79.252584956089748</v>
       </c>
     </row>
-    <row r="190" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:11">
       <c r="A190" s="15">
         <v>40205</v>
       </c>
@@ -22051,7 +22063,7 @@
         <v>66.112908932661171</v>
       </c>
     </row>
-    <row r="191" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:11">
       <c r="A191" s="15">
         <v>40212</v>
       </c>
@@ -22087,7 +22099,7 @@
         <v>68.480905740352668</v>
       </c>
     </row>
-    <row r="192" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:11">
       <c r="A192" s="15">
         <v>40219</v>
       </c>
@@ -22123,7 +22135,7 @@
         <v>68.820680112015253</v>
       </c>
     </row>
-    <row r="193" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:11">
       <c r="A193" s="15">
         <v>40226</v>
       </c>
@@ -22159,7 +22171,7 @@
         <v>59.032374376182737</v>
       </c>
     </row>
-    <row r="194" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:11">
       <c r="A194" s="15">
         <v>40233</v>
       </c>
@@ -22195,7 +22207,7 @@
         <v>60.995325657513426</v>
       </c>
     </row>
-    <row r="195" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:11">
       <c r="A195" s="15">
         <v>40240</v>
       </c>
@@ -22246,7 +22258,7 @@
         <v>61.01651833892263</v>
       </c>
     </row>
-    <row r="196" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:11">
       <c r="A196" s="15">
         <v>40247</v>
       </c>
@@ -22282,7 +22294,7 @@
         <v>68.948409164893818</v>
       </c>
     </row>
-    <row r="197" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:11">
       <c r="A197" s="15">
         <v>40254</v>
       </c>
@@ -22318,7 +22330,7 @@
         <v>55.495282272042076</v>
       </c>
     </row>
-    <row r="198" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:11">
       <c r="A198" s="15">
         <v>40261</v>
       </c>
@@ -22354,7 +22366,7 @@
         <v>57.756350696573961</v>
       </c>
     </row>
-    <row r="199" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:11">
       <c r="A199" s="15">
         <v>40268</v>
       </c>
@@ -22390,7 +22402,7 @@
         <v>46.374631010759359</v>
       </c>
     </row>
-    <row r="200" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:11">
       <c r="A200" s="15">
         <v>40275</v>
       </c>
@@ -22426,7 +22438,7 @@
         <v>50.035497779699199</v>
       </c>
     </row>
-    <row r="201" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:11">
       <c r="A201" s="15">
         <v>40282</v>
       </c>
@@ -22462,7 +22474,7 @@
         <v>45.14920394961522</v>
       </c>
     </row>
-    <row r="202" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:11">
       <c r="A202" s="15">
         <v>40289</v>
       </c>
@@ -22498,7 +22510,7 @@
         <v>42.330808834030208</v>
       </c>
     </row>
-    <row r="203" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:11">
       <c r="A203" s="15">
         <v>40296</v>
       </c>
@@ -22534,7 +22546,7 @@
         <v>46.031147244235598</v>
       </c>
     </row>
-    <row r="204" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:11">
       <c r="A204" s="15">
         <v>40303</v>
       </c>
@@ -22570,7 +22582,7 @@
         <v>73.783147168729855</v>
       </c>
     </row>
-    <row r="205" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:11">
       <c r="A205" s="15">
         <v>40310</v>
       </c>
@@ -22606,7 +22618,7 @@
         <v>67.420059029224618</v>
       </c>
     </row>
-    <row r="206" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:11">
       <c r="A206" s="15">
         <v>40317</v>
       </c>
@@ -22642,7 +22654,7 @@
         <v>65.236302377809508</v>
       </c>
     </row>
-    <row r="207" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:11">
       <c r="A207" s="15">
         <v>40324</v>
       </c>
@@ -22678,7 +22690,7 @@
         <v>45.438603264918548</v>
       </c>
     </row>
-    <row r="208" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:11">
       <c r="A208" s="15">
         <v>40331</v>
       </c>
@@ -22714,7 +22726,7 @@
         <v>55.842613656597415</v>
       </c>
     </row>
-    <row r="209" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:11">
       <c r="A209" s="15">
         <v>40338</v>
       </c>
@@ -22750,7 +22762,7 @@
         <v>50.566226976684703</v>
       </c>
     </row>
-    <row r="210" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:11">
       <c r="A210" s="15">
         <v>40345</v>
       </c>
@@ -22786,7 +22798,7 @@
         <v>60.167993983512531</v>
       </c>
     </row>
-    <row r="211" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:11">
       <c r="A211" s="15">
         <v>40352</v>
       </c>
@@ -22822,7 +22834,7 @@
         <v>59.384867216709665</v>
       </c>
     </row>
-    <row r="212" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:11">
       <c r="A212" s="15">
         <v>40359</v>
       </c>
@@ -22858,7 +22870,7 @@
         <v>51.877165703250242</v>
       </c>
     </row>
-    <row r="213" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:11">
       <c r="A213" s="15">
         <v>40366</v>
       </c>
@@ -22894,7 +22906,7 @@
         <v>60.791159694094574</v>
       </c>
     </row>
-    <row r="214" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:11">
       <c r="A214" s="15">
         <v>40373</v>
       </c>
@@ -22930,7 +22942,7 @@
         <v>52.381556868806406</v>
       </c>
     </row>
-    <row r="215" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:11">
       <c r="A215" s="15">
         <v>40380</v>
       </c>
@@ -22966,7 +22978,7 @@
         <v>55.497901708236633</v>
       </c>
     </row>
-    <row r="216" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:11">
       <c r="A216" s="15">
         <v>40387</v>
       </c>
@@ -23002,7 +23014,7 @@
         <v>63.648541403343927</v>
       </c>
     </row>
-    <row r="217" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:11">
       <c r="A217" s="15">
         <v>40394</v>
       </c>
@@ -23038,7 +23050,7 @@
         <v>58.51627398414611</v>
       </c>
     </row>
-    <row r="218" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:11">
       <c r="A218" s="15">
         <v>40401</v>
       </c>
@@ -23074,7 +23086,7 @@
         <v>70.168158657672691</v>
       </c>
     </row>
-    <row r="219" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:11">
       <c r="A219" s="15">
         <v>40408</v>
       </c>
@@ -23110,7 +23122,7 @@
         <v>53.947041077312385</v>
       </c>
     </row>
-    <row r="220" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:11">
       <c r="A220" s="15">
         <v>40415</v>
       </c>
@@ -23146,7 +23158,7 @@
         <v>55.908131213647891</v>
       </c>
     </row>
-    <row r="221" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:11">
       <c r="A221" s="15">
         <v>40422</v>
       </c>
@@ -23182,7 +23194,7 @@
         <v>62.564187638553811</v>
       </c>
     </row>
-    <row r="222" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:11">
       <c r="A222" s="15">
         <v>40429</v>
       </c>
@@ -23218,7 +23230,7 @@
         <v>72.423309874299363</v>
       </c>
     </row>
-    <row r="223" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:11">
       <c r="A223" s="15">
         <v>40436</v>
       </c>
@@ -23254,7 +23266,7 @@
         <v>73.388746907379783</v>
       </c>
     </row>
-    <row r="224" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:11">
       <c r="A224" s="15">
         <v>40443</v>
       </c>
@@ -23290,7 +23302,7 @@
         <v>74.427829003026858</v>
       </c>
     </row>
-    <row r="225" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:11">
       <c r="A225" s="15">
         <v>40450</v>
       </c>
@@ -23326,7 +23338,7 @@
         <v>65.974731715358232</v>
       </c>
     </row>
-    <row r="226" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:11">
       <c r="A226" s="15">
         <v>40457</v>
       </c>
@@ -23362,7 +23374,7 @@
         <v>59.692906241492011</v>
       </c>
     </row>
-    <row r="227" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:11">
       <c r="A227" s="15">
         <v>40464</v>
       </c>
@@ -23398,7 +23410,7 @@
         <v>55.007204521826623</v>
       </c>
     </row>
-    <row r="228" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:11">
       <c r="A228" s="15">
         <v>40471</v>
       </c>
@@ -23434,7 +23446,7 @@
         <v>54.037281159418455</v>
       </c>
     </row>
-    <row r="229" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:11">
       <c r="A229" s="15">
         <v>40478</v>
       </c>
@@ -23470,7 +23482,7 @@
         <v>74.053447495288836</v>
       </c>
     </row>
-    <row r="230" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:11">
       <c r="A230" s="15">
         <v>40485</v>
       </c>
@@ -23506,7 +23518,7 @@
         <v>57.599139747516887</v>
       </c>
     </row>
-    <row r="231" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:11">
       <c r="A231" s="15">
         <v>40493</v>
       </c>
@@ -23542,7 +23554,7 @@
         <v>73.628931758084974</v>
       </c>
     </row>
-    <row r="232" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:11">
       <c r="A232" s="15">
         <v>40499</v>
       </c>
@@ -23578,7 +23590,7 @@
         <v>64.712269652083734</v>
       </c>
     </row>
-    <row r="233" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:11">
       <c r="A233" s="15">
         <v>40506</v>
       </c>
@@ -23614,7 +23626,7 @@
         <v>68.728127833919316</v>
       </c>
     </row>
-    <row r="234" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:11">
       <c r="A234" s="15">
         <v>40513</v>
       </c>
@@ -23650,7 +23662,7 @@
         <v>71.396578703865657</v>
       </c>
     </row>
-    <row r="235" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:11">
       <c r="A235" s="15">
         <v>40520</v>
       </c>
@@ -23686,7 +23698,7 @@
         <v>56.848732557127434</v>
       </c>
     </row>
-    <row r="236" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:11">
       <c r="A236" s="15">
         <v>40527</v>
       </c>
@@ -23722,7 +23734,7 @@
         <v>48.876462768440668</v>
       </c>
     </row>
-    <row r="237" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:11">
       <c r="A237" s="15">
         <v>40534</v>
       </c>
@@ -23758,7 +23770,7 @@
         <v>30.939366105335772</v>
       </c>
     </row>
-    <row r="238" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:11">
       <c r="A238" s="15">
         <v>40541</v>
       </c>
@@ -23794,7 +23806,7 @@
         <v>25.867679114547297</v>
       </c>
     </row>
-    <row r="239" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:11">
       <c r="A239" s="15">
         <v>40548</v>
       </c>
@@ -23830,7 +23842,7 @@
         <v>35.99596195192472</v>
       </c>
     </row>
-    <row r="240" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:11">
       <c r="A240" s="15">
         <v>40555</v>
       </c>
@@ -23866,7 +23878,7 @@
         <v>34.5248029413723</v>
       </c>
     </row>
-    <row r="241" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:11">
       <c r="A241" s="15">
         <v>40562</v>
       </c>
@@ -23902,7 +23914,7 @@
         <v>48.204614903131251</v>
       </c>
     </row>
-    <row r="242" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:11">
       <c r="A242" s="15">
         <v>40569</v>
       </c>
@@ -23938,7 +23950,7 @@
         <v>44.563550516112116</v>
       </c>
     </row>
-    <row r="243" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:11">
       <c r="A243" s="15">
         <v>40576</v>
       </c>
@@ -23974,7 +23986,7 @@
         <v>37.30092994819298</v>
       </c>
     </row>
-    <row r="244" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:11">
       <c r="A244" s="15">
         <v>40583</v>
       </c>
@@ -24010,7 +24022,7 @@
         <v>36.241942484664484</v>
       </c>
     </row>
-    <row r="245" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:11">
       <c r="A245" s="15">
         <v>40590</v>
       </c>
@@ -24046,7 +24058,7 @@
         <v>39.530799594711759</v>
       </c>
     </row>
-    <row r="246" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:11">
       <c r="A246" s="15">
         <v>40597</v>
       </c>
@@ -24082,7 +24094,7 @@
         <v>53.939404659302646</v>
       </c>
     </row>
-    <row r="247" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:11">
       <c r="A247" s="15">
         <v>40604</v>
       </c>
@@ -24118,7 +24130,7 @@
         <v>43.942750002449529</v>
       </c>
     </row>
-    <row r="248" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:11">
       <c r="A248" s="15">
         <v>40611</v>
       </c>
@@ -24154,7 +24166,7 @@
         <v>34.894786457057684</v>
       </c>
     </row>
-    <row r="249" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:11">
       <c r="A249" s="15">
         <v>40618</v>
       </c>
@@ -24190,7 +24202,7 @@
         <v>64.316923641190016</v>
       </c>
     </row>
-    <row r="250" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:11">
       <c r="A250" s="15">
         <v>40625</v>
       </c>
@@ -24226,7 +24238,7 @@
         <v>54.669969412425644</v>
       </c>
     </row>
-    <row r="251" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:11">
       <c r="A251" s="15">
         <v>40632</v>
       </c>
@@ -24262,7 +24274,7 @@
         <v>33.436812839822487</v>
       </c>
     </row>
-    <row r="252" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:11">
       <c r="A252" s="15">
         <v>40639</v>
       </c>
@@ -24298,7 +24310,7 @@
         <v>39.172313642501635</v>
       </c>
     </row>
-    <row r="253" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:11">
       <c r="A253" s="15">
         <v>40646</v>
       </c>
@@ -24334,7 +24346,7 @@
         <v>38.729050102374607</v>
       </c>
     </row>
-    <row r="254" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:11">
       <c r="A254" s="15">
         <v>40653</v>
       </c>
@@ -24370,7 +24382,7 @@
         <v>41.715563146345993</v>
       </c>
     </row>
-    <row r="255" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:11">
       <c r="A255" s="15">
         <v>40660</v>
       </c>
@@ -24406,7 +24418,7 @@
         <v>43.741742077791095</v>
       </c>
     </row>
-    <row r="256" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:11">
       <c r="A256" s="15">
         <v>40667</v>
       </c>
@@ -24442,7 +24454,7 @@
         <v>47.873989122981456</v>
       </c>
     </row>
-    <row r="257" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:11">
       <c r="A257" s="15">
         <v>40674</v>
       </c>
@@ -24478,7 +24490,7 @@
         <v>51.779665709540218</v>
       </c>
     </row>
-    <row r="258" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:11">
       <c r="A258" s="15">
         <v>40681</v>
       </c>
@@ -24514,7 +24526,7 @@
         <v>57.023035358289334</v>
       </c>
     </row>
-    <row r="259" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:11">
       <c r="A259" s="15">
         <v>40688</v>
       </c>
@@ -24565,7 +24577,7 @@
         <v>56.87088409797628</v>
       </c>
     </row>
-    <row r="260" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:11">
       <c r="A260" s="15">
         <v>40695</v>
       </c>
@@ -24601,7 +24613,7 @@
         <v>47.063569688632143</v>
       </c>
     </row>
-    <row r="261" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:11">
       <c r="A261" s="15">
         <v>40702</v>
       </c>
@@ -24637,7 +24649,7 @@
         <v>58.561562455438484</v>
       </c>
     </row>
-    <row r="262" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:11">
       <c r="A262" s="15">
         <v>40709</v>
       </c>
@@ -24673,7 +24685,7 @@
         <v>54.876464024706216</v>
       </c>
     </row>
-    <row r="263" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:11">
       <c r="A263" s="15">
         <v>40716</v>
       </c>
@@ -24709,7 +24721,7 @@
         <v>48.129506282529015</v>
       </c>
     </row>
-    <row r="264" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:11">
       <c r="A264" s="15">
         <v>40723</v>
       </c>
@@ -24745,7 +24757,7 @@
         <v>53.998865301934728</v>
       </c>
     </row>
-    <row r="265" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:11">
       <c r="A265" s="15">
         <v>40730</v>
       </c>
@@ -24781,7 +24793,7 @@
         <v>57.89850820929329</v>
       </c>
     </row>
-    <row r="266" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:11">
       <c r="A266" s="15">
         <v>40737</v>
       </c>
@@ -24817,7 +24829,7 @@
         <v>53.479549570113456</v>
       </c>
     </row>
-    <row r="267" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:11">
       <c r="A267" s="15">
         <v>40744</v>
       </c>
@@ -24853,7 +24865,7 @@
         <v>49.79143878947302</v>
       </c>
     </row>
-    <row r="268" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:11">
       <c r="A268" s="15">
         <v>40751</v>
       </c>
@@ -24889,7 +24901,7 @@
         <v>42.651475813694034</v>
       </c>
     </row>
-    <row r="269" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:11">
       <c r="A269" s="15">
         <v>40758</v>
       </c>
@@ -24925,7 +24937,7 @@
         <v>50.439188817558389</v>
       </c>
     </row>
-    <row r="270" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:11">
       <c r="A270" s="15">
         <v>40765</v>
       </c>
@@ -24961,7 +24973,7 @@
         <v>42.049324508367285</v>
       </c>
     </row>
-    <row r="271" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:11">
       <c r="A271" s="15">
         <v>40772</v>
       </c>
@@ -24997,7 +25009,7 @@
         <v>47.516027185636773</v>
       </c>
     </row>
-    <row r="272" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:11">
       <c r="A272" s="15">
         <v>40779</v>
       </c>
@@ -25033,7 +25045,7 @@
         <v>40.399772058656886</v>
       </c>
     </row>
-    <row r="273" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:11">
       <c r="A273" s="15">
         <v>40786</v>
       </c>
@@ -25069,7 +25081,7 @@
         <v>44.783201620610939</v>
       </c>
     </row>
-    <row r="274" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:11">
       <c r="A274" s="15">
         <v>40793</v>
       </c>
@@ -25105,7 +25117,7 @@
         <v>46.854774319627346</v>
       </c>
     </row>
-    <row r="275" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:11">
       <c r="A275" s="15">
         <v>40800</v>
       </c>
@@ -25141,7 +25153,7 @@
         <v>50.572231681862235</v>
       </c>
     </row>
-    <row r="276" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:11">
       <c r="A276" s="15">
         <v>40807</v>
       </c>
@@ -25177,7 +25189,7 @@
         <v>51.000097894093308</v>
       </c>
     </row>
-    <row r="277" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:11">
       <c r="A277" s="15">
         <v>40814</v>
       </c>
@@ -25213,7 +25225,7 @@
         <v>38.969787977354969</v>
       </c>
     </row>
-    <row r="278" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:11">
       <c r="A278" s="15">
         <v>40821</v>
       </c>
@@ -25249,7 +25261,7 @@
         <v>54.517864058372737</v>
       </c>
     </row>
-    <row r="279" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:11">
       <c r="A279" s="15">
         <v>40828</v>
       </c>
@@ -25285,7 +25297,7 @@
         <v>58.875398087826127</v>
       </c>
     </row>
-    <row r="280" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:11">
       <c r="A280" s="15">
         <v>40835</v>
       </c>
@@ -25321,7 +25333,7 @@
         <v>40.918862469344425</v>
       </c>
     </row>
-    <row r="281" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:11">
       <c r="A281" s="15">
         <v>40842</v>
       </c>
@@ -25357,7 +25369,7 @@
         <v>45.233867381064172</v>
       </c>
     </row>
-    <row r="282" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:11">
       <c r="A282" s="15">
         <v>40849</v>
       </c>
@@ -25393,7 +25405,7 @@
         <v>55.320831293464849</v>
       </c>
     </row>
-    <row r="283" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:11">
       <c r="A283" s="15">
         <v>40856</v>
       </c>
@@ -25429,7 +25441,7 @@
         <v>55.690513263814637</v>
       </c>
     </row>
-    <row r="284" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:11">
       <c r="A284" s="15">
         <v>40863</v>
       </c>
@@ -25465,7 +25477,7 @@
         <v>51.999145292121014</v>
       </c>
     </row>
-    <row r="285" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:11">
       <c r="A285" s="15">
         <v>40870</v>
       </c>
@@ -25501,7 +25513,7 @@
         <v>45.873095396241652</v>
       </c>
     </row>
-    <row r="286" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:11">
       <c r="A286" s="15">
         <v>40877</v>
       </c>
@@ -25537,7 +25549,7 @@
         <v>42.216169288999922</v>
       </c>
     </row>
-    <row r="287" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:11">
       <c r="A287" s="15">
         <v>40884</v>
       </c>
@@ -25573,7 +25585,7 @@
         <v>43.664531422515303</v>
       </c>
     </row>
-    <row r="288" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:11">
       <c r="A288" s="15">
         <v>40891</v>
       </c>
@@ -25609,7 +25621,7 @@
         <v>48.198670933439651</v>
       </c>
     </row>
-    <row r="289" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:11">
       <c r="A289" s="15">
         <v>40898</v>
       </c>
@@ -25645,7 +25657,7 @@
         <v>39.516792034075834</v>
       </c>
     </row>
-    <row r="290" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:11">
       <c r="A290" s="15">
         <v>40905</v>
       </c>
@@ -25681,7 +25693,7 @@
         <v>28.563193765273795</v>
       </c>
     </row>
-    <row r="291" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:11">
       <c r="A291" s="15">
         <v>40912</v>
       </c>
@@ -25717,7 +25729,7 @@
         <v>41.403003244764143</v>
       </c>
     </row>
-    <row r="292" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:11">
       <c r="A292" s="15">
         <v>40919</v>
       </c>
@@ -25753,7 +25765,7 @@
         <v>47.072652594140706</v>
       </c>
     </row>
-    <row r="293" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:11">
       <c r="A293" s="15">
         <v>40926</v>
       </c>
@@ -25789,7 +25801,7 @@
         <v>49.053078858054825</v>
       </c>
     </row>
-    <row r="294" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:11">
       <c r="A294" s="15">
         <v>40933</v>
       </c>
@@ -25825,7 +25837,7 @@
         <v>53.510954226421923</v>
       </c>
     </row>
-    <row r="295" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:11">
       <c r="A295" s="15">
         <v>40940</v>
       </c>
@@ -25861,7 +25873,7 @@
         <v>39.384750530886507</v>
       </c>
     </row>
-    <row r="296" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:11">
       <c r="A296" s="15">
         <v>40947</v>
       </c>
@@ -25897,7 +25909,7 @@
         <v>36.817697808266423</v>
       </c>
     </row>
-    <row r="297" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:11">
       <c r="A297" s="15">
         <v>40954</v>
       </c>
@@ -25933,7 +25945,7 @@
         <v>36.233572758862671</v>
       </c>
     </row>
-    <row r="298" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:11">
       <c r="A298" s="15">
         <v>40961</v>
       </c>
@@ -25969,7 +25981,7 @@
         <v>37.171889580703322</v>
       </c>
     </row>
-    <row r="299" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:11">
       <c r="A299" s="15">
         <v>40968</v>
       </c>
@@ -26005,7 +26017,7 @@
         <v>36.759941210655207</v>
       </c>
     </row>
-    <row r="300" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:11">
       <c r="A300" s="15">
         <v>40975</v>
       </c>
@@ -26041,7 +26053,7 @@
         <v>56.661237586866619</v>
       </c>
     </row>
-    <row r="301" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:11">
       <c r="A301" s="15">
         <v>40982</v>
       </c>
@@ -26077,7 +26089,7 @@
         <v>47.798457305394521</v>
       </c>
     </row>
-    <row r="302" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:11">
       <c r="A302" s="15">
         <v>40989</v>
       </c>
@@ -26113,7 +26125,7 @@
         <v>47.064324329465158</v>
       </c>
     </row>
-    <row r="303" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:11">
       <c r="A303" s="15">
         <v>40996</v>
       </c>
@@ -26149,7 +26161,7 @@
         <v>40.595204301061202</v>
       </c>
     </row>
-    <row r="304" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:11">
       <c r="A304" s="15">
         <v>41003</v>
       </c>
@@ -26185,7 +26197,7 @@
         <v>38.549937035348876</v>
       </c>
     </row>
-    <row r="305" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:11">
       <c r="A305" s="15">
         <v>41010</v>
       </c>
@@ -26221,7 +26233,7 @@
         <v>53.214477468494394</v>
       </c>
     </row>
-    <row r="306" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:11">
       <c r="A306" s="15">
         <v>41017</v>
       </c>
@@ -26257,7 +26269,7 @@
         <v>56.900572530695925</v>
       </c>
     </row>
-    <row r="307" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:11">
       <c r="A307" s="15">
         <v>41024</v>
       </c>
@@ -26293,7 +26305,7 @@
         <v>56.771006536281874</v>
       </c>
     </row>
-    <row r="308" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:11">
       <c r="A308" s="15">
         <v>41031</v>
       </c>
@@ -26329,7 +26341,7 @@
         <v>50.543476884317684</v>
       </c>
     </row>
-    <row r="309" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:11">
       <c r="A309" s="15">
         <v>41038</v>
       </c>
@@ -26365,7 +26377,7 @@
         <v>54.137497957615317</v>
       </c>
     </row>
-    <row r="310" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:11">
       <c r="A310" s="15">
         <v>41045</v>
       </c>
@@ -26401,7 +26413,7 @@
         <v>41.363917899541384</v>
       </c>
     </row>
-    <row r="311" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:11">
       <c r="A311" s="15">
         <v>41052</v>
       </c>
@@ -26437,7 +26449,7 @@
         <v>45.49777201728218</v>
       </c>
     </row>
-    <row r="312" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:11">
       <c r="A312" s="15">
         <v>41059</v>
       </c>
@@ -26473,7 +26485,7 @@
         <v>46.729614872834489</v>
       </c>
     </row>
-    <row r="313" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:11">
       <c r="A313" s="15">
         <v>41066</v>
       </c>
@@ -26509,7 +26521,7 @@
         <v>34.956741028578463</v>
       </c>
     </row>
-    <row r="314" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:11">
       <c r="A314" s="15">
         <v>41073</v>
       </c>
@@ -26545,7 +26557,7 @@
         <v>29.532500348198187</v>
       </c>
     </row>
-    <row r="315" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:11">
       <c r="A315" s="15">
         <v>41080</v>
       </c>
@@ -26581,7 +26593,7 @@
         <v>45.65945115969452</v>
       </c>
     </row>
-    <row r="316" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:11">
       <c r="A316" s="15">
         <v>41087</v>
       </c>
@@ -26617,7 +26629,7 @@
         <v>48.136271215938542</v>
       </c>
     </row>
-    <row r="317" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:11">
       <c r="A317" s="15">
         <v>41095</v>
       </c>
@@ -26653,7 +26665,7 @@
         <v>49.207476611003706</v>
       </c>
     </row>
-    <row r="318" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:11">
       <c r="A318" s="15">
         <v>41101</v>
       </c>
@@ -26689,7 +26701,7 @@
         <v>53.618962087056566</v>
       </c>
     </row>
-    <row r="319" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:11">
       <c r="A319" s="15">
         <v>41108</v>
       </c>
@@ -26725,7 +26737,7 @@
         <v>52.76407806027715</v>
       </c>
     </row>
-    <row r="320" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:11">
       <c r="A320" s="15">
         <v>41115</v>
       </c>
@@ -26761,7 +26773,7 @@
         <v>50.011052339523104</v>
       </c>
     </row>
-    <row r="321" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:11">
       <c r="A321" s="15">
         <v>41122</v>
       </c>
@@ -26797,7 +26809,7 @@
         <v>53.937797639233743</v>
       </c>
     </row>
-    <row r="322" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:11">
       <c r="A322" s="15">
         <v>41129</v>
       </c>
@@ -26833,7 +26845,7 @@
         <v>39.420666681528402</v>
       </c>
     </row>
-    <row r="323" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:11">
       <c r="A323" s="15">
         <v>41136</v>
       </c>
@@ -26884,7 +26896,7 @@
         <v>42.597308792434582</v>
       </c>
     </row>
-    <row r="324" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:11">
       <c r="A324" s="15">
         <v>41143</v>
       </c>
@@ -26920,7 +26932,7 @@
         <v>59.566739758018073</v>
       </c>
     </row>
-    <row r="325" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:11">
       <c r="A325" s="15">
         <v>41150</v>
       </c>
@@ -26956,7 +26968,7 @@
         <v>40.667483971490398</v>
       </c>
     </row>
-    <row r="326" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:11">
       <c r="A326" s="15">
         <v>41157</v>
       </c>
@@ -26992,7 +27004,7 @@
         <v>50.154861297471179</v>
       </c>
     </row>
-    <row r="327" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:11">
       <c r="A327" s="15">
         <v>41164</v>
       </c>
@@ -27028,7 +27040,7 @@
         <v>50.124976846592538</v>
       </c>
     </row>
-    <row r="328" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:11">
       <c r="A328" s="15">
         <v>41171</v>
       </c>
@@ -27064,7 +27076,7 @@
         <v>52.943578895895669</v>
       </c>
     </row>
-    <row r="329" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:11">
       <c r="A329" s="15">
         <v>41178</v>
       </c>
@@ -27100,7 +27112,7 @@
         <v>56.021511245433409</v>
       </c>
     </row>
-    <row r="330" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:11">
       <c r="A330" s="15">
         <v>41185</v>
       </c>
@@ -27136,7 +27148,7 @@
         <v>57.266397751374981</v>
       </c>
     </row>
-    <row r="331" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:11">
       <c r="A331" s="15">
         <v>41192</v>
       </c>
@@ -27172,7 +27184,7 @@
         <v>66.483484497561491</v>
       </c>
     </row>
-    <row r="332" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:11">
       <c r="A332" s="15">
         <v>41199</v>
       </c>
@@ -27208,7 +27220,7 @@
         <v>71.777760309165402</v>
       </c>
     </row>
-    <row r="333" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:11">
       <c r="A333" s="15">
         <v>41206</v>
       </c>
@@ -27244,7 +27256,7 @@
         <v>59.778361750310793</v>
       </c>
     </row>
-    <row r="334" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:11">
       <c r="A334" s="15">
         <v>41213</v>
       </c>
@@ -27280,7 +27292,7 @@
         <v>59.216704581992914</v>
       </c>
     </row>
-    <row r="335" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:11">
       <c r="A335" s="15">
         <v>41220</v>
       </c>
@@ -27316,7 +27328,7 @@
         <v>57.538374466714032</v>
       </c>
     </row>
-    <row r="336" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:11">
       <c r="A336" s="15">
         <v>41227</v>
       </c>
@@ -27352,7 +27364,7 @@
         <v>64.794060427377659</v>
       </c>
     </row>
-    <row r="337" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:11">
       <c r="A337" s="15">
         <v>41234</v>
       </c>
@@ -27388,7 +27400,7 @@
         <v>42.978585224257763</v>
       </c>
     </row>
-    <row r="338" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:11">
       <c r="A338" s="15">
         <v>41241</v>
       </c>
@@ -27424,7 +27436,7 @@
         <v>58.262610437726366</v>
       </c>
     </row>
-    <row r="339" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:11">
       <c r="A339" s="15">
         <v>41248</v>
       </c>
@@ -27460,7 +27472,7 @@
         <v>53.947354080111261</v>
       </c>
     </row>
-    <row r="340" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:11">
       <c r="A340" s="15">
         <v>41255</v>
       </c>
@@ -27496,7 +27508,7 @@
         <v>40.867278029986856</v>
       </c>
     </row>
-    <row r="341" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:11">
       <c r="A341" s="15">
         <v>41262</v>
       </c>
@@ -27532,7 +27544,7 @@
         <v>49.812955030683419</v>
       </c>
     </row>
-    <row r="342" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:11">
       <c r="A342" s="15">
         <v>41269</v>
       </c>
@@ -27568,7 +27580,7 @@
         <v>44.510630134900872</v>
       </c>
     </row>
-    <row r="343" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:11">
       <c r="A343" s="15">
         <v>41276</v>
       </c>
@@ -27604,7 +27616,7 @@
         <v>53.24693033779436</v>
       </c>
     </row>
-    <row r="344" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:11">
       <c r="A344" s="15">
         <v>41283</v>
       </c>
@@ -27640,7 +27652,7 @@
         <v>43.585114686349307</v>
       </c>
     </row>
-    <row r="345" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:11">
       <c r="A345" s="15">
         <v>41290</v>
       </c>
@@ -27676,7 +27688,7 @@
         <v>60.84780147014353</v>
       </c>
     </row>
-    <row r="346" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:11">
       <c r="A346" s="15">
         <v>41297</v>
       </c>
@@ -27712,7 +27724,7 @@
         <v>53.953140270861297</v>
       </c>
     </row>
-    <row r="347" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:11">
       <c r="A347" s="15">
         <v>41304</v>
       </c>
@@ -27748,7 +27760,7 @@
         <v>32.239533185206014</v>
       </c>
     </row>
-    <row r="348" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:11">
       <c r="A348" s="15">
         <v>41311</v>
       </c>
@@ -27784,7 +27796,7 @@
         <v>40.084712867791588</v>
       </c>
     </row>
-    <row r="349" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:11">
       <c r="A349" s="15">
         <v>41318</v>
       </c>
@@ -27820,7 +27832,7 @@
         <v>38.38710256166938</v>
       </c>
     </row>
-    <row r="350" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:11">
       <c r="A350" s="15">
         <v>41325</v>
       </c>
@@ -27856,7 +27868,7 @@
         <v>38.080293444545788</v>
       </c>
     </row>
-    <row r="351" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:11">
       <c r="A351" s="15">
         <v>41332</v>
       </c>
@@ -27892,7 +27904,7 @@
         <v>48.402767285139547</v>
       </c>
     </row>
-    <row r="352" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:11">
       <c r="A352" s="15">
         <v>41339</v>
       </c>
@@ -27928,7 +27940,7 @@
         <v>40.094000618700669</v>
       </c>
     </row>
-    <row r="353" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:11">
       <c r="A353" s="15">
         <v>41346</v>
       </c>
@@ -27964,7 +27976,7 @@
         <v>42.821783159517786</v>
       </c>
     </row>
-    <row r="354" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:11">
       <c r="A354" s="15">
         <v>41353</v>
       </c>
@@ -28000,7 +28012,7 @@
         <v>32.607118719705234</v>
       </c>
     </row>
-    <row r="355" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:11">
       <c r="A355" s="15">
         <v>41360</v>
       </c>
@@ -28036,7 +28048,7 @@
         <v>40.659143503192773</v>
       </c>
     </row>
-    <row r="356" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:11">
       <c r="A356" s="15">
         <v>41367</v>
       </c>
@@ -28072,7 +28084,7 @@
         <v>61.567550890600387</v>
       </c>
     </row>
-    <row r="357" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:11">
       <c r="A357" s="15">
         <v>41374</v>
       </c>
@@ -28108,7 +28120,7 @@
         <v>52.116557963159231</v>
       </c>
     </row>
-    <row r="358" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:11">
       <c r="A358" s="15">
         <v>41381</v>
       </c>
@@ -28144,7 +28156,7 @@
         <v>53.354057268656028</v>
       </c>
     </row>
-    <row r="359" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:11">
       <c r="A359" s="15">
         <v>41388</v>
       </c>
@@ -28180,7 +28192,7 @@
         <v>58.802213497238505</v>
       </c>
     </row>
-    <row r="360" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:11">
       <c r="A360" s="15">
         <v>41395</v>
       </c>
@@ -28216,7 +28228,7 @@
         <v>37.937705662389739</v>
       </c>
     </row>
-    <row r="361" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:11">
       <c r="A361" s="15">
         <v>41402</v>
       </c>
@@ -28252,7 +28264,7 @@
         <v>54.929642662956802</v>
       </c>
     </row>
-    <row r="362" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:11">
       <c r="A362" s="15">
         <v>41409</v>
       </c>
@@ -28288,7 +28300,7 @@
         <v>35.515606966366008</v>
       </c>
     </row>
-    <row r="363" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:11">
       <c r="A363" s="15">
         <v>41416</v>
       </c>
@@ -28324,7 +28336,7 @@
         <v>47.22321621646487</v>
       </c>
     </row>
-    <row r="364" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:11">
       <c r="A364" s="15">
         <v>41423</v>
       </c>
@@ -28360,7 +28372,7 @@
         <v>58.20055953610327</v>
       </c>
     </row>
-    <row r="365" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:11">
       <c r="A365" s="15">
         <v>41430</v>
       </c>
@@ -28396,7 +28408,7 @@
         <v>58.972667790307163</v>
       </c>
     </row>
-    <row r="366" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:11">
       <c r="A366" s="15">
         <v>41437</v>
       </c>
@@ -28432,7 +28444,7 @@
         <v>54.209657868522129</v>
       </c>
     </row>
-    <row r="367" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:11">
       <c r="A367" s="15">
         <v>41444</v>
       </c>
@@ -28468,7 +28480,7 @@
         <v>49.424558707629132</v>
       </c>
     </row>
-    <row r="368" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:11">
       <c r="A368" s="15">
         <v>41451</v>
       </c>
@@ -28504,7 +28516,7 @@
         <v>49.303982121743722</v>
       </c>
     </row>
-    <row r="369" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:11">
       <c r="A369" s="15">
         <v>41458</v>
       </c>
@@ -28540,7 +28552,7 @@
         <v>35.218787549159295</v>
       </c>
     </row>
-    <row r="370" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:11">
       <c r="A370" s="15">
         <v>41465</v>
       </c>
@@ -28576,7 +28588,7 @@
         <v>55.882367115793201</v>
       </c>
     </row>
-    <row r="371" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:11">
       <c r="A371" s="15">
         <v>41472</v>
       </c>
@@ -28612,7 +28624,7 @@
         <v>53.110925423170286</v>
       </c>
     </row>
-    <row r="372" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:11">
       <c r="A372" s="15">
         <v>41479</v>
       </c>
@@ -28648,7 +28660,7 @@
         <v>33.44447705914984</v>
       </c>
     </row>
-    <row r="373" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:11">
       <c r="A373" s="15">
         <v>41486</v>
       </c>
@@ -28684,7 +28696,7 @@
         <v>54.484641664282961</v>
       </c>
     </row>
-    <row r="374" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:11">
       <c r="A374" s="15">
         <v>41493</v>
       </c>
@@ -28720,7 +28732,7 @@
         <v>30.238330855873073</v>
       </c>
     </row>
-    <row r="375" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:11">
       <c r="A375" s="15">
         <v>41500</v>
       </c>
@@ -28756,7 +28768,7 @@
         <v>42.699029269899285</v>
       </c>
     </row>
-    <row r="376" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:11">
       <c r="A376" s="15">
         <v>41507</v>
       </c>
@@ -28792,7 +28804,7 @@
         <v>56.528524201883307</v>
       </c>
     </row>
-    <row r="377" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:11">
       <c r="A377" s="15">
         <v>41514</v>
       </c>
@@ -28828,7 +28840,7 @@
         <v>45.736639980287038</v>
       </c>
     </row>
-    <row r="378" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:11">
       <c r="A378" s="15">
         <v>41521</v>
       </c>
@@ -28864,7 +28876,7 @@
         <v>44.32004194458554</v>
       </c>
     </row>
-    <row r="379" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:11">
       <c r="A379" s="15">
         <v>41528</v>
       </c>
@@ -28900,7 +28912,7 @@
         <v>31.097341411399512</v>
       </c>
     </row>
-    <row r="380" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:11">
       <c r="A380" s="15">
         <v>41535</v>
       </c>
@@ -28936,7 +28948,7 @@
         <v>32.054779929422871</v>
       </c>
     </row>
-    <row r="381" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:11">
       <c r="A381" s="15">
         <v>41542</v>
       </c>
@@ -28972,7 +28984,7 @@
         <v>48.279990820009985</v>
       </c>
     </row>
-    <row r="382" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:11">
       <c r="A382" s="15">
         <v>41549</v>
       </c>
@@ -29008,7 +29020,7 @@
         <v>55.268275006754301</v>
       </c>
     </row>
-    <row r="383" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:11">
       <c r="A383" s="15">
         <v>41556</v>
       </c>
@@ -29044,7 +29056,7 @@
         <v>64.648358122534788</v>
       </c>
     </row>
-    <row r="384" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:11">
       <c r="A384" s="15">
         <v>41563</v>
       </c>
@@ -29080,7 +29092,7 @@
         <v>30.40107245824677</v>
       </c>
     </row>
-    <row r="385" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:11">
       <c r="A385" s="15">
         <v>41570</v>
       </c>
@@ -29116,7 +29128,7 @@
         <v>46.050815851660722</v>
       </c>
     </row>
-    <row r="386" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:11">
       <c r="A386" s="15">
         <v>41577</v>
       </c>
@@ -29152,7 +29164,7 @@
         <v>29.663869105622428</v>
       </c>
     </row>
-    <row r="387" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:11">
       <c r="A387" s="15">
         <v>41584</v>
       </c>
@@ -29203,7 +29215,7 @@
         <v>29.763192589775961</v>
       </c>
     </row>
-    <row r="388" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:11">
       <c r="A388" s="15">
         <v>41591</v>
       </c>
@@ -29239,7 +29251,7 @@
         <v>53.718056830358535</v>
       </c>
     </row>
-    <row r="389" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:11">
       <c r="A389" s="15">
         <v>41598</v>
       </c>
@@ -29275,7 +29287,7 @@
         <v>47.320660371123139</v>
       </c>
     </row>
-    <row r="390" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:11">
       <c r="A390" s="15">
         <v>41605</v>
       </c>
@@ -29311,7 +29323,7 @@
         <v>26.84883647436958</v>
       </c>
     </row>
-    <row r="391" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:11">
       <c r="A391" s="15">
         <v>41612</v>
       </c>
@@ -29347,7 +29359,7 @@
         <v>30.228012575603316</v>
       </c>
     </row>
-    <row r="392" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:11">
       <c r="A392" s="15">
         <v>41619</v>
       </c>
@@ -29383,7 +29395,7 @@
         <v>35.628299402813028</v>
       </c>
     </row>
-    <row r="393" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:11">
       <c r="A393" s="15">
         <v>41626</v>
       </c>
@@ -29419,7 +29431,7 @@
         <v>29.564716897124189</v>
       </c>
     </row>
-    <row r="394" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:11">
       <c r="A394" s="15">
         <v>41634</v>
       </c>
@@ -29455,7 +29467,7 @@
         <v>25.48504766173663</v>
       </c>
     </row>
-    <row r="395" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:11">
       <c r="A395" s="15">
         <v>41641</v>
       </c>
@@ -29491,7 +29503,7 @@
         <v>29.440463564644233</v>
       </c>
     </row>
-    <row r="396" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:11">
       <c r="A396" s="15">
         <v>41647</v>
       </c>
@@ -29527,7 +29539,7 @@
         <v>36.868005424758209</v>
       </c>
     </row>
-    <row r="397" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:11">
       <c r="A397" s="15">
         <v>41654</v>
       </c>
@@ -29563,7 +29575,7 @@
         <v>33.543405654015224</v>
       </c>
     </row>
-    <row r="398" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:11">
       <c r="A398" s="15">
         <v>41661</v>
       </c>
@@ -29599,7 +29611,7 @@
         <v>33.281205492789098</v>
       </c>
     </row>
-    <row r="399" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:11">
       <c r="A399" s="15">
         <v>41668</v>
       </c>
@@ -29635,7 +29647,7 @@
         <v>48.6755678567065</v>
       </c>
     </row>
-    <row r="400" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:11">
       <c r="A400" s="15">
         <v>41675</v>
       </c>
@@ -29671,7 +29683,7 @@
         <v>48.899855436252473</v>
       </c>
     </row>
-    <row r="401" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:11">
       <c r="A401" s="15">
         <v>41682</v>
       </c>
@@ -29707,7 +29719,7 @@
         <v>50.456539714887306</v>
       </c>
     </row>
-    <row r="402" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:11">
       <c r="A402" s="15">
         <v>41689</v>
       </c>
@@ -29743,7 +29755,7 @@
         <v>53.893528968558918</v>
       </c>
     </row>
-    <row r="403" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:11">
       <c r="A403" s="15">
         <v>41696</v>
       </c>
@@ -29779,7 +29791,7 @@
         <v>32.173253175865931</v>
       </c>
     </row>
-    <row r="404" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:11">
       <c r="A404" s="15">
         <v>41703</v>
       </c>
@@ -29815,7 +29827,7 @@
         <v>28.177917475995674</v>
       </c>
     </row>
-    <row r="405" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:11">
       <c r="A405" s="15">
         <v>41710</v>
       </c>
@@ -29851,7 +29863,7 @@
         <v>38.591960706244812</v>
       </c>
     </row>
-    <row r="406" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:11">
       <c r="A406" s="15">
         <v>41716</v>
       </c>
@@ -29887,7 +29899,7 @@
         <v>62.434033436115925</v>
       </c>
     </row>
-    <row r="407" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:11">
       <c r="A407" s="15">
         <v>41717</v>
       </c>
@@ -29923,7 +29935,7 @@
         <v>38.474239554033893</v>
       </c>
     </row>
-    <row r="408" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:11">
       <c r="A408" s="15">
         <v>41724</v>
       </c>
@@ -29959,7 +29971,7 @@
         <v>30.022064656219442</v>
       </c>
     </row>
-    <row r="409" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:11">
       <c r="A409" s="15">
         <v>41731</v>
       </c>
@@ -29995,7 +30007,7 @@
         <v>44.188138476313277</v>
       </c>
     </row>
-    <row r="410" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:11">
       <c r="A410" s="15">
         <v>41738</v>
       </c>
@@ -30031,7 +30043,7 @@
         <v>31.323363729632899</v>
       </c>
     </row>
-    <row r="411" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:11">
       <c r="A411" s="15">
         <v>41745</v>
       </c>
@@ -30067,7 +30079,7 @@
         <v>35.606324792337006</v>
       </c>
     </row>
-    <row r="412" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:11">
       <c r="A412" s="15">
         <v>41752</v>
       </c>
@@ -30103,7 +30115,7 @@
         <v>35.382781553838939</v>
       </c>
     </row>
-    <row r="413" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:11">
       <c r="A413" s="15">
         <v>41759</v>
       </c>
@@ -30139,7 +30151,7 @@
         <v>45.803062444786249</v>
       </c>
     </row>
-    <row r="414" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:11">
       <c r="A414" s="15">
         <v>41766</v>
       </c>
@@ -30175,7 +30187,7 @@
         <v>37.395218193640751</v>
       </c>
     </row>
-    <row r="415" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:11">
       <c r="A415" s="15">
         <v>41773</v>
       </c>
@@ -30211,7 +30223,7 @@
         <v>30.364171137854051</v>
       </c>
     </row>
-    <row r="416" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:11">
       <c r="A416" s="15">
         <v>41780</v>
       </c>
@@ -30247,7 +30259,7 @@
         <v>46.926276851752007</v>
       </c>
     </row>
-    <row r="417" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:11">
       <c r="A417" s="15">
         <v>41787</v>
       </c>
@@ -30283,7 +30295,7 @@
         <v>56.381294114615542</v>
       </c>
     </row>
-    <row r="418" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:11">
       <c r="A418" s="15">
         <v>41794</v>
       </c>
@@ -30319,7 +30331,7 @@
         <v>42.349237020811792</v>
       </c>
     </row>
-    <row r="419" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:11">
       <c r="A419" s="15">
         <v>41801</v>
       </c>
@@ -30355,7 +30367,7 @@
         <v>38.373204647880215</v>
       </c>
     </row>
-    <row r="420" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:11">
       <c r="A420" s="15">
         <v>41808</v>
       </c>
@@ -30391,7 +30403,7 @@
         <v>44.314119769408713</v>
       </c>
     </row>
-    <row r="421" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:11">
       <c r="A421" s="15">
         <v>41815</v>
       </c>
@@ -30427,7 +30439,7 @@
         <v>60.45119572753616</v>
       </c>
     </row>
-    <row r="422" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:11">
       <c r="A422" s="15">
         <v>41822</v>
       </c>
@@ -30463,7 +30475,7 @@
         <v>47.49836466704955</v>
       </c>
     </row>
-    <row r="423" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:11">
       <c r="A423" s="15">
         <v>41829</v>
       </c>
@@ -30499,7 +30511,7 @@
         <v>35.064608489041966</v>
       </c>
     </row>
-    <row r="424" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:11">
       <c r="A424" s="15">
         <v>41836</v>
       </c>
@@ -30535,7 +30547,7 @@
         <v>44.721213423875326</v>
       </c>
     </row>
-    <row r="425" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:11">
       <c r="A425" s="15">
         <v>41843</v>
       </c>
@@ -30571,7 +30583,7 @@
         <v>39.312318980389804</v>
       </c>
     </row>
-    <row r="426" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:11">
       <c r="A426" s="15">
         <v>41850</v>
       </c>
@@ -30607,7 +30619,7 @@
         <v>34.47072790576</v>
       </c>
     </row>
-    <row r="427" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:11">
       <c r="A427" s="15">
         <v>41857</v>
       </c>
@@ -30643,7 +30655,7 @@
         <v>51.803015068152312</v>
       </c>
     </row>
-    <row r="428" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:11">
       <c r="A428" s="15">
         <v>41864</v>
       </c>
@@ -30679,7 +30691,7 @@
         <v>45.922649241726944</v>
       </c>
     </row>
-    <row r="429" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:11">
       <c r="A429" s="15">
         <v>41871</v>
       </c>
@@ -30715,7 +30727,7 @@
         <v>62.557833587887913</v>
       </c>
     </row>
-    <row r="430" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:11">
       <c r="A430" s="15">
         <v>41878</v>
       </c>
@@ -30751,7 +30763,7 @@
         <v>47.65914443041865</v>
       </c>
     </row>
-    <row r="431" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:11">
       <c r="A431" s="15">
         <v>41885</v>
       </c>
@@ -30787,7 +30799,7 @@
         <v>59.213557190072954</v>
       </c>
     </row>
-    <row r="432" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:11">
       <c r="A432" s="15">
         <v>41892</v>
       </c>
@@ -30823,7 +30835,7 @@
         <v>57.333019762644675</v>
       </c>
     </row>
-    <row r="433" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:11">
       <c r="A433" s="15">
         <v>41899</v>
       </c>
@@ -30859,7 +30871,7 @@
         <v>49.133395431991111</v>
       </c>
     </row>
-    <row r="434" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:11">
       <c r="A434" s="15">
         <v>41906</v>
       </c>
@@ -30895,7 +30907,7 @@
         <v>55.537677707137746</v>
       </c>
     </row>
-    <row r="435" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:11">
       <c r="A435" s="15">
         <v>41913</v>
       </c>
@@ -30931,7 +30943,7 @@
         <v>66.806525599248758</v>
       </c>
     </row>
-    <row r="436" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:11">
       <c r="A436" s="15">
         <v>41920</v>
       </c>
@@ -30967,7 +30979,7 @@
         <v>66.570355280429666</v>
       </c>
     </row>
-    <row r="437" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:11">
       <c r="A437" s="15">
         <v>41927</v>
       </c>
@@ -31003,7 +31015,7 @@
         <v>67.686973863523022</v>
       </c>
     </row>
-    <row r="438" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:11">
       <c r="A438" s="15">
         <v>41934</v>
       </c>
@@ -31039,7 +31051,7 @@
         <v>62.311923006128566</v>
       </c>
     </row>
-    <row r="439" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:11">
       <c r="A439" s="15">
         <v>41941</v>
       </c>
@@ -31075,7 +31087,7 @@
         <v>65.532799765784759</v>
       </c>
     </row>
-    <row r="440" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:11">
       <c r="A440" s="15">
         <v>41948</v>
       </c>
@@ -31111,7 +31123,7 @@
         <v>62.905619401035253</v>
       </c>
     </row>
-    <row r="441" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:11">
       <c r="A441" s="15">
         <v>41955</v>
       </c>
@@ -31147,7 +31159,7 @@
         <v>59.753766943925129</v>
       </c>
     </row>
-    <row r="442" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:11">
       <c r="A442" s="15">
         <v>41962</v>
       </c>
@@ -31183,7 +31195,7 @@
         <v>54.685208883890532</v>
       </c>
     </row>
-    <row r="443" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:11">
       <c r="A443" s="15">
         <v>41968</v>
       </c>
@@ -31219,7 +31231,7 @@
         <v>64.443637389582548</v>
       </c>
     </row>
-    <row r="444" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:11">
       <c r="A444" s="15">
         <v>41976</v>
       </c>
@@ -31255,7 +31267,7 @@
         <v>53.372403786390393</v>
       </c>
     </row>
-    <row r="445" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:11">
       <c r="A445" s="15">
         <v>41983</v>
       </c>
@@ -31291,7 +31303,7 @@
         <v>52.550400098141971</v>
       </c>
     </row>
-    <row r="446" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:11">
       <c r="A446" s="15">
         <v>41990</v>
       </c>
@@ -31327,7 +31339,7 @@
         <v>61.82397380318033</v>
       </c>
     </row>
-    <row r="447" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:11">
       <c r="A447" s="15">
         <v>41997</v>
       </c>
@@ -31363,7 +31375,7 @@
         <v>32.707053916439136</v>
       </c>
     </row>
-    <row r="448" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:11">
       <c r="A448" s="15">
         <v>42004</v>
       </c>
@@ -31399,7 +31411,7 @@
         <v>43.310807829305034</v>
       </c>
     </row>
-    <row r="449" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:11">
       <c r="A449" s="15">
         <v>42011</v>
       </c>
@@ -31435,7 +31447,7 @@
         <v>73.520753699141281</v>
       </c>
     </row>
-    <row r="450" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:11">
       <c r="A450" s="15">
         <v>42018</v>
       </c>
@@ -31471,7 +31483,7 @@
         <v>53.380532408043727</v>
       </c>
     </row>
-    <row r="451" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:11">
       <c r="A451" s="15">
         <v>42025</v>
       </c>
@@ -31522,7 +31534,7 @@
         <v>52.550400098141971</v>
       </c>
     </row>
-    <row r="452" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:11">
       <c r="A452" s="15">
         <v>42032</v>
       </c>
@@ -31558,7 +31570,7 @@
         <v>39.19736690032088</v>
       </c>
     </row>
-    <row r="453" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:11">
       <c r="A453" s="15">
         <v>42039</v>
       </c>
@@ -31594,7 +31606,7 @@
         <v>44.064003122982612</v>
       </c>
     </row>
-    <row r="454" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:11">
       <c r="A454" s="15">
         <v>42046</v>
       </c>
@@ -31630,7 +31642,7 @@
         <v>37.007673607771878</v>
       </c>
     </row>
-    <row r="455" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:11">
       <c r="A455" s="15">
         <v>42053</v>
       </c>
@@ -31666,7 +31678,7 @@
         <v>42.561466476456637</v>
       </c>
     </row>
-    <row r="456" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:11">
       <c r="A456" s="15">
         <v>42060</v>
       </c>
@@ -31702,7 +31714,7 @@
         <v>45.402755221031484</v>
       </c>
     </row>
-    <row r="457" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:11">
       <c r="A457" s="15">
         <v>42067</v>
       </c>
@@ -31738,7 +31750,7 @@
         <v>48.211272729748821</v>
       </c>
     </row>
-    <row r="458" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:11">
       <c r="A458" s="15">
         <v>42074</v>
       </c>
@@ -31774,7 +31786,7 @@
         <v>67.383421717313624</v>
       </c>
     </row>
-    <row r="459" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:11">
       <c r="A459" s="15">
         <v>42088</v>
       </c>
@@ -31810,7 +31822,7 @@
         <v>30.956834906605707</v>
       </c>
     </row>
-    <row r="460" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:11">
       <c r="A460" s="15">
         <v>42095</v>
       </c>
@@ -31846,7 +31858,7 @@
         <v>54.500081021599833</v>
       </c>
     </row>
-    <row r="461" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:11">
       <c r="A461" s="15">
         <v>42102</v>
       </c>
@@ -31882,7 +31894,7 @@
         <v>28.291363992271719</v>
       </c>
     </row>
-    <row r="462" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:11">
       <c r="A462" s="15">
         <v>42109</v>
       </c>
@@ -31918,7 +31930,7 @@
         <v>40.543750857694739</v>
       </c>
     </row>
-    <row r="463" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:11">
       <c r="A463" s="15">
         <v>42116</v>
       </c>
@@ -31954,7 +31966,7 @@
         <v>59.571201699918042</v>
       </c>
     </row>
-    <row r="464" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:11">
       <c r="A464" s="15">
         <v>42123</v>
       </c>
@@ -31990,7 +32002,7 @@
         <v>34.27313982014654</v>
       </c>
     </row>
-    <row r="465" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="465" spans="1:11">
       <c r="A465" s="15">
         <v>42130</v>
       </c>
@@ -32026,7 +32038,7 @@
         <v>56.955691995283715</v>
       </c>
     </row>
-    <row r="466" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:11">
       <c r="A466" s="15">
         <v>42137</v>
       </c>
@@ -32062,7 +32074,7 @@
         <v>54.764046582566408</v>
       </c>
     </row>
-    <row r="467" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:11">
       <c r="A467" s="15">
         <v>42144</v>
       </c>
@@ -32098,7 +32110,7 @@
         <v>55.757136500127764</v>
       </c>
     </row>
-    <row r="468" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:11">
       <c r="A468" s="15">
         <v>42151</v>
       </c>
@@ -32134,7 +32146,7 @@
         <v>59.139689894729841</v>
       </c>
     </row>
-    <row r="469" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:11">
       <c r="A469" s="15">
         <v>42158</v>
       </c>
@@ -32170,7 +32182,7 @@
         <v>58.565690013670491</v>
       </c>
     </row>
-    <row r="470" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:11">
       <c r="A470" s="15">
         <v>42165</v>
       </c>
@@ -32206,7 +32218,7 @@
         <v>58.285726582262178</v>
       </c>
     </row>
-    <row r="471" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:11">
       <c r="A471" s="15">
         <v>42172</v>
       </c>
@@ -32242,7 +32254,7 @@
         <v>51.057335391353512</v>
       </c>
     </row>
-    <row r="472" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="472" spans="1:11">
       <c r="A472" s="15">
         <v>42179</v>
       </c>
@@ -32278,7 +32290,7 @@
         <v>58.045476963818579</v>
       </c>
     </row>
-    <row r="473" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:11">
       <c r="A473" s="15">
         <v>42186</v>
       </c>
@@ -32314,7 +32326,7 @@
         <v>60.134571875867529</v>
       </c>
     </row>
-    <row r="474" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:11">
       <c r="A474" s="15">
         <v>42193</v>
       </c>
@@ -32350,7 +32362,7 @@
         <v>64.152197101026005</v>
       </c>
     </row>
-    <row r="475" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="475" spans="1:11">
       <c r="A475" s="15">
         <v>42200</v>
       </c>
@@ -32386,7 +32398,7 @@
         <v>62.876249643492336</v>
       </c>
     </row>
-    <row r="476" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="476" spans="1:11">
       <c r="A476" s="15">
         <v>42207</v>
       </c>
@@ -32422,7 +32434,7 @@
         <v>69.115289526281927</v>
       </c>
     </row>
-    <row r="477" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:11">
       <c r="A477" s="15">
         <v>42214</v>
       </c>
@@ -32458,7 +32470,7 @@
         <v>65.005582381367375</v>
       </c>
     </row>
-    <row r="478" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:11">
       <c r="A478" s="15">
         <v>42221</v>
       </c>
@@ -32494,7 +32506,7 @@
         <v>63.076909141434115</v>
       </c>
     </row>
-    <row r="479" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:11">
       <c r="A479" s="15">
         <v>42228</v>
       </c>
@@ -32530,7 +32542,7 @@
         <v>62.189535700762221</v>
       </c>
     </row>
-    <row r="480" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:11">
       <c r="A480" s="15">
         <v>42235</v>
       </c>
@@ -32566,7 +32578,7 @@
         <v>56.905421187389813</v>
       </c>
     </row>
-    <row r="481" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:11">
       <c r="A481" s="15">
         <v>42242</v>
       </c>
@@ -32602,7 +32614,7 @@
         <v>54.437212556646394</v>
       </c>
     </row>
-    <row r="482" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:11">
       <c r="A482" s="15">
         <v>42249</v>
       </c>
@@ -32638,7 +32650,7 @@
         <v>45.740626444393065</v>
       </c>
     </row>
-    <row r="483" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:11">
       <c r="A483" s="15">
         <v>42256</v>
       </c>
@@ -32674,7 +32686,7 @@
         <v>39.805313843808364</v>
       </c>
     </row>
-    <row r="484" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:11">
       <c r="A484" s="15">
         <v>42263</v>
       </c>
@@ -32710,7 +32722,7 @@
         <v>43.806543446148218</v>
       </c>
     </row>
-    <row r="485" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:11">
       <c r="A485" s="15">
         <v>42270</v>
       </c>
@@ -32746,7 +32758,7 @@
         <v>51.716685867776327</v>
       </c>
     </row>
-    <row r="486" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="486" spans="1:11">
       <c r="A486" s="15">
         <v>42277</v>
       </c>
@@ -32782,7 +32794,7 @@
         <v>58.081158609585614</v>
       </c>
     </row>
-    <row r="487" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="487" spans="1:11">
       <c r="A487" s="15">
         <v>42284</v>
       </c>
@@ -32818,7 +32830,7 @@
         <v>56.825158228391729</v>
       </c>
     </row>
-    <row r="488" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="488" spans="1:11">
       <c r="A488" s="15">
         <v>42291</v>
       </c>
@@ -32854,7 +32866,7 @@
         <v>67.174925319764782</v>
       </c>
     </row>
-    <row r="489" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:11">
       <c r="A489" s="15">
         <v>42298</v>
       </c>
@@ -32890,7 +32902,7 @@
         <v>45.345586579315764</v>
       </c>
     </row>
-    <row r="490" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="490" spans="1:11">
       <c r="A490" s="15">
         <v>42305</v>
       </c>
@@ -32926,7 +32938,7 @@
         <v>57.374167645036572</v>
       </c>
     </row>
-    <row r="491" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:11">
       <c r="A491" s="15">
         <v>42312</v>
       </c>
@@ -32962,7 +32974,7 @@
         <v>51.179056631292994</v>
       </c>
     </row>
-    <row r="492" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="492" spans="1:11">
       <c r="A492" s="15">
         <v>42319</v>
       </c>
@@ -32998,7 +33010,7 @@
         <v>53.107945174576969</v>
       </c>
     </row>
-    <row r="493" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="493" spans="1:11">
       <c r="A493" s="15">
         <v>42326</v>
       </c>
@@ -33034,7 +33046,7 @@
         <v>58.422447069085209</v>
       </c>
     </row>
-    <row r="494" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:11">
       <c r="A494" s="15">
         <v>42333</v>
       </c>
@@ -33070,7 +33082,7 @@
         <v>34.740224585926597</v>
       </c>
     </row>
-    <row r="495" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:11">
       <c r="A495" s="15">
         <v>42340</v>
       </c>
@@ -33106,7 +33118,7 @@
         <v>53.475606892716783</v>
       </c>
     </row>
-    <row r="496" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="496" spans="1:11">
       <c r="A496" s="15">
         <v>42347</v>
       </c>
@@ -33142,7 +33154,7 @@
         <v>49.782638326185712</v>
       </c>
     </row>
-    <row r="497" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="497" spans="1:11">
       <c r="A497" s="15">
         <v>42354</v>
       </c>
@@ -33178,7 +33190,7 @@
         <v>64.682794789944978</v>
       </c>
     </row>
-    <row r="498" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="498" spans="1:11">
       <c r="A498" s="15">
         <v>42361</v>
       </c>
@@ -33214,7 +33226,7 @@
         <v>58.632036840912747</v>
       </c>
     </row>
-    <row r="499" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="499" spans="1:11">
       <c r="A499" s="15">
         <v>42368</v>
       </c>
@@ -33250,7 +33262,7 @@
         <v>60.952600023373698</v>
       </c>
     </row>
-    <row r="500" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="500" spans="1:11">
       <c r="A500" s="15">
         <v>42375</v>
       </c>
@@ -33286,7 +33298,7 @@
         <v>66.58828791661989</v>
       </c>
     </row>
-    <row r="501" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="501" spans="1:11">
       <c r="A501" s="15">
         <v>42382</v>
       </c>
@@ -33322,7 +33334,7 @@
         <v>64.934642249421515</v>
       </c>
     </row>
-    <row r="502" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="502" spans="1:11">
       <c r="A502" s="15">
         <v>42396</v>
       </c>
@@ -33358,7 +33370,7 @@
         <v>41.40576650661113</v>
       </c>
     </row>
-    <row r="503" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="503" spans="1:11">
       <c r="A503" s="15">
         <v>42403</v>
       </c>
@@ -33394,7 +33406,7 @@
         <v>31.776137400465753</v>
       </c>
     </row>
-    <row r="504" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="504" spans="1:11">
       <c r="A504" s="15">
         <v>42410</v>
       </c>
@@ -33430,7 +33442,7 @@
         <v>53.128851841152972</v>
       </c>
     </row>
-    <row r="505" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="505" spans="1:11">
       <c r="A505" s="15">
         <v>42417</v>
       </c>
@@ -33466,7 +33478,7 @@
         <v>38.552772794324362</v>
       </c>
     </row>
-    <row r="506" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="506" spans="1:11">
       <c r="A506" s="15">
         <v>42424</v>
       </c>
@@ -33502,7 +33514,7 @@
         <v>57.386093846065783</v>
       </c>
     </row>
-    <row r="507" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="507" spans="1:11">
       <c r="A507" s="15">
         <v>42431</v>
       </c>
@@ -33538,7 +33550,7 @@
         <v>56.216108002049303</v>
       </c>
     </row>
-    <row r="508" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="508" spans="1:11">
       <c r="A508" s="15">
         <v>42438</v>
       </c>
@@ -33574,7 +33586,7 @@
         <v>49.345050684492676</v>
       </c>
     </row>
-    <row r="509" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="509" spans="1:11">
       <c r="A509" s="15">
         <v>42445</v>
       </c>
@@ -33610,7 +33622,7 @@
         <v>47.469934929618582</v>
       </c>
     </row>
-    <row r="510" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="510" spans="1:11">
       <c r="A510" s="15">
         <v>42452</v>
       </c>
@@ -33646,7 +33658,7 @@
         <v>55.942502690409157</v>
       </c>
     </row>
-    <row r="511" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="511" spans="1:11">
       <c r="A511" s="15">
         <v>42459</v>
       </c>
@@ -33682,7 +33694,7 @@
         <v>51.171281684204004</v>
       </c>
     </row>
-    <row r="512" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="512" spans="1:11">
       <c r="A512" s="15">
         <v>42466</v>
       </c>
@@ -33718,7 +33730,7 @@
         <v>44.987298684587493</v>
       </c>
     </row>
-    <row r="513" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="513" spans="1:11">
       <c r="A513" s="15">
         <v>42473</v>
       </c>
@@ -33754,7 +33766,7 @@
         <v>52.267754767722032</v>
       </c>
     </row>
-    <row r="514" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="514" spans="1:11">
       <c r="A514" s="15">
         <v>42480</v>
       </c>
@@ -33790,7 +33802,7 @@
         <v>59.274689783916969</v>
       </c>
     </row>
-    <row r="515" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="515" spans="1:11">
       <c r="A515" s="15">
         <v>42487</v>
       </c>
@@ -33841,7 +33853,7 @@
         <v>56.059043268503345</v>
       </c>
     </row>
-    <row r="516" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="516" spans="1:11">
       <c r="A516" s="15">
         <v>42494</v>
       </c>
@@ -33877,7 +33889,7 @@
         <v>63.557616832598796</v>
       </c>
     </row>
-    <row r="517" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="517" spans="1:11">
       <c r="A517" s="15">
         <v>42501</v>
       </c>
@@ -33913,7 +33925,7 @@
         <v>60.325228184861054</v>
       </c>
     </row>
-    <row r="518" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="518" spans="1:11">
       <c r="A518" s="15">
         <v>42508</v>
       </c>
@@ -33949,7 +33961,7 @@
         <v>66.025148795269672</v>
       </c>
     </row>
-    <row r="519" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="519" spans="1:11">
       <c r="A519" s="15">
         <v>42515</v>
       </c>
@@ -33985,7 +33997,7 @@
         <v>65.838860527469308</v>
       </c>
     </row>
-    <row r="520" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="520" spans="1:11">
       <c r="A520" s="15">
         <v>42522</v>
       </c>
@@ -34021,7 +34033,7 @@
         <v>58.204477883361697</v>
       </c>
     </row>
-    <row r="521" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="521" spans="1:11">
       <c r="A521" s="15">
         <v>42529</v>
       </c>
@@ -34057,7 +34069,7 @@
         <v>67.614110056909553</v>
       </c>
     </row>
-    <row r="522" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="522" spans="1:11">
       <c r="A522" s="15">
         <v>42536</v>
       </c>
@@ -34093,7 +34105,7 @@
         <v>74.11356391861203</v>
       </c>
     </row>
-    <row r="523" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="523" spans="1:11">
       <c r="A523" s="15">
         <v>42543</v>
       </c>
@@ -34129,7 +34141,7 @@
         <v>73.151472857827756</v>
       </c>
     </row>
-    <row r="524" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="524" spans="1:11">
       <c r="A524" s="15">
         <v>42550</v>
       </c>
@@ -34165,7 +34177,7 @@
         <v>61.145192933839347</v>
       </c>
     </row>
-    <row r="525" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="525" spans="1:11">
       <c r="A525" s="15">
         <v>42557</v>
       </c>
@@ -34201,7 +34213,7 @@
         <v>59.461294600399974</v>
       </c>
     </row>
-    <row r="526" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="526" spans="1:11">
       <c r="A526" s="15">
         <v>42564</v>
       </c>
@@ -34237,7 +34249,7 @@
         <v>55.474316952158986</v>
       </c>
     </row>
-    <row r="527" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="527" spans="1:11">
       <c r="A527" s="15">
         <v>42571</v>
       </c>
@@ -34273,7 +34285,7 @@
         <v>47.642829505911699</v>
       </c>
     </row>
-    <row r="528" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="528" spans="1:11">
       <c r="A528" s="15">
         <v>42578</v>
       </c>
@@ -34309,7 +34321,7 @@
         <v>38.757015074458316</v>
       </c>
     </row>
-    <row r="529" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="529" spans="1:11">
       <c r="A529" s="15">
         <v>42585</v>
       </c>
@@ -34345,7 +34357,7 @@
         <v>40.898792194128127</v>
       </c>
     </row>
-    <row r="530" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="530" spans="1:11">
       <c r="A530" s="15">
         <v>42592</v>
       </c>
@@ -34381,7 +34393,7 @@
         <v>44.684911157119551</v>
       </c>
     </row>
-    <row r="531" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="531" spans="1:11">
       <c r="A531" s="15">
         <v>42599</v>
       </c>
@@ -34417,7 +34429,7 @@
         <v>38.351540526685874</v>
       </c>
     </row>
-    <row r="532" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="532" spans="1:11">
       <c r="A532" s="15">
         <v>42606</v>
       </c>
@@ -34453,7 +34465,7 @@
         <v>52.845347659285657</v>
       </c>
     </row>
-    <row r="533" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="533" spans="1:11">
       <c r="A533" s="15">
         <v>42613</v>
       </c>
@@ -34489,7 +34501,7 @@
         <v>50.592178955136646</v>
       </c>
     </row>
-    <row r="534" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="534" spans="1:11">
       <c r="A534" s="15">
         <v>42620</v>
       </c>
@@ -34525,7 +34537,7 @@
         <v>45.8727017663767</v>
       </c>
     </row>
-    <row r="535" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="535" spans="1:11">
       <c r="A535" s="15">
         <v>42627</v>
       </c>
@@ -34561,7 +34573,7 @@
         <v>74.814030546861105</v>
       </c>
     </row>
-    <row r="536" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="536" spans="1:11">
       <c r="A536" s="15">
         <v>42634</v>
       </c>
@@ -34597,7 +34609,7 @@
         <v>53.632347230101267</v>
       </c>
     </row>
-    <row r="537" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="537" spans="1:11">
       <c r="A537" s="15">
         <v>42641</v>
       </c>
@@ -34633,7 +34645,7 @@
         <v>48.896571681685643</v>
       </c>
     </row>
-    <row r="538" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="538" spans="1:11">
       <c r="A538" s="15">
         <v>42648</v>
       </c>
@@ -34669,7 +34681,7 @@
         <v>61.205113840328835</v>
       </c>
     </row>
-    <row r="539" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="539" spans="1:11">
       <c r="A539" s="15">
         <v>42655</v>
       </c>
@@ -34705,7 +34717,7 @@
         <v>57.785327901705259</v>
       </c>
     </row>
-    <row r="540" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="540" spans="1:11">
       <c r="A540" s="15">
         <v>42662</v>
       </c>
@@ -34741,7 +34753,7 @@
         <v>79.940100561197539</v>
       </c>
     </row>
-    <row r="541" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="541" spans="1:11">
       <c r="A541" s="15">
         <v>42669</v>
       </c>
@@ -34777,7 +34789,7 @@
         <v>73.199803298495794</v>
       </c>
     </row>
-    <row r="542" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="542" spans="1:11">
       <c r="A542" s="15">
         <v>42676</v>
       </c>
@@ -34813,7 +34825,7 @@
         <v>81.972971493996454</v>
       </c>
     </row>
-    <row r="543" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="543" spans="1:11">
       <c r="A543" s="15">
         <v>42683</v>
       </c>
@@ -34849,7 +34861,7 @@
         <v>70.252181451028676</v>
       </c>
     </row>
-    <row r="544" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="544" spans="1:11">
       <c r="A544" s="15">
         <v>42689</v>
       </c>
@@ -34885,7 +34897,7 @@
         <v>45.034554333138182</v>
       </c>
     </row>
-    <row r="545" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="545" spans="1:11">
       <c r="A545" s="15">
         <v>42697</v>
       </c>
@@ -34921,7 +34933,7 @@
         <v>31.902622834964525</v>
       </c>
     </row>
-    <row r="546" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="546" spans="1:11">
       <c r="A546" s="15">
         <v>42704</v>
       </c>
@@ -34957,7 +34969,7 @@
         <v>33.812107442362681</v>
       </c>
     </row>
-    <row r="547" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="547" spans="1:11">
       <c r="A547" s="15">
         <v>42711</v>
       </c>
@@ -34993,7 +35005,7 @@
         <v>44.571790079241985</v>
       </c>
     </row>
-    <row r="548" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="548" spans="1:11">
       <c r="A548" s="15">
         <v>42718</v>
       </c>
@@ -35029,7 +35041,7 @@
         <v>51.225600837105361</v>
       </c>
     </row>
-    <row r="549" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="549" spans="1:11">
       <c r="A549" s="15">
         <v>42725</v>
       </c>
@@ -35065,7 +35077,7 @@
         <v>31.324298121335335</v>
       </c>
     </row>
-    <row r="550" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="550" spans="1:11">
       <c r="A550" s="15">
         <v>42732</v>
       </c>
@@ -35101,7 +35113,7 @@
         <v>40.560500686953205</v>
       </c>
     </row>
-    <row r="551" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="551" spans="1:11">
       <c r="A551" s="15">
         <v>42739</v>
       </c>
@@ -35137,7 +35149,7 @@
         <v>41.368869961849803</v>
       </c>
     </row>
-    <row r="552" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="552" spans="1:11">
       <c r="A552" s="15">
         <v>42746</v>
       </c>
@@ -35173,7 +35185,7 @@
         <v>36.188090354038536</v>
       </c>
     </row>
-    <row r="553" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="553" spans="1:11">
       <c r="A553" s="15">
         <v>42753</v>
       </c>
@@ -35209,7 +35221,7 @@
         <v>37.743249902447104</v>
       </c>
     </row>
-    <row r="554" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="554" spans="1:11">
       <c r="A554" s="15">
         <v>42760</v>
       </c>
@@ -35245,7 +35257,7 @@
         <v>38.125600177425255</v>
       </c>
     </row>
-    <row r="555" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="555" spans="1:11">
       <c r="A555" s="15">
         <v>42767</v>
       </c>
@@ -35281,7 +35293,7 @@
         <v>35.21374453775752</v>
       </c>
     </row>
-    <row r="556" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="556" spans="1:11">
       <c r="A556" s="15">
         <v>42774</v>
       </c>
@@ -35317,7 +35329,7 @@
         <v>37.200813418944776</v>
       </c>
     </row>
-    <row r="557" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="557" spans="1:11">
       <c r="A557" s="15">
         <v>42781</v>
       </c>
@@ -35353,7 +35365,7 @@
         <v>46.401461865606194</v>
       </c>
     </row>
-    <row r="558" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="558" spans="1:11">
       <c r="A558" s="15">
         <v>42788</v>
       </c>
@@ -35389,7 +35401,7 @@
         <v>47.306097125086168</v>
       </c>
     </row>
-    <row r="559" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="559" spans="1:11">
       <c r="A559" s="15">
         <v>42795</v>
       </c>
@@ -35425,7 +35437,7 @@
         <v>40.981014136054526</v>
       </c>
     </row>
-    <row r="560" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="560" spans="1:11">
       <c r="A560" s="15">
         <v>42802</v>
       </c>
@@ -35461,7 +35473,7 @@
         <v>33.994932520079296</v>
       </c>
     </row>
-    <row r="561" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="561" spans="1:11">
       <c r="A561" s="15">
         <v>42809</v>
       </c>
@@ -35497,7 +35509,7 @@
         <v>44.968363852363964</v>
       </c>
     </row>
-    <row r="562" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="562" spans="1:11">
       <c r="A562" s="15">
         <v>42816</v>
       </c>
@@ -35533,7 +35545,7 @@
         <v>49.659201917259722</v>
       </c>
     </row>
-    <row r="563" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="563" spans="1:11">
       <c r="A563" s="15">
         <v>42823</v>
       </c>
@@ -35569,7 +35581,7 @@
         <v>64.362780454268531</v>
       </c>
     </row>
-    <row r="564" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="564" spans="1:11">
       <c r="A564" s="15">
         <v>42830</v>
       </c>
@@ -35605,7 +35617,7 @@
         <v>64.776799001384475</v>
       </c>
     </row>
-    <row r="565" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="565" spans="1:11">
       <c r="A565" s="15">
         <v>42837</v>
       </c>
@@ -35641,7 +35653,7 @@
         <v>65.166932244503599</v>
       </c>
     </row>
-    <row r="566" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="566" spans="1:11">
       <c r="A566" s="15">
         <v>42844</v>
       </c>
@@ -35677,7 +35689,7 @@
         <v>59.958870200350503</v>
       </c>
     </row>
-    <row r="567" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="567" spans="1:11">
       <c r="A567" s="15">
         <v>42851</v>
       </c>
@@ -35713,7 +35725,7 @@
         <v>59.381621852968017</v>
       </c>
     </row>
-    <row r="568" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="568" spans="1:11">
       <c r="A568" s="15">
         <v>42858</v>
       </c>
@@ -35749,7 +35761,7 @@
         <v>43.61543763393874</v>
       </c>
     </row>
-    <row r="569" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="569" spans="1:11">
       <c r="A569" s="15">
         <v>42865</v>
       </c>
@@ -35785,7 +35797,7 @@
         <v>45.396879132363082</v>
       </c>
     </row>
-    <row r="570" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="570" spans="1:11">
       <c r="A570" s="15">
         <v>42872</v>
       </c>
@@ -35821,7 +35833,7 @@
         <v>57.001842496633159</v>
       </c>
     </row>
-    <row r="571" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="571" spans="1:11">
       <c r="A571" s="15">
         <v>42879</v>
       </c>
@@ -35857,7 +35869,7 @@
         <v>43.069217656771137</v>
       </c>
     </row>
-    <row r="572" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="572" spans="1:11">
       <c r="A572" s="15">
         <v>42886</v>
       </c>
@@ -35893,7 +35905,7 @@
         <v>48.392374712148168</v>
       </c>
     </row>
-    <row r="573" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="573" spans="1:11">
       <c r="A573" s="15">
         <v>42893</v>
       </c>
@@ -35929,7 +35941,7 @@
         <v>40.948483493075209</v>
       </c>
     </row>
-    <row r="574" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="574" spans="1:11">
       <c r="A574" s="15">
         <v>42900</v>
       </c>
@@ -35965,7 +35977,7 @@
         <v>37.402091766235387</v>
       </c>
     </row>
-    <row r="575" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="575" spans="1:11">
       <c r="A575" s="15">
         <v>42907</v>
       </c>
@@ -36001,7 +36013,7 @@
         <v>46.287563991280784</v>
       </c>
     </row>
-    <row r="576" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="576" spans="1:11">
       <c r="A576" s="15">
         <v>42914</v>
       </c>
@@ -36037,7 +36049,7 @@
         <v>51.63023920146022</v>
       </c>
     </row>
-    <row r="577" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="577" spans="1:11">
       <c r="A577" s="15">
         <v>42921</v>
       </c>
@@ -36073,7 +36085,7 @@
         <v>38.938715947404972</v>
       </c>
     </row>
-    <row r="578" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="578" spans="1:11">
       <c r="A578" s="15">
         <v>42928</v>
       </c>
@@ -36109,7 +36121,7 @@
         <v>32.992166958557021</v>
       </c>
     </row>
-    <row r="579" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="579" spans="1:11">
       <c r="A579" s="15">
         <v>42935</v>
       </c>
@@ -36160,7 +36172,7 @@
         <v>41.819650581896475</v>
       </c>
     </row>
-    <row r="580" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="580" spans="1:11">
       <c r="A580" s="15">
         <v>42942</v>
       </c>
@@ -36196,7 +36208,7 @@
         <v>50.264603848036046</v>
       </c>
     </row>
-    <row r="581" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="581" spans="1:11">
       <c r="A581" s="15">
         <v>42949</v>
       </c>
@@ -36232,7 +36244,7 @@
         <v>42.982310991380189</v>
       </c>
     </row>
-    <row r="582" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="582" spans="1:11">
       <c r="A582" s="15">
         <v>42956</v>
       </c>
@@ -36268,7 +36280,7 @@
         <v>42.602862162618685</v>
       </c>
     </row>
-    <row r="583" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="583" spans="1:11">
       <c r="A583" s="15">
         <v>42963</v>
       </c>
@@ -36304,7 +36316,7 @@
         <v>35.515471002867969</v>
       </c>
     </row>
-    <row r="584" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="584" spans="1:11">
       <c r="A584" s="15">
         <v>42970</v>
       </c>
@@ -36340,7 +36352,7 @@
         <v>41.20422836194178</v>
       </c>
     </row>
-    <row r="585" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="585" spans="1:11">
       <c r="A585" s="15">
         <v>42977</v>
       </c>
@@ -36376,7 +36388,7 @@
         <v>46.305875728509086</v>
       </c>
     </row>
-    <row r="586" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="586" spans="1:11">
       <c r="A586" s="15">
         <v>42984</v>
       </c>
@@ -36412,7 +36424,7 @@
         <v>52.28157999497369</v>
       </c>
     </row>
-    <row r="587" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="587" spans="1:11">
       <c r="A587" s="15">
         <v>42991</v>
       </c>
@@ -36448,7 +36460,7 @@
         <v>45.246656707228858</v>
       </c>
     </row>
-    <row r="588" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="588" spans="1:11">
       <c r="A588" s="15">
         <v>42998</v>
       </c>
@@ -36484,7 +36496,7 @@
         <v>42.836271786367632</v>
       </c>
     </row>
-    <row r="589" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="589" spans="1:11">
       <c r="A589" s="15">
         <v>43005</v>
       </c>
@@ -36520,7 +36532,7 @@
         <v>25.850229689501795</v>
       </c>
     </row>
-    <row r="590" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="590" spans="1:11">
       <c r="A590" s="15">
         <v>43012</v>
       </c>
@@ -36556,7 +36568,7 @@
         <v>29.219171788399478</v>
       </c>
     </row>
-    <row r="591" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="591" spans="1:11">
       <c r="A591" s="15">
         <v>43019</v>
       </c>
@@ -36592,7 +36604,7 @@
         <v>47.697764295090394</v>
       </c>
     </row>
-    <row r="592" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="592" spans="1:11">
       <c r="A592" s="15">
         <v>43026</v>
       </c>
@@ -36628,7 +36640,7 @@
         <v>38.422382980352594</v>
       </c>
     </row>
-    <row r="593" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="593" spans="1:11">
       <c r="A593" s="15">
         <v>43033</v>
       </c>
@@ -36664,7 +36676,7 @@
         <v>64.258296622360419</v>
       </c>
     </row>
-    <row r="594" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="594" spans="1:11">
       <c r="A594" s="15">
         <v>43040</v>
       </c>
@@ -36700,7 +36712,7 @@
         <v>57.905260906954553</v>
       </c>
     </row>
-    <row r="595" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="595" spans="1:11">
       <c r="A595" s="15">
         <v>43047</v>
       </c>
@@ -36736,7 +36748,7 @@
         <v>34.736286502733705</v>
       </c>
     </row>
-    <row r="596" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="596" spans="1:11">
       <c r="A596" s="15">
         <v>43054</v>
       </c>
@@ -36772,7 +36784,7 @@
         <v>68.592291112048443</v>
       </c>
     </row>
-    <row r="597" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="597" spans="1:11">
       <c r="A597" s="15">
         <v>43061</v>
       </c>
@@ -36808,7 +36820,7 @@
         <v>27.3096898737011</v>
       </c>
     </row>
-    <row r="598" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="598" spans="1:11">
       <c r="A598" s="15">
         <v>43068</v>
       </c>
@@ -36844,7 +36856,7 @@
         <v>47.380261477684584</v>
       </c>
     </row>
-    <row r="599" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="599" spans="1:11">
       <c r="A599" s="15">
         <v>43075</v>
       </c>
@@ -36880,7 +36892,7 @@
         <v>48.440037392978304</v>
       </c>
     </row>
-    <row r="600" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="600" spans="1:11">
       <c r="A600" s="15">
         <v>43082</v>
       </c>
@@ -36916,7 +36928,7 @@
         <v>44.562343622567724</v>
       </c>
     </row>
-    <row r="601" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="601" spans="1:11">
       <c r="A601" s="15">
         <v>43089</v>
       </c>
@@ -36952,7 +36964,7 @@
         <v>36.623281382599032</v>
       </c>
     </row>
-    <row r="602" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="602" spans="1:11">
       <c r="A602" s="15">
         <v>43096</v>
       </c>
@@ -36988,7 +37000,7 @@
         <v>34.643577434597006</v>
       </c>
     </row>
-    <row r="603" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="603" spans="1:11">
       <c r="A603" s="15">
         <v>43103</v>
       </c>
@@ -37024,7 +37036,7 @@
         <v>25.360655270394762</v>
       </c>
     </row>
-    <row r="604" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="604" spans="1:11">
       <c r="A604" s="15">
         <v>43110</v>
       </c>
@@ -37060,7 +37072,7 @@
         <v>25.396638870684793</v>
       </c>
     </row>
-    <row r="605" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="605" spans="1:11">
       <c r="A605" s="15">
         <v>43117</v>
       </c>
@@ -37096,7 +37108,7 @@
         <v>27.71</v>
       </c>
     </row>
-    <row r="606" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="606" spans="1:11">
       <c r="A606" s="15">
         <v>43124</v>
       </c>
@@ -37132,7 +37144,7 @@
         <v>29.33</v>
       </c>
     </row>
-    <row r="607" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="607" spans="1:11">
       <c r="A607" s="15">
         <v>43131</v>
       </c>
@@ -37168,7 +37180,7 @@
         <v>53.07</v>
       </c>
     </row>
-    <row r="608" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="608" spans="1:11">
       <c r="A608" s="15">
         <v>43138</v>
       </c>
@@ -37204,7 +37216,7 @@
         <v>44.02</v>
       </c>
     </row>
-    <row r="609" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="609" spans="1:11">
       <c r="A609" s="15">
         <v>43145</v>
       </c>
@@ -37240,7 +37252,7 @@
         <v>55.52</v>
       </c>
     </row>
-    <row r="610" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="610" spans="1:11">
       <c r="A610" s="15">
         <v>43152</v>
       </c>
@@ -37276,7 +37288,7 @@
         <v>50.17</v>
       </c>
     </row>
-    <row r="611" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="611" spans="1:11">
       <c r="A611" s="15">
         <v>43159</v>
       </c>
@@ -37312,7 +37324,7 @@
         <v>34.54</v>
       </c>
     </row>
-    <row r="612" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="612" spans="1:11">
       <c r="A612" s="15">
         <v>43166</v>
       </c>
@@ -37348,7 +37360,7 @@
         <v>53.35</v>
       </c>
     </row>
-    <row r="613" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="613" spans="1:11">
       <c r="A613" s="15">
         <v>43173</v>
       </c>
@@ -37384,7 +37396,7 @@
         <v>34.69</v>
       </c>
     </row>
-    <row r="614" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="614" spans="1:11">
       <c r="A614" s="15">
         <v>43180</v>
       </c>
@@ -37420,7 +37432,7 @@
         <v>50.12</v>
       </c>
     </row>
-    <row r="615" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="615" spans="1:11">
       <c r="A615" s="15">
         <v>43187</v>
       </c>
@@ -37456,7 +37468,7 @@
         <v>66.569999999999993</v>
       </c>
     </row>
-    <row r="616" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="616" spans="1:11">
       <c r="A616" s="15">
         <v>43194</v>
       </c>
@@ -37492,7 +37504,7 @@
         <v>58.83</v>
       </c>
     </row>
-    <row r="617" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="617" spans="1:11">
       <c r="A617" s="15">
         <v>43201</v>
       </c>
@@ -37528,7 +37540,7 @@
         <v>48.61</v>
       </c>
     </row>
-    <row r="618" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="618" spans="1:11">
       <c r="A618" s="15">
         <v>43208</v>
       </c>
@@ -37564,7 +37576,7 @@
         <v>38.979999999999997</v>
       </c>
     </row>
-    <row r="619" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="619" spans="1:11">
       <c r="A619" s="15">
         <v>43215</v>
       </c>
@@ -37600,7 +37612,7 @@
         <v>63.14</v>
       </c>
     </row>
-    <row r="620" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="620" spans="1:11">
       <c r="A620" s="15">
         <v>43222</v>
       </c>
@@ -37636,7 +37648,7 @@
         <v>68.150000000000006</v>
       </c>
     </row>
-    <row r="621" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="621" spans="1:11">
       <c r="A621" s="15">
         <v>43229</v>
       </c>
@@ -37672,7 +37684,7 @@
         <v>39.549999999999997</v>
       </c>
     </row>
-    <row r="622" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="622" spans="1:11">
       <c r="A622" s="15">
         <v>43236</v>
       </c>
@@ -37708,7 +37720,7 @@
         <v>54.33</v>
       </c>
     </row>
-    <row r="623" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="623" spans="1:11">
       <c r="A623" s="15">
         <v>43243</v>
       </c>
@@ -37744,7 +37756,7 @@
         <v>53.99</v>
       </c>
     </row>
-    <row r="624" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="624" spans="1:11">
       <c r="A624" s="15">
         <v>43250</v>
       </c>
@@ -37780,7 +37792,7 @@
         <v>39.76</v>
       </c>
     </row>
-    <row r="625" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="625" spans="1:11">
       <c r="A625" s="15">
         <v>43257</v>
       </c>
@@ -37816,7 +37828,7 @@
         <v>34.51</v>
       </c>
     </row>
-    <row r="626" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="626" spans="1:11">
       <c r="A626" s="15">
         <v>43264</v>
       </c>
@@ -37852,7 +37864,7 @@
         <v>41.63</v>
       </c>
     </row>
-    <row r="627" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="627" spans="1:11">
       <c r="A627" s="15">
         <v>43271</v>
       </c>
@@ -37888,7 +37900,7 @@
         <v>34.5</v>
       </c>
     </row>
-    <row r="628" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="628" spans="1:11">
       <c r="A628" s="15">
         <v>43278</v>
       </c>
@@ -37924,7 +37936,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="629" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="629" spans="1:11">
       <c r="A629" s="15">
         <v>43285</v>
       </c>
@@ -37960,7 +37972,7 @@
         <v>46.74</v>
       </c>
     </row>
-    <row r="630" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="630" spans="1:11">
       <c r="A630" s="15">
         <v>43292</v>
       </c>
@@ -37996,7 +38008,7 @@
         <v>38.47</v>
       </c>
     </row>
-    <row r="631" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="631" spans="1:11">
       <c r="A631" s="15">
         <v>43299</v>
       </c>
@@ -38032,7 +38044,7 @@
         <v>38.82</v>
       </c>
     </row>
-    <row r="632" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="632" spans="1:11">
       <c r="A632" s="15">
         <v>43306</v>
       </c>
@@ -38068,7 +38080,7 @@
         <v>39.159999999999997</v>
       </c>
     </row>
-    <row r="633" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="633" spans="1:11">
       <c r="A633" s="15">
         <v>43313</v>
       </c>
@@ -38104,7 +38116,7 @@
         <v>40.450000000000003</v>
       </c>
     </row>
-    <row r="634" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="634" spans="1:11">
       <c r="A634" s="15">
         <v>43320</v>
       </c>
@@ -38140,7 +38152,7 @@
         <v>32.78</v>
       </c>
     </row>
-    <row r="635" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="635" spans="1:11">
       <c r="A635" s="15">
         <v>43327</v>
       </c>
@@ -38176,7 +38188,7 @@
         <v>38.94</v>
       </c>
     </row>
-    <row r="636" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="636" spans="1:11">
       <c r="A636" s="15">
         <v>43334</v>
       </c>
@@ -38212,7 +38224,7 @@
         <v>31.73</v>
       </c>
     </row>
-    <row r="637" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="637" spans="1:11">
       <c r="A637" s="15">
         <v>43341</v>
       </c>
@@ -38248,7 +38260,7 @@
         <v>38.53</v>
       </c>
     </row>
-    <row r="638" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="638" spans="1:11">
       <c r="A638" s="15">
         <v>43348</v>
       </c>
@@ -38284,7 +38296,7 @@
         <v>43.57</v>
       </c>
     </row>
-    <row r="639" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="639" spans="1:11">
       <c r="A639" s="15">
         <v>43355</v>
       </c>
@@ -38320,7 +38332,7 @@
         <v>37.619999999999997</v>
       </c>
     </row>
-    <row r="640" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="640" spans="1:11">
       <c r="A640" s="15">
         <v>43362</v>
       </c>
@@ -38356,7 +38368,7 @@
         <v>38.020000000000003</v>
       </c>
     </row>
-    <row r="641" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="641" spans="1:11">
       <c r="A641" s="15">
         <v>43369</v>
       </c>
@@ -38392,7 +38404,7 @@
         <v>44.58</v>
       </c>
     </row>
-    <row r="642" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="642" spans="1:11">
       <c r="A642" s="15">
         <v>43376</v>
       </c>
@@ -38428,7 +38440,7 @@
         <v>43.37</v>
       </c>
     </row>
-    <row r="643" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="643" spans="1:11">
       <c r="A643" s="15">
         <v>43383</v>
       </c>
@@ -38479,7 +38491,7 @@
         <v>64.94</v>
       </c>
     </row>
-    <row r="644" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="644" spans="1:11">
       <c r="A644" s="15">
         <v>43391</v>
       </c>
@@ -38515,7 +38527,7 @@
         <v>45.19</v>
       </c>
     </row>
-    <row r="645" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="645" spans="1:11">
       <c r="A645" s="15">
         <v>43397</v>
       </c>
@@ -38551,7 +38563,7 @@
         <v>72.86</v>
       </c>
     </row>
-    <row r="646" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="646" spans="1:11">
       <c r="A646" s="15">
         <v>43404</v>
       </c>
@@ -38587,7 +38599,7 @@
         <v>38.96</v>
       </c>
     </row>
-    <row r="647" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="647" spans="1:11">
       <c r="A647" s="15">
         <v>43411</v>
       </c>
@@ -38623,7 +38635,7 @@
         <v>33.590000000000003</v>
       </c>
     </row>
-    <row r="648" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="648" spans="1:11">
       <c r="A648" s="15">
         <v>43418</v>
       </c>
@@ -38659,7 +38671,7 @@
         <v>48.37</v>
       </c>
     </row>
-    <row r="649" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="649" spans="1:11">
       <c r="A649" s="15">
         <v>43425</v>
       </c>
@@ -38695,7 +38707,7 @@
         <v>73.89</v>
       </c>
     </row>
-    <row r="650" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="650" spans="1:11">
       <c r="A650" s="15">
         <v>43432</v>
       </c>
@@ -38731,7 +38743,7 @@
         <v>39.99</v>
       </c>
     </row>
-    <row r="651" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="651" spans="1:11">
       <c r="A651" s="15">
         <v>43439</v>
       </c>
@@ -38767,7 +38779,7 @@
         <v>61.26</v>
       </c>
     </row>
-    <row r="652" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="652" spans="1:11">
       <c r="A652" s="15">
         <v>43446</v>
       </c>
@@ -38803,7 +38815,7 @@
         <v>50.14</v>
       </c>
     </row>
-    <row r="653" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="653" spans="1:11">
       <c r="A653" s="15">
         <v>43453</v>
       </c>
@@ -38839,7 +38851,7 @@
         <v>63.86</v>
       </c>
     </row>
-    <row r="654" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="654" spans="1:11">
       <c r="A654" s="15">
         <v>43460</v>
       </c>
@@ -38875,7 +38887,7 @@
         <v>50.7</v>
       </c>
     </row>
-    <row r="655" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="655" spans="1:11">
       <c r="A655" s="15">
         <v>43467</v>
       </c>
@@ -38911,7 +38923,7 @@
         <v>53.3</v>
       </c>
     </row>
-    <row r="656" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="656" spans="1:11">
       <c r="A656" s="15">
         <v>43474</v>
       </c>
@@ -38947,7 +38959,7 @@
         <v>60.63</v>
       </c>
     </row>
-    <row r="657" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="657" spans="1:11">
       <c r="A657" s="15">
         <v>43481</v>
       </c>
@@ -38983,7 +38995,7 @@
         <v>51.01</v>
       </c>
     </row>
-    <row r="658" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="658" spans="1:11">
       <c r="A658" s="15">
         <v>43488</v>
       </c>
@@ -39019,7 +39031,7 @@
         <v>45.67</v>
       </c>
     </row>
-    <row r="659" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="659" spans="1:11">
       <c r="A659" s="15">
         <v>43495</v>
       </c>
@@ -39055,7 +39067,7 @@
         <v>46.03</v>
       </c>
     </row>
-    <row r="660" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="660" spans="1:11">
       <c r="A660" s="15">
         <v>43502</v>
       </c>
@@ -39091,7 +39103,7 @@
         <v>42.17</v>
       </c>
     </row>
-    <row r="661" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="661" spans="1:11">
       <c r="A661" s="15">
         <v>43509</v>
       </c>
@@ -39127,7 +39139,7 @@
         <v>40.51</v>
       </c>
     </row>
-    <row r="662" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="662" spans="1:11">
       <c r="A662" s="15">
         <v>43516</v>
       </c>
@@ -39163,7 +39175,7 @@
         <v>46.58</v>
       </c>
     </row>
-    <row r="663" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="663" spans="1:11">
       <c r="A663" s="15">
         <v>43523</v>
       </c>
@@ -39199,7 +39211,7 @@
         <v>48.78</v>
       </c>
     </row>
-    <row r="664" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="664" spans="1:11">
       <c r="A664" s="15">
         <v>43530</v>
       </c>
@@ -39235,7 +39247,7 @@
         <v>51.87</v>
       </c>
     </row>
-    <row r="665" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="665" spans="1:11">
       <c r="A665" s="15">
         <v>43537</v>
       </c>
@@ -39271,7 +39283,7 @@
         <v>50.84</v>
       </c>
     </row>
-    <row r="666" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="666" spans="1:11">
       <c r="A666" s="15">
         <v>43544</v>
       </c>
@@ -39307,7 +39319,7 @@
         <v>57.44</v>
       </c>
     </row>
-    <row r="667" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="667" spans="1:11">
       <c r="A667" s="15">
         <v>43551</v>
       </c>
@@ -39343,7 +39355,7 @@
         <v>58.85</v>
       </c>
     </row>
-    <row r="668" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="668" spans="1:11">
       <c r="A668" s="15">
         <v>43558</v>
       </c>
@@ -39379,7 +39391,7 @@
         <v>37.44</v>
       </c>
     </row>
-    <row r="669" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="669" spans="1:11">
       <c r="A669" s="15">
         <v>43565</v>
       </c>
@@ -39415,7 +39427,7 @@
         <v>44.35</v>
       </c>
     </row>
-    <row r="670" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="670" spans="1:11">
       <c r="A670" s="15">
         <v>43572</v>
       </c>
@@ -39451,7 +39463,7 @@
         <v>29.9</v>
       </c>
     </row>
-    <row r="671" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="671" spans="1:11">
       <c r="A671" s="15">
         <v>43579</v>
       </c>
@@ -39487,7 +39499,7 @@
         <v>38.32</v>
       </c>
     </row>
-    <row r="672" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="672" spans="1:11">
       <c r="A672" s="15">
         <v>43586</v>
       </c>
@@ -39523,7 +39535,7 @@
         <v>43.11</v>
       </c>
     </row>
-    <row r="673" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="673" spans="1:11">
       <c r="A673" s="15">
         <v>43593</v>
       </c>
@@ -39559,7 +39571,7 @@
         <v>63.69</v>
       </c>
     </row>
-    <row r="674" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="674" spans="1:11">
       <c r="A674" s="15">
         <v>43600</v>
       </c>
@@ -39595,7 +39607,7 @@
         <v>54.45</v>
       </c>
     </row>
-    <row r="675" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="675" spans="1:11">
       <c r="A675" s="15">
         <v>43607</v>
       </c>
@@ -39631,7 +39643,7 @@
         <v>38.76</v>
       </c>
     </row>
-    <row r="676" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="676" spans="1:11">
       <c r="A676" s="15">
         <v>43614</v>
       </c>
@@ -39667,7 +39679,7 @@
         <v>76.66</v>
       </c>
     </row>
-    <row r="677" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="677" spans="1:11">
       <c r="A677" s="15">
         <v>43621</v>
       </c>
@@ -39703,7 +39715,7 @@
         <v>57.55</v>
       </c>
     </row>
-    <row r="678" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="678" spans="1:11">
       <c r="A678" s="15">
         <v>43628</v>
       </c>
@@ -39739,7 +39751,7 @@
         <v>36.67</v>
       </c>
     </row>
-    <row r="679" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="679" spans="1:11">
       <c r="A679" s="15">
         <v>43635</v>
       </c>
@@ -39775,7 +39787,7 @@
         <v>25.39</v>
       </c>
     </row>
-    <row r="680" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="680" spans="1:11">
       <c r="A680" s="15">
         <v>43642</v>
       </c>
@@ -39811,7 +39823,7 @@
         <v>56.56</v>
       </c>
     </row>
-    <row r="681" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="681" spans="1:11">
       <c r="A681" s="15">
         <v>43649</v>
       </c>
@@ -39847,7 +39859,7 @@
         <v>37.46</v>
       </c>
     </row>
-    <row r="682" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="682" spans="1:11">
       <c r="A682" s="15">
         <v>43656</v>
       </c>
@@ -39883,7 +39895,7 @@
         <v>35.630000000000003</v>
       </c>
     </row>
-    <row r="683" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="683" spans="1:11">
       <c r="A683" s="15">
         <v>43663</v>
       </c>
@@ -39919,7 +39931,7 @@
         <v>53.98</v>
       </c>
     </row>
-    <row r="684" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="684" spans="1:11">
       <c r="A684" s="15">
         <v>43670</v>
       </c>
@@ -39955,7 +39967,7 @@
         <v>37.93</v>
       </c>
     </row>
-    <row r="685" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="685" spans="1:11">
       <c r="A685" s="15">
         <v>43677</v>
       </c>
@@ -39991,7 +40003,7 @@
         <v>41.31</v>
       </c>
     </row>
-    <row r="686" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="686" spans="1:11">
       <c r="A686" s="15">
         <v>43684</v>
       </c>
@@ -40027,7 +40039,7 @@
         <v>61.58</v>
       </c>
     </row>
-    <row r="687" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="687" spans="1:11">
       <c r="A687" s="15">
         <v>43691</v>
       </c>
@@ -40063,7 +40075,7 @@
         <v>49.29</v>
       </c>
     </row>
-    <row r="688" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="688" spans="1:11">
       <c r="A688" s="15">
         <v>43698</v>
       </c>
@@ -40099,7 +40111,7 @@
         <v>60.34</v>
       </c>
     </row>
-    <row r="689" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="689" spans="1:11">
       <c r="A689" s="15">
         <v>43705</v>
       </c>
@@ -40135,7 +40147,7 @@
         <v>66.010000000000005</v>
       </c>
     </row>
-    <row r="690" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="690" spans="1:11">
       <c r="A690" s="15">
         <v>43712</v>
       </c>
@@ -40171,7 +40183,7 @@
         <v>53.29</v>
       </c>
     </row>
-    <row r="691" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="691" spans="1:11">
       <c r="A691" s="15">
         <v>43719</v>
       </c>
@@ -40207,7 +40219,7 @@
         <v>58.2</v>
       </c>
     </row>
-    <row r="692" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="692" spans="1:11">
       <c r="A692" s="15">
         <v>43726</v>
       </c>
@@ -40243,7 +40255,7 @@
         <v>62.04</v>
       </c>
     </row>
-    <row r="693" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="693" spans="1:11">
       <c r="A693" s="15">
         <v>43733</v>
       </c>
@@ -40279,7 +40291,7 @@
         <v>53.22</v>
       </c>
     </row>
-    <row r="694" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="694" spans="1:11">
       <c r="A694" s="15">
         <v>43740</v>
       </c>
@@ -40315,7 +40327,7 @@
         <v>78.3</v>
       </c>
     </row>
-    <row r="695" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="695" spans="1:11">
       <c r="A695" s="15">
         <v>43747</v>
       </c>
@@ -40351,7 +40363,7 @@
         <v>57.1</v>
       </c>
     </row>
-    <row r="696" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="696" spans="1:11">
       <c r="A696" s="15">
         <v>43754</v>
       </c>
@@ -40387,7 +40399,7 @@
         <v>67.400000000000006</v>
       </c>
     </row>
-    <row r="697" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="697" spans="1:11">
       <c r="A697" s="15">
         <v>43761</v>
       </c>
@@ -40423,7 +40435,7 @@
         <v>38.35</v>
       </c>
     </row>
-    <row r="698" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="698" spans="1:11">
       <c r="A698" s="15">
         <v>43768</v>
       </c>
@@ -40459,7 +40471,7 @@
         <v>39.58</v>
       </c>
     </row>
-    <row r="699" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="699" spans="1:11">
       <c r="A699" s="15">
         <v>43775</v>
       </c>
@@ -40495,7 +40507,7 @@
         <v>35.5</v>
       </c>
     </row>
-    <row r="700" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="700" spans="1:11">
       <c r="A700" s="15">
         <v>43782</v>
       </c>
@@ -40531,7 +40543,7 @@
         <v>49.68</v>
       </c>
     </row>
-    <row r="701" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="701" spans="1:11">
       <c r="A701" s="15">
         <v>43789</v>
       </c>
@@ -40567,7 +40579,7 @@
         <v>52.05</v>
       </c>
     </row>
-    <row r="702" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="702" spans="1:11">
       <c r="A702" s="15">
         <v>43796</v>
       </c>
@@ -40603,7 +40615,7 @@
         <v>41.28</v>
       </c>
     </row>
-    <row r="703" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="703" spans="1:11">
       <c r="A703" s="15">
         <v>43803</v>
       </c>
@@ -40639,7 +40651,7 @@
         <v>56.13</v>
       </c>
     </row>
-    <row r="704" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="704" spans="1:11">
       <c r="A704" s="15">
         <v>43810</v>
       </c>
@@ -40675,7 +40687,7 @@
         <v>50.69</v>
       </c>
     </row>
-    <row r="705" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="705" spans="1:11">
       <c r="A705" s="15">
         <v>43817</v>
       </c>
@@ -40711,7 +40723,7 @@
         <v>35.82</v>
       </c>
     </row>
-    <row r="706" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="706" spans="1:11">
       <c r="A706" s="15">
         <v>43824</v>
       </c>
@@ -40747,7 +40759,7 @@
         <v>29.16</v>
       </c>
     </row>
-    <row r="707" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="707" spans="1:11">
       <c r="A707" s="15">
         <v>43831</v>
       </c>
@@ -40798,7 +40810,7 @@
         <v>32.42</v>
       </c>
     </row>
-    <row r="708" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="708" spans="1:11">
       <c r="A708" s="15">
         <v>43838</v>
       </c>
@@ -40834,7 +40846,7 @@
         <v>40.659999999999997</v>
       </c>
     </row>
-    <row r="709" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="709" spans="1:11">
       <c r="A709" s="15">
         <v>43845</v>
       </c>
@@ -40870,7 +40882,7 @@
         <v>37.35</v>
       </c>
     </row>
-    <row r="710" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="710" spans="1:11">
       <c r="A710" s="15">
         <v>43852</v>
       </c>
@@ -40906,7 +40918,7 @@
         <v>21.13</v>
       </c>
     </row>
-    <row r="711" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="711" spans="1:11">
       <c r="A711" s="15">
         <v>43859</v>
       </c>
@@ -40942,7 +40954,7 @@
         <v>57.93</v>
       </c>
     </row>
-    <row r="712" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="712" spans="1:11">
       <c r="A712" s="15">
         <v>43866</v>
       </c>
@@ -40978,7 +40990,7 @@
         <v>57.84</v>
       </c>
     </row>
-    <row r="713" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="713" spans="1:11">
       <c r="A713" s="15">
         <v>43873</v>
       </c>
@@ -41014,7 +41026,7 @@
         <v>37.590000000000003</v>
       </c>
     </row>
-    <row r="714" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="714" spans="1:11">
       <c r="A714" s="15">
         <v>43880</v>
       </c>
@@ -41050,7 +41062,7 @@
         <v>35.15</v>
       </c>
     </row>
-    <row r="715" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="715" spans="1:11">
       <c r="A715" s="15">
         <v>43887</v>
       </c>
@@ -41086,7 +41098,7 @@
         <v>69.72</v>
       </c>
     </row>
-    <row r="716" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="716" spans="1:11">
       <c r="A716" s="15">
         <v>43894</v>
       </c>
@@ -41122,7 +41134,7 @@
         <v>72.709999999999994</v>
       </c>
     </row>
-    <row r="717" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="717" spans="1:11">
       <c r="A717" s="15">
         <v>43901</v>
       </c>
@@ -41158,7 +41170,7 @@
         <v>58.88</v>
       </c>
     </row>
-    <row r="718" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="718" spans="1:11">
       <c r="A718" s="15">
         <v>43908</v>
       </c>
@@ -41194,7 +41206,7 @@
         <v>42.67</v>
       </c>
     </row>
-    <row r="719" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="719" spans="1:11">
       <c r="A719" s="15">
         <v>43915</v>
       </c>
@@ -41230,7 +41242,7 @@
         <v>34.049999999999997</v>
       </c>
     </row>
-    <row r="720" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="720" spans="1:11">
       <c r="A720" s="15">
         <v>43922</v>
       </c>
@@ -41266,7 +41278,7 @@
         <v>40.64</v>
       </c>
     </row>
-    <row r="721" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="721" spans="1:11">
       <c r="A721" s="15">
         <v>43929</v>
       </c>
@@ -41302,7 +41314,7 @@
         <v>44.54</v>
       </c>
     </row>
-    <row r="722" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="722" spans="1:11">
       <c r="A722" s="15">
         <v>43936</v>
       </c>
@@ -41338,7 +41350,7 @@
         <v>56.57</v>
       </c>
     </row>
-    <row r="723" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="723" spans="1:11">
       <c r="A723" s="15">
         <v>43943</v>
       </c>
@@ -41374,7 +41386,7 @@
         <v>57.95</v>
       </c>
     </row>
-    <row r="724" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="724" spans="1:11">
       <c r="A724" s="15">
         <v>43950</v>
       </c>
@@ -41410,7 +41422,7 @@
         <v>41.89</v>
       </c>
     </row>
-    <row r="725" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="725" spans="1:11">
       <c r="A725" s="15">
         <v>43957</v>
       </c>
@@ -41446,7 +41458,7 @@
         <v>41.07</v>
       </c>
     </row>
-    <row r="726" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="726" spans="1:11">
       <c r="A726" s="15">
         <v>43964</v>
       </c>
@@ -41482,7 +41494,7 @@
         <v>49.3</v>
       </c>
     </row>
-    <row r="727" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="727" spans="1:11">
       <c r="A727" s="15">
         <v>43971</v>
       </c>
@@ -41518,7 +41530,7 @@
         <v>51.08</v>
       </c>
     </row>
-    <row r="728" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="728" spans="1:11">
       <c r="A728" s="15">
         <v>43978</v>
       </c>
@@ -41554,7 +41566,7 @@
         <v>43.17</v>
       </c>
     </row>
-    <row r="729" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="729" spans="1:11">
       <c r="A729" s="15">
         <v>43985</v>
       </c>
@@ -41590,7 +41602,7 @@
         <v>36.69</v>
       </c>
     </row>
-    <row r="730" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="730" spans="1:11">
       <c r="A730" s="15">
         <v>43992</v>
       </c>
@@ -41626,7 +41638,7 @@
         <v>54.73</v>
       </c>
     </row>
-    <row r="731" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="731" spans="1:11">
       <c r="A731" s="15">
         <v>43999</v>
       </c>
@@ -41662,7 +41674,7 @@
         <v>37.33</v>
       </c>
     </row>
-    <row r="732" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="732" spans="1:11">
       <c r="A732" s="15">
         <v>44006</v>
       </c>
@@ -41698,7 +41710,7 @@
         <v>43.91</v>
       </c>
     </row>
-    <row r="733" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="733" spans="1:11">
       <c r="A733" s="15">
         <v>44013</v>
       </c>
@@ -41734,7 +41746,7 @@
         <v>52.64</v>
       </c>
     </row>
-    <row r="734" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="734" spans="1:11">
       <c r="A734" s="15">
         <v>44020</v>
       </c>
@@ -41770,7 +41782,7 @@
         <v>50.49</v>
       </c>
     </row>
-    <row r="735" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="735" spans="1:11">
       <c r="A735" s="15">
         <v>44027</v>
       </c>
@@ -41806,7 +41818,7 @@
         <v>49.38</v>
       </c>
     </row>
-    <row r="736" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="736" spans="1:11">
       <c r="A736" s="15">
         <v>44034</v>
       </c>
@@ -41842,7 +41854,7 @@
         <v>33.909999999999997</v>
       </c>
     </row>
-    <row r="737" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="737" spans="1:11">
       <c r="A737" s="15">
         <v>44041</v>
       </c>
@@ -41878,7 +41890,7 @@
         <v>36.130000000000003</v>
       </c>
     </row>
-    <row r="738" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="738" spans="1:11">
       <c r="A738" s="15">
         <v>44048</v>
       </c>
@@ -41914,7 +41926,7 @@
         <v>49.4</v>
       </c>
     </row>
-    <row r="739" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="739" spans="1:11">
       <c r="A739" s="15">
         <v>44055</v>
       </c>
@@ -41950,7 +41962,7 @@
         <v>29.1</v>
       </c>
     </row>
-    <row r="740" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="740" spans="1:11">
       <c r="A740" s="15">
         <v>44062</v>
       </c>
@@ -41986,7 +41998,7 @@
         <v>42.31</v>
       </c>
     </row>
-    <row r="741" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="741" spans="1:11">
       <c r="A741" s="15">
         <v>44069</v>
       </c>
@@ -42022,7 +42034,7 @@
         <v>38.44</v>
       </c>
     </row>
-    <row r="742" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="742" spans="1:11">
       <c r="A742" s="15">
         <v>44076</v>
       </c>
@@ -42058,7 +42070,7 @@
         <v>35.47</v>
       </c>
     </row>
-    <row r="743" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="743" spans="1:11">
       <c r="A743" s="15">
         <v>44083</v>
       </c>
@@ -42094,7 +42106,7 @@
         <v>60.47</v>
       </c>
     </row>
-    <row r="744" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="744" spans="1:11">
       <c r="A744" s="15">
         <v>44090</v>
       </c>
@@ -42130,7 +42142,7 @@
         <v>71.73</v>
       </c>
     </row>
-    <row r="745" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="745" spans="1:11">
       <c r="A745" s="15">
         <v>44097</v>
       </c>
@@ -42166,7 +42178,7 @@
         <v>82.7</v>
       </c>
     </row>
-    <row r="746" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="746" spans="1:11">
       <c r="A746" s="15">
         <v>44104</v>
       </c>
@@ -42202,7 +42214,7 @@
         <v>62.62</v>
       </c>
     </row>
-    <row r="747" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="747" spans="1:11">
       <c r="A747" s="15">
         <v>44111</v>
       </c>
@@ -42238,7 +42250,7 @@
         <v>63.41</v>
       </c>
     </row>
-    <row r="748" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="748" spans="1:11">
       <c r="A748" s="15">
         <v>44118</v>
       </c>
@@ -42274,7 +42286,7 @@
         <v>41.56</v>
       </c>
     </row>
-    <row r="749" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="749" spans="1:11">
       <c r="A749" s="15">
         <v>44125</v>
       </c>
@@ -42310,7 +42322,7 @@
         <v>42.48</v>
       </c>
     </row>
-    <row r="750" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="750" spans="1:11">
       <c r="A750" s="15">
         <v>44132</v>
       </c>
@@ -42346,7 +42358,7 @@
         <v>49.64</v>
       </c>
     </row>
-    <row r="751" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="751" spans="1:11">
       <c r="A751" s="15">
         <v>44139</v>
       </c>
@@ -42382,7 +42394,7 @@
         <v>49.7</v>
       </c>
     </row>
-    <row r="752" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="752" spans="1:11">
       <c r="A752" s="15">
         <v>44146</v>
       </c>
@@ -42418,7 +42430,7 @@
         <v>50.26</v>
       </c>
     </row>
-    <row r="753" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="753" spans="1:11">
       <c r="A753" s="15">
         <v>44153</v>
       </c>
@@ -42454,7 +42466,7 @@
         <v>44.54</v>
       </c>
     </row>
-    <row r="754" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="754" spans="1:11">
       <c r="A754" s="15">
         <v>44160</v>
       </c>
@@ -42490,7 +42502,7 @@
         <v>44.54</v>
       </c>
     </row>
-    <row r="755" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="755" spans="1:11">
       <c r="A755" s="15">
         <v>44167</v>
       </c>
@@ -42526,7 +42538,7 @@
         <v>38.9</v>
       </c>
     </row>
-    <row r="756" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="756" spans="1:11">
       <c r="A756" s="15">
         <v>44174</v>
       </c>
@@ -42562,7 +42574,7 @@
         <v>40.98</v>
       </c>
     </row>
-    <row r="757" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="757" spans="1:11">
       <c r="A757" s="15">
         <v>44181</v>
       </c>
@@ -42598,7 +42610,7 @@
         <v>42.33</v>
       </c>
     </row>
-    <row r="758" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="758" spans="1:11">
       <c r="A758" s="15">
         <v>44188</v>
       </c>
@@ -42634,7 +42646,7 @@
         <v>44.19</v>
       </c>
     </row>
-    <row r="759" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="759" spans="1:11">
       <c r="A759" s="15">
         <v>44195</v>
       </c>
@@ -42670,7 +42682,7 @@
         <v>47.07</v>
       </c>
     </row>
-    <row r="760" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="760" spans="1:11">
       <c r="A760" s="15">
         <v>44202</v>
       </c>
@@ -42706,7 +42718,7 @@
         <v>39.11</v>
       </c>
     </row>
-    <row r="761" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="761" spans="1:11">
       <c r="A761" s="15">
         <v>44209</v>
       </c>
@@ -42742,7 +42754,7 @@
         <v>39.85</v>
       </c>
     </row>
-    <row r="762" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="762" spans="1:11">
       <c r="A762" s="15">
         <v>44216</v>
       </c>
@@ -42778,7 +42790,7 @@
         <v>36.46</v>
       </c>
     </row>
-    <row r="763" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="763" spans="1:11">
       <c r="A763" s="15">
         <v>44223</v>
       </c>
@@ -42814,7 +42826,7 @@
         <v>53.82</v>
       </c>
     </row>
-    <row r="764" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="764" spans="1:11">
       <c r="A764" s="15">
         <v>44230</v>
       </c>
@@ -42850,7 +42862,7 @@
         <v>50.88</v>
       </c>
     </row>
-    <row r="765" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="765" spans="1:11">
       <c r="A765" s="15">
         <v>44237</v>
       </c>
@@ -42886,7 +42898,7 @@
         <v>29.44</v>
       </c>
     </row>
-    <row r="766" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="766" spans="1:11">
       <c r="A766" s="15">
         <v>44244</v>
       </c>
@@ -42922,7 +42934,7 @@
         <v>44.76</v>
       </c>
     </row>
-    <row r="767" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="767" spans="1:11">
       <c r="A767" s="15">
         <v>44251</v>
       </c>
@@ -42958,7 +42970,7 @@
         <v>48.64</v>
       </c>
     </row>
-    <row r="768" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="768" spans="1:11">
       <c r="A768" s="15">
         <v>44258</v>
       </c>
@@ -42994,7 +43006,7 @@
         <v>62.65</v>
       </c>
     </row>
-    <row r="769" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="769" spans="1:11">
       <c r="A769" s="15">
         <v>44265</v>
       </c>
@@ -43030,7 +43042,7 @@
         <v>54.1</v>
       </c>
     </row>
-    <row r="770" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="770" spans="1:11">
       <c r="A770" s="15">
         <v>44272</v>
       </c>
@@ -43066,7 +43078,7 @@
         <v>33.979999999999997</v>
       </c>
     </row>
-    <row r="771" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="771" spans="1:11">
       <c r="A771" s="15">
         <v>44279</v>
       </c>
@@ -43117,7 +43129,7 @@
         <v>42.24</v>
       </c>
     </row>
-    <row r="772" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="772" spans="1:11">
       <c r="A772" s="15">
         <v>44286</v>
       </c>
@@ -43153,7 +43165,7 @@
         <v>47.49</v>
       </c>
     </row>
-    <row r="773" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="773" spans="1:11">
       <c r="A773" s="15">
         <v>44293</v>
       </c>
@@ -43189,7 +43201,7 @@
         <v>35.159999999999997</v>
       </c>
     </row>
-    <row r="774" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="774" spans="1:11">
       <c r="A774" s="15">
         <v>44300</v>
       </c>
@@ -43225,7 +43237,7 @@
         <v>39.590000000000003</v>
       </c>
     </row>
-    <row r="775" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="775" spans="1:11">
       <c r="A775" s="15">
         <v>44307</v>
       </c>
@@ -43261,7 +43273,7 @@
         <v>39.06</v>
       </c>
     </row>
-    <row r="776" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="776" spans="1:11">
       <c r="A776" s="15">
         <v>44314</v>
       </c>
@@ -43297,7 +43309,7 @@
         <v>43.65</v>
       </c>
     </row>
-    <row r="777" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="777" spans="1:11">
       <c r="A777" s="15">
         <v>44321</v>
       </c>
@@ -43333,7 +43345,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="778" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="778" spans="1:11">
       <c r="A778" s="15">
         <v>44328</v>
       </c>
@@ -43369,7 +43381,7 @@
         <v>44.2</v>
       </c>
     </row>
-    <row r="779" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="779" spans="1:11">
       <c r="A779" s="15">
         <v>44335</v>
       </c>
@@ -43405,7 +43417,7 @@
         <v>35.25</v>
       </c>
     </row>
-    <row r="780" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="780" spans="1:11">
       <c r="A780" s="15">
         <v>44342</v>
       </c>
@@ -43441,7 +43453,7 @@
         <v>35.119999999999997</v>
       </c>
     </row>
-    <row r="781" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="781" spans="1:11">
       <c r="A781" s="15">
         <v>44349</v>
       </c>
@@ -43477,7 +43489,7 @@
         <v>35.83</v>
       </c>
     </row>
-    <row r="782" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="782" spans="1:11">
       <c r="A782" s="15">
         <v>44356</v>
       </c>
@@ -43513,7 +43525,7 @@
         <v>38.92</v>
       </c>
     </row>
-    <row r="783" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="783" spans="1:11">
       <c r="A783" s="15">
         <v>44363</v>
       </c>
@@ -43549,7 +43561,7 @@
         <v>34.159999999999997</v>
       </c>
     </row>
-    <row r="784" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="784" spans="1:11">
       <c r="A784" s="15">
         <v>44370</v>
       </c>
@@ -43585,7 +43597,7 @@
         <v>42.79</v>
       </c>
     </row>
-    <row r="785" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="785" spans="1:11">
       <c r="A785" s="15">
         <v>44377</v>
       </c>
@@ -43621,7 +43633,7 @@
         <v>38.18</v>
       </c>
     </row>
-    <row r="786" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="786" spans="1:11">
       <c r="A786" s="15">
         <v>44384</v>
       </c>
@@ -43657,7 +43669,7 @@
         <v>42.66</v>
       </c>
     </row>
-    <row r="787" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="787" spans="1:11">
       <c r="A787" s="15">
         <v>44391</v>
       </c>
@@ -43693,7 +43705,7 @@
         <v>37.85</v>
       </c>
     </row>
-    <row r="788" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="788" spans="1:11">
       <c r="A788" s="15">
         <v>44398</v>
       </c>
@@ -43729,7 +43741,7 @@
         <v>48.75</v>
       </c>
     </row>
-    <row r="789" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="789" spans="1:11">
       <c r="A789" s="15">
         <v>44405</v>
       </c>
@@ -43765,7 +43777,7 @@
         <v>43.07</v>
       </c>
     </row>
-    <row r="790" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="790" spans="1:11">
       <c r="A790" s="15">
         <v>44412</v>
       </c>
@@ -43801,7 +43813,7 @@
         <v>41.16</v>
       </c>
     </row>
-    <row r="791" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="791" spans="1:11">
       <c r="A791" s="15">
         <v>44419</v>
       </c>
@@ -43837,7 +43849,7 @@
         <v>38.54</v>
       </c>
     </row>
-    <row r="792" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="792" spans="1:11">
       <c r="A792" s="15">
         <v>44426</v>
       </c>
@@ -43873,7 +43885,7 @@
         <v>58.22</v>
       </c>
     </row>
-    <row r="793" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="793" spans="1:11">
       <c r="A793" s="15">
         <v>44433</v>
       </c>
@@ -43909,7 +43921,7 @@
         <v>37.950000000000003</v>
       </c>
     </row>
-    <row r="794" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="794" spans="1:11">
       <c r="A794" s="15">
         <v>44440</v>
       </c>
@@ -43945,7 +43957,7 @@
         <v>39.24</v>
       </c>
     </row>
-    <row r="795" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="795" spans="1:11">
       <c r="A795" s="15">
         <v>44447</v>
       </c>
@@ -43981,7 +43993,7 @@
         <v>43.85</v>
       </c>
     </row>
-    <row r="796" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="796" spans="1:11">
       <c r="A796" s="15">
         <v>44454</v>
       </c>
@@ -44017,7 +44029,7 @@
         <v>47.86</v>
       </c>
     </row>
-    <row r="797" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="797" spans="1:11">
       <c r="A797" s="15">
         <v>44461</v>
       </c>
@@ -44053,7 +44065,7 @@
         <v>47.37</v>
       </c>
     </row>
-    <row r="798" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="798" spans="1:11">
       <c r="A798" s="15">
         <v>44468</v>
       </c>
@@ -44089,7 +44101,7 @@
         <v>72.13</v>
       </c>
     </row>
-    <row r="799" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="799" spans="1:11">
       <c r="A799" s="15">
         <v>44475</v>
       </c>
@@ -44125,7 +44137,7 @@
         <v>51.09</v>
       </c>
     </row>
-    <row r="800" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="800" spans="1:11">
       <c r="A800" s="15">
         <v>44482</v>
       </c>
@@ -44161,7 +44173,7 @@
         <v>52.37</v>
       </c>
     </row>
-    <row r="801" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="801" spans="1:11">
       <c r="A801" s="15">
         <v>44489</v>
       </c>
@@ -44197,7 +44209,7 @@
         <v>33.46</v>
       </c>
     </row>
-    <row r="802" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="802" spans="1:11">
       <c r="A802" s="15">
         <v>44496</v>
       </c>
@@ -44233,7 +44245,7 @@
         <v>33.03</v>
       </c>
     </row>
-    <row r="803" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="803" spans="1:11">
       <c r="A803" s="15">
         <v>44503</v>
       </c>
@@ -44269,7 +44281,7 @@
         <v>37.31</v>
       </c>
     </row>
-    <row r="804" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="804" spans="1:11">
       <c r="A804" s="15">
         <v>44510</v>
       </c>
@@ -44305,7 +44317,7 @@
         <v>43.41</v>
       </c>
     </row>
-    <row r="805" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="805" spans="1:11">
       <c r="A805" s="15">
         <v>44517</v>
       </c>
@@ -44341,7 +44353,7 @@
         <v>47.38</v>
       </c>
     </row>
-    <row r="806" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="806" spans="1:11">
       <c r="A806" s="15">
         <v>44524</v>
       </c>
@@ -44377,7 +44389,7 @@
         <v>46.63</v>
       </c>
     </row>
-    <row r="807" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="807" spans="1:11">
       <c r="A807" s="15">
         <v>44531</v>
       </c>
@@ -44413,7 +44425,7 @@
         <v>59.91</v>
       </c>
     </row>
-    <row r="808" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="808" spans="1:11">
       <c r="A808" s="15">
         <v>44538</v>
       </c>
@@ -44449,7 +44461,7 @@
         <v>78.33</v>
       </c>
     </row>
-    <row r="809" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="809" spans="1:11">
       <c r="A809" s="15">
         <v>44545</v>
       </c>
@@ -44485,7 +44497,7 @@
         <v>61.89</v>
       </c>
     </row>
-    <row r="810" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="810" spans="1:11">
       <c r="A810" s="15">
         <v>44552</v>
       </c>
@@ -44521,7 +44533,7 @@
         <v>51.45</v>
       </c>
     </row>
-    <row r="811" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="811" spans="1:11">
       <c r="A811" s="15">
         <v>44559</v>
       </c>
@@ -44557,7 +44569,7 @@
         <v>38.94</v>
       </c>
     </row>
-    <row r="812" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="812" spans="1:11">
       <c r="A812" s="15">
         <v>44566</v>
       </c>
@@ -44593,7 +44605,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="813" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="813" spans="1:11">
       <c r="A813" s="15">
         <v>44573</v>
       </c>
@@ -44629,7 +44641,7 @@
         <v>66.02</v>
       </c>
     </row>
-    <row r="814" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="814" spans="1:11">
       <c r="A814" s="15">
         <v>44580</v>
       </c>
@@ -44665,7 +44677,7 @@
         <v>76.22</v>
       </c>
     </row>
-    <row r="815" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="815" spans="1:11">
       <c r="A815" s="15">
         <v>44587</v>
       </c>
@@ -44701,7 +44713,7 @@
         <v>66.22</v>
       </c>
     </row>
-    <row r="816" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="816" spans="1:11">
       <c r="A816" s="15">
         <v>44594</v>
       </c>
@@ -44737,7 +44749,7 @@
         <v>49.17</v>
       </c>
     </row>
-    <row r="817" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="817" spans="1:11">
       <c r="A817" s="15">
         <v>44601</v>
       </c>
@@ -44773,7 +44785,7 @@
         <v>40.53</v>
       </c>
     </row>
-    <row r="818" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="818" spans="1:11">
       <c r="A818" s="15">
         <v>44608</v>
       </c>
@@ -44809,7 +44821,7 @@
         <v>72.38</v>
       </c>
     </row>
-    <row r="819" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="819" spans="1:11">
       <c r="A819" s="15">
         <v>44615</v>
       </c>
@@ -44845,7 +44857,7 @@
         <v>71.64</v>
       </c>
     </row>
-    <row r="820" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="820" spans="1:11">
       <c r="A820" s="15">
         <v>44622</v>
       </c>
@@ -44881,7 +44893,7 @@
         <v>72.260000000000005</v>
       </c>
     </row>
-    <row r="821" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="821" spans="1:11">
       <c r="A821" s="15">
         <v>44629</v>
       </c>
@@ -44917,7 +44929,7 @@
         <v>70.959999999999994</v>
       </c>
     </row>
-    <row r="822" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="822" spans="1:11">
       <c r="A822" s="15">
         <v>44636</v>
       </c>
@@ -44953,7 +44965,7 @@
         <v>60.48</v>
       </c>
     </row>
-    <row r="823" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="823" spans="1:11">
       <c r="A823" s="15">
         <v>44643</v>
       </c>
@@ -44989,7 +45001,7 @@
         <v>65.23</v>
       </c>
     </row>
-    <row r="824" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="824" spans="1:11">
       <c r="A824" s="15">
         <v>44650</v>
       </c>
@@ -45025,7 +45037,7 @@
         <v>21.67</v>
       </c>
     </row>
-    <row r="825" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="825" spans="1:11">
       <c r="A825" s="15">
         <v>44657</v>
       </c>
@@ -45061,7 +45073,7 @@
         <v>40.35</v>
       </c>
     </row>
-    <row r="826" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="826" spans="1:11">
       <c r="A826" s="15">
         <v>44664</v>
       </c>
@@ -45097,7 +45109,7 @@
         <v>31.86</v>
       </c>
     </row>
-    <row r="827" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="827" spans="1:11">
       <c r="A827" s="15">
         <v>44671</v>
       </c>
@@ -45133,7 +45145,7 @@
         <v>28.88</v>
       </c>
     </row>
-    <row r="828" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="828" spans="1:11">
       <c r="A828" s="15">
         <v>44678</v>
       </c>
@@ -45169,7 +45181,7 @@
         <v>69.22</v>
       </c>
     </row>
-    <row r="829" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="829" spans="1:11">
       <c r="A829" s="15">
         <v>44685</v>
       </c>
@@ -45205,7 +45217,7 @@
         <v>45.33</v>
       </c>
     </row>
-    <row r="830" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="830" spans="1:11">
       <c r="A830" s="15">
         <v>44692</v>
       </c>
@@ -45241,7 +45253,7 @@
         <v>58.81</v>
       </c>
     </row>
-    <row r="831" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="831" spans="1:11">
       <c r="A831" s="15">
         <v>44699</v>
       </c>
@@ -45277,7 +45289,7 @@
         <v>44.74</v>
       </c>
     </row>
-    <row r="832" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="832" spans="1:11">
       <c r="A832" s="15">
         <v>44706</v>
       </c>
@@ -45313,7 +45325,7 @@
         <v>35.08</v>
       </c>
     </row>
-    <row r="833" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="833" spans="1:11">
       <c r="A833" s="15">
         <v>44713</v>
       </c>
@@ -45349,7 +45361,7 @@
         <v>74.08</v>
       </c>
     </row>
-    <row r="834" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="834" spans="1:11">
       <c r="A834" s="15">
         <v>44720</v>
       </c>
@@ -45385,7 +45397,7 @@
         <v>43.01</v>
       </c>
     </row>
-    <row r="835" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="835" spans="1:11">
       <c r="A835" s="15">
         <v>44727</v>
       </c>
@@ -45436,7 +45448,7 @@
         <v>50.59</v>
       </c>
     </row>
-    <row r="836" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="836" spans="1:11">
       <c r="A836" s="15">
         <v>44734</v>
       </c>
@@ -45472,7 +45484,7 @@
         <v>59.84</v>
       </c>
     </row>
-    <row r="837" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="837" spans="1:11">
       <c r="A837" s="15">
         <v>44741</v>
       </c>
@@ -45508,7 +45520,7 @@
         <v>51.78</v>
       </c>
     </row>
-    <row r="838" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="838" spans="1:11">
       <c r="A838" s="15">
         <v>44748</v>
       </c>
@@ -45544,7 +45556,7 @@
         <v>62.05</v>
       </c>
     </row>
-    <row r="839" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="839" spans="1:11">
       <c r="A839" s="15">
         <v>44755</v>
       </c>
@@ -45580,7 +45592,7 @@
         <v>58.93</v>
       </c>
     </row>
-    <row r="840" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="840" spans="1:11">
       <c r="A840" s="15">
         <v>44762</v>
       </c>
@@ -45616,7 +45628,7 @@
         <v>51.59</v>
       </c>
     </row>
-    <row r="841" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="841" spans="1:11">
       <c r="A841" s="15">
         <v>44769</v>
       </c>
@@ -45652,7 +45664,7 @@
         <v>50.16</v>
       </c>
     </row>
-    <row r="842" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="842" spans="1:11">
       <c r="A842" s="15">
         <v>44776</v>
       </c>
@@ -45688,7 +45700,7 @@
         <v>53.21</v>
       </c>
     </row>
-    <row r="843" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="843" spans="1:11">
       <c r="A843" s="15">
         <v>44783</v>
       </c>
@@ -45724,7 +45736,7 @@
         <v>54.24</v>
       </c>
     </row>
-    <row r="844" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="844" spans="1:11">
       <c r="A844" s="15">
         <v>44790</v>
       </c>
@@ -45760,7 +45772,7 @@
         <v>54.27</v>
       </c>
     </row>
-    <row r="845" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="845" spans="1:11">
       <c r="A845" s="15">
         <v>44797</v>
       </c>
@@ -45796,7 +45808,7 @@
         <v>59.7</v>
       </c>
     </row>
-    <row r="846" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="846" spans="1:11">
       <c r="A846" s="15">
         <v>44804</v>
       </c>
@@ -45832,7 +45844,7 @@
         <v>60.43</v>
       </c>
     </row>
-    <row r="847" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="847" spans="1:11">
       <c r="A847" s="15">
         <v>44811</v>
       </c>
@@ -45868,7 +45880,7 @@
         <v>60.04</v>
       </c>
     </row>
-    <row r="848" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="848" spans="1:11">
       <c r="A848" s="15">
         <v>44818</v>
       </c>
@@ -45904,7 +45916,7 @@
         <v>70.459999999999994</v>
       </c>
     </row>
-    <row r="849" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="849" spans="1:11">
       <c r="A849" s="15">
         <v>44825</v>
       </c>
@@ -45940,7 +45952,7 @@
         <v>60.97</v>
       </c>
     </row>
-    <row r="850" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="850" spans="1:11">
       <c r="A850" s="15">
         <v>44832</v>
       </c>
@@ -45976,7 +45988,7 @@
         <v>66.88</v>
       </c>
     </row>
-    <row r="851" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="851" spans="1:11">
       <c r="A851" s="15">
         <v>44839</v>
       </c>
@@ -46012,7 +46024,7 @@
         <v>58.96</v>
       </c>
     </row>
-    <row r="852" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="852" spans="1:11">
       <c r="A852" s="15">
         <v>44846</v>
       </c>
@@ -46048,7 +46060,7 @@
         <v>59.65</v>
       </c>
     </row>
-    <row r="853" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="853" spans="1:11">
       <c r="A853" s="15">
         <v>44853</v>
       </c>
@@ -46084,7 +46096,7 @@
         <v>55.43</v>
       </c>
     </row>
-    <row r="854" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="854" spans="1:11">
       <c r="A854" s="15">
         <v>44860</v>
       </c>
@@ -46120,7 +46132,7 @@
         <v>54.08</v>
       </c>
     </row>
-    <row r="855" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="855" spans="1:11">
       <c r="A855" s="15">
         <v>44867</v>
       </c>
@@ -46156,7 +46168,7 @@
         <v>59.48</v>
       </c>
     </row>
-    <row r="856" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="856" spans="1:11">
       <c r="A856" s="15">
         <v>44874</v>
       </c>
@@ -46192,7 +46204,7 @@
         <v>54.63</v>
       </c>
     </row>
-    <row r="857" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="857" spans="1:11">
       <c r="A857" s="15">
         <v>44881</v>
       </c>
@@ -46228,7 +46240,7 @@
         <v>60.66</v>
       </c>
     </row>
-    <row r="858" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="858" spans="1:11">
       <c r="A858" s="15">
         <v>44888</v>
       </c>
@@ -46264,7 +46276,7 @@
         <v>56.55</v>
       </c>
     </row>
-    <row r="859" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="859" spans="1:11">
       <c r="A859" s="15">
         <v>44895</v>
       </c>
@@ -46300,7 +46312,7 @@
         <v>50.1</v>
       </c>
     </row>
-    <row r="860" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="860" spans="1:11">
       <c r="A860" s="15">
         <v>44902</v>
       </c>
@@ -46336,7 +46348,7 @@
         <v>50.27</v>
       </c>
     </row>
-    <row r="861" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="861" spans="1:11">
       <c r="A861" s="15">
         <v>44909</v>
       </c>
@@ -46372,7 +46384,7 @@
         <v>48.94</v>
       </c>
     </row>
-    <row r="862" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="862" spans="1:11">
       <c r="A862" s="15">
         <v>44916</v>
       </c>
@@ -46408,7 +46420,7 @@
         <v>53.8</v>
       </c>
     </row>
-    <row r="863" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="863" spans="1:11">
       <c r="A863" s="15">
         <v>44923</v>
       </c>
@@ -46444,7 +46456,7 @@
         <v>46.68</v>
       </c>
     </row>
-    <row r="864" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="864" spans="1:11">
       <c r="A864" s="15">
         <v>44930</v>
       </c>
@@ -46480,7 +46492,7 @@
         <v>53.9</v>
       </c>
     </row>
-    <row r="865" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="865" spans="1:11">
       <c r="A865" s="15">
         <v>44937</v>
       </c>
@@ -46516,7 +46528,7 @@
         <v>39.74</v>
       </c>
     </row>
-    <row r="866" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="866" spans="1:11">
       <c r="A866" s="15">
         <v>44944</v>
       </c>
@@ -46552,7 +46564,7 @@
         <v>58.85</v>
       </c>
     </row>
-    <row r="867" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="867" spans="1:11">
       <c r="A867" s="15">
         <v>44951</v>
       </c>
@@ -46588,7 +46600,7 @@
         <v>45.01</v>
       </c>
     </row>
-    <row r="868" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="868" spans="1:11">
       <c r="A868" s="15">
         <v>44958</v>
       </c>
@@ -46624,7 +46636,7 @@
         <v>44.29</v>
       </c>
     </row>
-    <row r="869" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="869" spans="1:11">
       <c r="A869" s="15">
         <v>44965</v>
       </c>
@@ -46660,7 +46672,7 @@
         <v>44.25</v>
       </c>
     </row>
-    <row r="870" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="870" spans="1:11">
       <c r="A870" s="15">
         <v>44972</v>
       </c>
@@ -46696,7 +46708,7 @@
         <v>47.28</v>
       </c>
     </row>
-    <row r="871" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="871" spans="1:11">
       <c r="A871" s="15">
         <v>44979</v>
       </c>
@@ -46732,7 +46744,7 @@
         <v>71.14</v>
       </c>
     </row>
-    <row r="872" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="872" spans="1:11">
       <c r="A872" s="15">
         <v>44986</v>
       </c>
@@ -46768,7 +46780,7 @@
         <v>69.319999999999993</v>
       </c>
     </row>
-    <row r="873" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="873" spans="1:11">
       <c r="A873" s="15">
         <v>44993</v>
       </c>
@@ -46804,7 +46816,7 @@
         <v>63.44</v>
       </c>
     </row>
-    <row r="874" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="874" spans="1:11">
       <c r="A874" s="15">
         <v>45000</v>
       </c>
@@ -46840,7 +46852,7 @@
         <v>66.69</v>
       </c>
     </row>
-    <row r="875" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="875" spans="1:11">
       <c r="A875" s="15">
         <v>45007</v>
       </c>
@@ -46876,7 +46888,7 @@
         <v>57.12</v>
       </c>
     </row>
-    <row r="876" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="876" spans="1:11">
       <c r="A876" s="15">
         <v>45014</v>
       </c>
@@ -46912,7 +46924,7 @@
         <v>49.69</v>
       </c>
     </row>
-    <row r="877" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="877" spans="1:11">
       <c r="A877" s="15">
         <v>45021</v>
       </c>
@@ -46948,7 +46960,7 @@
         <v>45.38</v>
       </c>
     </row>
-    <row r="878" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="878" spans="1:11">
       <c r="A878" s="15">
         <v>45028</v>
       </c>
@@ -46984,7 +46996,7 @@
         <v>64.83</v>
       </c>
     </row>
-    <row r="879" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="879" spans="1:11">
       <c r="A879" s="15">
         <v>45035</v>
       </c>
@@ -47020,7 +47032,7 @@
         <v>39.61</v>
       </c>
     </row>
-    <row r="880" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="880" spans="1:11">
       <c r="A880" s="15">
         <v>45042</v>
       </c>
@@ -47056,7 +47068,7 @@
         <v>56.93</v>
       </c>
     </row>
-    <row r="881" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="881" spans="1:11">
       <c r="A881" s="15">
         <v>45049</v>
       </c>
@@ -47092,7 +47104,7 @@
         <v>43.05</v>
       </c>
     </row>
-    <row r="882" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="882" spans="1:11">
       <c r="A882" s="15">
         <v>45056</v>
       </c>
@@ -47128,7 +47140,7 @@
         <v>50.84</v>
       </c>
     </row>
-    <row r="883" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="883" spans="1:11">
       <c r="A883" s="15">
         <v>45063</v>
       </c>
@@ -47164,7 +47176,7 @@
         <v>48.49</v>
       </c>
     </row>
-    <row r="884" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="884" spans="1:11">
       <c r="A884" s="15">
         <v>45070</v>
       </c>
@@ -47200,7 +47212,7 @@
         <v>52.21</v>
       </c>
     </row>
-    <row r="885" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="885" spans="1:11">
       <c r="A885" s="15">
         <v>45077</v>
       </c>
@@ -47236,7 +47248,7 @@
         <v>59.12</v>
       </c>
     </row>
-    <row r="886" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="886" spans="1:11">
       <c r="A886" s="15">
         <v>45084</v>
       </c>
@@ -47272,7 +47284,7 @@
         <v>40.46</v>
       </c>
     </row>
-    <row r="887" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="887" spans="1:11">
       <c r="A887" s="15">
         <v>45091</v>
       </c>
@@ -47308,7 +47320,7 @@
         <v>56.21</v>
       </c>
     </row>
-    <row r="888" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="888" spans="1:11">
       <c r="A888" s="15">
         <v>45098</v>
       </c>
@@ -47344,7 +47356,7 @@
         <v>45.51</v>
       </c>
     </row>
-    <row r="889" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="889" spans="1:11">
       <c r="A889" s="15">
         <v>45105</v>
       </c>
@@ -47380,7 +47392,7 @@
         <v>54.14</v>
       </c>
     </row>
-    <row r="890" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="890" spans="1:11">
       <c r="A890" s="15">
         <v>45112</v>
       </c>
@@ -47416,7 +47428,7 @@
         <v>50.49</v>
       </c>
     </row>
-    <row r="891" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="891" spans="1:11">
       <c r="A891" s="15">
         <v>45119</v>
       </c>
@@ -47452,7 +47464,7 @@
         <v>44.26</v>
       </c>
     </row>
-    <row r="892" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="892" spans="1:11">
       <c r="A892" s="15">
         <v>45126</v>
       </c>
@@ -47488,7 +47500,7 @@
         <v>44.69</v>
       </c>
     </row>
-    <row r="893" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="893" spans="1:11">
       <c r="A893" s="15">
         <v>45133</v>
       </c>
@@ -47524,7 +47536,7 @@
         <v>36.340000000000003</v>
       </c>
     </row>
-    <row r="894" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="894" spans="1:11">
       <c r="A894" s="15">
         <v>45140</v>
       </c>
@@ -47560,7 +47572,7 @@
         <v>72.739999999999995</v>
       </c>
     </row>
-    <row r="895" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="895" spans="1:11">
       <c r="A895" s="15">
         <v>45147</v>
       </c>
@@ -47596,7 +47608,7 @@
         <v>63.43</v>
       </c>
     </row>
-    <row r="896" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="896" spans="1:11">
       <c r="A896" s="15">
         <v>45154</v>
       </c>
@@ -47632,7 +47644,7 @@
         <v>67.22</v>
       </c>
     </row>
-    <row r="897" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="897" spans="1:11">
       <c r="A897" s="15">
         <v>45161</v>
       </c>
@@ -47668,7 +47680,7 @@
         <v>79.38</v>
       </c>
     </row>
-    <row r="898" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="898" spans="1:11">
       <c r="A898" s="15">
         <v>45168</v>
       </c>
@@ -47704,7 +47716,7 @@
         <v>63.6</v>
       </c>
     </row>
-    <row r="899" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="899" spans="1:11">
       <c r="A899" s="15">
         <v>45175</v>
       </c>
@@ -47755,7 +47767,7 @@
         <v>70.89</v>
       </c>
     </row>
-    <row r="900" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="900" spans="1:11">
       <c r="A900" s="15">
         <v>45182</v>
       </c>
@@ -47791,7 +47803,7 @@
         <v>64.010000000000005</v>
       </c>
     </row>
-    <row r="901" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="901" spans="1:11">
       <c r="A901" s="15">
         <v>45189</v>
       </c>
@@ -47827,7 +47839,7 @@
         <v>53.81</v>
       </c>
     </row>
-    <row r="902" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="902" spans="1:11">
       <c r="A902" s="15">
         <v>45196</v>
       </c>
@@ -47863,7 +47875,7 @@
         <v>60.53</v>
       </c>
     </row>
-    <row r="903" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="903" spans="1:11">
       <c r="A903" s="15">
         <v>45203</v>
       </c>
@@ -47899,7 +47911,7 @@
         <v>74.3</v>
       </c>
     </row>
-    <row r="904" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="904" spans="1:11">
       <c r="A904" s="15">
         <v>45210</v>
       </c>
@@ -47935,7 +47947,7 @@
         <v>70.16</v>
       </c>
     </row>
-    <row r="905" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="905" spans="1:11">
       <c r="A905" s="15">
         <v>45217</v>
       </c>
@@ -47971,7 +47983,7 @@
         <v>60.7</v>
       </c>
     </row>
-    <row r="906" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="906" spans="1:11">
       <c r="A906" s="15">
         <v>45224</v>
       </c>
@@ -48007,7 +48019,7 @@
         <v>73.540000000000006</v>
       </c>
     </row>
-    <row r="907" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="907" spans="1:11">
       <c r="A907" s="15">
         <v>45231</v>
       </c>
@@ -48043,7 +48055,7 @@
         <v>71.180000000000007</v>
       </c>
     </row>
-    <row r="908" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="908" spans="1:11">
       <c r="A908" s="15">
         <v>45238</v>
       </c>
@@ -48079,7 +48091,7 @@
         <v>52.63</v>
       </c>
     </row>
-    <row r="909" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="909" spans="1:11">
       <c r="A909" s="15">
         <v>45245</v>
       </c>
@@ -48115,7 +48127,7 @@
         <v>70.599999999999994</v>
       </c>
     </row>
-    <row r="910" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="910" spans="1:11">
       <c r="A910" s="15">
         <v>45252</v>
       </c>
@@ -48151,7 +48163,7 @@
         <v>68.56</v>
       </c>
     </row>
-    <row r="911" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="911" spans="1:11">
       <c r="A911" s="15">
         <v>45259</v>
       </c>
@@ -48187,7 +48199,7 @@
         <v>64.95</v>
       </c>
     </row>
-    <row r="912" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="912" spans="1:11">
       <c r="A912" s="15">
         <v>45266</v>
       </c>
@@ -48223,7 +48235,7 @@
         <v>71.14</v>
       </c>
     </row>
-    <row r="913" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="913" spans="1:11">
       <c r="A913" s="15">
         <v>45273</v>
       </c>
@@ -48259,7 +48271,7 @@
         <v>69.78</v>
       </c>
     </row>
-    <row r="914" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="914" spans="1:11">
       <c r="A914" s="15">
         <v>45280</v>
       </c>
@@ -48295,7 +48307,7 @@
         <v>49.87</v>
       </c>
     </row>
-    <row r="915" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="915" spans="1:11">
       <c r="A915" s="15">
         <v>45287</v>
       </c>
@@ -48331,7 +48343,7 @@
         <v>48.43</v>
       </c>
     </row>
-    <row r="916" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="916" spans="1:11">
       <c r="A916" s="15">
         <v>45294</v>
       </c>
@@ -48367,7 +48379,7 @@
         <v>68.19</v>
       </c>
     </row>
-    <row r="917" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="917" spans="1:11">
       <c r="A917" s="15">
         <v>45301</v>
       </c>
@@ -48403,7 +48415,7 @@
         <v>43.94</v>
       </c>
     </row>
-    <row r="918" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="918" spans="1:11">
       <c r="A918" s="15">
         <v>45308</v>
       </c>
@@ -48439,7 +48451,7 @@
         <v>71.66</v>
       </c>
     </row>
-    <row r="919" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="919" spans="1:11">
       <c r="A919" s="15">
         <v>45315</v>
       </c>
@@ -48475,7 +48487,7 @@
         <v>70.540000000000006</v>
       </c>
     </row>
-    <row r="920" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="920" spans="1:11">
       <c r="A920" s="15">
         <v>45322</v>
       </c>
@@ -48511,7 +48523,7 @@
         <v>67.72</v>
       </c>
     </row>
-    <row r="921" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="921" spans="1:11">
       <c r="A921" s="15">
         <v>45329</v>
       </c>
@@ -48547,7 +48559,7 @@
         <v>40.520000000000003</v>
       </c>
     </row>
-    <row r="922" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="922" spans="1:11">
       <c r="A922" s="15">
         <v>45336</v>
       </c>
@@ -48583,7 +48595,7 @@
         <v>42.93</v>
       </c>
     </row>
-    <row r="923" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="923" spans="1:11">
       <c r="A923" s="15">
         <v>45343</v>
       </c>
@@ -48619,7 +48631,7 @@
         <v>87.34</v>
       </c>
     </row>
-    <row r="924" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="924" spans="1:11">
       <c r="A924" s="15">
         <v>45350</v>
       </c>
@@ -48655,7 +48667,7 @@
         <v>63.8</v>
       </c>
     </row>
-    <row r="925" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="925" spans="1:11">
       <c r="A925" s="15">
         <v>45357</v>
       </c>
@@ -48691,7 +48703,7 @@
         <v>43.54</v>
       </c>
     </row>
-    <row r="926" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="926" spans="1:11">
       <c r="A926" s="15">
         <v>45364</v>
       </c>
@@ -48727,7 +48739,7 @@
         <v>45.2</v>
       </c>
     </row>
-    <row r="927" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="927" spans="1:11">
       <c r="A927" s="15">
         <v>45371</v>
       </c>
@@ -48763,7 +48775,7 @@
         <v>71.209999999999994</v>
       </c>
     </row>
-    <row r="928" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="928" spans="1:11">
       <c r="A928" s="15">
         <v>45378</v>
       </c>
@@ -48799,7 +48811,7 @@
         <v>31.21</v>
       </c>
     </row>
-    <row r="929" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="929" spans="1:11">
       <c r="A929" s="15">
         <v>45385</v>
       </c>
@@ -48835,7 +48847,7 @@
         <v>68.209999999999994</v>
       </c>
     </row>
-    <row r="930" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="930" spans="1:11">
       <c r="A930" s="15">
         <v>45392</v>
       </c>
@@ -48871,7 +48883,7 @@
         <v>65.73</v>
       </c>
     </row>
-    <row r="931" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="931" spans="1:11">
       <c r="A931" s="15">
         <v>45399</v>
       </c>
@@ -48907,7 +48919,7 @@
         <v>71.42</v>
       </c>
     </row>
-    <row r="932" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="932" spans="1:11">
       <c r="A932" s="15">
         <v>45406</v>
       </c>
@@ -48943,7 +48955,7 @@
         <v>70.790000000000006</v>
       </c>
     </row>
-    <row r="933" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="933" spans="1:11">
       <c r="A933" s="15">
         <v>45413</v>
       </c>
@@ -48979,7 +48991,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="934" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="934" spans="1:11">
       <c r="A934" s="15">
         <v>45420</v>
       </c>
@@ -49015,7 +49027,7 @@
         <v>59.39</v>
       </c>
     </row>
-    <row r="935" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="935" spans="1:11">
       <c r="A935" s="15">
         <v>45427</v>
       </c>
@@ -49051,7 +49063,7 @@
         <v>71.739999999999995</v>
       </c>
     </row>
-    <row r="936" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="936" spans="1:11">
       <c r="A936" s="15">
         <v>45434</v>
       </c>
@@ -49087,7 +49099,7 @@
         <v>72.540000000000006</v>
       </c>
     </row>
-    <row r="937" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="937" spans="1:11">
       <c r="A937" s="15">
         <v>45441</v>
       </c>
@@ -49123,7 +49135,7 @@
         <v>78.959999999999994</v>
       </c>
     </row>
-    <row r="938" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="938" spans="1:11">
       <c r="A938" s="15">
         <v>45448</v>
       </c>
@@ -49159,7 +49171,7 @@
         <v>90.94</v>
       </c>
     </row>
-    <row r="939" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="939" spans="1:11">
       <c r="A939" s="15">
         <v>45455</v>
       </c>
@@ -49195,7 +49207,7 @@
         <v>56.33</v>
       </c>
     </row>
-    <row r="940" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="940" spans="1:11">
       <c r="A940" s="15">
         <v>45462</v>
       </c>
@@ -49231,7 +49243,7 @@
         <v>74.87</v>
       </c>
     </row>
-    <row r="941" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="941" spans="1:11">
       <c r="A941" s="15">
         <v>45469</v>
       </c>
@@ -49267,7 +49279,7 @@
         <v>58.35</v>
       </c>
     </row>
-    <row r="942" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="942" spans="1:11">
       <c r="A942" s="15">
         <v>45476</v>
       </c>
@@ -49303,7 +49315,7 @@
         <v>55.2</v>
       </c>
     </row>
-    <row r="943" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="943" spans="1:11">
       <c r="A943" s="15">
         <v>45483</v>
       </c>
@@ -49339,7 +49351,7 @@
         <v>71.989999999999995</v>
       </c>
     </row>
-    <row r="944" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="944" spans="1:11">
       <c r="A944" s="15">
         <v>45490</v>
       </c>
@@ -49375,7 +49387,7 @@
         <v>71.55</v>
       </c>
     </row>
-    <row r="945" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="945" spans="1:11">
       <c r="A945" s="15">
         <v>45497</v>
       </c>
@@ -49411,7 +49423,7 @@
         <v>54.03</v>
       </c>
     </row>
-    <row r="946" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="946" spans="1:11">
       <c r="A946" s="15">
         <v>45504</v>
       </c>
@@ -49447,7 +49459,7 @@
         <v>62.38</v>
       </c>
     </row>
-    <row r="947" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="947" spans="1:11">
       <c r="A947" s="15">
         <v>45511</v>
       </c>
@@ -49483,7 +49495,7 @@
         <v>60.29</v>
       </c>
     </row>
-    <row r="948" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="948" spans="1:11">
       <c r="A948" s="15">
         <v>45518</v>
       </c>
@@ -49519,7 +49531,7 @@
         <v>89.06</v>
       </c>
     </row>
-    <row r="949" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="949" spans="1:11">
       <c r="A949" s="15">
         <v>45525</v>
       </c>
@@ -49555,7 +49567,7 @@
         <v>67.78</v>
       </c>
     </row>
-    <row r="950" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="950" spans="1:11">
       <c r="A950" s="15">
         <v>45532</v>
       </c>
@@ -49591,7 +49603,7 @@
         <v>76.260000000000005</v>
       </c>
     </row>
-    <row r="951" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="951" spans="1:11">
       <c r="A951" s="15">
         <v>45539</v>
       </c>
@@ -49627,7 +49639,7 @@
         <v>70.38</v>
       </c>
     </row>
-    <row r="952" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="952" spans="1:11">
       <c r="A952" s="15">
         <v>45546</v>
       </c>
@@ -49663,7 +49675,7 @@
         <v>70.66</v>
       </c>
     </row>
-    <row r="953" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="953" spans="1:11">
       <c r="A953" s="15">
         <v>45553</v>
       </c>
@@ -49699,7 +49711,7 @@
         <v>69.36</v>
       </c>
     </row>
-    <row r="954" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="954" spans="1:11">
       <c r="A954" s="15">
         <v>45560</v>
       </c>
@@ -49735,7 +49747,7 @@
         <v>75.61</v>
       </c>
     </row>
-    <row r="955" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="955" spans="1:11">
       <c r="A955" s="15">
         <v>45567</v>
       </c>
@@ -49771,7 +49783,7 @@
         <v>56.15</v>
       </c>
     </row>
-    <row r="956" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="956" spans="1:11">
       <c r="A956" s="15">
         <v>45574</v>
       </c>
@@ -49807,7 +49819,7 @@
         <v>54.22</v>
       </c>
     </row>
-    <row r="957" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="957" spans="1:11">
       <c r="A957" s="15">
         <v>45581</v>
       </c>
@@ -49843,7 +49855,7 @@
         <v>70.319999999999993</v>
       </c>
     </row>
-    <row r="958" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="958" spans="1:11">
       <c r="A958" s="15">
         <v>45588</v>
       </c>
@@ -49879,7 +49891,7 @@
         <v>75.64</v>
       </c>
     </row>
-    <row r="959" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="959" spans="1:11">
       <c r="A959" s="15">
         <v>45595</v>
       </c>
@@ -49915,7 +49927,7 @@
         <v>60.95</v>
       </c>
     </row>
-    <row r="960" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="960" spans="1:11">
       <c r="A960" s="15">
         <v>45602</v>
       </c>
@@ -49951,7 +49963,7 @@
         <v>56.27</v>
       </c>
     </row>
-    <row r="961" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="961" spans="1:11">
       <c r="A961" s="15">
         <v>45609</v>
       </c>
@@ -49987,7 +49999,7 @@
         <v>66.66</v>
       </c>
     </row>
-    <row r="962" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="962" spans="1:11">
       <c r="A962" s="15">
         <v>45616</v>
       </c>
@@ -50023,7 +50035,7 @@
         <v>55.21</v>
       </c>
     </row>
-    <row r="963" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="963" spans="1:11">
       <c r="A963" s="15">
         <v>45623</v>
       </c>
@@ -50074,7 +50086,7 @@
         <v>44.97</v>
       </c>
     </row>
-    <row r="964" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="964" spans="1:11">
       <c r="A964" s="15">
         <v>45630</v>
       </c>
@@ -50110,7 +50122,7 @@
         <v>65.58</v>
       </c>
     </row>
-    <row r="965" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="965" spans="1:11">
       <c r="A965" s="15">
         <v>45637</v>
       </c>
@@ -50146,7 +50158,7 @@
         <v>50.55</v>
       </c>
     </row>
-    <row r="966" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="966" spans="1:11">
       <c r="A966" s="15">
         <v>45644</v>
       </c>
@@ -50182,7 +50194,7 @@
         <v>55.02</v>
       </c>
     </row>
-    <row r="967" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="967" spans="1:11">
       <c r="A967" s="15">
         <v>45651</v>
       </c>
@@ -50218,7 +50230,7 @@
         <v>72.16</v>
       </c>
     </row>
-    <row r="968" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="968" spans="1:11">
       <c r="A968" s="15">
         <v>45658</v>
       </c>
@@ -50254,7 +50266,7 @@
         <v>90.01</v>
       </c>
     </row>
-    <row r="969" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="969" spans="1:11">
       <c r="A969" s="15">
         <v>45665</v>
       </c>
@@ -50290,7 +50302,7 @@
         <v>55.05</v>
       </c>
     </row>
-    <row r="970" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="970" spans="1:11">
       <c r="A970" s="15">
         <v>45672</v>
       </c>
@@ -50326,7 +50338,7 @@
         <v>58.09</v>
       </c>
     </row>
-    <row r="971" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="971" spans="1:11">
       <c r="A971" s="15">
         <v>45679</v>
       </c>
@@ -50362,7 +50374,7 @@
         <v>45.88</v>
       </c>
     </row>
-    <row r="972" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="972" spans="1:11">
       <c r="A972" s="15">
         <v>45686</v>
       </c>
@@ -50398,7 +50410,7 @@
         <v>65.86</v>
       </c>
     </row>
-    <row r="973" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="973" spans="1:11">
       <c r="A973" s="15">
         <v>45693</v>
       </c>
@@ -50434,7 +50446,7 @@
         <v>54.2</v>
       </c>
     </row>
-    <row r="974" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="974" spans="1:11">
       <c r="A974" s="15">
         <v>45700</v>
       </c>
@@ -50470,7 +50482,7 @@
         <v>52.44</v>
       </c>
     </row>
-    <row r="975" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="975" spans="1:11">
       <c r="A975" s="15">
         <v>45707</v>
       </c>
@@ -50506,7 +50518,7 @@
         <v>49.61</v>
       </c>
     </row>
-    <row r="976" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="976" spans="1:11">
       <c r="A976" s="15">
         <v>45714</v>
       </c>
@@ -50542,7 +50554,7 @@
         <v>51.43</v>
       </c>
     </row>
-    <row r="977" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="977" spans="1:11">
       <c r="A977" s="15">
         <v>45721</v>
       </c>
@@ -50578,7 +50590,7 @@
         <v>69.739999999999995</v>
       </c>
     </row>
-    <row r="978" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="978" spans="1:11">
       <c r="A978" s="15">
         <v>45728</v>
       </c>
@@ -50614,7 +50626,7 @@
         <v>70.47</v>
       </c>
     </row>
-    <row r="979" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="979" spans="1:11">
       <c r="A979" s="15">
         <v>45735</v>
       </c>
@@ -50650,7 +50662,7 @@
         <v>53.55</v>
       </c>
     </row>
-    <row r="980" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="980" spans="1:11">
       <c r="A980" s="15">
         <v>45742</v>
       </c>
@@ -50686,7 +50698,7 @@
         <v>54.17</v>
       </c>
     </row>
-    <row r="981" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="981" spans="1:11">
       <c r="A981" s="15">
         <v>45749</v>
       </c>
@@ -50722,7 +50734,7 @@
         <v>83.68</v>
       </c>
     </row>
-    <row r="982" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="982" spans="1:11">
       <c r="A982" s="15">
         <v>45756</v>
       </c>
@@ -50758,7 +50770,7 @@
         <v>60.04</v>
       </c>
     </row>
-    <row r="983" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="983" spans="1:11">
       <c r="A983" s="15">
         <v>45763</v>
       </c>
@@ -50794,7 +50806,7 @@
         <v>65.53</v>
       </c>
     </row>
-    <row r="984" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="984" spans="1:11">
       <c r="A984" s="15">
         <v>45770</v>
       </c>
@@ -50830,7 +50842,7 @@
         <v>50.87</v>
       </c>
     </row>
-    <row r="985" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="985" spans="1:11">
       <c r="A985" s="15">
         <v>45777</v>
       </c>
@@ -50866,7 +50878,7 @@
         <v>77.239999999999995</v>
       </c>
     </row>
-    <row r="986" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="986" spans="1:11">
       <c r="A986" s="15">
         <v>45784</v>
       </c>
@@ -50902,7 +50914,7 @@
         <v>51.46</v>
       </c>
     </row>
-    <row r="987" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="987" spans="1:11">
       <c r="A987" s="15">
         <v>45791</v>
       </c>
@@ -50938,7 +50950,7 @@
         <v>65.03</v>
       </c>
     </row>
-    <row r="988" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="988" spans="1:11">
       <c r="A988" s="15">
         <v>45798</v>
       </c>
@@ -50974,7 +50986,7 @@
         <v>60.35</v>
       </c>
     </row>
-    <row r="989" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="989" spans="1:11">
       <c r="A989" s="15">
         <v>45805</v>
       </c>
@@ -51010,7 +51022,7 @@
         <v>53.2</v>
       </c>
     </row>
-    <row r="990" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="990" spans="1:11">
       <c r="A990" s="15">
         <v>45812</v>
       </c>
@@ -51046,7 +51058,7 @@
         <v>67.680000000000007</v>
       </c>
     </row>
-    <row r="991" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="991" spans="1:11">
       <c r="A991" s="15">
         <v>45819</v>
       </c>
@@ -51082,7 +51094,7 @@
         <v>73.680000000000007</v>
       </c>
     </row>
-    <row r="992" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="992" spans="1:11">
       <c r="A992" s="15">
         <v>45826</v>
       </c>
@@ -51118,7 +51130,7 @@
         <v>52.15</v>
       </c>
     </row>
-    <row r="993" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="993" spans="1:11">
       <c r="A993" s="15">
         <v>45833</v>
       </c>
@@ -51154,7 +51166,7 @@
         <v>72.73</v>
       </c>
     </row>
-    <row r="994" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="994" spans="1:11">
       <c r="A994" s="15">
         <v>45840</v>
       </c>
@@ -51190,7 +51202,7 @@
         <v>54.77</v>
       </c>
     </row>
-    <row r="995" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="995" spans="1:11">
       <c r="A995" s="15">
         <v>45847</v>
       </c>
@@ -51226,7 +51238,7 @@
         <v>69.709999999999994</v>
       </c>
     </row>
-    <row r="996" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="996" spans="1:11">
       <c r="A996" s="15">
         <v>45854</v>
       </c>
@@ -51262,7 +51274,7 @@
         <v>57.22</v>
       </c>
     </row>
-    <row r="997" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="997" spans="1:11">
       <c r="A997" s="15">
         <v>45861</v>
       </c>
@@ -51298,7 +51310,7 @@
         <v>64.98</v>
       </c>
     </row>
-    <row r="998" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="998" spans="1:11">
       <c r="A998" s="15">
         <v>45868</v>
       </c>
@@ -51334,7 +51346,7 @@
         <v>64.89</v>
       </c>
     </row>
-    <row r="999" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="999" spans="1:11">
       <c r="A999" s="15">
         <v>45875</v>
       </c>
@@ -51370,7 +51382,7 @@
         <v>35.96</v>
       </c>
     </row>
-    <row r="1000" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1000" spans="1:11">
       <c r="A1000" s="15">
         <v>45882</v>
       </c>
@@ -51406,7 +51418,7 @@
         <v>69.55</v>
       </c>
     </row>
-    <row r="1001" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1001" spans="1:11">
       <c r="A1001" s="15">
         <v>45889</v>
       </c>
@@ -51442,7 +51454,7 @@
         <v>44.79</v>
       </c>
     </row>
-    <row r="1002" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1002" spans="1:11">
       <c r="A1002" s="15">
         <v>45896</v>
       </c>
@@ -51478,7 +51490,7 @@
         <v>44.7</v>
       </c>
     </row>
-    <row r="1003" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1003" spans="1:11">
       <c r="A1003" s="15">
         <v>45903</v>
       </c>
@@ -51514,7 +51526,7 @@
         <v>63.56</v>
       </c>
     </row>
-    <row r="1004" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1004" spans="1:11">
       <c r="A1004" s="15">
         <v>45910</v>
       </c>
@@ -51550,7 +51562,7 @@
         <v>71.06</v>
       </c>
     </row>
-    <row r="1005" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1005" spans="1:11">
       <c r="A1005" s="15">
         <v>45917</v>
       </c>
@@ -51586,7 +51598,7 @@
         <v>71.959999999999994</v>
       </c>
     </row>
-    <row r="1006" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1006" spans="1:11">
       <c r="A1006" s="15">
         <v>45924</v>
       </c>
@@ -51622,7 +51634,7 @@
         <v>66.77</v>
       </c>
     </row>
-    <row r="1007" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1007" spans="1:11">
       <c r="A1007" s="15">
         <v>45931</v>
       </c>
@@ -51658,7 +51670,7 @@
         <v>71.13</v>
       </c>
     </row>
-    <row r="1008" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1008" spans="1:11">
       <c r="A1008" s="15">
         <v>45938</v>
       </c>
@@ -51694,7 +51706,7 @@
         <v>69.27</v>
       </c>
     </row>
-    <row r="1009" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1009" spans="1:11">
       <c r="A1009" s="15">
         <v>45945</v>
       </c>
@@ -51730,7 +51742,7 @@
         <v>50.98</v>
       </c>
     </row>
-    <row r="1010" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1010" spans="1:11">
       <c r="A1010" s="15">
         <v>45952</v>
       </c>
@@ -51766,7 +51778,7 @@
         <v>52.1</v>
       </c>
     </row>
-    <row r="1011" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1011" spans="1:11">
       <c r="A1011" s="15">
         <v>45959</v>
       </c>
@@ -51802,7 +51814,7 @@
         <v>55.36</v>
       </c>
     </row>
-    <row r="1012" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1012" spans="1:11">
       <c r="A1012" s="15">
         <v>45966</v>
       </c>
@@ -51838,7 +51850,7 @@
         <v>40.86</v>
       </c>
     </row>
-    <row r="1013" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1013" spans="1:11">
       <c r="A1013" s="15">
         <v>45973</v>
       </c>
@@ -51874,7 +51886,7 @@
         <v>39.42</v>
       </c>
     </row>
-    <row r="1014" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1014" spans="1:11">
       <c r="A1014" s="15">
         <v>45980</v>
       </c>
@@ -51910,7 +51922,7 @@
         <v>51.59</v>
       </c>
     </row>
-    <row r="1015" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1015" spans="1:11">
       <c r="A1015" s="15">
         <v>45987</v>
       </c>
@@ -51946,7 +51958,7 @@
         <v>50.29</v>
       </c>
     </row>
-    <row r="1016" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1016" spans="1:11">
       <c r="A1016" s="15">
         <v>45994</v>
       </c>
@@ -51982,7 +51994,7 @@
         <v>47.59</v>
       </c>
     </row>
-    <row r="1017" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1017" spans="1:11">
       <c r="A1017" s="15">
         <v>46001</v>
       </c>
@@ -52018,7 +52030,7 @@
         <v>45.89</v>
       </c>
     </row>
-    <row r="1018" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1018" spans="1:11">
       <c r="A1018" s="15">
         <v>46008</v>
       </c>
@@ -52054,7 +52066,7 @@
         <v>46.38</v>
       </c>
     </row>
-    <row r="1019" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1019" spans="1:11">
       <c r="A1019" s="15">
         <v>46015</v>
       </c>
@@ -52090,7 +52102,7 @@
         <v>49.27</v>
       </c>
     </row>
-    <row r="1020" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1020" spans="1:11">
       <c r="A1020" s="15">
         <v>46022</v>
       </c>
@@ -52126,7 +52138,7 @@
         <v>48.97</v>
       </c>
     </row>
-    <row r="1021" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1021" spans="1:11">
       <c r="A1021" s="15">
         <v>46029</v>
       </c>
@@ -52162,7 +52174,7 @@
         <v>50.86</v>
       </c>
     </row>
-    <row r="1022" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1022" spans="1:11">
       <c r="A1022" s="15">
         <v>46036</v>
       </c>
@@ -52198,7 +52210,7 @@
         <v>50.37</v>
       </c>
     </row>
-    <row r="1023" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1023" spans="1:11">
       <c r="A1023" s="15">
         <v>46043</v>
       </c>
@@ -52234,7 +52246,7 @@
         <v>60.31</v>
       </c>
     </row>
-    <row r="1024" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1024" spans="1:11">
       <c r="A1024" s="15">
         <v>46050</v>
       </c>
@@ -52270,7 +52282,7 @@
         <v>46.41</v>
       </c>
     </row>
-    <row r="1025" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1025" spans="1:11">
       <c r="A1025" s="15">
         <v>46057</v>
       </c>
@@ -52306,7 +52318,7 @@
         <v>64.569999999999993</v>
       </c>
     </row>
-    <row r="1026" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1026" spans="1:11">
       <c r="A1026" s="15">
         <v>46064</v>
       </c>
@@ -52342,7 +52354,7 @@
         <v>63.52</v>
       </c>
     </row>
-    <row r="1027" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1027" spans="1:11">
       <c r="A1027" s="15">
         <v>46071</v>
       </c>
@@ -52393,7 +52405,7 @@
         <v>47.62</v>
       </c>
     </row>
-    <row r="1028" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1028" spans="1:11">
       <c r="A1028" s="15">
         <v>46078</v>
       </c>
@@ -52429,7 +52441,7 @@
         <v>64.84</v>
       </c>
     </row>
-    <row r="1029" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1029" spans="1:11">
       <c r="A1029" s="15">
         <v>46085</v>
       </c>
@@ -52465,7 +52477,7 @@
         <v>49.98</v>
       </c>
     </row>
-    <row r="1030" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1030" spans="1:11">
       <c r="A1030" s="15">
         <v>46092</v>
       </c>
@@ -52501,7 +52513,7 @@
         <v>62.78</v>
       </c>
     </row>
-    <row r="1031" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1031" spans="1:11">
       <c r="A1031" s="15">
         <v>46099</v>
       </c>
@@ -52537,7 +52549,7 @@
         <v>68.13</v>
       </c>
     </row>
-    <row r="1032" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1032" spans="1:11">
       <c r="A1032" s="15">
         <v>46106</v>
       </c>
@@ -52588,7 +52600,7 @@
         <v>47.03</v>
       </c>
     </row>
-    <row r="1033" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1033" spans="1:11">
       <c r="A1033" s="15">
         <v>46113</v>
       </c>
@@ -52624,7 +52636,7 @@
         <v>55.64</v>
       </c>
     </row>
-    <row r="1034" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1034" spans="1:11">
       <c r="A1034" s="15">
         <v>46120</v>
       </c>
@@ -52635,7 +52647,7 @@
         <v>0.41666666666668001</v>
       </c>
       <c r="D1034" s="15" t="str">
-        <f t="shared" ref="D1034" si="18">IF(
+        <f t="shared" ref="D1034:D1035" si="18">IF(
  AND(
   B1034 &gt;= IF(
          YEAR(B1034)&gt;=2007,
@@ -52675,6 +52687,42 @@
         <v>51.31</v>
       </c>
     </row>
+    <row r="1035" spans="1:11">
+      <c r="A1035" s="15">
+        <v>46127</v>
+      </c>
+      <c r="B1035" s="15">
+        <v>46128</v>
+      </c>
+      <c r="C1035" s="17">
+        <v>0.416666666666686</v>
+      </c>
+      <c r="D1035" s="15" t="str">
+        <f t="shared" si="18"/>
+        <v>UTC-4</v>
+      </c>
+      <c r="E1035" s="7">
+        <v>79.489999999999995</v>
+      </c>
+      <c r="F1035" s="8">
+        <v>-200</v>
+      </c>
+      <c r="G1035" s="7">
+        <v>50</v>
+      </c>
+      <c r="H1035" s="9">
+        <v>90</v>
+      </c>
+      <c r="I1035" s="9">
+        <v>100</v>
+      </c>
+      <c r="J1035" s="9">
+        <v>200</v>
+      </c>
+      <c r="K1035" s="7">
+        <v>68.87</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -52685,7 +52733,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{115169E1-C49D-409D-8D5D-92B2FD26EE0D}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData/>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -52696,9 +52744,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44703C2A-D4C6-BD4F-B5E9-874C8C9CFE9E}">
   <dimension ref="B2:C3"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.5"/>
   <sheetData>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:3">
       <c r="B2" t="s">
         <v>7</v>
       </c>
@@ -52706,7 +52754,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:3">
       <c r="B3" t="s">
         <v>8</v>
       </c>

--- a/data/sentiment/NAAIM Exposure Index.xlsx
+++ b/data/sentiment/NAAIM Exposure Index.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\sentiment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8EA0616-2DC9-44BB-8339-51A76115A03A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC4C067B-3E3C-4719-9AB4-09C37BF1CA72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -90,31 +90,31 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="178" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="179" formatCode="0.00_ "/>
-    <numFmt numFmtId="180" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="0.00_ "/>
+    <numFmt numFmtId="167" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="18"/>
       <color theme="3"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri Light"/>
       <family val="2"/>
       <scheme val="major"/>
     </font>
@@ -122,7 +122,7 @@
       <b/>
       <sz val="15"/>
       <color theme="3"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -130,7 +130,7 @@
       <b/>
       <sz val="13"/>
       <color theme="3"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -138,35 +138,35 @@
       <b/>
       <sz val="11"/>
       <color theme="3"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C5700"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -174,7 +174,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -182,14 +182,14 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -197,14 +197,14 @@
       <b/>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -212,7 +212,7 @@
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -220,20 +220,20 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -242,7 +242,7 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -600,7 +600,7 @@
     <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -608,44 +608,44 @@
   <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="43"/>
-    <xf numFmtId="177" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="20" fillId="0" borderId="0" xfId="42" applyFont="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" xfId="42" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="179" fontId="20" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="20" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="178" fontId="20" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="20" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="176" fontId="21" fillId="0" borderId="0" xfId="42" applyFont="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="21" fillId="0" borderId="0" xfId="42" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="179" fontId="21" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="21" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="178" fontId="21" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="21" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="176" fontId="21" fillId="0" borderId="0" xfId="42" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="21" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="21" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="21" fillId="0" borderId="0" xfId="42" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="21" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="21" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="180" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="180" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -3863,6 +3863,9 @@
                 <c:pt idx="1036">
                   <c:v>46149</c:v>
                 </c:pt>
+                <c:pt idx="1037">
+                  <c:v>46156</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -6982,6 +6985,9 @@
                 </c:pt>
                 <c:pt idx="1036">
                   <c:v>96.67</c:v>
+                </c:pt>
+                <c:pt idx="1037">
+                  <c:v>77.34</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10358,6 +10364,9 @@
                 <c:pt idx="1036">
                   <c:v>46149</c:v>
                 </c:pt>
+                <c:pt idx="1037">
+                  <c:v>46156</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -13477,6 +13486,9 @@
                 </c:pt>
                 <c:pt idx="1036">
                   <c:v>43.28</c:v>
+                </c:pt>
+                <c:pt idx="1037">
+                  <c:v>68.17</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15183,24 +15195,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K1038"/>
-  <sheetFormatPr defaultColWidth="8.8984375" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:K1039"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.69921875" style="15" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.3984375" style="15" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.296875" style="17" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.5" style="15" customWidth="1"/>
-    <col min="5" max="5" width="11.09765625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" style="15" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.44140625" style="15" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.33203125" style="17" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.44140625" style="15" customWidth="1"/>
+    <col min="5" max="5" width="11.109375" style="7" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14" style="8" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.3984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.19921875" style="9" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.3984375" style="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.44140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.21875" style="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.44140625" style="9" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="15" style="9" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="21.69921875" style="7" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="8.8984375" style="10"/>
+    <col min="11" max="11" width="21.6640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.88671875" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" s="6" customFormat="1">
       <c r="A1" s="2" t="s">
         <v>10</v>
       </c>
@@ -15235,7 +15247,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11">
       <c r="A2" s="15">
         <v>38903</v>
       </c>
@@ -15286,7 +15298,7 @@
         <v>55.55</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11">
       <c r="A3" s="15">
         <v>38910</v>
       </c>
@@ -15337,7 +15349,7 @@
         <v>47.84</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11">
       <c r="A4" s="15">
         <v>38903</v>
       </c>
@@ -15373,7 +15385,7 @@
         <v>55.549999722194443</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11">
       <c r="A5" s="15">
         <v>38910</v>
       </c>
@@ -15409,7 +15421,7 @@
         <v>47.838896308338889</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11">
       <c r="A6" s="15">
         <v>38917</v>
       </c>
@@ -15445,7 +15457,7 @@
         <v>38.170438823780898</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11">
       <c r="A7" s="15">
         <v>38924</v>
       </c>
@@ -15481,7 +15493,7 @@
         <v>33.778460222455372</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11">
       <c r="A8" s="15">
         <v>38931</v>
       </c>
@@ -15517,7 +15529,7 @@
         <v>43.692625871599382</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11">
       <c r="A9" s="15">
         <v>38938</v>
       </c>
@@ -15553,7 +15565,7 @@
         <v>47.483927790753583</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11">
       <c r="A10" s="15">
         <v>38945</v>
       </c>
@@ -15589,7 +15601,7 @@
         <v>56.524684873071166</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11">
       <c r="A11" s="15">
         <v>38952</v>
       </c>
@@ -15625,7 +15637,7 @@
         <v>45.170475778833321</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11">
       <c r="A12" s="15">
         <v>38959</v>
       </c>
@@ -15661,7 +15673,7 @@
         <v>45.170475778833321</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11">
       <c r="A13" s="15">
         <v>38966</v>
       </c>
@@ -15697,7 +15709,7 @@
         <v>50.374290674884271</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11">
       <c r="A14" s="15">
         <v>38973</v>
       </c>
@@ -15733,7 +15745,7 @@
         <v>56.228640389040173</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11">
       <c r="A15" s="15">
         <v>38980</v>
       </c>
@@ -15769,7 +15781,7 @@
         <v>31.264996401726965</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11">
       <c r="A16" s="15">
         <v>38987</v>
       </c>
@@ -15805,7 +15817,7 @@
         <v>55.807410979021469</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:11">
       <c r="A17" s="15">
         <v>38994</v>
       </c>
@@ -15841,7 +15853,7 @@
         <v>59.404629449227272</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:11">
       <c r="A18" s="15">
         <v>39001</v>
       </c>
@@ -15877,7 +15889,7 @@
         <v>59.825434763385545</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:11">
       <c r="A19" s="15">
         <v>39008</v>
       </c>
@@ -15913,7 +15925,7 @@
         <v>33.215082952435786</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:11">
       <c r="A20" s="15">
         <v>39015</v>
       </c>
@@ -15949,7 +15961,7 @@
         <v>53.121506002748077</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:11">
       <c r="A21" s="15">
         <v>39022</v>
       </c>
@@ -15985,7 +15997,7 @@
         <v>53.864396997357062</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:11">
       <c r="A22" s="15">
         <v>39029</v>
       </c>
@@ -16021,7 +16033,7 @@
         <v>46.653652879834993</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:11">
       <c r="A23" s="15">
         <v>39036</v>
       </c>
@@ -16057,7 +16069,7 @@
         <v>61.297793607386772</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:11">
       <c r="A24" s="15">
         <v>39043</v>
       </c>
@@ -16093,7 +16105,7 @@
         <v>20.824828195876073</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:11">
       <c r="A25" s="15">
         <v>39050</v>
       </c>
@@ -16129,7 +16141,7 @@
         <v>38.414042173363363</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:11">
       <c r="A26" s="15">
         <v>39057</v>
       </c>
@@ -16165,7 +16177,7 @@
         <v>58.029540018794734</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:11">
       <c r="A27" s="15">
         <v>39064</v>
       </c>
@@ -16201,7 +16213,7 @@
         <v>19.415261547359616</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:11">
       <c r="A28" s="15">
         <v>39071</v>
       </c>
@@ -16237,7 +16249,7 @@
         <v>22.354395725773102</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:11">
       <c r="A29" s="15">
         <v>39078</v>
       </c>
@@ -16273,7 +16285,7 @@
         <v>35.213204259954928</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:11">
       <c r="A30" s="15">
         <v>39085</v>
       </c>
@@ -16309,7 +16321,7 @@
         <v>32.236442245024186</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:11">
       <c r="A31" s="15">
         <v>39092</v>
       </c>
@@ -16345,7 +16357,7 @@
         <v>65.212862654704111</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:11">
       <c r="A32" s="15">
         <v>39099</v>
       </c>
@@ -16381,7 +16393,7 @@
         <v>27.899999503569333</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:11">
       <c r="A33" s="15">
         <v>39106</v>
       </c>
@@ -16417,7 +16429,7 @@
         <v>42.723911860082509</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:11">
       <c r="A34" s="15">
         <v>39113</v>
       </c>
@@ -16453,7 +16465,7 @@
         <v>49.378006237595294</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:11">
       <c r="A35" s="15">
         <v>39120</v>
       </c>
@@ -16489,7 +16501,7 @@
         <v>45.927163507298019</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:11">
       <c r="A36" s="15">
         <v>39127</v>
       </c>
@@ -16525,7 +16537,7 @@
         <v>55.649805268718424</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:11">
       <c r="A37" s="15">
         <v>39134</v>
       </c>
@@ -16561,7 +16573,7 @@
         <v>52.764818137257436</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:11">
       <c r="A38" s="15">
         <v>39141</v>
       </c>
@@ -16597,7 +16609,7 @@
         <v>53.726231363347424</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:11">
       <c r="A39" s="15">
         <v>39148</v>
       </c>
@@ -16633,7 +16645,7 @@
         <v>48.602880573068916</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:11">
       <c r="A40" s="15">
         <v>39155</v>
       </c>
@@ -16669,7 +16681,7 @@
         <v>68.635171039352031</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:11">
       <c r="A41" s="15">
         <v>39162</v>
       </c>
@@ -16705,7 +16717,7 @@
         <v>54.906588487696794</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:11">
       <c r="A42" s="15">
         <v>39169</v>
       </c>
@@ -16741,7 +16753,7 @@
         <v>61.630606010506028</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:11">
       <c r="A43" s="15">
         <v>39176</v>
       </c>
@@ -16777,7 +16789,7 @@
         <v>64.537968733792852</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:11">
       <c r="A44" s="15">
         <v>39183</v>
       </c>
@@ -16813,7 +16825,7 @@
         <v>57.825060311252592</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:11">
       <c r="A45" s="15">
         <v>39190</v>
       </c>
@@ -16849,7 +16861,7 @@
         <v>69.279479346364909</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:11">
       <c r="A46" s="15">
         <v>39197</v>
       </c>
@@ -16885,7 +16897,7 @@
         <v>59.001416591157486</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:11">
       <c r="A47" s="15">
         <v>39204</v>
       </c>
@@ -16921,7 +16933,7 @@
         <v>59.063995424924954</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:11">
       <c r="A48" s="15">
         <v>39211</v>
       </c>
@@ -16957,7 +16969,7 @@
         <v>55.064860745205635</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:11">
       <c r="A49" s="15">
         <v>39218</v>
       </c>
@@ -16993,7 +17005,7 @@
         <v>51.819247148139851</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:11">
       <c r="A50" s="15">
         <v>39225</v>
       </c>
@@ -17029,7 +17041,7 @@
         <v>53.983793864455286</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:11">
       <c r="A51" s="15">
         <v>39232</v>
       </c>
@@ -17065,7 +17077,7 @@
         <v>48.786852991286374</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:11">
       <c r="A52" s="15">
         <v>39239</v>
       </c>
@@ -17101,7 +17113,7 @@
         <v>62.811083593759328</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:11">
       <c r="A53" s="15">
         <v>39246</v>
       </c>
@@ -17137,7 +17149,7 @@
         <v>65.542340513594723</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:11">
       <c r="A54" s="15">
         <v>39253</v>
       </c>
@@ -17173,7 +17185,7 @@
         <v>67.954431672633518</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:11">
       <c r="A55" s="15">
         <v>39260</v>
       </c>
@@ -17209,7 +17221,7 @@
         <v>55.826175891531534</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:11">
       <c r="A56" s="15">
         <v>39268</v>
       </c>
@@ -17245,7 +17257,7 @@
         <v>60.176790324426577</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:11">
       <c r="A57" s="15">
         <v>39274</v>
       </c>
@@ -17281,7 +17293,7 @@
         <v>51.354938031690303</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:11">
       <c r="A58" s="15">
         <v>39281</v>
       </c>
@@ -17317,7 +17329,7 @@
         <v>45.888802797874582</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:11">
       <c r="A59" s="15">
         <v>39288</v>
       </c>
@@ -17353,7 +17365,7 @@
         <v>63.76609180512709</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:11">
       <c r="A60" s="15">
         <v>39295</v>
       </c>
@@ -17389,7 +17401,7 @@
         <v>59.657354953098618</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:11">
       <c r="A61" s="15">
         <v>39302</v>
       </c>
@@ -17425,7 +17437,7 @@
         <v>65.099669293697346</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:11">
       <c r="A62" s="15">
         <v>39309</v>
       </c>
@@ -17461,7 +17473,7 @@
         <v>57.034529015325447</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:11">
       <c r="A63" s="15">
         <v>39316</v>
       </c>
@@ -17497,7 +17509,7 @@
         <v>52.701658833000693</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:11">
       <c r="A64" s="15">
         <v>39323</v>
       </c>
@@ -17533,7 +17545,7 @@
         <v>72.566359583555496</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:11">
       <c r="A65" s="15">
         <v>39330</v>
       </c>
@@ -17569,7 +17581,7 @@
         <v>45.022968675258781</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:11">
       <c r="A66" s="15">
         <v>39337</v>
       </c>
@@ -17605,7 +17617,7 @@
         <v>69.603104472428257</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:11">
       <c r="A67" s="15">
         <v>39344</v>
       </c>
@@ -17656,7 +17668,7 @@
         <v>42.408304442812678</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:11">
       <c r="A68" s="15">
         <v>39351</v>
       </c>
@@ -17692,7 +17704,7 @@
         <v>38.186796212286225</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:11">
       <c r="A69" s="15">
         <v>39358</v>
       </c>
@@ -17728,7 +17740,7 @@
         <v>61.369548273391054</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:11">
       <c r="A70" s="15">
         <v>39365</v>
       </c>
@@ -17764,7 +17776,7 @@
         <v>56.227919122877815</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:11">
       <c r="A71" s="15">
         <v>39372</v>
       </c>
@@ -17800,7 +17812,7 @@
         <v>49.208363214031834</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:11">
       <c r="A72" s="15">
         <v>39379</v>
       </c>
@@ -17836,7 +17848,7 @@
         <v>65.850867379966061</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:11">
       <c r="A73" s="15">
         <v>39386</v>
       </c>
@@ -17872,7 +17884,7 @@
         <v>75.074716234904798</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:11">
       <c r="A74" s="15">
         <v>39393</v>
       </c>
@@ -17908,7 +17920,7 @@
         <v>52.534527153195896</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:11">
       <c r="A75" s="15">
         <v>39400</v>
       </c>
@@ -17944,7 +17956,7 @@
         <v>40.679745770792763</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:11">
       <c r="A76" s="15">
         <v>39407</v>
       </c>
@@ -17980,7 +17992,7 @@
         <v>60.493442596881707</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:11">
       <c r="A77" s="15">
         <v>39414</v>
       </c>
@@ -18016,7 +18028,7 @@
         <v>68.934714752142</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:11">
       <c r="A78" s="15">
         <v>39421</v>
       </c>
@@ -18052,7 +18064,7 @@
         <v>60.536316005812211</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:11">
       <c r="A79" s="15">
         <v>39428</v>
       </c>
@@ -18088,7 +18100,7 @@
         <v>69.021440028975547</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:11">
       <c r="A80" s="15">
         <v>39435</v>
       </c>
@@ -18124,7 +18136,7 @@
         <v>71.467344717337483</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:11">
       <c r="A81" s="15">
         <v>39442</v>
       </c>
@@ -18160,7 +18172,7 @@
         <v>50.496362770611753</v>
       </c>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:11">
       <c r="A82" s="15">
         <v>39449</v>
       </c>
@@ -18196,7 +18208,7 @@
         <v>55.229668567997003</v>
       </c>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:11">
       <c r="A83" s="15">
         <v>39456</v>
       </c>
@@ -18232,7 +18244,7 @@
         <v>75.139220764041383</v>
       </c>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:11">
       <c r="A84" s="15">
         <v>39463</v>
       </c>
@@ -18268,7 +18280,7 @@
         <v>58.387484404345059</v>
       </c>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:11">
       <c r="A85" s="15">
         <v>39470</v>
       </c>
@@ -18304,7 +18316,7 @@
         <v>74.040278246155765</v>
       </c>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:11">
       <c r="A86" s="15">
         <v>39477</v>
       </c>
@@ -18340,7 +18352,7 @@
         <v>62.164148383994373</v>
       </c>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:11">
       <c r="A87" s="15">
         <v>39484</v>
       </c>
@@ -18376,7 +18388,7 @@
         <v>70.447213919214661</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:11">
       <c r="A88" s="15">
         <v>39491</v>
       </c>
@@ -18412,7 +18424,7 @@
         <v>74.676338659280532</v>
       </c>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:11">
       <c r="A89" s="15">
         <v>39498</v>
       </c>
@@ -18448,7 +18460,7 @@
         <v>57.328488167363666</v>
       </c>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:11">
       <c r="A90" s="15">
         <v>39505</v>
       </c>
@@ -18484,7 +18496,7 @@
         <v>82.926777823027351</v>
       </c>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:11">
       <c r="A91" s="15">
         <v>39512</v>
       </c>
@@ -18520,7 +18532,7 @@
         <v>56.330836013124284</v>
       </c>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:11">
       <c r="A92" s="15">
         <v>39519</v>
       </c>
@@ -18556,7 +18568,7 @@
         <v>63.152843166400672</v>
       </c>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:11">
       <c r="A93" s="15">
         <v>39526</v>
       </c>
@@ -18592,7 +18604,7 @@
         <v>44.173359780366653</v>
       </c>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:11">
       <c r="A94" s="15">
         <v>39533</v>
       </c>
@@ -18628,7 +18640,7 @@
         <v>69.09468937538611</v>
       </c>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:11">
       <c r="A95" s="15">
         <v>39540</v>
       </c>
@@ -18664,7 +18676,7 @@
         <v>72.946618726802328</v>
       </c>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:11">
       <c r="A96" s="15">
         <v>39547</v>
       </c>
@@ -18700,7 +18712,7 @@
         <v>69.469947459315094</v>
       </c>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:11">
       <c r="A97" s="15">
         <v>39554</v>
       </c>
@@ -18736,7 +18748,7 @@
         <v>56.323052699867915</v>
       </c>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:11">
       <c r="A98" s="15">
         <v>39561</v>
       </c>
@@ -18772,7 +18784,7 @@
         <v>41.974862158849767</v>
       </c>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:11">
       <c r="A99" s="15">
         <v>39569</v>
       </c>
@@ -18808,7 +18820,7 @@
         <v>44.962229438992097</v>
       </c>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:11">
       <c r="A100" s="15">
         <v>39575</v>
       </c>
@@ -18844,7 +18856,7 @@
         <v>37.798178950335576</v>
       </c>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:11">
       <c r="A101" s="15">
         <v>39582</v>
       </c>
@@ -18880,7 +18892,7 @@
         <v>68.460251596471679</v>
       </c>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:11">
       <c r="A102" s="15">
         <v>39589</v>
       </c>
@@ -18916,7 +18928,7 @@
         <v>65.70356446097523</v>
       </c>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:11">
       <c r="A103" s="15">
         <v>39596</v>
       </c>
@@ -18952,7 +18964,7 @@
         <v>66.213667550072984</v>
       </c>
     </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:11">
       <c r="A104" s="15">
         <v>39603</v>
       </c>
@@ -18988,7 +19000,7 @@
         <v>65.788974489430842</v>
       </c>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:11">
       <c r="A105" s="15">
         <v>39610</v>
       </c>
@@ -19024,7 +19036,7 @@
         <v>78.830161121302538</v>
       </c>
     </row>
-    <row r="106" spans="1:11" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:11" s="11" customFormat="1">
       <c r="A106" s="15">
         <v>39617</v>
       </c>
@@ -19060,7 +19072,7 @@
         <v>65.083754207393383</v>
       </c>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:11">
       <c r="A107" s="15">
         <v>39624</v>
       </c>
@@ -19096,7 +19108,7 @@
         <v>55.264758647687017</v>
       </c>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:11">
       <c r="A108" s="15">
         <v>39631</v>
       </c>
@@ -19132,7 +19144,7 @@
         <v>52.723327174933317</v>
       </c>
     </row>
-    <row r="109" spans="1:11" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:11" s="11" customFormat="1">
       <c r="A109" s="15">
         <v>39638</v>
       </c>
@@ -19168,7 +19180,7 @@
         <v>75.848904583590468</v>
       </c>
     </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:11">
       <c r="A110" s="15">
         <v>39645</v>
       </c>
@@ -19204,7 +19216,7 @@
         <v>51.278326455349131</v>
       </c>
     </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:11">
       <c r="A111" s="15">
         <v>39652</v>
       </c>
@@ -19240,7 +19252,7 @@
         <v>57.909108469652679</v>
       </c>
     </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:11">
       <c r="A112" s="15">
         <v>39659</v>
       </c>
@@ -19276,7 +19288,7 @@
         <v>61.750517406739192</v>
       </c>
     </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:11">
       <c r="A113" s="15">
         <v>39666</v>
       </c>
@@ -19312,7 +19324,7 @@
         <v>52.661575232504951</v>
       </c>
     </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:11">
       <c r="A114" s="15">
         <v>39673</v>
       </c>
@@ -19348,7 +19360,7 @@
         <v>53.118250871076597</v>
       </c>
     </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:11">
       <c r="A115" s="15">
         <v>39681</v>
       </c>
@@ -19384,7 +19396,7 @@
         <v>50.104043997600584</v>
       </c>
     </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:11">
       <c r="A116" s="15">
         <v>39687</v>
       </c>
@@ -19420,7 +19432,7 @@
         <v>50.177676148596895</v>
       </c>
     </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:11">
       <c r="A117" s="15">
         <v>39694</v>
       </c>
@@ -19456,7 +19468,7 @@
         <v>65.073504542370074</v>
       </c>
     </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:11">
       <c r="A118" s="15">
         <v>39701</v>
       </c>
@@ -19492,7 +19504,7 @@
         <v>44.254182598587626</v>
       </c>
     </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:11">
       <c r="A119" s="15">
         <v>39708</v>
       </c>
@@ -19528,7 +19540,7 @@
         <v>47.422942867393644</v>
       </c>
     </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:11">
       <c r="A120" s="15">
         <v>39715</v>
       </c>
@@ -19564,7 +19576,7 @@
         <v>46.359571574198242</v>
       </c>
     </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:11">
       <c r="A121" s="15">
         <v>39722</v>
       </c>
@@ -19600,7 +19612,7 @@
         <v>33.405873873919091</v>
       </c>
     </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:11">
       <c r="A122" s="15">
         <v>39729</v>
       </c>
@@ -19636,7 +19648,7 @@
         <v>51.281080608690978</v>
       </c>
     </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:11">
       <c r="A123" s="15">
         <v>39736</v>
       </c>
@@ -19672,7 +19684,7 @@
         <v>40.551750201988128</v>
       </c>
     </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:11">
       <c r="A124" s="15">
         <v>39743</v>
       </c>
@@ -19708,7 +19720,7 @@
         <v>44.129844927173707</v>
       </c>
     </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:11">
       <c r="A125" s="15">
         <v>39750</v>
       </c>
@@ -19744,7 +19756,7 @@
         <v>53.882588406027168</v>
       </c>
     </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:11">
       <c r="A126" s="15">
         <v>39757</v>
       </c>
@@ -19780,7 +19792,7 @@
         <v>49.886350075701394</v>
       </c>
     </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:11">
       <c r="A127" s="15">
         <v>39764</v>
       </c>
@@ -19816,7 +19828,7 @@
         <v>44.405800463275128</v>
       </c>
     </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:11">
       <c r="A128" s="15">
         <v>39771</v>
       </c>
@@ -19852,7 +19864,7 @@
         <v>43.976952126529874</v>
       </c>
     </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:11">
       <c r="A129" s="15">
         <v>39778</v>
       </c>
@@ -19888,7 +19900,7 @@
         <v>57.854397526301433</v>
       </c>
     </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:11">
       <c r="A130" s="15">
         <v>39785</v>
       </c>
@@ -19924,7 +19936,7 @@
         <v>45.357327933111691</v>
       </c>
     </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:11">
       <c r="A131" s="15">
         <v>39792</v>
       </c>
@@ -19975,7 +19987,7 @@
         <v>49.214072926201013</v>
       </c>
     </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:11">
       <c r="A132" s="15">
         <v>39799</v>
       </c>
@@ -20011,7 +20023,7 @@
         <v>53.491406900967732</v>
       </c>
     </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:11">
       <c r="A133" s="15">
         <v>39806</v>
       </c>
@@ -20047,7 +20059,7 @@
         <v>55.286482576750558</v>
       </c>
     </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:11">
       <c r="A134" s="15">
         <v>39813</v>
       </c>
@@ -20083,7 +20095,7 @@
         <v>55.143723549589758</v>
       </c>
     </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:11">
       <c r="A135" s="15">
         <v>39820</v>
       </c>
@@ -20119,7 +20131,7 @@
         <v>51.012811516083978</v>
       </c>
     </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:11">
       <c r="A136" s="15">
         <v>39827</v>
       </c>
@@ -20155,7 +20167,7 @@
         <v>64.584992254313974</v>
       </c>
     </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:11">
       <c r="A137" s="15">
         <v>39834</v>
       </c>
@@ -20191,7 +20203,7 @@
         <v>51.036330889936345</v>
       </c>
     </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:11">
       <c r="A138" s="15">
         <v>39841</v>
       </c>
@@ -20227,7 +20239,7 @@
         <v>49.006860617093729</v>
       </c>
     </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:11">
       <c r="A139" s="15">
         <v>39848</v>
       </c>
@@ -20263,7 +20275,7 @@
         <v>33.08758938678627</v>
       </c>
     </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:11">
       <c r="A140" s="15">
         <v>39855</v>
       </c>
@@ -20299,7 +20311,7 @@
         <v>42.688334209137516</v>
       </c>
     </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:11">
       <c r="A141" s="15">
         <v>39862</v>
       </c>
@@ -20335,7 +20347,7 @@
         <v>49.836210913235156</v>
       </c>
     </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:11">
       <c r="A142" s="15">
         <v>39869</v>
       </c>
@@ -20371,7 +20383,7 @@
         <v>46.376897362766087</v>
       </c>
     </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:11">
       <c r="A143" s="15">
         <v>39876</v>
       </c>
@@ -20407,7 +20419,7 @@
         <v>48.797982331083887</v>
       </c>
     </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:11">
       <c r="A144" s="15">
         <v>39883</v>
       </c>
@@ -20443,7 +20455,7 @@
         <v>50.995285896575474</v>
       </c>
     </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:11">
       <c r="A145" s="15">
         <v>39890</v>
       </c>
@@ -20479,7 +20491,7 @@
         <v>50.632752300623871</v>
       </c>
     </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:11">
       <c r="A146" s="15">
         <v>39897</v>
       </c>
@@ -20515,7 +20527,7 @@
         <v>49.159815906896966</v>
       </c>
     </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:11">
       <c r="A147" s="15">
         <v>39904</v>
       </c>
@@ -20551,7 +20563,7 @@
         <v>67.93322071407249</v>
       </c>
     </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:11">
       <c r="A148" s="15">
         <v>39911</v>
       </c>
@@ -20587,7 +20599,7 @@
         <v>59.144140747470985</v>
       </c>
     </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:11">
       <c r="A149" s="15">
         <v>39918</v>
       </c>
@@ -20623,7 +20635,7 @@
         <v>48.417328037810883</v>
       </c>
     </row>
-    <row r="150" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:11">
       <c r="A150" s="15">
         <v>39925</v>
       </c>
@@ -20659,7 +20671,7 @@
         <v>65.507189828231219</v>
       </c>
     </row>
-    <row r="151" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:11">
       <c r="A151" s="15">
         <v>39932</v>
       </c>
@@ -20695,7 +20707,7 @@
         <v>67.77459535800439</v>
       </c>
     </row>
-    <row r="152" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:11">
       <c r="A152" s="15">
         <v>39939</v>
       </c>
@@ -20731,7 +20743,7 @@
         <v>67.144419826628891</v>
       </c>
     </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:11">
       <c r="A153" s="15">
         <v>39946</v>
       </c>
@@ -20767,7 +20779,7 @@
         <v>50.709106035336958</v>
       </c>
     </row>
-    <row r="154" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:11">
       <c r="A154" s="15">
         <v>39953</v>
       </c>
@@ -20803,7 +20815,7 @@
         <v>45.673803993182069</v>
       </c>
     </row>
-    <row r="155" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:11">
       <c r="A155" s="15">
         <v>39960</v>
       </c>
@@ -20839,7 +20851,7 @@
         <v>56.578290137928242</v>
       </c>
     </row>
-    <row r="156" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:11">
       <c r="A156" s="15">
         <v>39967</v>
       </c>
@@ -20875,7 +20887,7 @@
         <v>65.158129608233793</v>
       </c>
     </row>
-    <row r="157" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:11">
       <c r="A157" s="15">
         <v>39974</v>
       </c>
@@ -20911,7 +20923,7 @@
         <v>44.471505975736868</v>
       </c>
     </row>
-    <row r="158" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:11">
       <c r="A158" s="15">
         <v>39981</v>
       </c>
@@ -20947,7 +20959,7 @@
         <v>52.627079222161107</v>
       </c>
     </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:11">
       <c r="A159" s="15">
         <v>39988</v>
       </c>
@@ -20983,7 +20995,7 @@
         <v>66.261051954921754</v>
       </c>
     </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:11">
       <c r="A160" s="15">
         <v>39995</v>
       </c>
@@ -21019,7 +21031,7 @@
         <v>54.893058424976317</v>
       </c>
     </row>
-    <row r="161" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:11">
       <c r="A161" s="15">
         <v>40002</v>
       </c>
@@ -21055,7 +21067,7 @@
         <v>64.161205849108597</v>
       </c>
     </row>
-    <row r="162" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:11">
       <c r="A162" s="15">
         <v>40009</v>
       </c>
@@ -21091,7 +21103,7 @@
         <v>52.811235830415114</v>
       </c>
     </row>
-    <row r="163" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:11">
       <c r="A163" s="15">
         <v>40016</v>
       </c>
@@ -21127,7 +21139,7 @@
         <v>57.645867319279404</v>
       </c>
     </row>
-    <row r="164" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:11">
       <c r="A164" s="15">
         <v>40023</v>
       </c>
@@ -21163,7 +21175,7 @@
         <v>61.365403956693434</v>
       </c>
     </row>
-    <row r="165" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:11">
       <c r="A165" s="15">
         <v>40030</v>
       </c>
@@ -21199,7 +21211,7 @@
         <v>44.582988427682338</v>
       </c>
     </row>
-    <row r="166" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:11">
       <c r="A166" s="15">
         <v>40037</v>
       </c>
@@ -21235,7 +21247,7 @@
         <v>54.166951121047973</v>
       </c>
     </row>
-    <row r="167" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:11">
       <c r="A167" s="15">
         <v>40044</v>
       </c>
@@ -21271,7 +21283,7 @@
         <v>76.385981144531414</v>
       </c>
     </row>
-    <row r="168" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:11">
       <c r="A168" s="15">
         <v>40051</v>
       </c>
@@ -21307,7 +21319,7 @@
         <v>71.141667275747665</v>
       </c>
     </row>
-    <row r="169" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:11">
       <c r="A169" s="15">
         <v>40058</v>
       </c>
@@ -21343,7 +21355,7 @@
         <v>81.41339889263179</v>
       </c>
     </row>
-    <row r="170" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:11">
       <c r="A170" s="15">
         <v>40065</v>
       </c>
@@ -21379,7 +21391,7 @@
         <v>63.355150657102897</v>
       </c>
     </row>
-    <row r="171" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:11">
       <c r="A171" s="15">
         <v>40072</v>
       </c>
@@ -21415,7 +21427,7 @@
         <v>63.586872250336747</v>
       </c>
     </row>
-    <row r="172" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:11">
       <c r="A172" s="15">
         <v>40079</v>
       </c>
@@ -21451,7 +21463,7 @@
         <v>53.318827599106207</v>
       </c>
     </row>
-    <row r="173" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:11">
       <c r="A173" s="15">
         <v>40086</v>
       </c>
@@ -21487,7 +21499,7 @@
         <v>49.477873007591704</v>
       </c>
     </row>
-    <row r="174" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:11">
       <c r="A174" s="15">
         <v>40093</v>
       </c>
@@ -21523,7 +21535,7 @@
         <v>71.403538470599969</v>
       </c>
     </row>
-    <row r="175" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:11">
       <c r="A175" s="15">
         <v>40100</v>
       </c>
@@ -21559,7 +21571,7 @@
         <v>61.732827908030352</v>
       </c>
     </row>
-    <row r="176" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:11">
       <c r="A176" s="15">
         <v>40107</v>
       </c>
@@ -21595,7 +21607,7 @@
         <v>52.229993511604249</v>
       </c>
     </row>
-    <row r="177" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:11">
       <c r="A177" s="15">
         <v>40114</v>
       </c>
@@ -21631,7 +21643,7 @@
         <v>64.598575021541549</v>
       </c>
     </row>
-    <row r="178" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:11">
       <c r="A178" s="15">
         <v>40121</v>
       </c>
@@ -21667,7 +21679,7 @@
         <v>61.131436014016572</v>
       </c>
     </row>
-    <row r="179" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:11">
       <c r="A179" s="15">
         <v>40128</v>
       </c>
@@ -21703,7 +21715,7 @@
         <v>53.907207534999003</v>
       </c>
     </row>
-    <row r="180" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:11">
       <c r="A180" s="15">
         <v>40135</v>
       </c>
@@ -21739,7 +21751,7 @@
         <v>44.756939056977522</v>
       </c>
     </row>
-    <row r="181" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:11">
       <c r="A181" s="15">
         <v>40142</v>
       </c>
@@ -21775,7 +21787,7 @@
         <v>56.685418081441156</v>
       </c>
     </row>
-    <row r="182" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:11">
       <c r="A182" s="15">
         <v>40149</v>
       </c>
@@ -21811,7 +21823,7 @@
         <v>49.326994067650219</v>
       </c>
     </row>
-    <row r="183" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:11">
       <c r="A183" s="15">
         <v>40156</v>
       </c>
@@ -21847,7 +21859,7 @@
         <v>56.94789248873581</v>
       </c>
     </row>
-    <row r="184" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:11">
       <c r="A184" s="15">
         <v>40163</v>
       </c>
@@ -21883,7 +21895,7 @@
         <v>53.684534257154517</v>
       </c>
     </row>
-    <row r="185" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:11">
       <c r="A185" s="15">
         <v>40170</v>
       </c>
@@ -21919,7 +21931,7 @@
         <v>65.364947708147739</v>
       </c>
     </row>
-    <row r="186" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:11">
       <c r="A186" s="15">
         <v>40177</v>
       </c>
@@ -21955,7 +21967,7 @@
         <v>53.704634029690361</v>
       </c>
     </row>
-    <row r="187" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:11">
       <c r="A187" s="15">
         <v>40184</v>
       </c>
@@ -21991,7 +22003,7 @@
         <v>54.771375546492628</v>
       </c>
     </row>
-    <row r="188" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:11">
       <c r="A188" s="15">
         <v>40191</v>
       </c>
@@ -22027,7 +22039,7 @@
         <v>57.833752535015343</v>
       </c>
     </row>
-    <row r="189" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:11">
       <c r="A189" s="15">
         <v>40198</v>
       </c>
@@ -22063,7 +22075,7 @@
         <v>79.252584956089748</v>
       </c>
     </row>
-    <row r="190" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:11">
       <c r="A190" s="15">
         <v>40205</v>
       </c>
@@ -22099,7 +22111,7 @@
         <v>66.112908932661171</v>
       </c>
     </row>
-    <row r="191" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:11">
       <c r="A191" s="15">
         <v>40212</v>
       </c>
@@ -22135,7 +22147,7 @@
         <v>68.480905740352668</v>
       </c>
     </row>
-    <row r="192" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:11">
       <c r="A192" s="15">
         <v>40219</v>
       </c>
@@ -22171,7 +22183,7 @@
         <v>68.820680112015253</v>
       </c>
     </row>
-    <row r="193" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:11">
       <c r="A193" s="15">
         <v>40226</v>
       </c>
@@ -22207,7 +22219,7 @@
         <v>59.032374376182737</v>
       </c>
     </row>
-    <row r="194" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:11">
       <c r="A194" s="15">
         <v>40233</v>
       </c>
@@ -22243,7 +22255,7 @@
         <v>60.995325657513426</v>
       </c>
     </row>
-    <row r="195" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:11">
       <c r="A195" s="15">
         <v>40240</v>
       </c>
@@ -22294,7 +22306,7 @@
         <v>61.01651833892263</v>
       </c>
     </row>
-    <row r="196" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:11">
       <c r="A196" s="15">
         <v>40247</v>
       </c>
@@ -22330,7 +22342,7 @@
         <v>68.948409164893818</v>
       </c>
     </row>
-    <row r="197" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:11">
       <c r="A197" s="15">
         <v>40254</v>
       </c>
@@ -22366,7 +22378,7 @@
         <v>55.495282272042076</v>
       </c>
     </row>
-    <row r="198" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:11">
       <c r="A198" s="15">
         <v>40261</v>
       </c>
@@ -22402,7 +22414,7 @@
         <v>57.756350696573961</v>
       </c>
     </row>
-    <row r="199" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:11">
       <c r="A199" s="15">
         <v>40268</v>
       </c>
@@ -22438,7 +22450,7 @@
         <v>46.374631010759359</v>
       </c>
     </row>
-    <row r="200" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:11">
       <c r="A200" s="15">
         <v>40275</v>
       </c>
@@ -22474,7 +22486,7 @@
         <v>50.035497779699199</v>
       </c>
     </row>
-    <row r="201" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:11">
       <c r="A201" s="15">
         <v>40282</v>
       </c>
@@ -22510,7 +22522,7 @@
         <v>45.14920394961522</v>
       </c>
     </row>
-    <row r="202" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:11">
       <c r="A202" s="15">
         <v>40289</v>
       </c>
@@ -22546,7 +22558,7 @@
         <v>42.330808834030208</v>
       </c>
     </row>
-    <row r="203" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:11">
       <c r="A203" s="15">
         <v>40296</v>
       </c>
@@ -22582,7 +22594,7 @@
         <v>46.031147244235598</v>
       </c>
     </row>
-    <row r="204" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:11">
       <c r="A204" s="15">
         <v>40303</v>
       </c>
@@ -22618,7 +22630,7 @@
         <v>73.783147168729855</v>
       </c>
     </row>
-    <row r="205" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:11">
       <c r="A205" s="15">
         <v>40310</v>
       </c>
@@ -22654,7 +22666,7 @@
         <v>67.420059029224618</v>
       </c>
     </row>
-    <row r="206" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:11">
       <c r="A206" s="15">
         <v>40317</v>
       </c>
@@ -22690,7 +22702,7 @@
         <v>65.236302377809508</v>
       </c>
     </row>
-    <row r="207" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:11">
       <c r="A207" s="15">
         <v>40324</v>
       </c>
@@ -22726,7 +22738,7 @@
         <v>45.438603264918548</v>
       </c>
     </row>
-    <row r="208" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:11">
       <c r="A208" s="15">
         <v>40331</v>
       </c>
@@ -22762,7 +22774,7 @@
         <v>55.842613656597415</v>
       </c>
     </row>
-    <row r="209" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:11">
       <c r="A209" s="15">
         <v>40338</v>
       </c>
@@ -22798,7 +22810,7 @@
         <v>50.566226976684703</v>
       </c>
     </row>
-    <row r="210" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:11">
       <c r="A210" s="15">
         <v>40345</v>
       </c>
@@ -22834,7 +22846,7 @@
         <v>60.167993983512531</v>
       </c>
     </row>
-    <row r="211" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:11">
       <c r="A211" s="15">
         <v>40352</v>
       </c>
@@ -22870,7 +22882,7 @@
         <v>59.384867216709665</v>
       </c>
     </row>
-    <row r="212" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:11">
       <c r="A212" s="15">
         <v>40359</v>
       </c>
@@ -22906,7 +22918,7 @@
         <v>51.877165703250242</v>
       </c>
     </row>
-    <row r="213" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:11">
       <c r="A213" s="15">
         <v>40366</v>
       </c>
@@ -22942,7 +22954,7 @@
         <v>60.791159694094574</v>
       </c>
     </row>
-    <row r="214" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:11">
       <c r="A214" s="15">
         <v>40373</v>
       </c>
@@ -22978,7 +22990,7 @@
         <v>52.381556868806406</v>
       </c>
     </row>
-    <row r="215" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:11">
       <c r="A215" s="15">
         <v>40380</v>
       </c>
@@ -23014,7 +23026,7 @@
         <v>55.497901708236633</v>
       </c>
     </row>
-    <row r="216" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:11">
       <c r="A216" s="15">
         <v>40387</v>
       </c>
@@ -23050,7 +23062,7 @@
         <v>63.648541403343927</v>
       </c>
     </row>
-    <row r="217" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:11">
       <c r="A217" s="15">
         <v>40394</v>
       </c>
@@ -23086,7 +23098,7 @@
         <v>58.51627398414611</v>
       </c>
     </row>
-    <row r="218" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:11">
       <c r="A218" s="15">
         <v>40401</v>
       </c>
@@ -23122,7 +23134,7 @@
         <v>70.168158657672691</v>
       </c>
     </row>
-    <row r="219" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:11">
       <c r="A219" s="15">
         <v>40408</v>
       </c>
@@ -23158,7 +23170,7 @@
         <v>53.947041077312385</v>
       </c>
     </row>
-    <row r="220" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:11">
       <c r="A220" s="15">
         <v>40415</v>
       </c>
@@ -23194,7 +23206,7 @@
         <v>55.908131213647891</v>
       </c>
     </row>
-    <row r="221" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:11">
       <c r="A221" s="15">
         <v>40422</v>
       </c>
@@ -23230,7 +23242,7 @@
         <v>62.564187638553811</v>
       </c>
     </row>
-    <row r="222" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:11">
       <c r="A222" s="15">
         <v>40429</v>
       </c>
@@ -23266,7 +23278,7 @@
         <v>72.423309874299363</v>
       </c>
     </row>
-    <row r="223" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:11">
       <c r="A223" s="15">
         <v>40436</v>
       </c>
@@ -23302,7 +23314,7 @@
         <v>73.388746907379783</v>
       </c>
     </row>
-    <row r="224" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:11">
       <c r="A224" s="15">
         <v>40443</v>
       </c>
@@ -23338,7 +23350,7 @@
         <v>74.427829003026858</v>
       </c>
     </row>
-    <row r="225" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:11">
       <c r="A225" s="15">
         <v>40450</v>
       </c>
@@ -23374,7 +23386,7 @@
         <v>65.974731715358232</v>
       </c>
     </row>
-    <row r="226" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:11">
       <c r="A226" s="15">
         <v>40457</v>
       </c>
@@ -23410,7 +23422,7 @@
         <v>59.692906241492011</v>
       </c>
     </row>
-    <row r="227" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:11">
       <c r="A227" s="15">
         <v>40464</v>
       </c>
@@ -23446,7 +23458,7 @@
         <v>55.007204521826623</v>
       </c>
     </row>
-    <row r="228" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:11">
       <c r="A228" s="15">
         <v>40471</v>
       </c>
@@ -23482,7 +23494,7 @@
         <v>54.037281159418455</v>
       </c>
     </row>
-    <row r="229" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:11">
       <c r="A229" s="15">
         <v>40478</v>
       </c>
@@ -23518,7 +23530,7 @@
         <v>74.053447495288836</v>
       </c>
     </row>
-    <row r="230" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:11">
       <c r="A230" s="15">
         <v>40485</v>
       </c>
@@ -23554,7 +23566,7 @@
         <v>57.599139747516887</v>
       </c>
     </row>
-    <row r="231" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:11">
       <c r="A231" s="15">
         <v>40493</v>
       </c>
@@ -23590,7 +23602,7 @@
         <v>73.628931758084974</v>
       </c>
     </row>
-    <row r="232" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:11">
       <c r="A232" s="15">
         <v>40499</v>
       </c>
@@ -23626,7 +23638,7 @@
         <v>64.712269652083734</v>
       </c>
     </row>
-    <row r="233" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:11">
       <c r="A233" s="15">
         <v>40506</v>
       </c>
@@ -23662,7 +23674,7 @@
         <v>68.728127833919316</v>
       </c>
     </row>
-    <row r="234" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:11">
       <c r="A234" s="15">
         <v>40513</v>
       </c>
@@ -23698,7 +23710,7 @@
         <v>71.396578703865657</v>
       </c>
     </row>
-    <row r="235" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:11">
       <c r="A235" s="15">
         <v>40520</v>
       </c>
@@ -23734,7 +23746,7 @@
         <v>56.848732557127434</v>
       </c>
     </row>
-    <row r="236" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:11">
       <c r="A236" s="15">
         <v>40527</v>
       </c>
@@ -23770,7 +23782,7 @@
         <v>48.876462768440668</v>
       </c>
     </row>
-    <row r="237" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:11">
       <c r="A237" s="15">
         <v>40534</v>
       </c>
@@ -23806,7 +23818,7 @@
         <v>30.939366105335772</v>
       </c>
     </row>
-    <row r="238" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:11">
       <c r="A238" s="15">
         <v>40541</v>
       </c>
@@ -23842,7 +23854,7 @@
         <v>25.867679114547297</v>
       </c>
     </row>
-    <row r="239" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:11">
       <c r="A239" s="15">
         <v>40548</v>
       </c>
@@ -23878,7 +23890,7 @@
         <v>35.99596195192472</v>
       </c>
     </row>
-    <row r="240" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:11">
       <c r="A240" s="15">
         <v>40555</v>
       </c>
@@ -23914,7 +23926,7 @@
         <v>34.5248029413723</v>
       </c>
     </row>
-    <row r="241" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:11">
       <c r="A241" s="15">
         <v>40562</v>
       </c>
@@ -23950,7 +23962,7 @@
         <v>48.204614903131251</v>
       </c>
     </row>
-    <row r="242" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:11">
       <c r="A242" s="15">
         <v>40569</v>
       </c>
@@ -23986,7 +23998,7 @@
         <v>44.563550516112116</v>
       </c>
     </row>
-    <row r="243" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:11">
       <c r="A243" s="15">
         <v>40576</v>
       </c>
@@ -24022,7 +24034,7 @@
         <v>37.30092994819298</v>
       </c>
     </row>
-    <row r="244" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:11">
       <c r="A244" s="15">
         <v>40583</v>
       </c>
@@ -24058,7 +24070,7 @@
         <v>36.241942484664484</v>
       </c>
     </row>
-    <row r="245" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:11">
       <c r="A245" s="15">
         <v>40590</v>
       </c>
@@ -24094,7 +24106,7 @@
         <v>39.530799594711759</v>
       </c>
     </row>
-    <row r="246" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:11">
       <c r="A246" s="15">
         <v>40597</v>
       </c>
@@ -24130,7 +24142,7 @@
         <v>53.939404659302646</v>
       </c>
     </row>
-    <row r="247" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:11">
       <c r="A247" s="15">
         <v>40604</v>
       </c>
@@ -24166,7 +24178,7 @@
         <v>43.942750002449529</v>
       </c>
     </row>
-    <row r="248" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:11">
       <c r="A248" s="15">
         <v>40611</v>
       </c>
@@ -24202,7 +24214,7 @@
         <v>34.894786457057684</v>
       </c>
     </row>
-    <row r="249" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:11">
       <c r="A249" s="15">
         <v>40618</v>
       </c>
@@ -24238,7 +24250,7 @@
         <v>64.316923641190016</v>
       </c>
     </row>
-    <row r="250" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:11">
       <c r="A250" s="15">
         <v>40625</v>
       </c>
@@ -24274,7 +24286,7 @@
         <v>54.669969412425644</v>
       </c>
     </row>
-    <row r="251" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:11">
       <c r="A251" s="15">
         <v>40632</v>
       </c>
@@ -24310,7 +24322,7 @@
         <v>33.436812839822487</v>
       </c>
     </row>
-    <row r="252" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:11">
       <c r="A252" s="15">
         <v>40639</v>
       </c>
@@ -24346,7 +24358,7 @@
         <v>39.172313642501635</v>
       </c>
     </row>
-    <row r="253" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:11">
       <c r="A253" s="15">
         <v>40646</v>
       </c>
@@ -24382,7 +24394,7 @@
         <v>38.729050102374607</v>
       </c>
     </row>
-    <row r="254" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:11">
       <c r="A254" s="15">
         <v>40653</v>
       </c>
@@ -24418,7 +24430,7 @@
         <v>41.715563146345993</v>
       </c>
     </row>
-    <row r="255" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:11">
       <c r="A255" s="15">
         <v>40660</v>
       </c>
@@ -24454,7 +24466,7 @@
         <v>43.741742077791095</v>
       </c>
     </row>
-    <row r="256" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:11">
       <c r="A256" s="15">
         <v>40667</v>
       </c>
@@ -24490,7 +24502,7 @@
         <v>47.873989122981456</v>
       </c>
     </row>
-    <row r="257" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:11">
       <c r="A257" s="15">
         <v>40674</v>
       </c>
@@ -24526,7 +24538,7 @@
         <v>51.779665709540218</v>
       </c>
     </row>
-    <row r="258" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:11">
       <c r="A258" s="15">
         <v>40681</v>
       </c>
@@ -24562,7 +24574,7 @@
         <v>57.023035358289334</v>
       </c>
     </row>
-    <row r="259" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:11">
       <c r="A259" s="15">
         <v>40688</v>
       </c>
@@ -24613,7 +24625,7 @@
         <v>56.87088409797628</v>
       </c>
     </row>
-    <row r="260" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:11">
       <c r="A260" s="15">
         <v>40695</v>
       </c>
@@ -24649,7 +24661,7 @@
         <v>47.063569688632143</v>
       </c>
     </row>
-    <row r="261" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:11">
       <c r="A261" s="15">
         <v>40702</v>
       </c>
@@ -24685,7 +24697,7 @@
         <v>58.561562455438484</v>
       </c>
     </row>
-    <row r="262" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:11">
       <c r="A262" s="15">
         <v>40709</v>
       </c>
@@ -24721,7 +24733,7 @@
         <v>54.876464024706216</v>
       </c>
     </row>
-    <row r="263" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:11">
       <c r="A263" s="15">
         <v>40716</v>
       </c>
@@ -24757,7 +24769,7 @@
         <v>48.129506282529015</v>
       </c>
     </row>
-    <row r="264" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:11">
       <c r="A264" s="15">
         <v>40723</v>
       </c>
@@ -24793,7 +24805,7 @@
         <v>53.998865301934728</v>
       </c>
     </row>
-    <row r="265" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:11">
       <c r="A265" s="15">
         <v>40730</v>
       </c>
@@ -24829,7 +24841,7 @@
         <v>57.89850820929329</v>
       </c>
     </row>
-    <row r="266" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:11">
       <c r="A266" s="15">
         <v>40737</v>
       </c>
@@ -24865,7 +24877,7 @@
         <v>53.479549570113456</v>
       </c>
     </row>
-    <row r="267" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:11">
       <c r="A267" s="15">
         <v>40744</v>
       </c>
@@ -24901,7 +24913,7 @@
         <v>49.79143878947302</v>
       </c>
     </row>
-    <row r="268" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:11">
       <c r="A268" s="15">
         <v>40751</v>
       </c>
@@ -24937,7 +24949,7 @@
         <v>42.651475813694034</v>
       </c>
     </row>
-    <row r="269" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:11">
       <c r="A269" s="15">
         <v>40758</v>
       </c>
@@ -24973,7 +24985,7 @@
         <v>50.439188817558389</v>
       </c>
     </row>
-    <row r="270" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:11">
       <c r="A270" s="15">
         <v>40765</v>
       </c>
@@ -25009,7 +25021,7 @@
         <v>42.049324508367285</v>
       </c>
     </row>
-    <row r="271" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:11">
       <c r="A271" s="15">
         <v>40772</v>
       </c>
@@ -25045,7 +25057,7 @@
         <v>47.516027185636773</v>
       </c>
     </row>
-    <row r="272" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:11">
       <c r="A272" s="15">
         <v>40779</v>
       </c>
@@ -25081,7 +25093,7 @@
         <v>40.399772058656886</v>
       </c>
     </row>
-    <row r="273" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:11">
       <c r="A273" s="15">
         <v>40786</v>
       </c>
@@ -25117,7 +25129,7 @@
         <v>44.783201620610939</v>
       </c>
     </row>
-    <row r="274" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:11">
       <c r="A274" s="15">
         <v>40793</v>
       </c>
@@ -25153,7 +25165,7 @@
         <v>46.854774319627346</v>
       </c>
     </row>
-    <row r="275" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:11">
       <c r="A275" s="15">
         <v>40800</v>
       </c>
@@ -25189,7 +25201,7 @@
         <v>50.572231681862235</v>
       </c>
     </row>
-    <row r="276" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:11">
       <c r="A276" s="15">
         <v>40807</v>
       </c>
@@ -25225,7 +25237,7 @@
         <v>51.000097894093308</v>
       </c>
     </row>
-    <row r="277" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:11">
       <c r="A277" s="15">
         <v>40814</v>
       </c>
@@ -25261,7 +25273,7 @@
         <v>38.969787977354969</v>
       </c>
     </row>
-    <row r="278" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:11">
       <c r="A278" s="15">
         <v>40821</v>
       </c>
@@ -25297,7 +25309,7 @@
         <v>54.517864058372737</v>
       </c>
     </row>
-    <row r="279" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:11">
       <c r="A279" s="15">
         <v>40828</v>
       </c>
@@ -25333,7 +25345,7 @@
         <v>58.875398087826127</v>
       </c>
     </row>
-    <row r="280" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:11">
       <c r="A280" s="15">
         <v>40835</v>
       </c>
@@ -25369,7 +25381,7 @@
         <v>40.918862469344425</v>
       </c>
     </row>
-    <row r="281" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:11">
       <c r="A281" s="15">
         <v>40842</v>
       </c>
@@ -25405,7 +25417,7 @@
         <v>45.233867381064172</v>
       </c>
     </row>
-    <row r="282" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:11">
       <c r="A282" s="15">
         <v>40849</v>
       </c>
@@ -25441,7 +25453,7 @@
         <v>55.320831293464849</v>
       </c>
     </row>
-    <row r="283" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:11">
       <c r="A283" s="15">
         <v>40856</v>
       </c>
@@ -25477,7 +25489,7 @@
         <v>55.690513263814637</v>
       </c>
     </row>
-    <row r="284" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:11">
       <c r="A284" s="15">
         <v>40863</v>
       </c>
@@ -25513,7 +25525,7 @@
         <v>51.999145292121014</v>
       </c>
     </row>
-    <row r="285" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:11">
       <c r="A285" s="15">
         <v>40870</v>
       </c>
@@ -25549,7 +25561,7 @@
         <v>45.873095396241652</v>
       </c>
     </row>
-    <row r="286" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:11">
       <c r="A286" s="15">
         <v>40877</v>
       </c>
@@ -25585,7 +25597,7 @@
         <v>42.216169288999922</v>
       </c>
     </row>
-    <row r="287" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:11">
       <c r="A287" s="15">
         <v>40884</v>
       </c>
@@ -25621,7 +25633,7 @@
         <v>43.664531422515303</v>
       </c>
     </row>
-    <row r="288" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:11">
       <c r="A288" s="15">
         <v>40891</v>
       </c>
@@ -25657,7 +25669,7 @@
         <v>48.198670933439651</v>
       </c>
     </row>
-    <row r="289" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:11">
       <c r="A289" s="15">
         <v>40898</v>
       </c>
@@ -25693,7 +25705,7 @@
         <v>39.516792034075834</v>
       </c>
     </row>
-    <row r="290" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:11">
       <c r="A290" s="15">
         <v>40905</v>
       </c>
@@ -25729,7 +25741,7 @@
         <v>28.563193765273795</v>
       </c>
     </row>
-    <row r="291" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:11">
       <c r="A291" s="15">
         <v>40912</v>
       </c>
@@ -25765,7 +25777,7 @@
         <v>41.403003244764143</v>
       </c>
     </row>
-    <row r="292" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:11">
       <c r="A292" s="15">
         <v>40919</v>
       </c>
@@ -25801,7 +25813,7 @@
         <v>47.072652594140706</v>
       </c>
     </row>
-    <row r="293" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:11">
       <c r="A293" s="15">
         <v>40926</v>
       </c>
@@ -25837,7 +25849,7 @@
         <v>49.053078858054825</v>
       </c>
     </row>
-    <row r="294" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:11">
       <c r="A294" s="15">
         <v>40933</v>
       </c>
@@ -25873,7 +25885,7 @@
         <v>53.510954226421923</v>
       </c>
     </row>
-    <row r="295" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:11">
       <c r="A295" s="15">
         <v>40940</v>
       </c>
@@ -25909,7 +25921,7 @@
         <v>39.384750530886507</v>
       </c>
     </row>
-    <row r="296" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:11">
       <c r="A296" s="15">
         <v>40947</v>
       </c>
@@ -25945,7 +25957,7 @@
         <v>36.817697808266423</v>
       </c>
     </row>
-    <row r="297" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:11">
       <c r="A297" s="15">
         <v>40954</v>
       </c>
@@ -25981,7 +25993,7 @@
         <v>36.233572758862671</v>
       </c>
     </row>
-    <row r="298" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:11">
       <c r="A298" s="15">
         <v>40961</v>
       </c>
@@ -26017,7 +26029,7 @@
         <v>37.171889580703322</v>
       </c>
     </row>
-    <row r="299" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:11">
       <c r="A299" s="15">
         <v>40968</v>
       </c>
@@ -26053,7 +26065,7 @@
         <v>36.759941210655207</v>
       </c>
     </row>
-    <row r="300" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:11">
       <c r="A300" s="15">
         <v>40975</v>
       </c>
@@ -26089,7 +26101,7 @@
         <v>56.661237586866619</v>
       </c>
     </row>
-    <row r="301" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:11">
       <c r="A301" s="15">
         <v>40982</v>
       </c>
@@ -26125,7 +26137,7 @@
         <v>47.798457305394521</v>
       </c>
     </row>
-    <row r="302" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:11">
       <c r="A302" s="15">
         <v>40989</v>
       </c>
@@ -26161,7 +26173,7 @@
         <v>47.064324329465158</v>
       </c>
     </row>
-    <row r="303" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:11">
       <c r="A303" s="15">
         <v>40996</v>
       </c>
@@ -26197,7 +26209,7 @@
         <v>40.595204301061202</v>
       </c>
     </row>
-    <row r="304" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:11">
       <c r="A304" s="15">
         <v>41003</v>
       </c>
@@ -26233,7 +26245,7 @@
         <v>38.549937035348876</v>
       </c>
     </row>
-    <row r="305" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:11">
       <c r="A305" s="15">
         <v>41010</v>
       </c>
@@ -26269,7 +26281,7 @@
         <v>53.214477468494394</v>
       </c>
     </row>
-    <row r="306" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:11">
       <c r="A306" s="15">
         <v>41017</v>
       </c>
@@ -26305,7 +26317,7 @@
         <v>56.900572530695925</v>
       </c>
     </row>
-    <row r="307" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:11">
       <c r="A307" s="15">
         <v>41024</v>
       </c>
@@ -26341,7 +26353,7 @@
         <v>56.771006536281874</v>
       </c>
     </row>
-    <row r="308" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:11">
       <c r="A308" s="15">
         <v>41031</v>
       </c>
@@ -26377,7 +26389,7 @@
         <v>50.543476884317684</v>
       </c>
     </row>
-    <row r="309" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:11">
       <c r="A309" s="15">
         <v>41038</v>
       </c>
@@ -26413,7 +26425,7 @@
         <v>54.137497957615317</v>
       </c>
     </row>
-    <row r="310" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:11">
       <c r="A310" s="15">
         <v>41045</v>
       </c>
@@ -26449,7 +26461,7 @@
         <v>41.363917899541384</v>
       </c>
     </row>
-    <row r="311" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:11">
       <c r="A311" s="15">
         <v>41052</v>
       </c>
@@ -26485,7 +26497,7 @@
         <v>45.49777201728218</v>
       </c>
     </row>
-    <row r="312" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:11">
       <c r="A312" s="15">
         <v>41059</v>
       </c>
@@ -26521,7 +26533,7 @@
         <v>46.729614872834489</v>
       </c>
     </row>
-    <row r="313" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:11">
       <c r="A313" s="15">
         <v>41066</v>
       </c>
@@ -26557,7 +26569,7 @@
         <v>34.956741028578463</v>
       </c>
     </row>
-    <row r="314" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:11">
       <c r="A314" s="15">
         <v>41073</v>
       </c>
@@ -26593,7 +26605,7 @@
         <v>29.532500348198187</v>
       </c>
     </row>
-    <row r="315" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:11">
       <c r="A315" s="15">
         <v>41080</v>
       </c>
@@ -26629,7 +26641,7 @@
         <v>45.65945115969452</v>
       </c>
     </row>
-    <row r="316" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:11">
       <c r="A316" s="15">
         <v>41087</v>
       </c>
@@ -26665,7 +26677,7 @@
         <v>48.136271215938542</v>
       </c>
     </row>
-    <row r="317" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:11">
       <c r="A317" s="15">
         <v>41095</v>
       </c>
@@ -26701,7 +26713,7 @@
         <v>49.207476611003706</v>
       </c>
     </row>
-    <row r="318" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:11">
       <c r="A318" s="15">
         <v>41101</v>
       </c>
@@ -26737,7 +26749,7 @@
         <v>53.618962087056566</v>
       </c>
     </row>
-    <row r="319" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:11">
       <c r="A319" s="15">
         <v>41108</v>
       </c>
@@ -26773,7 +26785,7 @@
         <v>52.76407806027715</v>
       </c>
     </row>
-    <row r="320" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:11">
       <c r="A320" s="15">
         <v>41115</v>
       </c>
@@ -26809,7 +26821,7 @@
         <v>50.011052339523104</v>
       </c>
     </row>
-    <row r="321" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:11">
       <c r="A321" s="15">
         <v>41122</v>
       </c>
@@ -26845,7 +26857,7 @@
         <v>53.937797639233743</v>
       </c>
     </row>
-    <row r="322" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:11">
       <c r="A322" s="15">
         <v>41129</v>
       </c>
@@ -26881,7 +26893,7 @@
         <v>39.420666681528402</v>
       </c>
     </row>
-    <row r="323" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:11">
       <c r="A323" s="15">
         <v>41136</v>
       </c>
@@ -26932,7 +26944,7 @@
         <v>42.597308792434582</v>
       </c>
     </row>
-    <row r="324" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:11">
       <c r="A324" s="15">
         <v>41143</v>
       </c>
@@ -26968,7 +26980,7 @@
         <v>59.566739758018073</v>
       </c>
     </row>
-    <row r="325" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:11">
       <c r="A325" s="15">
         <v>41150</v>
       </c>
@@ -27004,7 +27016,7 @@
         <v>40.667483971490398</v>
       </c>
     </row>
-    <row r="326" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:11">
       <c r="A326" s="15">
         <v>41157</v>
       </c>
@@ -27040,7 +27052,7 @@
         <v>50.154861297471179</v>
       </c>
     </row>
-    <row r="327" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:11">
       <c r="A327" s="15">
         <v>41164</v>
       </c>
@@ -27076,7 +27088,7 @@
         <v>50.124976846592538</v>
       </c>
     </row>
-    <row r="328" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:11">
       <c r="A328" s="15">
         <v>41171</v>
       </c>
@@ -27112,7 +27124,7 @@
         <v>52.943578895895669</v>
       </c>
     </row>
-    <row r="329" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:11">
       <c r="A329" s="15">
         <v>41178</v>
       </c>
@@ -27148,7 +27160,7 @@
         <v>56.021511245433409</v>
       </c>
     </row>
-    <row r="330" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:11">
       <c r="A330" s="15">
         <v>41185</v>
       </c>
@@ -27184,7 +27196,7 @@
         <v>57.266397751374981</v>
       </c>
     </row>
-    <row r="331" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:11">
       <c r="A331" s="15">
         <v>41192</v>
       </c>
@@ -27220,7 +27232,7 @@
         <v>66.483484497561491</v>
       </c>
     </row>
-    <row r="332" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:11">
       <c r="A332" s="15">
         <v>41199</v>
       </c>
@@ -27256,7 +27268,7 @@
         <v>71.777760309165402</v>
       </c>
     </row>
-    <row r="333" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:11">
       <c r="A333" s="15">
         <v>41206</v>
       </c>
@@ -27292,7 +27304,7 @@
         <v>59.778361750310793</v>
       </c>
     </row>
-    <row r="334" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:11">
       <c r="A334" s="15">
         <v>41213</v>
       </c>
@@ -27328,7 +27340,7 @@
         <v>59.216704581992914</v>
       </c>
     </row>
-    <row r="335" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:11">
       <c r="A335" s="15">
         <v>41220</v>
       </c>
@@ -27364,7 +27376,7 @@
         <v>57.538374466714032</v>
       </c>
     </row>
-    <row r="336" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:11">
       <c r="A336" s="15">
         <v>41227</v>
       </c>
@@ -27400,7 +27412,7 @@
         <v>64.794060427377659</v>
       </c>
     </row>
-    <row r="337" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:11">
       <c r="A337" s="15">
         <v>41234</v>
       </c>
@@ -27436,7 +27448,7 @@
         <v>42.978585224257763</v>
       </c>
     </row>
-    <row r="338" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:11">
       <c r="A338" s="15">
         <v>41241</v>
       </c>
@@ -27472,7 +27484,7 @@
         <v>58.262610437726366</v>
       </c>
     </row>
-    <row r="339" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:11">
       <c r="A339" s="15">
         <v>41248</v>
       </c>
@@ -27508,7 +27520,7 @@
         <v>53.947354080111261</v>
       </c>
     </row>
-    <row r="340" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:11">
       <c r="A340" s="15">
         <v>41255</v>
       </c>
@@ -27544,7 +27556,7 @@
         <v>40.867278029986856</v>
       </c>
     </row>
-    <row r="341" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:11">
       <c r="A341" s="15">
         <v>41262</v>
       </c>
@@ -27580,7 +27592,7 @@
         <v>49.812955030683419</v>
       </c>
     </row>
-    <row r="342" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:11">
       <c r="A342" s="15">
         <v>41269</v>
       </c>
@@ -27616,7 +27628,7 @@
         <v>44.510630134900872</v>
       </c>
     </row>
-    <row r="343" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:11">
       <c r="A343" s="15">
         <v>41276</v>
       </c>
@@ -27652,7 +27664,7 @@
         <v>53.24693033779436</v>
       </c>
     </row>
-    <row r="344" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:11">
       <c r="A344" s="15">
         <v>41283</v>
       </c>
@@ -27688,7 +27700,7 @@
         <v>43.585114686349307</v>
       </c>
     </row>
-    <row r="345" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:11">
       <c r="A345" s="15">
         <v>41290</v>
       </c>
@@ -27724,7 +27736,7 @@
         <v>60.84780147014353</v>
       </c>
     </row>
-    <row r="346" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:11">
       <c r="A346" s="15">
         <v>41297</v>
       </c>
@@ -27760,7 +27772,7 @@
         <v>53.953140270861297</v>
       </c>
     </row>
-    <row r="347" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:11">
       <c r="A347" s="15">
         <v>41304</v>
       </c>
@@ -27796,7 +27808,7 @@
         <v>32.239533185206014</v>
       </c>
     </row>
-    <row r="348" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:11">
       <c r="A348" s="15">
         <v>41311</v>
       </c>
@@ -27832,7 +27844,7 @@
         <v>40.084712867791588</v>
       </c>
     </row>
-    <row r="349" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:11">
       <c r="A349" s="15">
         <v>41318</v>
       </c>
@@ -27868,7 +27880,7 @@
         <v>38.38710256166938</v>
       </c>
     </row>
-    <row r="350" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:11">
       <c r="A350" s="15">
         <v>41325</v>
       </c>
@@ -27904,7 +27916,7 @@
         <v>38.080293444545788</v>
       </c>
     </row>
-    <row r="351" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:11">
       <c r="A351" s="15">
         <v>41332</v>
       </c>
@@ -27940,7 +27952,7 @@
         <v>48.402767285139547</v>
       </c>
     </row>
-    <row r="352" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:11">
       <c r="A352" s="15">
         <v>41339</v>
       </c>
@@ -27976,7 +27988,7 @@
         <v>40.094000618700669</v>
       </c>
     </row>
-    <row r="353" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:11">
       <c r="A353" s="15">
         <v>41346</v>
       </c>
@@ -28012,7 +28024,7 @@
         <v>42.821783159517786</v>
       </c>
     </row>
-    <row r="354" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:11">
       <c r="A354" s="15">
         <v>41353</v>
       </c>
@@ -28048,7 +28060,7 @@
         <v>32.607118719705234</v>
       </c>
     </row>
-    <row r="355" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:11">
       <c r="A355" s="15">
         <v>41360</v>
       </c>
@@ -28084,7 +28096,7 @@
         <v>40.659143503192773</v>
       </c>
     </row>
-    <row r="356" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:11">
       <c r="A356" s="15">
         <v>41367</v>
       </c>
@@ -28120,7 +28132,7 @@
         <v>61.567550890600387</v>
       </c>
     </row>
-    <row r="357" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:11">
       <c r="A357" s="15">
         <v>41374</v>
       </c>
@@ -28156,7 +28168,7 @@
         <v>52.116557963159231</v>
       </c>
     </row>
-    <row r="358" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:11">
       <c r="A358" s="15">
         <v>41381</v>
       </c>
@@ -28192,7 +28204,7 @@
         <v>53.354057268656028</v>
       </c>
     </row>
-    <row r="359" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:11">
       <c r="A359" s="15">
         <v>41388</v>
       </c>
@@ -28228,7 +28240,7 @@
         <v>58.802213497238505</v>
       </c>
     </row>
-    <row r="360" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:11">
       <c r="A360" s="15">
         <v>41395</v>
       </c>
@@ -28264,7 +28276,7 @@
         <v>37.937705662389739</v>
       </c>
     </row>
-    <row r="361" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:11">
       <c r="A361" s="15">
         <v>41402</v>
       </c>
@@ -28300,7 +28312,7 @@
         <v>54.929642662956802</v>
       </c>
     </row>
-    <row r="362" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:11">
       <c r="A362" s="15">
         <v>41409</v>
       </c>
@@ -28336,7 +28348,7 @@
         <v>35.515606966366008</v>
       </c>
     </row>
-    <row r="363" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:11">
       <c r="A363" s="15">
         <v>41416</v>
       </c>
@@ -28372,7 +28384,7 @@
         <v>47.22321621646487</v>
       </c>
     </row>
-    <row r="364" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:11">
       <c r="A364" s="15">
         <v>41423</v>
       </c>
@@ -28408,7 +28420,7 @@
         <v>58.20055953610327</v>
       </c>
     </row>
-    <row r="365" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:11">
       <c r="A365" s="15">
         <v>41430</v>
       </c>
@@ -28444,7 +28456,7 @@
         <v>58.972667790307163</v>
       </c>
     </row>
-    <row r="366" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:11">
       <c r="A366" s="15">
         <v>41437</v>
       </c>
@@ -28480,7 +28492,7 @@
         <v>54.209657868522129</v>
       </c>
     </row>
-    <row r="367" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:11">
       <c r="A367" s="15">
         <v>41444</v>
       </c>
@@ -28516,7 +28528,7 @@
         <v>49.424558707629132</v>
       </c>
     </row>
-    <row r="368" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:11">
       <c r="A368" s="15">
         <v>41451</v>
       </c>
@@ -28552,7 +28564,7 @@
         <v>49.303982121743722</v>
       </c>
     </row>
-    <row r="369" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:11">
       <c r="A369" s="15">
         <v>41458</v>
       </c>
@@ -28588,7 +28600,7 @@
         <v>35.218787549159295</v>
       </c>
     </row>
-    <row r="370" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:11">
       <c r="A370" s="15">
         <v>41465</v>
       </c>
@@ -28624,7 +28636,7 @@
         <v>55.882367115793201</v>
       </c>
     </row>
-    <row r="371" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:11">
       <c r="A371" s="15">
         <v>41472</v>
       </c>
@@ -28660,7 +28672,7 @@
         <v>53.110925423170286</v>
       </c>
     </row>
-    <row r="372" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:11">
       <c r="A372" s="15">
         <v>41479</v>
       </c>
@@ -28696,7 +28708,7 @@
         <v>33.44447705914984</v>
       </c>
     </row>
-    <row r="373" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:11">
       <c r="A373" s="15">
         <v>41486</v>
       </c>
@@ -28732,7 +28744,7 @@
         <v>54.484641664282961</v>
       </c>
     </row>
-    <row r="374" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:11">
       <c r="A374" s="15">
         <v>41493</v>
       </c>
@@ -28768,7 +28780,7 @@
         <v>30.238330855873073</v>
       </c>
     </row>
-    <row r="375" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:11">
       <c r="A375" s="15">
         <v>41500</v>
       </c>
@@ -28804,7 +28816,7 @@
         <v>42.699029269899285</v>
       </c>
     </row>
-    <row r="376" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:11">
       <c r="A376" s="15">
         <v>41507</v>
       </c>
@@ -28840,7 +28852,7 @@
         <v>56.528524201883307</v>
       </c>
     </row>
-    <row r="377" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:11">
       <c r="A377" s="15">
         <v>41514</v>
       </c>
@@ -28876,7 +28888,7 @@
         <v>45.736639980287038</v>
       </c>
     </row>
-    <row r="378" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:11">
       <c r="A378" s="15">
         <v>41521</v>
       </c>
@@ -28912,7 +28924,7 @@
         <v>44.32004194458554</v>
       </c>
     </row>
-    <row r="379" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:11">
       <c r="A379" s="15">
         <v>41528</v>
       </c>
@@ -28948,7 +28960,7 @@
         <v>31.097341411399512</v>
       </c>
     </row>
-    <row r="380" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:11">
       <c r="A380" s="15">
         <v>41535</v>
       </c>
@@ -28984,7 +28996,7 @@
         <v>32.054779929422871</v>
       </c>
     </row>
-    <row r="381" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:11">
       <c r="A381" s="15">
         <v>41542</v>
       </c>
@@ -29020,7 +29032,7 @@
         <v>48.279990820009985</v>
       </c>
     </row>
-    <row r="382" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:11">
       <c r="A382" s="15">
         <v>41549</v>
       </c>
@@ -29056,7 +29068,7 @@
         <v>55.268275006754301</v>
       </c>
     </row>
-    <row r="383" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:11">
       <c r="A383" s="15">
         <v>41556</v>
       </c>
@@ -29092,7 +29104,7 @@
         <v>64.648358122534788</v>
       </c>
     </row>
-    <row r="384" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:11">
       <c r="A384" s="15">
         <v>41563</v>
       </c>
@@ -29128,7 +29140,7 @@
         <v>30.40107245824677</v>
       </c>
     </row>
-    <row r="385" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:11">
       <c r="A385" s="15">
         <v>41570</v>
       </c>
@@ -29164,7 +29176,7 @@
         <v>46.050815851660722</v>
       </c>
     </row>
-    <row r="386" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:11">
       <c r="A386" s="15">
         <v>41577</v>
       </c>
@@ -29200,7 +29212,7 @@
         <v>29.663869105622428</v>
       </c>
     </row>
-    <row r="387" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:11">
       <c r="A387" s="15">
         <v>41584</v>
       </c>
@@ -29251,7 +29263,7 @@
         <v>29.763192589775961</v>
       </c>
     </row>
-    <row r="388" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:11">
       <c r="A388" s="15">
         <v>41591</v>
       </c>
@@ -29287,7 +29299,7 @@
         <v>53.718056830358535</v>
       </c>
     </row>
-    <row r="389" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:11">
       <c r="A389" s="15">
         <v>41598</v>
       </c>
@@ -29323,7 +29335,7 @@
         <v>47.320660371123139</v>
       </c>
     </row>
-    <row r="390" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:11">
       <c r="A390" s="15">
         <v>41605</v>
       </c>
@@ -29359,7 +29371,7 @@
         <v>26.84883647436958</v>
       </c>
     </row>
-    <row r="391" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:11">
       <c r="A391" s="15">
         <v>41612</v>
       </c>
@@ -29395,7 +29407,7 @@
         <v>30.228012575603316</v>
       </c>
     </row>
-    <row r="392" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:11">
       <c r="A392" s="15">
         <v>41619</v>
       </c>
@@ -29431,7 +29443,7 @@
         <v>35.628299402813028</v>
       </c>
     </row>
-    <row r="393" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:11">
       <c r="A393" s="15">
         <v>41626</v>
       </c>
@@ -29467,7 +29479,7 @@
         <v>29.564716897124189</v>
       </c>
     </row>
-    <row r="394" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:11">
       <c r="A394" s="15">
         <v>41634</v>
       </c>
@@ -29503,7 +29515,7 @@
         <v>25.48504766173663</v>
       </c>
     </row>
-    <row r="395" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:11">
       <c r="A395" s="15">
         <v>41641</v>
       </c>
@@ -29539,7 +29551,7 @@
         <v>29.440463564644233</v>
       </c>
     </row>
-    <row r="396" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:11">
       <c r="A396" s="15">
         <v>41647</v>
       </c>
@@ -29575,7 +29587,7 @@
         <v>36.868005424758209</v>
       </c>
     </row>
-    <row r="397" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:11">
       <c r="A397" s="15">
         <v>41654</v>
       </c>
@@ -29611,7 +29623,7 @@
         <v>33.543405654015224</v>
       </c>
     </row>
-    <row r="398" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:11">
       <c r="A398" s="15">
         <v>41661</v>
       </c>
@@ -29647,7 +29659,7 @@
         <v>33.281205492789098</v>
       </c>
     </row>
-    <row r="399" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:11">
       <c r="A399" s="15">
         <v>41668</v>
       </c>
@@ -29683,7 +29695,7 @@
         <v>48.6755678567065</v>
       </c>
     </row>
-    <row r="400" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:11">
       <c r="A400" s="15">
         <v>41675</v>
       </c>
@@ -29719,7 +29731,7 @@
         <v>48.899855436252473</v>
       </c>
     </row>
-    <row r="401" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:11">
       <c r="A401" s="15">
         <v>41682</v>
       </c>
@@ -29755,7 +29767,7 @@
         <v>50.456539714887306</v>
       </c>
     </row>
-    <row r="402" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:11">
       <c r="A402" s="15">
         <v>41689</v>
       </c>
@@ -29791,7 +29803,7 @@
         <v>53.893528968558918</v>
       </c>
     </row>
-    <row r="403" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:11">
       <c r="A403" s="15">
         <v>41696</v>
       </c>
@@ -29827,7 +29839,7 @@
         <v>32.173253175865931</v>
       </c>
     </row>
-    <row r="404" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:11">
       <c r="A404" s="15">
         <v>41703</v>
       </c>
@@ -29863,7 +29875,7 @@
         <v>28.177917475995674</v>
       </c>
     </row>
-    <row r="405" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:11">
       <c r="A405" s="15">
         <v>41710</v>
       </c>
@@ -29899,7 +29911,7 @@
         <v>38.591960706244812</v>
       </c>
     </row>
-    <row r="406" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:11">
       <c r="A406" s="15">
         <v>41716</v>
       </c>
@@ -29935,7 +29947,7 @@
         <v>62.434033436115925</v>
       </c>
     </row>
-    <row r="407" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:11">
       <c r="A407" s="15">
         <v>41717</v>
       </c>
@@ -29971,7 +29983,7 @@
         <v>38.474239554033893</v>
       </c>
     </row>
-    <row r="408" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:11">
       <c r="A408" s="15">
         <v>41724</v>
       </c>
@@ -30007,7 +30019,7 @@
         <v>30.022064656219442</v>
       </c>
     </row>
-    <row r="409" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:11">
       <c r="A409" s="15">
         <v>41731</v>
       </c>
@@ -30043,7 +30055,7 @@
         <v>44.188138476313277</v>
       </c>
     </row>
-    <row r="410" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:11">
       <c r="A410" s="15">
         <v>41738</v>
       </c>
@@ -30079,7 +30091,7 @@
         <v>31.323363729632899</v>
       </c>
     </row>
-    <row r="411" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:11">
       <c r="A411" s="15">
         <v>41745</v>
       </c>
@@ -30115,7 +30127,7 @@
         <v>35.606324792337006</v>
       </c>
     </row>
-    <row r="412" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:11">
       <c r="A412" s="15">
         <v>41752</v>
       </c>
@@ -30151,7 +30163,7 @@
         <v>35.382781553838939</v>
       </c>
     </row>
-    <row r="413" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:11">
       <c r="A413" s="15">
         <v>41759</v>
       </c>
@@ -30187,7 +30199,7 @@
         <v>45.803062444786249</v>
       </c>
     </row>
-    <row r="414" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:11">
       <c r="A414" s="15">
         <v>41766</v>
       </c>
@@ -30223,7 +30235,7 @@
         <v>37.395218193640751</v>
       </c>
     </row>
-    <row r="415" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:11">
       <c r="A415" s="15">
         <v>41773</v>
       </c>
@@ -30259,7 +30271,7 @@
         <v>30.364171137854051</v>
       </c>
     </row>
-    <row r="416" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:11">
       <c r="A416" s="15">
         <v>41780</v>
       </c>
@@ -30295,7 +30307,7 @@
         <v>46.926276851752007</v>
       </c>
     </row>
-    <row r="417" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:11">
       <c r="A417" s="15">
         <v>41787</v>
       </c>
@@ -30331,7 +30343,7 @@
         <v>56.381294114615542</v>
       </c>
     </row>
-    <row r="418" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:11">
       <c r="A418" s="15">
         <v>41794</v>
       </c>
@@ -30367,7 +30379,7 @@
         <v>42.349237020811792</v>
       </c>
     </row>
-    <row r="419" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:11">
       <c r="A419" s="15">
         <v>41801</v>
       </c>
@@ -30403,7 +30415,7 @@
         <v>38.373204647880215</v>
       </c>
     </row>
-    <row r="420" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:11">
       <c r="A420" s="15">
         <v>41808</v>
       </c>
@@ -30439,7 +30451,7 @@
         <v>44.314119769408713</v>
       </c>
     </row>
-    <row r="421" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:11">
       <c r="A421" s="15">
         <v>41815</v>
       </c>
@@ -30475,7 +30487,7 @@
         <v>60.45119572753616</v>
       </c>
     </row>
-    <row r="422" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:11">
       <c r="A422" s="15">
         <v>41822</v>
       </c>
@@ -30511,7 +30523,7 @@
         <v>47.49836466704955</v>
       </c>
     </row>
-    <row r="423" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:11">
       <c r="A423" s="15">
         <v>41829</v>
       </c>
@@ -30547,7 +30559,7 @@
         <v>35.064608489041966</v>
       </c>
     </row>
-    <row r="424" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:11">
       <c r="A424" s="15">
         <v>41836</v>
       </c>
@@ -30583,7 +30595,7 @@
         <v>44.721213423875326</v>
       </c>
     </row>
-    <row r="425" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:11">
       <c r="A425" s="15">
         <v>41843</v>
       </c>
@@ -30619,7 +30631,7 @@
         <v>39.312318980389804</v>
       </c>
     </row>
-    <row r="426" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:11">
       <c r="A426" s="15">
         <v>41850</v>
       </c>
@@ -30655,7 +30667,7 @@
         <v>34.47072790576</v>
       </c>
     </row>
-    <row r="427" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:11">
       <c r="A427" s="15">
         <v>41857</v>
       </c>
@@ -30691,7 +30703,7 @@
         <v>51.803015068152312</v>
       </c>
     </row>
-    <row r="428" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:11">
       <c r="A428" s="15">
         <v>41864</v>
       </c>
@@ -30727,7 +30739,7 @@
         <v>45.922649241726944</v>
       </c>
     </row>
-    <row r="429" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:11">
       <c r="A429" s="15">
         <v>41871</v>
       </c>
@@ -30763,7 +30775,7 @@
         <v>62.557833587887913</v>
       </c>
     </row>
-    <row r="430" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:11">
       <c r="A430" s="15">
         <v>41878</v>
       </c>
@@ -30799,7 +30811,7 @@
         <v>47.65914443041865</v>
       </c>
     </row>
-    <row r="431" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:11">
       <c r="A431" s="15">
         <v>41885</v>
       </c>
@@ -30835,7 +30847,7 @@
         <v>59.213557190072954</v>
       </c>
     </row>
-    <row r="432" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:11">
       <c r="A432" s="15">
         <v>41892</v>
       </c>
@@ -30871,7 +30883,7 @@
         <v>57.333019762644675</v>
       </c>
     </row>
-    <row r="433" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:11">
       <c r="A433" s="15">
         <v>41899</v>
       </c>
@@ -30907,7 +30919,7 @@
         <v>49.133395431991111</v>
       </c>
     </row>
-    <row r="434" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:11">
       <c r="A434" s="15">
         <v>41906</v>
       </c>
@@ -30943,7 +30955,7 @@
         <v>55.537677707137746</v>
       </c>
     </row>
-    <row r="435" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:11">
       <c r="A435" s="15">
         <v>41913</v>
       </c>
@@ -30979,7 +30991,7 @@
         <v>66.806525599248758</v>
       </c>
     </row>
-    <row r="436" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:11">
       <c r="A436" s="15">
         <v>41920</v>
       </c>
@@ -31015,7 +31027,7 @@
         <v>66.570355280429666</v>
       </c>
     </row>
-    <row r="437" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:11">
       <c r="A437" s="15">
         <v>41927</v>
       </c>
@@ -31051,7 +31063,7 @@
         <v>67.686973863523022</v>
       </c>
     </row>
-    <row r="438" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:11">
       <c r="A438" s="15">
         <v>41934</v>
       </c>
@@ -31087,7 +31099,7 @@
         <v>62.311923006128566</v>
       </c>
     </row>
-    <row r="439" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:11">
       <c r="A439" s="15">
         <v>41941</v>
       </c>
@@ -31123,7 +31135,7 @@
         <v>65.532799765784759</v>
       </c>
     </row>
-    <row r="440" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:11">
       <c r="A440" s="15">
         <v>41948</v>
       </c>
@@ -31159,7 +31171,7 @@
         <v>62.905619401035253</v>
       </c>
     </row>
-    <row r="441" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:11">
       <c r="A441" s="15">
         <v>41955</v>
       </c>
@@ -31195,7 +31207,7 @@
         <v>59.753766943925129</v>
       </c>
     </row>
-    <row r="442" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:11">
       <c r="A442" s="15">
         <v>41962</v>
       </c>
@@ -31231,7 +31243,7 @@
         <v>54.685208883890532</v>
       </c>
     </row>
-    <row r="443" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:11">
       <c r="A443" s="15">
         <v>41968</v>
       </c>
@@ -31267,7 +31279,7 @@
         <v>64.443637389582548</v>
       </c>
     </row>
-    <row r="444" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:11">
       <c r="A444" s="15">
         <v>41976</v>
       </c>
@@ -31303,7 +31315,7 @@
         <v>53.372403786390393</v>
       </c>
     </row>
-    <row r="445" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:11">
       <c r="A445" s="15">
         <v>41983</v>
       </c>
@@ -31339,7 +31351,7 @@
         <v>52.550400098141971</v>
       </c>
     </row>
-    <row r="446" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:11">
       <c r="A446" s="15">
         <v>41990</v>
       </c>
@@ -31375,7 +31387,7 @@
         <v>61.82397380318033</v>
       </c>
     </row>
-    <row r="447" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:11">
       <c r="A447" s="15">
         <v>41997</v>
       </c>
@@ -31411,7 +31423,7 @@
         <v>32.707053916439136</v>
       </c>
     </row>
-    <row r="448" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:11">
       <c r="A448" s="15">
         <v>42004</v>
       </c>
@@ -31447,7 +31459,7 @@
         <v>43.310807829305034</v>
       </c>
     </row>
-    <row r="449" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:11">
       <c r="A449" s="15">
         <v>42011</v>
       </c>
@@ -31483,7 +31495,7 @@
         <v>73.520753699141281</v>
       </c>
     </row>
-    <row r="450" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:11">
       <c r="A450" s="15">
         <v>42018</v>
       </c>
@@ -31519,7 +31531,7 @@
         <v>53.380532408043727</v>
       </c>
     </row>
-    <row r="451" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:11">
       <c r="A451" s="15">
         <v>42025</v>
       </c>
@@ -31570,7 +31582,7 @@
         <v>52.550400098141971</v>
       </c>
     </row>
-    <row r="452" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:11">
       <c r="A452" s="15">
         <v>42032</v>
       </c>
@@ -31606,7 +31618,7 @@
         <v>39.19736690032088</v>
       </c>
     </row>
-    <row r="453" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:11">
       <c r="A453" s="15">
         <v>42039</v>
       </c>
@@ -31642,7 +31654,7 @@
         <v>44.064003122982612</v>
       </c>
     </row>
-    <row r="454" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:11">
       <c r="A454" s="15">
         <v>42046</v>
       </c>
@@ -31678,7 +31690,7 @@
         <v>37.007673607771878</v>
       </c>
     </row>
-    <row r="455" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:11">
       <c r="A455" s="15">
         <v>42053</v>
       </c>
@@ -31714,7 +31726,7 @@
         <v>42.561466476456637</v>
       </c>
     </row>
-    <row r="456" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:11">
       <c r="A456" s="15">
         <v>42060</v>
       </c>
@@ -31750,7 +31762,7 @@
         <v>45.402755221031484</v>
       </c>
     </row>
-    <row r="457" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:11">
       <c r="A457" s="15">
         <v>42067</v>
       </c>
@@ -31786,7 +31798,7 @@
         <v>48.211272729748821</v>
       </c>
     </row>
-    <row r="458" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:11">
       <c r="A458" s="15">
         <v>42074</v>
       </c>
@@ -31822,7 +31834,7 @@
         <v>67.383421717313624</v>
       </c>
     </row>
-    <row r="459" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:11">
       <c r="A459" s="15">
         <v>42088</v>
       </c>
@@ -31858,7 +31870,7 @@
         <v>30.956834906605707</v>
       </c>
     </row>
-    <row r="460" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:11">
       <c r="A460" s="15">
         <v>42095</v>
       </c>
@@ -31894,7 +31906,7 @@
         <v>54.500081021599833</v>
       </c>
     </row>
-    <row r="461" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:11">
       <c r="A461" s="15">
         <v>42102</v>
       </c>
@@ -31930,7 +31942,7 @@
         <v>28.291363992271719</v>
       </c>
     </row>
-    <row r="462" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:11">
       <c r="A462" s="15">
         <v>42109</v>
       </c>
@@ -31966,7 +31978,7 @@
         <v>40.543750857694739</v>
       </c>
     </row>
-    <row r="463" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:11">
       <c r="A463" s="15">
         <v>42116</v>
       </c>
@@ -32002,7 +32014,7 @@
         <v>59.571201699918042</v>
       </c>
     </row>
-    <row r="464" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:11">
       <c r="A464" s="15">
         <v>42123</v>
       </c>
@@ -32038,7 +32050,7 @@
         <v>34.27313982014654</v>
       </c>
     </row>
-    <row r="465" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="465" spans="1:11">
       <c r="A465" s="15">
         <v>42130</v>
       </c>
@@ -32074,7 +32086,7 @@
         <v>56.955691995283715</v>
       </c>
     </row>
-    <row r="466" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:11">
       <c r="A466" s="15">
         <v>42137</v>
       </c>
@@ -32110,7 +32122,7 @@
         <v>54.764046582566408</v>
       </c>
     </row>
-    <row r="467" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:11">
       <c r="A467" s="15">
         <v>42144</v>
       </c>
@@ -32146,7 +32158,7 @@
         <v>55.757136500127764</v>
       </c>
     </row>
-    <row r="468" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:11">
       <c r="A468" s="15">
         <v>42151</v>
       </c>
@@ -32182,7 +32194,7 @@
         <v>59.139689894729841</v>
       </c>
     </row>
-    <row r="469" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:11">
       <c r="A469" s="15">
         <v>42158</v>
       </c>
@@ -32218,7 +32230,7 @@
         <v>58.565690013670491</v>
       </c>
     </row>
-    <row r="470" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:11">
       <c r="A470" s="15">
         <v>42165</v>
       </c>
@@ -32254,7 +32266,7 @@
         <v>58.285726582262178</v>
       </c>
     </row>
-    <row r="471" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:11">
       <c r="A471" s="15">
         <v>42172</v>
       </c>
@@ -32290,7 +32302,7 @@
         <v>51.057335391353512</v>
       </c>
     </row>
-    <row r="472" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="472" spans="1:11">
       <c r="A472" s="15">
         <v>42179</v>
       </c>
@@ -32326,7 +32338,7 @@
         <v>58.045476963818579</v>
       </c>
     </row>
-    <row r="473" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:11">
       <c r="A473" s="15">
         <v>42186</v>
       </c>
@@ -32362,7 +32374,7 @@
         <v>60.134571875867529</v>
       </c>
     </row>
-    <row r="474" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:11">
       <c r="A474" s="15">
         <v>42193</v>
       </c>
@@ -32398,7 +32410,7 @@
         <v>64.152197101026005</v>
       </c>
     </row>
-    <row r="475" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="475" spans="1:11">
       <c r="A475" s="15">
         <v>42200</v>
       </c>
@@ -32434,7 +32446,7 @@
         <v>62.876249643492336</v>
       </c>
     </row>
-    <row r="476" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="476" spans="1:11">
       <c r="A476" s="15">
         <v>42207</v>
       </c>
@@ -32470,7 +32482,7 @@
         <v>69.115289526281927</v>
       </c>
     </row>
-    <row r="477" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:11">
       <c r="A477" s="15">
         <v>42214</v>
       </c>
@@ -32506,7 +32518,7 @@
         <v>65.005582381367375</v>
       </c>
     </row>
-    <row r="478" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:11">
       <c r="A478" s="15">
         <v>42221</v>
       </c>
@@ -32542,7 +32554,7 @@
         <v>63.076909141434115</v>
       </c>
     </row>
-    <row r="479" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:11">
       <c r="A479" s="15">
         <v>42228</v>
       </c>
@@ -32578,7 +32590,7 @@
         <v>62.189535700762221</v>
       </c>
     </row>
-    <row r="480" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:11">
       <c r="A480" s="15">
         <v>42235</v>
       </c>
@@ -32614,7 +32626,7 @@
         <v>56.905421187389813</v>
       </c>
     </row>
-    <row r="481" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:11">
       <c r="A481" s="15">
         <v>42242</v>
       </c>
@@ -32650,7 +32662,7 @@
         <v>54.437212556646394</v>
       </c>
     </row>
-    <row r="482" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:11">
       <c r="A482" s="15">
         <v>42249</v>
       </c>
@@ -32686,7 +32698,7 @@
         <v>45.740626444393065</v>
       </c>
     </row>
-    <row r="483" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:11">
       <c r="A483" s="15">
         <v>42256</v>
       </c>
@@ -32722,7 +32734,7 @@
         <v>39.805313843808364</v>
       </c>
     </row>
-    <row r="484" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:11">
       <c r="A484" s="15">
         <v>42263</v>
       </c>
@@ -32758,7 +32770,7 @@
         <v>43.806543446148218</v>
       </c>
     </row>
-    <row r="485" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:11">
       <c r="A485" s="15">
         <v>42270</v>
       </c>
@@ -32794,7 +32806,7 @@
         <v>51.716685867776327</v>
       </c>
     </row>
-    <row r="486" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="486" spans="1:11">
       <c r="A486" s="15">
         <v>42277</v>
       </c>
@@ -32830,7 +32842,7 @@
         <v>58.081158609585614</v>
       </c>
     </row>
-    <row r="487" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="487" spans="1:11">
       <c r="A487" s="15">
         <v>42284</v>
       </c>
@@ -32866,7 +32878,7 @@
         <v>56.825158228391729</v>
       </c>
     </row>
-    <row r="488" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="488" spans="1:11">
       <c r="A488" s="15">
         <v>42291</v>
       </c>
@@ -32902,7 +32914,7 @@
         <v>67.174925319764782</v>
       </c>
     </row>
-    <row r="489" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:11">
       <c r="A489" s="15">
         <v>42298</v>
       </c>
@@ -32938,7 +32950,7 @@
         <v>45.345586579315764</v>
       </c>
     </row>
-    <row r="490" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="490" spans="1:11">
       <c r="A490" s="15">
         <v>42305</v>
       </c>
@@ -32974,7 +32986,7 @@
         <v>57.374167645036572</v>
       </c>
     </row>
-    <row r="491" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:11">
       <c r="A491" s="15">
         <v>42312</v>
       </c>
@@ -33010,7 +33022,7 @@
         <v>51.179056631292994</v>
       </c>
     </row>
-    <row r="492" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="492" spans="1:11">
       <c r="A492" s="15">
         <v>42319</v>
       </c>
@@ -33046,7 +33058,7 @@
         <v>53.107945174576969</v>
       </c>
     </row>
-    <row r="493" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="493" spans="1:11">
       <c r="A493" s="15">
         <v>42326</v>
       </c>
@@ -33082,7 +33094,7 @@
         <v>58.422447069085209</v>
       </c>
     </row>
-    <row r="494" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:11">
       <c r="A494" s="15">
         <v>42333</v>
       </c>
@@ -33118,7 +33130,7 @@
         <v>34.740224585926597</v>
       </c>
     </row>
-    <row r="495" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:11">
       <c r="A495" s="15">
         <v>42340</v>
       </c>
@@ -33154,7 +33166,7 @@
         <v>53.475606892716783</v>
       </c>
     </row>
-    <row r="496" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="496" spans="1:11">
       <c r="A496" s="15">
         <v>42347</v>
       </c>
@@ -33190,7 +33202,7 @@
         <v>49.782638326185712</v>
       </c>
     </row>
-    <row r="497" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="497" spans="1:11">
       <c r="A497" s="15">
         <v>42354</v>
       </c>
@@ -33226,7 +33238,7 @@
         <v>64.682794789944978</v>
       </c>
     </row>
-    <row r="498" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="498" spans="1:11">
       <c r="A498" s="15">
         <v>42361</v>
       </c>
@@ -33262,7 +33274,7 @@
         <v>58.632036840912747</v>
       </c>
     </row>
-    <row r="499" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="499" spans="1:11">
       <c r="A499" s="15">
         <v>42368</v>
       </c>
@@ -33298,7 +33310,7 @@
         <v>60.952600023373698</v>
       </c>
     </row>
-    <row r="500" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="500" spans="1:11">
       <c r="A500" s="15">
         <v>42375</v>
       </c>
@@ -33334,7 +33346,7 @@
         <v>66.58828791661989</v>
       </c>
     </row>
-    <row r="501" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="501" spans="1:11">
       <c r="A501" s="15">
         <v>42382</v>
       </c>
@@ -33370,7 +33382,7 @@
         <v>64.934642249421515</v>
       </c>
     </row>
-    <row r="502" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="502" spans="1:11">
       <c r="A502" s="15">
         <v>42396</v>
       </c>
@@ -33406,7 +33418,7 @@
         <v>41.40576650661113</v>
       </c>
     </row>
-    <row r="503" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="503" spans="1:11">
       <c r="A503" s="15">
         <v>42403</v>
       </c>
@@ -33442,7 +33454,7 @@
         <v>31.776137400465753</v>
       </c>
     </row>
-    <row r="504" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="504" spans="1:11">
       <c r="A504" s="15">
         <v>42410</v>
       </c>
@@ -33478,7 +33490,7 @@
         <v>53.128851841152972</v>
       </c>
     </row>
-    <row r="505" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="505" spans="1:11">
       <c r="A505" s="15">
         <v>42417</v>
       </c>
@@ -33514,7 +33526,7 @@
         <v>38.552772794324362</v>
       </c>
     </row>
-    <row r="506" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="506" spans="1:11">
       <c r="A506" s="15">
         <v>42424</v>
       </c>
@@ -33550,7 +33562,7 @@
         <v>57.386093846065783</v>
       </c>
     </row>
-    <row r="507" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="507" spans="1:11">
       <c r="A507" s="15">
         <v>42431</v>
       </c>
@@ -33586,7 +33598,7 @@
         <v>56.216108002049303</v>
       </c>
     </row>
-    <row r="508" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="508" spans="1:11">
       <c r="A508" s="15">
         <v>42438</v>
       </c>
@@ -33622,7 +33634,7 @@
         <v>49.345050684492676</v>
       </c>
     </row>
-    <row r="509" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="509" spans="1:11">
       <c r="A509" s="15">
         <v>42445</v>
       </c>
@@ -33658,7 +33670,7 @@
         <v>47.469934929618582</v>
       </c>
     </row>
-    <row r="510" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="510" spans="1:11">
       <c r="A510" s="15">
         <v>42452</v>
       </c>
@@ -33694,7 +33706,7 @@
         <v>55.942502690409157</v>
       </c>
     </row>
-    <row r="511" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="511" spans="1:11">
       <c r="A511" s="15">
         <v>42459</v>
       </c>
@@ -33730,7 +33742,7 @@
         <v>51.171281684204004</v>
       </c>
     </row>
-    <row r="512" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="512" spans="1:11">
       <c r="A512" s="15">
         <v>42466</v>
       </c>
@@ -33766,7 +33778,7 @@
         <v>44.987298684587493</v>
       </c>
     </row>
-    <row r="513" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="513" spans="1:11">
       <c r="A513" s="15">
         <v>42473</v>
       </c>
@@ -33802,7 +33814,7 @@
         <v>52.267754767722032</v>
       </c>
     </row>
-    <row r="514" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="514" spans="1:11">
       <c r="A514" s="15">
         <v>42480</v>
       </c>
@@ -33838,7 +33850,7 @@
         <v>59.274689783916969</v>
       </c>
     </row>
-    <row r="515" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="515" spans="1:11">
       <c r="A515" s="15">
         <v>42487</v>
       </c>
@@ -33889,7 +33901,7 @@
         <v>56.059043268503345</v>
       </c>
     </row>
-    <row r="516" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="516" spans="1:11">
       <c r="A516" s="15">
         <v>42494</v>
       </c>
@@ -33925,7 +33937,7 @@
         <v>63.557616832598796</v>
       </c>
     </row>
-    <row r="517" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="517" spans="1:11">
       <c r="A517" s="15">
         <v>42501</v>
       </c>
@@ -33961,7 +33973,7 @@
         <v>60.325228184861054</v>
       </c>
     </row>
-    <row r="518" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="518" spans="1:11">
       <c r="A518" s="15">
         <v>42508</v>
       </c>
@@ -33997,7 +34009,7 @@
         <v>66.025148795269672</v>
       </c>
     </row>
-    <row r="519" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="519" spans="1:11">
       <c r="A519" s="15">
         <v>42515</v>
       </c>
@@ -34033,7 +34045,7 @@
         <v>65.838860527469308</v>
       </c>
     </row>
-    <row r="520" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="520" spans="1:11">
       <c r="A520" s="15">
         <v>42522</v>
       </c>
@@ -34069,7 +34081,7 @@
         <v>58.204477883361697</v>
       </c>
     </row>
-    <row r="521" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="521" spans="1:11">
       <c r="A521" s="15">
         <v>42529</v>
       </c>
@@ -34105,7 +34117,7 @@
         <v>67.614110056909553</v>
       </c>
     </row>
-    <row r="522" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="522" spans="1:11">
       <c r="A522" s="15">
         <v>42536</v>
       </c>
@@ -34141,7 +34153,7 @@
         <v>74.11356391861203</v>
       </c>
     </row>
-    <row r="523" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="523" spans="1:11">
       <c r="A523" s="15">
         <v>42543</v>
       </c>
@@ -34177,7 +34189,7 @@
         <v>73.151472857827756</v>
       </c>
     </row>
-    <row r="524" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="524" spans="1:11">
       <c r="A524" s="15">
         <v>42550</v>
       </c>
@@ -34213,7 +34225,7 @@
         <v>61.145192933839347</v>
       </c>
     </row>
-    <row r="525" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="525" spans="1:11">
       <c r="A525" s="15">
         <v>42557</v>
       </c>
@@ -34249,7 +34261,7 @@
         <v>59.461294600399974</v>
       </c>
     </row>
-    <row r="526" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="526" spans="1:11">
       <c r="A526" s="15">
         <v>42564</v>
       </c>
@@ -34285,7 +34297,7 @@
         <v>55.474316952158986</v>
       </c>
     </row>
-    <row r="527" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="527" spans="1:11">
       <c r="A527" s="15">
         <v>42571</v>
       </c>
@@ -34321,7 +34333,7 @@
         <v>47.642829505911699</v>
       </c>
     </row>
-    <row r="528" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="528" spans="1:11">
       <c r="A528" s="15">
         <v>42578</v>
       </c>
@@ -34357,7 +34369,7 @@
         <v>38.757015074458316</v>
       </c>
     </row>
-    <row r="529" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="529" spans="1:11">
       <c r="A529" s="15">
         <v>42585</v>
       </c>
@@ -34393,7 +34405,7 @@
         <v>40.898792194128127</v>
       </c>
     </row>
-    <row r="530" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="530" spans="1:11">
       <c r="A530" s="15">
         <v>42592</v>
       </c>
@@ -34429,7 +34441,7 @@
         <v>44.684911157119551</v>
       </c>
     </row>
-    <row r="531" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="531" spans="1:11">
       <c r="A531" s="15">
         <v>42599</v>
       </c>
@@ -34465,7 +34477,7 @@
         <v>38.351540526685874</v>
       </c>
     </row>
-    <row r="532" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="532" spans="1:11">
       <c r="A532" s="15">
         <v>42606</v>
       </c>
@@ -34501,7 +34513,7 @@
         <v>52.845347659285657</v>
       </c>
     </row>
-    <row r="533" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="533" spans="1:11">
       <c r="A533" s="15">
         <v>42613</v>
       </c>
@@ -34537,7 +34549,7 @@
         <v>50.592178955136646</v>
       </c>
     </row>
-    <row r="534" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="534" spans="1:11">
       <c r="A534" s="15">
         <v>42620</v>
       </c>
@@ -34573,7 +34585,7 @@
         <v>45.8727017663767</v>
       </c>
     </row>
-    <row r="535" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="535" spans="1:11">
       <c r="A535" s="15">
         <v>42627</v>
       </c>
@@ -34609,7 +34621,7 @@
         <v>74.814030546861105</v>
       </c>
     </row>
-    <row r="536" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="536" spans="1:11">
       <c r="A536" s="15">
         <v>42634</v>
       </c>
@@ -34645,7 +34657,7 @@
         <v>53.632347230101267</v>
       </c>
     </row>
-    <row r="537" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="537" spans="1:11">
       <c r="A537" s="15">
         <v>42641</v>
       </c>
@@ -34681,7 +34693,7 @@
         <v>48.896571681685643</v>
       </c>
     </row>
-    <row r="538" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="538" spans="1:11">
       <c r="A538" s="15">
         <v>42648</v>
       </c>
@@ -34717,7 +34729,7 @@
         <v>61.205113840328835</v>
       </c>
     </row>
-    <row r="539" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="539" spans="1:11">
       <c r="A539" s="15">
         <v>42655</v>
       </c>
@@ -34753,7 +34765,7 @@
         <v>57.785327901705259</v>
       </c>
     </row>
-    <row r="540" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="540" spans="1:11">
       <c r="A540" s="15">
         <v>42662</v>
       </c>
@@ -34789,7 +34801,7 @@
         <v>79.940100561197539</v>
       </c>
     </row>
-    <row r="541" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="541" spans="1:11">
       <c r="A541" s="15">
         <v>42669</v>
       </c>
@@ -34825,7 +34837,7 @@
         <v>73.199803298495794</v>
       </c>
     </row>
-    <row r="542" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="542" spans="1:11">
       <c r="A542" s="15">
         <v>42676</v>
       </c>
@@ -34861,7 +34873,7 @@
         <v>81.972971493996454</v>
       </c>
     </row>
-    <row r="543" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="543" spans="1:11">
       <c r="A543" s="15">
         <v>42683</v>
       </c>
@@ -34897,7 +34909,7 @@
         <v>70.252181451028676</v>
       </c>
     </row>
-    <row r="544" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="544" spans="1:11">
       <c r="A544" s="15">
         <v>42689</v>
       </c>
@@ -34933,7 +34945,7 @@
         <v>45.034554333138182</v>
       </c>
     </row>
-    <row r="545" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="545" spans="1:11">
       <c r="A545" s="15">
         <v>42697</v>
       </c>
@@ -34969,7 +34981,7 @@
         <v>31.902622834964525</v>
       </c>
     </row>
-    <row r="546" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="546" spans="1:11">
       <c r="A546" s="15">
         <v>42704</v>
       </c>
@@ -35005,7 +35017,7 @@
         <v>33.812107442362681</v>
       </c>
     </row>
-    <row r="547" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="547" spans="1:11">
       <c r="A547" s="15">
         <v>42711</v>
       </c>
@@ -35041,7 +35053,7 @@
         <v>44.571790079241985</v>
       </c>
     </row>
-    <row r="548" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="548" spans="1:11">
       <c r="A548" s="15">
         <v>42718</v>
       </c>
@@ -35077,7 +35089,7 @@
         <v>51.225600837105361</v>
       </c>
     </row>
-    <row r="549" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="549" spans="1:11">
       <c r="A549" s="15">
         <v>42725</v>
       </c>
@@ -35113,7 +35125,7 @@
         <v>31.324298121335335</v>
       </c>
     </row>
-    <row r="550" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="550" spans="1:11">
       <c r="A550" s="15">
         <v>42732</v>
       </c>
@@ -35149,7 +35161,7 @@
         <v>40.560500686953205</v>
       </c>
     </row>
-    <row r="551" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="551" spans="1:11">
       <c r="A551" s="15">
         <v>42739</v>
       </c>
@@ -35185,7 +35197,7 @@
         <v>41.368869961849803</v>
       </c>
     </row>
-    <row r="552" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="552" spans="1:11">
       <c r="A552" s="15">
         <v>42746</v>
       </c>
@@ -35221,7 +35233,7 @@
         <v>36.188090354038536</v>
       </c>
     </row>
-    <row r="553" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="553" spans="1:11">
       <c r="A553" s="15">
         <v>42753</v>
       </c>
@@ -35257,7 +35269,7 @@
         <v>37.743249902447104</v>
       </c>
     </row>
-    <row r="554" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="554" spans="1:11">
       <c r="A554" s="15">
         <v>42760</v>
       </c>
@@ -35293,7 +35305,7 @@
         <v>38.125600177425255</v>
       </c>
     </row>
-    <row r="555" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="555" spans="1:11">
       <c r="A555" s="15">
         <v>42767</v>
       </c>
@@ -35329,7 +35341,7 @@
         <v>35.21374453775752</v>
       </c>
     </row>
-    <row r="556" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="556" spans="1:11">
       <c r="A556" s="15">
         <v>42774</v>
       </c>
@@ -35365,7 +35377,7 @@
         <v>37.200813418944776</v>
       </c>
     </row>
-    <row r="557" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="557" spans="1:11">
       <c r="A557" s="15">
         <v>42781</v>
       </c>
@@ -35401,7 +35413,7 @@
         <v>46.401461865606194</v>
       </c>
     </row>
-    <row r="558" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="558" spans="1:11">
       <c r="A558" s="15">
         <v>42788</v>
       </c>
@@ -35437,7 +35449,7 @@
         <v>47.306097125086168</v>
       </c>
     </row>
-    <row r="559" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="559" spans="1:11">
       <c r="A559" s="15">
         <v>42795</v>
       </c>
@@ -35473,7 +35485,7 @@
         <v>40.981014136054526</v>
       </c>
     </row>
-    <row r="560" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="560" spans="1:11">
       <c r="A560" s="15">
         <v>42802</v>
       </c>
@@ -35509,7 +35521,7 @@
         <v>33.994932520079296</v>
       </c>
     </row>
-    <row r="561" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="561" spans="1:11">
       <c r="A561" s="15">
         <v>42809</v>
       </c>
@@ -35545,7 +35557,7 @@
         <v>44.968363852363964</v>
       </c>
     </row>
-    <row r="562" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="562" spans="1:11">
       <c r="A562" s="15">
         <v>42816</v>
       </c>
@@ -35581,7 +35593,7 @@
         <v>49.659201917259722</v>
       </c>
     </row>
-    <row r="563" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="563" spans="1:11">
       <c r="A563" s="15">
         <v>42823</v>
       </c>
@@ -35617,7 +35629,7 @@
         <v>64.362780454268531</v>
       </c>
     </row>
-    <row r="564" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="564" spans="1:11">
       <c r="A564" s="15">
         <v>42830</v>
       </c>
@@ -35653,7 +35665,7 @@
         <v>64.776799001384475</v>
       </c>
     </row>
-    <row r="565" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="565" spans="1:11">
       <c r="A565" s="15">
         <v>42837</v>
       </c>
@@ -35689,7 +35701,7 @@
         <v>65.166932244503599</v>
       </c>
     </row>
-    <row r="566" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="566" spans="1:11">
       <c r="A566" s="15">
         <v>42844</v>
       </c>
@@ -35725,7 +35737,7 @@
         <v>59.958870200350503</v>
       </c>
     </row>
-    <row r="567" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="567" spans="1:11">
       <c r="A567" s="15">
         <v>42851</v>
       </c>
@@ -35761,7 +35773,7 @@
         <v>59.381621852968017</v>
       </c>
     </row>
-    <row r="568" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="568" spans="1:11">
       <c r="A568" s="15">
         <v>42858</v>
       </c>
@@ -35797,7 +35809,7 @@
         <v>43.61543763393874</v>
       </c>
     </row>
-    <row r="569" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="569" spans="1:11">
       <c r="A569" s="15">
         <v>42865</v>
       </c>
@@ -35833,7 +35845,7 @@
         <v>45.396879132363082</v>
       </c>
     </row>
-    <row r="570" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="570" spans="1:11">
       <c r="A570" s="15">
         <v>42872</v>
       </c>
@@ -35869,7 +35881,7 @@
         <v>57.001842496633159</v>
       </c>
     </row>
-    <row r="571" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="571" spans="1:11">
       <c r="A571" s="15">
         <v>42879</v>
       </c>
@@ -35905,7 +35917,7 @@
         <v>43.069217656771137</v>
       </c>
     </row>
-    <row r="572" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="572" spans="1:11">
       <c r="A572" s="15">
         <v>42886</v>
       </c>
@@ -35941,7 +35953,7 @@
         <v>48.392374712148168</v>
       </c>
     </row>
-    <row r="573" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="573" spans="1:11">
       <c r="A573" s="15">
         <v>42893</v>
       </c>
@@ -35977,7 +35989,7 @@
         <v>40.948483493075209</v>
       </c>
     </row>
-    <row r="574" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="574" spans="1:11">
       <c r="A574" s="15">
         <v>42900</v>
       </c>
@@ -36013,7 +36025,7 @@
         <v>37.402091766235387</v>
       </c>
     </row>
-    <row r="575" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="575" spans="1:11">
       <c r="A575" s="15">
         <v>42907</v>
       </c>
@@ -36049,7 +36061,7 @@
         <v>46.287563991280784</v>
       </c>
     </row>
-    <row r="576" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="576" spans="1:11">
       <c r="A576" s="15">
         <v>42914</v>
       </c>
@@ -36085,7 +36097,7 @@
         <v>51.63023920146022</v>
       </c>
     </row>
-    <row r="577" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="577" spans="1:11">
       <c r="A577" s="15">
         <v>42921</v>
       </c>
@@ -36121,7 +36133,7 @@
         <v>38.938715947404972</v>
       </c>
     </row>
-    <row r="578" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="578" spans="1:11">
       <c r="A578" s="15">
         <v>42928</v>
       </c>
@@ -36157,7 +36169,7 @@
         <v>32.992166958557021</v>
       </c>
     </row>
-    <row r="579" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="579" spans="1:11">
       <c r="A579" s="15">
         <v>42935</v>
       </c>
@@ -36208,7 +36220,7 @@
         <v>41.819650581896475</v>
       </c>
     </row>
-    <row r="580" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="580" spans="1:11">
       <c r="A580" s="15">
         <v>42942</v>
       </c>
@@ -36244,7 +36256,7 @@
         <v>50.264603848036046</v>
       </c>
     </row>
-    <row r="581" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="581" spans="1:11">
       <c r="A581" s="15">
         <v>42949</v>
       </c>
@@ -36280,7 +36292,7 @@
         <v>42.982310991380189</v>
       </c>
     </row>
-    <row r="582" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="582" spans="1:11">
       <c r="A582" s="15">
         <v>42956</v>
       </c>
@@ -36316,7 +36328,7 @@
         <v>42.602862162618685</v>
       </c>
     </row>
-    <row r="583" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="583" spans="1:11">
       <c r="A583" s="15">
         <v>42963</v>
       </c>
@@ -36352,7 +36364,7 @@
         <v>35.515471002867969</v>
       </c>
     </row>
-    <row r="584" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="584" spans="1:11">
       <c r="A584" s="15">
         <v>42970</v>
       </c>
@@ -36388,7 +36400,7 @@
         <v>41.20422836194178</v>
       </c>
     </row>
-    <row r="585" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="585" spans="1:11">
       <c r="A585" s="15">
         <v>42977</v>
       </c>
@@ -36424,7 +36436,7 @@
         <v>46.305875728509086</v>
       </c>
     </row>
-    <row r="586" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="586" spans="1:11">
       <c r="A586" s="15">
         <v>42984</v>
       </c>
@@ -36460,7 +36472,7 @@
         <v>52.28157999497369</v>
       </c>
     </row>
-    <row r="587" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="587" spans="1:11">
       <c r="A587" s="15">
         <v>42991</v>
       </c>
@@ -36496,7 +36508,7 @@
         <v>45.246656707228858</v>
       </c>
     </row>
-    <row r="588" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="588" spans="1:11">
       <c r="A588" s="15">
         <v>42998</v>
       </c>
@@ -36532,7 +36544,7 @@
         <v>42.836271786367632</v>
       </c>
     </row>
-    <row r="589" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="589" spans="1:11">
       <c r="A589" s="15">
         <v>43005</v>
       </c>
@@ -36568,7 +36580,7 @@
         <v>25.850229689501795</v>
       </c>
     </row>
-    <row r="590" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="590" spans="1:11">
       <c r="A590" s="15">
         <v>43012</v>
       </c>
@@ -36604,7 +36616,7 @@
         <v>29.219171788399478</v>
       </c>
     </row>
-    <row r="591" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="591" spans="1:11">
       <c r="A591" s="15">
         <v>43019</v>
       </c>
@@ -36640,7 +36652,7 @@
         <v>47.697764295090394</v>
       </c>
     </row>
-    <row r="592" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="592" spans="1:11">
       <c r="A592" s="15">
         <v>43026</v>
       </c>
@@ -36676,7 +36688,7 @@
         <v>38.422382980352594</v>
       </c>
     </row>
-    <row r="593" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="593" spans="1:11">
       <c r="A593" s="15">
         <v>43033</v>
       </c>
@@ -36712,7 +36724,7 @@
         <v>64.258296622360419</v>
       </c>
     </row>
-    <row r="594" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="594" spans="1:11">
       <c r="A594" s="15">
         <v>43040</v>
       </c>
@@ -36748,7 +36760,7 @@
         <v>57.905260906954553</v>
       </c>
     </row>
-    <row r="595" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="595" spans="1:11">
       <c r="A595" s="15">
         <v>43047</v>
       </c>
@@ -36784,7 +36796,7 @@
         <v>34.736286502733705</v>
       </c>
     </row>
-    <row r="596" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="596" spans="1:11">
       <c r="A596" s="15">
         <v>43054</v>
       </c>
@@ -36820,7 +36832,7 @@
         <v>68.592291112048443</v>
       </c>
     </row>
-    <row r="597" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="597" spans="1:11">
       <c r="A597" s="15">
         <v>43061</v>
       </c>
@@ -36856,7 +36868,7 @@
         <v>27.3096898737011</v>
       </c>
     </row>
-    <row r="598" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="598" spans="1:11">
       <c r="A598" s="15">
         <v>43068</v>
       </c>
@@ -36892,7 +36904,7 @@
         <v>47.380261477684584</v>
       </c>
     </row>
-    <row r="599" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="599" spans="1:11">
       <c r="A599" s="15">
         <v>43075</v>
       </c>
@@ -36928,7 +36940,7 @@
         <v>48.440037392978304</v>
       </c>
     </row>
-    <row r="600" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="600" spans="1:11">
       <c r="A600" s="15">
         <v>43082</v>
       </c>
@@ -36964,7 +36976,7 @@
         <v>44.562343622567724</v>
       </c>
     </row>
-    <row r="601" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="601" spans="1:11">
       <c r="A601" s="15">
         <v>43089</v>
       </c>
@@ -37000,7 +37012,7 @@
         <v>36.623281382599032</v>
       </c>
     </row>
-    <row r="602" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="602" spans="1:11">
       <c r="A602" s="15">
         <v>43096</v>
       </c>
@@ -37036,7 +37048,7 @@
         <v>34.643577434597006</v>
       </c>
     </row>
-    <row r="603" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="603" spans="1:11">
       <c r="A603" s="15">
         <v>43103</v>
       </c>
@@ -37072,7 +37084,7 @@
         <v>25.360655270394762</v>
       </c>
     </row>
-    <row r="604" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="604" spans="1:11">
       <c r="A604" s="15">
         <v>43110</v>
       </c>
@@ -37108,7 +37120,7 @@
         <v>25.396638870684793</v>
       </c>
     </row>
-    <row r="605" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="605" spans="1:11">
       <c r="A605" s="15">
         <v>43117</v>
       </c>
@@ -37144,7 +37156,7 @@
         <v>27.71</v>
       </c>
     </row>
-    <row r="606" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="606" spans="1:11">
       <c r="A606" s="15">
         <v>43124</v>
       </c>
@@ -37180,7 +37192,7 @@
         <v>29.33</v>
       </c>
     </row>
-    <row r="607" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="607" spans="1:11">
       <c r="A607" s="15">
         <v>43131</v>
       </c>
@@ -37216,7 +37228,7 @@
         <v>53.07</v>
       </c>
     </row>
-    <row r="608" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="608" spans="1:11">
       <c r="A608" s="15">
         <v>43138</v>
       </c>
@@ -37252,7 +37264,7 @@
         <v>44.02</v>
       </c>
     </row>
-    <row r="609" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="609" spans="1:11">
       <c r="A609" s="15">
         <v>43145</v>
       </c>
@@ -37288,7 +37300,7 @@
         <v>55.52</v>
       </c>
     </row>
-    <row r="610" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="610" spans="1:11">
       <c r="A610" s="15">
         <v>43152</v>
       </c>
@@ -37324,7 +37336,7 @@
         <v>50.17</v>
       </c>
     </row>
-    <row r="611" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="611" spans="1:11">
       <c r="A611" s="15">
         <v>43159</v>
       </c>
@@ -37360,7 +37372,7 @@
         <v>34.54</v>
       </c>
     </row>
-    <row r="612" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="612" spans="1:11">
       <c r="A612" s="15">
         <v>43166</v>
       </c>
@@ -37396,7 +37408,7 @@
         <v>53.35</v>
       </c>
     </row>
-    <row r="613" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="613" spans="1:11">
       <c r="A613" s="15">
         <v>43173</v>
       </c>
@@ -37432,7 +37444,7 @@
         <v>34.69</v>
       </c>
     </row>
-    <row r="614" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="614" spans="1:11">
       <c r="A614" s="15">
         <v>43180</v>
       </c>
@@ -37468,7 +37480,7 @@
         <v>50.12</v>
       </c>
     </row>
-    <row r="615" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="615" spans="1:11">
       <c r="A615" s="15">
         <v>43187</v>
       </c>
@@ -37504,7 +37516,7 @@
         <v>66.569999999999993</v>
       </c>
     </row>
-    <row r="616" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="616" spans="1:11">
       <c r="A616" s="15">
         <v>43194</v>
       </c>
@@ -37540,7 +37552,7 @@
         <v>58.83</v>
       </c>
     </row>
-    <row r="617" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="617" spans="1:11">
       <c r="A617" s="15">
         <v>43201</v>
       </c>
@@ -37576,7 +37588,7 @@
         <v>48.61</v>
       </c>
     </row>
-    <row r="618" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="618" spans="1:11">
       <c r="A618" s="15">
         <v>43208</v>
       </c>
@@ -37612,7 +37624,7 @@
         <v>38.979999999999997</v>
       </c>
     </row>
-    <row r="619" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="619" spans="1:11">
       <c r="A619" s="15">
         <v>43215</v>
       </c>
@@ -37648,7 +37660,7 @@
         <v>63.14</v>
       </c>
     </row>
-    <row r="620" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="620" spans="1:11">
       <c r="A620" s="15">
         <v>43222</v>
       </c>
@@ -37684,7 +37696,7 @@
         <v>68.150000000000006</v>
       </c>
     </row>
-    <row r="621" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="621" spans="1:11">
       <c r="A621" s="15">
         <v>43229</v>
       </c>
@@ -37720,7 +37732,7 @@
         <v>39.549999999999997</v>
       </c>
     </row>
-    <row r="622" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="622" spans="1:11">
       <c r="A622" s="15">
         <v>43236</v>
       </c>
@@ -37756,7 +37768,7 @@
         <v>54.33</v>
       </c>
     </row>
-    <row r="623" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="623" spans="1:11">
       <c r="A623" s="15">
         <v>43243</v>
       </c>
@@ -37792,7 +37804,7 @@
         <v>53.99</v>
       </c>
     </row>
-    <row r="624" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="624" spans="1:11">
       <c r="A624" s="15">
         <v>43250</v>
       </c>
@@ -37828,7 +37840,7 @@
         <v>39.76</v>
       </c>
     </row>
-    <row r="625" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="625" spans="1:11">
       <c r="A625" s="15">
         <v>43257</v>
       </c>
@@ -37864,7 +37876,7 @@
         <v>34.51</v>
       </c>
     </row>
-    <row r="626" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="626" spans="1:11">
       <c r="A626" s="15">
         <v>43264</v>
       </c>
@@ -37900,7 +37912,7 @@
         <v>41.63</v>
       </c>
     </row>
-    <row r="627" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="627" spans="1:11">
       <c r="A627" s="15">
         <v>43271</v>
       </c>
@@ -37936,7 +37948,7 @@
         <v>34.5</v>
       </c>
     </row>
-    <row r="628" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="628" spans="1:11">
       <c r="A628" s="15">
         <v>43278</v>
       </c>
@@ -37972,7 +37984,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="629" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="629" spans="1:11">
       <c r="A629" s="15">
         <v>43285</v>
       </c>
@@ -38008,7 +38020,7 @@
         <v>46.74</v>
       </c>
     </row>
-    <row r="630" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="630" spans="1:11">
       <c r="A630" s="15">
         <v>43292</v>
       </c>
@@ -38044,7 +38056,7 @@
         <v>38.47</v>
       </c>
     </row>
-    <row r="631" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="631" spans="1:11">
       <c r="A631" s="15">
         <v>43299</v>
       </c>
@@ -38080,7 +38092,7 @@
         <v>38.82</v>
       </c>
     </row>
-    <row r="632" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="632" spans="1:11">
       <c r="A632" s="15">
         <v>43306</v>
       </c>
@@ -38116,7 +38128,7 @@
         <v>39.159999999999997</v>
       </c>
     </row>
-    <row r="633" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="633" spans="1:11">
       <c r="A633" s="15">
         <v>43313</v>
       </c>
@@ -38152,7 +38164,7 @@
         <v>40.450000000000003</v>
       </c>
     </row>
-    <row r="634" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="634" spans="1:11">
       <c r="A634" s="15">
         <v>43320</v>
       </c>
@@ -38188,7 +38200,7 @@
         <v>32.78</v>
       </c>
     </row>
-    <row r="635" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="635" spans="1:11">
       <c r="A635" s="15">
         <v>43327</v>
       </c>
@@ -38224,7 +38236,7 @@
         <v>38.94</v>
       </c>
     </row>
-    <row r="636" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="636" spans="1:11">
       <c r="A636" s="15">
         <v>43334</v>
       </c>
@@ -38260,7 +38272,7 @@
         <v>31.73</v>
       </c>
     </row>
-    <row r="637" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="637" spans="1:11">
       <c r="A637" s="15">
         <v>43341</v>
       </c>
@@ -38296,7 +38308,7 @@
         <v>38.53</v>
       </c>
     </row>
-    <row r="638" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="638" spans="1:11">
       <c r="A638" s="15">
         <v>43348</v>
       </c>
@@ -38332,7 +38344,7 @@
         <v>43.57</v>
       </c>
     </row>
-    <row r="639" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="639" spans="1:11">
       <c r="A639" s="15">
         <v>43355</v>
       </c>
@@ -38368,7 +38380,7 @@
         <v>37.619999999999997</v>
       </c>
     </row>
-    <row r="640" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="640" spans="1:11">
       <c r="A640" s="15">
         <v>43362</v>
       </c>
@@ -38404,7 +38416,7 @@
         <v>38.020000000000003</v>
       </c>
     </row>
-    <row r="641" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="641" spans="1:11">
       <c r="A641" s="15">
         <v>43369</v>
       </c>
@@ -38440,7 +38452,7 @@
         <v>44.58</v>
       </c>
     </row>
-    <row r="642" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="642" spans="1:11">
       <c r="A642" s="15">
         <v>43376</v>
       </c>
@@ -38476,7 +38488,7 @@
         <v>43.37</v>
       </c>
     </row>
-    <row r="643" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="643" spans="1:11">
       <c r="A643" s="15">
         <v>43383</v>
       </c>
@@ -38527,7 +38539,7 @@
         <v>64.94</v>
       </c>
     </row>
-    <row r="644" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="644" spans="1:11">
       <c r="A644" s="15">
         <v>43391</v>
       </c>
@@ -38563,7 +38575,7 @@
         <v>45.19</v>
       </c>
     </row>
-    <row r="645" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="645" spans="1:11">
       <c r="A645" s="15">
         <v>43397</v>
       </c>
@@ -38599,7 +38611,7 @@
         <v>72.86</v>
       </c>
     </row>
-    <row r="646" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="646" spans="1:11">
       <c r="A646" s="15">
         <v>43404</v>
       </c>
@@ -38635,7 +38647,7 @@
         <v>38.96</v>
       </c>
     </row>
-    <row r="647" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="647" spans="1:11">
       <c r="A647" s="15">
         <v>43411</v>
       </c>
@@ -38671,7 +38683,7 @@
         <v>33.590000000000003</v>
       </c>
     </row>
-    <row r="648" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="648" spans="1:11">
       <c r="A648" s="15">
         <v>43418</v>
       </c>
@@ -38707,7 +38719,7 @@
         <v>48.37</v>
       </c>
     </row>
-    <row r="649" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="649" spans="1:11">
       <c r="A649" s="15">
         <v>43425</v>
       </c>
@@ -38743,7 +38755,7 @@
         <v>73.89</v>
       </c>
     </row>
-    <row r="650" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="650" spans="1:11">
       <c r="A650" s="15">
         <v>43432</v>
       </c>
@@ -38779,7 +38791,7 @@
         <v>39.99</v>
       </c>
     </row>
-    <row r="651" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="651" spans="1:11">
       <c r="A651" s="15">
         <v>43439</v>
       </c>
@@ -38815,7 +38827,7 @@
         <v>61.26</v>
       </c>
     </row>
-    <row r="652" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="652" spans="1:11">
       <c r="A652" s="15">
         <v>43446</v>
       </c>
@@ -38851,7 +38863,7 @@
         <v>50.14</v>
       </c>
     </row>
-    <row r="653" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="653" spans="1:11">
       <c r="A653" s="15">
         <v>43453</v>
       </c>
@@ -38887,7 +38899,7 @@
         <v>63.86</v>
       </c>
     </row>
-    <row r="654" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="654" spans="1:11">
       <c r="A654" s="15">
         <v>43460</v>
       </c>
@@ -38923,7 +38935,7 @@
         <v>50.7</v>
       </c>
     </row>
-    <row r="655" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="655" spans="1:11">
       <c r="A655" s="15">
         <v>43467</v>
       </c>
@@ -38959,7 +38971,7 @@
         <v>53.3</v>
       </c>
     </row>
-    <row r="656" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="656" spans="1:11">
       <c r="A656" s="15">
         <v>43474</v>
       </c>
@@ -38995,7 +39007,7 @@
         <v>60.63</v>
       </c>
     </row>
-    <row r="657" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="657" spans="1:11">
       <c r="A657" s="15">
         <v>43481</v>
       </c>
@@ -39031,7 +39043,7 @@
         <v>51.01</v>
       </c>
     </row>
-    <row r="658" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="658" spans="1:11">
       <c r="A658" s="15">
         <v>43488</v>
       </c>
@@ -39067,7 +39079,7 @@
         <v>45.67</v>
       </c>
     </row>
-    <row r="659" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="659" spans="1:11">
       <c r="A659" s="15">
         <v>43495</v>
       </c>
@@ -39103,7 +39115,7 @@
         <v>46.03</v>
       </c>
     </row>
-    <row r="660" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="660" spans="1:11">
       <c r="A660" s="15">
         <v>43502</v>
       </c>
@@ -39139,7 +39151,7 @@
         <v>42.17</v>
       </c>
     </row>
-    <row r="661" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="661" spans="1:11">
       <c r="A661" s="15">
         <v>43509</v>
       </c>
@@ -39175,7 +39187,7 @@
         <v>40.51</v>
       </c>
     </row>
-    <row r="662" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="662" spans="1:11">
       <c r="A662" s="15">
         <v>43516</v>
       </c>
@@ -39211,7 +39223,7 @@
         <v>46.58</v>
       </c>
     </row>
-    <row r="663" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="663" spans="1:11">
       <c r="A663" s="15">
         <v>43523</v>
       </c>
@@ -39247,7 +39259,7 @@
         <v>48.78</v>
       </c>
     </row>
-    <row r="664" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="664" spans="1:11">
       <c r="A664" s="15">
         <v>43530</v>
       </c>
@@ -39283,7 +39295,7 @@
         <v>51.87</v>
       </c>
     </row>
-    <row r="665" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="665" spans="1:11">
       <c r="A665" s="15">
         <v>43537</v>
       </c>
@@ -39319,7 +39331,7 @@
         <v>50.84</v>
       </c>
     </row>
-    <row r="666" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="666" spans="1:11">
       <c r="A666" s="15">
         <v>43544</v>
       </c>
@@ -39355,7 +39367,7 @@
         <v>57.44</v>
       </c>
     </row>
-    <row r="667" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="667" spans="1:11">
       <c r="A667" s="15">
         <v>43551</v>
       </c>
@@ -39391,7 +39403,7 @@
         <v>58.85</v>
       </c>
     </row>
-    <row r="668" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="668" spans="1:11">
       <c r="A668" s="15">
         <v>43558</v>
       </c>
@@ -39427,7 +39439,7 @@
         <v>37.44</v>
       </c>
     </row>
-    <row r="669" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="669" spans="1:11">
       <c r="A669" s="15">
         <v>43565</v>
       </c>
@@ -39463,7 +39475,7 @@
         <v>44.35</v>
       </c>
     </row>
-    <row r="670" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="670" spans="1:11">
       <c r="A670" s="15">
         <v>43572</v>
       </c>
@@ -39499,7 +39511,7 @@
         <v>29.9</v>
       </c>
     </row>
-    <row r="671" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="671" spans="1:11">
       <c r="A671" s="15">
         <v>43579</v>
       </c>
@@ -39535,7 +39547,7 @@
         <v>38.32</v>
       </c>
     </row>
-    <row r="672" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="672" spans="1:11">
       <c r="A672" s="15">
         <v>43586</v>
       </c>
@@ -39571,7 +39583,7 @@
         <v>43.11</v>
       </c>
     </row>
-    <row r="673" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="673" spans="1:11">
       <c r="A673" s="15">
         <v>43593</v>
       </c>
@@ -39607,7 +39619,7 @@
         <v>63.69</v>
       </c>
     </row>
-    <row r="674" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="674" spans="1:11">
       <c r="A674" s="15">
         <v>43600</v>
       </c>
@@ -39643,7 +39655,7 @@
         <v>54.45</v>
       </c>
     </row>
-    <row r="675" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="675" spans="1:11">
       <c r="A675" s="15">
         <v>43607</v>
       </c>
@@ -39679,7 +39691,7 @@
         <v>38.76</v>
       </c>
     </row>
-    <row r="676" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="676" spans="1:11">
       <c r="A676" s="15">
         <v>43614</v>
       </c>
@@ -39715,7 +39727,7 @@
         <v>76.66</v>
       </c>
     </row>
-    <row r="677" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="677" spans="1:11">
       <c r="A677" s="15">
         <v>43621</v>
       </c>
@@ -39751,7 +39763,7 @@
         <v>57.55</v>
       </c>
     </row>
-    <row r="678" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="678" spans="1:11">
       <c r="A678" s="15">
         <v>43628</v>
       </c>
@@ -39787,7 +39799,7 @@
         <v>36.67</v>
       </c>
     </row>
-    <row r="679" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="679" spans="1:11">
       <c r="A679" s="15">
         <v>43635</v>
       </c>
@@ -39823,7 +39835,7 @@
         <v>25.39</v>
       </c>
     </row>
-    <row r="680" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="680" spans="1:11">
       <c r="A680" s="15">
         <v>43642</v>
       </c>
@@ -39859,7 +39871,7 @@
         <v>56.56</v>
       </c>
     </row>
-    <row r="681" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="681" spans="1:11">
       <c r="A681" s="15">
         <v>43649</v>
       </c>
@@ -39895,7 +39907,7 @@
         <v>37.46</v>
       </c>
     </row>
-    <row r="682" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="682" spans="1:11">
       <c r="A682" s="15">
         <v>43656</v>
       </c>
@@ -39931,7 +39943,7 @@
         <v>35.630000000000003</v>
       </c>
     </row>
-    <row r="683" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="683" spans="1:11">
       <c r="A683" s="15">
         <v>43663</v>
       </c>
@@ -39967,7 +39979,7 @@
         <v>53.98</v>
       </c>
     </row>
-    <row r="684" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="684" spans="1:11">
       <c r="A684" s="15">
         <v>43670</v>
       </c>
@@ -40003,7 +40015,7 @@
         <v>37.93</v>
       </c>
     </row>
-    <row r="685" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="685" spans="1:11">
       <c r="A685" s="15">
         <v>43677</v>
       </c>
@@ -40039,7 +40051,7 @@
         <v>41.31</v>
       </c>
     </row>
-    <row r="686" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="686" spans="1:11">
       <c r="A686" s="15">
         <v>43684</v>
       </c>
@@ -40075,7 +40087,7 @@
         <v>61.58</v>
       </c>
     </row>
-    <row r="687" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="687" spans="1:11">
       <c r="A687" s="15">
         <v>43691</v>
       </c>
@@ -40111,7 +40123,7 @@
         <v>49.29</v>
       </c>
     </row>
-    <row r="688" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="688" spans="1:11">
       <c r="A688" s="15">
         <v>43698</v>
       </c>
@@ -40147,7 +40159,7 @@
         <v>60.34</v>
       </c>
     </row>
-    <row r="689" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="689" spans="1:11">
       <c r="A689" s="15">
         <v>43705</v>
       </c>
@@ -40183,7 +40195,7 @@
         <v>66.010000000000005</v>
       </c>
     </row>
-    <row r="690" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="690" spans="1:11">
       <c r="A690" s="15">
         <v>43712</v>
       </c>
@@ -40219,7 +40231,7 @@
         <v>53.29</v>
       </c>
     </row>
-    <row r="691" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="691" spans="1:11">
       <c r="A691" s="15">
         <v>43719</v>
       </c>
@@ -40255,7 +40267,7 @@
         <v>58.2</v>
       </c>
     </row>
-    <row r="692" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="692" spans="1:11">
       <c r="A692" s="15">
         <v>43726</v>
       </c>
@@ -40291,7 +40303,7 @@
         <v>62.04</v>
       </c>
     </row>
-    <row r="693" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="693" spans="1:11">
       <c r="A693" s="15">
         <v>43733</v>
       </c>
@@ -40327,7 +40339,7 @@
         <v>53.22</v>
       </c>
     </row>
-    <row r="694" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="694" spans="1:11">
       <c r="A694" s="15">
         <v>43740</v>
       </c>
@@ -40363,7 +40375,7 @@
         <v>78.3</v>
       </c>
     </row>
-    <row r="695" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="695" spans="1:11">
       <c r="A695" s="15">
         <v>43747</v>
       </c>
@@ -40399,7 +40411,7 @@
         <v>57.1</v>
       </c>
     </row>
-    <row r="696" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="696" spans="1:11">
       <c r="A696" s="15">
         <v>43754</v>
       </c>
@@ -40435,7 +40447,7 @@
         <v>67.400000000000006</v>
       </c>
     </row>
-    <row r="697" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="697" spans="1:11">
       <c r="A697" s="15">
         <v>43761</v>
       </c>
@@ -40471,7 +40483,7 @@
         <v>38.35</v>
       </c>
     </row>
-    <row r="698" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="698" spans="1:11">
       <c r="A698" s="15">
         <v>43768</v>
       </c>
@@ -40507,7 +40519,7 @@
         <v>39.58</v>
       </c>
     </row>
-    <row r="699" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="699" spans="1:11">
       <c r="A699" s="15">
         <v>43775</v>
       </c>
@@ -40543,7 +40555,7 @@
         <v>35.5</v>
       </c>
     </row>
-    <row r="700" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="700" spans="1:11">
       <c r="A700" s="15">
         <v>43782</v>
       </c>
@@ -40579,7 +40591,7 @@
         <v>49.68</v>
       </c>
     </row>
-    <row r="701" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="701" spans="1:11">
       <c r="A701" s="15">
         <v>43789</v>
       </c>
@@ -40615,7 +40627,7 @@
         <v>52.05</v>
       </c>
     </row>
-    <row r="702" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="702" spans="1:11">
       <c r="A702" s="15">
         <v>43796</v>
       </c>
@@ -40651,7 +40663,7 @@
         <v>41.28</v>
       </c>
     </row>
-    <row r="703" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="703" spans="1:11">
       <c r="A703" s="15">
         <v>43803</v>
       </c>
@@ -40687,7 +40699,7 @@
         <v>56.13</v>
       </c>
     </row>
-    <row r="704" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="704" spans="1:11">
       <c r="A704" s="15">
         <v>43810</v>
       </c>
@@ -40723,7 +40735,7 @@
         <v>50.69</v>
       </c>
     </row>
-    <row r="705" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="705" spans="1:11">
       <c r="A705" s="15">
         <v>43817</v>
       </c>
@@ -40759,7 +40771,7 @@
         <v>35.82</v>
       </c>
     </row>
-    <row r="706" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="706" spans="1:11">
       <c r="A706" s="15">
         <v>43824</v>
       </c>
@@ -40795,7 +40807,7 @@
         <v>29.16</v>
       </c>
     </row>
-    <row r="707" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="707" spans="1:11">
       <c r="A707" s="15">
         <v>43831</v>
       </c>
@@ -40846,7 +40858,7 @@
         <v>32.42</v>
       </c>
     </row>
-    <row r="708" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="708" spans="1:11">
       <c r="A708" s="15">
         <v>43838</v>
       </c>
@@ -40882,7 +40894,7 @@
         <v>40.659999999999997</v>
       </c>
     </row>
-    <row r="709" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="709" spans="1:11">
       <c r="A709" s="15">
         <v>43845</v>
       </c>
@@ -40918,7 +40930,7 @@
         <v>37.35</v>
       </c>
     </row>
-    <row r="710" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="710" spans="1:11">
       <c r="A710" s="15">
         <v>43852</v>
       </c>
@@ -40954,7 +40966,7 @@
         <v>21.13</v>
       </c>
     </row>
-    <row r="711" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="711" spans="1:11">
       <c r="A711" s="15">
         <v>43859</v>
       </c>
@@ -40990,7 +41002,7 @@
         <v>57.93</v>
       </c>
     </row>
-    <row r="712" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="712" spans="1:11">
       <c r="A712" s="15">
         <v>43866</v>
       </c>
@@ -41026,7 +41038,7 @@
         <v>57.84</v>
       </c>
     </row>
-    <row r="713" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="713" spans="1:11">
       <c r="A713" s="15">
         <v>43873</v>
       </c>
@@ -41062,7 +41074,7 @@
         <v>37.590000000000003</v>
       </c>
     </row>
-    <row r="714" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="714" spans="1:11">
       <c r="A714" s="15">
         <v>43880</v>
       </c>
@@ -41098,7 +41110,7 @@
         <v>35.15</v>
       </c>
     </row>
-    <row r="715" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="715" spans="1:11">
       <c r="A715" s="15">
         <v>43887</v>
       </c>
@@ -41134,7 +41146,7 @@
         <v>69.72</v>
       </c>
     </row>
-    <row r="716" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="716" spans="1:11">
       <c r="A716" s="15">
         <v>43894</v>
       </c>
@@ -41170,7 +41182,7 @@
         <v>72.709999999999994</v>
       </c>
     </row>
-    <row r="717" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="717" spans="1:11">
       <c r="A717" s="15">
         <v>43901</v>
       </c>
@@ -41206,7 +41218,7 @@
         <v>58.88</v>
       </c>
     </row>
-    <row r="718" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="718" spans="1:11">
       <c r="A718" s="15">
         <v>43908</v>
       </c>
@@ -41242,7 +41254,7 @@
         <v>42.67</v>
       </c>
     </row>
-    <row r="719" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="719" spans="1:11">
       <c r="A719" s="15">
         <v>43915</v>
       </c>
@@ -41278,7 +41290,7 @@
         <v>34.049999999999997</v>
       </c>
     </row>
-    <row r="720" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="720" spans="1:11">
       <c r="A720" s="15">
         <v>43922</v>
       </c>
@@ -41314,7 +41326,7 @@
         <v>40.64</v>
       </c>
     </row>
-    <row r="721" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="721" spans="1:11">
       <c r="A721" s="15">
         <v>43929</v>
       </c>
@@ -41350,7 +41362,7 @@
         <v>44.54</v>
       </c>
     </row>
-    <row r="722" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="722" spans="1:11">
       <c r="A722" s="15">
         <v>43936</v>
       </c>
@@ -41386,7 +41398,7 @@
         <v>56.57</v>
       </c>
     </row>
-    <row r="723" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="723" spans="1:11">
       <c r="A723" s="15">
         <v>43943</v>
       </c>
@@ -41422,7 +41434,7 @@
         <v>57.95</v>
       </c>
     </row>
-    <row r="724" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="724" spans="1:11">
       <c r="A724" s="15">
         <v>43950</v>
       </c>
@@ -41458,7 +41470,7 @@
         <v>41.89</v>
       </c>
     </row>
-    <row r="725" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="725" spans="1:11">
       <c r="A725" s="15">
         <v>43957</v>
       </c>
@@ -41494,7 +41506,7 @@
         <v>41.07</v>
       </c>
     </row>
-    <row r="726" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="726" spans="1:11">
       <c r="A726" s="15">
         <v>43964</v>
       </c>
@@ -41530,7 +41542,7 @@
         <v>49.3</v>
       </c>
     </row>
-    <row r="727" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="727" spans="1:11">
       <c r="A727" s="15">
         <v>43971</v>
       </c>
@@ -41566,7 +41578,7 @@
         <v>51.08</v>
       </c>
     </row>
-    <row r="728" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="728" spans="1:11">
       <c r="A728" s="15">
         <v>43978</v>
       </c>
@@ -41602,7 +41614,7 @@
         <v>43.17</v>
       </c>
     </row>
-    <row r="729" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="729" spans="1:11">
       <c r="A729" s="15">
         <v>43985</v>
       </c>
@@ -41638,7 +41650,7 @@
         <v>36.69</v>
       </c>
     </row>
-    <row r="730" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="730" spans="1:11">
       <c r="A730" s="15">
         <v>43992</v>
       </c>
@@ -41674,7 +41686,7 @@
         <v>54.73</v>
       </c>
     </row>
-    <row r="731" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="731" spans="1:11">
       <c r="A731" s="15">
         <v>43999</v>
       </c>
@@ -41710,7 +41722,7 @@
         <v>37.33</v>
       </c>
     </row>
-    <row r="732" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="732" spans="1:11">
       <c r="A732" s="15">
         <v>44006</v>
       </c>
@@ -41746,7 +41758,7 @@
         <v>43.91</v>
       </c>
     </row>
-    <row r="733" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="733" spans="1:11">
       <c r="A733" s="15">
         <v>44013</v>
       </c>
@@ -41782,7 +41794,7 @@
         <v>52.64</v>
       </c>
     </row>
-    <row r="734" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="734" spans="1:11">
       <c r="A734" s="15">
         <v>44020</v>
       </c>
@@ -41818,7 +41830,7 @@
         <v>50.49</v>
       </c>
     </row>
-    <row r="735" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="735" spans="1:11">
       <c r="A735" s="15">
         <v>44027</v>
       </c>
@@ -41854,7 +41866,7 @@
         <v>49.38</v>
       </c>
     </row>
-    <row r="736" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="736" spans="1:11">
       <c r="A736" s="15">
         <v>44034</v>
       </c>
@@ -41890,7 +41902,7 @@
         <v>33.909999999999997</v>
       </c>
     </row>
-    <row r="737" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="737" spans="1:11">
       <c r="A737" s="15">
         <v>44041</v>
       </c>
@@ -41926,7 +41938,7 @@
         <v>36.130000000000003</v>
       </c>
     </row>
-    <row r="738" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="738" spans="1:11">
       <c r="A738" s="15">
         <v>44048</v>
       </c>
@@ -41962,7 +41974,7 @@
         <v>49.4</v>
       </c>
     </row>
-    <row r="739" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="739" spans="1:11">
       <c r="A739" s="15">
         <v>44055</v>
       </c>
@@ -41998,7 +42010,7 @@
         <v>29.1</v>
       </c>
     </row>
-    <row r="740" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="740" spans="1:11">
       <c r="A740" s="15">
         <v>44062</v>
       </c>
@@ -42034,7 +42046,7 @@
         <v>42.31</v>
       </c>
     </row>
-    <row r="741" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="741" spans="1:11">
       <c r="A741" s="15">
         <v>44069</v>
       </c>
@@ -42070,7 +42082,7 @@
         <v>38.44</v>
       </c>
     </row>
-    <row r="742" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="742" spans="1:11">
       <c r="A742" s="15">
         <v>44076</v>
       </c>
@@ -42106,7 +42118,7 @@
         <v>35.47</v>
       </c>
     </row>
-    <row r="743" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="743" spans="1:11">
       <c r="A743" s="15">
         <v>44083</v>
       </c>
@@ -42142,7 +42154,7 @@
         <v>60.47</v>
       </c>
     </row>
-    <row r="744" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="744" spans="1:11">
       <c r="A744" s="15">
         <v>44090</v>
       </c>
@@ -42178,7 +42190,7 @@
         <v>71.73</v>
       </c>
     </row>
-    <row r="745" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="745" spans="1:11">
       <c r="A745" s="15">
         <v>44097</v>
       </c>
@@ -42214,7 +42226,7 @@
         <v>82.7</v>
       </c>
     </row>
-    <row r="746" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="746" spans="1:11">
       <c r="A746" s="15">
         <v>44104</v>
       </c>
@@ -42250,7 +42262,7 @@
         <v>62.62</v>
       </c>
     </row>
-    <row r="747" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="747" spans="1:11">
       <c r="A747" s="15">
         <v>44111</v>
       </c>
@@ -42286,7 +42298,7 @@
         <v>63.41</v>
       </c>
     </row>
-    <row r="748" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="748" spans="1:11">
       <c r="A748" s="15">
         <v>44118</v>
       </c>
@@ -42322,7 +42334,7 @@
         <v>41.56</v>
       </c>
     </row>
-    <row r="749" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="749" spans="1:11">
       <c r="A749" s="15">
         <v>44125</v>
       </c>
@@ -42358,7 +42370,7 @@
         <v>42.48</v>
       </c>
     </row>
-    <row r="750" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="750" spans="1:11">
       <c r="A750" s="15">
         <v>44132</v>
       </c>
@@ -42394,7 +42406,7 @@
         <v>49.64</v>
       </c>
     </row>
-    <row r="751" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="751" spans="1:11">
       <c r="A751" s="15">
         <v>44139</v>
       </c>
@@ -42430,7 +42442,7 @@
         <v>49.7</v>
       </c>
     </row>
-    <row r="752" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="752" spans="1:11">
       <c r="A752" s="15">
         <v>44146</v>
       </c>
@@ -42466,7 +42478,7 @@
         <v>50.26</v>
       </c>
     </row>
-    <row r="753" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="753" spans="1:11">
       <c r="A753" s="15">
         <v>44153</v>
       </c>
@@ -42502,7 +42514,7 @@
         <v>44.54</v>
       </c>
     </row>
-    <row r="754" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="754" spans="1:11">
       <c r="A754" s="15">
         <v>44160</v>
       </c>
@@ -42538,7 +42550,7 @@
         <v>44.54</v>
       </c>
     </row>
-    <row r="755" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="755" spans="1:11">
       <c r="A755" s="15">
         <v>44167</v>
       </c>
@@ -42574,7 +42586,7 @@
         <v>38.9</v>
       </c>
     </row>
-    <row r="756" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="756" spans="1:11">
       <c r="A756" s="15">
         <v>44174</v>
       </c>
@@ -42610,7 +42622,7 @@
         <v>40.98</v>
       </c>
     </row>
-    <row r="757" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="757" spans="1:11">
       <c r="A757" s="15">
         <v>44181</v>
       </c>
@@ -42646,7 +42658,7 @@
         <v>42.33</v>
       </c>
     </row>
-    <row r="758" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="758" spans="1:11">
       <c r="A758" s="15">
         <v>44188</v>
       </c>
@@ -42682,7 +42694,7 @@
         <v>44.19</v>
       </c>
     </row>
-    <row r="759" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="759" spans="1:11">
       <c r="A759" s="15">
         <v>44195</v>
       </c>
@@ -42718,7 +42730,7 @@
         <v>47.07</v>
       </c>
     </row>
-    <row r="760" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="760" spans="1:11">
       <c r="A760" s="15">
         <v>44202</v>
       </c>
@@ -42754,7 +42766,7 @@
         <v>39.11</v>
       </c>
     </row>
-    <row r="761" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="761" spans="1:11">
       <c r="A761" s="15">
         <v>44209</v>
       </c>
@@ -42790,7 +42802,7 @@
         <v>39.85</v>
       </c>
     </row>
-    <row r="762" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="762" spans="1:11">
       <c r="A762" s="15">
         <v>44216</v>
       </c>
@@ -42826,7 +42838,7 @@
         <v>36.46</v>
       </c>
     </row>
-    <row r="763" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="763" spans="1:11">
       <c r="A763" s="15">
         <v>44223</v>
       </c>
@@ -42862,7 +42874,7 @@
         <v>53.82</v>
       </c>
     </row>
-    <row r="764" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="764" spans="1:11">
       <c r="A764" s="15">
         <v>44230</v>
       </c>
@@ -42898,7 +42910,7 @@
         <v>50.88</v>
       </c>
     </row>
-    <row r="765" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="765" spans="1:11">
       <c r="A765" s="15">
         <v>44237</v>
       </c>
@@ -42934,7 +42946,7 @@
         <v>29.44</v>
       </c>
     </row>
-    <row r="766" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="766" spans="1:11">
       <c r="A766" s="15">
         <v>44244</v>
       </c>
@@ -42970,7 +42982,7 @@
         <v>44.76</v>
       </c>
     </row>
-    <row r="767" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="767" spans="1:11">
       <c r="A767" s="15">
         <v>44251</v>
       </c>
@@ -43006,7 +43018,7 @@
         <v>48.64</v>
       </c>
     </row>
-    <row r="768" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="768" spans="1:11">
       <c r="A768" s="15">
         <v>44258</v>
       </c>
@@ -43042,7 +43054,7 @@
         <v>62.65</v>
       </c>
     </row>
-    <row r="769" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="769" spans="1:11">
       <c r="A769" s="15">
         <v>44265</v>
       </c>
@@ -43078,7 +43090,7 @@
         <v>54.1</v>
       </c>
     </row>
-    <row r="770" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="770" spans="1:11">
       <c r="A770" s="15">
         <v>44272</v>
       </c>
@@ -43114,7 +43126,7 @@
         <v>33.979999999999997</v>
       </c>
     </row>
-    <row r="771" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="771" spans="1:11">
       <c r="A771" s="15">
         <v>44279</v>
       </c>
@@ -43165,7 +43177,7 @@
         <v>42.24</v>
       </c>
     </row>
-    <row r="772" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="772" spans="1:11">
       <c r="A772" s="15">
         <v>44286</v>
       </c>
@@ -43201,7 +43213,7 @@
         <v>47.49</v>
       </c>
     </row>
-    <row r="773" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="773" spans="1:11">
       <c r="A773" s="15">
         <v>44293</v>
       </c>
@@ -43237,7 +43249,7 @@
         <v>35.159999999999997</v>
       </c>
     </row>
-    <row r="774" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="774" spans="1:11">
       <c r="A774" s="15">
         <v>44300</v>
       </c>
@@ -43273,7 +43285,7 @@
         <v>39.590000000000003</v>
       </c>
     </row>
-    <row r="775" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="775" spans="1:11">
       <c r="A775" s="15">
         <v>44307</v>
       </c>
@@ -43309,7 +43321,7 @@
         <v>39.06</v>
       </c>
     </row>
-    <row r="776" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="776" spans="1:11">
       <c r="A776" s="15">
         <v>44314</v>
       </c>
@@ -43345,7 +43357,7 @@
         <v>43.65</v>
       </c>
     </row>
-    <row r="777" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="777" spans="1:11">
       <c r="A777" s="15">
         <v>44321</v>
       </c>
@@ -43381,7 +43393,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="778" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="778" spans="1:11">
       <c r="A778" s="15">
         <v>44328</v>
       </c>
@@ -43417,7 +43429,7 @@
         <v>44.2</v>
       </c>
     </row>
-    <row r="779" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="779" spans="1:11">
       <c r="A779" s="15">
         <v>44335</v>
       </c>
@@ -43453,7 +43465,7 @@
         <v>35.25</v>
       </c>
     </row>
-    <row r="780" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="780" spans="1:11">
       <c r="A780" s="15">
         <v>44342</v>
       </c>
@@ -43489,7 +43501,7 @@
         <v>35.119999999999997</v>
       </c>
     </row>
-    <row r="781" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="781" spans="1:11">
       <c r="A781" s="15">
         <v>44349</v>
       </c>
@@ -43525,7 +43537,7 @@
         <v>35.83</v>
       </c>
     </row>
-    <row r="782" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="782" spans="1:11">
       <c r="A782" s="15">
         <v>44356</v>
       </c>
@@ -43561,7 +43573,7 @@
         <v>38.92</v>
       </c>
     </row>
-    <row r="783" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="783" spans="1:11">
       <c r="A783" s="15">
         <v>44363</v>
       </c>
@@ -43597,7 +43609,7 @@
         <v>34.159999999999997</v>
       </c>
     </row>
-    <row r="784" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="784" spans="1:11">
       <c r="A784" s="15">
         <v>44370</v>
       </c>
@@ -43633,7 +43645,7 @@
         <v>42.79</v>
       </c>
     </row>
-    <row r="785" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="785" spans="1:11">
       <c r="A785" s="15">
         <v>44377</v>
       </c>
@@ -43669,7 +43681,7 @@
         <v>38.18</v>
       </c>
     </row>
-    <row r="786" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="786" spans="1:11">
       <c r="A786" s="15">
         <v>44384</v>
       </c>
@@ -43705,7 +43717,7 @@
         <v>42.66</v>
       </c>
     </row>
-    <row r="787" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="787" spans="1:11">
       <c r="A787" s="15">
         <v>44391</v>
       </c>
@@ -43741,7 +43753,7 @@
         <v>37.85</v>
       </c>
     </row>
-    <row r="788" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="788" spans="1:11">
       <c r="A788" s="15">
         <v>44398</v>
       </c>
@@ -43777,7 +43789,7 @@
         <v>48.75</v>
       </c>
     </row>
-    <row r="789" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="789" spans="1:11">
       <c r="A789" s="15">
         <v>44405</v>
       </c>
@@ -43813,7 +43825,7 @@
         <v>43.07</v>
       </c>
     </row>
-    <row r="790" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="790" spans="1:11">
       <c r="A790" s="15">
         <v>44412</v>
       </c>
@@ -43849,7 +43861,7 @@
         <v>41.16</v>
       </c>
     </row>
-    <row r="791" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="791" spans="1:11">
       <c r="A791" s="15">
         <v>44419</v>
       </c>
@@ -43885,7 +43897,7 @@
         <v>38.54</v>
       </c>
     </row>
-    <row r="792" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="792" spans="1:11">
       <c r="A792" s="15">
         <v>44426</v>
       </c>
@@ -43921,7 +43933,7 @@
         <v>58.22</v>
       </c>
     </row>
-    <row r="793" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="793" spans="1:11">
       <c r="A793" s="15">
         <v>44433</v>
       </c>
@@ -43957,7 +43969,7 @@
         <v>37.950000000000003</v>
       </c>
     </row>
-    <row r="794" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="794" spans="1:11">
       <c r="A794" s="15">
         <v>44440</v>
       </c>
@@ -43993,7 +44005,7 @@
         <v>39.24</v>
       </c>
     </row>
-    <row r="795" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="795" spans="1:11">
       <c r="A795" s="15">
         <v>44447</v>
       </c>
@@ -44029,7 +44041,7 @@
         <v>43.85</v>
       </c>
     </row>
-    <row r="796" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="796" spans="1:11">
       <c r="A796" s="15">
         <v>44454</v>
       </c>
@@ -44065,7 +44077,7 @@
         <v>47.86</v>
       </c>
     </row>
-    <row r="797" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="797" spans="1:11">
       <c r="A797" s="15">
         <v>44461</v>
       </c>
@@ -44101,7 +44113,7 @@
         <v>47.37</v>
       </c>
     </row>
-    <row r="798" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="798" spans="1:11">
       <c r="A798" s="15">
         <v>44468</v>
       </c>
@@ -44137,7 +44149,7 @@
         <v>72.13</v>
       </c>
     </row>
-    <row r="799" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="799" spans="1:11">
       <c r="A799" s="15">
         <v>44475</v>
       </c>
@@ -44173,7 +44185,7 @@
         <v>51.09</v>
       </c>
     </row>
-    <row r="800" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="800" spans="1:11">
       <c r="A800" s="15">
         <v>44482</v>
       </c>
@@ -44209,7 +44221,7 @@
         <v>52.37</v>
       </c>
     </row>
-    <row r="801" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="801" spans="1:11">
       <c r="A801" s="15">
         <v>44489</v>
       </c>
@@ -44245,7 +44257,7 @@
         <v>33.46</v>
       </c>
     </row>
-    <row r="802" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="802" spans="1:11">
       <c r="A802" s="15">
         <v>44496</v>
       </c>
@@ -44281,7 +44293,7 @@
         <v>33.03</v>
       </c>
     </row>
-    <row r="803" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="803" spans="1:11">
       <c r="A803" s="15">
         <v>44503</v>
       </c>
@@ -44317,7 +44329,7 @@
         <v>37.31</v>
       </c>
     </row>
-    <row r="804" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="804" spans="1:11">
       <c r="A804" s="15">
         <v>44510</v>
       </c>
@@ -44353,7 +44365,7 @@
         <v>43.41</v>
       </c>
     </row>
-    <row r="805" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="805" spans="1:11">
       <c r="A805" s="15">
         <v>44517</v>
       </c>
@@ -44389,7 +44401,7 @@
         <v>47.38</v>
       </c>
     </row>
-    <row r="806" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="806" spans="1:11">
       <c r="A806" s="15">
         <v>44524</v>
       </c>
@@ -44425,7 +44437,7 @@
         <v>46.63</v>
       </c>
     </row>
-    <row r="807" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="807" spans="1:11">
       <c r="A807" s="15">
         <v>44531</v>
       </c>
@@ -44461,7 +44473,7 @@
         <v>59.91</v>
       </c>
     </row>
-    <row r="808" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="808" spans="1:11">
       <c r="A808" s="15">
         <v>44538</v>
       </c>
@@ -44497,7 +44509,7 @@
         <v>78.33</v>
       </c>
     </row>
-    <row r="809" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="809" spans="1:11">
       <c r="A809" s="15">
         <v>44545</v>
       </c>
@@ -44533,7 +44545,7 @@
         <v>61.89</v>
       </c>
     </row>
-    <row r="810" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="810" spans="1:11">
       <c r="A810" s="15">
         <v>44552</v>
       </c>
@@ -44569,7 +44581,7 @@
         <v>51.45</v>
       </c>
     </row>
-    <row r="811" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="811" spans="1:11">
       <c r="A811" s="15">
         <v>44559</v>
       </c>
@@ -44605,7 +44617,7 @@
         <v>38.94</v>
       </c>
     </row>
-    <row r="812" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="812" spans="1:11">
       <c r="A812" s="15">
         <v>44566</v>
       </c>
@@ -44641,7 +44653,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="813" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="813" spans="1:11">
       <c r="A813" s="15">
         <v>44573</v>
       </c>
@@ -44677,7 +44689,7 @@
         <v>66.02</v>
       </c>
     </row>
-    <row r="814" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="814" spans="1:11">
       <c r="A814" s="15">
         <v>44580</v>
       </c>
@@ -44713,7 +44725,7 @@
         <v>76.22</v>
       </c>
     </row>
-    <row r="815" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="815" spans="1:11">
       <c r="A815" s="15">
         <v>44587</v>
       </c>
@@ -44749,7 +44761,7 @@
         <v>66.22</v>
       </c>
     </row>
-    <row r="816" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="816" spans="1:11">
       <c r="A816" s="15">
         <v>44594</v>
       </c>
@@ -44785,7 +44797,7 @@
         <v>49.17</v>
       </c>
     </row>
-    <row r="817" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="817" spans="1:11">
       <c r="A817" s="15">
         <v>44601</v>
       </c>
@@ -44821,7 +44833,7 @@
         <v>40.53</v>
       </c>
     </row>
-    <row r="818" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="818" spans="1:11">
       <c r="A818" s="15">
         <v>44608</v>
       </c>
@@ -44857,7 +44869,7 @@
         <v>72.38</v>
       </c>
     </row>
-    <row r="819" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="819" spans="1:11">
       <c r="A819" s="15">
         <v>44615</v>
       </c>
@@ -44893,7 +44905,7 @@
         <v>71.64</v>
       </c>
     </row>
-    <row r="820" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="820" spans="1:11">
       <c r="A820" s="15">
         <v>44622</v>
       </c>
@@ -44929,7 +44941,7 @@
         <v>72.260000000000005</v>
       </c>
     </row>
-    <row r="821" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="821" spans="1:11">
       <c r="A821" s="15">
         <v>44629</v>
       </c>
@@ -44965,7 +44977,7 @@
         <v>70.959999999999994</v>
       </c>
     </row>
-    <row r="822" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="822" spans="1:11">
       <c r="A822" s="15">
         <v>44636</v>
       </c>
@@ -45001,7 +45013,7 @@
         <v>60.48</v>
       </c>
     </row>
-    <row r="823" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="823" spans="1:11">
       <c r="A823" s="15">
         <v>44643</v>
       </c>
@@ -45037,7 +45049,7 @@
         <v>65.23</v>
       </c>
     </row>
-    <row r="824" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="824" spans="1:11">
       <c r="A824" s="15">
         <v>44650</v>
       </c>
@@ -45073,7 +45085,7 @@
         <v>21.67</v>
       </c>
     </row>
-    <row r="825" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="825" spans="1:11">
       <c r="A825" s="15">
         <v>44657</v>
       </c>
@@ -45109,7 +45121,7 @@
         <v>40.35</v>
       </c>
     </row>
-    <row r="826" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="826" spans="1:11">
       <c r="A826" s="15">
         <v>44664</v>
       </c>
@@ -45145,7 +45157,7 @@
         <v>31.86</v>
       </c>
     </row>
-    <row r="827" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="827" spans="1:11">
       <c r="A827" s="15">
         <v>44671</v>
       </c>
@@ -45181,7 +45193,7 @@
         <v>28.88</v>
       </c>
     </row>
-    <row r="828" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="828" spans="1:11">
       <c r="A828" s="15">
         <v>44678</v>
       </c>
@@ -45217,7 +45229,7 @@
         <v>69.22</v>
       </c>
     </row>
-    <row r="829" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="829" spans="1:11">
       <c r="A829" s="15">
         <v>44685</v>
       </c>
@@ -45253,7 +45265,7 @@
         <v>45.33</v>
       </c>
     </row>
-    <row r="830" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="830" spans="1:11">
       <c r="A830" s="15">
         <v>44692</v>
       </c>
@@ -45289,7 +45301,7 @@
         <v>58.81</v>
       </c>
     </row>
-    <row r="831" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="831" spans="1:11">
       <c r="A831" s="15">
         <v>44699</v>
       </c>
@@ -45325,7 +45337,7 @@
         <v>44.74</v>
       </c>
     </row>
-    <row r="832" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="832" spans="1:11">
       <c r="A832" s="15">
         <v>44706</v>
       </c>
@@ -45361,7 +45373,7 @@
         <v>35.08</v>
       </c>
     </row>
-    <row r="833" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="833" spans="1:11">
       <c r="A833" s="15">
         <v>44713</v>
       </c>
@@ -45397,7 +45409,7 @@
         <v>74.08</v>
       </c>
     </row>
-    <row r="834" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="834" spans="1:11">
       <c r="A834" s="15">
         <v>44720</v>
       </c>
@@ -45433,7 +45445,7 @@
         <v>43.01</v>
       </c>
     </row>
-    <row r="835" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="835" spans="1:11">
       <c r="A835" s="15">
         <v>44727</v>
       </c>
@@ -45484,7 +45496,7 @@
         <v>50.59</v>
       </c>
     </row>
-    <row r="836" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="836" spans="1:11">
       <c r="A836" s="15">
         <v>44734</v>
       </c>
@@ -45520,7 +45532,7 @@
         <v>59.84</v>
       </c>
     </row>
-    <row r="837" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="837" spans="1:11">
       <c r="A837" s="15">
         <v>44741</v>
       </c>
@@ -45556,7 +45568,7 @@
         <v>51.78</v>
       </c>
     </row>
-    <row r="838" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="838" spans="1:11">
       <c r="A838" s="15">
         <v>44748</v>
       </c>
@@ -45592,7 +45604,7 @@
         <v>62.05</v>
       </c>
     </row>
-    <row r="839" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="839" spans="1:11">
       <c r="A839" s="15">
         <v>44755</v>
       </c>
@@ -45628,7 +45640,7 @@
         <v>58.93</v>
       </c>
     </row>
-    <row r="840" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="840" spans="1:11">
       <c r="A840" s="15">
         <v>44762</v>
       </c>
@@ -45664,7 +45676,7 @@
         <v>51.59</v>
       </c>
     </row>
-    <row r="841" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="841" spans="1:11">
       <c r="A841" s="15">
         <v>44769</v>
       </c>
@@ -45700,7 +45712,7 @@
         <v>50.16</v>
       </c>
     </row>
-    <row r="842" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="842" spans="1:11">
       <c r="A842" s="15">
         <v>44776</v>
       </c>
@@ -45736,7 +45748,7 @@
         <v>53.21</v>
       </c>
     </row>
-    <row r="843" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="843" spans="1:11">
       <c r="A843" s="15">
         <v>44783</v>
       </c>
@@ -45772,7 +45784,7 @@
         <v>54.24</v>
       </c>
     </row>
-    <row r="844" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="844" spans="1:11">
       <c r="A844" s="15">
         <v>44790</v>
       </c>
@@ -45808,7 +45820,7 @@
         <v>54.27</v>
       </c>
     </row>
-    <row r="845" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="845" spans="1:11">
       <c r="A845" s="15">
         <v>44797</v>
       </c>
@@ -45844,7 +45856,7 @@
         <v>59.7</v>
       </c>
     </row>
-    <row r="846" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="846" spans="1:11">
       <c r="A846" s="15">
         <v>44804</v>
       </c>
@@ -45880,7 +45892,7 @@
         <v>60.43</v>
       </c>
     </row>
-    <row r="847" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="847" spans="1:11">
       <c r="A847" s="15">
         <v>44811</v>
       </c>
@@ -45916,7 +45928,7 @@
         <v>60.04</v>
       </c>
     </row>
-    <row r="848" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="848" spans="1:11">
       <c r="A848" s="15">
         <v>44818</v>
       </c>
@@ -45952,7 +45964,7 @@
         <v>70.459999999999994</v>
       </c>
     </row>
-    <row r="849" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="849" spans="1:11">
       <c r="A849" s="15">
         <v>44825</v>
       </c>
@@ -45988,7 +46000,7 @@
         <v>60.97</v>
       </c>
     </row>
-    <row r="850" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="850" spans="1:11">
       <c r="A850" s="15">
         <v>44832</v>
       </c>
@@ -46024,7 +46036,7 @@
         <v>66.88</v>
       </c>
     </row>
-    <row r="851" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="851" spans="1:11">
       <c r="A851" s="15">
         <v>44839</v>
       </c>
@@ -46060,7 +46072,7 @@
         <v>58.96</v>
       </c>
     </row>
-    <row r="852" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="852" spans="1:11">
       <c r="A852" s="15">
         <v>44846</v>
       </c>
@@ -46096,7 +46108,7 @@
         <v>59.65</v>
       </c>
     </row>
-    <row r="853" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="853" spans="1:11">
       <c r="A853" s="15">
         <v>44853</v>
       </c>
@@ -46132,7 +46144,7 @@
         <v>55.43</v>
       </c>
     </row>
-    <row r="854" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="854" spans="1:11">
       <c r="A854" s="15">
         <v>44860</v>
       </c>
@@ -46168,7 +46180,7 @@
         <v>54.08</v>
       </c>
     </row>
-    <row r="855" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="855" spans="1:11">
       <c r="A855" s="15">
         <v>44867</v>
       </c>
@@ -46204,7 +46216,7 @@
         <v>59.48</v>
       </c>
     </row>
-    <row r="856" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="856" spans="1:11">
       <c r="A856" s="15">
         <v>44874</v>
       </c>
@@ -46240,7 +46252,7 @@
         <v>54.63</v>
       </c>
     </row>
-    <row r="857" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="857" spans="1:11">
       <c r="A857" s="15">
         <v>44881</v>
       </c>
@@ -46276,7 +46288,7 @@
         <v>60.66</v>
       </c>
     </row>
-    <row r="858" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="858" spans="1:11">
       <c r="A858" s="15">
         <v>44888</v>
       </c>
@@ -46312,7 +46324,7 @@
         <v>56.55</v>
       </c>
     </row>
-    <row r="859" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="859" spans="1:11">
       <c r="A859" s="15">
         <v>44895</v>
       </c>
@@ -46348,7 +46360,7 @@
         <v>50.1</v>
       </c>
     </row>
-    <row r="860" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="860" spans="1:11">
       <c r="A860" s="15">
         <v>44902</v>
       </c>
@@ -46384,7 +46396,7 @@
         <v>50.27</v>
       </c>
     </row>
-    <row r="861" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="861" spans="1:11">
       <c r="A861" s="15">
         <v>44909</v>
       </c>
@@ -46420,7 +46432,7 @@
         <v>48.94</v>
       </c>
     </row>
-    <row r="862" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="862" spans="1:11">
       <c r="A862" s="15">
         <v>44916</v>
       </c>
@@ -46456,7 +46468,7 @@
         <v>53.8</v>
       </c>
     </row>
-    <row r="863" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="863" spans="1:11">
       <c r="A863" s="15">
         <v>44923</v>
       </c>
@@ -46492,7 +46504,7 @@
         <v>46.68</v>
       </c>
     </row>
-    <row r="864" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="864" spans="1:11">
       <c r="A864" s="15">
         <v>44930</v>
       </c>
@@ -46528,7 +46540,7 @@
         <v>53.9</v>
       </c>
     </row>
-    <row r="865" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="865" spans="1:11">
       <c r="A865" s="15">
         <v>44937</v>
       </c>
@@ -46564,7 +46576,7 @@
         <v>39.74</v>
       </c>
     </row>
-    <row r="866" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="866" spans="1:11">
       <c r="A866" s="15">
         <v>44944</v>
       </c>
@@ -46600,7 +46612,7 @@
         <v>58.85</v>
       </c>
     </row>
-    <row r="867" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="867" spans="1:11">
       <c r="A867" s="15">
         <v>44951</v>
       </c>
@@ -46636,7 +46648,7 @@
         <v>45.01</v>
       </c>
     </row>
-    <row r="868" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="868" spans="1:11">
       <c r="A868" s="15">
         <v>44958</v>
       </c>
@@ -46672,7 +46684,7 @@
         <v>44.29</v>
       </c>
     </row>
-    <row r="869" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="869" spans="1:11">
       <c r="A869" s="15">
         <v>44965</v>
       </c>
@@ -46708,7 +46720,7 @@
         <v>44.25</v>
       </c>
     </row>
-    <row r="870" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="870" spans="1:11">
       <c r="A870" s="15">
         <v>44972</v>
       </c>
@@ -46744,7 +46756,7 @@
         <v>47.28</v>
       </c>
     </row>
-    <row r="871" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="871" spans="1:11">
       <c r="A871" s="15">
         <v>44979</v>
       </c>
@@ -46780,7 +46792,7 @@
         <v>71.14</v>
       </c>
     </row>
-    <row r="872" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="872" spans="1:11">
       <c r="A872" s="15">
         <v>44986</v>
       </c>
@@ -46816,7 +46828,7 @@
         <v>69.319999999999993</v>
       </c>
     </row>
-    <row r="873" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="873" spans="1:11">
       <c r="A873" s="15">
         <v>44993</v>
       </c>
@@ -46852,7 +46864,7 @@
         <v>63.44</v>
       </c>
     </row>
-    <row r="874" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="874" spans="1:11">
       <c r="A874" s="15">
         <v>45000</v>
       </c>
@@ -46888,7 +46900,7 @@
         <v>66.69</v>
       </c>
     </row>
-    <row r="875" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="875" spans="1:11">
       <c r="A875" s="15">
         <v>45007</v>
       </c>
@@ -46924,7 +46936,7 @@
         <v>57.12</v>
       </c>
     </row>
-    <row r="876" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="876" spans="1:11">
       <c r="A876" s="15">
         <v>45014</v>
       </c>
@@ -46960,7 +46972,7 @@
         <v>49.69</v>
       </c>
     </row>
-    <row r="877" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="877" spans="1:11">
       <c r="A877" s="15">
         <v>45021</v>
       </c>
@@ -46996,7 +47008,7 @@
         <v>45.38</v>
       </c>
     </row>
-    <row r="878" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="878" spans="1:11">
       <c r="A878" s="15">
         <v>45028</v>
       </c>
@@ -47032,7 +47044,7 @@
         <v>64.83</v>
       </c>
     </row>
-    <row r="879" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="879" spans="1:11">
       <c r="A879" s="15">
         <v>45035</v>
       </c>
@@ -47068,7 +47080,7 @@
         <v>39.61</v>
       </c>
     </row>
-    <row r="880" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="880" spans="1:11">
       <c r="A880" s="15">
         <v>45042</v>
       </c>
@@ -47104,7 +47116,7 @@
         <v>56.93</v>
       </c>
     </row>
-    <row r="881" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="881" spans="1:11">
       <c r="A881" s="15">
         <v>45049</v>
       </c>
@@ -47140,7 +47152,7 @@
         <v>43.05</v>
       </c>
     </row>
-    <row r="882" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="882" spans="1:11">
       <c r="A882" s="15">
         <v>45056</v>
       </c>
@@ -47176,7 +47188,7 @@
         <v>50.84</v>
       </c>
     </row>
-    <row r="883" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="883" spans="1:11">
       <c r="A883" s="15">
         <v>45063</v>
       </c>
@@ -47212,7 +47224,7 @@
         <v>48.49</v>
       </c>
     </row>
-    <row r="884" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="884" spans="1:11">
       <c r="A884" s="15">
         <v>45070</v>
       </c>
@@ -47248,7 +47260,7 @@
         <v>52.21</v>
       </c>
     </row>
-    <row r="885" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="885" spans="1:11">
       <c r="A885" s="15">
         <v>45077</v>
       </c>
@@ -47284,7 +47296,7 @@
         <v>59.12</v>
       </c>
     </row>
-    <row r="886" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="886" spans="1:11">
       <c r="A886" s="15">
         <v>45084</v>
       </c>
@@ -47320,7 +47332,7 @@
         <v>40.46</v>
       </c>
     </row>
-    <row r="887" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="887" spans="1:11">
       <c r="A887" s="15">
         <v>45091</v>
       </c>
@@ -47356,7 +47368,7 @@
         <v>56.21</v>
       </c>
     </row>
-    <row r="888" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="888" spans="1:11">
       <c r="A888" s="15">
         <v>45098</v>
       </c>
@@ -47392,7 +47404,7 @@
         <v>45.51</v>
       </c>
     </row>
-    <row r="889" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="889" spans="1:11">
       <c r="A889" s="15">
         <v>45105</v>
       </c>
@@ -47428,7 +47440,7 @@
         <v>54.14</v>
       </c>
     </row>
-    <row r="890" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="890" spans="1:11">
       <c r="A890" s="15">
         <v>45112</v>
       </c>
@@ -47464,7 +47476,7 @@
         <v>50.49</v>
       </c>
     </row>
-    <row r="891" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="891" spans="1:11">
       <c r="A891" s="15">
         <v>45119</v>
       </c>
@@ -47500,7 +47512,7 @@
         <v>44.26</v>
       </c>
     </row>
-    <row r="892" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="892" spans="1:11">
       <c r="A892" s="15">
         <v>45126</v>
       </c>
@@ -47536,7 +47548,7 @@
         <v>44.69</v>
       </c>
     </row>
-    <row r="893" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="893" spans="1:11">
       <c r="A893" s="15">
         <v>45133</v>
       </c>
@@ -47572,7 +47584,7 @@
         <v>36.340000000000003</v>
       </c>
     </row>
-    <row r="894" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="894" spans="1:11">
       <c r="A894" s="15">
         <v>45140</v>
       </c>
@@ -47608,7 +47620,7 @@
         <v>72.739999999999995</v>
       </c>
     </row>
-    <row r="895" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="895" spans="1:11">
       <c r="A895" s="15">
         <v>45147</v>
       </c>
@@ -47644,7 +47656,7 @@
         <v>63.43</v>
       </c>
     </row>
-    <row r="896" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="896" spans="1:11">
       <c r="A896" s="15">
         <v>45154</v>
       </c>
@@ -47680,7 +47692,7 @@
         <v>67.22</v>
       </c>
     </row>
-    <row r="897" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="897" spans="1:11">
       <c r="A897" s="15">
         <v>45161</v>
       </c>
@@ -47716,7 +47728,7 @@
         <v>79.38</v>
       </c>
     </row>
-    <row r="898" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="898" spans="1:11">
       <c r="A898" s="15">
         <v>45168</v>
       </c>
@@ -47752,7 +47764,7 @@
         <v>63.6</v>
       </c>
     </row>
-    <row r="899" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="899" spans="1:11">
       <c r="A899" s="15">
         <v>45175</v>
       </c>
@@ -47803,7 +47815,7 @@
         <v>70.89</v>
       </c>
     </row>
-    <row r="900" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="900" spans="1:11">
       <c r="A900" s="15">
         <v>45182</v>
       </c>
@@ -47839,7 +47851,7 @@
         <v>64.010000000000005</v>
       </c>
     </row>
-    <row r="901" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="901" spans="1:11">
       <c r="A901" s="15">
         <v>45189</v>
       </c>
@@ -47875,7 +47887,7 @@
         <v>53.81</v>
       </c>
     </row>
-    <row r="902" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="902" spans="1:11">
       <c r="A902" s="15">
         <v>45196</v>
       </c>
@@ -47911,7 +47923,7 @@
         <v>60.53</v>
       </c>
     </row>
-    <row r="903" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="903" spans="1:11">
       <c r="A903" s="15">
         <v>45203</v>
       </c>
@@ -47947,7 +47959,7 @@
         <v>74.3</v>
       </c>
     </row>
-    <row r="904" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="904" spans="1:11">
       <c r="A904" s="15">
         <v>45210</v>
       </c>
@@ -47983,7 +47995,7 @@
         <v>70.16</v>
       </c>
     </row>
-    <row r="905" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="905" spans="1:11">
       <c r="A905" s="15">
         <v>45217</v>
       </c>
@@ -48019,7 +48031,7 @@
         <v>60.7</v>
       </c>
     </row>
-    <row r="906" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="906" spans="1:11">
       <c r="A906" s="15">
         <v>45224</v>
       </c>
@@ -48055,7 +48067,7 @@
         <v>73.540000000000006</v>
       </c>
     </row>
-    <row r="907" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="907" spans="1:11">
       <c r="A907" s="15">
         <v>45231</v>
       </c>
@@ -48091,7 +48103,7 @@
         <v>71.180000000000007</v>
       </c>
     </row>
-    <row r="908" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="908" spans="1:11">
       <c r="A908" s="15">
         <v>45238</v>
       </c>
@@ -48127,7 +48139,7 @@
         <v>52.63</v>
       </c>
     </row>
-    <row r="909" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="909" spans="1:11">
       <c r="A909" s="15">
         <v>45245</v>
       </c>
@@ -48163,7 +48175,7 @@
         <v>70.599999999999994</v>
       </c>
     </row>
-    <row r="910" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="910" spans="1:11">
       <c r="A910" s="15">
         <v>45252</v>
       </c>
@@ -48199,7 +48211,7 @@
         <v>68.56</v>
       </c>
     </row>
-    <row r="911" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="911" spans="1:11">
       <c r="A911" s="15">
         <v>45259</v>
       </c>
@@ -48235,7 +48247,7 @@
         <v>64.95</v>
       </c>
     </row>
-    <row r="912" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="912" spans="1:11">
       <c r="A912" s="15">
         <v>45266</v>
       </c>
@@ -48271,7 +48283,7 @@
         <v>71.14</v>
       </c>
     </row>
-    <row r="913" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="913" spans="1:11">
       <c r="A913" s="15">
         <v>45273</v>
       </c>
@@ -48307,7 +48319,7 @@
         <v>69.78</v>
       </c>
     </row>
-    <row r="914" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="914" spans="1:11">
       <c r="A914" s="15">
         <v>45280</v>
       </c>
@@ -48343,7 +48355,7 @@
         <v>49.87</v>
       </c>
     </row>
-    <row r="915" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="915" spans="1:11">
       <c r="A915" s="15">
         <v>45287</v>
       </c>
@@ -48379,7 +48391,7 @@
         <v>48.43</v>
       </c>
     </row>
-    <row r="916" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="916" spans="1:11">
       <c r="A916" s="15">
         <v>45294</v>
       </c>
@@ -48415,7 +48427,7 @@
         <v>68.19</v>
       </c>
     </row>
-    <row r="917" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="917" spans="1:11">
       <c r="A917" s="15">
         <v>45301</v>
       </c>
@@ -48451,7 +48463,7 @@
         <v>43.94</v>
       </c>
     </row>
-    <row r="918" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="918" spans="1:11">
       <c r="A918" s="15">
         <v>45308</v>
       </c>
@@ -48487,7 +48499,7 @@
         <v>71.66</v>
       </c>
     </row>
-    <row r="919" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="919" spans="1:11">
       <c r="A919" s="15">
         <v>45315</v>
       </c>
@@ -48523,7 +48535,7 @@
         <v>70.540000000000006</v>
       </c>
     </row>
-    <row r="920" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="920" spans="1:11">
       <c r="A920" s="15">
         <v>45322</v>
       </c>
@@ -48559,7 +48571,7 @@
         <v>67.72</v>
       </c>
     </row>
-    <row r="921" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="921" spans="1:11">
       <c r="A921" s="15">
         <v>45329</v>
       </c>
@@ -48595,7 +48607,7 @@
         <v>40.520000000000003</v>
       </c>
     </row>
-    <row r="922" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="922" spans="1:11">
       <c r="A922" s="15">
         <v>45336</v>
       </c>
@@ -48631,7 +48643,7 @@
         <v>42.93</v>
       </c>
     </row>
-    <row r="923" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="923" spans="1:11">
       <c r="A923" s="15">
         <v>45343</v>
       </c>
@@ -48667,7 +48679,7 @@
         <v>87.34</v>
       </c>
     </row>
-    <row r="924" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="924" spans="1:11">
       <c r="A924" s="15">
         <v>45350</v>
       </c>
@@ -48703,7 +48715,7 @@
         <v>63.8</v>
       </c>
     </row>
-    <row r="925" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="925" spans="1:11">
       <c r="A925" s="15">
         <v>45357</v>
       </c>
@@ -48739,7 +48751,7 @@
         <v>43.54</v>
       </c>
     </row>
-    <row r="926" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="926" spans="1:11">
       <c r="A926" s="15">
         <v>45364</v>
       </c>
@@ -48775,7 +48787,7 @@
         <v>45.2</v>
       </c>
     </row>
-    <row r="927" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="927" spans="1:11">
       <c r="A927" s="15">
         <v>45371</v>
       </c>
@@ -48811,7 +48823,7 @@
         <v>71.209999999999994</v>
       </c>
     </row>
-    <row r="928" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="928" spans="1:11">
       <c r="A928" s="15">
         <v>45378</v>
       </c>
@@ -48847,7 +48859,7 @@
         <v>31.21</v>
       </c>
     </row>
-    <row r="929" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="929" spans="1:11">
       <c r="A929" s="15">
         <v>45385</v>
       </c>
@@ -48883,7 +48895,7 @@
         <v>68.209999999999994</v>
       </c>
     </row>
-    <row r="930" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="930" spans="1:11">
       <c r="A930" s="15">
         <v>45392</v>
       </c>
@@ -48919,7 +48931,7 @@
         <v>65.73</v>
       </c>
     </row>
-    <row r="931" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="931" spans="1:11">
       <c r="A931" s="15">
         <v>45399</v>
       </c>
@@ -48955,7 +48967,7 @@
         <v>71.42</v>
       </c>
     </row>
-    <row r="932" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="932" spans="1:11">
       <c r="A932" s="15">
         <v>45406</v>
       </c>
@@ -48991,7 +49003,7 @@
         <v>70.790000000000006</v>
       </c>
     </row>
-    <row r="933" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="933" spans="1:11">
       <c r="A933" s="15">
         <v>45413</v>
       </c>
@@ -49027,7 +49039,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="934" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="934" spans="1:11">
       <c r="A934" s="15">
         <v>45420</v>
       </c>
@@ -49063,7 +49075,7 @@
         <v>59.39</v>
       </c>
     </row>
-    <row r="935" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="935" spans="1:11">
       <c r="A935" s="15">
         <v>45427</v>
       </c>
@@ -49099,7 +49111,7 @@
         <v>71.739999999999995</v>
       </c>
     </row>
-    <row r="936" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="936" spans="1:11">
       <c r="A936" s="15">
         <v>45434</v>
       </c>
@@ -49135,7 +49147,7 @@
         <v>72.540000000000006</v>
       </c>
     </row>
-    <row r="937" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="937" spans="1:11">
       <c r="A937" s="15">
         <v>45441</v>
       </c>
@@ -49171,7 +49183,7 @@
         <v>78.959999999999994</v>
       </c>
     </row>
-    <row r="938" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="938" spans="1:11">
       <c r="A938" s="15">
         <v>45448</v>
       </c>
@@ -49207,7 +49219,7 @@
         <v>90.94</v>
       </c>
     </row>
-    <row r="939" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="939" spans="1:11">
       <c r="A939" s="15">
         <v>45455</v>
       </c>
@@ -49243,7 +49255,7 @@
         <v>56.33</v>
       </c>
     </row>
-    <row r="940" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="940" spans="1:11">
       <c r="A940" s="15">
         <v>45462</v>
       </c>
@@ -49279,7 +49291,7 @@
         <v>74.87</v>
       </c>
     </row>
-    <row r="941" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="941" spans="1:11">
       <c r="A941" s="15">
         <v>45469</v>
       </c>
@@ -49315,7 +49327,7 @@
         <v>58.35</v>
       </c>
     </row>
-    <row r="942" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="942" spans="1:11">
       <c r="A942" s="15">
         <v>45476</v>
       </c>
@@ -49351,7 +49363,7 @@
         <v>55.2</v>
       </c>
     </row>
-    <row r="943" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="943" spans="1:11">
       <c r="A943" s="15">
         <v>45483</v>
       </c>
@@ -49387,7 +49399,7 @@
         <v>71.989999999999995</v>
       </c>
     </row>
-    <row r="944" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="944" spans="1:11">
       <c r="A944" s="15">
         <v>45490</v>
       </c>
@@ -49423,7 +49435,7 @@
         <v>71.55</v>
       </c>
     </row>
-    <row r="945" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="945" spans="1:11">
       <c r="A945" s="15">
         <v>45497</v>
       </c>
@@ -49459,7 +49471,7 @@
         <v>54.03</v>
       </c>
     </row>
-    <row r="946" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="946" spans="1:11">
       <c r="A946" s="15">
         <v>45504</v>
       </c>
@@ -49495,7 +49507,7 @@
         <v>62.38</v>
       </c>
     </row>
-    <row r="947" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="947" spans="1:11">
       <c r="A947" s="15">
         <v>45511</v>
       </c>
@@ -49531,7 +49543,7 @@
         <v>60.29</v>
       </c>
     </row>
-    <row r="948" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="948" spans="1:11">
       <c r="A948" s="15">
         <v>45518</v>
       </c>
@@ -49567,7 +49579,7 @@
         <v>89.06</v>
       </c>
     </row>
-    <row r="949" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="949" spans="1:11">
       <c r="A949" s="15">
         <v>45525</v>
       </c>
@@ -49603,7 +49615,7 @@
         <v>67.78</v>
       </c>
     </row>
-    <row r="950" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="950" spans="1:11">
       <c r="A950" s="15">
         <v>45532</v>
       </c>
@@ -49639,7 +49651,7 @@
         <v>76.260000000000005</v>
       </c>
     </row>
-    <row r="951" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="951" spans="1:11">
       <c r="A951" s="15">
         <v>45539</v>
       </c>
@@ -49675,7 +49687,7 @@
         <v>70.38</v>
       </c>
     </row>
-    <row r="952" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="952" spans="1:11">
       <c r="A952" s="15">
         <v>45546</v>
       </c>
@@ -49711,7 +49723,7 @@
         <v>70.66</v>
       </c>
     </row>
-    <row r="953" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="953" spans="1:11">
       <c r="A953" s="15">
         <v>45553</v>
       </c>
@@ -49747,7 +49759,7 @@
         <v>69.36</v>
       </c>
     </row>
-    <row r="954" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="954" spans="1:11">
       <c r="A954" s="15">
         <v>45560</v>
       </c>
@@ -49783,7 +49795,7 @@
         <v>75.61</v>
       </c>
     </row>
-    <row r="955" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="955" spans="1:11">
       <c r="A955" s="15">
         <v>45567</v>
       </c>
@@ -49819,7 +49831,7 @@
         <v>56.15</v>
       </c>
     </row>
-    <row r="956" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="956" spans="1:11">
       <c r="A956" s="15">
         <v>45574</v>
       </c>
@@ -49855,7 +49867,7 @@
         <v>54.22</v>
       </c>
     </row>
-    <row r="957" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="957" spans="1:11">
       <c r="A957" s="15">
         <v>45581</v>
       </c>
@@ -49891,7 +49903,7 @@
         <v>70.319999999999993</v>
       </c>
     </row>
-    <row r="958" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="958" spans="1:11">
       <c r="A958" s="15">
         <v>45588</v>
       </c>
@@ -49927,7 +49939,7 @@
         <v>75.64</v>
       </c>
     </row>
-    <row r="959" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="959" spans="1:11">
       <c r="A959" s="15">
         <v>45595</v>
       </c>
@@ -49963,7 +49975,7 @@
         <v>60.95</v>
       </c>
     </row>
-    <row r="960" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="960" spans="1:11">
       <c r="A960" s="15">
         <v>45602</v>
       </c>
@@ -49999,7 +50011,7 @@
         <v>56.27</v>
       </c>
     </row>
-    <row r="961" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="961" spans="1:11">
       <c r="A961" s="15">
         <v>45609</v>
       </c>
@@ -50035,7 +50047,7 @@
         <v>66.66</v>
       </c>
     </row>
-    <row r="962" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="962" spans="1:11">
       <c r="A962" s="15">
         <v>45616</v>
       </c>
@@ -50071,7 +50083,7 @@
         <v>55.21</v>
       </c>
     </row>
-    <row r="963" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="963" spans="1:11">
       <c r="A963" s="15">
         <v>45623</v>
       </c>
@@ -50122,7 +50134,7 @@
         <v>44.97</v>
       </c>
     </row>
-    <row r="964" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="964" spans="1:11">
       <c r="A964" s="15">
         <v>45630</v>
       </c>
@@ -50158,7 +50170,7 @@
         <v>65.58</v>
       </c>
     </row>
-    <row r="965" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="965" spans="1:11">
       <c r="A965" s="15">
         <v>45637</v>
       </c>
@@ -50194,7 +50206,7 @@
         <v>50.55</v>
       </c>
     </row>
-    <row r="966" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="966" spans="1:11">
       <c r="A966" s="15">
         <v>45644</v>
       </c>
@@ -50230,7 +50242,7 @@
         <v>55.02</v>
       </c>
     </row>
-    <row r="967" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="967" spans="1:11">
       <c r="A967" s="15">
         <v>45651</v>
       </c>
@@ -50266,7 +50278,7 @@
         <v>72.16</v>
       </c>
     </row>
-    <row r="968" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="968" spans="1:11">
       <c r="A968" s="15">
         <v>45658</v>
       </c>
@@ -50302,7 +50314,7 @@
         <v>90.01</v>
       </c>
     </row>
-    <row r="969" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="969" spans="1:11">
       <c r="A969" s="15">
         <v>45665</v>
       </c>
@@ -50338,7 +50350,7 @@
         <v>55.05</v>
       </c>
     </row>
-    <row r="970" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="970" spans="1:11">
       <c r="A970" s="15">
         <v>45672</v>
       </c>
@@ -50374,7 +50386,7 @@
         <v>58.09</v>
       </c>
     </row>
-    <row r="971" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="971" spans="1:11">
       <c r="A971" s="15">
         <v>45679</v>
       </c>
@@ -50410,7 +50422,7 @@
         <v>45.88</v>
       </c>
     </row>
-    <row r="972" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="972" spans="1:11">
       <c r="A972" s="15">
         <v>45686</v>
       </c>
@@ -50446,7 +50458,7 @@
         <v>65.86</v>
       </c>
     </row>
-    <row r="973" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="973" spans="1:11">
       <c r="A973" s="15">
         <v>45693</v>
       </c>
@@ -50482,7 +50494,7 @@
         <v>54.2</v>
       </c>
     </row>
-    <row r="974" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="974" spans="1:11">
       <c r="A974" s="15">
         <v>45700</v>
       </c>
@@ -50518,7 +50530,7 @@
         <v>52.44</v>
       </c>
     </row>
-    <row r="975" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="975" spans="1:11">
       <c r="A975" s="15">
         <v>45707</v>
       </c>
@@ -50554,7 +50566,7 @@
         <v>49.61</v>
       </c>
     </row>
-    <row r="976" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="976" spans="1:11">
       <c r="A976" s="15">
         <v>45714</v>
       </c>
@@ -50590,7 +50602,7 @@
         <v>51.43</v>
       </c>
     </row>
-    <row r="977" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="977" spans="1:11">
       <c r="A977" s="15">
         <v>45721</v>
       </c>
@@ -50626,7 +50638,7 @@
         <v>69.739999999999995</v>
       </c>
     </row>
-    <row r="978" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="978" spans="1:11">
       <c r="A978" s="15">
         <v>45728</v>
       </c>
@@ -50662,7 +50674,7 @@
         <v>70.47</v>
       </c>
     </row>
-    <row r="979" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="979" spans="1:11">
       <c r="A979" s="15">
         <v>45735</v>
       </c>
@@ -50698,7 +50710,7 @@
         <v>53.55</v>
       </c>
     </row>
-    <row r="980" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="980" spans="1:11">
       <c r="A980" s="15">
         <v>45742</v>
       </c>
@@ -50734,7 +50746,7 @@
         <v>54.17</v>
       </c>
     </row>
-    <row r="981" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="981" spans="1:11">
       <c r="A981" s="15">
         <v>45749</v>
       </c>
@@ -50770,7 +50782,7 @@
         <v>83.68</v>
       </c>
     </row>
-    <row r="982" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="982" spans="1:11">
       <c r="A982" s="15">
         <v>45756</v>
       </c>
@@ -50806,7 +50818,7 @@
         <v>60.04</v>
       </c>
     </row>
-    <row r="983" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="983" spans="1:11">
       <c r="A983" s="15">
         <v>45763</v>
       </c>
@@ -50842,7 +50854,7 @@
         <v>65.53</v>
       </c>
     </row>
-    <row r="984" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="984" spans="1:11">
       <c r="A984" s="15">
         <v>45770</v>
       </c>
@@ -50878,7 +50890,7 @@
         <v>50.87</v>
       </c>
     </row>
-    <row r="985" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="985" spans="1:11">
       <c r="A985" s="15">
         <v>45777</v>
       </c>
@@ -50914,7 +50926,7 @@
         <v>77.239999999999995</v>
       </c>
     </row>
-    <row r="986" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="986" spans="1:11">
       <c r="A986" s="15">
         <v>45784</v>
       </c>
@@ -50950,7 +50962,7 @@
         <v>51.46</v>
       </c>
     </row>
-    <row r="987" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="987" spans="1:11">
       <c r="A987" s="15">
         <v>45791</v>
       </c>
@@ -50986,7 +50998,7 @@
         <v>65.03</v>
       </c>
     </row>
-    <row r="988" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="988" spans="1:11">
       <c r="A988" s="15">
         <v>45798</v>
       </c>
@@ -51022,7 +51034,7 @@
         <v>60.35</v>
       </c>
     </row>
-    <row r="989" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="989" spans="1:11">
       <c r="A989" s="15">
         <v>45805</v>
       </c>
@@ -51058,7 +51070,7 @@
         <v>53.2</v>
       </c>
     </row>
-    <row r="990" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="990" spans="1:11">
       <c r="A990" s="15">
         <v>45812</v>
       </c>
@@ -51094,7 +51106,7 @@
         <v>67.680000000000007</v>
       </c>
     </row>
-    <row r="991" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="991" spans="1:11">
       <c r="A991" s="15">
         <v>45819</v>
       </c>
@@ -51130,7 +51142,7 @@
         <v>73.680000000000007</v>
       </c>
     </row>
-    <row r="992" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="992" spans="1:11">
       <c r="A992" s="15">
         <v>45826</v>
       </c>
@@ -51166,7 +51178,7 @@
         <v>52.15</v>
       </c>
     </row>
-    <row r="993" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="993" spans="1:11">
       <c r="A993" s="15">
         <v>45833</v>
       </c>
@@ -51202,7 +51214,7 @@
         <v>72.73</v>
       </c>
     </row>
-    <row r="994" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="994" spans="1:11">
       <c r="A994" s="15">
         <v>45840</v>
       </c>
@@ -51238,7 +51250,7 @@
         <v>54.77</v>
       </c>
     </row>
-    <row r="995" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="995" spans="1:11">
       <c r="A995" s="15">
         <v>45847</v>
       </c>
@@ -51274,7 +51286,7 @@
         <v>69.709999999999994</v>
       </c>
     </row>
-    <row r="996" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="996" spans="1:11">
       <c r="A996" s="15">
         <v>45854</v>
       </c>
@@ -51310,7 +51322,7 @@
         <v>57.22</v>
       </c>
     </row>
-    <row r="997" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="997" spans="1:11">
       <c r="A997" s="15">
         <v>45861</v>
       </c>
@@ -51346,7 +51358,7 @@
         <v>64.98</v>
       </c>
     </row>
-    <row r="998" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="998" spans="1:11">
       <c r="A998" s="15">
         <v>45868</v>
       </c>
@@ -51382,7 +51394,7 @@
         <v>64.89</v>
       </c>
     </row>
-    <row r="999" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="999" spans="1:11">
       <c r="A999" s="15">
         <v>45875</v>
       </c>
@@ -51418,7 +51430,7 @@
         <v>35.96</v>
       </c>
     </row>
-    <row r="1000" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1000" spans="1:11">
       <c r="A1000" s="15">
         <v>45882</v>
       </c>
@@ -51454,7 +51466,7 @@
         <v>69.55</v>
       </c>
     </row>
-    <row r="1001" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1001" spans="1:11">
       <c r="A1001" s="15">
         <v>45889</v>
       </c>
@@ -51490,7 +51502,7 @@
         <v>44.79</v>
       </c>
     </row>
-    <row r="1002" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1002" spans="1:11">
       <c r="A1002" s="15">
         <v>45896</v>
       </c>
@@ -51526,7 +51538,7 @@
         <v>44.7</v>
       </c>
     </row>
-    <row r="1003" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1003" spans="1:11">
       <c r="A1003" s="15">
         <v>45903</v>
       </c>
@@ -51562,7 +51574,7 @@
         <v>63.56</v>
       </c>
     </row>
-    <row r="1004" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1004" spans="1:11">
       <c r="A1004" s="15">
         <v>45910</v>
       </c>
@@ -51598,7 +51610,7 @@
         <v>71.06</v>
       </c>
     </row>
-    <row r="1005" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1005" spans="1:11">
       <c r="A1005" s="15">
         <v>45917</v>
       </c>
@@ -51634,7 +51646,7 @@
         <v>71.959999999999994</v>
       </c>
     </row>
-    <row r="1006" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1006" spans="1:11">
       <c r="A1006" s="15">
         <v>45924</v>
       </c>
@@ -51670,7 +51682,7 @@
         <v>66.77</v>
       </c>
     </row>
-    <row r="1007" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1007" spans="1:11">
       <c r="A1007" s="15">
         <v>45931</v>
       </c>
@@ -51706,7 +51718,7 @@
         <v>71.13</v>
       </c>
     </row>
-    <row r="1008" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1008" spans="1:11">
       <c r="A1008" s="15">
         <v>45938</v>
       </c>
@@ -51742,7 +51754,7 @@
         <v>69.27</v>
       </c>
     </row>
-    <row r="1009" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1009" spans="1:11">
       <c r="A1009" s="15">
         <v>45945</v>
       </c>
@@ -51778,7 +51790,7 @@
         <v>50.98</v>
       </c>
     </row>
-    <row r="1010" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1010" spans="1:11">
       <c r="A1010" s="15">
         <v>45952</v>
       </c>
@@ -51814,7 +51826,7 @@
         <v>52.1</v>
       </c>
     </row>
-    <row r="1011" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1011" spans="1:11">
       <c r="A1011" s="15">
         <v>45959</v>
       </c>
@@ -51850,7 +51862,7 @@
         <v>55.36</v>
       </c>
     </row>
-    <row r="1012" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1012" spans="1:11">
       <c r="A1012" s="15">
         <v>45966</v>
       </c>
@@ -51886,7 +51898,7 @@
         <v>40.86</v>
       </c>
     </row>
-    <row r="1013" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1013" spans="1:11">
       <c r="A1013" s="15">
         <v>45973</v>
       </c>
@@ -51922,7 +51934,7 @@
         <v>39.42</v>
       </c>
     </row>
-    <row r="1014" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1014" spans="1:11">
       <c r="A1014" s="15">
         <v>45980</v>
       </c>
@@ -51958,7 +51970,7 @@
         <v>51.59</v>
       </c>
     </row>
-    <row r="1015" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1015" spans="1:11">
       <c r="A1015" s="15">
         <v>45987</v>
       </c>
@@ -51994,7 +52006,7 @@
         <v>50.29</v>
       </c>
     </row>
-    <row r="1016" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1016" spans="1:11">
       <c r="A1016" s="15">
         <v>45994</v>
       </c>
@@ -52030,7 +52042,7 @@
         <v>47.59</v>
       </c>
     </row>
-    <row r="1017" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1017" spans="1:11">
       <c r="A1017" s="15">
         <v>46001</v>
       </c>
@@ -52066,7 +52078,7 @@
         <v>45.89</v>
       </c>
     </row>
-    <row r="1018" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1018" spans="1:11">
       <c r="A1018" s="15">
         <v>46008</v>
       </c>
@@ -52102,7 +52114,7 @@
         <v>46.38</v>
       </c>
     </row>
-    <row r="1019" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1019" spans="1:11">
       <c r="A1019" s="15">
         <v>46015</v>
       </c>
@@ -52138,7 +52150,7 @@
         <v>49.27</v>
       </c>
     </row>
-    <row r="1020" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1020" spans="1:11">
       <c r="A1020" s="15">
         <v>46022</v>
       </c>
@@ -52174,7 +52186,7 @@
         <v>48.97</v>
       </c>
     </row>
-    <row r="1021" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1021" spans="1:11">
       <c r="A1021" s="15">
         <v>46029</v>
       </c>
@@ -52210,7 +52222,7 @@
         <v>50.86</v>
       </c>
     </row>
-    <row r="1022" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1022" spans="1:11">
       <c r="A1022" s="15">
         <v>46036</v>
       </c>
@@ -52246,7 +52258,7 @@
         <v>50.37</v>
       </c>
     </row>
-    <row r="1023" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1023" spans="1:11">
       <c r="A1023" s="15">
         <v>46043</v>
       </c>
@@ -52282,7 +52294,7 @@
         <v>60.31</v>
       </c>
     </row>
-    <row r="1024" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1024" spans="1:11">
       <c r="A1024" s="15">
         <v>46050</v>
       </c>
@@ -52318,7 +52330,7 @@
         <v>46.41</v>
       </c>
     </row>
-    <row r="1025" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1025" spans="1:11">
       <c r="A1025" s="15">
         <v>46057</v>
       </c>
@@ -52354,7 +52366,7 @@
         <v>64.569999999999993</v>
       </c>
     </row>
-    <row r="1026" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1026" spans="1:11">
       <c r="A1026" s="15">
         <v>46064</v>
       </c>
@@ -52390,7 +52402,7 @@
         <v>63.52</v>
       </c>
     </row>
-    <row r="1027" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1027" spans="1:11">
       <c r="A1027" s="15">
         <v>46071</v>
       </c>
@@ -52441,7 +52453,7 @@
         <v>47.62</v>
       </c>
     </row>
-    <row r="1028" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1028" spans="1:11">
       <c r="A1028" s="15">
         <v>46078</v>
       </c>
@@ -52477,7 +52489,7 @@
         <v>64.84</v>
       </c>
     </row>
-    <row r="1029" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1029" spans="1:11">
       <c r="A1029" s="15">
         <v>46085</v>
       </c>
@@ -52513,7 +52525,7 @@
         <v>49.98</v>
       </c>
     </row>
-    <row r="1030" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1030" spans="1:11">
       <c r="A1030" s="15">
         <v>46092</v>
       </c>
@@ -52549,7 +52561,7 @@
         <v>62.78</v>
       </c>
     </row>
-    <row r="1031" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1031" spans="1:11">
       <c r="A1031" s="15">
         <v>46099</v>
       </c>
@@ -52585,7 +52597,7 @@
         <v>68.13</v>
       </c>
     </row>
-    <row r="1032" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1032" spans="1:11">
       <c r="A1032" s="15">
         <v>46106</v>
       </c>
@@ -52636,7 +52648,7 @@
         <v>47.03</v>
       </c>
     </row>
-    <row r="1033" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1033" spans="1:11">
       <c r="A1033" s="15">
         <v>46113</v>
       </c>
@@ -52672,7 +52684,7 @@
         <v>55.64</v>
       </c>
     </row>
-    <row r="1034" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1034" spans="1:11">
       <c r="A1034" s="15">
         <v>46120</v>
       </c>
@@ -52723,7 +52735,7 @@
         <v>51.31</v>
       </c>
     </row>
-    <row r="1035" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1035" spans="1:11">
       <c r="A1035" s="15">
         <v>46127</v>
       </c>
@@ -52759,7 +52771,7 @@
         <v>68.87</v>
       </c>
     </row>
-    <row r="1036" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1036" spans="1:11">
       <c r="A1036" s="15">
         <v>46134</v>
       </c>
@@ -52795,7 +52807,7 @@
         <v>51.9</v>
       </c>
     </row>
-    <row r="1037" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1037" spans="1:11">
       <c r="A1037" s="15">
         <v>46141</v>
       </c>
@@ -52806,7 +52818,7 @@
         <v>0.41666666666669799</v>
       </c>
       <c r="D1037" s="15" t="str">
-        <f t="shared" ref="D1037:D1038" si="19">IF(
+        <f t="shared" ref="D1037:D1039" si="19">IF(
  AND(
   B1037 &gt;= IF(
          YEAR(B1037)&gt;=2007,
@@ -52846,7 +52858,7 @@
         <v>48.61</v>
       </c>
     </row>
-    <row r="1038" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1038" spans="1:11">
       <c r="A1038" s="15">
         <v>46148</v>
       </c>
@@ -52880,6 +52892,42 @@
       </c>
       <c r="K1038" s="7">
         <v>43.28</v>
+      </c>
+    </row>
+    <row r="1039" spans="1:11">
+      <c r="A1039" s="15">
+        <v>46155</v>
+      </c>
+      <c r="B1039" s="15">
+        <v>46156</v>
+      </c>
+      <c r="C1039" s="17">
+        <v>0.41666666666670998</v>
+      </c>
+      <c r="D1039" s="15" t="str">
+        <f t="shared" si="19"/>
+        <v>UTC-4</v>
+      </c>
+      <c r="E1039" s="7">
+        <v>77.34</v>
+      </c>
+      <c r="F1039" s="8">
+        <v>-200</v>
+      </c>
+      <c r="G1039" s="7">
+        <v>78.75</v>
+      </c>
+      <c r="H1039" s="9">
+        <v>99</v>
+      </c>
+      <c r="I1039" s="9">
+        <v>100</v>
+      </c>
+      <c r="J1039" s="9">
+        <v>200</v>
+      </c>
+      <c r="K1039" s="7">
+        <v>68.17</v>
       </c>
     </row>
   </sheetData>
@@ -52892,7 +52940,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{115169E1-C49D-409D-8D5D-92B2FD26EE0D}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData/>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -52903,9 +52951,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44703C2A-D4C6-BD4F-B5E9-874C8C9CFE9E}">
   <dimension ref="B2:C3"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.4"/>
   <sheetData>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:3">
       <c r="B2" t="s">
         <v>7</v>
       </c>
@@ -52913,7 +52961,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:3">
       <c r="B3" t="s">
         <v>8</v>
       </c>

--- a/data/sentiment/NAAIM Exposure Index.xlsx
+++ b/data/sentiment/NAAIM Exposure Index.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\sentiment\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\sentiment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5A41448-21E9-47DC-9546-E8FA93381990}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC1BE83C-9FC4-4EF5-ACF9-268FB060E6E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NAAIM" sheetId="1" r:id="rId1"/>
@@ -650,50 +650,50 @@
     </xf>
   </cellXfs>
   <cellStyles count="44">
-    <cellStyle name="20% - 강조색1" xfId="19" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20% - 강조색2" xfId="23" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20% - 강조색3" xfId="27" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20% - 강조색4" xfId="31" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20% - 강조색5" xfId="35" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20% - 강조색6" xfId="39" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="40% - 강조색1" xfId="20" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40% - 강조색2" xfId="24" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40% - 강조색3" xfId="28" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40% - 강조색4" xfId="32" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40% - 강조색5" xfId="36" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40% - 강조색6" xfId="40" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="60% - 강조색1" xfId="21" builtinId="32" customBuiltin="1"/>
-    <cellStyle name="60% - 강조색2" xfId="25" builtinId="36" customBuiltin="1"/>
-    <cellStyle name="60% - 강조색3" xfId="29" builtinId="40" customBuiltin="1"/>
-    <cellStyle name="60% - 강조색4" xfId="33" builtinId="44" customBuiltin="1"/>
-    <cellStyle name="60% - 강조색5" xfId="37" builtinId="48" customBuiltin="1"/>
-    <cellStyle name="60% - 강조색6" xfId="41" builtinId="52" customBuiltin="1"/>
-    <cellStyle name="강조색1" xfId="18" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="강조색2" xfId="22" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="강조색3" xfId="26" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="강조색4" xfId="30" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="강조색5" xfId="34" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="강조색6" xfId="38" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="경고문" xfId="14" builtinId="11" customBuiltin="1"/>
-    <cellStyle name="계산" xfId="11" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="나쁨" xfId="7" builtinId="27" customBuiltin="1"/>
-    <cellStyle name="메모" xfId="15" builtinId="10" customBuiltin="1"/>
-    <cellStyle name="보통" xfId="8" builtinId="28" customBuiltin="1"/>
-    <cellStyle name="설명 텍스트" xfId="16" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="셀 확인" xfId="13" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="쉼표" xfId="42" builtinId="3"/>
-    <cellStyle name="연결된 셀" xfId="12" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="요약" xfId="17" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="입력" xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="제목" xfId="1" builtinId="15" customBuiltin="1"/>
-    <cellStyle name="제목 1" xfId="2" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="제목 2" xfId="3" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="제목 3" xfId="4" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="제목 4" xfId="5" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="좋음" xfId="6" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="출력" xfId="10" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="하이퍼링크" xfId="43" builtinId="8"/>
+    <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - Accent4" xfId="31" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - Accent5" xfId="35" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - Accent6" xfId="39" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - Accent1" xfId="20" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - Accent2" xfId="24" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - Accent3" xfId="28" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - Accent4" xfId="32" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - Accent5" xfId="36" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - Accent6" xfId="40" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - Accent1" xfId="21" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - Accent2" xfId="25" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - Accent3" xfId="29" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - Accent4" xfId="33" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - Accent5" xfId="37" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - Accent6" xfId="41" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="Accent1" xfId="18" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="Accent2" xfId="22" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="Accent3" xfId="26" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Comma" xfId="42" builtinId="3"/>
+    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Hyperlink" xfId="43" builtinId="8"/>
+    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -711,7 +711,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -735,10 +735,14 @@
             <c:v>NAAIM Index</c:v>
           </c:tx>
           <c:spPr>
-            <a:ln w="25400" cap="rnd">
+            <a:ln w="19050" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent1"/>
+                <a:schemeClr val="accent5">
+                  <a:lumMod val="60000"/>
+                  <a:lumOff val="40000"/>
+                </a:schemeClr>
               </a:solidFill>
+              <a:prstDash val="sysDot"/>
               <a:round/>
             </a:ln>
             <a:effectLst/>
@@ -746,6 +750,21 @@
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="25400" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="movingAvg"/>
+            <c:period val="12"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
           <c:cat>
             <c:numRef>
               <c:f>NAAIM!$B$2:$B$11030</c:f>
@@ -3868,6 +3887,9 @@
                 </c:pt>
                 <c:pt idx="1038">
                   <c:v>46163</c:v>
+                </c:pt>
+                <c:pt idx="1039">
+                  <c:v>46170</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6994,6 +7016,9 @@
                 </c:pt>
                 <c:pt idx="1038">
                   <c:v>82.02</c:v>
+                </c:pt>
+                <c:pt idx="1039">
+                  <c:v>98.39</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7210,7 +7235,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -7242,10 +7267,14 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="25400" cap="rnd">
+            <a:ln w="19050" cap="rnd">
               <a:solidFill>
-                <a:srgbClr val="C00000"/>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="60000"/>
+                  <a:lumOff val="40000"/>
+                </a:schemeClr>
               </a:solidFill>
+              <a:prstDash val="sysDot"/>
               <a:round/>
             </a:ln>
             <a:effectLst/>
@@ -7253,6 +7282,21 @@
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="25400" cap="rnd">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="movingAvg"/>
+            <c:period val="12"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
           <c:cat>
             <c:numRef>
               <c:f>NAAIM!$B$2:$B$11031</c:f>
@@ -10375,6 +10419,9 @@
                 </c:pt>
                 <c:pt idx="1038">
                   <c:v>46163</c:v>
+                </c:pt>
+                <c:pt idx="1039">
+                  <c:v>46170</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13501,6 +13548,9 @@
                 </c:pt>
                 <c:pt idx="1038">
                   <c:v>55.01</c:v>
+                </c:pt>
+                <c:pt idx="1039">
+                  <c:v>47.62</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14911,9 +14961,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -14951,7 +15001,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -15057,7 +15107,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -15199,7 +15249,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -15207,21 +15257,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K1040"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="12.6"/>
+  <dimension ref="A1:K1041"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.6640625" style="15" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.44140625" style="15" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.33203125" style="17" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.44140625" style="15" customWidth="1"/>
-    <col min="5" max="5" width="11.109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.6328125" style="15" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.453125" style="15" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.36328125" style="17" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.453125" style="15" customWidth="1"/>
+    <col min="5" max="5" width="11.08984375" style="7" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14" style="8" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.44140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.21875" style="9" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.44140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.453125" style="7" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.1796875" style="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.453125" style="9" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="15" style="9" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="21.6640625" style="7" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="8.88671875" style="10"/>
+    <col min="11" max="11" width="21.6328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.90625" style="10"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="6" customFormat="1">
@@ -52953,7 +53003,7 @@
         <v>0.41666666666671598</v>
       </c>
       <c r="D1040" s="15" t="str">
-        <f t="shared" ref="D1040" si="20">IF(
+        <f t="shared" ref="D1040:D1041" si="20">IF(
  AND(
   B1040 &gt;= IF(
          YEAR(B1040)&gt;=2007,
@@ -52993,6 +53043,42 @@
         <v>55.01</v>
       </c>
     </row>
+    <row r="1041" spans="1:11">
+      <c r="A1041" s="15">
+        <v>46169</v>
+      </c>
+      <c r="B1041" s="15">
+        <v>46170</v>
+      </c>
+      <c r="C1041" s="17">
+        <v>0.41666666666672197</v>
+      </c>
+      <c r="D1041" s="15" t="str">
+        <f t="shared" si="20"/>
+        <v>UTC-4</v>
+      </c>
+      <c r="E1041" s="7">
+        <v>98.39</v>
+      </c>
+      <c r="F1041" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1041" s="7">
+        <v>87.5</v>
+      </c>
+      <c r="H1041" s="9">
+        <v>100</v>
+      </c>
+      <c r="I1041" s="9">
+        <v>100</v>
+      </c>
+      <c r="J1041" s="9">
+        <v>200</v>
+      </c>
+      <c r="K1041" s="7">
+        <v>47.62</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -53003,7 +53089,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{115169E1-C49D-409D-8D5D-92B2FD26EE0D}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData/>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -53014,7 +53100,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44703C2A-D4C6-BD4F-B5E9-874C8C9CFE9E}">
   <dimension ref="B2:C3"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="2" spans="2:3">
       <c r="B2" t="s">
